--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_145421C56AF441D8E013A430062350172584A27E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{447EC397-FC1B-4443-8105-855B7100C4DB}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="11_145421C56AF441D8E013A430062350172584A27E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C19F9C85-7C23-467B-9C0F-87829441185A}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="851" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="851" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1303,10 +1303,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1766,7 +1762,7 @@
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>'Playoff Wild Card'!B14</f>
-        <v>Daddy Michael</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="B6">
         <f>'Playoff Wild Card'!C14</f>
@@ -1968,7 +1964,7 @@
       </c>
       <c r="B13" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>Daddy Michael</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="C13">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
@@ -2117,7 +2113,7 @@
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>A6</f>
-        <v>Daddy Michael</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="B22" s="3">
         <v>0</v>
@@ -2330,7 +2326,7 @@
       </c>
       <c r="C2">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H6,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G6,0)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D2">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H21,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G21,0)</f>
@@ -2354,7 +2350,7 @@
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I13" si="0">SUM(C2:H2)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J2">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F6="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F21="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F36="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F51="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F66="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F81="W"),1,0)</f>
@@ -2362,7 +2358,7 @@
       </c>
       <c r="K2">
         <f>I2+0.0001</f>
-        <v>1.0001</v>
+        <v>5.0000999999999998</v>
       </c>
       <c r="L2">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H6,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G6,0)</f>
@@ -2442,11 +2438,11 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE13" si="2">I2+R2+AC2</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF2">
         <f>AE2+0.0001</f>
-        <v>1.0001</v>
+        <v>5.0000999999999998</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2459,7 +2455,7 @@
       </c>
       <c r="C3">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H7,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G7,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H22,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G22,0)</f>
@@ -2483,7 +2479,7 @@
       </c>
       <c r="I3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J3">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F7="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F22="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F37="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F52="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F67="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F82="W"),1,0)</f>
@@ -2491,7 +2487,7 @@
       </c>
       <c r="K3">
         <f>I3+0.0002</f>
-        <v>2.0000000000000001E-4</v>
+        <v>6.0002000000000004</v>
       </c>
       <c r="L3">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H7,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G7,0)</f>
@@ -2571,11 +2567,11 @@
       </c>
       <c r="AE3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF3">
         <f>AE3+0.0002</f>
-        <v>2.0000000000000001E-4</v>
+        <v>6.0002000000000004</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2588,7 +2584,7 @@
       </c>
       <c r="C4">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H8,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G8,0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D4">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H23,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G23,0)</f>
@@ -2612,7 +2608,7 @@
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F8="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F23="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F38="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F53="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F68="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F83="W"),1,0)</f>
@@ -2620,7 +2616,7 @@
       </c>
       <c r="K4">
         <f>I4+0.0003</f>
-        <v>2.9999999999999997E-4</v>
+        <v>8.0002999999999993</v>
       </c>
       <c r="L4">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H8,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G8,0)</f>
@@ -2700,11 +2696,11 @@
       </c>
       <c r="AE4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AF4">
         <f>AE4+0.0003</f>
-        <v>2.9999999999999997E-4</v>
+        <v>8.0002999999999993</v>
       </c>
     </row>
     <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2717,7 +2713,7 @@
       </c>
       <c r="C5">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H9,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G9,0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H24,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G24,0)</f>
@@ -2741,7 +2737,7 @@
       </c>
       <c r="I5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F9="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F24="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F39="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F54="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F69="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F84="W"),1,0)</f>
@@ -2749,7 +2745,7 @@
       </c>
       <c r="K5">
         <f>I5+0.0004</f>
-        <v>4.0000000000000002E-4</v>
+        <v>5.0004</v>
       </c>
       <c r="L5">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H9,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G9,0)</f>
@@ -2829,11 +2825,11 @@
       </c>
       <c r="AE5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF5">
         <f>AE5+0.0004</f>
-        <v>4.0000000000000002E-4</v>
+        <v>5.0004</v>
       </c>
     </row>
     <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2846,7 +2842,7 @@
       </c>
       <c r="C6">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H10,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G10,0)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H25,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G25,0)</f>
@@ -2870,7 +2866,7 @@
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F10="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F25="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F40="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F55="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F70="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F85="W"),1,0)</f>
@@ -2878,7 +2874,7 @@
       </c>
       <c r="K6">
         <f>I6+0.0005</f>
-        <v>2.0005000000000002</v>
+        <v>10.000500000000001</v>
       </c>
       <c r="L6">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H10,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G10,0)</f>
@@ -2958,11 +2954,11 @@
       </c>
       <c r="AE6">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AF6">
         <f>AE6+0.0005</f>
-        <v>2.0005000000000002</v>
+        <v>10.000500000000001</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2975,7 +2971,7 @@
       </c>
       <c r="C7">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H11,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G11,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H26,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G26,0)</f>
@@ -2999,7 +2995,7 @@
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F11="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F26="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F41="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F56="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F71="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F86="W"),1,0)</f>
@@ -3007,7 +3003,7 @@
       </c>
       <c r="K7">
         <f>I7+0.0006</f>
-        <v>5.9999999999999995E-4</v>
+        <v>6.0006000000000004</v>
       </c>
       <c r="L7">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H11,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G11,0)</f>
@@ -3087,11 +3083,11 @@
       </c>
       <c r="AE7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF7">
         <f>AE7+0.0006</f>
-        <v>5.9999999999999995E-4</v>
+        <v>6.0006000000000004</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3104,7 +3100,7 @@
       </c>
       <c r="C8">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H12,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G12,0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H27,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G27,0)</f>
@@ -3128,7 +3124,7 @@
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J8">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F12="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F27="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F42="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F57="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F72="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F87="W"),1,0)</f>
@@ -3136,7 +3132,7 @@
       </c>
       <c r="K8">
         <f>I8+0.0007</f>
-        <v>6.9999999999999999E-4</v>
+        <v>7.0007000000000001</v>
       </c>
       <c r="L8">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H12,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G12,0)</f>
@@ -3216,11 +3212,11 @@
       </c>
       <c r="AE8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF8">
         <f>AE8+0.0007</f>
-        <v>6.9999999999999999E-4</v>
+        <v>7.0007000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3233,7 +3229,7 @@
       </c>
       <c r="C9">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H13,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G13,0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H28,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G28,0)</f>
@@ -3257,7 +3253,7 @@
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F13="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F28="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F43="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F58="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F73="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F88="W"),1,0)</f>
@@ -3265,7 +3261,7 @@
       </c>
       <c r="K9">
         <f>I9+0.0008</f>
-        <v>8.0000000000000004E-4</v>
+        <v>8.0007999999999999</v>
       </c>
       <c r="L9">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H13,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G13,0)</f>
@@ -3345,11 +3341,11 @@
       </c>
       <c r="AE9">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AF9">
         <f>AE9+0.0008</f>
-        <v>8.0000000000000004E-4</v>
+        <v>8.0007999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3362,7 +3358,7 @@
       </c>
       <c r="C10">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H14,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G14,0)</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D10">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H29,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G29,0)</f>
@@ -3386,7 +3382,7 @@
       </c>
       <c r="I10">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F14="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F29="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F44="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F59="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F74="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F89="W"),1,0)</f>
@@ -3394,7 +3390,7 @@
       </c>
       <c r="K10">
         <f>I10+0.0009</f>
-        <v>2.0009000000000001</v>
+        <v>8.0008999999999997</v>
       </c>
       <c r="L10">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H14,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G14,0)</f>
@@ -3474,11 +3470,11 @@
       </c>
       <c r="AE10">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AF10">
         <f>AE10+0.0009</f>
-        <v>2.0009000000000001</v>
+        <v>8.0008999999999997</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3491,7 +3487,7 @@
       </c>
       <c r="C11">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H15,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G15,0)</f>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D11">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H30,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G30,0)</f>
@@ -3515,7 +3511,7 @@
       </c>
       <c r="I11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J11">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F15="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F30="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F45="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F60="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F75="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F90="W"),1,0)</f>
@@ -3523,7 +3519,7 @@
       </c>
       <c r="K11">
         <f>I11+0.001</f>
-        <v>1.0009999999999999</v>
+        <v>11.000999999999999</v>
       </c>
       <c r="L11">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H15,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G15,0)</f>
@@ -3603,11 +3599,11 @@
       </c>
       <c r="AE11">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AF11">
         <f>AE11+0.001</f>
-        <v>1.0009999999999999</v>
+        <v>11.000999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3620,7 +3616,7 @@
       </c>
       <c r="C12">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H16,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G16,0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D12">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H31,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G31,0)</f>
@@ -3644,7 +3640,7 @@
       </c>
       <c r="I12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J12">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F16="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F31="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F46="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F61="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F76="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F91="W"),1,0)</f>
@@ -3652,7 +3648,7 @@
       </c>
       <c r="K12">
         <f>I12+0.0011</f>
-        <v>1.1000000000000001E-3</v>
+        <v>10.001099999999999</v>
       </c>
       <c r="L12">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H16,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G16,0)</f>
@@ -3732,11 +3728,11 @@
       </c>
       <c r="AE12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF12">
         <f>AE12+0.0011</f>
-        <v>1.1000000000000001E-3</v>
+        <v>10.001099999999999</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3749,7 +3745,7 @@
       </c>
       <c r="C13">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H17,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G17,0)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D13">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H32,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G32,0)</f>
@@ -3773,7 +3769,7 @@
       </c>
       <c r="I13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F17="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F32="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F47="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F62="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F77="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F92="W"),1,0)</f>
@@ -3781,7 +3777,7 @@
       </c>
       <c r="K13">
         <f>I13+0.0012</f>
-        <v>1.0012000000000001</v>
+        <v>8.0012000000000008</v>
       </c>
       <c r="L13">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H17,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G17,0)</f>
@@ -3861,11 +3857,11 @@
       </c>
       <c r="AE13">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AF13">
         <f>AE13+0.0012</f>
-        <v>1.0012000000000001</v>
+        <v>8.0012000000000008</v>
       </c>
     </row>
   </sheetData>
@@ -6879,16 +6875,25 @@
       <c r="D5" t="s">
         <v>71</v>
       </c>
+      <c r="E5">
+        <v>59</v>
+      </c>
       <c r="F5" t="s">
         <v>72</v>
       </c>
+      <c r="G5">
+        <v>37</v>
+      </c>
+      <c r="H5">
+        <v>-2.5</v>
+      </c>
       <c r="I5" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>CHI</v>
       </c>
       <c r="J5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>CHI</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6904,16 +6909,25 @@
       <c r="D6" t="s">
         <v>73</v>
       </c>
+      <c r="E6">
+        <v>27</v>
+      </c>
       <c r="F6" t="s">
         <v>74</v>
       </c>
+      <c r="G6">
+        <v>33</v>
+      </c>
+      <c r="H6">
+        <v>3.5</v>
+      </c>
       <c r="I6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>CIN</v>
       </c>
       <c r="J6" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>CIN</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6929,16 +6943,25 @@
       <c r="D7" t="s">
         <v>75</v>
       </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
       <c r="F7" t="s">
         <v>76</v>
       </c>
+      <c r="G7">
+        <v>31</v>
+      </c>
+      <c r="H7">
+        <v>7.5</v>
+      </c>
       <c r="I7" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>DET</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>NO</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6954,16 +6977,25 @@
       <c r="D8" t="s">
         <v>77</v>
       </c>
+      <c r="E8">
+        <v>36</v>
+      </c>
       <c r="F8" t="s">
         <v>78</v>
       </c>
+      <c r="G8">
+        <v>31</v>
+      </c>
+      <c r="H8">
+        <v>1.5</v>
+      </c>
       <c r="I8" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>BUF</v>
       </c>
       <c r="J8" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>BUF</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6979,16 +7011,25 @@
       <c r="D9" t="s">
         <v>79</v>
       </c>
+      <c r="E9">
+        <v>41</v>
+      </c>
       <c r="F9" t="s">
         <v>80</v>
       </c>
+      <c r="G9">
+        <v>23</v>
+      </c>
+      <c r="H9">
+        <v>-3.5</v>
+      </c>
       <c r="I9" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>BAL</v>
       </c>
       <c r="J9" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>BAL</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7004,16 +7045,25 @@
       <c r="D10" t="s">
         <v>81</v>
       </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
       <c r="F10" t="s">
         <v>82</v>
       </c>
+      <c r="G10">
+        <v>34</v>
+      </c>
+      <c r="H10">
+        <v>7.5</v>
+      </c>
       <c r="I10" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>JAX</v>
       </c>
       <c r="J10" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>JAX</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7029,16 +7079,25 @@
       <c r="D11" t="s">
         <v>83</v>
       </c>
+      <c r="E11">
+        <v>13</v>
+      </c>
       <c r="F11" t="s">
         <v>84</v>
       </c>
+      <c r="G11">
+        <v>20</v>
+      </c>
+      <c r="H11">
+        <v>3.5</v>
+      </c>
       <c r="I11" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>PIT</v>
       </c>
       <c r="J11" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>PIT</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7054,16 +7113,25 @@
       <c r="D12" t="s">
         <v>85</v>
       </c>
+      <c r="E12">
+        <v>23</v>
+      </c>
       <c r="F12" t="s">
         <v>86</v>
       </c>
+      <c r="G12">
+        <v>10</v>
+      </c>
+      <c r="H12">
+        <v>2.5</v>
+      </c>
       <c r="I12" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>NYJ</v>
       </c>
       <c r="J12" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>NYJ</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7079,16 +7147,25 @@
       <c r="D13" t="s">
         <v>88</v>
       </c>
+      <c r="E13">
+        <v>26</v>
+      </c>
       <c r="F13" t="s">
         <v>89</v>
       </c>
+      <c r="G13">
+        <v>14</v>
+      </c>
+      <c r="H13">
+        <v>10.5</v>
+      </c>
       <c r="I13" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>ARI</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>ARI</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7104,16 +7181,25 @@
       <c r="D14" t="s">
         <v>90</v>
       </c>
+      <c r="E14">
+        <v>13</v>
+      </c>
       <c r="F14" t="s">
         <v>91</v>
       </c>
+      <c r="G14">
+        <v>27</v>
+      </c>
+      <c r="H14">
+        <v>3.5</v>
+      </c>
       <c r="I14" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>LV</v>
       </c>
       <c r="J14" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>LV</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7129,16 +7215,25 @@
       <c r="D15" t="s">
         <v>92</v>
       </c>
+      <c r="E15">
+        <v>22</v>
+      </c>
       <c r="F15" t="s">
         <v>93</v>
       </c>
+      <c r="G15">
+        <v>39</v>
+      </c>
+      <c r="H15">
+        <v>1.5</v>
+      </c>
       <c r="I15" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>MIN</v>
       </c>
       <c r="J15" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>MIN</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7154,16 +7249,25 @@
       <c r="D16" t="s">
         <v>94</v>
       </c>
+      <c r="E16">
+        <v>22</v>
+      </c>
       <c r="F16" t="s">
         <v>95</v>
       </c>
+      <c r="G16">
+        <v>24</v>
+      </c>
+      <c r="H16">
+        <v>4.5</v>
+      </c>
       <c r="I16" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>PHI</v>
       </c>
       <c r="J16" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>WAS</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7179,16 +7283,25 @@
       <c r="D17" t="s">
         <v>96</v>
       </c>
+      <c r="E17">
+        <v>20</v>
+      </c>
       <c r="F17" t="s">
         <v>97</v>
       </c>
+      <c r="G17">
+        <v>28</v>
+      </c>
+      <c r="H17">
+        <v>-2.5</v>
+      </c>
       <c r="I17" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>NYG</v>
       </c>
       <c r="J17" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>NYG</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14679,14 +14792,14 @@
         <v>Evan Loeser</v>
       </c>
       <c r="C6" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>5</v>
       </c>
       <c r="E6">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(5,A$6:A$17,0)),0)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F6" t="str">
         <f t="shared" ref="F6:F17" si="0">IF(C6=0,"-",IF(C6&gt;E6,"W",IF(C6&lt;E6,"L","T")))</f>
@@ -14698,11 +14811,11 @@
       </c>
       <c r="H6">
         <f t="shared" ref="H6:H17" si="2">IF(C6="",0,C6)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <f t="shared" ref="I6:I17" si="3">G6+H6</f>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14713,29 +14826,31 @@
         <f>Roster!B4</f>
         <v>Chris Simmons</v>
       </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="3">
+        <v>6</v>
+      </c>
       <c r="D7">
         <v>6</v>
       </c>
       <c r="E7">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(6,A$6:A$17,0)),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F7" t="str">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>T</v>
       </c>
       <c r="G7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14746,29 +14861,31 @@
         <f>Roster!B5</f>
         <v>Jack Smith</v>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="3">
+        <v>8</v>
+      </c>
       <c r="D8">
         <v>9</v>
       </c>
       <c r="E8">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(9,A$6:A$17,0)),0)</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F8" t="str">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>T</v>
       </c>
       <c r="G8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14779,17 +14896,19 @@
         <f>Roster!B6</f>
         <v>Luke Ussery</v>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="3">
+        <v>5</v>
+      </c>
       <c r="D9">
         <v>10</v>
       </c>
       <c r="E9">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(10,A$6:A$17,0)),0)</f>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F9" t="str">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G9">
         <f t="shared" si="1"/>
@@ -14797,11 +14916,11 @@
       </c>
       <c r="H9">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14813,14 +14932,14 @@
         <v>Mikayla Simmons</v>
       </c>
       <c r="C10" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(1,A$6:A$17,0)),0)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F10" t="str">
         <f t="shared" si="0"/>
@@ -14832,11 +14951,11 @@
       </c>
       <c r="H10">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I10">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14847,29 +14966,31 @@
         <f>Roster!B8</f>
         <v>Alan Loeser</v>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="3">
+        <v>6</v>
+      </c>
       <c r="D11">
         <v>2</v>
       </c>
       <c r="E11">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(2,A$6:A$17,0)),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F11" t="str">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>T</v>
       </c>
       <c r="G11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14880,17 +15001,19 @@
         <f>Roster!B9</f>
         <v>Caleb Simmons</v>
       </c>
-      <c r="C12" s="3"/>
+      <c r="C12" s="3">
+        <v>7</v>
+      </c>
       <c r="D12">
         <v>11</v>
       </c>
       <c r="E12">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(11,A$6:A$17,0)),0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F12" t="str">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G12">
         <f t="shared" si="1"/>
@@ -14898,11 +15021,11 @@
       </c>
       <c r="H12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14913,29 +15036,31 @@
         <f>Roster!B10</f>
         <v>Larry Loeser</v>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="3">
+        <v>8</v>
+      </c>
       <c r="D13">
         <v>12</v>
       </c>
       <c r="E13">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(12,A$6:A$17,0)),0)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>T</v>
       </c>
       <c r="G13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14947,30 +15072,30 @@
         <v>Daddy Michael</v>
       </c>
       <c r="C14" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
       <c r="E14">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(3,A$6:A$17,0)),0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F14" t="str">
         <f t="shared" si="0"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="G14">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H14">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I14">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14982,14 +15107,14 @@
         <v>Zach Zarra</v>
       </c>
       <c r="C15" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D15">
         <v>4</v>
       </c>
       <c r="E15">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(4,A$6:A$17,0)),0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F15" t="str">
         <f t="shared" si="0"/>
@@ -15001,11 +15126,11 @@
       </c>
       <c r="H15">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I15">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15016,29 +15141,31 @@
         <f>Roster!B13</f>
         <v>Jeffrey Loeser</v>
       </c>
-      <c r="C16" s="3"/>
+      <c r="C16" s="3">
+        <v>10</v>
+      </c>
       <c r="D16">
         <v>7</v>
       </c>
       <c r="E16">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(7,A$6:A$17,0)),0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F16" t="str">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I16">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15050,30 +15177,30 @@
         <v>Jake Andrews</v>
       </c>
       <c r="C17" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D17">
         <v>8</v>
       </c>
       <c r="E17">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(8,A$6:A$17,0)),0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F17" t="str">
         <f t="shared" si="0"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="G17">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H17">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I17">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22539,7 +22666,7 @@
       </c>
       <c r="C3">
         <f>Helper!C2</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3">
         <f>Helper!D2</f>
@@ -22563,7 +22690,7 @@
       </c>
       <c r="I3">
         <f>Helper!I2</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J3">
         <f>Helper!J2</f>
@@ -22571,7 +22698,7 @@
       </c>
       <c r="K3">
         <f>MAX(Helper!C2:H2)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22584,7 +22711,7 @@
       </c>
       <c r="C4">
         <f>Helper!C3</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <f>Helper!D3</f>
@@ -22608,7 +22735,7 @@
       </c>
       <c r="I4">
         <f>Helper!I3</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <f>Helper!J3</f>
@@ -22616,7 +22743,7 @@
       </c>
       <c r="K4">
         <f>MAX(Helper!C3:H3)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22629,7 +22756,7 @@
       </c>
       <c r="C5">
         <f>Helper!C4</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <f>Helper!D4</f>
@@ -22653,7 +22780,7 @@
       </c>
       <c r="I5">
         <f>Helper!I4</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <f>Helper!J4</f>
@@ -22661,7 +22788,7 @@
       </c>
       <c r="K5">
         <f>MAX(Helper!C4:H4)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22674,7 +22801,7 @@
       </c>
       <c r="C6">
         <f>Helper!C5</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <f>Helper!D5</f>
@@ -22698,7 +22825,7 @@
       </c>
       <c r="I6">
         <f>Helper!I5</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <f>Helper!J5</f>
@@ -22706,7 +22833,7 @@
       </c>
       <c r="K6">
         <f>MAX(Helper!C5:H5)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22719,7 +22846,7 @@
       </c>
       <c r="C7">
         <f>Helper!C6</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D7">
         <f>Helper!D6</f>
@@ -22743,7 +22870,7 @@
       </c>
       <c r="I7">
         <f>Helper!I6</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <f>Helper!J6</f>
@@ -22751,7 +22878,7 @@
       </c>
       <c r="K7">
         <f>MAX(Helper!C6:H6)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22764,7 +22891,7 @@
       </c>
       <c r="C8">
         <f>Helper!C7</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D8">
         <f>Helper!D7</f>
@@ -22788,7 +22915,7 @@
       </c>
       <c r="I8">
         <f>Helper!I7</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J8">
         <f>Helper!J7</f>
@@ -22796,7 +22923,7 @@
       </c>
       <c r="K8">
         <f>MAX(Helper!C7:H7)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22809,7 +22936,7 @@
       </c>
       <c r="C9">
         <f>Helper!C8</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D9">
         <f>Helper!D8</f>
@@ -22833,7 +22960,7 @@
       </c>
       <c r="I9">
         <f>Helper!I8</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J9">
         <f>Helper!J8</f>
@@ -22841,7 +22968,7 @@
       </c>
       <c r="K9">
         <f>MAX(Helper!C8:H8)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22854,7 +22981,7 @@
       </c>
       <c r="C10">
         <f>Helper!C9</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D10">
         <f>Helper!D9</f>
@@ -22878,7 +23005,7 @@
       </c>
       <c r="I10">
         <f>Helper!I9</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <f>Helper!J9</f>
@@ -22886,7 +23013,7 @@
       </c>
       <c r="K10">
         <f>MAX(Helper!C9:H9)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22899,7 +23026,7 @@
       </c>
       <c r="C11">
         <f>Helper!C10</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <f>Helper!D10</f>
@@ -22923,7 +23050,7 @@
       </c>
       <c r="I11">
         <f>Helper!I10</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <f>Helper!J10</f>
@@ -22931,7 +23058,7 @@
       </c>
       <c r="K11">
         <f>MAX(Helper!C10:H10)</f>
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22944,7 +23071,7 @@
       </c>
       <c r="C12">
         <f>Helper!C11</f>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D12">
         <f>Helper!D11</f>
@@ -22968,7 +23095,7 @@
       </c>
       <c r="I12">
         <f>Helper!I11</f>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J12">
         <f>Helper!J11</f>
@@ -22976,7 +23103,7 @@
       </c>
       <c r="K12">
         <f>MAX(Helper!C11:H11)</f>
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22989,7 +23116,7 @@
       </c>
       <c r="C13">
         <f>Helper!C12</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D13">
         <f>Helper!D12</f>
@@ -23013,7 +23140,7 @@
       </c>
       <c r="I13">
         <f>Helper!I12</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J13">
         <f>Helper!J12</f>
@@ -23021,7 +23148,7 @@
       </c>
       <c r="K13">
         <f>MAX(Helper!C12:H12)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23034,7 +23161,7 @@
       </c>
       <c r="C14">
         <f>Helper!C13</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <f>Helper!D13</f>
@@ -23058,7 +23185,7 @@
       </c>
       <c r="I14">
         <f>Helper!I13</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <f>Helper!J13</f>
@@ -23066,7 +23193,7 @@
       </c>
       <c r="K14">
         <f>MAX(Helper!C13:H13)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -24382,7 +24509,7 @@
       </c>
       <c r="C57">
         <f>Helper!I2</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D57">
         <f>Helper!R2</f>
@@ -24394,11 +24521,11 @@
       </c>
       <c r="F57">
         <f>Helper!AE2</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G57">
         <f>Helper!K2</f>
-        <v>1.0001</v>
+        <v>5.0000999999999998</v>
       </c>
       <c r="H57">
         <f>Helper!T2</f>
@@ -24415,7 +24542,7 @@
       </c>
       <c r="C58">
         <f>Helper!I3</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D58">
         <f>Helper!R3</f>
@@ -24427,11 +24554,11 @@
       </c>
       <c r="F58">
         <f>Helper!AE3</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G58">
         <f>Helper!K3</f>
-        <v>2.0000000000000001E-4</v>
+        <v>6.0002000000000004</v>
       </c>
       <c r="H58">
         <f>Helper!T3</f>
@@ -24448,7 +24575,7 @@
       </c>
       <c r="C59">
         <f>Helper!I4</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D59">
         <f>Helper!R4</f>
@@ -24460,11 +24587,11 @@
       </c>
       <c r="F59">
         <f>Helper!AE4</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G59">
         <f>Helper!K4</f>
-        <v>2.9999999999999997E-4</v>
+        <v>8.0002999999999993</v>
       </c>
       <c r="H59">
         <f>Helper!T4</f>
@@ -24481,7 +24608,7 @@
       </c>
       <c r="C60">
         <f>Helper!I5</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D60">
         <f>Helper!R5</f>
@@ -24493,11 +24620,11 @@
       </c>
       <c r="F60">
         <f>Helper!AE5</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G60">
         <f>Helper!K5</f>
-        <v>4.0000000000000002E-4</v>
+        <v>5.0004</v>
       </c>
       <c r="H60">
         <f>Helper!T5</f>
@@ -24514,7 +24641,7 @@
       </c>
       <c r="C61">
         <f>Helper!I6</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D61">
         <f>Helper!R6</f>
@@ -24526,11 +24653,11 @@
       </c>
       <c r="F61">
         <f>Helper!AE6</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G61">
         <f>Helper!K6</f>
-        <v>2.0005000000000002</v>
+        <v>10.000500000000001</v>
       </c>
       <c r="H61">
         <f>Helper!T6</f>
@@ -24547,7 +24674,7 @@
       </c>
       <c r="C62">
         <f>Helper!I7</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D62">
         <f>Helper!R7</f>
@@ -24559,11 +24686,11 @@
       </c>
       <c r="F62">
         <f>Helper!AE7</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G62">
         <f>Helper!K7</f>
-        <v>5.9999999999999995E-4</v>
+        <v>6.0006000000000004</v>
       </c>
       <c r="H62">
         <f>Helper!T7</f>
@@ -24580,7 +24707,7 @@
       </c>
       <c r="C63">
         <f>Helper!I8</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D63">
         <f>Helper!R8</f>
@@ -24592,11 +24719,11 @@
       </c>
       <c r="F63">
         <f>Helper!AE8</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G63">
         <f>Helper!K8</f>
-        <v>6.9999999999999999E-4</v>
+        <v>7.0007000000000001</v>
       </c>
       <c r="H63">
         <f>Helper!T8</f>
@@ -24613,7 +24740,7 @@
       </c>
       <c r="C64">
         <f>Helper!I9</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D64">
         <f>Helper!R9</f>
@@ -24625,11 +24752,11 @@
       </c>
       <c r="F64">
         <f>Helper!AE9</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G64">
         <f>Helper!K9</f>
-        <v>8.0000000000000004E-4</v>
+        <v>8.0007999999999999</v>
       </c>
       <c r="H64">
         <f>Helper!T9</f>
@@ -24646,7 +24773,7 @@
       </c>
       <c r="C65">
         <f>Helper!I10</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D65">
         <f>Helper!R10</f>
@@ -24658,11 +24785,11 @@
       </c>
       <c r="F65">
         <f>Helper!AE10</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G65">
         <f>Helper!K10</f>
-        <v>2.0009000000000001</v>
+        <v>8.0008999999999997</v>
       </c>
       <c r="H65">
         <f>Helper!T10</f>
@@ -24679,7 +24806,7 @@
       </c>
       <c r="C66">
         <f>Helper!I11</f>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D66">
         <f>Helper!R11</f>
@@ -24691,11 +24818,11 @@
       </c>
       <c r="F66">
         <f>Helper!AE11</f>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G66">
         <f>Helper!K11</f>
-        <v>1.0009999999999999</v>
+        <v>11.000999999999999</v>
       </c>
       <c r="H66">
         <f>Helper!T11</f>
@@ -24712,7 +24839,7 @@
       </c>
       <c r="C67">
         <f>Helper!I12</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D67">
         <f>Helper!R12</f>
@@ -24724,11 +24851,11 @@
       </c>
       <c r="F67">
         <f>Helper!AE12</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G67">
         <f>Helper!K12</f>
-        <v>1.1000000000000001E-3</v>
+        <v>10.001099999999999</v>
       </c>
       <c r="H67">
         <f>Helper!T12</f>
@@ -24745,7 +24872,7 @@
       </c>
       <c r="C68">
         <f>Helper!I13</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D68">
         <f>Helper!R13</f>
@@ -24757,11 +24884,11 @@
       </c>
       <c r="F68">
         <f>Helper!AE13</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G68">
         <f>Helper!K13</f>
-        <v>1.0012000000000001</v>
+        <v>8.0012000000000008</v>
       </c>
       <c r="H68">
         <f>Helper!T13</f>
@@ -24831,7 +24958,7 @@
       </c>
       <c r="B5" t="str">
         <f>INDEX(Helper!B$2:B$13,MATCH(MAX(Helper!K$2:K$13),Helper!K$2:K$13,0))</f>
-        <v>Daddy Michael</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="C5" t="s">
         <v>247</v>
@@ -24841,7 +24968,7 @@
       </c>
       <c r="E5" t="str">
         <f>B5</f>
-        <v>Daddy Michael</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="F5" t="str">
         <f>IF(B5="","—","QUALIFIED")</f>
@@ -25003,7 +25130,7 @@
       </c>
       <c r="C13">
         <f>INDEX(I$40:I$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D13" t="s">
         <v>258</v>
@@ -25049,7 +25176,7 @@
       </c>
       <c r="B17" t="str">
         <f>E5</f>
-        <v>Daddy Michael</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="C17" t="str">
         <f>D5</f>
@@ -25479,7 +25606,7 @@
       </c>
       <c r="I40">
         <f>Helper!AE2</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J40" t="b">
         <f t="shared" ref="J40:J51" si="1">OR(H40=$E$5,H40=$E$6,H40=$E$7,H40=$E$8,H40=$E$9)</f>
@@ -25487,7 +25614,7 @@
       </c>
       <c r="K40">
         <f>IF(J40,-1,I40+0.00001)</f>
-        <v>1.0000100000000001</v>
+        <v>5.0000099999999996</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25497,7 +25624,7 @@
       </c>
       <c r="I41">
         <f>Helper!AE3</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J41" t="b">
         <f t="shared" si="1"/>
@@ -25505,7 +25632,7 @@
       </c>
       <c r="K41">
         <f>IF(J41,-1,I41+0.00002)</f>
-        <v>2.0000000000000002E-5</v>
+        <v>6.0000200000000001</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25515,7 +25642,7 @@
       </c>
       <c r="I42">
         <f>Helper!AE4</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J42" t="b">
         <f t="shared" si="1"/>
@@ -25523,7 +25650,7 @@
       </c>
       <c r="K42">
         <f>IF(J42,-1,I42+0.00003)</f>
-        <v>3.0000000000000001E-5</v>
+        <v>8.0000300000000006</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25533,7 +25660,7 @@
       </c>
       <c r="I43">
         <f>Helper!AE5</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J43" t="b">
         <f t="shared" si="1"/>
@@ -25551,7 +25678,7 @@
       </c>
       <c r="I44">
         <f>Helper!AE6</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J44" t="b">
         <f t="shared" si="1"/>
@@ -25559,7 +25686,7 @@
       </c>
       <c r="K44">
         <f>IF(J44,-1,I44+0.00005)</f>
-        <v>2.0000499999999999</v>
+        <v>10.00005</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25569,7 +25696,7 @@
       </c>
       <c r="I45">
         <f>Helper!AE7</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J45" t="b">
         <f t="shared" si="1"/>
@@ -25577,7 +25704,7 @@
       </c>
       <c r="K45">
         <f>IF(J45,-1,I45+0.00006)</f>
-        <v>6.0000000000000002E-5</v>
+        <v>6.0000600000000004</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25587,7 +25714,7 @@
       </c>
       <c r="I46">
         <f>Helper!AE8</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J46" t="b">
         <f t="shared" si="1"/>
@@ -25595,7 +25722,7 @@
       </c>
       <c r="K46">
         <f>IF(J46,-1,I46+0.00007)</f>
-        <v>6.9999999999999994E-5</v>
+        <v>7.00007</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25605,7 +25732,7 @@
       </c>
       <c r="I47">
         <f>Helper!AE9</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J47" t="b">
         <f t="shared" si="1"/>
@@ -25623,15 +25750,15 @@
       </c>
       <c r="I48">
         <f>Helper!AE10</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J48" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48">
         <f>IF(J48,-1,I48+0.00009)</f>
-        <v>-1</v>
+        <v>8.0000900000000001</v>
       </c>
     </row>
     <row r="49" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25641,15 +25768,15 @@
       </c>
       <c r="I49">
         <f>Helper!AE11</f>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J49" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49">
         <f>IF(J49,-1,I49+0.0001)</f>
-        <v>1.0001</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="50" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25659,7 +25786,7 @@
       </c>
       <c r="I50">
         <f>Helper!AE12</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J50" t="b">
         <f t="shared" si="1"/>
@@ -25677,7 +25804,7 @@
       </c>
       <c r="I51">
         <f>Helper!AE13</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J51" t="b">
         <f t="shared" si="1"/>
@@ -25744,7 +25871,7 @@
       </c>
       <c r="B5" t="str">
         <f>'Playoff Picture'!B17</f>
-        <v>Daddy Michael</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="C5" s="3">
         <v>6</v>
@@ -25938,7 +26065,7 @@
       </c>
       <c r="B14" t="str">
         <f>INDEX($B$5:$B$10,MATCH(LARGE($H$5:$H$10,1),$H$5:$H$10,0))</f>
-        <v>Daddy Michael</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="C14">
         <f>INDEX($C$5:$C$10,MATCH(LARGE($H$5:$H$10,1),$H$5:$H$10,0))</f>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eloeser\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{035A4E32-DCBE-467C-B207-B5FB4F5D6D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_A98005C6E9195966979F624F4D766EEF87D9B954" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFE59628-DE77-46EF-A1E1-F04585EFE1CC}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="801" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3341" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3399" uniqueCount="346">
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -315,6 +315,9 @@
   </si>
   <si>
     <t>KC</t>
+  </si>
+  <si>
+    <t>MNF Total</t>
   </si>
   <si>
     <t>WEEK 2</t>
@@ -1089,7 +1092,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1167,6 +1170,33 @@
     <font>
       <sz val="10"/>
       <color rgb="FF58A6FF"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFD29922"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF3FB950"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFD29922"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFD29922"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
@@ -1304,7 +1334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1336,11 +1366,27 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1836,12 +1882,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1849,25 +1895,25 @@
         <v>27</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2045,23 +2091,23 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
-        <v>279</v>
+      <c r="A12" s="27" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2182,50 +2228,50 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>282</v>
+      <c r="A4" s="27" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2397,39 +2443,39 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>292</v>
+      <c r="A11" s="27" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B13" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
@@ -2456,12 +2502,12 @@
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B14" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
@@ -2488,12 +2534,12 @@
         <v>5</v>
       </c>
       <c r="H14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B15" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
@@ -2520,12 +2566,12 @@
         <v>4</v>
       </c>
       <c r="H15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B16" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
@@ -2552,31 +2598,31 @@
         <v>3</v>
       </c>
       <c r="H16" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="23" t="s">
-        <v>306</v>
+      <c r="A18" s="29" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
-        <v>307</v>
+      <c r="A20" s="27" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2661,18 +2707,18 @@
   <sheetData>
     <row r="1" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2695,94 +2741,94 @@
         <v>29</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O1" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="T1" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="U1" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="V1" s="11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="W1" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="X1" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Y1" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Z1" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AA1" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AB1" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AC1" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AD1" s="11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AE1" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AF1" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3698,7 +3744,7 @@
       </c>
       <c r="C9">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H13,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G13,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H28,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G28,0)</f>
@@ -3722,7 +3768,7 @@
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J9">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F13="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F28="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F43="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F58="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F73="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F88="W"),1,0)</f>
@@ -3730,7 +3776,7 @@
       </c>
       <c r="K9">
         <f>I9+0.0008</f>
-        <v>8.0007999999999999</v>
+        <v>9.0007999999999999</v>
       </c>
       <c r="L9">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H13,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G13,0)</f>
@@ -3810,11 +3856,11 @@
       </c>
       <c r="AE9">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF9">
         <f>AE9+0.0008</f>
-        <v>8.0007999999999999</v>
+        <v>9.0007999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4214,7 +4260,7 @@
       </c>
       <c r="C13">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H17,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G17,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H32,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G32,0)</f>
@@ -4238,7 +4284,7 @@
       </c>
       <c r="I13">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J13">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F17="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F32="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F47="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F62="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F77="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F92="W"),1,0)</f>
@@ -4246,7 +4292,7 @@
       </c>
       <c r="K13">
         <f>I13+0.0012</f>
-        <v>8.0012000000000008</v>
+        <v>9.0012000000000008</v>
       </c>
       <c r="L13">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H17,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G17,0)</f>
@@ -4326,11 +4372,11 @@
       </c>
       <c r="AE13">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF13">
         <f>AE13+0.0012</f>
-        <v>8.0012000000000008</v>
+        <v>9.0012000000000008</v>
       </c>
     </row>
   </sheetData>
@@ -7223,7 +7269,7 @@
   <sheetPr>
     <tabColor rgb="FF1F6FEB"/>
   </sheetPr>
-  <dimension ref="A1:Q328"/>
+  <dimension ref="A1:Q329"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -8175,24 +8221,64 @@
       </c>
       <c r="E21" s="17" t="str">
         <f>'NFL Schedule'!J18</f>
-        <v/>
-      </c>
-      <c r="F21" s="18"/>
+        <v>KC</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>87</v>
+      </c>
       <c r="G21" s="18"/>
       <c r="H21" s="18"/>
       <c r="I21" s="18"/>
-      <c r="J21" s="18"/>
+      <c r="J21" s="18" t="s">
+        <v>87</v>
+      </c>
       <c r="K21" s="18"/>
       <c r="L21" s="18"/>
-      <c r="M21" s="18"/>
+      <c r="M21" s="18" t="s">
+        <v>88</v>
+      </c>
       <c r="N21" s="18"/>
       <c r="O21" s="18"/>
       <c r="P21" s="18"/>
-      <c r="Q21" s="18"/>
+      <c r="Q21" s="18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="21">
+        <f>'NFL Schedule'!E19</f>
+        <v>51</v>
+      </c>
+      <c r="F22" s="22">
+        <v>48</v>
+      </c>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22">
+        <v>47</v>
+      </c>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="22">
+        <v>50</v>
+      </c>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22">
+        <v>47</v>
+      </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -8744,9 +8830,33 @@
       <c r="P40" s="18"/>
       <c r="Q40" s="18"/>
     </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E41" s="21" t="str">
+        <f>'NFL Schedule'!E38</f>
+        <v/>
+      </c>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
+      <c r="N41" s="22"/>
+      <c r="O41" s="22"/>
+      <c r="P41" s="22"/>
+      <c r="Q41" s="22"/>
+    </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -9298,9 +9408,33 @@
       <c r="P59" s="18"/>
       <c r="Q59" s="18"/>
     </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A60" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B60" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E60" s="21" t="str">
+        <f>'NFL Schedule'!E57</f>
+        <v/>
+      </c>
+      <c r="F60" s="22"/>
+      <c r="G60" s="22"/>
+      <c r="H60" s="22"/>
+      <c r="I60" s="22"/>
+      <c r="J60" s="22"/>
+      <c r="K60" s="22"/>
+      <c r="L60" s="22"/>
+      <c r="M60" s="22"/>
+      <c r="N60" s="22"/>
+      <c r="O60" s="22"/>
+      <c r="P60" s="22"/>
+      <c r="Q60" s="22"/>
+    </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -9852,9 +9986,33 @@
       <c r="P78" s="18"/>
       <c r="Q78" s="18"/>
     </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A79" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B79" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E79" s="21" t="str">
+        <f>'NFL Schedule'!E76</f>
+        <v/>
+      </c>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="22"/>
+      <c r="K79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+    </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -10376,9 +10534,33 @@
       <c r="P96" s="18"/>
       <c r="Q96" s="18"/>
     </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A97" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B97" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E97" s="21" t="str">
+        <f>'NFL Schedule'!E94</f>
+        <v/>
+      </c>
+      <c r="F97" s="22"/>
+      <c r="G97" s="22"/>
+      <c r="H97" s="22"/>
+      <c r="I97" s="22"/>
+      <c r="J97" s="22"/>
+      <c r="K97" s="22"/>
+      <c r="L97" s="22"/>
+      <c r="M97" s="22"/>
+      <c r="N97" s="22"/>
+      <c r="O97" s="22"/>
+      <c r="P97" s="22"/>
+      <c r="Q97" s="22"/>
+    </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -10870,9 +11052,33 @@
       <c r="P113" s="18"/>
       <c r="Q113" s="18"/>
     </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A114" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B114" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E114" s="21" t="str">
+        <f>'NFL Schedule'!E111</f>
+        <v/>
+      </c>
+      <c r="F114" s="22"/>
+      <c r="G114" s="22"/>
+      <c r="H114" s="22"/>
+      <c r="I114" s="22"/>
+      <c r="J114" s="22"/>
+      <c r="K114" s="22"/>
+      <c r="L114" s="22"/>
+      <c r="M114" s="22"/>
+      <c r="N114" s="22"/>
+      <c r="O114" s="22"/>
+      <c r="P114" s="22"/>
+      <c r="Q114" s="22"/>
+    </row>
     <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -11364,9 +11570,33 @@
       <c r="P130" s="18"/>
       <c r="Q130" s="18"/>
     </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A131" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B131" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E131" s="21" t="str">
+        <f>'NFL Schedule'!E128</f>
+        <v/>
+      </c>
+      <c r="F131" s="22"/>
+      <c r="G131" s="22"/>
+      <c r="H131" s="22"/>
+      <c r="I131" s="22"/>
+      <c r="J131" s="22"/>
+      <c r="K131" s="22"/>
+      <c r="L131" s="22"/>
+      <c r="M131" s="22"/>
+      <c r="N131" s="22"/>
+      <c r="O131" s="22"/>
+      <c r="P131" s="22"/>
+      <c r="Q131" s="22"/>
+    </row>
     <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
@@ -11858,9 +12088,33 @@
       <c r="P147" s="18"/>
       <c r="Q147" s="18"/>
     </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A148" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B148" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E148" s="21" t="str">
+        <f>'NFL Schedule'!E145</f>
+        <v/>
+      </c>
+      <c r="F148" s="22"/>
+      <c r="G148" s="22"/>
+      <c r="H148" s="22"/>
+      <c r="I148" s="22"/>
+      <c r="J148" s="22"/>
+      <c r="K148" s="22"/>
+      <c r="L148" s="22"/>
+      <c r="M148" s="22"/>
+      <c r="N148" s="22"/>
+      <c r="O148" s="22"/>
+      <c r="P148" s="22"/>
+      <c r="Q148" s="22"/>
+    </row>
     <row r="149" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -12382,9 +12636,33 @@
       <c r="P165" s="18"/>
       <c r="Q165" s="18"/>
     </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A166" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B166" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E166" s="21" t="str">
+        <f>'NFL Schedule'!E163</f>
+        <v/>
+      </c>
+      <c r="F166" s="22"/>
+      <c r="G166" s="22"/>
+      <c r="H166" s="22"/>
+      <c r="I166" s="22"/>
+      <c r="J166" s="22"/>
+      <c r="K166" s="22"/>
+      <c r="L166" s="22"/>
+      <c r="M166" s="22"/>
+      <c r="N166" s="22"/>
+      <c r="O166" s="22"/>
+      <c r="P166" s="22"/>
+      <c r="Q166" s="22"/>
+    </row>
     <row r="167" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -12876,9 +13154,33 @@
       <c r="P182" s="18"/>
       <c r="Q182" s="18"/>
     </row>
+    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A183" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B183" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E183" s="21" t="str">
+        <f>'NFL Schedule'!E180</f>
+        <v/>
+      </c>
+      <c r="F183" s="22"/>
+      <c r="G183" s="22"/>
+      <c r="H183" s="22"/>
+      <c r="I183" s="22"/>
+      <c r="J183" s="22"/>
+      <c r="K183" s="22"/>
+      <c r="L183" s="22"/>
+      <c r="M183" s="22"/>
+      <c r="N183" s="22"/>
+      <c r="O183" s="22"/>
+      <c r="P183" s="22"/>
+      <c r="Q183" s="22"/>
+    </row>
     <row r="184" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -13340,9 +13642,33 @@
       <c r="P198" s="18"/>
       <c r="Q198" s="18"/>
     </row>
+    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A199" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B199" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E199" s="21" t="str">
+        <f>'NFL Schedule'!E196</f>
+        <v/>
+      </c>
+      <c r="F199" s="22"/>
+      <c r="G199" s="22"/>
+      <c r="H199" s="22"/>
+      <c r="I199" s="22"/>
+      <c r="J199" s="22"/>
+      <c r="K199" s="22"/>
+      <c r="L199" s="22"/>
+      <c r="M199" s="22"/>
+      <c r="N199" s="22"/>
+      <c r="O199" s="22"/>
+      <c r="P199" s="22"/>
+      <c r="Q199" s="22"/>
+    </row>
     <row r="200" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
@@ -13894,9 +14220,33 @@
       <c r="P217" s="18"/>
       <c r="Q217" s="18"/>
     </row>
+    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A218" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B218" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E218" s="21" t="str">
+        <f>'NFL Schedule'!E215</f>
+        <v/>
+      </c>
+      <c r="F218" s="22"/>
+      <c r="G218" s="22"/>
+      <c r="H218" s="22"/>
+      <c r="I218" s="22"/>
+      <c r="J218" s="22"/>
+      <c r="K218" s="22"/>
+      <c r="L218" s="22"/>
+      <c r="M218" s="22"/>
+      <c r="N218" s="22"/>
+      <c r="O218" s="22"/>
+      <c r="P218" s="22"/>
+      <c r="Q218" s="22"/>
+    </row>
     <row r="219" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
@@ -14388,9 +14738,33 @@
       <c r="P234" s="18"/>
       <c r="Q234" s="18"/>
     </row>
+    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A235" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B235" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E235" s="21" t="str">
+        <f>'NFL Schedule'!E232</f>
+        <v/>
+      </c>
+      <c r="F235" s="22"/>
+      <c r="G235" s="22"/>
+      <c r="H235" s="22"/>
+      <c r="I235" s="22"/>
+      <c r="J235" s="22"/>
+      <c r="K235" s="22"/>
+      <c r="L235" s="22"/>
+      <c r="M235" s="22"/>
+      <c r="N235" s="22"/>
+      <c r="O235" s="22"/>
+      <c r="P235" s="22"/>
+      <c r="Q235" s="22"/>
+    </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
@@ -14912,9 +15286,33 @@
       <c r="P252" s="18"/>
       <c r="Q252" s="18"/>
     </row>
+    <row r="253" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A253" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B253" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E253" s="21" t="str">
+        <f>'NFL Schedule'!E250</f>
+        <v/>
+      </c>
+      <c r="F253" s="22"/>
+      <c r="G253" s="22"/>
+      <c r="H253" s="22"/>
+      <c r="I253" s="22"/>
+      <c r="J253" s="22"/>
+      <c r="K253" s="22"/>
+      <c r="L253" s="22"/>
+      <c r="M253" s="22"/>
+      <c r="N253" s="22"/>
+      <c r="O253" s="22"/>
+      <c r="P253" s="22"/>
+      <c r="Q253" s="22"/>
+    </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B254" s="4"/>
       <c r="C254" s="4"/>
@@ -15466,9 +15864,33 @@
       <c r="P271" s="18"/>
       <c r="Q271" s="18"/>
     </row>
+    <row r="272" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A272" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B272" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E272" s="21" t="str">
+        <f>'NFL Schedule'!E269</f>
+        <v/>
+      </c>
+      <c r="F272" s="22"/>
+      <c r="G272" s="22"/>
+      <c r="H272" s="22"/>
+      <c r="I272" s="22"/>
+      <c r="J272" s="22"/>
+      <c r="K272" s="22"/>
+      <c r="L272" s="22"/>
+      <c r="M272" s="22"/>
+      <c r="N272" s="22"/>
+      <c r="O272" s="22"/>
+      <c r="P272" s="22"/>
+      <c r="Q272" s="22"/>
+    </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
@@ -16020,9 +16442,33 @@
       <c r="P290" s="18"/>
       <c r="Q290" s="18"/>
     </row>
+    <row r="291" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A291" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B291" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E291" s="21" t="str">
+        <f>'NFL Schedule'!E288</f>
+        <v/>
+      </c>
+      <c r="F291" s="22"/>
+      <c r="G291" s="22"/>
+      <c r="H291" s="22"/>
+      <c r="I291" s="22"/>
+      <c r="J291" s="22"/>
+      <c r="K291" s="22"/>
+      <c r="L291" s="22"/>
+      <c r="M291" s="22"/>
+      <c r="N291" s="22"/>
+      <c r="O291" s="22"/>
+      <c r="P291" s="22"/>
+      <c r="Q291" s="22"/>
+    </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B292" s="4"/>
       <c r="C292" s="4"/>
@@ -16574,9 +17020,33 @@
       <c r="P309" s="18"/>
       <c r="Q309" s="18"/>
     </row>
+    <row r="310" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A310" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B310" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E310" s="21" t="str">
+        <f>'NFL Schedule'!E307</f>
+        <v/>
+      </c>
+      <c r="F310" s="22"/>
+      <c r="G310" s="22"/>
+      <c r="H310" s="22"/>
+      <c r="I310" s="22"/>
+      <c r="J310" s="22"/>
+      <c r="K310" s="22"/>
+      <c r="L310" s="22"/>
+      <c r="M310" s="22"/>
+      <c r="N310" s="22"/>
+      <c r="O310" s="22"/>
+      <c r="P310" s="22"/>
+      <c r="Q310" s="22"/>
+    </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
@@ -17127,6 +17597,30 @@
       <c r="O328" s="18"/>
       <c r="P328" s="18"/>
       <c r="Q328" s="18"/>
+    </row>
+    <row r="329" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A329" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B329" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E329" s="21" t="str">
+        <f>'NFL Schedule'!E326</f>
+        <v/>
+      </c>
+      <c r="F329" s="22"/>
+      <c r="G329" s="22"/>
+      <c r="H329" s="22"/>
+      <c r="I329" s="22"/>
+      <c r="J329" s="22"/>
+      <c r="K329" s="22"/>
+      <c r="L329" s="22"/>
+      <c r="M329" s="22"/>
+      <c r="N329" s="22"/>
+      <c r="O329" s="22"/>
+      <c r="P329" s="22"/>
+      <c r="Q329" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -17504,723 +17998,723 @@
       <formula1>"PIT,TB"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LAR or KC" promptTitle="ATS Pick" prompt="Pick LAR or KC" sqref="F110:Q110" xr:uid="{00000000-0002-0000-0200-000059000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LAR or KC" promptTitle="ATS Pick" prompt="Pick LAR or KC" sqref="F110:Q110" xr:uid="{00000000-0002-0000-0200-000058000000}">
       <formula1>"LAR,KC"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BUF or LV" promptTitle="ATS Pick" prompt="Pick BUF or LV" sqref="F111:Q111" xr:uid="{00000000-0002-0000-0200-00005A000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BUF or LV" promptTitle="ATS Pick" prompt="Pick BUF or LV" sqref="F111:Q111" xr:uid="{00000000-0002-0000-0200-000059000000}">
       <formula1>"BUF,LV"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DAL or GB" promptTitle="ATS Pick" prompt="Pick DAL or GB" sqref="F112:Q112" xr:uid="{00000000-0002-0000-0200-00005B000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DAL or GB" promptTitle="ATS Pick" prompt="Pick DAL or GB" sqref="F112:Q112" xr:uid="{00000000-0002-0000-0200-00005A000000}">
       <formula1>"DAL,GB"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be WAS or SF" promptTitle="ATS Pick" prompt="Pick WAS or SF" sqref="F113:Q113" xr:uid="{00000000-0002-0000-0200-00005C000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be WAS or SF" promptTitle="ATS Pick" prompt="Pick WAS or SF" sqref="F113:Q113" xr:uid="{00000000-0002-0000-0200-00005B000000}">
       <formula1>"WAS,SF"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or CHI" promptTitle="ATS Pick" prompt="Pick NE or CHI" sqref="F117:Q117" xr:uid="{00000000-0002-0000-0200-00005D000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or CHI" promptTitle="ATS Pick" prompt="Pick NE or CHI" sqref="F117:Q117" xr:uid="{00000000-0002-0000-0200-00005C000000}">
       <formula1>"NE,CHI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be PIT or NO" promptTitle="ATS Pick" prompt="Pick PIT or NO" sqref="F118:Q118" xr:uid="{00000000-0002-0000-0200-00005E000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be PIT or NO" promptTitle="ATS Pick" prompt="Pick PIT or NO" sqref="F118:Q118" xr:uid="{00000000-0002-0000-0200-00005D000000}">
       <formula1>"PIT,NO"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be SF or ATL" promptTitle="ATS Pick" prompt="Pick SF or ATL" sqref="F119:Q119" xr:uid="{00000000-0002-0000-0200-00005F000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be SF or ATL" promptTitle="ATS Pick" prompt="Pick SF or ATL" sqref="F119:Q119" xr:uid="{00000000-0002-0000-0200-00005E000000}">
       <formula1>"SF,ATL"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CLE or TEN" promptTitle="ATS Pick" prompt="Pick CLE or TEN" sqref="F120:Q120" xr:uid="{00000000-0002-0000-0200-000060000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CLE or TEN" promptTitle="ATS Pick" prompt="Pick CLE or TEN" sqref="F120:Q120" xr:uid="{00000000-0002-0000-0200-00005F000000}">
       <formula1>"CLE,TEN"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be IND or MIN" promptTitle="ATS Pick" prompt="Pick IND or MIN" sqref="F121:Q121" xr:uid="{00000000-0002-0000-0200-000061000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be IND or MIN" promptTitle="ATS Pick" prompt="Pick IND or MIN" sqref="F121:Q121" xr:uid="{00000000-0002-0000-0200-000060000000}">
       <formula1>"IND,MIN"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be MIA or NYJ" promptTitle="ATS Pick" prompt="Pick MIA or NYJ" sqref="F122:Q122" xr:uid="{00000000-0002-0000-0200-000062000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be MIA or NYJ" promptTitle="ATS Pick" prompt="Pick MIA or NYJ" sqref="F122:Q122" xr:uid="{00000000-0002-0000-0200-000061000000}">
       <formula1>"MIA,NYJ"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TB or CAR" promptTitle="ATS Pick" prompt="Pick TB or CAR" sqref="F123:Q123" xr:uid="{00000000-0002-0000-0200-000063000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TB or CAR" promptTitle="ATS Pick" prompt="Pick TB or CAR" sqref="F123:Q123" xr:uid="{00000000-0002-0000-0200-000062000000}">
       <formula1>"TB,CAR"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CIN or BAL" promptTitle="ATS Pick" prompt="Pick CIN or BAL" sqref="F124:Q124" xr:uid="{00000000-0002-0000-0200-000064000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CIN or BAL" promptTitle="ATS Pick" prompt="Pick CIN or BAL" sqref="F124:Q124" xr:uid="{00000000-0002-0000-0200-000063000000}">
       <formula1>"CIN,BAL"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NYG or HOU" promptTitle="ATS Pick" prompt="Pick NYG or HOU" sqref="F125:Q125" xr:uid="{00000000-0002-0000-0200-000065000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NYG or HOU" promptTitle="ATS Pick" prompt="Pick NYG or HOU" sqref="F125:Q125" xr:uid="{00000000-0002-0000-0200-000064000000}">
       <formula1>"NYG,HOU"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DEN or ARI" promptTitle="ATS Pick" prompt="Pick DEN or ARI" sqref="F126:Q126" xr:uid="{00000000-0002-0000-0200-000066000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DEN or ARI" promptTitle="ATS Pick" prompt="Pick DEN or ARI" sqref="F126:Q126" xr:uid="{00000000-0002-0000-0200-000065000000}">
       <formula1>"DEN,ARI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be GB or DET" promptTitle="ATS Pick" prompt="Pick GB or DET" sqref="F127:Q127" xr:uid="{00000000-0002-0000-0200-000067000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be GB or DET" promptTitle="ATS Pick" prompt="Pick GB or DET" sqref="F127:Q127" xr:uid="{00000000-0002-0000-0200-000066000000}">
       <formula1>"GB,DET"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LAR or LV" promptTitle="ATS Pick" prompt="Pick LAR or LV" sqref="F128:Q128" xr:uid="{00000000-0002-0000-0200-000068000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LAR or LV" promptTitle="ATS Pick" prompt="Pick LAR or LV" sqref="F128:Q128" xr:uid="{00000000-0002-0000-0200-000067000000}">
       <formula1>"LAR,LV"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be KC or SEA" promptTitle="ATS Pick" prompt="Pick KC or SEA" sqref="F129:Q129" xr:uid="{00000000-0002-0000-0200-000069000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be KC or SEA" promptTitle="ATS Pick" prompt="Pick KC or SEA" sqref="F129:Q129" xr:uid="{00000000-0002-0000-0200-000068000000}">
       <formula1>"KC,SEA"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DAL or PHI" promptTitle="ATS Pick" prompt="Pick DAL or PHI" sqref="F130:Q130" xr:uid="{00000000-0002-0000-0200-00006A000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DAL or PHI" promptTitle="ATS Pick" prompt="Pick DAL or PHI" sqref="F130:Q130" xr:uid="{00000000-0002-0000-0200-000069000000}">
       <formula1>"DAL,PHI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CAR or GB" promptTitle="ATS Pick" prompt="Pick CAR or GB" sqref="F134:Q134" xr:uid="{00000000-0002-0000-0200-00006B000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CAR or GB" promptTitle="ATS Pick" prompt="Pick CAR or GB" sqref="F134:Q134" xr:uid="{00000000-0002-0000-0200-00006A000000}">
       <formula1>"CAR,GB"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BAL or BUF" promptTitle="ATS Pick" prompt="Pick BAL or BUF" sqref="F135:Q135" xr:uid="{00000000-0002-0000-0200-00006C000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BAL or BUF" promptTitle="ATS Pick" prompt="Pick BAL or BUF" sqref="F135:Q135" xr:uid="{00000000-0002-0000-0200-00006B000000}">
       <formula1>"BAL,BUF"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TEN or CIN" promptTitle="ATS Pick" prompt="Pick TEN or CIN" sqref="F136:Q136" xr:uid="{00000000-0002-0000-0200-00006D000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TEN or CIN" promptTitle="ATS Pick" prompt="Pick TEN or CIN" sqref="F136:Q136" xr:uid="{00000000-0002-0000-0200-00006C000000}">
       <formula1>"TEN,CIN"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be ARI or DAL" promptTitle="ATS Pick" prompt="Pick ARI or DAL" sqref="F137:Q137" xr:uid="{00000000-0002-0000-0200-00006E000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be ARI or DAL" promptTitle="ATS Pick" prompt="Pick ARI or DAL" sqref="F137:Q137" xr:uid="{00000000-0002-0000-0200-00006D000000}">
       <formula1>"ARI,DAL"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be MIN or DET" promptTitle="ATS Pick" prompt="Pick MIN or DET" sqref="F138:Q138" xr:uid="{00000000-0002-0000-0200-00006F000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be MIN or DET" promptTitle="ATS Pick" prompt="Pick MIN or DET" sqref="F138:Q138" xr:uid="{00000000-0002-0000-0200-00006E000000}">
       <formula1>"MIN,DET"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LV or NYJ" promptTitle="ATS Pick" prompt="Pick LV or NYJ" sqref="F139:Q139" xr:uid="{00000000-0002-0000-0200-000070000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LV or NYJ" promptTitle="ATS Pick" prompt="Pick LV or NYJ" sqref="F139:Q139" xr:uid="{00000000-0002-0000-0200-00006F000000}">
       <formula1>"LV,NYJ"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CLE or PIT" promptTitle="ATS Pick" prompt="Pick CLE or PIT" sqref="F140:Q140" xr:uid="{00000000-0002-0000-0200-000071000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CLE or PIT" promptTitle="ATS Pick" prompt="Pick CLE or PIT" sqref="F140:Q140" xr:uid="{00000000-0002-0000-0200-000070000000}">
       <formula1>"CLE,PIT"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be ATL or TB" promptTitle="ATS Pick" prompt="Pick ATL or TB" sqref="F141:Q141" xr:uid="{00000000-0002-0000-0200-000072000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be ATL or TB" promptTitle="ATS Pick" prompt="Pick ATL or TB" sqref="F141:Q141" xr:uid="{00000000-0002-0000-0200-000071000000}">
       <formula1>"ATL,TB"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be IND or JAX" promptTitle="ATS Pick" prompt="Pick IND or JAX" sqref="F142:Q142" xr:uid="{00000000-0002-0000-0200-000073000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be IND or JAX" promptTitle="ATS Pick" prompt="Pick IND or JAX" sqref="F142:Q142" xr:uid="{00000000-0002-0000-0200-000072000000}">
       <formula1>"IND,JAX"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LAR or LAC" promptTitle="ATS Pick" prompt="Pick LAR or LAC" sqref="F143:Q143" xr:uid="{00000000-0002-0000-0200-000074000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LAR or LAC" promptTitle="ATS Pick" prompt="Pick LAR or LAC" sqref="F143:Q143" xr:uid="{00000000-0002-0000-0200-000073000000}">
       <formula1>"LAR,LAC"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be KC or DEN" promptTitle="ATS Pick" prompt="Pick KC or DEN" sqref="F144:Q144" xr:uid="{00000000-0002-0000-0200-000075000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be KC or DEN" promptTitle="ATS Pick" prompt="Pick KC or DEN" sqref="F144:Q144" xr:uid="{00000000-0002-0000-0200-000074000000}">
       <formula1>"KC,DEN"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or MIA" promptTitle="ATS Pick" prompt="Pick NE or MIA" sqref="F145:Q145" xr:uid="{00000000-0002-0000-0200-000076000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or MIA" promptTitle="ATS Pick" prompt="Pick NE or MIA" sqref="F145:Q145" xr:uid="{00000000-0002-0000-0200-000075000000}">
       <formula1>"NE,MIA"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be PHI or WAS" promptTitle="ATS Pick" prompt="Pick PHI or WAS" sqref="F146:Q146" xr:uid="{00000000-0002-0000-0200-000077000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be PHI or WAS" promptTitle="ATS Pick" prompt="Pick PHI or WAS" sqref="F146:Q146" xr:uid="{00000000-0002-0000-0200-000076000000}">
       <formula1>"PHI,WAS"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CHI or SEA" promptTitle="ATS Pick" prompt="Pick CHI or SEA" sqref="F147:Q147" xr:uid="{00000000-0002-0000-0200-000078000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CHI or SEA" promptTitle="ATS Pick" prompt="Pick CHI or SEA" sqref="F147:Q147" xr:uid="{00000000-0002-0000-0200-000077000000}">
       <formula1>"CHI,SEA"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be JAX or BAL" promptTitle="ATS Pick" prompt="Pick JAX or BAL" sqref="F151:Q151" xr:uid="{00000000-0002-0000-0200-000079000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be JAX or BAL" promptTitle="ATS Pick" prompt="Pick JAX or BAL" sqref="F151:Q151" xr:uid="{00000000-0002-0000-0200-000078000000}">
       <formula1>"JAX,BAL"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CIN or ATL" promptTitle="ATS Pick" prompt="Pick CIN or ATL" sqref="F152:Q152" xr:uid="{00000000-0002-0000-0200-00007A000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CIN or ATL" promptTitle="ATS Pick" prompt="Pick CIN or ATL" sqref="F152:Q152" xr:uid="{00000000-0002-0000-0200-000079000000}">
       <formula1>"CIN,ATL"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DAL or IND" promptTitle="ATS Pick" prompt="Pick DAL or IND" sqref="F153:Q153" xr:uid="{00000000-0002-0000-0200-00007B000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DAL or IND" promptTitle="ATS Pick" prompt="Pick DAL or IND" sqref="F153:Q153" xr:uid="{00000000-0002-0000-0200-00007A000000}">
       <formula1>"DAL,IND"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NYJ or KC" promptTitle="ATS Pick" prompt="Pick NYJ or KC" sqref="F154:Q154" xr:uid="{00000000-0002-0000-0200-00007C000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NYJ or KC" promptTitle="ATS Pick" prompt="Pick NYJ or KC" sqref="F154:Q154" xr:uid="{00000000-0002-0000-0200-00007B000000}">
       <formula1>"NYJ,KC"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DET or MIA" promptTitle="ATS Pick" prompt="Pick DET or MIA" sqref="F155:Q155" xr:uid="{00000000-0002-0000-0200-00007D000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DET or MIA" promptTitle="ATS Pick" prompt="Pick DET or MIA" sqref="F155:Q155" xr:uid="{00000000-0002-0000-0200-00007C000000}">
       <formula1>"DET,MIA"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CLE or NO" promptTitle="ATS Pick" prompt="Pick CLE or NO" sqref="F156:Q156" xr:uid="{00000000-0002-0000-0200-00007E000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CLE or NO" promptTitle="ATS Pick" prompt="Pick CLE or NO" sqref="F156:Q156" xr:uid="{00000000-0002-0000-0200-00007D000000}">
       <formula1>"CLE,NO"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NYG or PHI" promptTitle="ATS Pick" prompt="Pick NYG or PHI" sqref="F157:Q157" xr:uid="{00000000-0002-0000-0200-00007F000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NYG or PHI" promptTitle="ATS Pick" prompt="Pick NYG or PHI" sqref="F157:Q157" xr:uid="{00000000-0002-0000-0200-00007E000000}">
       <formula1>"NYG,PHI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LAR or WAS" promptTitle="ATS Pick" prompt="Pick LAR or WAS" sqref="F158:Q158" xr:uid="{00000000-0002-0000-0200-000080000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LAR or WAS" promptTitle="ATS Pick" prompt="Pick LAR or WAS" sqref="F158:Q158" xr:uid="{00000000-0002-0000-0200-00007F000000}">
       <formula1>"LAR,WAS"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DEN or CAR" promptTitle="ATS Pick" prompt="Pick DEN or CAR" sqref="F159:Q159" xr:uid="{00000000-0002-0000-0200-000081000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DEN or CAR" promptTitle="ATS Pick" prompt="Pick DEN or CAR" sqref="F159:Q159" xr:uid="{00000000-0002-0000-0200-000080000000}">
       <formula1>"DEN,CAR"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be HOU or LAC" promptTitle="ATS Pick" prompt="Pick HOU or LAC" sqref="F160:Q160" xr:uid="{00000000-0002-0000-0200-000082000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be HOU or LAC" promptTitle="ATS Pick" prompt="Pick HOU or LAC" sqref="F160:Q160" xr:uid="{00000000-0002-0000-0200-000081000000}">
       <formula1>"HOU,LAC"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LV or SF" promptTitle="ATS Pick" prompt="Pick LV or SF" sqref="F161:Q161" xr:uid="{00000000-0002-0000-0200-000083000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LV or SF" promptTitle="ATS Pick" prompt="Pick LV or SF" sqref="F161:Q161" xr:uid="{00000000-0002-0000-0200-000082000000}">
       <formula1>"LV,SF"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be GB or NE" promptTitle="ATS Pick" prompt="Pick GB or NE" sqref="F162:Q162" xr:uid="{00000000-0002-0000-0200-000084000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be GB or NE" promptTitle="ATS Pick" prompt="Pick GB or NE" sqref="F162:Q162" xr:uid="{00000000-0002-0000-0200-000083000000}">
       <formula1>"GB,NE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be ARI or SEA" promptTitle="ATS Pick" prompt="Pick ARI or SEA" sqref="F163:Q163" xr:uid="{00000000-0002-0000-0200-000085000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be ARI or SEA" promptTitle="ATS Pick" prompt="Pick ARI or SEA" sqref="F163:Q163" xr:uid="{00000000-0002-0000-0200-000084000000}">
       <formula1>"ARI,SEA"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TB or CHI" promptTitle="ATS Pick" prompt="Pick TB or CHI" sqref="F164:Q164" xr:uid="{00000000-0002-0000-0200-000086000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TB or CHI" promptTitle="ATS Pick" prompt="Pick TB or CHI" sqref="F164:Q164" xr:uid="{00000000-0002-0000-0200-000085000000}">
       <formula1>"TB,CHI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BUF or MIN" promptTitle="ATS Pick" prompt="Pick BUF or MIN" sqref="F165:Q165" xr:uid="{00000000-0002-0000-0200-000087000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BUF or MIN" promptTitle="ATS Pick" prompt="Pick BUF or MIN" sqref="F165:Q165" xr:uid="{00000000-0002-0000-0200-000086000000}">
       <formula1>"BUF,MIN"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be WAS or NYG" promptTitle="ATS Pick" prompt="Pick WAS or NYG" sqref="F169:Q169" xr:uid="{00000000-0002-0000-0200-000088000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be WAS or NYG" promptTitle="ATS Pick" prompt="Pick WAS or NYG" sqref="F169:Q169" xr:uid="{00000000-0002-0000-0200-000087000000}">
       <formula1>"WAS,NYG"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or DET" promptTitle="ATS Pick" prompt="Pick NE or DET" sqref="F170:Q170" xr:uid="{00000000-0002-0000-0200-000089000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or DET" promptTitle="ATS Pick" prompt="Pick NE or DET" sqref="F170:Q170" xr:uid="{00000000-0002-0000-0200-000088000000}">
       <formula1>"NE,DET"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be KC or ATL" promptTitle="ATS Pick" prompt="Pick KC or ATL" sqref="F171:Q171" xr:uid="{00000000-0002-0000-0200-00008A000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be KC or ATL" promptTitle="ATS Pick" prompt="Pick KC or ATL" sqref="F171:Q171" xr:uid="{00000000-0002-0000-0200-000089000000}">
       <formula1>"KC,ATL"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be HOU or CLE" promptTitle="ATS Pick" prompt="Pick HOU or CLE" sqref="F172:Q172" xr:uid="{00000000-0002-0000-0200-00008B000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be HOU or CLE" promptTitle="ATS Pick" prompt="Pick HOU or CLE" sqref="F172:Q172" xr:uid="{00000000-0002-0000-0200-00008A000000}">
       <formula1>"HOU,CLE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be MIN or GB" promptTitle="ATS Pick" prompt="Pick MIN or GB" sqref="F173:Q173" xr:uid="{00000000-0002-0000-0200-00008C000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be MIN or GB" promptTitle="ATS Pick" prompt="Pick MIN or GB" sqref="F173:Q173" xr:uid="{00000000-0002-0000-0200-00008B000000}">
       <formula1>"MIN,GB"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be JAX or TEN" promptTitle="ATS Pick" prompt="Pick JAX or TEN" sqref="F174:Q174" xr:uid="{00000000-0002-0000-0200-00008D000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be JAX or TEN" promptTitle="ATS Pick" prompt="Pick JAX or TEN" sqref="F174:Q174" xr:uid="{00000000-0002-0000-0200-00008C000000}">
       <formula1>"JAX,TEN"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be MIA or IND" promptTitle="ATS Pick" prompt="Pick MIA or IND" sqref="F175:Q175" xr:uid="{00000000-0002-0000-0200-00008E000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be MIA or IND" promptTitle="ATS Pick" prompt="Pick MIA or IND" sqref="F175:Q175" xr:uid="{00000000-0002-0000-0200-00008D000000}">
       <formula1>"MIA,IND"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CAR or NO" promptTitle="ATS Pick" prompt="Pick CAR or NO" sqref="F176:Q176" xr:uid="{00000000-0002-0000-0200-00008F000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CAR or NO" promptTitle="ATS Pick" prompt="Pick CAR or NO" sqref="F176:Q176" xr:uid="{00000000-0002-0000-0200-00008E000000}">
       <formula1>"CAR,NO"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BUF or NYJ" promptTitle="ATS Pick" prompt="Pick BUF or NYJ" sqref="F177:Q177" xr:uid="{00000000-0002-0000-0200-000090000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BUF or NYJ" promptTitle="ATS Pick" prompt="Pick BUF or NYJ" sqref="F177:Q177" xr:uid="{00000000-0002-0000-0200-00008F000000}">
       <formula1>"BUF,NYJ"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be SEA or LV" promptTitle="ATS Pick" prompt="Pick SEA or LV" sqref="F178:Q178" xr:uid="{00000000-0002-0000-0200-000091000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be SEA or LV" promptTitle="ATS Pick" prompt="Pick SEA or LV" sqref="F178:Q178" xr:uid="{00000000-0002-0000-0200-000090000000}">
       <formula1>"SEA,LV"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LAR or ARI" promptTitle="ATS Pick" prompt="Pick LAR or ARI" sqref="F179:Q179" xr:uid="{00000000-0002-0000-0200-000092000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LAR or ARI" promptTitle="ATS Pick" prompt="Pick LAR or ARI" sqref="F179:Q179" xr:uid="{00000000-0002-0000-0200-000091000000}">
       <formula1>"LAR,ARI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be SF or DAL" promptTitle="ATS Pick" prompt="Pick SF or DAL" sqref="F180:Q180" xr:uid="{00000000-0002-0000-0200-000093000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be SF or DAL" promptTitle="ATS Pick" prompt="Pick SF or DAL" sqref="F180:Q180" xr:uid="{00000000-0002-0000-0200-000092000000}">
       <formula1>"SF,DAL"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be PIT or CIN" promptTitle="ATS Pick" prompt="Pick PIT or CIN" sqref="F181:Q181" xr:uid="{00000000-0002-0000-0200-000094000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be PIT or CIN" promptTitle="ATS Pick" prompt="Pick PIT or CIN" sqref="F181:Q181" xr:uid="{00000000-0002-0000-0200-000093000000}">
       <formula1>"PIT,CIN"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LAC or BAL" promptTitle="ATS Pick" prompt="Pick LAC or BAL" sqref="F182:Q182" xr:uid="{00000000-0002-0000-0200-000095000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LAC or BAL" promptTitle="ATS Pick" prompt="Pick LAC or BAL" sqref="F182:Q182" xr:uid="{00000000-0002-0000-0200-000094000000}">
       <formula1>"LAC,BAL"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be IND or HOU" promptTitle="ATS Pick" prompt="Pick IND or HOU" sqref="F186:Q186" xr:uid="{00000000-0002-0000-0200-000096000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be IND or HOU" promptTitle="ATS Pick" prompt="Pick IND or HOU" sqref="F186:Q186" xr:uid="{00000000-0002-0000-0200-000095000000}">
       <formula1>"IND,HOU"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be MIA or BUF" promptTitle="ATS Pick" prompt="Pick MIA or BUF" sqref="F187:Q187" xr:uid="{00000000-0002-0000-0200-000097000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be MIA or BUF" promptTitle="ATS Pick" prompt="Pick MIA or BUF" sqref="F187:Q187" xr:uid="{00000000-0002-0000-0200-000096000000}">
       <formula1>"MIA,BUF"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NO or CHI" promptTitle="ATS Pick" prompt="Pick NO or CHI" sqref="F188:Q188" xr:uid="{00000000-0002-0000-0200-000098000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NO or CHI" promptTitle="ATS Pick" prompt="Pick NO or CHI" sqref="F188:Q188" xr:uid="{00000000-0002-0000-0200-000097000000}">
       <formula1>"NO,CHI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TEN or DAL" promptTitle="ATS Pick" prompt="Pick TEN or DAL" sqref="F189:Q189" xr:uid="{00000000-0002-0000-0200-000099000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TEN or DAL" promptTitle="ATS Pick" prompt="Pick TEN or DAL" sqref="F189:Q189" xr:uid="{00000000-0002-0000-0200-000098000000}">
       <formula1>"TEN,DAL"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TB or DET" promptTitle="ATS Pick" prompt="Pick TB or DET" sqref="F190:Q190" xr:uid="{00000000-0002-0000-0200-00009A000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TB or DET" promptTitle="ATS Pick" prompt="Pick TB or DET" sqref="F190:Q190" xr:uid="{00000000-0002-0000-0200-000099000000}">
       <formula1>"TB,DET"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be ARI or KC" promptTitle="ATS Pick" prompt="Pick ARI or KC" sqref="F191:Q191" xr:uid="{00000000-0002-0000-0200-00009B000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be ARI or KC" promptTitle="ATS Pick" prompt="Pick ARI or KC" sqref="F191:Q191" xr:uid="{00000000-0002-0000-0200-00009A000000}">
       <formula1>"ARI,KC"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be JAX or NYG" promptTitle="ATS Pick" prompt="Pick JAX or NYG" sqref="F192:Q192" xr:uid="{00000000-0002-0000-0200-00009C000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be JAX or NYG" promptTitle="ATS Pick" prompt="Pick JAX or NYG" sqref="F192:Q192" xr:uid="{00000000-0002-0000-0200-00009B000000}">
       <formula1>"JAX,NYG"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BAL or CAR" promptTitle="ATS Pick" prompt="Pick BAL or CAR" sqref="F193:Q193" xr:uid="{00000000-0002-0000-0200-00009D000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BAL or CAR" promptTitle="ATS Pick" prompt="Pick BAL or CAR" sqref="F193:Q193" xr:uid="{00000000-0002-0000-0200-00009C000000}">
       <formula1>"BAL,CAR"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NYJ or LAC" promptTitle="ATS Pick" prompt="Pick NYJ or LAC" sqref="F194:Q194" xr:uid="{00000000-0002-0000-0200-00009E000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NYJ or LAC" promptTitle="ATS Pick" prompt="Pick NYJ or LAC" sqref="F194:Q194" xr:uid="{00000000-0002-0000-0200-00009D000000}">
       <formula1>"NYJ,LAC"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LV or DEN" promptTitle="ATS Pick" prompt="Pick LV or DEN" sqref="F195:Q195" xr:uid="{00000000-0002-0000-0200-00009F000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LV or DEN" promptTitle="ATS Pick" prompt="Pick LV or DEN" sqref="F195:Q195" xr:uid="{00000000-0002-0000-0200-00009E000000}">
       <formula1>"LV,DEN"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be PIT or PHI" promptTitle="ATS Pick" prompt="Pick PIT or PHI" sqref="F196:Q196" xr:uid="{00000000-0002-0000-0200-0000A0000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be PIT or PHI" promptTitle="ATS Pick" prompt="Pick PIT or PHI" sqref="F196:Q196" xr:uid="{00000000-0002-0000-0200-00009F000000}">
       <formula1>"PIT,PHI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be MIN or SF" promptTitle="ATS Pick" prompt="Pick MIN or SF" sqref="F197:Q197" xr:uid="{00000000-0002-0000-0200-0000A1000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be MIN or SF" promptTitle="ATS Pick" prompt="Pick MIN or SF" sqref="F197:Q197" xr:uid="{00000000-0002-0000-0200-0000A0000000}">
       <formula1>"MIN,SF"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CIN or WAS" promptTitle="ATS Pick" prompt="Pick CIN or WAS" sqref="F198:Q198" xr:uid="{00000000-0002-0000-0200-0000A2000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CIN or WAS" promptTitle="ATS Pick" prompt="Pick CIN or WAS" sqref="F198:Q198" xr:uid="{00000000-0002-0000-0200-0000A1000000}">
       <formula1>"CIN,WAS"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be GB or LAR" promptTitle="ATS Pick" prompt="Pick GB or LAR" sqref="F202:Q202" xr:uid="{00000000-0002-0000-0200-0000A3000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be GB or LAR" promptTitle="ATS Pick" prompt="Pick GB or LAR" sqref="F202:Q202" xr:uid="{00000000-0002-0000-0200-0000A2000000}">
       <formula1>"GB,LAR"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CHI or DET" promptTitle="ATS Pick" prompt="Pick CHI or DET" sqref="F203:Q203" xr:uid="{00000000-0002-0000-0200-0000A4000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CHI or DET" promptTitle="ATS Pick" prompt="Pick CHI or DET" sqref="F203:Q203" xr:uid="{00000000-0002-0000-0200-0000A3000000}">
       <formula1>"CHI,DET"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be PHI or DAL" promptTitle="ATS Pick" prompt="Pick PHI or DAL" sqref="F204:Q204" xr:uid="{00000000-0002-0000-0200-0000A5000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be PHI or DAL" promptTitle="ATS Pick" prompt="Pick PHI or DAL" sqref="F204:Q204" xr:uid="{00000000-0002-0000-0200-0000A4000000}">
       <formula1>"PHI,DAL"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be KC or BUF" promptTitle="ATS Pick" prompt="Pick KC or BUF" sqref="F205:Q205" xr:uid="{00000000-0002-0000-0200-0000A6000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be KC or BUF" promptTitle="ATS Pick" prompt="Pick KC or BUF" sqref="F205:Q205" xr:uid="{00000000-0002-0000-0200-0000A5000000}">
       <formula1>"KC,BUF"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DEN or PIT" promptTitle="ATS Pick" prompt="Pick DEN or PIT" sqref="F206:Q206" xr:uid="{00000000-0002-0000-0200-0000A7000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DEN or PIT" promptTitle="ATS Pick" prompt="Pick DEN or PIT" sqref="F206:Q206" xr:uid="{00000000-0002-0000-0200-0000A6000000}">
       <formula1>"DEN,PIT"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NO or CIN" promptTitle="ATS Pick" prompt="Pick NO or CIN" sqref="F207:Q207" xr:uid="{00000000-0002-0000-0200-0000A8000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NO or CIN" promptTitle="ATS Pick" prompt="Pick NO or CIN" sqref="F207:Q207" xr:uid="{00000000-0002-0000-0200-0000A7000000}">
       <formula1>"NO,CIN"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LV or CLE" promptTitle="ATS Pick" prompt="Pick LV or CLE" sqref="F208:Q208" xr:uid="{00000000-0002-0000-0200-0000A9000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LV or CLE" promptTitle="ATS Pick" prompt="Pick LV or CLE" sqref="F208:Q208" xr:uid="{00000000-0002-0000-0200-0000A8000000}">
       <formula1>"LV,CLE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NYG or IND" promptTitle="ATS Pick" prompt="Pick NYG or IND" sqref="F209:Q209" xr:uid="{00000000-0002-0000-0200-0000AA000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NYG or IND" promptTitle="ATS Pick" prompt="Pick NYG or IND" sqref="F209:Q209" xr:uid="{00000000-0002-0000-0200-0000A9000000}">
       <formula1>"NYG,IND"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NYJ or MIA" promptTitle="ATS Pick" prompt="Pick NYJ or MIA" sqref="F210:Q210" xr:uid="{00000000-0002-0000-0200-0000AB000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NYJ or MIA" promptTitle="ATS Pick" prompt="Pick NYJ or MIA" sqref="F210:Q210" xr:uid="{00000000-0002-0000-0200-0000AA000000}">
       <formula1>"NYJ,MIA"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be ATL or MIN" promptTitle="ATS Pick" prompt="Pick ATL or MIN" sqref="F211:Q211" xr:uid="{00000000-0002-0000-0200-0000AC000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be ATL or MIN" promptTitle="ATS Pick" prompt="Pick ATL or MIN" sqref="F211:Q211" xr:uid="{00000000-0002-0000-0200-0000AB000000}">
       <formula1>"ATL,MIN"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BAL or HOU" promptTitle="ATS Pick" prompt="Pick BAL or HOU" sqref="F212:Q212" xr:uid="{00000000-0002-0000-0200-0000AD000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BAL or HOU" promptTitle="ATS Pick" prompt="Pick BAL or HOU" sqref="F212:Q212" xr:uid="{00000000-0002-0000-0200-0000AC000000}">
       <formula1>"BAL,HOU"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TEN or JAX" promptTitle="ATS Pick" prompt="Pick TEN or JAX" sqref="F213:Q213" xr:uid="{00000000-0002-0000-0200-0000AE000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TEN or JAX" promptTitle="ATS Pick" prompt="Pick TEN or JAX" sqref="F213:Q213" xr:uid="{00000000-0002-0000-0200-0000AD000000}">
       <formula1>"TEN,JAX"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be WAS or ARI" promptTitle="ATS Pick" prompt="Pick WAS or ARI" sqref="F214:Q214" xr:uid="{00000000-0002-0000-0200-0000AF000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be WAS or ARI" promptTitle="ATS Pick" prompt="Pick WAS or ARI" sqref="F214:Q214" xr:uid="{00000000-0002-0000-0200-0000AE000000}">
       <formula1>"WAS,ARI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be SEA or SF" promptTitle="ATS Pick" prompt="Pick SEA or SF" sqref="F215:Q215" xr:uid="{00000000-0002-0000-0200-0000B0000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be SEA or SF" promptTitle="ATS Pick" prompt="Pick SEA or SF" sqref="F215:Q215" xr:uid="{00000000-0002-0000-0200-0000AF000000}">
       <formula1>"SEA,SF"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or LAC" promptTitle="ATS Pick" prompt="Pick NE or LAC" sqref="F216:Q216" xr:uid="{00000000-0002-0000-0200-0000B1000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or LAC" promptTitle="ATS Pick" prompt="Pick NE or LAC" sqref="F216:Q216" xr:uid="{00000000-0002-0000-0200-0000B0000000}">
       <formula1>"NE,LAC"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CAR or TB" promptTitle="ATS Pick" prompt="Pick CAR or TB" sqref="F217:Q217" xr:uid="{00000000-0002-0000-0200-0000B2000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CAR or TB" promptTitle="ATS Pick" prompt="Pick CAR or TB" sqref="F217:Q217" xr:uid="{00000000-0002-0000-0200-0000B1000000}">
       <formula1>"CAR,TB"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be KC or LAC" promptTitle="ATS Pick" prompt="Pick KC or LAC" sqref="F221:Q221 F307:Q307" xr:uid="{00000000-0002-0000-0200-0000B3000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be KC or LAC" promptTitle="ATS Pick" prompt="Pick KC or LAC" sqref="F221:Q221 F307:Q307" xr:uid="{00000000-0002-0000-0200-0000B2000000}">
       <formula1>"KC,LAC"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DET or ATL" promptTitle="ATS Pick" prompt="Pick DET or ATL" sqref="F222:Q222" xr:uid="{00000000-0002-0000-0200-0000B4000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DET or ATL" promptTitle="ATS Pick" prompt="Pick DET or ATL" sqref="F222:Q222" xr:uid="{00000000-0002-0000-0200-0000B3000000}">
       <formula1>"DET,ATL"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be JAX or CHI" promptTitle="ATS Pick" prompt="Pick JAX or CHI" sqref="F223:Q223" xr:uid="{00000000-0002-0000-0200-0000B5000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be JAX or CHI" promptTitle="ATS Pick" prompt="Pick JAX or CHI" sqref="F223:Q223" xr:uid="{00000000-0002-0000-0200-0000B4000000}">
       <formula1>"JAX,CHI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CIN or CLE" promptTitle="ATS Pick" prompt="Pick CIN or CLE" sqref="F224:Q224" xr:uid="{00000000-0002-0000-0200-0000B6000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CIN or CLE" promptTitle="ATS Pick" prompt="Pick CIN or CLE" sqref="F224:Q224" xr:uid="{00000000-0002-0000-0200-0000B5000000}">
       <formula1>"CIN,CLE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be WAS or TEN" promptTitle="ATS Pick" prompt="Pick WAS or TEN" sqref="F225:Q225" xr:uid="{00000000-0002-0000-0200-0000B7000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be WAS or TEN" promptTitle="ATS Pick" prompt="Pick WAS or TEN" sqref="F225:Q225" xr:uid="{00000000-0002-0000-0200-0000B6000000}">
       <formula1>"WAS,TEN"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be GB or NO" promptTitle="ATS Pick" prompt="Pick GB or NO" sqref="F226:Q226" xr:uid="{00000000-0002-0000-0200-0000B8000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be GB or NO" promptTitle="ATS Pick" prompt="Pick GB or NO" sqref="F226:Q226" xr:uid="{00000000-0002-0000-0200-0000B7000000}">
       <formula1>"GB,NO"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be SF or NYG" promptTitle="ATS Pick" prompt="Pick SF or NYG" sqref="F227:Q227" xr:uid="{00000000-0002-0000-0200-0000B9000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be SF or NYG" promptTitle="ATS Pick" prompt="Pick SF or NYG" sqref="F227:Q227" xr:uid="{00000000-0002-0000-0200-0000B8000000}">
       <formula1>"SF,NYG"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LAR or TB" promptTitle="ATS Pick" prompt="Pick LAR or TB" sqref="F228:Q228 F308:Q308" xr:uid="{00000000-0002-0000-0200-0000BA000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LAR or TB" promptTitle="ATS Pick" prompt="Pick LAR or TB" sqref="F228:Q228 F308:Q308" xr:uid="{00000000-0002-0000-0200-0000B9000000}">
       <formula1>"LAR,TB"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be MIA or DEN" promptTitle="ATS Pick" prompt="Pick MIA or DEN" sqref="F229:Q229" xr:uid="{00000000-0002-0000-0200-0000BB000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be MIA or DEN" promptTitle="ATS Pick" prompt="Pick MIA or DEN" sqref="F229:Q229" xr:uid="{00000000-0002-0000-0200-0000BA000000}">
       <formula1>"MIA,DEN"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be PHI or ARI" promptTitle="ATS Pick" prompt="Pick PHI or ARI" sqref="F230:Q230" xr:uid="{00000000-0002-0000-0200-0000BC000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be PHI or ARI" promptTitle="ATS Pick" prompt="Pick PHI or ARI" sqref="F230:Q230" xr:uid="{00000000-0002-0000-0200-0000BB000000}">
       <formula1>"PHI,ARI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CAR or MIN" promptTitle="ATS Pick" prompt="Pick CAR or MIN" sqref="F231:Q231" xr:uid="{00000000-0002-0000-0200-0000BD000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CAR or MIN" promptTitle="ATS Pick" prompt="Pick CAR or MIN" sqref="F231:Q231" xr:uid="{00000000-0002-0000-0200-0000BC000000}">
       <formula1>"CAR,MIN"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BUF or NE" promptTitle="ATS Pick" prompt="Pick BUF or NE" sqref="F232:Q232" xr:uid="{00000000-0002-0000-0200-0000BE000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BUF or NE" promptTitle="ATS Pick" prompt="Pick BUF or NE" sqref="F232:Q232" xr:uid="{00000000-0002-0000-0200-0000BD000000}">
       <formula1>"BUF,NE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be HOU or PIT" promptTitle="ATS Pick" prompt="Pick HOU or PIT" sqref="F233:Q233" xr:uid="{00000000-0002-0000-0200-0000BF000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be HOU or PIT" promptTitle="ATS Pick" prompt="Pick HOU or PIT" sqref="F233:Q233" xr:uid="{00000000-0002-0000-0200-0000BE000000}">
       <formula1>"HOU,PIT"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DAL or SEA" promptTitle="ATS Pick" prompt="Pick DAL or SEA" sqref="F234:Q234" xr:uid="{00000000-0002-0000-0200-0000C0000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DAL or SEA" promptTitle="ATS Pick" prompt="Pick DAL or SEA" sqref="F234:Q234" xr:uid="{00000000-0002-0000-0200-0000BF000000}">
       <formula1>"DAL,SEA"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be MIN or NE" promptTitle="ATS Pick" prompt="Pick MIN or NE" sqref="F238:Q238" xr:uid="{00000000-0002-0000-0200-0000C1000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be MIN or NE" promptTitle="ATS Pick" prompt="Pick MIN or NE" sqref="F238:Q238" xr:uid="{00000000-0002-0000-0200-0000C0000000}">
       <formula1>"MIN,NE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be ATL or CLE" promptTitle="ATS Pick" prompt="Pick ATL or CLE" sqref="F239:Q239" xr:uid="{00000000-0002-0000-0200-0000C2000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be ATL or CLE" promptTitle="ATS Pick" prompt="Pick ATL or CLE" sqref="F239:Q239" xr:uid="{00000000-0002-0000-0200-0000C1000000}">
       <formula1>"ATL,CLE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TEN or DET" promptTitle="ATS Pick" prompt="Pick TEN or DET" sqref="F240:Q240" xr:uid="{00000000-0002-0000-0200-0000C3000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TEN or DET" promptTitle="ATS Pick" prompt="Pick TEN or DET" sqref="F240:Q240" xr:uid="{00000000-0002-0000-0200-0000C2000000}">
       <formula1>"TEN,DET"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CHI or MIA" promptTitle="ATS Pick" prompt="Pick CHI or MIA" sqref="F241:Q241" xr:uid="{00000000-0002-0000-0200-0000C4000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CHI or MIA" promptTitle="ATS Pick" prompt="Pick CHI or MIA" sqref="F241:Q241" xr:uid="{00000000-0002-0000-0200-0000C3000000}">
       <formula1>"CHI,MIA"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DEN or NYJ" promptTitle="ATS Pick" prompt="Pick DEN or NYJ" sqref="F242:Q242" xr:uid="{00000000-0002-0000-0200-0000C5000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DEN or NYJ" promptTitle="ATS Pick" prompt="Pick DEN or NYJ" sqref="F242:Q242" xr:uid="{00000000-0002-0000-0200-0000C4000000}">
       <formula1>"DEN,NYJ"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be IND or PHI" promptTitle="ATS Pick" prompt="Pick IND or PHI" sqref="F243:Q243" xr:uid="{00000000-0002-0000-0200-0000C6000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be IND or PHI" promptTitle="ATS Pick" prompt="Pick IND or PHI" sqref="F243:Q243" xr:uid="{00000000-0002-0000-0200-0000C5000000}">
       <formula1>"IND,PHI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be HOU or WAS" promptTitle="ATS Pick" prompt="Pick HOU or WAS" sqref="F244:Q244" xr:uid="{00000000-0002-0000-0200-0000C7000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be HOU or WAS" promptTitle="ATS Pick" prompt="Pick HOU or WAS" sqref="F244:Q244" xr:uid="{00000000-0002-0000-0200-0000C6000000}">
       <formula1>"HOU,WAS"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NO or CAR" promptTitle="ATS Pick" prompt="Pick NO or CAR" sqref="F245:Q245" xr:uid="{00000000-0002-0000-0200-0000C8000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NO or CAR" promptTitle="ATS Pick" prompt="Pick NO or CAR" sqref="F245:Q245" xr:uid="{00000000-0002-0000-0200-0000C7000000}">
       <formula1>"NO,CAR"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TB or BAL" promptTitle="ATS Pick" prompt="Pick TB or BAL" sqref="F246:Q246" xr:uid="{00000000-0002-0000-0200-0000C9000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TB or BAL" promptTitle="ATS Pick" prompt="Pick TB or BAL" sqref="F246:Q246" xr:uid="{00000000-0002-0000-0200-0000C8000000}">
       <formula1>"TB,BAL"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LAC or LV" promptTitle="ATS Pick" prompt="Pick LAC or LV" sqref="F247:Q247" xr:uid="{00000000-0002-0000-0200-0000CA000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LAC or LV" promptTitle="ATS Pick" prompt="Pick LAC or LV" sqref="F247:Q247" xr:uid="{00000000-0002-0000-0200-0000C9000000}">
       <formula1>"LAC,LV"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be KC or CIN" promptTitle="ATS Pick" prompt="Pick KC or CIN" sqref="F248:Q248" xr:uid="{00000000-0002-0000-0200-0000CB000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be KC or CIN" promptTitle="ATS Pick" prompt="Pick KC or CIN" sqref="F248:Q248" xr:uid="{00000000-0002-0000-0200-0000CA000000}">
       <formula1>"KC,CIN"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LAR or SF" promptTitle="ATS Pick" prompt="Pick LAR or SF" sqref="F249:Q249" xr:uid="{00000000-0002-0000-0200-0000CC000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LAR or SF" promptTitle="ATS Pick" prompt="Pick LAR or SF" sqref="F249:Q249" xr:uid="{00000000-0002-0000-0200-0000CB000000}">
       <formula1>"LAR,SF"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NYG or SEA" promptTitle="ATS Pick" prompt="Pick NYG or SEA" sqref="F250:Q250" xr:uid="{00000000-0002-0000-0200-0000CD000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NYG or SEA" promptTitle="ATS Pick" prompt="Pick NYG or SEA" sqref="F250:Q250" xr:uid="{00000000-0002-0000-0200-0000CC000000}">
       <formula1>"NYG,SEA"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BUF or GB" promptTitle="ATS Pick" prompt="Pick BUF or GB" sqref="F251:Q251" xr:uid="{00000000-0002-0000-0200-0000CE000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BUF or GB" promptTitle="ATS Pick" prompt="Pick BUF or GB" sqref="F251:Q251" xr:uid="{00000000-0002-0000-0200-0000CD000000}">
       <formula1>"BUF,GB"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be PIT or JAX" promptTitle="ATS Pick" prompt="Pick PIT or JAX" sqref="F252:Q252" xr:uid="{00000000-0002-0000-0200-0000CF000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be PIT or JAX" promptTitle="ATS Pick" prompt="Pick PIT or JAX" sqref="F252:Q252" xr:uid="{00000000-0002-0000-0200-0000CE000000}">
       <formula1>"PIT,JAX"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be SF or LAC" promptTitle="ATS Pick" prompt="Pick SF or LAC" sqref="F256:Q256" xr:uid="{00000000-0002-0000-0200-0000D0000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be SF or LAC" promptTitle="ATS Pick" prompt="Pick SF or LAC" sqref="F256:Q256" xr:uid="{00000000-0002-0000-0200-0000CF000000}">
       <formula1>"SF,LAC"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be SEA or PHI" promptTitle="ATS Pick" prompt="Pick SEA or PHI" sqref="F257:Q257" xr:uid="{00000000-0002-0000-0200-0000D1000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be SEA or PHI" promptTitle="ATS Pick" prompt="Pick SEA or PHI" sqref="F257:Q257" xr:uid="{00000000-0002-0000-0200-0000D0000000}">
       <formula1>"SEA,PHI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CHI or BUF" promptTitle="ATS Pick" prompt="Pick CHI or BUF" sqref="F258:Q258" xr:uid="{00000000-0002-0000-0200-0000D2000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CHI or BUF" promptTitle="ATS Pick" prompt="Pick CHI or BUF" sqref="F258:Q258" xr:uid="{00000000-0002-0000-0200-0000D1000000}">
       <formula1>"CHI,BUF"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be MIA or GB" promptTitle="ATS Pick" prompt="Pick MIA or GB" sqref="F259:Q259" xr:uid="{00000000-0002-0000-0200-0000D3000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be MIA or GB" promptTitle="ATS Pick" prompt="Pick MIA or GB" sqref="F259:Q259" xr:uid="{00000000-0002-0000-0200-0000D2000000}">
       <formula1>"MIA,GB"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be IND or TEN" promptTitle="ATS Pick" prompt="Pick IND or TEN" sqref="F260:Q260" xr:uid="{00000000-0002-0000-0200-0000D4000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be IND or TEN" promptTitle="ATS Pick" prompt="Pick IND or TEN" sqref="F260:Q260" xr:uid="{00000000-0002-0000-0200-0000D3000000}">
       <formula1>"IND,TEN"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CLE or NYG" promptTitle="ATS Pick" prompt="Pick CLE or NYG" sqref="F261:Q261" xr:uid="{00000000-0002-0000-0200-0000D5000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CLE or NYG" promptTitle="ATS Pick" prompt="Pick CLE or NYG" sqref="F261:Q261" xr:uid="{00000000-0002-0000-0200-0000D4000000}">
       <formula1>"CLE,NYG"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BAL or PIT" promptTitle="ATS Pick" prompt="Pick BAL or PIT" sqref="F262:Q262" xr:uid="{00000000-0002-0000-0200-0000D6000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BAL or PIT" promptTitle="ATS Pick" prompt="Pick BAL or PIT" sqref="F262:Q262" xr:uid="{00000000-0002-0000-0200-0000D5000000}">
       <formula1>"BAL,PIT"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NO or TB" promptTitle="ATS Pick" prompt="Pick NO or TB" sqref="F263:Q263" xr:uid="{00000000-0002-0000-0200-0000D7000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NO or TB" promptTitle="ATS Pick" prompt="Pick NO or TB" sqref="F263:Q263" xr:uid="{00000000-0002-0000-0200-0000D6000000}">
       <formula1>"NO,TB"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be ATL or WAS" promptTitle="ATS Pick" prompt="Pick ATL or WAS" sqref="F264:Q264" xr:uid="{00000000-0002-0000-0200-0000D8000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be ATL or WAS" promptTitle="ATS Pick" prompt="Pick ATL or WAS" sqref="F264:Q264" xr:uid="{00000000-0002-0000-0200-0000D7000000}">
       <formula1>"ATL,WAS"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CIN or CAR" promptTitle="ATS Pick" prompt="Pick CIN or CAR" sqref="F265:Q265" xr:uid="{00000000-0002-0000-0200-0000D9000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CIN or CAR" promptTitle="ATS Pick" prompt="Pick CIN or CAR" sqref="F265:Q265" xr:uid="{00000000-0002-0000-0200-0000D8000000}">
       <formula1>"CIN,CAR"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be JAX or HOU" promptTitle="ATS Pick" prompt="Pick JAX or HOU" sqref="F266:Q266" xr:uid="{00000000-0002-0000-0200-0000DA000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be JAX or HOU" promptTitle="ATS Pick" prompt="Pick JAX or HOU" sqref="F266:Q266" xr:uid="{00000000-0002-0000-0200-0000D9000000}">
       <formula1>"JAX,HOU"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NYJ or ARI" promptTitle="ATS Pick" prompt="Pick NYJ or ARI" sqref="F267:Q267" xr:uid="{00000000-0002-0000-0200-0000DB000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NYJ or ARI" promptTitle="ATS Pick" prompt="Pick NYJ or ARI" sqref="F267:Q267" xr:uid="{00000000-0002-0000-0200-0000DA000000}">
       <formula1>"NYJ,ARI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DEN or LV" promptTitle="ATS Pick" prompt="Pick DEN or LV" sqref="F268:Q268" xr:uid="{00000000-0002-0000-0200-0000DC000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DEN or LV" promptTitle="ATS Pick" prompt="Pick DEN or LV" sqref="F268:Q268" xr:uid="{00000000-0002-0000-0200-0000DB000000}">
       <formula1>"DEN,LV"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DAL or LAR" promptTitle="ATS Pick" prompt="Pick DAL or LAR" sqref="F269:Q269" xr:uid="{00000000-0002-0000-0200-0000DD000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DAL or LAR" promptTitle="ATS Pick" prompt="Pick DAL or LAR" sqref="F269:Q269" xr:uid="{00000000-0002-0000-0200-0000DC000000}">
       <formula1>"DAL,LAR"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DET or MIN" promptTitle="ATS Pick" prompt="Pick DET or MIN" sqref="F270:Q270" xr:uid="{00000000-0002-0000-0200-0000DE000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DET or MIN" promptTitle="ATS Pick" prompt="Pick DET or MIN" sqref="F270:Q270" xr:uid="{00000000-0002-0000-0200-0000DD000000}">
       <formula1>"DET,MIN"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or KC" promptTitle="ATS Pick" prompt="Pick NE or KC" sqref="F271:Q271" xr:uid="{00000000-0002-0000-0200-0000DF000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or KC" promptTitle="ATS Pick" prompt="Pick NE or KC" sqref="F271:Q271" xr:uid="{00000000-0002-0000-0200-0000DE000000}">
       <formula1>"NE,KC"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be HOU or PHI" promptTitle="ATS Pick" prompt="Pick HOU or PHI" sqref="F275:Q275" xr:uid="{00000000-0002-0000-0200-0000E0000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be HOU or PHI" promptTitle="ATS Pick" prompt="Pick HOU or PHI" sqref="F275:Q275" xr:uid="{00000000-0002-0000-0200-0000DF000000}">
       <formula1>"HOU,PHI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be GB or CHI" promptTitle="ATS Pick" prompt="Pick GB or CHI" sqref="F276:Q276" xr:uid="{00000000-0002-0000-0200-0000E1000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be GB or CHI" promptTitle="ATS Pick" prompt="Pick GB or CHI" sqref="F276:Q276" xr:uid="{00000000-0002-0000-0200-0000E0000000}">
       <formula1>"GB,CHI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BUF or DEN" promptTitle="ATS Pick" prompt="Pick BUF or DEN" sqref="F277:Q277" xr:uid="{00000000-0002-0000-0200-0000E2000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BUF or DEN" promptTitle="ATS Pick" prompt="Pick BUF or DEN" sqref="F277:Q277" xr:uid="{00000000-0002-0000-0200-0000E1000000}">
       <formula1>"BUF,DEN"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LAR or SEA" promptTitle="ATS Pick" prompt="Pick LAR or SEA" sqref="F278:Q278" xr:uid="{00000000-0002-0000-0200-0000E3000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LAR or SEA" promptTitle="ATS Pick" prompt="Pick LAR or SEA" sqref="F278:Q278" xr:uid="{00000000-0002-0000-0200-0000E2000000}">
       <formula1>"LAR,SEA"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LAC or MIA" promptTitle="ATS Pick" prompt="Pick LAC or MIA" sqref="F279:Q279" xr:uid="{00000000-0002-0000-0200-0000E4000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LAC or MIA" promptTitle="ATS Pick" prompt="Pick LAC or MIA" sqref="F279:Q279" xr:uid="{00000000-0002-0000-0200-0000E3000000}">
       <formula1>"LAC,MIA"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be ARI or NO" promptTitle="ATS Pick" prompt="Pick ARI or NO" sqref="F280:Q280" xr:uid="{00000000-0002-0000-0200-0000E5000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be ARI or NO" promptTitle="ATS Pick" prompt="Pick ARI or NO" sqref="F280:Q280" xr:uid="{00000000-0002-0000-0200-0000E4000000}">
       <formula1>"ARI,NO"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or NYJ" promptTitle="ATS Pick" prompt="Pick NE or NYJ" sqref="F281:Q281" xr:uid="{00000000-0002-0000-0200-0000E6000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or NYJ" promptTitle="ATS Pick" prompt="Pick NE or NYJ" sqref="F281:Q281" xr:uid="{00000000-0002-0000-0200-0000E5000000}">
       <formula1>"NE,NYJ"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CLE or BAL" promptTitle="ATS Pick" prompt="Pick CLE or BAL" sqref="F282:Q282" xr:uid="{00000000-0002-0000-0200-0000E7000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CLE or BAL" promptTitle="ATS Pick" prompt="Pick CLE or BAL" sqref="F282:Q282" xr:uid="{00000000-0002-0000-0200-0000E6000000}">
       <formula1>"CLE,BAL"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TEN or LV" promptTitle="ATS Pick" prompt="Pick TEN or LV" sqref="F283:Q283" xr:uid="{00000000-0002-0000-0200-0000E8000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TEN or LV" promptTitle="ATS Pick" prompt="Pick TEN or LV" sqref="F283:Q283" xr:uid="{00000000-0002-0000-0200-0000E7000000}">
       <formula1>"TEN,LV"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be SF or KC" promptTitle="ATS Pick" prompt="Pick SF or KC" sqref="F284:Q284" xr:uid="{00000000-0002-0000-0200-0000E9000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be SF or KC" promptTitle="ATS Pick" prompt="Pick SF or KC" sqref="F284:Q284" xr:uid="{00000000-0002-0000-0200-0000E8000000}">
       <formula1>"SF,KC"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be JAX or DAL" promptTitle="ATS Pick" prompt="Pick JAX or DAL" sqref="F285:Q285" xr:uid="{00000000-0002-0000-0200-0000EA000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be JAX or DAL" promptTitle="ATS Pick" prompt="Pick JAX or DAL" sqref="F285:Q285" xr:uid="{00000000-0002-0000-0200-0000E9000000}">
       <formula1>"JAX,DAL"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NYG or DET" promptTitle="ATS Pick" prompt="Pick NYG or DET" sqref="F286:Q286" xr:uid="{00000000-0002-0000-0200-0000EB000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NYG or DET" promptTitle="ATS Pick" prompt="Pick NYG or DET" sqref="F286:Q286" xr:uid="{00000000-0002-0000-0200-0000EA000000}">
       <formula1>"NYG,DET"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TB or ATL" promptTitle="ATS Pick" prompt="Pick TB or ATL" sqref="F287:Q287" xr:uid="{00000000-0002-0000-0200-0000EC000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TB or ATL" promptTitle="ATS Pick" prompt="Pick TB or ATL" sqref="F287:Q287" xr:uid="{00000000-0002-0000-0200-0000EB000000}">
       <formula1>"TB,ATL"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CIN or IND" promptTitle="ATS Pick" prompt="Pick CIN or IND" sqref="F288:Q288" xr:uid="{00000000-0002-0000-0200-0000ED000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CIN or IND" promptTitle="ATS Pick" prompt="Pick CIN or IND" sqref="F288:Q288" xr:uid="{00000000-0002-0000-0200-0000EC000000}">
       <formula1>"CIN,IND"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be WAS or MIN" promptTitle="ATS Pick" prompt="Pick WAS or MIN" sqref="F289:Q289" xr:uid="{00000000-0002-0000-0200-0000EE000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be WAS or MIN" promptTitle="ATS Pick" prompt="Pick WAS or MIN" sqref="F289:Q289" xr:uid="{00000000-0002-0000-0200-0000ED000000}">
       <formula1>"WAS,MIN"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CAR or PIT" promptTitle="ATS Pick" prompt="Pick CAR or PIT" sqref="F290:Q290" xr:uid="{00000000-0002-0000-0200-0000EF000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CAR or PIT" promptTitle="ATS Pick" prompt="Pick CAR or PIT" sqref="F290:Q290" xr:uid="{00000000-0002-0000-0200-0000EE000000}">
       <formula1>"CAR,PIT"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BAL or CIN" promptTitle="ATS Pick" prompt="Pick BAL or CIN" sqref="F294:Q294" xr:uid="{00000000-0002-0000-0200-0000F0000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BAL or CIN" promptTitle="ATS Pick" prompt="Pick BAL or CIN" sqref="F294:Q294" xr:uid="{00000000-0002-0000-0200-0000EF000000}">
       <formula1>"BAL,CIN"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NO or ATL" promptTitle="ATS Pick" prompt="Pick NO or ATL" sqref="F295:Q295" xr:uid="{00000000-0002-0000-0200-0000F1000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NO or ATL" promptTitle="ATS Pick" prompt="Pick NO or ATL" sqref="F295:Q295" xr:uid="{00000000-0002-0000-0200-0000F0000000}">
       <formula1>"NO,ATL"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be IND or CLE" promptTitle="ATS Pick" prompt="Pick IND or CLE" sqref="F296:Q296" xr:uid="{00000000-0002-0000-0200-0000F2000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be IND or CLE" promptTitle="ATS Pick" prompt="Pick IND or CLE" sqref="F296:Q296" xr:uid="{00000000-0002-0000-0200-0000F1000000}">
       <formula1>"IND,CLE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NYG or DAL" promptTitle="ATS Pick" prompt="Pick NYG or DAL" sqref="F297:Q297" xr:uid="{00000000-0002-0000-0200-0000F3000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NYG or DAL" promptTitle="ATS Pick" prompt="Pick NYG or DAL" sqref="F297:Q297" xr:uid="{00000000-0002-0000-0200-0000F2000000}">
       <formula1>"NYG,DAL"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be PIT or TEN" promptTitle="ATS Pick" prompt="Pick PIT or TEN" sqref="F298:Q298" xr:uid="{00000000-0002-0000-0200-0000F4000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be PIT or TEN" promptTitle="ATS Pick" prompt="Pick PIT or TEN" sqref="F298:Q298" xr:uid="{00000000-0002-0000-0200-0000F3000000}">
       <formula1>"PIT,TEN"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BUF or MIA" promptTitle="ATS Pick" prompt="Pick BUF or MIA" sqref="F299:Q299" xr:uid="{00000000-0002-0000-0200-0000F5000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be BUF or MIA" promptTitle="ATS Pick" prompt="Pick BUF or MIA" sqref="F299:Q299" xr:uid="{00000000-0002-0000-0200-0000F4000000}">
       <formula1>"BUF,MIA"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be MIN or NYJ" promptTitle="ATS Pick" prompt="Pick MIN or NYJ" sqref="F300:Q300" xr:uid="{00000000-0002-0000-0200-0000F6000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be MIN or NYJ" promptTitle="ATS Pick" prompt="Pick MIN or NYJ" sqref="F300:Q300" xr:uid="{00000000-0002-0000-0200-0000F5000000}">
       <formula1>"MIN,NYJ"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be SEA or CAR" promptTitle="ATS Pick" prompt="Pick SEA or CAR" sqref="F301:Q301" xr:uid="{00000000-0002-0000-0200-0000F7000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be SEA or CAR" promptTitle="ATS Pick" prompt="Pick SEA or CAR" sqref="F301:Q301" xr:uid="{00000000-0002-0000-0200-0000F6000000}">
       <formula1>"SEA,CAR"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LV or ARI" promptTitle="ATS Pick" prompt="Pick LV or ARI" sqref="F302:Q302" xr:uid="{00000000-0002-0000-0200-0000F8000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LV or ARI" promptTitle="ATS Pick" prompt="Pick LV or ARI" sqref="F302:Q302" xr:uid="{00000000-0002-0000-0200-0000F7000000}">
       <formula1>"LV,ARI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DET or CHI" promptTitle="ATS Pick" prompt="Pick DET or CHI" sqref="F303:Q303" xr:uid="{00000000-0002-0000-0200-0000F9000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DET or CHI" promptTitle="ATS Pick" prompt="Pick DET or CHI" sqref="F303:Q303" xr:uid="{00000000-0002-0000-0200-0000F8000000}">
       <formula1>"DET,CHI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be PHI or SF" promptTitle="ATS Pick" prompt="Pick PHI or SF" sqref="F304:Q304" xr:uid="{00000000-0002-0000-0200-0000FA000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be PHI or SF" promptTitle="ATS Pick" prompt="Pick PHI or SF" sqref="F304:Q304" xr:uid="{00000000-0002-0000-0200-0000F9000000}">
       <formula1>"PHI,SF"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be HOU or GB" promptTitle="ATS Pick" prompt="Pick HOU or GB" sqref="F305:Q305" xr:uid="{00000000-0002-0000-0200-0000FB000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be HOU or GB" promptTitle="ATS Pick" prompt="Pick HOU or GB" sqref="F305:Q305" xr:uid="{00000000-0002-0000-0200-0000FA000000}">
       <formula1>"HOU,GB"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DEN or NE" promptTitle="ATS Pick" prompt="Pick DEN or NE" sqref="F306:Q306" xr:uid="{00000000-0002-0000-0200-0000FC000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DEN or NE" promptTitle="ATS Pick" prompt="Pick DEN or NE" sqref="F306:Q306" xr:uid="{00000000-0002-0000-0200-0000FB000000}">
       <formula1>"DEN,NE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be WAS or JAX" promptTitle="ATS Pick" prompt="Pick WAS or JAX" sqref="F309:Q309" xr:uid="{00000000-0002-0000-0200-0000FF000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be WAS or JAX" promptTitle="ATS Pick" prompt="Pick WAS or JAX" sqref="F309:Q309" xr:uid="{00000000-0002-0000-0200-0000FC000000}">
       <formula1>"WAS,JAX"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NYJ or BUF" promptTitle="ATS Pick" prompt="Pick NYJ or BUF" sqref="F313:Q313" xr:uid="{00000000-0002-0000-0200-000000010000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NYJ or BUF" promptTitle="ATS Pick" prompt="Pick NYJ or BUF" sqref="F313:Q313" xr:uid="{00000000-0002-0000-0200-0000FD000000}">
       <formula1>"NYJ,BUF"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CLE or CIN" promptTitle="ATS Pick" prompt="Pick CLE or CIN" sqref="F314:Q314" xr:uid="{00000000-0002-0000-0200-000001010000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CLE or CIN" promptTitle="ATS Pick" prompt="Pick CLE or CIN" sqref="F314:Q314" xr:uid="{00000000-0002-0000-0200-0000FE000000}">
       <formula1>"CLE,CIN"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DET or GB" promptTitle="ATS Pick" prompt="Pick DET or GB" sqref="F316:Q316" xr:uid="{00000000-0002-0000-0200-000003010000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DET or GB" promptTitle="ATS Pick" prompt="Pick DET or GB" sqref="F316:Q316" xr:uid="{00000000-0002-0000-0200-0000FF000000}">
       <formula1>"DET,GB"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be JAX or IND" promptTitle="ATS Pick" prompt="Pick JAX or IND" sqref="F317:Q317" xr:uid="{00000000-0002-0000-0200-000004010000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be JAX or IND" promptTitle="ATS Pick" prompt="Pick JAX or IND" sqref="F317:Q317" xr:uid="{00000000-0002-0000-0200-000000010000}">
       <formula1>"JAX,IND"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LV or KC" promptTitle="ATS Pick" prompt="Pick LV or KC" sqref="F318:Q318" xr:uid="{00000000-0002-0000-0200-000005010000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be LV or KC" promptTitle="ATS Pick" prompt="Pick LV or KC" sqref="F318:Q318" xr:uid="{00000000-0002-0000-0200-000001010000}">
       <formula1>"LV,KC"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be SEA or LAC" promptTitle="ATS Pick" prompt="Pick SEA or LAC" sqref="F319:Q319" xr:uid="{00000000-0002-0000-0200-000006010000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be SEA or LAC" promptTitle="ATS Pick" prompt="Pick SEA or LAC" sqref="F319:Q319" xr:uid="{00000000-0002-0000-0200-000002010000}">
       <formula1>"SEA,LAC"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CHI or MIN" promptTitle="ATS Pick" prompt="Pick CHI or MIN" sqref="F320:Q320" xr:uid="{00000000-0002-0000-0200-000007010000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be CHI or MIN" promptTitle="ATS Pick" prompt="Pick CHI or MIN" sqref="F320:Q320" xr:uid="{00000000-0002-0000-0200-000003010000}">
       <formula1>"CHI,MIN"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be MIA or NE" promptTitle="ATS Pick" prompt="Pick MIA or NE" sqref="F321:Q321" xr:uid="{00000000-0002-0000-0200-000008010000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be MIA or NE" promptTitle="ATS Pick" prompt="Pick MIA or NE" sqref="F321:Q321" xr:uid="{00000000-0002-0000-0200-000004010000}">
       <formula1>"MIA,NE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TB or NO" promptTitle="ATS Pick" prompt="Pick TB or NO" sqref="F322:Q322" xr:uid="{00000000-0002-0000-0200-000009010000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TB or NO" promptTitle="ATS Pick" prompt="Pick TB or NO" sqref="F322:Q322" xr:uid="{00000000-0002-0000-0200-000005010000}">
       <formula1>"TB,NO"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be PHI or NYG" promptTitle="ATS Pick" prompt="Pick PHI or NYG" sqref="F323:Q323" xr:uid="{00000000-0002-0000-0200-00000A010000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be PHI or NYG" promptTitle="ATS Pick" prompt="Pick PHI or NYG" sqref="F323:Q323" xr:uid="{00000000-0002-0000-0200-000006010000}">
       <formula1>"PHI,NYG"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be SF or ARI" promptTitle="ATS Pick" prompt="Pick SF or ARI" sqref="F324:Q324" xr:uid="{00000000-0002-0000-0200-00000B010000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be SF or ARI" promptTitle="ATS Pick" prompt="Pick SF or ARI" sqref="F324:Q324" xr:uid="{00000000-0002-0000-0200-000007010000}">
       <formula1>"SF,ARI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DAL or WAS" promptTitle="ATS Pick" prompt="Pick DAL or WAS" sqref="F325:Q325" xr:uid="{00000000-0002-0000-0200-00000C010000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be DAL or WAS" promptTitle="ATS Pick" prompt="Pick DAL or WAS" sqref="F325:Q325" xr:uid="{00000000-0002-0000-0200-000008010000}">
       <formula1>"DAL,WAS"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be ATL or CAR" promptTitle="ATS Pick" prompt="Pick ATL or CAR" sqref="F326:Q326" xr:uid="{00000000-0002-0000-0200-00000D010000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be ATL or CAR" promptTitle="ATS Pick" prompt="Pick ATL or CAR" sqref="F326:Q326" xr:uid="{00000000-0002-0000-0200-000009010000}">
       <formula1>"ATL,CAR"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be PIT or BAL" promptTitle="ATS Pick" prompt="Pick PIT or BAL" sqref="F327:Q327" xr:uid="{00000000-0002-0000-0200-00000E010000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be PIT or BAL" promptTitle="ATS Pick" prompt="Pick PIT or BAL" sqref="F327:Q327" xr:uid="{00000000-0002-0000-0200-00000A010000}">
       <formula1>"PIT,BAL"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TEN or HOU" promptTitle="ATS Pick" prompt="Pick TEN or HOU" sqref="F328:Q328" xr:uid="{00000000-0002-0000-0200-00000F010000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be TEN or HOU" promptTitle="ATS Pick" prompt="Pick TEN or HOU" sqref="F328:Q328" xr:uid="{00000000-0002-0000-0200-00000B010000}">
       <formula1>"TEN,HOU"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -18245,34 +18739,34 @@
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
         <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F2" t="s">
         <v>55</v>
       </c>
       <c r="G2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18280,10 +18774,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
         <v>57</v>
@@ -18314,10 +18808,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D4" t="s">
         <v>59</v>
@@ -18348,10 +18842,10 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
         <v>61</v>
@@ -18382,10 +18876,10 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D6" t="s">
         <v>63</v>
@@ -18416,10 +18910,10 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D7" t="s">
         <v>65</v>
@@ -18450,10 +18944,10 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D8" t="s">
         <v>67</v>
@@ -18484,10 +18978,10 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D9" t="s">
         <v>69</v>
@@ -18518,10 +19012,10 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D10" t="s">
         <v>71</v>
@@ -18552,10 +19046,10 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D11" t="s">
         <v>73</v>
@@ -18586,10 +19080,10 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D12" t="s">
         <v>75</v>
@@ -18620,10 +19114,10 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D13" t="s">
         <v>77</v>
@@ -18654,10 +19148,10 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s">
         <v>79</v>
@@ -18688,10 +19182,10 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D15" t="s">
         <v>81</v>
@@ -18722,10 +19216,10 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
         <v>83</v>
@@ -18756,10 +19250,10 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
         <v>85</v>
@@ -18790,61 +19284,79 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D18" t="s">
         <v>87</v>
       </c>
+      <c r="E18">
+        <v>25</v>
+      </c>
       <c r="F18" t="s">
         <v>88</v>
       </c>
+      <c r="G18">
+        <v>26</v>
+      </c>
+      <c r="H18">
+        <v>-2.5</v>
+      </c>
       <c r="I18" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>KC</v>
       </c>
       <c r="J18" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>KC</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D19" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E19" s="24">
+        <f>IF(AND(E18&lt;&gt;"",G18&lt;&gt;""),E18+G18,"")</f>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21" t="s">
         <v>53</v>
       </c>
       <c r="E21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F21" t="s">
         <v>55</v>
       </c>
       <c r="G21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18852,10 +19364,10 @@
         <v>2</v>
       </c>
       <c r="B22" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" t="s">
         <v>123</v>
-      </c>
-      <c r="C22" t="s">
-        <v>122</v>
       </c>
       <c r="D22" t="s">
         <v>66</v>
@@ -18877,10 +19389,10 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
         <v>62</v>
@@ -18902,10 +19414,10 @@
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D24" t="s">
         <v>65</v>
@@ -18927,10 +19439,10 @@
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C25" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D25" t="s">
         <v>82</v>
@@ -18952,10 +19464,10 @@
         <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D26" t="s">
         <v>64</v>
@@ -18977,10 +19489,10 @@
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C27" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D27" t="s">
         <v>74</v>
@@ -19002,10 +19514,10 @@
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D28" t="s">
         <v>81</v>
@@ -19027,10 +19539,10 @@
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s">
         <v>71</v>
@@ -19052,10 +19564,10 @@
         <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
         <v>84</v>
@@ -19077,10 +19589,10 @@
         <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D31" t="s">
         <v>72</v>
@@ -19102,10 +19614,10 @@
         <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D32" t="s">
         <v>80</v>
@@ -19127,10 +19639,10 @@
         <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D33" t="s">
         <v>58</v>
@@ -19152,10 +19664,10 @@
         <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
         <v>83</v>
@@ -19177,10 +19689,10 @@
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
         <v>79</v>
@@ -19202,10 +19714,10 @@
         <v>2</v>
       </c>
       <c r="B36" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C36" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D36" t="s">
         <v>70</v>
@@ -19227,10 +19739,10 @@
         <v>2</v>
       </c>
       <c r="B37" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C37" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D37" t="s">
         <v>86</v>
@@ -19247,41 +19759,50 @@
         <v/>
       </c>
     </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D38" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E38" s="24" t="str">
+        <f>IF(AND(E37&lt;&gt;"",G37&lt;&gt;""),E37+G37,"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B40" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C40" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D40" t="s">
         <v>53</v>
       </c>
       <c r="E40" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F40" t="s">
         <v>55</v>
       </c>
       <c r="G40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I40" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J40" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19289,10 +19810,10 @@
         <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C41" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D41" t="s">
         <v>73</v>
@@ -19314,10 +19835,10 @@
         <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C42" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D42" t="s">
         <v>78</v>
@@ -19339,10 +19860,10 @@
         <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C43" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D43" t="s">
         <v>62</v>
@@ -19364,10 +19885,10 @@
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C44" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D44" t="s">
         <v>75</v>
@@ -19389,10 +19910,10 @@
         <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C45" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D45" t="s">
         <v>68</v>
@@ -19414,10 +19935,10 @@
         <v>3</v>
       </c>
       <c r="B46" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C46" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D46" t="s">
         <v>88</v>
@@ -19439,10 +19960,10 @@
         <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C47" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D47" t="s">
         <v>76</v>
@@ -19464,10 +19985,10 @@
         <v>3</v>
       </c>
       <c r="B48" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D48" t="s">
         <v>64</v>
@@ -19489,10 +20010,10 @@
         <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C49" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D49" t="s">
         <v>58</v>
@@ -19514,10 +20035,10 @@
         <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C50" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D50" t="s">
         <v>57</v>
@@ -19539,10 +20060,10 @@
         <v>3</v>
       </c>
       <c r="B51" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C51" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D51" t="s">
         <v>77</v>
@@ -19564,10 +20085,10 @@
         <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C52" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D52" t="s">
         <v>82</v>
@@ -19589,10 +20110,10 @@
         <v>3</v>
       </c>
       <c r="B53" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C53" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D53" t="s">
         <v>69</v>
@@ -19614,10 +20135,10 @@
         <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C54" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D54" t="s">
         <v>80</v>
@@ -19639,10 +20160,10 @@
         <v>3</v>
       </c>
       <c r="B55" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C55" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D55" t="s">
         <v>60</v>
@@ -19664,10 +20185,10 @@
         <v>3</v>
       </c>
       <c r="B56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D56" t="s">
         <v>84</v>
@@ -19684,41 +20205,50 @@
         <v/>
       </c>
     </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D57" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E57" s="24" t="str">
+        <f>IF(AND(E56&lt;&gt;"",G56&lt;&gt;""),E56+G56,"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B59" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C59" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D59" t="s">
         <v>53</v>
       </c>
       <c r="E59" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F59" t="s">
         <v>55</v>
       </c>
       <c r="G59" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H59" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I59" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J59" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19726,10 +20256,10 @@
         <v>4</v>
       </c>
       <c r="B60" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C60" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D60" t="s">
         <v>74</v>
@@ -19751,10 +20281,10 @@
         <v>4</v>
       </c>
       <c r="B61" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C61" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D61" t="s">
         <v>70</v>
@@ -19776,10 +20306,10 @@
         <v>4</v>
       </c>
       <c r="B62" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C62" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D62" t="s">
         <v>57</v>
@@ -19801,10 +20331,10 @@
         <v>4</v>
       </c>
       <c r="B63" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C63" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D63" t="s">
         <v>75</v>
@@ -19826,10 +20356,10 @@
         <v>4</v>
       </c>
       <c r="B64" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C64" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D64" t="s">
         <v>72</v>
@@ -19851,10 +20381,10 @@
         <v>4</v>
       </c>
       <c r="B65" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C65" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D65" t="s">
         <v>77</v>
@@ -19876,10 +20406,10 @@
         <v>4</v>
       </c>
       <c r="B66" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C66" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D66" t="s">
         <v>60</v>
@@ -19901,10 +20431,10 @@
         <v>4</v>
       </c>
       <c r="B67" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C67" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D67" t="s">
         <v>81</v>
@@ -19926,10 +20456,10 @@
         <v>4</v>
       </c>
       <c r="B68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C68" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D68" t="s">
         <v>76</v>
@@ -19951,10 +20481,10 @@
         <v>4</v>
       </c>
       <c r="B69" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C69" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D69" t="s">
         <v>85</v>
@@ -19976,10 +20506,10 @@
         <v>4</v>
       </c>
       <c r="B70" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C70" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D70" t="s">
         <v>79</v>
@@ -20001,10 +20531,10 @@
         <v>4</v>
       </c>
       <c r="B71" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C71" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D71" t="s">
         <v>88</v>
@@ -20026,10 +20556,10 @@
         <v>4</v>
       </c>
       <c r="B72" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C72" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D72" t="s">
         <v>87</v>
@@ -20051,10 +20581,10 @@
         <v>4</v>
       </c>
       <c r="B73" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C73" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D73" t="s">
         <v>78</v>
@@ -20076,10 +20606,10 @@
         <v>4</v>
       </c>
       <c r="B74" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C74" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D74" t="s">
         <v>66</v>
@@ -20101,10 +20631,10 @@
         <v>4</v>
       </c>
       <c r="B75" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C75" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D75" t="s">
         <v>73</v>
@@ -20121,41 +20651,50 @@
         <v/>
       </c>
     </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D76" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E76" s="24" t="str">
+        <f>IF(AND(E75&lt;&gt;"",G75&lt;&gt;""),E75+G75,"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="77" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B78" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C78" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D78" t="s">
         <v>53</v>
       </c>
       <c r="E78" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F78" t="s">
         <v>55</v>
       </c>
       <c r="G78" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H78" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I78" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J78" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20163,10 +20702,10 @@
         <v>5</v>
       </c>
       <c r="B79" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C79" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D79" t="s">
         <v>63</v>
@@ -20188,10 +20727,10 @@
         <v>5</v>
       </c>
       <c r="B80" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C80" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D80" t="s">
         <v>84</v>
@@ -20213,10 +20752,10 @@
         <v>5</v>
       </c>
       <c r="B81" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C81" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D81" t="s">
         <v>68</v>
@@ -20238,10 +20777,10 @@
         <v>5</v>
       </c>
       <c r="B82" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C82" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D82" t="s">
         <v>64</v>
@@ -20263,10 +20802,10 @@
         <v>5</v>
       </c>
       <c r="B83" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C83" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D83" t="s">
         <v>80</v>
@@ -20288,10 +20827,10 @@
         <v>5</v>
       </c>
       <c r="B84" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C84" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D84" t="s">
         <v>82</v>
@@ -20313,10 +20852,10 @@
         <v>5</v>
       </c>
       <c r="B85" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C85" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D85" t="s">
         <v>71</v>
@@ -20338,10 +20877,10 @@
         <v>5</v>
       </c>
       <c r="B86" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C86" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D86" t="s">
         <v>70</v>
@@ -20363,10 +20902,10 @@
         <v>5</v>
       </c>
       <c r="B87" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C87" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D87" t="s">
         <v>86</v>
@@ -20388,10 +20927,10 @@
         <v>5</v>
       </c>
       <c r="B88" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C88" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D88" t="s">
         <v>87</v>
@@ -20413,10 +20952,10 @@
         <v>5</v>
       </c>
       <c r="B89" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C89" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D89" t="s">
         <v>61</v>
@@ -20438,10 +20977,10 @@
         <v>5</v>
       </c>
       <c r="B90" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C90" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D90" t="s">
         <v>66</v>
@@ -20463,10 +21002,10 @@
         <v>5</v>
       </c>
       <c r="B91" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C91" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D91" t="s">
         <v>59</v>
@@ -20488,10 +21027,10 @@
         <v>5</v>
       </c>
       <c r="B92" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C92" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D92" t="s">
         <v>69</v>
@@ -20513,10 +21052,10 @@
         <v>5</v>
       </c>
       <c r="B93" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C93" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D93" t="s">
         <v>67</v>
@@ -20533,41 +21072,50 @@
         <v/>
       </c>
     </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D94" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E94" s="24" t="str">
+        <f>IF(AND(E93&lt;&gt;"",G93&lt;&gt;""),E93+G93,"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="95" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B96" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C96" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D96" t="s">
         <v>53</v>
       </c>
       <c r="E96" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F96" t="s">
         <v>55</v>
       </c>
       <c r="G96" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H96" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I96" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J96" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20575,10 +21123,10 @@
         <v>6</v>
       </c>
       <c r="B97" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C97" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D97" t="s">
         <v>58</v>
@@ -20600,10 +21148,10 @@
         <v>6</v>
       </c>
       <c r="B98" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C98" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D98" t="s">
         <v>68</v>
@@ -20625,10 +21173,10 @@
         <v>6</v>
       </c>
       <c r="B99" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C99" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D99" t="s">
         <v>61</v>
@@ -20650,10 +21198,10 @@
         <v>6</v>
       </c>
       <c r="B100" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C100" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D100" t="s">
         <v>69</v>
@@ -20675,10 +21223,10 @@
         <v>6</v>
       </c>
       <c r="B101" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C101" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D101" t="s">
         <v>76</v>
@@ -20700,10 +21248,10 @@
         <v>6</v>
       </c>
       <c r="B102" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C102" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D102" t="s">
         <v>75</v>
@@ -20725,10 +21273,10 @@
         <v>6</v>
       </c>
       <c r="B103" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C103" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D103" t="s">
         <v>65</v>
@@ -20750,10 +21298,10 @@
         <v>6</v>
       </c>
       <c r="B104" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C104" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D104" t="s">
         <v>62</v>
@@ -20775,10 +21323,10 @@
         <v>6</v>
       </c>
       <c r="B105" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C105" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D105" t="s">
         <v>74</v>
@@ -20800,10 +21348,10 @@
         <v>6</v>
       </c>
       <c r="B106" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C106" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D106" t="s">
         <v>77</v>
@@ -20825,10 +21373,10 @@
         <v>6</v>
       </c>
       <c r="B107" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C107" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D107" t="s">
         <v>60</v>
@@ -20850,10 +21398,10 @@
         <v>6</v>
       </c>
       <c r="B108" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C108" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D108" t="s">
         <v>67</v>
@@ -20875,10 +21423,10 @@
         <v>6</v>
       </c>
       <c r="B109" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C109" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D109" t="s">
         <v>85</v>
@@ -20900,10 +21448,10 @@
         <v>6</v>
       </c>
       <c r="B110" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C110" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D110" t="s">
         <v>83</v>
@@ -20920,41 +21468,50 @@
         <v/>
       </c>
     </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D111" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E111" s="24" t="str">
+        <f>IF(AND(E110&lt;&gt;"",G110&lt;&gt;""),E110+G110,"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="112" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B113" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C113" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D113" t="s">
         <v>53</v>
       </c>
       <c r="E113" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F113" t="s">
         <v>55</v>
       </c>
       <c r="G113" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H113" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I113" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J113" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20962,10 +21519,10 @@
         <v>7</v>
       </c>
       <c r="B114" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C114" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D114" t="s">
         <v>57</v>
@@ -20987,10 +21544,10 @@
         <v>7</v>
       </c>
       <c r="B115" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C115" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D115" t="s">
         <v>74</v>
@@ -21012,10 +21569,10 @@
         <v>7</v>
       </c>
       <c r="B116" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C116" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D116" t="s">
         <v>59</v>
@@ -21037,10 +21594,10 @@
         <v>7</v>
       </c>
       <c r="B117" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C117" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D117" t="s">
         <v>71</v>
@@ -21062,10 +21619,10 @@
         <v>7</v>
       </c>
       <c r="B118" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C118" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D118" t="s">
         <v>70</v>
@@ -21087,10 +21644,10 @@
         <v>7</v>
       </c>
       <c r="B119" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C119" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D119" t="s">
         <v>79</v>
@@ -21112,10 +21669,10 @@
         <v>7</v>
       </c>
       <c r="B120" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C120" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D120" t="s">
         <v>63</v>
@@ -21137,10 +21694,10 @@
         <v>7</v>
       </c>
       <c r="B121" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C121" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D121" t="s">
         <v>64</v>
@@ -21162,10 +21719,10 @@
         <v>7</v>
       </c>
       <c r="B122" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C122" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D122" t="s">
         <v>86</v>
@@ -21187,10 +21744,10 @@
         <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C123" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D123" t="s">
         <v>87</v>
@@ -21212,10 +21769,10 @@
         <v>7</v>
       </c>
       <c r="B124" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C124" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D124" t="s">
         <v>81</v>
@@ -21237,10 +21794,10 @@
         <v>7</v>
       </c>
       <c r="B125" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C125" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D125" t="s">
         <v>60</v>
@@ -21262,10 +21819,10 @@
         <v>7</v>
       </c>
       <c r="B126" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C126" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D126" t="s">
         <v>88</v>
@@ -21287,10 +21844,10 @@
         <v>7</v>
       </c>
       <c r="B127" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C127" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D127" t="s">
         <v>85</v>
@@ -21307,41 +21864,50 @@
         <v/>
       </c>
     </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D128" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E128" s="24" t="str">
+        <f>IF(AND(E127&lt;&gt;"",G127&lt;&gt;""),E127+G127,"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="129" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B130" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C130" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D130" t="s">
         <v>53</v>
       </c>
       <c r="E130" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F130" t="s">
         <v>55</v>
       </c>
       <c r="G130" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H130" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I130" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J130" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="131" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21349,10 +21915,10 @@
         <v>8</v>
       </c>
       <c r="B131" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C131" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D131" t="s">
         <v>62</v>
@@ -21374,10 +21940,10 @@
         <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C132" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D132" t="s">
         <v>69</v>
@@ -21399,10 +21965,10 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C133" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D133" t="s">
         <v>76</v>
@@ -21424,10 +21990,10 @@
         <v>8</v>
       </c>
       <c r="B134" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C134" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D134" t="s">
         <v>77</v>
@@ -21449,10 +22015,10 @@
         <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C135" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D135" t="s">
         <v>82</v>
@@ -21474,10 +22040,10 @@
         <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C136" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D136" t="s">
         <v>80</v>
@@ -21499,10 +22065,10 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C137" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D137" t="s">
         <v>71</v>
@@ -21524,10 +22090,10 @@
         <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C138" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D138" t="s">
         <v>73</v>
@@ -21549,10 +22115,10 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C139" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D139" t="s">
         <v>70</v>
@@ -21574,10 +22140,10 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C140" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D140" t="s">
         <v>60</v>
@@ -21599,10 +22165,10 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C141" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D141" t="s">
         <v>88</v>
@@ -21624,10 +22190,10 @@
         <v>8</v>
       </c>
       <c r="B142" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C142" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D142" t="s">
         <v>57</v>
@@ -21649,10 +22215,10 @@
         <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C143" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D143" t="s">
         <v>84</v>
@@ -21674,10 +22240,10 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C144" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D144" t="s">
         <v>61</v>
@@ -21694,41 +22260,50 @@
         <v/>
       </c>
     </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D145" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E145" s="24" t="str">
+        <f>IF(AND(E144&lt;&gt;"",G144&lt;&gt;""),E144+G144,"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="146" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="147" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B147" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C147" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D147" t="s">
         <v>53</v>
       </c>
       <c r="E147" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F147" t="s">
         <v>55</v>
       </c>
       <c r="G147" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H147" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I147" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J147" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="148" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21736,10 +22311,10 @@
         <v>9</v>
       </c>
       <c r="B148" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C148" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D148" t="s">
         <v>72</v>
@@ -21761,10 +22336,10 @@
         <v>9</v>
       </c>
       <c r="B149" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C149" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D149" t="s">
         <v>64</v>
@@ -21786,10 +22361,10 @@
         <v>9</v>
       </c>
       <c r="B150" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C150" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D150" t="s">
         <v>85</v>
@@ -21811,10 +22386,10 @@
         <v>9</v>
       </c>
       <c r="B151" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C151" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D151" t="s">
         <v>75</v>
@@ -21836,10 +22411,10 @@
         <v>9</v>
       </c>
       <c r="B152" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C152" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D152" t="s">
         <v>66</v>
@@ -21861,10 +22436,10 @@
         <v>9</v>
       </c>
       <c r="B153" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C153" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D153" t="s">
         <v>71</v>
@@ -21886,10 +22461,10 @@
         <v>9</v>
       </c>
       <c r="B154" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C154" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D154" t="s">
         <v>86</v>
@@ -21911,10 +22486,10 @@
         <v>9</v>
       </c>
       <c r="B155" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C155" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D155" t="s">
         <v>60</v>
@@ -21936,10 +22511,10 @@
         <v>9</v>
       </c>
       <c r="B156" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C156" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D156" t="s">
         <v>87</v>
@@ -21961,10 +22536,10 @@
         <v>9</v>
       </c>
       <c r="B157" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C157" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D157" t="s">
         <v>68</v>
@@ -21986,10 +22561,10 @@
         <v>9</v>
       </c>
       <c r="B158" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C158" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D158" t="s">
         <v>80</v>
@@ -22011,10 +22586,10 @@
         <v>9</v>
       </c>
       <c r="B159" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C159" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D159" t="s">
         <v>81</v>
@@ -22036,10 +22611,10 @@
         <v>9</v>
       </c>
       <c r="B160" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C160" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D160" t="s">
         <v>77</v>
@@ -22061,10 +22636,10 @@
         <v>9</v>
       </c>
       <c r="B161" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C161" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D161" t="s">
         <v>63</v>
@@ -22086,10 +22661,10 @@
         <v>9</v>
       </c>
       <c r="B162" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C162" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D162" t="s">
         <v>67</v>
@@ -22106,41 +22681,50 @@
         <v/>
       </c>
     </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D163" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E163" s="24" t="str">
+        <f>IF(AND(E162&lt;&gt;"",G162&lt;&gt;""),E162+G162,"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="164" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="165" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B165" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C165" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D165" t="s">
         <v>53</v>
       </c>
       <c r="E165" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F165" t="s">
         <v>55</v>
       </c>
       <c r="G165" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H165" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I165" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J165" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="166" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22148,10 +22732,10 @@
         <v>10</v>
       </c>
       <c r="B166" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C166" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D166" t="s">
         <v>83</v>
@@ -22173,10 +22757,10 @@
         <v>10</v>
       </c>
       <c r="B167" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C167" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D167" t="s">
         <v>57</v>
@@ -22198,10 +22782,10 @@
         <v>10</v>
       </c>
       <c r="B168" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C168" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D168" t="s">
         <v>88</v>
@@ -22223,10 +22807,10 @@
         <v>10</v>
       </c>
       <c r="B169" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C169" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D169" t="s">
         <v>68</v>
@@ -22248,10 +22832,10 @@
         <v>10</v>
       </c>
       <c r="B170" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C170" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D170" t="s">
         <v>82</v>
@@ -22273,10 +22857,10 @@
         <v>10</v>
       </c>
       <c r="B171" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C171" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D171" t="s">
         <v>72</v>
@@ -22298,10 +22882,10 @@
         <v>10</v>
       </c>
       <c r="B172" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C172" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D172" t="s">
         <v>79</v>
@@ -22323,10 +22907,10 @@
         <v>10</v>
       </c>
       <c r="B173" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C173" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D173" t="s">
         <v>62</v>
@@ -22348,10 +22932,10 @@
         <v>10</v>
       </c>
       <c r="B174" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C174" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D174" t="s">
         <v>67</v>
@@ -22373,10 +22957,10 @@
         <v>10</v>
       </c>
       <c r="B175" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C175" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D175" t="s">
         <v>58</v>
@@ -22398,10 +22982,10 @@
         <v>10</v>
       </c>
       <c r="B176" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C176" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D176" t="s">
         <v>60</v>
@@ -22423,10 +23007,10 @@
         <v>10</v>
       </c>
       <c r="B177" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C177" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D177" t="s">
         <v>59</v>
@@ -22448,10 +23032,10 @@
         <v>10</v>
       </c>
       <c r="B178" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C178" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D178" t="s">
         <v>74</v>
@@ -22473,10 +23057,10 @@
         <v>10</v>
       </c>
       <c r="B179" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C179" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D179" t="s">
         <v>78</v>
@@ -22493,41 +23077,50 @@
         <v/>
       </c>
     </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D180" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E180" s="24" t="str">
+        <f>IF(AND(E179&lt;&gt;"",G179&lt;&gt;""),E179+G179,"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="181" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="182" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B182" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C182" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D182" t="s">
         <v>53</v>
       </c>
       <c r="E182" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F182" t="s">
         <v>55</v>
       </c>
       <c r="G182" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H182" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I182" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J182" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="183" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22535,10 +23128,10 @@
         <v>11</v>
       </c>
       <c r="B183" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C183" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D183" t="s">
         <v>70</v>
@@ -22560,10 +23153,10 @@
         <v>11</v>
       </c>
       <c r="B184" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C184" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D184" t="s">
         <v>79</v>
@@ -22585,10 +23178,10 @@
         <v>11</v>
       </c>
       <c r="B185" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C185" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D185" t="s">
         <v>65</v>
@@ -22610,10 +23203,10 @@
         <v>11</v>
       </c>
       <c r="B186" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C186" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D186" t="s">
         <v>76</v>
@@ -22635,10 +23228,10 @@
         <v>11</v>
       </c>
       <c r="B187" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C187" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D187" t="s">
         <v>63</v>
@@ -22660,10 +23253,10 @@
         <v>11</v>
       </c>
       <c r="B188" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C188" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D188" t="s">
         <v>77</v>
@@ -22685,10 +23278,10 @@
         <v>11</v>
       </c>
       <c r="B189" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C189" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D189" t="s">
         <v>72</v>
@@ -22710,10 +23303,10 @@
         <v>11</v>
       </c>
       <c r="B190" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C190" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D190" t="s">
         <v>69</v>
@@ -22735,10 +23328,10 @@
         <v>11</v>
       </c>
       <c r="B191" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C191" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D191" t="s">
         <v>75</v>
@@ -22760,10 +23353,10 @@
         <v>11</v>
       </c>
       <c r="B192" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C192" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D192" t="s">
         <v>80</v>
@@ -22785,10 +23378,10 @@
         <v>11</v>
       </c>
       <c r="B193" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C193" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D193" t="s">
         <v>74</v>
@@ -22810,10 +23403,10 @@
         <v>11</v>
       </c>
       <c r="B194" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C194" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D194" t="s">
         <v>82</v>
@@ -22835,10 +23428,10 @@
         <v>11</v>
       </c>
       <c r="B195" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C195" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D195" t="s">
         <v>64</v>
@@ -22855,41 +23448,50 @@
         <v/>
       </c>
     </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D196" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E196" s="24" t="str">
+        <f>IF(AND(E195&lt;&gt;"",G195&lt;&gt;""),E195+G195,"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="197" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="198" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B198" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C198" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D198" t="s">
         <v>53</v>
       </c>
       <c r="E198" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F198" t="s">
         <v>55</v>
       </c>
       <c r="G198" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H198" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I198" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J198" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="199" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22897,10 +23499,10 @@
         <v>12</v>
       </c>
       <c r="B199" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C199" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D199" t="s">
         <v>81</v>
@@ -22922,10 +23524,10 @@
         <v>12</v>
       </c>
       <c r="B200" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C200" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D200" t="s">
         <v>61</v>
@@ -22947,10 +23549,10 @@
         <v>12</v>
       </c>
       <c r="B201" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C201" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D201" t="s">
         <v>84</v>
@@ -22972,10 +23574,10 @@
         <v>12</v>
       </c>
       <c r="B202" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C202" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D202" t="s">
         <v>88</v>
@@ -22997,10 +23599,10 @@
         <v>12</v>
       </c>
       <c r="B203" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C203" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D203" t="s">
         <v>87</v>
@@ -23022,10 +23624,10 @@
         <v>12</v>
       </c>
       <c r="B204" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C204" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D204" t="s">
         <v>65</v>
@@ -23047,10 +23649,10 @@
         <v>12</v>
       </c>
       <c r="B205" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C205" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D205" t="s">
         <v>80</v>
@@ -23072,10 +23674,10 @@
         <v>12</v>
       </c>
       <c r="B206" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C206" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D206" t="s">
         <v>86</v>
@@ -23097,10 +23699,10 @@
         <v>12</v>
       </c>
       <c r="B207" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C207" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D207" t="s">
         <v>75</v>
@@ -23122,10 +23724,10 @@
         <v>12</v>
       </c>
       <c r="B208" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C208" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D208" t="s">
         <v>73</v>
@@ -23147,10 +23749,10 @@
         <v>12</v>
       </c>
       <c r="B209" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C209" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D209" t="s">
         <v>69</v>
@@ -23172,10 +23774,10 @@
         <v>12</v>
       </c>
       <c r="B210" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C210" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D210" t="s">
         <v>76</v>
@@ -23197,10 +23799,10 @@
         <v>12</v>
       </c>
       <c r="B211" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C211" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D211" t="s">
         <v>83</v>
@@ -23222,10 +23824,10 @@
         <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C212" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D212" t="s">
         <v>58</v>
@@ -23247,10 +23849,10 @@
         <v>12</v>
       </c>
       <c r="B213" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C213" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D213" t="s">
         <v>57</v>
@@ -23272,10 +23874,10 @@
         <v>12</v>
       </c>
       <c r="B214" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C214" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D214" t="s">
         <v>62</v>
@@ -23292,41 +23894,50 @@
         <v/>
       </c>
     </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D215" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E215" s="24" t="str">
+        <f>IF(AND(E214&lt;&gt;"",G214&lt;&gt;""),E214+G214,"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="216" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="217" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B217" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C217" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D217" t="s">
         <v>53</v>
       </c>
       <c r="E217" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F217" t="s">
         <v>55</v>
       </c>
       <c r="G217" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H217" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I217" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J217" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="218" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23334,10 +23945,10 @@
         <v>13</v>
       </c>
       <c r="B218" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C218" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D218" t="s">
         <v>88</v>
@@ -23359,10 +23970,10 @@
         <v>13</v>
       </c>
       <c r="B219" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C219" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D219" t="s">
         <v>66</v>
@@ -23384,10 +23995,10 @@
         <v>13</v>
       </c>
       <c r="B220" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C220" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D220" t="s">
         <v>72</v>
@@ -23409,10 +24020,10 @@
         <v>13</v>
       </c>
       <c r="B221" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C221" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D221" t="s">
         <v>64</v>
@@ -23434,10 +24045,10 @@
         <v>13</v>
       </c>
       <c r="B222" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C222" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D222" t="s">
         <v>83</v>
@@ -23459,10 +24070,10 @@
         <v>13</v>
       </c>
       <c r="B223" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C223" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D223" t="s">
         <v>81</v>
@@ -23484,10 +24095,10 @@
         <v>13</v>
       </c>
       <c r="B224" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C224" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D224" t="s">
         <v>59</v>
@@ -23509,10 +24120,10 @@
         <v>13</v>
       </c>
       <c r="B225" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C225" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D225" t="s">
         <v>60</v>
@@ -23534,10 +24145,10 @@
         <v>13</v>
       </c>
       <c r="B226" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C226" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D226" t="s">
         <v>79</v>
@@ -23559,10 +24170,10 @@
         <v>13</v>
       </c>
       <c r="B227" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C227" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D227" t="s">
         <v>84</v>
@@ -23584,10 +24195,10 @@
         <v>13</v>
       </c>
       <c r="B228" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C228" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D228" t="s">
         <v>62</v>
@@ -23609,10 +24220,10 @@
         <v>13</v>
       </c>
       <c r="B229" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C229" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D229" t="s">
         <v>67</v>
@@ -23634,10 +24245,10 @@
         <v>13</v>
       </c>
       <c r="B230" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C230" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D230" t="s">
         <v>68</v>
@@ -23659,10 +24270,10 @@
         <v>13</v>
       </c>
       <c r="B231" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C231" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D231" t="s">
         <v>85</v>
@@ -23679,41 +24290,50 @@
         <v/>
       </c>
     </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D232" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E232" s="24" t="str">
+        <f>IF(AND(E231&lt;&gt;"",G231&lt;&gt;""),E231+G231,"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="233" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="234" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B234" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C234" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D234" t="s">
         <v>53</v>
       </c>
       <c r="E234" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F234" t="s">
         <v>55</v>
       </c>
       <c r="G234" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H234" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I234" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J234" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="235" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23721,10 +24341,10 @@
         <v>14</v>
       </c>
       <c r="B235" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C235" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D235" t="s">
         <v>82</v>
@@ -23746,10 +24366,10 @@
         <v>14</v>
       </c>
       <c r="B236" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C236" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D236" t="s">
         <v>73</v>
@@ -23771,10 +24391,10 @@
         <v>14</v>
       </c>
       <c r="B237" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C237" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D237" t="s">
         <v>76</v>
@@ -23796,10 +24416,10 @@
         <v>14</v>
       </c>
       <c r="B238" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C238" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D238" t="s">
         <v>61</v>
@@ -23821,10 +24441,10 @@
         <v>14</v>
       </c>
       <c r="B239" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C239" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D239" t="s">
         <v>87</v>
@@ -23846,10 +24466,10 @@
         <v>14</v>
       </c>
       <c r="B240" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C240" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D240" t="s">
         <v>70</v>
@@ -23871,10 +24491,10 @@
         <v>14</v>
       </c>
       <c r="B241" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C241" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D241" t="s">
         <v>68</v>
@@ -23896,10 +24516,10 @@
         <v>14</v>
       </c>
       <c r="B242" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C242" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D242" t="s">
         <v>65</v>
@@ -23921,10 +24541,10 @@
         <v>14</v>
       </c>
       <c r="B243" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C243" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D243" t="s">
         <v>63</v>
@@ -23946,10 +24566,10 @@
         <v>14</v>
       </c>
       <c r="B244" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C244" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D244" t="s">
         <v>78</v>
@@ -23971,10 +24591,10 @@
         <v>14</v>
       </c>
       <c r="B245" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C245" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D245" t="s">
         <v>88</v>
@@ -23996,10 +24616,10 @@
         <v>14</v>
       </c>
       <c r="B246" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C246" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D246" t="s">
         <v>60</v>
@@ -24021,10 +24641,10 @@
         <v>14</v>
       </c>
       <c r="B247" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C247" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D247" t="s">
         <v>86</v>
@@ -24046,10 +24666,10 @@
         <v>14</v>
       </c>
       <c r="B248" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C248" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D248" t="s">
         <v>67</v>
@@ -24071,10 +24691,10 @@
         <v>14</v>
       </c>
       <c r="B249" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C249" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D249" t="s">
         <v>74</v>
@@ -24091,41 +24711,50 @@
         <v/>
       </c>
     </row>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D250" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E250" s="24" t="str">
+        <f>IF(AND(E249&lt;&gt;"",G249&lt;&gt;""),E249+G249,"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="251" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="252" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B252" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C252" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D252" t="s">
         <v>53</v>
       </c>
       <c r="E252" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F252" t="s">
         <v>55</v>
       </c>
       <c r="G252" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H252" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I252" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J252" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="253" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24133,10 +24762,10 @@
         <v>15</v>
       </c>
       <c r="B253" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C253" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D253" t="s">
         <v>59</v>
@@ -24158,10 +24787,10 @@
         <v>15</v>
       </c>
       <c r="B254" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C254" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D254" t="s">
         <v>58</v>
@@ -24183,10 +24812,10 @@
         <v>15</v>
       </c>
       <c r="B255" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C255" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D255" t="s">
         <v>61</v>
@@ -24208,10 +24837,10 @@
         <v>15</v>
       </c>
       <c r="B256" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C256" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D256" t="s">
         <v>79</v>
@@ -24233,10 +24862,10 @@
         <v>15</v>
       </c>
       <c r="B257" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C257" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D257" t="s">
         <v>70</v>
@@ -24258,10 +24887,10 @@
         <v>15</v>
       </c>
       <c r="B258" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C258" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D258" t="s">
         <v>71</v>
@@ -24283,10 +24912,10 @@
         <v>15</v>
       </c>
       <c r="B259" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C259" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D259" t="s">
         <v>69</v>
@@ -24308,10 +24937,10 @@
         <v>15</v>
       </c>
       <c r="B260" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C260" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D260" t="s">
         <v>65</v>
@@ -24333,10 +24962,10 @@
         <v>15</v>
       </c>
       <c r="B261" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C261" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D261" t="s">
         <v>73</v>
@@ -24358,10 +24987,10 @@
         <v>15</v>
       </c>
       <c r="B262" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C262" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D262" t="s">
         <v>64</v>
@@ -24383,10 +25012,10 @@
         <v>15</v>
       </c>
       <c r="B263" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C263" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D263" t="s">
         <v>72</v>
@@ -24408,10 +25037,10 @@
         <v>15</v>
       </c>
       <c r="B264" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C264" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D264" t="s">
         <v>75</v>
@@ -24433,10 +25062,10 @@
         <v>15</v>
       </c>
       <c r="B265" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C265" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D265" t="s">
         <v>87</v>
@@ -24458,10 +25087,10 @@
         <v>15</v>
       </c>
       <c r="B266" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C266" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D266" t="s">
         <v>85</v>
@@ -24483,10 +25112,10 @@
         <v>15</v>
       </c>
       <c r="B267" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C267" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D267" t="s">
         <v>66</v>
@@ -24508,10 +25137,10 @@
         <v>15</v>
       </c>
       <c r="B268" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C268" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D268" t="s">
         <v>57</v>
@@ -24528,41 +25157,50 @@
         <v/>
       </c>
     </row>
+    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D269" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E269" s="24" t="str">
+        <f>IF(AND(E268&lt;&gt;"",G268&lt;&gt;""),E268+G268,"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="270" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="271" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B271" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C271" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D271" t="s">
         <v>53</v>
       </c>
       <c r="E271" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F271" t="s">
         <v>55</v>
       </c>
       <c r="G271" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H271" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I271" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J271" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="272" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24570,10 +25208,10 @@
         <v>16</v>
       </c>
       <c r="B272" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C272" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D272" t="s">
         <v>68</v>
@@ -24595,10 +25233,10 @@
         <v>16</v>
       </c>
       <c r="B273" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C273" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D273" t="s">
         <v>81</v>
@@ -24620,10 +25258,10 @@
         <v>16</v>
       </c>
       <c r="B274" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C274" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D274" t="s">
         <v>67</v>
@@ -24645,10 +25283,10 @@
         <v>16</v>
       </c>
       <c r="B275" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C275" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D275" t="s">
         <v>60</v>
@@ -24670,10 +25308,10 @@
         <v>16</v>
       </c>
       <c r="B276" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C276" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D276" t="s">
         <v>78</v>
@@ -24695,10 +25333,10 @@
         <v>16</v>
       </c>
       <c r="B277" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C277" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D277" t="s">
         <v>77</v>
@@ -24720,10 +25358,10 @@
         <v>16</v>
       </c>
       <c r="B278" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C278" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D278" t="s">
         <v>57</v>
@@ -24745,10 +25383,10 @@
         <v>16</v>
       </c>
       <c r="B279" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C279" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D279" t="s">
         <v>71</v>
@@ -24770,10 +25408,10 @@
         <v>16</v>
       </c>
       <c r="B280" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C280" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D280" t="s">
         <v>76</v>
@@ -24795,10 +25433,10 @@
         <v>16</v>
       </c>
       <c r="B281" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C281" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D281" t="s">
         <v>59</v>
@@ -24820,10 +25458,10 @@
         <v>16</v>
       </c>
       <c r="B282" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C282" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D282" t="s">
         <v>72</v>
@@ -24845,10 +25483,10 @@
         <v>16</v>
       </c>
       <c r="B283" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C283" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D283" t="s">
         <v>86</v>
@@ -24870,10 +25508,10 @@
         <v>16</v>
       </c>
       <c r="B284" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C284" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D284" t="s">
         <v>63</v>
@@ -24895,10 +25533,10 @@
         <v>16</v>
       </c>
       <c r="B285" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C285" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D285" t="s">
         <v>64</v>
@@ -24920,10 +25558,10 @@
         <v>16</v>
       </c>
       <c r="B286" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C286" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D286" t="s">
         <v>83</v>
@@ -24945,10 +25583,10 @@
         <v>16</v>
       </c>
       <c r="B287" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C287" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D287" t="s">
         <v>62</v>
@@ -24965,41 +25603,50 @@
         <v/>
       </c>
     </row>
+    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D288" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E288" s="24" t="str">
+        <f>IF(AND(E287&lt;&gt;"",G287&lt;&gt;""),E287+G287,"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="289" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="290" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B290" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C290" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D290" t="s">
         <v>53</v>
       </c>
       <c r="E290" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F290" t="s">
         <v>55</v>
       </c>
       <c r="G290" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H290" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I290" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J290" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="291" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25007,10 +25654,10 @@
         <v>17</v>
       </c>
       <c r="B291" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C291" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D291" t="s">
         <v>69</v>
@@ -25032,10 +25679,10 @@
         <v>17</v>
       </c>
       <c r="B292" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C292" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D292" t="s">
         <v>65</v>
@@ -25057,10 +25704,10 @@
         <v>17</v>
       </c>
       <c r="B293" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C293" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D293" t="s">
         <v>70</v>
@@ -25082,10 +25729,10 @@
         <v>17</v>
       </c>
       <c r="B294" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C294" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D294" t="s">
         <v>86</v>
@@ -25107,10 +25754,10 @@
         <v>17</v>
       </c>
       <c r="B295" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C295" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D295" t="s">
         <v>74</v>
@@ -25132,10 +25779,10 @@
         <v>17</v>
       </c>
       <c r="B296" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C296" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D296" t="s">
         <v>67</v>
@@ -25157,10 +25804,10 @@
         <v>17</v>
       </c>
       <c r="B297" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C297" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D297" t="s">
         <v>82</v>
@@ -25182,10 +25829,10 @@
         <v>17</v>
       </c>
       <c r="B298" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C298" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D298" t="s">
         <v>58</v>
@@ -25207,10 +25854,10 @@
         <v>17</v>
       </c>
       <c r="B299" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C299" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D299" t="s">
         <v>80</v>
@@ -25232,10 +25879,10 @@
         <v>17</v>
       </c>
       <c r="B300" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C300" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D300" t="s">
         <v>66</v>
@@ -25257,10 +25904,10 @@
         <v>17</v>
       </c>
       <c r="B301" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C301" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D301" t="s">
         <v>84</v>
@@ -25282,10 +25929,10 @@
         <v>17</v>
       </c>
       <c r="B302" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C302" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D302" t="s">
         <v>68</v>
@@ -25307,10 +25954,10 @@
         <v>17</v>
       </c>
       <c r="B303" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C303" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D303" t="s">
         <v>87</v>
@@ -25332,10 +25979,10 @@
         <v>17</v>
       </c>
       <c r="B304" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C304" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D304" t="s">
         <v>88</v>
@@ -25357,10 +26004,10 @@
         <v>17</v>
       </c>
       <c r="B305" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C305" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D305" t="s">
         <v>60</v>
@@ -25382,10 +26029,10 @@
         <v>17</v>
       </c>
       <c r="B306" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C306" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D306" t="s">
         <v>83</v>
@@ -25402,41 +26049,50 @@
         <v/>
       </c>
     </row>
+    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D307" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E307" s="24" t="str">
+        <f>IF(AND(E306&lt;&gt;"",G306&lt;&gt;""),E306+G306,"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="308" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="309" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B309" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C309" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D309" t="s">
         <v>53</v>
       </c>
       <c r="E309" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F309" t="s">
         <v>55</v>
       </c>
       <c r="G309" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H309" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I309" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J309" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="310" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25444,10 +26100,10 @@
         <v>18</v>
       </c>
       <c r="B310" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C310" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D310" t="s">
         <v>75</v>
@@ -25469,10 +26125,10 @@
         <v>18</v>
       </c>
       <c r="B311" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C311" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D311" t="s">
         <v>71</v>
@@ -25494,10 +26150,10 @@
         <v>18</v>
       </c>
       <c r="B312" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C312" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D312" t="s">
         <v>60</v>
@@ -25519,10 +26175,10 @@
         <v>18</v>
       </c>
       <c r="B313" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C313" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D313" t="s">
         <v>66</v>
@@ -25544,10 +26200,10 @@
         <v>18</v>
       </c>
       <c r="B314" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C314" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D314" t="s">
         <v>72</v>
@@ -25569,10 +26225,10 @@
         <v>18</v>
       </c>
       <c r="B315" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C315" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D315" t="s">
         <v>80</v>
@@ -25594,10 +26250,10 @@
         <v>18</v>
       </c>
       <c r="B316" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C316" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D316" t="s">
         <v>58</v>
@@ -25619,10 +26275,10 @@
         <v>18</v>
       </c>
       <c r="B317" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C317" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D317" t="s">
         <v>61</v>
@@ -25644,10 +26300,10 @@
         <v>18</v>
       </c>
       <c r="B318" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C318" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D318" t="s">
         <v>79</v>
@@ -25669,10 +26325,10 @@
         <v>18</v>
       </c>
       <c r="B319" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C319" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D319" t="s">
         <v>63</v>
@@ -25694,10 +26350,10 @@
         <v>18</v>
       </c>
       <c r="B320" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C320" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D320" t="s">
         <v>84</v>
@@ -25719,10 +26375,10 @@
         <v>18</v>
       </c>
       <c r="B321" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C321" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D321" t="s">
         <v>59</v>
@@ -25744,10 +26400,10 @@
         <v>18</v>
       </c>
       <c r="B322" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C322" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D322" t="s">
         <v>85</v>
@@ -25769,10 +26425,10 @@
         <v>18</v>
       </c>
       <c r="B323" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C323" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D323" t="s">
         <v>73</v>
@@ -25794,10 +26450,10 @@
         <v>18</v>
       </c>
       <c r="B324" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C324" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D324" t="s">
         <v>74</v>
@@ -25819,10 +26475,10 @@
         <v>18</v>
       </c>
       <c r="B325" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C325" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D325" t="s">
         <v>76</v>
@@ -25839,41 +26495,50 @@
         <v/>
       </c>
     </row>
+    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D326" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E326" s="24" t="str">
+        <f>IF(AND(E325&lt;&gt;"",G325&lt;&gt;""),E325+G325,"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="327" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="328" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B328" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C328" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D328" t="s">
         <v>53</v>
       </c>
       <c r="E328" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F328" t="s">
         <v>55</v>
       </c>
       <c r="G328" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H328" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I328" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J328" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="329" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25881,10 +26546,10 @@
         <v>19</v>
       </c>
       <c r="B329" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C329" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I329" t="str">
         <f>IF(OR(E329="",G329=""),"",IF(E329&gt;G329,D329,IF(G329&gt;E329,F329,"TIE")))</f>
@@ -25900,10 +26565,10 @@
         <v>19</v>
       </c>
       <c r="B330" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C330" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I330" t="str">
         <f>IF(OR(E330="",G330=""),"",IF(E330&gt;G330,D330,IF(G330&gt;E330,F330,"TIE")))</f>
@@ -25919,10 +26584,10 @@
         <v>19</v>
       </c>
       <c r="B331" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C331" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I331" t="str">
         <f>IF(OR(E331="",G331=""),"",IF(E331&gt;G331,D331,IF(G331&gt;E331,F331,"TIE")))</f>
@@ -25938,10 +26603,10 @@
         <v>19</v>
       </c>
       <c r="B332" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C332" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I332" t="str">
         <f>IF(OR(E332="",G332=""),"",IF(E332&gt;G332,D332,IF(G332&gt;E332,F332,"TIE")))</f>
@@ -25954,39 +26619,39 @@
     </row>
     <row r="334" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="335" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B335" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C335" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D335" t="s">
         <v>53</v>
       </c>
       <c r="E335" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F335" t="s">
         <v>55</v>
       </c>
       <c r="G335" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H335" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I335" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J335" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="336" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25994,10 +26659,10 @@
         <v>20</v>
       </c>
       <c r="B336" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C336" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I336" t="str">
         <f>IF(OR(E336="",G336=""),"",IF(E336&gt;G336,D336,IF(G336&gt;E336,F336,"TIE")))</f>
@@ -26013,10 +26678,10 @@
         <v>20</v>
       </c>
       <c r="B337" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C337" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I337" t="str">
         <f>IF(OR(E337="",G337=""),"",IF(E337&gt;G337,D337,IF(G337&gt;E337,F337,"TIE")))</f>
@@ -26032,10 +26697,10 @@
         <v>20</v>
       </c>
       <c r="B338" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C338" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I338" t="str">
         <f>IF(OR(E338="",G338=""),"",IF(E338&gt;G338,D338,IF(G338&gt;E338,F338,"TIE")))</f>
@@ -26051,10 +26716,10 @@
         <v>20</v>
       </c>
       <c r="B339" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C339" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I339" t="str">
         <f>IF(OR(E339="",G339=""),"",IF(E339&gt;G339,D339,IF(G339&gt;E339,F339,"TIE")))</f>
@@ -26067,39 +26732,39 @@
     </row>
     <row r="341" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="342" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B342" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C342" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D342" t="s">
         <v>53</v>
       </c>
       <c r="E342" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F342" t="s">
         <v>55</v>
       </c>
       <c r="G342" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H342" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I342" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J342" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="343" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26107,10 +26772,10 @@
         <v>21</v>
       </c>
       <c r="B343" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C343" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I343" t="str">
         <f>IF(OR(E343="",G343=""),"",IF(E343&gt;G343,D343,IF(G343&gt;E343,F343,"TIE")))</f>
@@ -26126,10 +26791,10 @@
         <v>21</v>
       </c>
       <c r="B344" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C344" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I344" t="str">
         <f>IF(OR(E344="",G344=""),"",IF(E344&gt;G344,D344,IF(G344&gt;E344,F344,"TIE")))</f>
@@ -26142,39 +26807,39 @@
     </row>
     <row r="346" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="347" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B347" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C347" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D347" t="s">
         <v>53</v>
       </c>
       <c r="E347" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F347" t="s">
         <v>55</v>
       </c>
       <c r="G347" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H347" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I347" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J347" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="348" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26182,10 +26847,10 @@
         <v>22</v>
       </c>
       <c r="B348" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C348" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I348" t="str">
         <f>IF(OR(E348="",G348=""),"",IF(E348&gt;G348,D348,IF(G348&gt;E348,F348,"TIE")))</f>
@@ -26214,7 +26879,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -26227,11 +26892,11 @@
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="25" t="s">
         <v>52</v>
       </c>
     </row>
@@ -26243,25 +26908,25 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26526,14 +27191,14 @@
       </c>
       <c r="C13" s="10">
         <f>SUMPRODUCT(('Picks Detail'!M6:M21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*('Picks Detail'!M6:M21='Picks Detail'!E6:E21))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13">
         <v>12</v>
       </c>
       <c r="E13">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(12,A$6:A$17,0)),0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="0"/>
@@ -26545,11 +27210,11 @@
       </c>
       <c r="H13">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I13">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26670,14 +27335,14 @@
       </c>
       <c r="C17" s="10">
         <f>SUMPRODUCT(('Picks Detail'!Q6:Q21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*('Picks Detail'!Q6:Q21='Picks Detail'!E6:E21))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17">
         <v>8</v>
       </c>
       <c r="E17">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(8,A$6:A$17,0)),0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="str">
         <f t="shared" si="0"/>
@@ -26689,16 +27354,16 @@
       </c>
       <c r="H17">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I17">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
-        <v>89</v>
+      <c r="A19" s="25" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26709,25 +27374,25 @@
         <v>2</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27163,8 +27828,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
-        <v>90</v>
+      <c r="A34" s="25" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27175,25 +27840,25 @@
         <v>2</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27629,8 +28294,8 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="19" t="s">
-        <v>91</v>
+      <c r="A49" s="25" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27641,25 +28306,25 @@
         <v>2</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28095,8 +28760,8 @@
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="19" t="s">
-        <v>92</v>
+      <c r="A64" s="25" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28107,25 +28772,25 @@
         <v>2</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28561,8 +29226,8 @@
       </c>
     </row>
     <row r="79" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="19" t="s">
-        <v>93</v>
+      <c r="A79" s="25" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28573,25 +29238,25 @@
         <v>2</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I80" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29047,7 +29712,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -29060,12 +29725,12 @@
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>94</v>
+      <c r="A4" s="25" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29076,25 +29741,25 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29530,8 +30195,8 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
-        <v>95</v>
+      <c r="A19" s="25" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29542,25 +30207,25 @@
         <v>2</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29996,8 +30661,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
-        <v>96</v>
+      <c r="A34" s="25" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30008,25 +30673,25 @@
         <v>2</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30462,8 +31127,8 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="19" t="s">
-        <v>97</v>
+      <c r="A49" s="25" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30474,25 +31139,25 @@
         <v>2</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30928,8 +31593,8 @@
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="19" t="s">
-        <v>98</v>
+      <c r="A64" s="25" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30940,25 +31605,25 @@
         <v>2</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31394,8 +32059,8 @@
       </c>
     </row>
     <row r="79" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="19" t="s">
-        <v>99</v>
+      <c r="A79" s="25" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31406,25 +32071,25 @@
         <v>2</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I80" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31880,7 +32545,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -31893,12 +32558,12 @@
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>100</v>
+      <c r="A4" s="25" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31909,25 +32574,25 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32363,8 +33028,8 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
-        <v>101</v>
+      <c r="A19" s="25" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32375,25 +33040,25 @@
         <v>2</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32829,8 +33494,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
-        <v>102</v>
+      <c r="A34" s="25" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32841,25 +33506,25 @@
         <v>2</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -33295,8 +33960,8 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="19" t="s">
-        <v>103</v>
+      <c r="A49" s="25" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -33307,25 +33972,25 @@
         <v>2</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -33761,8 +34426,8 @@
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="19" t="s">
-        <v>104</v>
+      <c r="A64" s="25" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -33773,25 +34438,25 @@
         <v>2</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34227,8 +34892,8 @@
       </c>
     </row>
     <row r="79" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="19" t="s">
-        <v>105</v>
+      <c r="A79" s="25" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34239,25 +34904,25 @@
         <v>2</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I80" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34713,7 +35378,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -34728,37 +35393,37 @@
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35086,7 +35751,7 @@
       </c>
       <c r="C10">
         <f>Helper!C9</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <f>Helper!D9</f>
@@ -35110,7 +35775,7 @@
       </c>
       <c r="I10">
         <f>Helper!I9</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J10">
         <f>Helper!J9</f>
@@ -35118,7 +35783,7 @@
       </c>
       <c r="K10">
         <f>MAX(Helper!C9:H9)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35266,7 +35931,7 @@
       </c>
       <c r="C14">
         <f>Helper!C13</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14">
         <f>Helper!D13</f>
@@ -35290,7 +35955,7 @@
       </c>
       <c r="I14">
         <f>Helper!I13</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J14">
         <f>Helper!J13</f>
@@ -35298,12 +35963,12 @@
       </c>
       <c r="K14">
         <f>MAX(Helper!C13:H13)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -35318,37 +35983,37 @@
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35893,7 +36558,7 @@
     </row>
     <row r="31" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -35907,43 +36572,43 @@
       <c r="K31" s="2"/>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
-        <v>224</v>
+      <c r="A32" s="26" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K33" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36127,43 +36792,43 @@
       </c>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="20" t="s">
-        <v>232</v>
+      <c r="A39" s="26" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36347,43 +37012,43 @@
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="20" t="s">
-        <v>233</v>
+      <c r="A46" s="26" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K47" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36568,7 +37233,7 @@
     </row>
     <row r="55" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -36580,28 +37245,28 @@
     </row>
     <row r="56" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36845,7 +37510,7 @@
       </c>
       <c r="C64">
         <f>Helper!I9</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D64">
         <f>Helper!R9</f>
@@ -36857,11 +37522,11 @@
       </c>
       <c r="F64">
         <f>Helper!AE9</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G64">
         <f>Helper!K9</f>
-        <v>8.0007999999999999</v>
+        <v>9.0007999999999999</v>
       </c>
       <c r="H64">
         <f>Helper!T9</f>
@@ -36977,7 +37642,7 @@
       </c>
       <c r="C68">
         <f>Helper!I13</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D68">
         <f>Helper!R13</f>
@@ -36989,11 +37654,11 @@
       </c>
       <c r="F68">
         <f>Helper!AE13</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G68">
         <f>Helper!K13</f>
-        <v>8.0012000000000008</v>
+        <v>9.0012000000000008</v>
       </c>
       <c r="H68">
         <f>Helper!T13</f>
@@ -37026,50 +37691,50 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
-        <v>242</v>
+      <c r="A3" s="27" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="H4" s="22" t="s">
         <v>249</v>
+      </c>
+      <c r="H4" s="28" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B5" t="str">
         <f>INDEX(Helper!B$2:B$13,MATCH(MAX(Helper!K$2:K$13),Helper!K$2:K$13,0))</f>
         <v>Zach Zarra</v>
       </c>
       <c r="C5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E5" t="str">
         <f>B5</f>
@@ -37086,17 +37751,17 @@
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B6" t="str">
         <f>INDEX(Helper!B$2:B$13,MATCH(MAX(Helper!T$2:T$13),Helper!T$2:T$13,0))</f>
         <v>Jake Andrews</v>
       </c>
       <c r="C6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E6" t="str">
         <f>IF(B6&lt;&gt;$E$5,B6,INDEX(Helper!B$2:B$13,MATCH(LARGE(Helper!T$2:T$13,2),Helper!T$2:T$13,0)))</f>
@@ -37113,14 +37778,14 @@
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B7" t="str">
         <f>H5</f>
         <v>Luke Ussery</v>
       </c>
       <c r="C7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -37140,14 +37805,14 @@
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B8" t="str">
         <f>H9</f>
         <v>Larry Loeser</v>
       </c>
       <c r="C8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D8" t="s">
         <v>13</v>
@@ -37167,14 +37832,14 @@
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B9" t="str">
         <f>H13</f>
         <v>Jake Andrews</v>
       </c>
       <c r="C9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D9" t="s">
         <v>19</v>
@@ -37199,8 +37864,8 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>259</v>
+      <c r="A11" s="27" t="s">
+        <v>260</v>
       </c>
       <c r="H11" t="str">
         <f>INDEX(Helper!B$6:B$9,MATCH(LARGE(Helper!AD$6:AD$9,3),Helper!AD$6:AD$9,0))</f>
@@ -37209,16 +37874,16 @@
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H12" t="str">
         <f>INDEX(Helper!B$6:B$9,MATCH(LARGE(Helper!AD$6:AD$9,4),Helper!AD$6:AD$9,0))</f>
@@ -37227,7 +37892,7 @@
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B13" t="str">
         <f>INDEX(H$40:H$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
@@ -37238,7 +37903,7 @@
         <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H13" t="str">
         <f>INDEX(Helper!B$10:B$13,MATCH(LARGE(Helper!AD$10:AD$13,1),Helper!AD$10:AD$13,0))</f>
@@ -37252,8 +37917,8 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
-        <v>263</v>
+      <c r="A15" s="27" t="s">
+        <v>264</v>
       </c>
       <c r="H15" t="str">
         <f>INDEX(Helper!B$10:B$13,MATCH(LARGE(Helper!AD$10:AD$13,3),Helper!AD$10:AD$13,0))</f>
@@ -37265,10 +37930,10 @@
         <v>27</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H16" t="str">
         <f>INDEX(Helper!B$10:B$13,MATCH(LARGE(Helper!AD$10:AD$13,4),Helper!AD$10:AD$13,0))</f>
@@ -37354,8 +38019,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
-        <v>265</v>
+      <c r="A24" s="27" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37363,19 +38028,19 @@
         <v>27</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37680,7 +38345,7 @@
     </row>
     <row r="38" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C38">
         <f>SUM(C26:C37)</f>
@@ -37700,8 +38365,8 @@
       </c>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H39" s="22" t="s">
-        <v>271</v>
+      <c r="H39" s="28" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37837,7 +38502,7 @@
       </c>
       <c r="I47">
         <f>Helper!AE9</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J47" t="b">
         <f t="shared" si="1"/>
@@ -37909,7 +38574,7 @@
       </c>
       <c r="I51">
         <f>Helper!AE13</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J51" t="b">
         <f t="shared" si="1"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_A98005C6E9195966979F624F4D766EEF87D9B954" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{753570AB-C0E9-4044-BB38-9156E28BCF5D}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_A98005C6E9195966979F624F4D766EEF87D9B954" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3AE45DA-17E4-4881-940A-2C26D78B0977}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="3540" windowWidth="21600" windowHeight="11775" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1377,9 +1377,9 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1859,7 +1859,7 @@
         <v>23</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="C3">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H7,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G7,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D3">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H22,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G22,0)</f>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="I3">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J3">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F7="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F22="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F37="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F52="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F67="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F82="W"),1,0)</f>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="K3">
         <f>I3+0.0002</f>
-        <v>6.0002000000000004</v>
+        <v>9.0001999999999995</v>
       </c>
       <c r="L3">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H7,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G7,0)</f>
@@ -3086,11 +3086,11 @@
       </c>
       <c r="AE3">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AF3">
         <f>AE3+0.0002</f>
-        <v>6.0002000000000004</v>
+        <v>9.0001999999999995</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C4">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H8,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G8,0)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D4">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H23,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G23,0)</f>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J4">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F8="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F23="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F38="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F53="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F68="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F83="W"),1,0)</f>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="K4">
         <f>I4+0.0003</f>
-        <v>8.0002999999999993</v>
+        <v>11.000299999999999</v>
       </c>
       <c r="L4">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H8,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G8,0)</f>
@@ -3215,11 +3215,11 @@
       </c>
       <c r="AE4">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AF4">
         <f>AE4+0.0003</f>
-        <v>8.0002999999999993</v>
+        <v>11.000299999999999</v>
       </c>
     </row>
     <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="C6">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H10,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G10,0)</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H25,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G25,0)</f>
@@ -3385,15 +3385,15 @@
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J6">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F10="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F25="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F40="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F55="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F70="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F85="W"),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
         <f>I6+0.0005</f>
-        <v>10.000500000000001</v>
+        <v>16.000499999999999</v>
       </c>
       <c r="L6">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H10,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G10,0)</f>
@@ -3473,11 +3473,11 @@
       </c>
       <c r="AE6">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AF6">
         <f>AE6+0.0005</f>
-        <v>10.000500000000001</v>
+        <v>16.000499999999999</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="C7">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H11,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G11,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D7">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H26,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G26,0)</f>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J7">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F11="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F26="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F41="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F56="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F71="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F86="W"),1,0)</f>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="K7">
         <f>I7+0.0006</f>
-        <v>6.0006000000000004</v>
+        <v>9.0006000000000004</v>
       </c>
       <c r="L7">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H11,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G11,0)</f>
@@ -3602,11 +3602,11 @@
       </c>
       <c r="AE7">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AF7">
         <f>AE7+0.0006</f>
-        <v>6.0006000000000004</v>
+        <v>9.0006000000000004</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="C9">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H13,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G13,0)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D9">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H28,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G28,0)</f>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J9">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F13="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F28="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F43="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F58="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F73="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F88="W"),1,0)</f>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="K9">
         <f>I9+0.0008</f>
-        <v>9.0007999999999999</v>
+        <v>12.0008</v>
       </c>
       <c r="L9">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H13,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G13,0)</f>
@@ -3860,11 +3860,11 @@
       </c>
       <c r="AE9">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AF9">
         <f>AE9+0.0008</f>
-        <v>9.0007999999999999</v>
+        <v>12.0008</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="C10">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H14,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G14,0)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D10">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H29,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G29,0)</f>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="I10">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J10">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F14="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F29="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F44="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F59="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F74="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F89="W"),1,0)</f>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="K10">
         <f>I10+0.0009</f>
-        <v>8.0008999999999997</v>
+        <v>11.0009</v>
       </c>
       <c r="L10">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H14,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G14,0)</f>
@@ -3989,11 +3989,11 @@
       </c>
       <c r="AE10">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AF10">
         <f>AE10+0.0009</f>
-        <v>8.0008999999999997</v>
+        <v>11.0009</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="C11">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H15,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G15,0)</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D11">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H30,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G30,0)</f>
@@ -4030,15 +4030,15 @@
       </c>
       <c r="I11">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J11">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F15="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F30="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F45="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F60="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F75="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F90="W"),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <f>I11+0.001</f>
-        <v>11.000999999999999</v>
+        <v>17.001000000000001</v>
       </c>
       <c r="L11">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H15,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G15,0)</f>
@@ -4118,11 +4118,11 @@
       </c>
       <c r="AE11">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AF11">
         <f>AE11+0.001</f>
-        <v>11.000999999999999</v>
+        <v>17.001000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="C12">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H16,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G16,0)</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D12">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H31,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G31,0)</f>
@@ -4159,15 +4159,15 @@
       </c>
       <c r="I12">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J12">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F16="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F31="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F46="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F61="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F76="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F91="W"),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <f>I12+0.0011</f>
-        <v>10.001099999999999</v>
+        <v>16.001100000000001</v>
       </c>
       <c r="L12">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H16,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G16,0)</f>
@@ -4247,11 +4247,11 @@
       </c>
       <c r="AE12">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AF12">
         <f>AE12+0.0011</f>
-        <v>10.001099999999999</v>
+        <v>16.001100000000001</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="C13">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H17,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G17,0)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D13">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H32,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G32,0)</f>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="I13">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J13">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F17="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F32="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F47="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F62="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F77="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F92="W"),1,0)</f>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="K13">
         <f>I13+0.0012</f>
-        <v>9.0012000000000008</v>
+        <v>12.001200000000001</v>
       </c>
       <c r="L13">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H17,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G17,0)</f>
@@ -4376,11 +4376,11 @@
       </c>
       <c r="AE13">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AF13">
         <f>AE13+0.0012</f>
-        <v>9.0012000000000008</v>
+        <v>12.001200000000001</v>
       </c>
     </row>
   </sheetData>
@@ -7285,67 +7285,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8281,25 +8281,25 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="22"/>
-      <c r="O23" s="22"/>
-      <c r="P23" s="22"/>
-      <c r="Q23" s="22"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="24"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="24"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -8859,25 +8859,25 @@
       <c r="Q41" s="14"/>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="22" t="s">
+      <c r="A42" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="22"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="22"/>
-      <c r="I42" s="22"/>
-      <c r="J42" s="22"/>
-      <c r="K42" s="22"/>
-      <c r="L42" s="22"/>
-      <c r="M42" s="22"/>
-      <c r="N42" s="22"/>
-      <c r="O42" s="22"/>
-      <c r="P42" s="22"/>
-      <c r="Q42" s="22"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="24"/>
+      <c r="N42" s="24"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="24"/>
+      <c r="Q42" s="24"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -9437,25 +9437,25 @@
       <c r="Q60" s="14"/>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="22" t="s">
+      <c r="A61" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="22"/>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="22"/>
-      <c r="H61" s="22"/>
-      <c r="I61" s="22"/>
-      <c r="J61" s="22"/>
-      <c r="K61" s="22"/>
-      <c r="L61" s="22"/>
-      <c r="M61" s="22"/>
-      <c r="N61" s="22"/>
-      <c r="O61" s="22"/>
-      <c r="P61" s="22"/>
-      <c r="Q61" s="22"/>
+      <c r="B61" s="24"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="24"/>
+      <c r="J61" s="24"/>
+      <c r="K61" s="24"/>
+      <c r="L61" s="24"/>
+      <c r="M61" s="24"/>
+      <c r="N61" s="24"/>
+      <c r="O61" s="24"/>
+      <c r="P61" s="24"/>
+      <c r="Q61" s="24"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -10015,25 +10015,25 @@
       <c r="Q79" s="14"/>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="22" t="s">
+      <c r="A80" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="22"/>
-      <c r="C80" s="22"/>
-      <c r="D80" s="22"/>
-      <c r="E80" s="22"/>
-      <c r="F80" s="22"/>
-      <c r="G80" s="22"/>
-      <c r="H80" s="22"/>
-      <c r="I80" s="22"/>
-      <c r="J80" s="22"/>
-      <c r="K80" s="22"/>
-      <c r="L80" s="22"/>
-      <c r="M80" s="22"/>
-      <c r="N80" s="22"/>
-      <c r="O80" s="22"/>
-      <c r="P80" s="22"/>
-      <c r="Q80" s="22"/>
+      <c r="B80" s="24"/>
+      <c r="C80" s="24"/>
+      <c r="D80" s="24"/>
+      <c r="E80" s="24"/>
+      <c r="F80" s="24"/>
+      <c r="G80" s="24"/>
+      <c r="H80" s="24"/>
+      <c r="I80" s="24"/>
+      <c r="J80" s="24"/>
+      <c r="K80" s="24"/>
+      <c r="L80" s="24"/>
+      <c r="M80" s="24"/>
+      <c r="N80" s="24"/>
+      <c r="O80" s="24"/>
+      <c r="P80" s="24"/>
+      <c r="Q80" s="24"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -10563,25 +10563,25 @@
       <c r="Q97" s="14"/>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="22" t="s">
+      <c r="A98" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="22"/>
-      <c r="C98" s="22"/>
-      <c r="D98" s="22"/>
-      <c r="E98" s="22"/>
-      <c r="F98" s="22"/>
-      <c r="G98" s="22"/>
-      <c r="H98" s="22"/>
-      <c r="I98" s="22"/>
-      <c r="J98" s="22"/>
-      <c r="K98" s="22"/>
-      <c r="L98" s="22"/>
-      <c r="M98" s="22"/>
-      <c r="N98" s="22"/>
-      <c r="O98" s="22"/>
-      <c r="P98" s="22"/>
-      <c r="Q98" s="22"/>
+      <c r="B98" s="24"/>
+      <c r="C98" s="24"/>
+      <c r="D98" s="24"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24"/>
+      <c r="H98" s="24"/>
+      <c r="I98" s="24"/>
+      <c r="J98" s="24"/>
+      <c r="K98" s="24"/>
+      <c r="L98" s="24"/>
+      <c r="M98" s="24"/>
+      <c r="N98" s="24"/>
+      <c r="O98" s="24"/>
+      <c r="P98" s="24"/>
+      <c r="Q98" s="24"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -11081,25 +11081,25 @@
       <c r="Q114" s="14"/>
     </row>
     <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="22" t="s">
+      <c r="A115" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="22"/>
-      <c r="C115" s="22"/>
-      <c r="D115" s="22"/>
-      <c r="E115" s="22"/>
-      <c r="F115" s="22"/>
-      <c r="G115" s="22"/>
-      <c r="H115" s="22"/>
-      <c r="I115" s="22"/>
-      <c r="J115" s="22"/>
-      <c r="K115" s="22"/>
-      <c r="L115" s="22"/>
-      <c r="M115" s="22"/>
-      <c r="N115" s="22"/>
-      <c r="O115" s="22"/>
-      <c r="P115" s="22"/>
-      <c r="Q115" s="22"/>
+      <c r="B115" s="24"/>
+      <c r="C115" s="24"/>
+      <c r="D115" s="24"/>
+      <c r="E115" s="24"/>
+      <c r="F115" s="24"/>
+      <c r="G115" s="24"/>
+      <c r="H115" s="24"/>
+      <c r="I115" s="24"/>
+      <c r="J115" s="24"/>
+      <c r="K115" s="24"/>
+      <c r="L115" s="24"/>
+      <c r="M115" s="24"/>
+      <c r="N115" s="24"/>
+      <c r="O115" s="24"/>
+      <c r="P115" s="24"/>
+      <c r="Q115" s="24"/>
     </row>
     <row r="116" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -11599,25 +11599,25 @@
       <c r="Q131" s="14"/>
     </row>
     <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="22" t="s">
+      <c r="A132" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="B132" s="22"/>
-      <c r="C132" s="22"/>
-      <c r="D132" s="22"/>
-      <c r="E132" s="22"/>
-      <c r="F132" s="22"/>
-      <c r="G132" s="22"/>
-      <c r="H132" s="22"/>
-      <c r="I132" s="22"/>
-      <c r="J132" s="22"/>
-      <c r="K132" s="22"/>
-      <c r="L132" s="22"/>
-      <c r="M132" s="22"/>
-      <c r="N132" s="22"/>
-      <c r="O132" s="22"/>
-      <c r="P132" s="22"/>
-      <c r="Q132" s="22"/>
+      <c r="B132" s="24"/>
+      <c r="C132" s="24"/>
+      <c r="D132" s="24"/>
+      <c r="E132" s="24"/>
+      <c r="F132" s="24"/>
+      <c r="G132" s="24"/>
+      <c r="H132" s="24"/>
+      <c r="I132" s="24"/>
+      <c r="J132" s="24"/>
+      <c r="K132" s="24"/>
+      <c r="L132" s="24"/>
+      <c r="M132" s="24"/>
+      <c r="N132" s="24"/>
+      <c r="O132" s="24"/>
+      <c r="P132" s="24"/>
+      <c r="Q132" s="24"/>
     </row>
     <row r="133" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -12117,25 +12117,25 @@
       <c r="Q148" s="14"/>
     </row>
     <row r="149" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="22" t="s">
+      <c r="A149" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="B149" s="22"/>
-      <c r="C149" s="22"/>
-      <c r="D149" s="22"/>
-      <c r="E149" s="22"/>
-      <c r="F149" s="22"/>
-      <c r="G149" s="22"/>
-      <c r="H149" s="22"/>
-      <c r="I149" s="22"/>
-      <c r="J149" s="22"/>
-      <c r="K149" s="22"/>
-      <c r="L149" s="22"/>
-      <c r="M149" s="22"/>
-      <c r="N149" s="22"/>
-      <c r="O149" s="22"/>
-      <c r="P149" s="22"/>
-      <c r="Q149" s="22"/>
+      <c r="B149" s="24"/>
+      <c r="C149" s="24"/>
+      <c r="D149" s="24"/>
+      <c r="E149" s="24"/>
+      <c r="F149" s="24"/>
+      <c r="G149" s="24"/>
+      <c r="H149" s="24"/>
+      <c r="I149" s="24"/>
+      <c r="J149" s="24"/>
+      <c r="K149" s="24"/>
+      <c r="L149" s="24"/>
+      <c r="M149" s="24"/>
+      <c r="N149" s="24"/>
+      <c r="O149" s="24"/>
+      <c r="P149" s="24"/>
+      <c r="Q149" s="24"/>
     </row>
     <row r="150" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -12665,25 +12665,25 @@
       <c r="Q166" s="14"/>
     </row>
     <row r="167" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="22" t="s">
+      <c r="A167" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="B167" s="22"/>
-      <c r="C167" s="22"/>
-      <c r="D167" s="22"/>
-      <c r="E167" s="22"/>
-      <c r="F167" s="22"/>
-      <c r="G167" s="22"/>
-      <c r="H167" s="22"/>
-      <c r="I167" s="22"/>
-      <c r="J167" s="22"/>
-      <c r="K167" s="22"/>
-      <c r="L167" s="22"/>
-      <c r="M167" s="22"/>
-      <c r="N167" s="22"/>
-      <c r="O167" s="22"/>
-      <c r="P167" s="22"/>
-      <c r="Q167" s="22"/>
+      <c r="B167" s="24"/>
+      <c r="C167" s="24"/>
+      <c r="D167" s="24"/>
+      <c r="E167" s="24"/>
+      <c r="F167" s="24"/>
+      <c r="G167" s="24"/>
+      <c r="H167" s="24"/>
+      <c r="I167" s="24"/>
+      <c r="J167" s="24"/>
+      <c r="K167" s="24"/>
+      <c r="L167" s="24"/>
+      <c r="M167" s="24"/>
+      <c r="N167" s="24"/>
+      <c r="O167" s="24"/>
+      <c r="P167" s="24"/>
+      <c r="Q167" s="24"/>
     </row>
     <row r="168" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -13183,25 +13183,25 @@
       <c r="Q183" s="14"/>
     </row>
     <row r="184" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="22" t="s">
+      <c r="A184" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="B184" s="22"/>
-      <c r="C184" s="22"/>
-      <c r="D184" s="22"/>
-      <c r="E184" s="22"/>
-      <c r="F184" s="22"/>
-      <c r="G184" s="22"/>
-      <c r="H184" s="22"/>
-      <c r="I184" s="22"/>
-      <c r="J184" s="22"/>
-      <c r="K184" s="22"/>
-      <c r="L184" s="22"/>
-      <c r="M184" s="22"/>
-      <c r="N184" s="22"/>
-      <c r="O184" s="22"/>
-      <c r="P184" s="22"/>
-      <c r="Q184" s="22"/>
+      <c r="B184" s="24"/>
+      <c r="C184" s="24"/>
+      <c r="D184" s="24"/>
+      <c r="E184" s="24"/>
+      <c r="F184" s="24"/>
+      <c r="G184" s="24"/>
+      <c r="H184" s="24"/>
+      <c r="I184" s="24"/>
+      <c r="J184" s="24"/>
+      <c r="K184" s="24"/>
+      <c r="L184" s="24"/>
+      <c r="M184" s="24"/>
+      <c r="N184" s="24"/>
+      <c r="O184" s="24"/>
+      <c r="P184" s="24"/>
+      <c r="Q184" s="24"/>
     </row>
     <row r="185" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -13671,25 +13671,25 @@
       <c r="Q199" s="14"/>
     </row>
     <row r="200" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="22" t="s">
+      <c r="A200" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="B200" s="22"/>
-      <c r="C200" s="22"/>
-      <c r="D200" s="22"/>
-      <c r="E200" s="22"/>
-      <c r="F200" s="22"/>
-      <c r="G200" s="22"/>
-      <c r="H200" s="22"/>
-      <c r="I200" s="22"/>
-      <c r="J200" s="22"/>
-      <c r="K200" s="22"/>
-      <c r="L200" s="22"/>
-      <c r="M200" s="22"/>
-      <c r="N200" s="22"/>
-      <c r="O200" s="22"/>
-      <c r="P200" s="22"/>
-      <c r="Q200" s="22"/>
+      <c r="B200" s="24"/>
+      <c r="C200" s="24"/>
+      <c r="D200" s="24"/>
+      <c r="E200" s="24"/>
+      <c r="F200" s="24"/>
+      <c r="G200" s="24"/>
+      <c r="H200" s="24"/>
+      <c r="I200" s="24"/>
+      <c r="J200" s="24"/>
+      <c r="K200" s="24"/>
+      <c r="L200" s="24"/>
+      <c r="M200" s="24"/>
+      <c r="N200" s="24"/>
+      <c r="O200" s="24"/>
+      <c r="P200" s="24"/>
+      <c r="Q200" s="24"/>
     </row>
     <row r="201" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -14249,25 +14249,25 @@
       <c r="Q218" s="14"/>
     </row>
     <row r="219" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="22" t="s">
+      <c r="A219" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="B219" s="22"/>
-      <c r="C219" s="22"/>
-      <c r="D219" s="22"/>
-      <c r="E219" s="22"/>
-      <c r="F219" s="22"/>
-      <c r="G219" s="22"/>
-      <c r="H219" s="22"/>
-      <c r="I219" s="22"/>
-      <c r="J219" s="22"/>
-      <c r="K219" s="22"/>
-      <c r="L219" s="22"/>
-      <c r="M219" s="22"/>
-      <c r="N219" s="22"/>
-      <c r="O219" s="22"/>
-      <c r="P219" s="22"/>
-      <c r="Q219" s="22"/>
+      <c r="B219" s="24"/>
+      <c r="C219" s="24"/>
+      <c r="D219" s="24"/>
+      <c r="E219" s="24"/>
+      <c r="F219" s="24"/>
+      <c r="G219" s="24"/>
+      <c r="H219" s="24"/>
+      <c r="I219" s="24"/>
+      <c r="J219" s="24"/>
+      <c r="K219" s="24"/>
+      <c r="L219" s="24"/>
+      <c r="M219" s="24"/>
+      <c r="N219" s="24"/>
+      <c r="O219" s="24"/>
+      <c r="P219" s="24"/>
+      <c r="Q219" s="24"/>
     </row>
     <row r="220" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -14767,25 +14767,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="22" t="s">
+      <c r="A236" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B236" s="22"/>
-      <c r="C236" s="22"/>
-      <c r="D236" s="22"/>
-      <c r="E236" s="22"/>
-      <c r="F236" s="22"/>
-      <c r="G236" s="22"/>
-      <c r="H236" s="22"/>
-      <c r="I236" s="22"/>
-      <c r="J236" s="22"/>
-      <c r="K236" s="22"/>
-      <c r="L236" s="22"/>
-      <c r="M236" s="22"/>
-      <c r="N236" s="22"/>
-      <c r="O236" s="22"/>
-      <c r="P236" s="22"/>
-      <c r="Q236" s="22"/>
+      <c r="B236" s="24"/>
+      <c r="C236" s="24"/>
+      <c r="D236" s="24"/>
+      <c r="E236" s="24"/>
+      <c r="F236" s="24"/>
+      <c r="G236" s="24"/>
+      <c r="H236" s="24"/>
+      <c r="I236" s="24"/>
+      <c r="J236" s="24"/>
+      <c r="K236" s="24"/>
+      <c r="L236" s="24"/>
+      <c r="M236" s="24"/>
+      <c r="N236" s="24"/>
+      <c r="O236" s="24"/>
+      <c r="P236" s="24"/>
+      <c r="Q236" s="24"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -15315,25 +15315,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="22" t="s">
+      <c r="A254" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="B254" s="22"/>
-      <c r="C254" s="22"/>
-      <c r="D254" s="22"/>
-      <c r="E254" s="22"/>
-      <c r="F254" s="22"/>
-      <c r="G254" s="22"/>
-      <c r="H254" s="22"/>
-      <c r="I254" s="22"/>
-      <c r="J254" s="22"/>
-      <c r="K254" s="22"/>
-      <c r="L254" s="22"/>
-      <c r="M254" s="22"/>
-      <c r="N254" s="22"/>
-      <c r="O254" s="22"/>
-      <c r="P254" s="22"/>
-      <c r="Q254" s="22"/>
+      <c r="B254" s="24"/>
+      <c r="C254" s="24"/>
+      <c r="D254" s="24"/>
+      <c r="E254" s="24"/>
+      <c r="F254" s="24"/>
+      <c r="G254" s="24"/>
+      <c r="H254" s="24"/>
+      <c r="I254" s="24"/>
+      <c r="J254" s="24"/>
+      <c r="K254" s="24"/>
+      <c r="L254" s="24"/>
+      <c r="M254" s="24"/>
+      <c r="N254" s="24"/>
+      <c r="O254" s="24"/>
+      <c r="P254" s="24"/>
+      <c r="Q254" s="24"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -15893,25 +15893,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="22" t="s">
+      <c r="A273" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="B273" s="22"/>
-      <c r="C273" s="22"/>
-      <c r="D273" s="22"/>
-      <c r="E273" s="22"/>
-      <c r="F273" s="22"/>
-      <c r="G273" s="22"/>
-      <c r="H273" s="22"/>
-      <c r="I273" s="22"/>
-      <c r="J273" s="22"/>
-      <c r="K273" s="22"/>
-      <c r="L273" s="22"/>
-      <c r="M273" s="22"/>
-      <c r="N273" s="22"/>
-      <c r="O273" s="22"/>
-      <c r="P273" s="22"/>
-      <c r="Q273" s="22"/>
+      <c r="B273" s="24"/>
+      <c r="C273" s="24"/>
+      <c r="D273" s="24"/>
+      <c r="E273" s="24"/>
+      <c r="F273" s="24"/>
+      <c r="G273" s="24"/>
+      <c r="H273" s="24"/>
+      <c r="I273" s="24"/>
+      <c r="J273" s="24"/>
+      <c r="K273" s="24"/>
+      <c r="L273" s="24"/>
+      <c r="M273" s="24"/>
+      <c r="N273" s="24"/>
+      <c r="O273" s="24"/>
+      <c r="P273" s="24"/>
+      <c r="Q273" s="24"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -16471,25 +16471,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="22" t="s">
+      <c r="A292" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="B292" s="22"/>
-      <c r="C292" s="22"/>
-      <c r="D292" s="22"/>
-      <c r="E292" s="22"/>
-      <c r="F292" s="22"/>
-      <c r="G292" s="22"/>
-      <c r="H292" s="22"/>
-      <c r="I292" s="22"/>
-      <c r="J292" s="22"/>
-      <c r="K292" s="22"/>
-      <c r="L292" s="22"/>
-      <c r="M292" s="22"/>
-      <c r="N292" s="22"/>
-      <c r="O292" s="22"/>
-      <c r="P292" s="22"/>
-      <c r="Q292" s="22"/>
+      <c r="B292" s="24"/>
+      <c r="C292" s="24"/>
+      <c r="D292" s="24"/>
+      <c r="E292" s="24"/>
+      <c r="F292" s="24"/>
+      <c r="G292" s="24"/>
+      <c r="H292" s="24"/>
+      <c r="I292" s="24"/>
+      <c r="J292" s="24"/>
+      <c r="K292" s="24"/>
+      <c r="L292" s="24"/>
+      <c r="M292" s="24"/>
+      <c r="N292" s="24"/>
+      <c r="O292" s="24"/>
+      <c r="P292" s="24"/>
+      <c r="Q292" s="24"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -17049,25 +17049,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="22" t="s">
+      <c r="A311" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="B311" s="22"/>
-      <c r="C311" s="22"/>
-      <c r="D311" s="22"/>
-      <c r="E311" s="22"/>
-      <c r="F311" s="22"/>
-      <c r="G311" s="22"/>
-      <c r="H311" s="22"/>
-      <c r="I311" s="22"/>
-      <c r="J311" s="22"/>
-      <c r="K311" s="22"/>
-      <c r="L311" s="22"/>
-      <c r="M311" s="22"/>
-      <c r="N311" s="22"/>
-      <c r="O311" s="22"/>
-      <c r="P311" s="22"/>
-      <c r="Q311" s="22"/>
+      <c r="B311" s="24"/>
+      <c r="C311" s="24"/>
+      <c r="D311" s="24"/>
+      <c r="E311" s="24"/>
+      <c r="F311" s="24"/>
+      <c r="G311" s="24"/>
+      <c r="H311" s="24"/>
+      <c r="I311" s="24"/>
+      <c r="J311" s="24"/>
+      <c r="K311" s="24"/>
+      <c r="L311" s="24"/>
+      <c r="M311" s="24"/>
+      <c r="N311" s="24"/>
+      <c r="O311" s="24"/>
+      <c r="P311" s="24"/>
+      <c r="Q311" s="24"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -17628,26 +17628,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A236:Q236"/>
+    <mergeCell ref="A254:Q254"/>
+    <mergeCell ref="A273:Q273"/>
+    <mergeCell ref="A292:Q292"/>
+    <mergeCell ref="A311:Q311"/>
+    <mergeCell ref="A149:Q149"/>
+    <mergeCell ref="A167:Q167"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A219:Q219"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="A132:Q132"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A4:Q4"/>
     <mergeCell ref="A23:Q23"/>
     <mergeCell ref="A42:Q42"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A167:Q167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A236:Q236"/>
-    <mergeCell ref="A254:Q254"/>
-    <mergeCell ref="A273:Q273"/>
-    <mergeCell ref="A292:Q292"/>
-    <mergeCell ref="A311:Q311"/>
   </mergeCells>
   <dataValidations count="268">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or SEA" promptTitle="ATS Pick" prompt="Pick NE or SEA" sqref="F6:Q6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -35485,7 +35485,7 @@
       </c>
       <c r="C4">
         <f>Helper!C3</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <f>Helper!D3</f>
@@ -35509,7 +35509,7 @@
       </c>
       <c r="I4">
         <f>Helper!I3</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <f>Helper!J3</f>
@@ -35517,7 +35517,7 @@
       </c>
       <c r="K4">
         <f>MAX(Helper!C3:H3)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35530,7 +35530,7 @@
       </c>
       <c r="C5">
         <f>Helper!C4</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D5">
         <f>Helper!D4</f>
@@ -35554,7 +35554,7 @@
       </c>
       <c r="I5">
         <f>Helper!I4</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J5">
         <f>Helper!J4</f>
@@ -35562,7 +35562,7 @@
       </c>
       <c r="K5">
         <f>MAX(Helper!C4:H4)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35620,7 +35620,7 @@
       </c>
       <c r="C7">
         <f>Helper!C6</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D7">
         <f>Helper!D6</f>
@@ -35644,15 +35644,15 @@
       </c>
       <c r="I7">
         <f>Helper!I6</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J7">
         <f>Helper!J6</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <f>MAX(Helper!C6:H6)</f>
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="C8">
         <f>Helper!C7</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D8">
         <f>Helper!D7</f>
@@ -35689,7 +35689,7 @@
       </c>
       <c r="I8">
         <f>Helper!I7</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J8">
         <f>Helper!J7</f>
@@ -35697,7 +35697,7 @@
       </c>
       <c r="K8">
         <f>MAX(Helper!C7:H7)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35755,7 +35755,7 @@
       </c>
       <c r="C10">
         <f>Helper!C9</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D10">
         <f>Helper!D9</f>
@@ -35779,7 +35779,7 @@
       </c>
       <c r="I10">
         <f>Helper!I9</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J10">
         <f>Helper!J9</f>
@@ -35787,7 +35787,7 @@
       </c>
       <c r="K10">
         <f>MAX(Helper!C9:H9)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35800,7 +35800,7 @@
       </c>
       <c r="C11">
         <f>Helper!C10</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D11">
         <f>Helper!D10</f>
@@ -35824,7 +35824,7 @@
       </c>
       <c r="I11">
         <f>Helper!I10</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J11">
         <f>Helper!J10</f>
@@ -35832,7 +35832,7 @@
       </c>
       <c r="K11">
         <f>MAX(Helper!C10:H10)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35845,7 +35845,7 @@
       </c>
       <c r="C12">
         <f>Helper!C11</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D12">
         <f>Helper!D11</f>
@@ -35869,15 +35869,15 @@
       </c>
       <c r="I12">
         <f>Helper!I11</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J12">
         <f>Helper!J11</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <f>MAX(Helper!C11:H11)</f>
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35890,7 +35890,7 @@
       </c>
       <c r="C13">
         <f>Helper!C12</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D13">
         <f>Helper!D12</f>
@@ -35914,15 +35914,15 @@
       </c>
       <c r="I13">
         <f>Helper!I12</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J13">
         <f>Helper!J12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <f>MAX(Helper!C12:H12)</f>
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35935,7 +35935,7 @@
       </c>
       <c r="C14">
         <f>Helper!C13</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D14">
         <f>Helper!D13</f>
@@ -35959,7 +35959,7 @@
       </c>
       <c r="I14">
         <f>Helper!I13</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J14">
         <f>Helper!J13</f>
@@ -35967,7 +35967,7 @@
       </c>
       <c r="K14">
         <f>MAX(Helper!C13:H13)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -37316,7 +37316,7 @@
       </c>
       <c r="C58">
         <f>Helper!I3</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D58">
         <f>Helper!R3</f>
@@ -37328,11 +37328,11 @@
       </c>
       <c r="F58">
         <f>Helper!AE3</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G58">
         <f>Helper!K3</f>
-        <v>6.0002000000000004</v>
+        <v>9.0001999999999995</v>
       </c>
       <c r="H58">
         <f>Helper!T3</f>
@@ -37349,7 +37349,7 @@
       </c>
       <c r="C59">
         <f>Helper!I4</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D59">
         <f>Helper!R4</f>
@@ -37361,11 +37361,11 @@
       </c>
       <c r="F59">
         <f>Helper!AE4</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G59">
         <f>Helper!K4</f>
-        <v>8.0002999999999993</v>
+        <v>11.000299999999999</v>
       </c>
       <c r="H59">
         <f>Helper!T4</f>
@@ -37415,7 +37415,7 @@
       </c>
       <c r="C61">
         <f>Helper!I6</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D61">
         <f>Helper!R6</f>
@@ -37427,11 +37427,11 @@
       </c>
       <c r="F61">
         <f>Helper!AE6</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G61">
         <f>Helper!K6</f>
-        <v>10.000500000000001</v>
+        <v>16.000499999999999</v>
       </c>
       <c r="H61">
         <f>Helper!T6</f>
@@ -37448,7 +37448,7 @@
       </c>
       <c r="C62">
         <f>Helper!I7</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D62">
         <f>Helper!R7</f>
@@ -37460,11 +37460,11 @@
       </c>
       <c r="F62">
         <f>Helper!AE7</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G62">
         <f>Helper!K7</f>
-        <v>6.0006000000000004</v>
+        <v>9.0006000000000004</v>
       </c>
       <c r="H62">
         <f>Helper!T7</f>
@@ -37514,7 +37514,7 @@
       </c>
       <c r="C64">
         <f>Helper!I9</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D64">
         <f>Helper!R9</f>
@@ -37526,11 +37526,11 @@
       </c>
       <c r="F64">
         <f>Helper!AE9</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G64">
         <f>Helper!K9</f>
-        <v>9.0007999999999999</v>
+        <v>12.0008</v>
       </c>
       <c r="H64">
         <f>Helper!T9</f>
@@ -37547,7 +37547,7 @@
       </c>
       <c r="C65">
         <f>Helper!I10</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D65">
         <f>Helper!R10</f>
@@ -37559,11 +37559,11 @@
       </c>
       <c r="F65">
         <f>Helper!AE10</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G65">
         <f>Helper!K10</f>
-        <v>8.0008999999999997</v>
+        <v>11.0009</v>
       </c>
       <c r="H65">
         <f>Helper!T10</f>
@@ -37580,7 +37580,7 @@
       </c>
       <c r="C66">
         <f>Helper!I11</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D66">
         <f>Helper!R11</f>
@@ -37592,11 +37592,11 @@
       </c>
       <c r="F66">
         <f>Helper!AE11</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G66">
         <f>Helper!K11</f>
-        <v>11.000999999999999</v>
+        <v>17.001000000000001</v>
       </c>
       <c r="H66">
         <f>Helper!T11</f>
@@ -37613,7 +37613,7 @@
       </c>
       <c r="C67">
         <f>Helper!I12</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D67">
         <f>Helper!R12</f>
@@ -37625,11 +37625,11 @@
       </c>
       <c r="F67">
         <f>Helper!AE12</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G67">
         <f>Helper!K12</f>
-        <v>10.001099999999999</v>
+        <v>16.001100000000001</v>
       </c>
       <c r="H67">
         <f>Helper!T12</f>
@@ -37646,7 +37646,7 @@
       </c>
       <c r="C68">
         <f>Helper!I13</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D68">
         <f>Helper!R13</f>
@@ -37658,11 +37658,11 @@
       </c>
       <c r="F68">
         <f>Helper!AE13</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G68">
         <f>Helper!K13</f>
-        <v>9.0012000000000008</v>
+        <v>12.001200000000001</v>
       </c>
       <c r="H68">
         <f>Helper!T13</f>
@@ -37904,7 +37904,7 @@
       </c>
       <c r="C13">
         <f>INDEX(I$40:I$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
         <v>263</v>
@@ -38398,7 +38398,7 @@
       </c>
       <c r="I41">
         <f>Helper!AE3</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J41" t="b">
         <f t="shared" si="1"/>
@@ -38406,7 +38406,7 @@
       </c>
       <c r="K41">
         <f>IF(J41,-1,I41+0.00002)</f>
-        <v>6.0000200000000001</v>
+        <v>9.0000199999999992</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38416,7 +38416,7 @@
       </c>
       <c r="I42">
         <f>Helper!AE4</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J42" t="b">
         <f t="shared" si="1"/>
@@ -38424,7 +38424,7 @@
       </c>
       <c r="K42">
         <f>IF(J42,-1,I42+0.00003)</f>
-        <v>8.0000300000000006</v>
+        <v>11.000030000000001</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38452,7 +38452,7 @@
       </c>
       <c r="I44">
         <f>Helper!AE6</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J44" t="b">
         <f t="shared" si="1"/>
@@ -38460,7 +38460,7 @@
       </c>
       <c r="K44">
         <f>IF(J44,-1,I44+0.00005)</f>
-        <v>10.00005</v>
+        <v>16.000050000000002</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38470,7 +38470,7 @@
       </c>
       <c r="I45">
         <f>Helper!AE7</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J45" t="b">
         <f t="shared" si="1"/>
@@ -38478,7 +38478,7 @@
       </c>
       <c r="K45">
         <f>IF(J45,-1,I45+0.00006)</f>
-        <v>6.0000600000000004</v>
+        <v>9.0000599999999995</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38506,7 +38506,7 @@
       </c>
       <c r="I47">
         <f>Helper!AE9</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J47" t="b">
         <f t="shared" si="1"/>
@@ -38524,7 +38524,7 @@
       </c>
       <c r="I48">
         <f>Helper!AE10</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J48" t="b">
         <f t="shared" si="1"/>
@@ -38532,7 +38532,7 @@
       </c>
       <c r="K48">
         <f>IF(J48,-1,I48+0.00009)</f>
-        <v>8.0000900000000001</v>
+        <v>11.00009</v>
       </c>
     </row>
     <row r="49" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38542,7 +38542,7 @@
       </c>
       <c r="I49">
         <f>Helper!AE11</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J49" t="b">
         <f t="shared" si="1"/>
@@ -38560,7 +38560,7 @@
       </c>
       <c r="I50">
         <f>Helper!AE12</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J50" t="b">
         <f t="shared" si="1"/>
@@ -38578,7 +38578,7 @@
       </c>
       <c r="I51">
         <f>Helper!AE13</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J51" t="b">
         <f t="shared" si="1"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_A98005C6E9195966979F624F4D766EEF87D9B954" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3AE45DA-17E4-4881-940A-2C26D78B0977}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_A98005C6E9195966979F624F4D766EEF87D9B954" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9362984-6E5D-45C2-A40B-68E1C3742DC2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1377,13 +1377,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1470,10 +1470,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1665,12 +1661,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -4402,14 +4398,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -5354,14 +5350,14 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="26" t="s">
+      <c r="A56" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="26"/>
-      <c r="C56" s="26"/>
-      <c r="D56" s="26"/>
-      <c r="E56" s="26"/>
-      <c r="F56" s="26"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
@@ -6306,14 +6302,14 @@
       </c>
     </row>
     <row r="111" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="26" t="s">
+      <c r="A111" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B111" s="26"/>
-      <c r="C111" s="26"/>
-      <c r="D111" s="26"/>
-      <c r="E111" s="26"/>
-      <c r="F111" s="26"/>
+      <c r="B111" s="23"/>
+      <c r="C111" s="23"/>
+      <c r="D111" s="23"/>
+      <c r="E111" s="23"/>
+      <c r="F111" s="23"/>
     </row>
     <row r="112" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
@@ -7285,46 +7281,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
@@ -8277,7 +8273,7 @@
       <c r="O22" s="14"/>
       <c r="P22" s="14"/>
       <c r="Q22" s="14">
-        <v>52</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17628,26 +17624,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A23:Q23"/>
+    <mergeCell ref="A42:Q42"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="A132:Q132"/>
+    <mergeCell ref="A149:Q149"/>
+    <mergeCell ref="A167:Q167"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A219:Q219"/>
     <mergeCell ref="A236:Q236"/>
     <mergeCell ref="A254:Q254"/>
     <mergeCell ref="A273:Q273"/>
     <mergeCell ref="A292:Q292"/>
     <mergeCell ref="A311:Q311"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A167:Q167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="A23:Q23"/>
-    <mergeCell ref="A42:Q42"/>
   </mergeCells>
   <dataValidations count="268">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or SEA" promptTitle="ATS Pick" prompt="Pick NE or SEA" sqref="F6:Q6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -26882,17 +26878,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -29715,17 +29711,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -32548,17 +32544,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -35381,19 +35377,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_A98005C6E9195966979F624F4D766EEF87D9B954" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9362984-6E5D-45C2-A40B-68E1C3742DC2}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="11_A98005C6E9195966979F624F4D766EEF87D9B954" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{900FC9A1-3522-4C3A-AB7C-5D6F082351A4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3399" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3395" uniqueCount="346">
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -1377,13 +1377,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1661,12 +1661,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="C9">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H13,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G13,0)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D9">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H28,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G28,0)</f>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J9">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F13="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F28="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F43="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F58="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F73="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F88="W"),1,0)</f>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="K9">
         <f>I9+0.0008</f>
-        <v>12.0008</v>
+        <v>11.0008</v>
       </c>
       <c r="L9">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H13,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G13,0)</f>
@@ -3856,11 +3856,11 @@
       </c>
       <c r="AE9">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF9">
         <f>AE9+0.0008</f>
-        <v>12.0008</v>
+        <v>11.0008</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="C13">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H17,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G17,0)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D13">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H32,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G32,0)</f>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="I13">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J13">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F17="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F32="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F47="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F62="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F77="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F92="W"),1,0)</f>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="K13">
         <f>I13+0.0012</f>
-        <v>12.001200000000001</v>
+        <v>11.001200000000001</v>
       </c>
       <c r="L13">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H17,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G17,0)</f>
@@ -4372,11 +4372,11 @@
       </c>
       <c r="AE13">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF13">
         <f>AE13+0.0012</f>
-        <v>12.001200000000001</v>
+        <v>11.001200000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4398,14 +4398,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -5350,14 +5350,14 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
+      <c r="B56" s="26"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
@@ -6302,14 +6302,14 @@
       </c>
     </row>
     <row r="111" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="23" t="s">
+      <c r="A111" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="B111" s="23"/>
-      <c r="C111" s="23"/>
-      <c r="D111" s="23"/>
-      <c r="E111" s="23"/>
-      <c r="F111" s="23"/>
+      <c r="B111" s="26"/>
+      <c r="C111" s="26"/>
+      <c r="D111" s="26"/>
+      <c r="E111" s="26"/>
+      <c r="F111" s="26"/>
     </row>
     <row r="112" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
@@ -7281,46 +7281,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
@@ -8221,28 +8221,20 @@
       </c>
       <c r="E21" s="9" t="str">
         <f>'NFL Schedule'!J18</f>
-        <v>KC</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>87</v>
-      </c>
+        <v/>
+      </c>
+      <c r="F21" s="10"/>
       <c r="G21" s="10"/>
       <c r="H21" s="10"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="10" t="s">
-        <v>87</v>
-      </c>
+      <c r="J21" s="10"/>
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
-      <c r="M21" s="10" t="s">
-        <v>88</v>
-      </c>
+      <c r="M21" s="10"/>
       <c r="N21" s="10"/>
       <c r="O21" s="10"/>
       <c r="P21" s="10"/>
-      <c r="Q21" s="10" t="s">
-        <v>88</v>
-      </c>
+      <c r="Q21" s="10"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
@@ -8251,30 +8243,22 @@
       <c r="B22" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="13" t="str">
         <f>'NFL Schedule'!E19</f>
-        <v>51</v>
-      </c>
-      <c r="F22" s="14">
-        <v>48</v>
-      </c>
+        <v/>
+      </c>
+      <c r="F22" s="14"/>
       <c r="G22" s="14"/>
       <c r="H22" s="14"/>
       <c r="I22" s="14"/>
-      <c r="J22" s="14">
-        <v>47</v>
-      </c>
+      <c r="J22" s="14"/>
       <c r="K22" s="14"/>
       <c r="L22" s="14"/>
-      <c r="M22" s="14">
-        <v>50</v>
-      </c>
+      <c r="M22" s="14"/>
       <c r="N22" s="14"/>
       <c r="O22" s="14"/>
       <c r="P22" s="14"/>
-      <c r="Q22" s="14">
-        <v>30</v>
-      </c>
+      <c r="Q22" s="14"/>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
@@ -17624,26 +17608,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A236:Q236"/>
+    <mergeCell ref="A254:Q254"/>
+    <mergeCell ref="A273:Q273"/>
+    <mergeCell ref="A292:Q292"/>
+    <mergeCell ref="A311:Q311"/>
+    <mergeCell ref="A149:Q149"/>
+    <mergeCell ref="A167:Q167"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A219:Q219"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="A132:Q132"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A4:Q4"/>
     <mergeCell ref="A23:Q23"/>
     <mergeCell ref="A42:Q42"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A167:Q167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A236:Q236"/>
-    <mergeCell ref="A254:Q254"/>
-    <mergeCell ref="A273:Q273"/>
-    <mergeCell ref="A292:Q292"/>
-    <mergeCell ref="A311:Q311"/>
   </mergeCells>
   <dataValidations count="268">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or SEA" promptTitle="ATS Pick" prompt="Pick NE or SEA" sqref="F6:Q6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -19292,34 +19276,25 @@
       <c r="D18" t="s">
         <v>87</v>
       </c>
-      <c r="E18">
-        <v>25</v>
-      </c>
       <c r="F18" t="s">
         <v>88</v>
       </c>
-      <c r="G18">
-        <v>26</v>
-      </c>
-      <c r="H18">
-        <v>-2.5</v>
-      </c>
       <c r="I18" t="str">
         <f t="shared" si="0"/>
-        <v>KC</v>
+        <v/>
       </c>
       <c r="J18" t="str">
         <f t="shared" si="1"/>
-        <v>KC</v>
+        <v/>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D19" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="16" t="str">
         <f>IF(AND(E18&lt;&gt;"",G18&lt;&gt;""),E18+G18,"")</f>
-        <v>51</v>
+        <v/>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26878,17 +26853,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -27191,14 +27166,14 @@
       </c>
       <c r="C13" s="3">
         <f>SUMPRODUCT(('Picks Detail'!M6:M21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*('Picks Detail'!M6:M21='Picks Detail'!E6:E21))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13">
         <v>12</v>
       </c>
       <c r="E13">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(12,A$6:A$17,0)),0)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="0"/>
@@ -27210,11 +27185,11 @@
       </c>
       <c r="H13">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I13">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27335,14 +27310,14 @@
       </c>
       <c r="C17" s="3">
         <f>SUMPRODUCT(('Picks Detail'!Q6:Q21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*('Picks Detail'!Q6:Q21='Picks Detail'!E6:E21))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17">
         <v>8</v>
       </c>
       <c r="E17">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(8,A$6:A$17,0)),0)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="str">
         <f t="shared" si="0"/>
@@ -27354,11 +27329,11 @@
       </c>
       <c r="H17">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I17">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29711,17 +29686,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -32544,17 +32519,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -35377,19 +35352,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -35751,7 +35726,7 @@
       </c>
       <c r="C10">
         <f>Helper!C9</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10">
         <f>Helper!D9</f>
@@ -35775,7 +35750,7 @@
       </c>
       <c r="I10">
         <f>Helper!I9</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J10">
         <f>Helper!J9</f>
@@ -35783,7 +35758,7 @@
       </c>
       <c r="K10">
         <f>MAX(Helper!C9:H9)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35931,7 +35906,7 @@
       </c>
       <c r="C14">
         <f>Helper!C13</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14">
         <f>Helper!D13</f>
@@ -35955,7 +35930,7 @@
       </c>
       <c r="I14">
         <f>Helper!I13</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J14">
         <f>Helper!J13</f>
@@ -35963,7 +35938,7 @@
       </c>
       <c r="K14">
         <f>MAX(Helper!C13:H13)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -37510,7 +37485,7 @@
       </c>
       <c r="C64">
         <f>Helper!I9</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D64">
         <f>Helper!R9</f>
@@ -37522,11 +37497,11 @@
       </c>
       <c r="F64">
         <f>Helper!AE9</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G64">
         <f>Helper!K9</f>
-        <v>12.0008</v>
+        <v>11.0008</v>
       </c>
       <c r="H64">
         <f>Helper!T9</f>
@@ -37642,7 +37617,7 @@
       </c>
       <c r="C68">
         <f>Helper!I13</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D68">
         <f>Helper!R13</f>
@@ -37654,11 +37629,11 @@
       </c>
       <c r="F68">
         <f>Helper!AE13</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G68">
         <f>Helper!K13</f>
-        <v>12.001200000000001</v>
+        <v>11.001200000000001</v>
       </c>
       <c r="H68">
         <f>Helper!T13</f>
@@ -38502,7 +38477,7 @@
       </c>
       <c r="I47">
         <f>Helper!AE9</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J47" t="b">
         <f t="shared" si="1"/>
@@ -38574,7 +38549,7 @@
       </c>
       <c r="I51">
         <f>Helper!AE13</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J51" t="b">
         <f t="shared" si="1"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="11_A98005C6E9195966979F624F4D766EEF87D9B954" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{900FC9A1-3522-4C3A-AB7C-5D6F082351A4}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_A98005C6E9195966979F624F4D766EEF87D9B954" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48E56B81-9808-46A4-B17F-A2190747DA58}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1377,9 +1377,9 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1470,6 +1470,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1855,7 +1859,7 @@
         <v>23</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2970,7 +2974,7 @@
       </c>
       <c r="C3">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H7,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G7,0)</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H22,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G22,0)</f>
@@ -2994,7 +2998,7 @@
       </c>
       <c r="I3">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J3">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F7="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F22="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F37="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F52="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F67="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F82="W"),1,0)</f>
@@ -3002,7 +3006,7 @@
       </c>
       <c r="K3">
         <f>I3+0.0002</f>
-        <v>9.0001999999999995</v>
+        <v>6.0002000000000004</v>
       </c>
       <c r="L3">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H7,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G7,0)</f>
@@ -3082,11 +3086,11 @@
       </c>
       <c r="AE3">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AF3">
         <f>AE3+0.0002</f>
-        <v>9.0001999999999995</v>
+        <v>6.0002000000000004</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3099,7 +3103,7 @@
       </c>
       <c r="C4">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H8,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G8,0)</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D4">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H23,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G23,0)</f>
@@ -3123,7 +3127,7 @@
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F8="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F23="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F38="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F53="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F68="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F83="W"),1,0)</f>
@@ -3131,7 +3135,7 @@
       </c>
       <c r="K4">
         <f>I4+0.0003</f>
-        <v>11.000299999999999</v>
+        <v>8.0002999999999993</v>
       </c>
       <c r="L4">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H8,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G8,0)</f>
@@ -3211,11 +3215,11 @@
       </c>
       <c r="AE4">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AF4">
         <f>AE4+0.0003</f>
-        <v>11.000299999999999</v>
+        <v>8.0002999999999993</v>
       </c>
     </row>
     <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3357,7 +3361,7 @@
       </c>
       <c r="C6">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H10,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G10,0)</f>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H25,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G25,0)</f>
@@ -3381,15 +3385,15 @@
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F10="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F25="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F40="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F55="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F70="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F85="W"),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <f>I6+0.0005</f>
-        <v>16.000499999999999</v>
+        <v>10.000500000000001</v>
       </c>
       <c r="L6">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H10,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G10,0)</f>
@@ -3469,11 +3473,11 @@
       </c>
       <c r="AE6">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AF6">
         <f>AE6+0.0005</f>
-        <v>16.000499999999999</v>
+        <v>10.000500000000001</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3486,7 +3490,7 @@
       </c>
       <c r="C7">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H11,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G11,0)</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H26,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G26,0)</f>
@@ -3510,7 +3514,7 @@
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F11="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F26="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F41="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F56="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F71="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F86="W"),1,0)</f>
@@ -3518,7 +3522,7 @@
       </c>
       <c r="K7">
         <f>I7+0.0006</f>
-        <v>9.0006000000000004</v>
+        <v>6.0006000000000004</v>
       </c>
       <c r="L7">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H11,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G11,0)</f>
@@ -3598,11 +3602,11 @@
       </c>
       <c r="AE7">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AF7">
         <f>AE7+0.0006</f>
-        <v>9.0006000000000004</v>
+        <v>6.0006000000000004</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3744,7 +3748,7 @@
       </c>
       <c r="C9">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H13,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G13,0)</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H28,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G28,0)</f>
@@ -3768,7 +3772,7 @@
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F13="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F28="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F43="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F58="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F73="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F88="W"),1,0)</f>
@@ -3776,7 +3780,7 @@
       </c>
       <c r="K9">
         <f>I9+0.0008</f>
-        <v>11.0008</v>
+        <v>8.0007999999999999</v>
       </c>
       <c r="L9">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H13,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G13,0)</f>
@@ -3856,11 +3860,11 @@
       </c>
       <c r="AE9">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AF9">
         <f>AE9+0.0008</f>
-        <v>11.0008</v>
+        <v>8.0007999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3873,7 +3877,7 @@
       </c>
       <c r="C10">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H14,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G14,0)</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D10">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H29,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G29,0)</f>
@@ -3897,7 +3901,7 @@
       </c>
       <c r="I10">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F14="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F29="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F44="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F59="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F74="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F89="W"),1,0)</f>
@@ -3905,7 +3909,7 @@
       </c>
       <c r="K10">
         <f>I10+0.0009</f>
-        <v>11.0009</v>
+        <v>8.0008999999999997</v>
       </c>
       <c r="L10">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H14,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G14,0)</f>
@@ -3985,11 +3989,11 @@
       </c>
       <c r="AE10">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AF10">
         <f>AE10+0.0009</f>
-        <v>11.0009</v>
+        <v>8.0008999999999997</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4002,7 +4006,7 @@
       </c>
       <c r="C11">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H15,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G15,0)</f>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D11">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H30,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G30,0)</f>
@@ -4026,15 +4030,15 @@
       </c>
       <c r="I11">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J11">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F15="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F30="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F45="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F60="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F75="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F90="W"),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11">
         <f>I11+0.001</f>
-        <v>17.001000000000001</v>
+        <v>11.000999999999999</v>
       </c>
       <c r="L11">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H15,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G15,0)</f>
@@ -4114,11 +4118,11 @@
       </c>
       <c r="AE11">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AF11">
         <f>AE11+0.001</f>
-        <v>17.001000000000001</v>
+        <v>11.000999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4131,7 +4135,7 @@
       </c>
       <c r="C12">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H16,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G16,0)</f>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D12">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H31,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G31,0)</f>
@@ -4155,15 +4159,15 @@
       </c>
       <c r="I12">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J12">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F16="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F31="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F46="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F61="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F76="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F91="W"),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <f>I12+0.0011</f>
-        <v>16.001100000000001</v>
+        <v>10.001099999999999</v>
       </c>
       <c r="L12">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H16,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G16,0)</f>
@@ -4243,11 +4247,11 @@
       </c>
       <c r="AE12">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AF12">
         <f>AE12+0.0011</f>
-        <v>16.001100000000001</v>
+        <v>10.001099999999999</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4260,7 +4264,7 @@
       </c>
       <c r="C13">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H17,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G17,0)</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D13">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H32,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G32,0)</f>
@@ -4284,7 +4288,7 @@
       </c>
       <c r="I13">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F17="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F32="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F47="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F62="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F77="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F92="W"),1,0)</f>
@@ -4292,7 +4296,7 @@
       </c>
       <c r="K13">
         <f>I13+0.0012</f>
-        <v>11.001200000000001</v>
+        <v>8.0012000000000008</v>
       </c>
       <c r="L13">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H17,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G17,0)</f>
@@ -4372,11 +4376,11 @@
       </c>
       <c r="AE13">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AF13">
         <f>AE13+0.0012</f>
-        <v>11.001200000000001</v>
+        <v>8.0012000000000008</v>
       </c>
     </row>
   </sheetData>
@@ -7281,67 +7285,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="24"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8261,25 +8265,25 @@
       <c r="Q22" s="14"/>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="24"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -8839,25 +8843,25 @@
       <c r="Q41" s="14"/>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+      <c r="A42" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="24"/>
-      <c r="K42" s="24"/>
-      <c r="L42" s="24"/>
-      <c r="M42" s="24"/>
-      <c r="N42" s="24"/>
-      <c r="O42" s="24"/>
-      <c r="P42" s="24"/>
-      <c r="Q42" s="24"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="22"/>
+      <c r="N42" s="22"/>
+      <c r="O42" s="22"/>
+      <c r="P42" s="22"/>
+      <c r="Q42" s="22"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -9417,25 +9421,25 @@
       <c r="Q60" s="14"/>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="24" t="s">
+      <c r="A61" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="24"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="24"/>
-      <c r="J61" s="24"/>
-      <c r="K61" s="24"/>
-      <c r="L61" s="24"/>
-      <c r="M61" s="24"/>
-      <c r="N61" s="24"/>
-      <c r="O61" s="24"/>
-      <c r="P61" s="24"/>
-      <c r="Q61" s="24"/>
+      <c r="B61" s="22"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="22"/>
+      <c r="I61" s="22"/>
+      <c r="J61" s="22"/>
+      <c r="K61" s="22"/>
+      <c r="L61" s="22"/>
+      <c r="M61" s="22"/>
+      <c r="N61" s="22"/>
+      <c r="O61" s="22"/>
+      <c r="P61" s="22"/>
+      <c r="Q61" s="22"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -9995,25 +9999,25 @@
       <c r="Q79" s="14"/>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="24" t="s">
+      <c r="A80" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="24"/>
-      <c r="C80" s="24"/>
-      <c r="D80" s="24"/>
-      <c r="E80" s="24"/>
-      <c r="F80" s="24"/>
-      <c r="G80" s="24"/>
-      <c r="H80" s="24"/>
-      <c r="I80" s="24"/>
-      <c r="J80" s="24"/>
-      <c r="K80" s="24"/>
-      <c r="L80" s="24"/>
-      <c r="M80" s="24"/>
-      <c r="N80" s="24"/>
-      <c r="O80" s="24"/>
-      <c r="P80" s="24"/>
-      <c r="Q80" s="24"/>
+      <c r="B80" s="22"/>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="F80" s="22"/>
+      <c r="G80" s="22"/>
+      <c r="H80" s="22"/>
+      <c r="I80" s="22"/>
+      <c r="J80" s="22"/>
+      <c r="K80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -10543,25 +10547,25 @@
       <c r="Q97" s="14"/>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="24" t="s">
+      <c r="A98" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="24"/>
-      <c r="C98" s="24"/>
-      <c r="D98" s="24"/>
-      <c r="E98" s="24"/>
-      <c r="F98" s="24"/>
-      <c r="G98" s="24"/>
-      <c r="H98" s="24"/>
-      <c r="I98" s="24"/>
-      <c r="J98" s="24"/>
-      <c r="K98" s="24"/>
-      <c r="L98" s="24"/>
-      <c r="M98" s="24"/>
-      <c r="N98" s="24"/>
-      <c r="O98" s="24"/>
-      <c r="P98" s="24"/>
-      <c r="Q98" s="24"/>
+      <c r="B98" s="22"/>
+      <c r="C98" s="22"/>
+      <c r="D98" s="22"/>
+      <c r="E98" s="22"/>
+      <c r="F98" s="22"/>
+      <c r="G98" s="22"/>
+      <c r="H98" s="22"/>
+      <c r="I98" s="22"/>
+      <c r="J98" s="22"/>
+      <c r="K98" s="22"/>
+      <c r="L98" s="22"/>
+      <c r="M98" s="22"/>
+      <c r="N98" s="22"/>
+      <c r="O98" s="22"/>
+      <c r="P98" s="22"/>
+      <c r="Q98" s="22"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -11061,25 +11065,25 @@
       <c r="Q114" s="14"/>
     </row>
     <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="24" t="s">
+      <c r="A115" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="24"/>
-      <c r="C115" s="24"/>
-      <c r="D115" s="24"/>
-      <c r="E115" s="24"/>
-      <c r="F115" s="24"/>
-      <c r="G115" s="24"/>
-      <c r="H115" s="24"/>
-      <c r="I115" s="24"/>
-      <c r="J115" s="24"/>
-      <c r="K115" s="24"/>
-      <c r="L115" s="24"/>
-      <c r="M115" s="24"/>
-      <c r="N115" s="24"/>
-      <c r="O115" s="24"/>
-      <c r="P115" s="24"/>
-      <c r="Q115" s="24"/>
+      <c r="B115" s="22"/>
+      <c r="C115" s="22"/>
+      <c r="D115" s="22"/>
+      <c r="E115" s="22"/>
+      <c r="F115" s="22"/>
+      <c r="G115" s="22"/>
+      <c r="H115" s="22"/>
+      <c r="I115" s="22"/>
+      <c r="J115" s="22"/>
+      <c r="K115" s="22"/>
+      <c r="L115" s="22"/>
+      <c r="M115" s="22"/>
+      <c r="N115" s="22"/>
+      <c r="O115" s="22"/>
+      <c r="P115" s="22"/>
+      <c r="Q115" s="22"/>
     </row>
     <row r="116" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -11579,25 +11583,25 @@
       <c r="Q131" s="14"/>
     </row>
     <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="24" t="s">
+      <c r="A132" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="B132" s="24"/>
-      <c r="C132" s="24"/>
-      <c r="D132" s="24"/>
-      <c r="E132" s="24"/>
-      <c r="F132" s="24"/>
-      <c r="G132" s="24"/>
-      <c r="H132" s="24"/>
-      <c r="I132" s="24"/>
-      <c r="J132" s="24"/>
-      <c r="K132" s="24"/>
-      <c r="L132" s="24"/>
-      <c r="M132" s="24"/>
-      <c r="N132" s="24"/>
-      <c r="O132" s="24"/>
-      <c r="P132" s="24"/>
-      <c r="Q132" s="24"/>
+      <c r="B132" s="22"/>
+      <c r="C132" s="22"/>
+      <c r="D132" s="22"/>
+      <c r="E132" s="22"/>
+      <c r="F132" s="22"/>
+      <c r="G132" s="22"/>
+      <c r="H132" s="22"/>
+      <c r="I132" s="22"/>
+      <c r="J132" s="22"/>
+      <c r="K132" s="22"/>
+      <c r="L132" s="22"/>
+      <c r="M132" s="22"/>
+      <c r="N132" s="22"/>
+      <c r="O132" s="22"/>
+      <c r="P132" s="22"/>
+      <c r="Q132" s="22"/>
     </row>
     <row r="133" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -12097,25 +12101,25 @@
       <c r="Q148" s="14"/>
     </row>
     <row r="149" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="24" t="s">
+      <c r="A149" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="B149" s="24"/>
-      <c r="C149" s="24"/>
-      <c r="D149" s="24"/>
-      <c r="E149" s="24"/>
-      <c r="F149" s="24"/>
-      <c r="G149" s="24"/>
-      <c r="H149" s="24"/>
-      <c r="I149" s="24"/>
-      <c r="J149" s="24"/>
-      <c r="K149" s="24"/>
-      <c r="L149" s="24"/>
-      <c r="M149" s="24"/>
-      <c r="N149" s="24"/>
-      <c r="O149" s="24"/>
-      <c r="P149" s="24"/>
-      <c r="Q149" s="24"/>
+      <c r="B149" s="22"/>
+      <c r="C149" s="22"/>
+      <c r="D149" s="22"/>
+      <c r="E149" s="22"/>
+      <c r="F149" s="22"/>
+      <c r="G149" s="22"/>
+      <c r="H149" s="22"/>
+      <c r="I149" s="22"/>
+      <c r="J149" s="22"/>
+      <c r="K149" s="22"/>
+      <c r="L149" s="22"/>
+      <c r="M149" s="22"/>
+      <c r="N149" s="22"/>
+      <c r="O149" s="22"/>
+      <c r="P149" s="22"/>
+      <c r="Q149" s="22"/>
     </row>
     <row r="150" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -12645,25 +12649,25 @@
       <c r="Q166" s="14"/>
     </row>
     <row r="167" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="24" t="s">
+      <c r="A167" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="B167" s="24"/>
-      <c r="C167" s="24"/>
-      <c r="D167" s="24"/>
-      <c r="E167" s="24"/>
-      <c r="F167" s="24"/>
-      <c r="G167" s="24"/>
-      <c r="H167" s="24"/>
-      <c r="I167" s="24"/>
-      <c r="J167" s="24"/>
-      <c r="K167" s="24"/>
-      <c r="L167" s="24"/>
-      <c r="M167" s="24"/>
-      <c r="N167" s="24"/>
-      <c r="O167" s="24"/>
-      <c r="P167" s="24"/>
-      <c r="Q167" s="24"/>
+      <c r="B167" s="22"/>
+      <c r="C167" s="22"/>
+      <c r="D167" s="22"/>
+      <c r="E167" s="22"/>
+      <c r="F167" s="22"/>
+      <c r="G167" s="22"/>
+      <c r="H167" s="22"/>
+      <c r="I167" s="22"/>
+      <c r="J167" s="22"/>
+      <c r="K167" s="22"/>
+      <c r="L167" s="22"/>
+      <c r="M167" s="22"/>
+      <c r="N167" s="22"/>
+      <c r="O167" s="22"/>
+      <c r="P167" s="22"/>
+      <c r="Q167" s="22"/>
     </row>
     <row r="168" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -13163,25 +13167,25 @@
       <c r="Q183" s="14"/>
     </row>
     <row r="184" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="24" t="s">
+      <c r="A184" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="B184" s="24"/>
-      <c r="C184" s="24"/>
-      <c r="D184" s="24"/>
-      <c r="E184" s="24"/>
-      <c r="F184" s="24"/>
-      <c r="G184" s="24"/>
-      <c r="H184" s="24"/>
-      <c r="I184" s="24"/>
-      <c r="J184" s="24"/>
-      <c r="K184" s="24"/>
-      <c r="L184" s="24"/>
-      <c r="M184" s="24"/>
-      <c r="N184" s="24"/>
-      <c r="O184" s="24"/>
-      <c r="P184" s="24"/>
-      <c r="Q184" s="24"/>
+      <c r="B184" s="22"/>
+      <c r="C184" s="22"/>
+      <c r="D184" s="22"/>
+      <c r="E184" s="22"/>
+      <c r="F184" s="22"/>
+      <c r="G184" s="22"/>
+      <c r="H184" s="22"/>
+      <c r="I184" s="22"/>
+      <c r="J184" s="22"/>
+      <c r="K184" s="22"/>
+      <c r="L184" s="22"/>
+      <c r="M184" s="22"/>
+      <c r="N184" s="22"/>
+      <c r="O184" s="22"/>
+      <c r="P184" s="22"/>
+      <c r="Q184" s="22"/>
     </row>
     <row r="185" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -13651,25 +13655,25 @@
       <c r="Q199" s="14"/>
     </row>
     <row r="200" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="24" t="s">
+      <c r="A200" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="B200" s="24"/>
-      <c r="C200" s="24"/>
-      <c r="D200" s="24"/>
-      <c r="E200" s="24"/>
-      <c r="F200" s="24"/>
-      <c r="G200" s="24"/>
-      <c r="H200" s="24"/>
-      <c r="I200" s="24"/>
-      <c r="J200" s="24"/>
-      <c r="K200" s="24"/>
-      <c r="L200" s="24"/>
-      <c r="M200" s="24"/>
-      <c r="N200" s="24"/>
-      <c r="O200" s="24"/>
-      <c r="P200" s="24"/>
-      <c r="Q200" s="24"/>
+      <c r="B200" s="22"/>
+      <c r="C200" s="22"/>
+      <c r="D200" s="22"/>
+      <c r="E200" s="22"/>
+      <c r="F200" s="22"/>
+      <c r="G200" s="22"/>
+      <c r="H200" s="22"/>
+      <c r="I200" s="22"/>
+      <c r="J200" s="22"/>
+      <c r="K200" s="22"/>
+      <c r="L200" s="22"/>
+      <c r="M200" s="22"/>
+      <c r="N200" s="22"/>
+      <c r="O200" s="22"/>
+      <c r="P200" s="22"/>
+      <c r="Q200" s="22"/>
     </row>
     <row r="201" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -14229,25 +14233,25 @@
       <c r="Q218" s="14"/>
     </row>
     <row r="219" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="24" t="s">
+      <c r="A219" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="B219" s="24"/>
-      <c r="C219" s="24"/>
-      <c r="D219" s="24"/>
-      <c r="E219" s="24"/>
-      <c r="F219" s="24"/>
-      <c r="G219" s="24"/>
-      <c r="H219" s="24"/>
-      <c r="I219" s="24"/>
-      <c r="J219" s="24"/>
-      <c r="K219" s="24"/>
-      <c r="L219" s="24"/>
-      <c r="M219" s="24"/>
-      <c r="N219" s="24"/>
-      <c r="O219" s="24"/>
-      <c r="P219" s="24"/>
-      <c r="Q219" s="24"/>
+      <c r="B219" s="22"/>
+      <c r="C219" s="22"/>
+      <c r="D219" s="22"/>
+      <c r="E219" s="22"/>
+      <c r="F219" s="22"/>
+      <c r="G219" s="22"/>
+      <c r="H219" s="22"/>
+      <c r="I219" s="22"/>
+      <c r="J219" s="22"/>
+      <c r="K219" s="22"/>
+      <c r="L219" s="22"/>
+      <c r="M219" s="22"/>
+      <c r="N219" s="22"/>
+      <c r="O219" s="22"/>
+      <c r="P219" s="22"/>
+      <c r="Q219" s="22"/>
     </row>
     <row r="220" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -14747,25 +14751,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="24" t="s">
+      <c r="A236" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="B236" s="24"/>
-      <c r="C236" s="24"/>
-      <c r="D236" s="24"/>
-      <c r="E236" s="24"/>
-      <c r="F236" s="24"/>
-      <c r="G236" s="24"/>
-      <c r="H236" s="24"/>
-      <c r="I236" s="24"/>
-      <c r="J236" s="24"/>
-      <c r="K236" s="24"/>
-      <c r="L236" s="24"/>
-      <c r="M236" s="24"/>
-      <c r="N236" s="24"/>
-      <c r="O236" s="24"/>
-      <c r="P236" s="24"/>
-      <c r="Q236" s="24"/>
+      <c r="B236" s="22"/>
+      <c r="C236" s="22"/>
+      <c r="D236" s="22"/>
+      <c r="E236" s="22"/>
+      <c r="F236" s="22"/>
+      <c r="G236" s="22"/>
+      <c r="H236" s="22"/>
+      <c r="I236" s="22"/>
+      <c r="J236" s="22"/>
+      <c r="K236" s="22"/>
+      <c r="L236" s="22"/>
+      <c r="M236" s="22"/>
+      <c r="N236" s="22"/>
+      <c r="O236" s="22"/>
+      <c r="P236" s="22"/>
+      <c r="Q236" s="22"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -15295,25 +15299,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="24" t="s">
+      <c r="A254" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="B254" s="24"/>
-      <c r="C254" s="24"/>
-      <c r="D254" s="24"/>
-      <c r="E254" s="24"/>
-      <c r="F254" s="24"/>
-      <c r="G254" s="24"/>
-      <c r="H254" s="24"/>
-      <c r="I254" s="24"/>
-      <c r="J254" s="24"/>
-      <c r="K254" s="24"/>
-      <c r="L254" s="24"/>
-      <c r="M254" s="24"/>
-      <c r="N254" s="24"/>
-      <c r="O254" s="24"/>
-      <c r="P254" s="24"/>
-      <c r="Q254" s="24"/>
+      <c r="B254" s="22"/>
+      <c r="C254" s="22"/>
+      <c r="D254" s="22"/>
+      <c r="E254" s="22"/>
+      <c r="F254" s="22"/>
+      <c r="G254" s="22"/>
+      <c r="H254" s="22"/>
+      <c r="I254" s="22"/>
+      <c r="J254" s="22"/>
+      <c r="K254" s="22"/>
+      <c r="L254" s="22"/>
+      <c r="M254" s="22"/>
+      <c r="N254" s="22"/>
+      <c r="O254" s="22"/>
+      <c r="P254" s="22"/>
+      <c r="Q254" s="22"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -15873,25 +15877,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="24" t="s">
+      <c r="A273" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="B273" s="24"/>
-      <c r="C273" s="24"/>
-      <c r="D273" s="24"/>
-      <c r="E273" s="24"/>
-      <c r="F273" s="24"/>
-      <c r="G273" s="24"/>
-      <c r="H273" s="24"/>
-      <c r="I273" s="24"/>
-      <c r="J273" s="24"/>
-      <c r="K273" s="24"/>
-      <c r="L273" s="24"/>
-      <c r="M273" s="24"/>
-      <c r="N273" s="24"/>
-      <c r="O273" s="24"/>
-      <c r="P273" s="24"/>
-      <c r="Q273" s="24"/>
+      <c r="B273" s="22"/>
+      <c r="C273" s="22"/>
+      <c r="D273" s="22"/>
+      <c r="E273" s="22"/>
+      <c r="F273" s="22"/>
+      <c r="G273" s="22"/>
+      <c r="H273" s="22"/>
+      <c r="I273" s="22"/>
+      <c r="J273" s="22"/>
+      <c r="K273" s="22"/>
+      <c r="L273" s="22"/>
+      <c r="M273" s="22"/>
+      <c r="N273" s="22"/>
+      <c r="O273" s="22"/>
+      <c r="P273" s="22"/>
+      <c r="Q273" s="22"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -16451,25 +16455,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="24" t="s">
+      <c r="A292" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="B292" s="24"/>
-      <c r="C292" s="24"/>
-      <c r="D292" s="24"/>
-      <c r="E292" s="24"/>
-      <c r="F292" s="24"/>
-      <c r="G292" s="24"/>
-      <c r="H292" s="24"/>
-      <c r="I292" s="24"/>
-      <c r="J292" s="24"/>
-      <c r="K292" s="24"/>
-      <c r="L292" s="24"/>
-      <c r="M292" s="24"/>
-      <c r="N292" s="24"/>
-      <c r="O292" s="24"/>
-      <c r="P292" s="24"/>
-      <c r="Q292" s="24"/>
+      <c r="B292" s="22"/>
+      <c r="C292" s="22"/>
+      <c r="D292" s="22"/>
+      <c r="E292" s="22"/>
+      <c r="F292" s="22"/>
+      <c r="G292" s="22"/>
+      <c r="H292" s="22"/>
+      <c r="I292" s="22"/>
+      <c r="J292" s="22"/>
+      <c r="K292" s="22"/>
+      <c r="L292" s="22"/>
+      <c r="M292" s="22"/>
+      <c r="N292" s="22"/>
+      <c r="O292" s="22"/>
+      <c r="P292" s="22"/>
+      <c r="Q292" s="22"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -17029,25 +17033,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="24" t="s">
+      <c r="A311" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="B311" s="24"/>
-      <c r="C311" s="24"/>
-      <c r="D311" s="24"/>
-      <c r="E311" s="24"/>
-      <c r="F311" s="24"/>
-      <c r="G311" s="24"/>
-      <c r="H311" s="24"/>
-      <c r="I311" s="24"/>
-      <c r="J311" s="24"/>
-      <c r="K311" s="24"/>
-      <c r="L311" s="24"/>
-      <c r="M311" s="24"/>
-      <c r="N311" s="24"/>
-      <c r="O311" s="24"/>
-      <c r="P311" s="24"/>
-      <c r="Q311" s="24"/>
+      <c r="B311" s="22"/>
+      <c r="C311" s="22"/>
+      <c r="D311" s="22"/>
+      <c r="E311" s="22"/>
+      <c r="F311" s="22"/>
+      <c r="G311" s="22"/>
+      <c r="H311" s="22"/>
+      <c r="I311" s="22"/>
+      <c r="J311" s="22"/>
+      <c r="K311" s="22"/>
+      <c r="L311" s="22"/>
+      <c r="M311" s="22"/>
+      <c r="N311" s="22"/>
+      <c r="O311" s="22"/>
+      <c r="P311" s="22"/>
+      <c r="Q311" s="22"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -17608,26 +17612,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A23:Q23"/>
+    <mergeCell ref="A42:Q42"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="A132:Q132"/>
+    <mergeCell ref="A149:Q149"/>
+    <mergeCell ref="A167:Q167"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A219:Q219"/>
     <mergeCell ref="A236:Q236"/>
     <mergeCell ref="A254:Q254"/>
     <mergeCell ref="A273:Q273"/>
     <mergeCell ref="A292:Q292"/>
     <mergeCell ref="A311:Q311"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A167:Q167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="A23:Q23"/>
-    <mergeCell ref="A42:Q42"/>
   </mergeCells>
   <dataValidations count="268">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or SEA" promptTitle="ATS Pick" prompt="Pick NE or SEA" sqref="F6:Q6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -35456,7 +35460,7 @@
       </c>
       <c r="C4">
         <f>Helper!C3</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <f>Helper!D3</f>
@@ -35480,7 +35484,7 @@
       </c>
       <c r="I4">
         <f>Helper!I3</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <f>Helper!J3</f>
@@ -35488,7 +35492,7 @@
       </c>
       <c r="K4">
         <f>MAX(Helper!C3:H3)</f>
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35501,7 +35505,7 @@
       </c>
       <c r="C5">
         <f>Helper!C4</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <f>Helper!D4</f>
@@ -35525,7 +35529,7 @@
       </c>
       <c r="I5">
         <f>Helper!I4</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <f>Helper!J4</f>
@@ -35533,7 +35537,7 @@
       </c>
       <c r="K5">
         <f>MAX(Helper!C4:H4)</f>
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35591,7 +35595,7 @@
       </c>
       <c r="C7">
         <f>Helper!C6</f>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D7">
         <f>Helper!D6</f>
@@ -35615,15 +35619,15 @@
       </c>
       <c r="I7">
         <f>Helper!I6</f>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <f>Helper!J6</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <f>MAX(Helper!C6:H6)</f>
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35636,7 +35640,7 @@
       </c>
       <c r="C8">
         <f>Helper!C7</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D8">
         <f>Helper!D7</f>
@@ -35660,7 +35664,7 @@
       </c>
       <c r="I8">
         <f>Helper!I7</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J8">
         <f>Helper!J7</f>
@@ -35668,7 +35672,7 @@
       </c>
       <c r="K8">
         <f>MAX(Helper!C7:H7)</f>
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35726,7 +35730,7 @@
       </c>
       <c r="C10">
         <f>Helper!C9</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D10">
         <f>Helper!D9</f>
@@ -35750,7 +35754,7 @@
       </c>
       <c r="I10">
         <f>Helper!I9</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <f>Helper!J9</f>
@@ -35758,7 +35762,7 @@
       </c>
       <c r="K10">
         <f>MAX(Helper!C9:H9)</f>
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35771,7 +35775,7 @@
       </c>
       <c r="C11">
         <f>Helper!C10</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <f>Helper!D10</f>
@@ -35795,7 +35799,7 @@
       </c>
       <c r="I11">
         <f>Helper!I10</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <f>Helper!J10</f>
@@ -35803,7 +35807,7 @@
       </c>
       <c r="K11">
         <f>MAX(Helper!C10:H10)</f>
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35816,7 +35820,7 @@
       </c>
       <c r="C12">
         <f>Helper!C11</f>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D12">
         <f>Helper!D11</f>
@@ -35840,15 +35844,15 @@
       </c>
       <c r="I12">
         <f>Helper!I11</f>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J12">
         <f>Helper!J11</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <f>MAX(Helper!C11:H11)</f>
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35861,7 +35865,7 @@
       </c>
       <c r="C13">
         <f>Helper!C12</f>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D13">
         <f>Helper!D12</f>
@@ -35885,15 +35889,15 @@
       </c>
       <c r="I13">
         <f>Helper!I12</f>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J13">
         <f>Helper!J12</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13">
         <f>MAX(Helper!C12:H12)</f>
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35906,7 +35910,7 @@
       </c>
       <c r="C14">
         <f>Helper!C13</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <f>Helper!D13</f>
@@ -35930,7 +35934,7 @@
       </c>
       <c r="I14">
         <f>Helper!I13</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <f>Helper!J13</f>
@@ -35938,7 +35942,7 @@
       </c>
       <c r="K14">
         <f>MAX(Helper!C13:H13)</f>
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -37287,7 +37291,7 @@
       </c>
       <c r="C58">
         <f>Helper!I3</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D58">
         <f>Helper!R3</f>
@@ -37299,11 +37303,11 @@
       </c>
       <c r="F58">
         <f>Helper!AE3</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G58">
         <f>Helper!K3</f>
-        <v>9.0001999999999995</v>
+        <v>6.0002000000000004</v>
       </c>
       <c r="H58">
         <f>Helper!T3</f>
@@ -37320,7 +37324,7 @@
       </c>
       <c r="C59">
         <f>Helper!I4</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D59">
         <f>Helper!R4</f>
@@ -37332,11 +37336,11 @@
       </c>
       <c r="F59">
         <f>Helper!AE4</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G59">
         <f>Helper!K4</f>
-        <v>11.000299999999999</v>
+        <v>8.0002999999999993</v>
       </c>
       <c r="H59">
         <f>Helper!T4</f>
@@ -37386,7 +37390,7 @@
       </c>
       <c r="C61">
         <f>Helper!I6</f>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D61">
         <f>Helper!R6</f>
@@ -37398,11 +37402,11 @@
       </c>
       <c r="F61">
         <f>Helper!AE6</f>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G61">
         <f>Helper!K6</f>
-        <v>16.000499999999999</v>
+        <v>10.000500000000001</v>
       </c>
       <c r="H61">
         <f>Helper!T6</f>
@@ -37419,7 +37423,7 @@
       </c>
       <c r="C62">
         <f>Helper!I7</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D62">
         <f>Helper!R7</f>
@@ -37431,11 +37435,11 @@
       </c>
       <c r="F62">
         <f>Helper!AE7</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G62">
         <f>Helper!K7</f>
-        <v>9.0006000000000004</v>
+        <v>6.0006000000000004</v>
       </c>
       <c r="H62">
         <f>Helper!T7</f>
@@ -37485,7 +37489,7 @@
       </c>
       <c r="C64">
         <f>Helper!I9</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D64">
         <f>Helper!R9</f>
@@ -37497,11 +37501,11 @@
       </c>
       <c r="F64">
         <f>Helper!AE9</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G64">
         <f>Helper!K9</f>
-        <v>11.0008</v>
+        <v>8.0007999999999999</v>
       </c>
       <c r="H64">
         <f>Helper!T9</f>
@@ -37518,7 +37522,7 @@
       </c>
       <c r="C65">
         <f>Helper!I10</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D65">
         <f>Helper!R10</f>
@@ -37530,11 +37534,11 @@
       </c>
       <c r="F65">
         <f>Helper!AE10</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G65">
         <f>Helper!K10</f>
-        <v>11.0009</v>
+        <v>8.0008999999999997</v>
       </c>
       <c r="H65">
         <f>Helper!T10</f>
@@ -37551,7 +37555,7 @@
       </c>
       <c r="C66">
         <f>Helper!I11</f>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D66">
         <f>Helper!R11</f>
@@ -37563,11 +37567,11 @@
       </c>
       <c r="F66">
         <f>Helper!AE11</f>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G66">
         <f>Helper!K11</f>
-        <v>17.001000000000001</v>
+        <v>11.000999999999999</v>
       </c>
       <c r="H66">
         <f>Helper!T11</f>
@@ -37584,7 +37588,7 @@
       </c>
       <c r="C67">
         <f>Helper!I12</f>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D67">
         <f>Helper!R12</f>
@@ -37596,11 +37600,11 @@
       </c>
       <c r="F67">
         <f>Helper!AE12</f>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G67">
         <f>Helper!K12</f>
-        <v>16.001100000000001</v>
+        <v>10.001099999999999</v>
       </c>
       <c r="H67">
         <f>Helper!T12</f>
@@ -37617,7 +37621,7 @@
       </c>
       <c r="C68">
         <f>Helper!I13</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D68">
         <f>Helper!R13</f>
@@ -37629,11 +37633,11 @@
       </c>
       <c r="F68">
         <f>Helper!AE13</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G68">
         <f>Helper!K13</f>
-        <v>11.001200000000001</v>
+        <v>8.0012000000000008</v>
       </c>
       <c r="H68">
         <f>Helper!T13</f>
@@ -37875,7 +37879,7 @@
       </c>
       <c r="C13">
         <f>INDEX(I$40:I$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D13" t="s">
         <v>263</v>
@@ -38369,7 +38373,7 @@
       </c>
       <c r="I41">
         <f>Helper!AE3</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J41" t="b">
         <f t="shared" si="1"/>
@@ -38377,7 +38381,7 @@
       </c>
       <c r="K41">
         <f>IF(J41,-1,I41+0.00002)</f>
-        <v>9.0000199999999992</v>
+        <v>6.0000200000000001</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38387,7 +38391,7 @@
       </c>
       <c r="I42">
         <f>Helper!AE4</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J42" t="b">
         <f t="shared" si="1"/>
@@ -38395,7 +38399,7 @@
       </c>
       <c r="K42">
         <f>IF(J42,-1,I42+0.00003)</f>
-        <v>11.000030000000001</v>
+        <v>8.0000300000000006</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38423,7 +38427,7 @@
       </c>
       <c r="I44">
         <f>Helper!AE6</f>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J44" t="b">
         <f t="shared" si="1"/>
@@ -38431,7 +38435,7 @@
       </c>
       <c r="K44">
         <f>IF(J44,-1,I44+0.00005)</f>
-        <v>16.000050000000002</v>
+        <v>10.00005</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38441,7 +38445,7 @@
       </c>
       <c r="I45">
         <f>Helper!AE7</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J45" t="b">
         <f t="shared" si="1"/>
@@ -38449,7 +38453,7 @@
       </c>
       <c r="K45">
         <f>IF(J45,-1,I45+0.00006)</f>
-        <v>9.0000599999999995</v>
+        <v>6.0000600000000004</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38477,7 +38481,7 @@
       </c>
       <c r="I47">
         <f>Helper!AE9</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J47" t="b">
         <f t="shared" si="1"/>
@@ -38495,7 +38499,7 @@
       </c>
       <c r="I48">
         <f>Helper!AE10</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J48" t="b">
         <f t="shared" si="1"/>
@@ -38503,7 +38507,7 @@
       </c>
       <c r="K48">
         <f>IF(J48,-1,I48+0.00009)</f>
-        <v>11.00009</v>
+        <v>8.0000900000000001</v>
       </c>
     </row>
     <row r="49" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38513,7 +38517,7 @@
       </c>
       <c r="I49">
         <f>Helper!AE11</f>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J49" t="b">
         <f t="shared" si="1"/>
@@ -38531,7 +38535,7 @@
       </c>
       <c r="I50">
         <f>Helper!AE12</f>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J50" t="b">
         <f t="shared" si="1"/>
@@ -38549,7 +38553,7 @@
       </c>
       <c r="I51">
         <f>Helper!AE13</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J51" t="b">
         <f t="shared" si="1"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A54A9CC-24FF-4567-8677-5824C811EB55}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AD18BB0-0DBD-4B56-A4AD-219CD650D677}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3395" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3407" uniqueCount="346">
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -1472,10 +1472,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1859,7 +1855,7 @@
         <v>23</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2704,7 +2700,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
@@ -2974,7 +2970,7 @@
       </c>
       <c r="C3">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H7,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G7,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H22,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G22,0)</f>
@@ -2998,7 +2994,7 @@
       </c>
       <c r="I3">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F7="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F22="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F37="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F52="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F67="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F82="W"),1,0)</f>
@@ -3006,7 +3002,7 @@
       </c>
       <c r="K3">
         <f>I3+0.0002</f>
-        <v>6.0002000000000004</v>
+        <v>7.0002000000000004</v>
       </c>
       <c r="L3">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H7,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G7,0)</f>
@@ -3086,11 +3082,11 @@
       </c>
       <c r="AE3">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF3">
         <f>AE3+0.0002</f>
-        <v>6.0002000000000004</v>
+        <v>7.0002000000000004</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3103,7 +3099,7 @@
       </c>
       <c r="C4">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H8,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G8,0)</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H23,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G23,0)</f>
@@ -3127,15 +3123,15 @@
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J4">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F8="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F23="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F38="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F53="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F68="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F83="W"),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <f>I4+0.0003</f>
-        <v>8.0002999999999993</v>
+        <v>14.000299999999999</v>
       </c>
       <c r="L4">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H8,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G8,0)</f>
@@ -3215,11 +3211,11 @@
       </c>
       <c r="AE4">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AF4">
         <f>AE4+0.0003</f>
-        <v>8.0002999999999993</v>
+        <v>14.000299999999999</v>
       </c>
     </row>
     <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3232,7 +3228,7 @@
       </c>
       <c r="C5">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H9,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G9,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H24,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G24,0)</f>
@@ -3256,7 +3252,7 @@
       </c>
       <c r="I5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F9="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F24="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F39="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F54="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F69="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F84="W"),1,0)</f>
@@ -3264,7 +3260,7 @@
       </c>
       <c r="K5">
         <f>I5+0.0004</f>
-        <v>5.0004</v>
+        <v>6.0004</v>
       </c>
       <c r="L5">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H9,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G9,0)</f>
@@ -3344,11 +3340,11 @@
       </c>
       <c r="AE5">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF5">
         <f>AE5+0.0004</f>
-        <v>5.0004</v>
+        <v>6.0004</v>
       </c>
     </row>
     <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3361,7 +3357,7 @@
       </c>
       <c r="C6">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H10,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G10,0)</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H25,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G25,0)</f>
@@ -3385,15 +3381,15 @@
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J6">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F10="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F25="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F40="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F55="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F70="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F85="W"),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
         <f>I6+0.0005</f>
-        <v>10.000500000000001</v>
+        <v>16.000499999999999</v>
       </c>
       <c r="L6">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H10,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G10,0)</f>
@@ -3473,11 +3469,11 @@
       </c>
       <c r="AE6">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AF6">
         <f>AE6+0.0005</f>
-        <v>10.000500000000001</v>
+        <v>16.000499999999999</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3490,7 +3486,7 @@
       </c>
       <c r="C7">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H11,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G11,0)</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D7">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H26,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G26,0)</f>
@@ -3514,15 +3510,15 @@
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J7">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F11="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F26="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F41="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F56="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F71="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F86="W"),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <f>I7+0.0006</f>
-        <v>6.0006000000000004</v>
+        <v>13.0006</v>
       </c>
       <c r="L7">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H11,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G11,0)</f>
@@ -3602,11 +3598,11 @@
       </c>
       <c r="AE7">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AF7">
         <f>AE7+0.0006</f>
-        <v>6.0006000000000004</v>
+        <v>13.0006</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4006,7 +4002,7 @@
       </c>
       <c r="C11">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H15,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G15,0)</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D11">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H30,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G30,0)</f>
@@ -4030,15 +4026,15 @@
       </c>
       <c r="I11">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J11">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F15="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F30="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F45="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F60="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F75="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F90="W"),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <f>I11+0.001</f>
-        <v>11.000999999999999</v>
+        <v>17.001000000000001</v>
       </c>
       <c r="L11">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H15,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G15,0)</f>
@@ -4118,11 +4114,11 @@
       </c>
       <c r="AE11">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AF11">
         <f>AE11+0.001</f>
-        <v>11.000999999999999</v>
+        <v>17.001000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4135,7 +4131,7 @@
       </c>
       <c r="C12">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H16,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G16,0)</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D12">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H31,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G31,0)</f>
@@ -4159,15 +4155,15 @@
       </c>
       <c r="I12">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J12">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F16="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F31="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F46="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F61="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F76="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F91="W"),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <f>I12+0.0011</f>
-        <v>10.001099999999999</v>
+        <v>16.001100000000001</v>
       </c>
       <c r="L12">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H16,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G16,0)</f>
@@ -4247,11 +4243,11 @@
       </c>
       <c r="AE12">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AF12">
         <f>AE12+0.0011</f>
-        <v>10.001099999999999</v>
+        <v>16.001100000000001</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4264,7 +4260,7 @@
       </c>
       <c r="C13">
         <f>IF(Roster!$B$16&gt;=1,'Wk 1-6 Input'!H17,0)+IF(Roster!$B$16&gt;1,'Wk 1-6 Input'!G17,0)</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H32,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G32,0)</f>
@@ -4288,15 +4284,15 @@
       </c>
       <c r="I13">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J13">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F17="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F32="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F47="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F62="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F77="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F92="W"),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <f>I13+0.0012</f>
-        <v>8.0012000000000008</v>
+        <v>15.001200000000001</v>
       </c>
       <c r="L13">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H17,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G17,0)</f>
@@ -4376,11 +4372,11 @@
       </c>
       <c r="AE13">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AF13">
         <f>AE13+0.0012</f>
-        <v>8.0012000000000008</v>
+        <v>15.001200000000001</v>
       </c>
     </row>
   </sheetData>
@@ -8225,20 +8221,44 @@
       </c>
       <c r="E21" s="9" t="str">
         <f>'NFL Schedule'!J18</f>
-        <v/>
-      </c>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="10"/>
-      <c r="Q21" s="10"/>
+        <v>KC</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="L21" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="M21" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="N21" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="O21" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="P21" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q21" s="10" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
@@ -8247,22 +8267,46 @@
       <c r="B22" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="E22" s="13" t="str">
+      <c r="E22" s="13">
         <f>'NFL Schedule'!E19</f>
-        <v/>
-      </c>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14"/>
-      <c r="Q22" s="14"/>
+        <v>41</v>
+      </c>
+      <c r="F22" s="14">
+        <v>43</v>
+      </c>
+      <c r="G22" s="14">
+        <v>50</v>
+      </c>
+      <c r="H22" s="14">
+        <v>39</v>
+      </c>
+      <c r="I22" s="14">
+        <v>40</v>
+      </c>
+      <c r="J22" s="14">
+        <v>30</v>
+      </c>
+      <c r="K22" s="14">
+        <v>42</v>
+      </c>
+      <c r="L22" s="14">
+        <v>52</v>
+      </c>
+      <c r="M22" s="14">
+        <v>46</v>
+      </c>
+      <c r="N22" s="14">
+        <v>44</v>
+      </c>
+      <c r="O22" s="14">
+        <v>34</v>
+      </c>
+      <c r="P22" s="14">
+        <v>41</v>
+      </c>
+      <c r="Q22" s="14">
+        <v>51</v>
+      </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
@@ -19280,21 +19324,34 @@
       <c r="D18" t="s">
         <v>87</v>
       </c>
+      <c r="E18">
+        <v>10</v>
+      </c>
       <c r="F18" t="s">
         <v>88</v>
       </c>
+      <c r="G18">
+        <v>31</v>
+      </c>
+      <c r="H18">
+        <v>2.5</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" si="0"/>
+        <v>KC</v>
+      </c>
       <c r="J18" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>KC</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D19" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="E19" s="16" t="str">
+      <c r="E19" s="16">
         <f>IF(AND(E18&lt;&gt;"",G18&lt;&gt;""),E18+G18,"")</f>
-        <v/>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26950,30 +27007,30 @@
       </c>
       <c r="C7" s="3">
         <f>SUMPRODUCT(('Picks Detail'!G6:G21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*('Picks Detail'!G6:G21='Picks Detail'!E6:E21))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>6</v>
       </c>
       <c r="E7">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(6,A$6:A$17,0)),0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" t="str">
         <f>IF(C7=0,"-",IF(C7&gt;E7,"W",IF(C7&lt;E7,"L",IF(AND('Picks Detail'!E22&lt;&gt;"",INDEX('Picks Detail'!F22:Q22,1,A7)&lt;&gt;"",INDEX('Picks Detail'!F22:Q22,1,D7)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F22:Q22,1,A7)-'Picks Detail'!E22)&lt;ABS(INDEX('Picks Detail'!F22:Q22,1,D7)-'Picks Detail'!E22),"W",IF(ABS(INDEX('Picks Detail'!F22:Q22,1,A7)-'Picks Detail'!E22)&gt;ABS(INDEX('Picks Detail'!F22:Q22,1,D7)-'Picks Detail'!E22),"L","T")),"T"))))</f>
-        <v>T</v>
+        <v>L</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26997,11 +27054,11 @@
       </c>
       <c r="F8" t="str">
         <f>IF(C8=0,"-",IF(C8&gt;E8,"W",IF(C8&lt;E8,"L",IF(AND('Picks Detail'!E22&lt;&gt;"",INDEX('Picks Detail'!F22:Q22,1,A8)&lt;&gt;"",INDEX('Picks Detail'!F22:Q22,1,D8)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F22:Q22,1,A8)-'Picks Detail'!E22)&lt;ABS(INDEX('Picks Detail'!F22:Q22,1,D8)-'Picks Detail'!E22),"W",IF(ABS(INDEX('Picks Detail'!F22:Q22,1,A8)-'Picks Detail'!E22)&gt;ABS(INDEX('Picks Detail'!F22:Q22,1,D8)-'Picks Detail'!E22),"L","T")),"T"))))</f>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H8">
         <f t="shared" si="1"/>
@@ -27009,7 +27066,7 @@
       </c>
       <c r="I8">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27022,7 +27079,7 @@
       </c>
       <c r="C9" s="3">
         <f>SUMPRODUCT(('Picks Detail'!I6:I21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*('Picks Detail'!I6:I21='Picks Detail'!E6:E21))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9">
         <v>10</v>
@@ -27041,11 +27098,11 @@
       </c>
       <c r="H9">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27094,30 +27151,30 @@
       </c>
       <c r="C11" s="3">
         <f>SUMPRODUCT(('Picks Detail'!K6:K21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*('Picks Detail'!K6:K21='Picks Detail'!E6:E21))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
       <c r="E11">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(2,A$6:A$17,0)),0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" t="str">
         <f>IF(C11=0,"-",IF(C11&gt;E11,"W",IF(C11&lt;E11,"L",IF(AND('Picks Detail'!E22&lt;&gt;"",INDEX('Picks Detail'!F22:Q22,1,A11)&lt;&gt;"",INDEX('Picks Detail'!F22:Q22,1,D11)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F22:Q22,1,A11)-'Picks Detail'!E22)&lt;ABS(INDEX('Picks Detail'!F22:Q22,1,D11)-'Picks Detail'!E22),"W",IF(ABS(INDEX('Picks Detail'!F22:Q22,1,A11)-'Picks Detail'!E22)&gt;ABS(INDEX('Picks Detail'!F22:Q22,1,D11)-'Picks Detail'!E22),"L","T")),"T"))))</f>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="G11">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H11">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I11">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27173,15 +27230,15 @@
       </c>
       <c r="E13">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(12,A$6:A$17,0)),0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="str">
         <f>IF(C13=0,"-",IF(C13&gt;E13,"W",IF(C13&lt;E13,"L",IF(AND('Picks Detail'!E22&lt;&gt;"",INDEX('Picks Detail'!F22:Q22,1,A13)&lt;&gt;"",INDEX('Picks Detail'!F22:Q22,1,D13)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F22:Q22,1,A13)-'Picks Detail'!E22)&lt;ABS(INDEX('Picks Detail'!F22:Q22,1,D13)-'Picks Detail'!E22),"W",IF(ABS(INDEX('Picks Detail'!F22:Q22,1,A13)-'Picks Detail'!E22)&gt;ABS(INDEX('Picks Detail'!F22:Q22,1,D13)-'Picks Detail'!E22),"L","T")),"T"))))</f>
-        <v>T</v>
+        <v>L</v>
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H13">
         <f t="shared" si="1"/>
@@ -27189,7 +27246,7 @@
       </c>
       <c r="I13">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27213,11 +27270,11 @@
       </c>
       <c r="F14" t="str">
         <f>IF(C14=0,"-",IF(C14&gt;E14,"W",IF(C14&lt;E14,"L",IF(AND('Picks Detail'!E22&lt;&gt;"",INDEX('Picks Detail'!F22:Q22,1,A14)&lt;&gt;"",INDEX('Picks Detail'!F22:Q22,1,D14)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F22:Q22,1,A14)-'Picks Detail'!E22)&lt;ABS(INDEX('Picks Detail'!F22:Q22,1,D14)-'Picks Detail'!E22),"W",IF(ABS(INDEX('Picks Detail'!F22:Q22,1,A14)-'Picks Detail'!E22)&gt;ABS(INDEX('Picks Detail'!F22:Q22,1,D14)-'Picks Detail'!E22),"L","T")),"T"))))</f>
-        <v>T</v>
+        <v>L</v>
       </c>
       <c r="G14">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H14">
         <f t="shared" si="1"/>
@@ -27225,7 +27282,7 @@
       </c>
       <c r="I14">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27245,7 +27302,7 @@
       </c>
       <c r="E15">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(4,A$6:A$17,0)),0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F15" t="str">
         <f>IF(C15=0,"-",IF(C15&gt;E15,"W",IF(C15&lt;E15,"L",IF(AND('Picks Detail'!E22&lt;&gt;"",INDEX('Picks Detail'!F22:Q22,1,A15)&lt;&gt;"",INDEX('Picks Detail'!F22:Q22,1,D15)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F22:Q22,1,A15)-'Picks Detail'!E22)&lt;ABS(INDEX('Picks Detail'!F22:Q22,1,D15)-'Picks Detail'!E22),"W",IF(ABS(INDEX('Picks Detail'!F22:Q22,1,A15)-'Picks Detail'!E22)&gt;ABS(INDEX('Picks Detail'!F22:Q22,1,D15)-'Picks Detail'!E22),"L","T")),"T"))))</f>
@@ -27310,7 +27367,7 @@
       </c>
       <c r="C17" s="3">
         <f>SUMPRODUCT(('Picks Detail'!Q6:Q21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*('Picks Detail'!Q6:Q21='Picks Detail'!E6:E21))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17">
         <v>8</v>
@@ -27321,19 +27378,19 @@
       </c>
       <c r="F17" t="str">
         <f>IF(C17=0,"-",IF(C17&gt;E17,"W",IF(C17&lt;E17,"L",IF(AND('Picks Detail'!E22&lt;&gt;"",INDEX('Picks Detail'!F22:Q22,1,A17)&lt;&gt;"",INDEX('Picks Detail'!F22:Q22,1,D17)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F22:Q22,1,A17)-'Picks Detail'!E22)&lt;ABS(INDEX('Picks Detail'!F22:Q22,1,D17)-'Picks Detail'!E22),"W",IF(ABS(INDEX('Picks Detail'!F22:Q22,1,A17)-'Picks Detail'!E22)&gt;ABS(INDEX('Picks Detail'!F22:Q22,1,D17)-'Picks Detail'!E22),"L","T")),"T"))))</f>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="G17">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H17">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I17">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35456,7 +35513,7 @@
       </c>
       <c r="C4">
         <f>Helper!C3</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <f>Helper!D3</f>
@@ -35480,7 +35537,7 @@
       </c>
       <c r="I4">
         <f>Helper!I3</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <f>Helper!J3</f>
@@ -35488,7 +35545,7 @@
       </c>
       <c r="K4">
         <f>MAX(Helper!C3:H3)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35501,7 +35558,7 @@
       </c>
       <c r="C5">
         <f>Helper!C4</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D5">
         <f>Helper!D4</f>
@@ -35525,15 +35582,15 @@
       </c>
       <c r="I5">
         <f>Helper!I4</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J5">
         <f>Helper!J4</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <f>MAX(Helper!C4:H4)</f>
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35546,7 +35603,7 @@
       </c>
       <c r="C6">
         <f>Helper!C5</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6">
         <f>Helper!D5</f>
@@ -35570,7 +35627,7 @@
       </c>
       <c r="I6">
         <f>Helper!I5</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <f>Helper!J5</f>
@@ -35578,7 +35635,7 @@
       </c>
       <c r="K6">
         <f>MAX(Helper!C5:H5)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35591,7 +35648,7 @@
       </c>
       <c r="C7">
         <f>Helper!C6</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D7">
         <f>Helper!D6</f>
@@ -35615,15 +35672,15 @@
       </c>
       <c r="I7">
         <f>Helper!I6</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J7">
         <f>Helper!J6</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <f>MAX(Helper!C6:H6)</f>
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35636,7 +35693,7 @@
       </c>
       <c r="C8">
         <f>Helper!C7</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D8">
         <f>Helper!D7</f>
@@ -35660,15 +35717,15 @@
       </c>
       <c r="I8">
         <f>Helper!I7</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J8">
         <f>Helper!J7</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
         <f>MAX(Helper!C7:H7)</f>
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35816,7 +35873,7 @@
       </c>
       <c r="C12">
         <f>Helper!C11</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D12">
         <f>Helper!D11</f>
@@ -35840,15 +35897,15 @@
       </c>
       <c r="I12">
         <f>Helper!I11</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J12">
         <f>Helper!J11</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <f>MAX(Helper!C11:H11)</f>
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35861,7 +35918,7 @@
       </c>
       <c r="C13">
         <f>Helper!C12</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D13">
         <f>Helper!D12</f>
@@ -35885,15 +35942,15 @@
       </c>
       <c r="I13">
         <f>Helper!I12</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J13">
         <f>Helper!J12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <f>MAX(Helper!C12:H12)</f>
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35906,7 +35963,7 @@
       </c>
       <c r="C14">
         <f>Helper!C13</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D14">
         <f>Helper!D13</f>
@@ -35930,15 +35987,15 @@
       </c>
       <c r="I14">
         <f>Helper!I13</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J14">
         <f>Helper!J13</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <f>MAX(Helper!C13:H13)</f>
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -37287,7 +37344,7 @@
       </c>
       <c r="C58">
         <f>Helper!I3</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D58">
         <f>Helper!R3</f>
@@ -37299,11 +37356,11 @@
       </c>
       <c r="F58">
         <f>Helper!AE3</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G58">
         <f>Helper!K3</f>
-        <v>6.0002000000000004</v>
+        <v>7.0002000000000004</v>
       </c>
       <c r="H58">
         <f>Helper!T3</f>
@@ -37320,7 +37377,7 @@
       </c>
       <c r="C59">
         <f>Helper!I4</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D59">
         <f>Helper!R4</f>
@@ -37332,11 +37389,11 @@
       </c>
       <c r="F59">
         <f>Helper!AE4</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G59">
         <f>Helper!K4</f>
-        <v>8.0002999999999993</v>
+        <v>14.000299999999999</v>
       </c>
       <c r="H59">
         <f>Helper!T4</f>
@@ -37353,7 +37410,7 @@
       </c>
       <c r="C60">
         <f>Helper!I5</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D60">
         <f>Helper!R5</f>
@@ -37365,11 +37422,11 @@
       </c>
       <c r="F60">
         <f>Helper!AE5</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G60">
         <f>Helper!K5</f>
-        <v>5.0004</v>
+        <v>6.0004</v>
       </c>
       <c r="H60">
         <f>Helper!T5</f>
@@ -37386,7 +37443,7 @@
       </c>
       <c r="C61">
         <f>Helper!I6</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D61">
         <f>Helper!R6</f>
@@ -37398,11 +37455,11 @@
       </c>
       <c r="F61">
         <f>Helper!AE6</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G61">
         <f>Helper!K6</f>
-        <v>10.000500000000001</v>
+        <v>16.000499999999999</v>
       </c>
       <c r="H61">
         <f>Helper!T6</f>
@@ -37419,7 +37476,7 @@
       </c>
       <c r="C62">
         <f>Helper!I7</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D62">
         <f>Helper!R7</f>
@@ -37431,11 +37488,11 @@
       </c>
       <c r="F62">
         <f>Helper!AE7</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G62">
         <f>Helper!K7</f>
-        <v>6.0006000000000004</v>
+        <v>13.0006</v>
       </c>
       <c r="H62">
         <f>Helper!T7</f>
@@ -37551,7 +37608,7 @@
       </c>
       <c r="C66">
         <f>Helper!I11</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D66">
         <f>Helper!R11</f>
@@ -37563,11 +37620,11 @@
       </c>
       <c r="F66">
         <f>Helper!AE11</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G66">
         <f>Helper!K11</f>
-        <v>11.000999999999999</v>
+        <v>17.001000000000001</v>
       </c>
       <c r="H66">
         <f>Helper!T11</f>
@@ -37584,7 +37641,7 @@
       </c>
       <c r="C67">
         <f>Helper!I12</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D67">
         <f>Helper!R12</f>
@@ -37596,11 +37653,11 @@
       </c>
       <c r="F67">
         <f>Helper!AE12</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G67">
         <f>Helper!K12</f>
-        <v>10.001099999999999</v>
+        <v>16.001100000000001</v>
       </c>
       <c r="H67">
         <f>Helper!T12</f>
@@ -37617,7 +37674,7 @@
       </c>
       <c r="C68">
         <f>Helper!I13</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D68">
         <f>Helper!R13</f>
@@ -37629,11 +37686,11 @@
       </c>
       <c r="F68">
         <f>Helper!AE13</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G68">
         <f>Helper!K13</f>
-        <v>8.0012000000000008</v>
+        <v>15.001200000000001</v>
       </c>
       <c r="H68">
         <f>Helper!T13</f>
@@ -37875,7 +37932,7 @@
       </c>
       <c r="C13">
         <f>INDEX(I$40:I$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
         <v>263</v>
@@ -38369,7 +38426,7 @@
       </c>
       <c r="I41">
         <f>Helper!AE3</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J41" t="b">
         <f t="shared" si="1"/>
@@ -38377,7 +38434,7 @@
       </c>
       <c r="K41">
         <f>IF(J41,-1,I41+0.00002)</f>
-        <v>6.0000200000000001</v>
+        <v>7.0000200000000001</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38387,7 +38444,7 @@
       </c>
       <c r="I42">
         <f>Helper!AE4</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J42" t="b">
         <f t="shared" si="1"/>
@@ -38395,7 +38452,7 @@
       </c>
       <c r="K42">
         <f>IF(J42,-1,I42+0.00003)</f>
-        <v>8.0000300000000006</v>
+        <v>14.000030000000001</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38405,7 +38462,7 @@
       </c>
       <c r="I43">
         <f>Helper!AE5</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J43" t="b">
         <f t="shared" si="1"/>
@@ -38423,7 +38480,7 @@
       </c>
       <c r="I44">
         <f>Helper!AE6</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J44" t="b">
         <f t="shared" si="1"/>
@@ -38431,7 +38488,7 @@
       </c>
       <c r="K44">
         <f>IF(J44,-1,I44+0.00005)</f>
-        <v>10.00005</v>
+        <v>16.000050000000002</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38441,7 +38498,7 @@
       </c>
       <c r="I45">
         <f>Helper!AE7</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J45" t="b">
         <f t="shared" si="1"/>
@@ -38449,7 +38506,7 @@
       </c>
       <c r="K45">
         <f>IF(J45,-1,I45+0.00006)</f>
-        <v>6.0000600000000004</v>
+        <v>13.00006</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38513,7 +38570,7 @@
       </c>
       <c r="I49">
         <f>Helper!AE11</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J49" t="b">
         <f t="shared" si="1"/>
@@ -38531,7 +38588,7 @@
       </c>
       <c r="I50">
         <f>Helper!AE12</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J50" t="b">
         <f t="shared" si="1"/>
@@ -38549,7 +38606,7 @@
       </c>
       <c r="I51">
         <f>Helper!AE13</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J51" t="b">
         <f t="shared" si="1"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AD18BB0-0DBD-4B56-A4AD-219CD650D677}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26ECA4AB-7CAB-409D-9E8D-B317035D7FAE}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3407" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3419" uniqueCount="346">
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -1377,16 +1377,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1470,6 +1470,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1661,12 +1665,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -2845,7 +2849,7 @@
       </c>
       <c r="D2">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H21,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G21,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H36,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G36,0)</f>
@@ -2865,7 +2869,7 @@
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I13" si="0">SUM(C2:H2)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J2">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F6="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F21="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F36="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F51="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F66="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F81="W"),1,0)</f>
@@ -2873,7 +2877,7 @@
       </c>
       <c r="K2">
         <f>I2+0.0001</f>
-        <v>5.0000999999999998</v>
+        <v>6.0000999999999998</v>
       </c>
       <c r="L2">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H6,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G6,0)</f>
@@ -2953,11 +2957,11 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE13" si="2">I2+R2+AC2</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF2">
         <f>AE2+0.0001</f>
-        <v>5.0000999999999998</v>
+        <v>6.0000999999999998</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2974,7 +2978,7 @@
       </c>
       <c r="D3">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H22,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G22,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H37,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G37,0)</f>
@@ -2994,7 +2998,7 @@
       </c>
       <c r="I3">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J3">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F7="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F22="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F37="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F52="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F67="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F82="W"),1,0)</f>
@@ -3002,7 +3006,7 @@
       </c>
       <c r="K3">
         <f>I3+0.0002</f>
-        <v>7.0002000000000004</v>
+        <v>8.0001999999999995</v>
       </c>
       <c r="L3">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H7,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G7,0)</f>
@@ -3082,11 +3086,11 @@
       </c>
       <c r="AE3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF3">
         <f>AE3+0.0002</f>
-        <v>7.0002000000000004</v>
+        <v>8.0001999999999995</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3232,7 +3236,7 @@
       </c>
       <c r="D5">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H24,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G24,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H39,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G39,0)</f>
@@ -3252,7 +3256,7 @@
       </c>
       <c r="I5">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F9="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F24="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F39="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F54="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F69="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F84="W"),1,0)</f>
@@ -3260,7 +3264,7 @@
       </c>
       <c r="K5">
         <f>I5+0.0004</f>
-        <v>6.0004</v>
+        <v>7.0004</v>
       </c>
       <c r="L5">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H9,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G9,0)</f>
@@ -3340,11 +3344,11 @@
       </c>
       <c r="AE5">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF5">
         <f>AE5+0.0004</f>
-        <v>6.0004</v>
+        <v>7.0004</v>
       </c>
     </row>
     <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3361,7 +3365,7 @@
       </c>
       <c r="D6">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H25,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G25,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H40,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G40,0)</f>
@@ -3381,7 +3385,7 @@
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J6">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F10="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F25="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F40="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F55="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F70="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F85="W"),1,0)</f>
@@ -3389,7 +3393,7 @@
       </c>
       <c r="K6">
         <f>I6+0.0005</f>
-        <v>16.000499999999999</v>
+        <v>17.000499999999999</v>
       </c>
       <c r="L6">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H10,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G10,0)</f>
@@ -3469,11 +3473,11 @@
       </c>
       <c r="AE6">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF6">
         <f>AE6+0.0005</f>
-        <v>16.000499999999999</v>
+        <v>17.000499999999999</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3490,7 +3494,7 @@
       </c>
       <c r="D7">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H26,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G26,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H41,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G41,0)</f>
@@ -3510,7 +3514,7 @@
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F11="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F26="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F41="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F56="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F71="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F86="W"),1,0)</f>
@@ -3518,7 +3522,7 @@
       </c>
       <c r="K7">
         <f>I7+0.0006</f>
-        <v>13.0006</v>
+        <v>14.0006</v>
       </c>
       <c r="L7">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H11,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G11,0)</f>
@@ -3598,11 +3602,11 @@
       </c>
       <c r="AE7">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF7">
         <f>AE7+0.0006</f>
-        <v>13.0006</v>
+        <v>14.0006</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3619,7 +3623,7 @@
       </c>
       <c r="D8">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H27,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G27,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H42,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G42,0)</f>
@@ -3639,7 +3643,7 @@
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F12="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F27="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F42="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F57="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F72="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F87="W"),1,0)</f>
@@ -3647,7 +3651,7 @@
       </c>
       <c r="K8">
         <f>I8+0.0007</f>
-        <v>7.0007000000000001</v>
+        <v>8.0007000000000001</v>
       </c>
       <c r="L8">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H12,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G12,0)</f>
@@ -3727,11 +3731,11 @@
       </c>
       <c r="AE8">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF8">
         <f>AE8+0.0007</f>
-        <v>7.0007000000000001</v>
+        <v>8.0007000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3748,7 +3752,7 @@
       </c>
       <c r="D9">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H28,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G28,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H43,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G43,0)</f>
@@ -3768,7 +3772,7 @@
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J9">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F13="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F28="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F43="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F58="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F73="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F88="W"),1,0)</f>
@@ -3776,7 +3780,7 @@
       </c>
       <c r="K9">
         <f>I9+0.0008</f>
-        <v>8.0007999999999999</v>
+        <v>9.0007999999999999</v>
       </c>
       <c r="L9">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H13,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G13,0)</f>
@@ -3856,11 +3860,11 @@
       </c>
       <c r="AE9">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF9">
         <f>AE9+0.0008</f>
-        <v>8.0007999999999999</v>
+        <v>9.0007999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4006,7 +4010,7 @@
       </c>
       <c r="D11">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H30,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G30,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H45,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G45,0)</f>
@@ -4026,7 +4030,7 @@
       </c>
       <c r="I11">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J11">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F15="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F30="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F45="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F60="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F75="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F90="W"),1,0)</f>
@@ -4034,7 +4038,7 @@
       </c>
       <c r="K11">
         <f>I11+0.001</f>
-        <v>17.001000000000001</v>
+        <v>18.001000000000001</v>
       </c>
       <c r="L11">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H15,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G15,0)</f>
@@ -4114,11 +4118,11 @@
       </c>
       <c r="AE11">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF11">
         <f>AE11+0.001</f>
-        <v>17.001000000000001</v>
+        <v>18.001000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4264,7 +4268,7 @@
       </c>
       <c r="D13">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H32,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G32,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H47,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G47,0)</f>
@@ -4284,7 +4288,7 @@
       </c>
       <c r="I13">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J13">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F17="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F32="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F47="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F62="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F77="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F92="W"),1,0)</f>
@@ -4292,7 +4296,7 @@
       </c>
       <c r="K13">
         <f>I13+0.0012</f>
-        <v>15.001200000000001</v>
+        <v>16.001200000000001</v>
       </c>
       <c r="L13">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H17,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G17,0)</f>
@@ -4372,11 +4376,11 @@
       </c>
       <c r="AE13">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF13">
         <f>AE13+0.0012</f>
-        <v>15.001200000000001</v>
+        <v>16.001200000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4398,14 +4402,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -5350,14 +5354,14 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
@@ -6302,14 +6306,14 @@
       </c>
     </row>
     <row r="111" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="23" t="s">
+      <c r="A111" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B111" s="23"/>
-      <c r="C111" s="23"/>
-      <c r="D111" s="23"/>
-      <c r="E111" s="23"/>
-      <c r="F111" s="23"/>
+      <c r="B111" s="22"/>
+      <c r="C111" s="22"/>
+      <c r="D111" s="22"/>
+      <c r="E111" s="22"/>
+      <c r="F111" s="22"/>
     </row>
     <row r="112" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
@@ -7281,67 +7285,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="24"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8309,25 +8313,25 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="24"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -8397,20 +8401,44 @@
       </c>
       <c r="E25" s="9" t="str">
         <f>'NFL Schedule'!J22</f>
-        <v/>
-      </c>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="10"/>
-      <c r="Q25" s="10"/>
+        <v>BUF</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="M25" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="N25" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="O25" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="P25" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q25" s="10" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
@@ -8887,25 +8915,25 @@
       <c r="Q41" s="14"/>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+      <c r="A42" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="24"/>
-      <c r="K42" s="24"/>
-      <c r="L42" s="24"/>
-      <c r="M42" s="24"/>
-      <c r="N42" s="24"/>
-      <c r="O42" s="24"/>
-      <c r="P42" s="24"/>
-      <c r="Q42" s="24"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
+      <c r="I42" s="29"/>
+      <c r="J42" s="29"/>
+      <c r="K42" s="29"/>
+      <c r="L42" s="29"/>
+      <c r="M42" s="29"/>
+      <c r="N42" s="29"/>
+      <c r="O42" s="29"/>
+      <c r="P42" s="29"/>
+      <c r="Q42" s="29"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -9465,25 +9493,25 @@
       <c r="Q60" s="14"/>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="24" t="s">
+      <c r="A61" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="24"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="24"/>
-      <c r="J61" s="24"/>
-      <c r="K61" s="24"/>
-      <c r="L61" s="24"/>
-      <c r="M61" s="24"/>
-      <c r="N61" s="24"/>
-      <c r="O61" s="24"/>
-      <c r="P61" s="24"/>
-      <c r="Q61" s="24"/>
+      <c r="B61" s="29"/>
+      <c r="C61" s="29"/>
+      <c r="D61" s="29"/>
+      <c r="E61" s="29"/>
+      <c r="F61" s="29"/>
+      <c r="G61" s="29"/>
+      <c r="H61" s="29"/>
+      <c r="I61" s="29"/>
+      <c r="J61" s="29"/>
+      <c r="K61" s="29"/>
+      <c r="L61" s="29"/>
+      <c r="M61" s="29"/>
+      <c r="N61" s="29"/>
+      <c r="O61" s="29"/>
+      <c r="P61" s="29"/>
+      <c r="Q61" s="29"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -10043,25 +10071,25 @@
       <c r="Q79" s="14"/>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="24" t="s">
+      <c r="A80" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="24"/>
-      <c r="C80" s="24"/>
-      <c r="D80" s="24"/>
-      <c r="E80" s="24"/>
-      <c r="F80" s="24"/>
-      <c r="G80" s="24"/>
-      <c r="H80" s="24"/>
-      <c r="I80" s="24"/>
-      <c r="J80" s="24"/>
-      <c r="K80" s="24"/>
-      <c r="L80" s="24"/>
-      <c r="M80" s="24"/>
-      <c r="N80" s="24"/>
-      <c r="O80" s="24"/>
-      <c r="P80" s="24"/>
-      <c r="Q80" s="24"/>
+      <c r="B80" s="29"/>
+      <c r="C80" s="29"/>
+      <c r="D80" s="29"/>
+      <c r="E80" s="29"/>
+      <c r="F80" s="29"/>
+      <c r="G80" s="29"/>
+      <c r="H80" s="29"/>
+      <c r="I80" s="29"/>
+      <c r="J80" s="29"/>
+      <c r="K80" s="29"/>
+      <c r="L80" s="29"/>
+      <c r="M80" s="29"/>
+      <c r="N80" s="29"/>
+      <c r="O80" s="29"/>
+      <c r="P80" s="29"/>
+      <c r="Q80" s="29"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -10591,25 +10619,25 @@
       <c r="Q97" s="14"/>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="24" t="s">
+      <c r="A98" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="24"/>
-      <c r="C98" s="24"/>
-      <c r="D98" s="24"/>
-      <c r="E98" s="24"/>
-      <c r="F98" s="24"/>
-      <c r="G98" s="24"/>
-      <c r="H98" s="24"/>
-      <c r="I98" s="24"/>
-      <c r="J98" s="24"/>
-      <c r="K98" s="24"/>
-      <c r="L98" s="24"/>
-      <c r="M98" s="24"/>
-      <c r="N98" s="24"/>
-      <c r="O98" s="24"/>
-      <c r="P98" s="24"/>
-      <c r="Q98" s="24"/>
+      <c r="B98" s="29"/>
+      <c r="C98" s="29"/>
+      <c r="D98" s="29"/>
+      <c r="E98" s="29"/>
+      <c r="F98" s="29"/>
+      <c r="G98" s="29"/>
+      <c r="H98" s="29"/>
+      <c r="I98" s="29"/>
+      <c r="J98" s="29"/>
+      <c r="K98" s="29"/>
+      <c r="L98" s="29"/>
+      <c r="M98" s="29"/>
+      <c r="N98" s="29"/>
+      <c r="O98" s="29"/>
+      <c r="P98" s="29"/>
+      <c r="Q98" s="29"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -11109,25 +11137,25 @@
       <c r="Q114" s="14"/>
     </row>
     <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="24" t="s">
+      <c r="A115" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="24"/>
-      <c r="C115" s="24"/>
-      <c r="D115" s="24"/>
-      <c r="E115" s="24"/>
-      <c r="F115" s="24"/>
-      <c r="G115" s="24"/>
-      <c r="H115" s="24"/>
-      <c r="I115" s="24"/>
-      <c r="J115" s="24"/>
-      <c r="K115" s="24"/>
-      <c r="L115" s="24"/>
-      <c r="M115" s="24"/>
-      <c r="N115" s="24"/>
-      <c r="O115" s="24"/>
-      <c r="P115" s="24"/>
-      <c r="Q115" s="24"/>
+      <c r="B115" s="29"/>
+      <c r="C115" s="29"/>
+      <c r="D115" s="29"/>
+      <c r="E115" s="29"/>
+      <c r="F115" s="29"/>
+      <c r="G115" s="29"/>
+      <c r="H115" s="29"/>
+      <c r="I115" s="29"/>
+      <c r="J115" s="29"/>
+      <c r="K115" s="29"/>
+      <c r="L115" s="29"/>
+      <c r="M115" s="29"/>
+      <c r="N115" s="29"/>
+      <c r="O115" s="29"/>
+      <c r="P115" s="29"/>
+      <c r="Q115" s="29"/>
     </row>
     <row r="116" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -11627,25 +11655,25 @@
       <c r="Q131" s="14"/>
     </row>
     <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="24" t="s">
+      <c r="A132" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="B132" s="24"/>
-      <c r="C132" s="24"/>
-      <c r="D132" s="24"/>
-      <c r="E132" s="24"/>
-      <c r="F132" s="24"/>
-      <c r="G132" s="24"/>
-      <c r="H132" s="24"/>
-      <c r="I132" s="24"/>
-      <c r="J132" s="24"/>
-      <c r="K132" s="24"/>
-      <c r="L132" s="24"/>
-      <c r="M132" s="24"/>
-      <c r="N132" s="24"/>
-      <c r="O132" s="24"/>
-      <c r="P132" s="24"/>
-      <c r="Q132" s="24"/>
+      <c r="B132" s="29"/>
+      <c r="C132" s="29"/>
+      <c r="D132" s="29"/>
+      <c r="E132" s="29"/>
+      <c r="F132" s="29"/>
+      <c r="G132" s="29"/>
+      <c r="H132" s="29"/>
+      <c r="I132" s="29"/>
+      <c r="J132" s="29"/>
+      <c r="K132" s="29"/>
+      <c r="L132" s="29"/>
+      <c r="M132" s="29"/>
+      <c r="N132" s="29"/>
+      <c r="O132" s="29"/>
+      <c r="P132" s="29"/>
+      <c r="Q132" s="29"/>
     </row>
     <row r="133" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -12145,25 +12173,25 @@
       <c r="Q148" s="14"/>
     </row>
     <row r="149" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="24" t="s">
+      <c r="A149" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="B149" s="24"/>
-      <c r="C149" s="24"/>
-      <c r="D149" s="24"/>
-      <c r="E149" s="24"/>
-      <c r="F149" s="24"/>
-      <c r="G149" s="24"/>
-      <c r="H149" s="24"/>
-      <c r="I149" s="24"/>
-      <c r="J149" s="24"/>
-      <c r="K149" s="24"/>
-      <c r="L149" s="24"/>
-      <c r="M149" s="24"/>
-      <c r="N149" s="24"/>
-      <c r="O149" s="24"/>
-      <c r="P149" s="24"/>
-      <c r="Q149" s="24"/>
+      <c r="B149" s="29"/>
+      <c r="C149" s="29"/>
+      <c r="D149" s="29"/>
+      <c r="E149" s="29"/>
+      <c r="F149" s="29"/>
+      <c r="G149" s="29"/>
+      <c r="H149" s="29"/>
+      <c r="I149" s="29"/>
+      <c r="J149" s="29"/>
+      <c r="K149" s="29"/>
+      <c r="L149" s="29"/>
+      <c r="M149" s="29"/>
+      <c r="N149" s="29"/>
+      <c r="O149" s="29"/>
+      <c r="P149" s="29"/>
+      <c r="Q149" s="29"/>
     </row>
     <row r="150" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -12693,25 +12721,25 @@
       <c r="Q166" s="14"/>
     </row>
     <row r="167" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="24" t="s">
+      <c r="A167" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="B167" s="24"/>
-      <c r="C167" s="24"/>
-      <c r="D167" s="24"/>
-      <c r="E167" s="24"/>
-      <c r="F167" s="24"/>
-      <c r="G167" s="24"/>
-      <c r="H167" s="24"/>
-      <c r="I167" s="24"/>
-      <c r="J167" s="24"/>
-      <c r="K167" s="24"/>
-      <c r="L167" s="24"/>
-      <c r="M167" s="24"/>
-      <c r="N167" s="24"/>
-      <c r="O167" s="24"/>
-      <c r="P167" s="24"/>
-      <c r="Q167" s="24"/>
+      <c r="B167" s="29"/>
+      <c r="C167" s="29"/>
+      <c r="D167" s="29"/>
+      <c r="E167" s="29"/>
+      <c r="F167" s="29"/>
+      <c r="G167" s="29"/>
+      <c r="H167" s="29"/>
+      <c r="I167" s="29"/>
+      <c r="J167" s="29"/>
+      <c r="K167" s="29"/>
+      <c r="L167" s="29"/>
+      <c r="M167" s="29"/>
+      <c r="N167" s="29"/>
+      <c r="O167" s="29"/>
+      <c r="P167" s="29"/>
+      <c r="Q167" s="29"/>
     </row>
     <row r="168" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -13211,25 +13239,25 @@
       <c r="Q183" s="14"/>
     </row>
     <row r="184" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="24" t="s">
+      <c r="A184" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="B184" s="24"/>
-      <c r="C184" s="24"/>
-      <c r="D184" s="24"/>
-      <c r="E184" s="24"/>
-      <c r="F184" s="24"/>
-      <c r="G184" s="24"/>
-      <c r="H184" s="24"/>
-      <c r="I184" s="24"/>
-      <c r="J184" s="24"/>
-      <c r="K184" s="24"/>
-      <c r="L184" s="24"/>
-      <c r="M184" s="24"/>
-      <c r="N184" s="24"/>
-      <c r="O184" s="24"/>
-      <c r="P184" s="24"/>
-      <c r="Q184" s="24"/>
+      <c r="B184" s="29"/>
+      <c r="C184" s="29"/>
+      <c r="D184" s="29"/>
+      <c r="E184" s="29"/>
+      <c r="F184" s="29"/>
+      <c r="G184" s="29"/>
+      <c r="H184" s="29"/>
+      <c r="I184" s="29"/>
+      <c r="J184" s="29"/>
+      <c r="K184" s="29"/>
+      <c r="L184" s="29"/>
+      <c r="M184" s="29"/>
+      <c r="N184" s="29"/>
+      <c r="O184" s="29"/>
+      <c r="P184" s="29"/>
+      <c r="Q184" s="29"/>
     </row>
     <row r="185" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -13699,25 +13727,25 @@
       <c r="Q199" s="14"/>
     </row>
     <row r="200" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="24" t="s">
+      <c r="A200" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="B200" s="24"/>
-      <c r="C200" s="24"/>
-      <c r="D200" s="24"/>
-      <c r="E200" s="24"/>
-      <c r="F200" s="24"/>
-      <c r="G200" s="24"/>
-      <c r="H200" s="24"/>
-      <c r="I200" s="24"/>
-      <c r="J200" s="24"/>
-      <c r="K200" s="24"/>
-      <c r="L200" s="24"/>
-      <c r="M200" s="24"/>
-      <c r="N200" s="24"/>
-      <c r="O200" s="24"/>
-      <c r="P200" s="24"/>
-      <c r="Q200" s="24"/>
+      <c r="B200" s="29"/>
+      <c r="C200" s="29"/>
+      <c r="D200" s="29"/>
+      <c r="E200" s="29"/>
+      <c r="F200" s="29"/>
+      <c r="G200" s="29"/>
+      <c r="H200" s="29"/>
+      <c r="I200" s="29"/>
+      <c r="J200" s="29"/>
+      <c r="K200" s="29"/>
+      <c r="L200" s="29"/>
+      <c r="M200" s="29"/>
+      <c r="N200" s="29"/>
+      <c r="O200" s="29"/>
+      <c r="P200" s="29"/>
+      <c r="Q200" s="29"/>
     </row>
     <row r="201" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -14277,25 +14305,25 @@
       <c r="Q218" s="14"/>
     </row>
     <row r="219" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="24" t="s">
+      <c r="A219" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="B219" s="24"/>
-      <c r="C219" s="24"/>
-      <c r="D219" s="24"/>
-      <c r="E219" s="24"/>
-      <c r="F219" s="24"/>
-      <c r="G219" s="24"/>
-      <c r="H219" s="24"/>
-      <c r="I219" s="24"/>
-      <c r="J219" s="24"/>
-      <c r="K219" s="24"/>
-      <c r="L219" s="24"/>
-      <c r="M219" s="24"/>
-      <c r="N219" s="24"/>
-      <c r="O219" s="24"/>
-      <c r="P219" s="24"/>
-      <c r="Q219" s="24"/>
+      <c r="B219" s="29"/>
+      <c r="C219" s="29"/>
+      <c r="D219" s="29"/>
+      <c r="E219" s="29"/>
+      <c r="F219" s="29"/>
+      <c r="G219" s="29"/>
+      <c r="H219" s="29"/>
+      <c r="I219" s="29"/>
+      <c r="J219" s="29"/>
+      <c r="K219" s="29"/>
+      <c r="L219" s="29"/>
+      <c r="M219" s="29"/>
+      <c r="N219" s="29"/>
+      <c r="O219" s="29"/>
+      <c r="P219" s="29"/>
+      <c r="Q219" s="29"/>
     </row>
     <row r="220" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -14795,25 +14823,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="24" t="s">
+      <c r="A236" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="B236" s="24"/>
-      <c r="C236" s="24"/>
-      <c r="D236" s="24"/>
-      <c r="E236" s="24"/>
-      <c r="F236" s="24"/>
-      <c r="G236" s="24"/>
-      <c r="H236" s="24"/>
-      <c r="I236" s="24"/>
-      <c r="J236" s="24"/>
-      <c r="K236" s="24"/>
-      <c r="L236" s="24"/>
-      <c r="M236" s="24"/>
-      <c r="N236" s="24"/>
-      <c r="O236" s="24"/>
-      <c r="P236" s="24"/>
-      <c r="Q236" s="24"/>
+      <c r="B236" s="29"/>
+      <c r="C236" s="29"/>
+      <c r="D236" s="29"/>
+      <c r="E236" s="29"/>
+      <c r="F236" s="29"/>
+      <c r="G236" s="29"/>
+      <c r="H236" s="29"/>
+      <c r="I236" s="29"/>
+      <c r="J236" s="29"/>
+      <c r="K236" s="29"/>
+      <c r="L236" s="29"/>
+      <c r="M236" s="29"/>
+      <c r="N236" s="29"/>
+      <c r="O236" s="29"/>
+      <c r="P236" s="29"/>
+      <c r="Q236" s="29"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -15343,25 +15371,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="24" t="s">
+      <c r="A254" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="B254" s="24"/>
-      <c r="C254" s="24"/>
-      <c r="D254" s="24"/>
-      <c r="E254" s="24"/>
-      <c r="F254" s="24"/>
-      <c r="G254" s="24"/>
-      <c r="H254" s="24"/>
-      <c r="I254" s="24"/>
-      <c r="J254" s="24"/>
-      <c r="K254" s="24"/>
-      <c r="L254" s="24"/>
-      <c r="M254" s="24"/>
-      <c r="N254" s="24"/>
-      <c r="O254" s="24"/>
-      <c r="P254" s="24"/>
-      <c r="Q254" s="24"/>
+      <c r="B254" s="29"/>
+      <c r="C254" s="29"/>
+      <c r="D254" s="29"/>
+      <c r="E254" s="29"/>
+      <c r="F254" s="29"/>
+      <c r="G254" s="29"/>
+      <c r="H254" s="29"/>
+      <c r="I254" s="29"/>
+      <c r="J254" s="29"/>
+      <c r="K254" s="29"/>
+      <c r="L254" s="29"/>
+      <c r="M254" s="29"/>
+      <c r="N254" s="29"/>
+      <c r="O254" s="29"/>
+      <c r="P254" s="29"/>
+      <c r="Q254" s="29"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -15921,25 +15949,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="24" t="s">
+      <c r="A273" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="B273" s="24"/>
-      <c r="C273" s="24"/>
-      <c r="D273" s="24"/>
-      <c r="E273" s="24"/>
-      <c r="F273" s="24"/>
-      <c r="G273" s="24"/>
-      <c r="H273" s="24"/>
-      <c r="I273" s="24"/>
-      <c r="J273" s="24"/>
-      <c r="K273" s="24"/>
-      <c r="L273" s="24"/>
-      <c r="M273" s="24"/>
-      <c r="N273" s="24"/>
-      <c r="O273" s="24"/>
-      <c r="P273" s="24"/>
-      <c r="Q273" s="24"/>
+      <c r="B273" s="29"/>
+      <c r="C273" s="29"/>
+      <c r="D273" s="29"/>
+      <c r="E273" s="29"/>
+      <c r="F273" s="29"/>
+      <c r="G273" s="29"/>
+      <c r="H273" s="29"/>
+      <c r="I273" s="29"/>
+      <c r="J273" s="29"/>
+      <c r="K273" s="29"/>
+      <c r="L273" s="29"/>
+      <c r="M273" s="29"/>
+      <c r="N273" s="29"/>
+      <c r="O273" s="29"/>
+      <c r="P273" s="29"/>
+      <c r="Q273" s="29"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -16499,25 +16527,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="24" t="s">
+      <c r="A292" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="B292" s="24"/>
-      <c r="C292" s="24"/>
-      <c r="D292" s="24"/>
-      <c r="E292" s="24"/>
-      <c r="F292" s="24"/>
-      <c r="G292" s="24"/>
-      <c r="H292" s="24"/>
-      <c r="I292" s="24"/>
-      <c r="J292" s="24"/>
-      <c r="K292" s="24"/>
-      <c r="L292" s="24"/>
-      <c r="M292" s="24"/>
-      <c r="N292" s="24"/>
-      <c r="O292" s="24"/>
-      <c r="P292" s="24"/>
-      <c r="Q292" s="24"/>
+      <c r="B292" s="29"/>
+      <c r="C292" s="29"/>
+      <c r="D292" s="29"/>
+      <c r="E292" s="29"/>
+      <c r="F292" s="29"/>
+      <c r="G292" s="29"/>
+      <c r="H292" s="29"/>
+      <c r="I292" s="29"/>
+      <c r="J292" s="29"/>
+      <c r="K292" s="29"/>
+      <c r="L292" s="29"/>
+      <c r="M292" s="29"/>
+      <c r="N292" s="29"/>
+      <c r="O292" s="29"/>
+      <c r="P292" s="29"/>
+      <c r="Q292" s="29"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -17077,25 +17105,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="24" t="s">
+      <c r="A311" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="B311" s="24"/>
-      <c r="C311" s="24"/>
-      <c r="D311" s="24"/>
-      <c r="E311" s="24"/>
-      <c r="F311" s="24"/>
-      <c r="G311" s="24"/>
-      <c r="H311" s="24"/>
-      <c r="I311" s="24"/>
-      <c r="J311" s="24"/>
-      <c r="K311" s="24"/>
-      <c r="L311" s="24"/>
-      <c r="M311" s="24"/>
-      <c r="N311" s="24"/>
-      <c r="O311" s="24"/>
-      <c r="P311" s="24"/>
-      <c r="Q311" s="24"/>
+      <c r="B311" s="29"/>
+      <c r="C311" s="29"/>
+      <c r="D311" s="29"/>
+      <c r="E311" s="29"/>
+      <c r="F311" s="29"/>
+      <c r="G311" s="29"/>
+      <c r="H311" s="29"/>
+      <c r="I311" s="29"/>
+      <c r="J311" s="29"/>
+      <c r="K311" s="29"/>
+      <c r="L311" s="29"/>
+      <c r="M311" s="29"/>
+      <c r="N311" s="29"/>
+      <c r="O311" s="29"/>
+      <c r="P311" s="29"/>
+      <c r="Q311" s="29"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -17656,26 +17684,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A236:Q236"/>
+    <mergeCell ref="A254:Q254"/>
+    <mergeCell ref="A273:Q273"/>
+    <mergeCell ref="A292:Q292"/>
+    <mergeCell ref="A311:Q311"/>
+    <mergeCell ref="A149:Q149"/>
+    <mergeCell ref="A167:Q167"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A219:Q219"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="A132:Q132"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A4:Q4"/>
     <mergeCell ref="A23:Q23"/>
     <mergeCell ref="A42:Q42"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A167:Q167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A236:Q236"/>
-    <mergeCell ref="A254:Q254"/>
-    <mergeCell ref="A273:Q273"/>
-    <mergeCell ref="A292:Q292"/>
-    <mergeCell ref="A311:Q311"/>
   </mergeCells>
   <dataValidations count="268">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or SEA" promptTitle="ATS Pick" prompt="Pick NE or SEA" sqref="F6:Q6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -19404,16 +19432,25 @@
       <c r="D22" t="s">
         <v>66</v>
       </c>
+      <c r="E22">
+        <v>31</v>
+      </c>
       <c r="F22" t="s">
         <v>67</v>
       </c>
+      <c r="G22">
+        <v>41</v>
+      </c>
+      <c r="H22">
+        <v>4.5</v>
+      </c>
       <c r="I22" t="str">
         <f t="shared" ref="I22:I37" si="2">IF(OR(E22="",G22=""),"",IF(E22&gt;G22,D22,IF(G22&gt;E22,F22,"TIE")))</f>
-        <v/>
+        <v>BUF</v>
       </c>
       <c r="J22" t="str">
         <f t="shared" ref="J22:J37" si="3">IF(OR(E22="",G22="",H22=""),"",IF(E22+H22&gt;G22,D22,IF(E22+H22&lt;G22,F22,"PUSH")))</f>
-        <v/>
+        <v>BUF</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26910,17 +26947,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -27437,30 +27474,30 @@
       </c>
       <c r="C21" s="3">
         <f>SUMPRODUCT(('Picks Detail'!F25:F40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!F25:F40='Picks Detail'!E25:E40))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21">
         <v>6</v>
       </c>
       <c r="E21">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(6,A$21:A$32,0)),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="str">
         <f>IF(C21=0,"-",IF(C21&gt;E21,"W",IF(C21&lt;E21,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A21)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D21)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A21)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D21)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A21)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D21)-'Picks Detail'!E41),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>T</v>
       </c>
       <c r="G21">
         <f t="shared" ref="G21:G32" si="3">IF(F21="W",6,IF(F21="T",3,0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H21">
         <f t="shared" ref="H21:H32" si="4">IF(C21="",0,C21)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <f t="shared" ref="I21:I32" si="5">G21+H21</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27473,30 +27510,30 @@
       </c>
       <c r="C22" s="3">
         <f>SUMPRODUCT(('Picks Detail'!G25:G40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!G25:G40='Picks Detail'!E25:E40))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22">
         <v>5</v>
       </c>
       <c r="E22">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(5,A$21:A$32,0)),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="str">
         <f>IF(C22=0,"-",IF(C22&gt;E22,"W",IF(C22&lt;E22,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A22)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D22)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A22)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D22)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A22)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D22)-'Picks Detail'!E41),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>T</v>
       </c>
       <c r="G22">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H22">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27516,7 +27553,7 @@
       </c>
       <c r="E23">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(10,A$21:A$32,0)),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="str">
         <f>IF(C23=0,"-",IF(C23&gt;E23,"W",IF(C23&lt;E23,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A23)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D23)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A23)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D23)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A23)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D23)-'Picks Detail'!E41),"L","T")),"T"))))</f>
@@ -27545,7 +27582,7 @@
       </c>
       <c r="C24" s="3">
         <f>SUMPRODUCT(('Picks Detail'!I25:I40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!I25:I40='Picks Detail'!E25:E40))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24">
         <v>9</v>
@@ -27556,19 +27593,19 @@
       </c>
       <c r="F24" t="str">
         <f>IF(C24=0,"-",IF(C24&gt;E24,"W",IF(C24&lt;E24,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A24)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D24)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A24)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D24)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A24)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D24)-'Picks Detail'!E41),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G24">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H24">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27581,30 +27618,30 @@
       </c>
       <c r="C25" s="3">
         <f>SUMPRODUCT(('Picks Detail'!J25:J40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!J25:J40='Picks Detail'!E25:E40))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
         <v>2</v>
       </c>
       <c r="E25">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(2,A$21:A$32,0)),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="str">
         <f>IF(C25=0,"-",IF(C25&gt;E25,"W",IF(C25&lt;E25,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A25)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D25)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A25)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D25)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A25)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D25)-'Picks Detail'!E41),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>T</v>
       </c>
       <c r="G25">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H25">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27617,30 +27654,30 @@
       </c>
       <c r="C26" s="3">
         <f>SUMPRODUCT(('Picks Detail'!K25:K40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!K25:K40='Picks Detail'!E25:E40))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(1,A$21:A$32,0)),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="str">
         <f>IF(C26=0,"-",IF(C26&gt;E26,"W",IF(C26&lt;E26,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A26)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D26)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A26)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D26)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A26)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D26)-'Picks Detail'!E41),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>T</v>
       </c>
       <c r="G26">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H26">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27653,30 +27690,30 @@
       </c>
       <c r="C27" s="3">
         <f>SUMPRODUCT(('Picks Detail'!L25:L40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!L25:L40='Picks Detail'!E25:E40))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
         <v>12</v>
       </c>
       <c r="E27">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(12,A$21:A$32,0)),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="str">
         <f>IF(C27=0,"-",IF(C27&gt;E27,"W",IF(C27&lt;E27,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A27)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D27)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A27)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D27)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A27)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D27)-'Picks Detail'!E41),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>T</v>
       </c>
       <c r="G27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27689,7 +27726,7 @@
       </c>
       <c r="C28" s="3">
         <f>SUMPRODUCT(('Picks Detail'!M25:M40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!M25:M40='Picks Detail'!E25:E40))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28">
         <v>11</v>
@@ -27700,19 +27737,19 @@
       </c>
       <c r="F28" t="str">
         <f>IF(C28=0,"-",IF(C28&gt;E28,"W",IF(C28&lt;E28,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A28)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D28)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A28)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D28)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A28)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D28)-'Picks Detail'!E41),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G28">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H28">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27732,7 +27769,7 @@
       </c>
       <c r="E29">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(4,A$21:A$32,0)),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="str">
         <f>IF(C29=0,"-",IF(C29&gt;E29,"W",IF(C29&lt;E29,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A29)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D29)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A29)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D29)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A29)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D29)-'Picks Detail'!E41),"L","T")),"T"))))</f>
@@ -27761,7 +27798,7 @@
       </c>
       <c r="C30" s="3">
         <f>SUMPRODUCT(('Picks Detail'!O25:O40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!O25:O40='Picks Detail'!E25:E40))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30">
         <v>3</v>
@@ -27772,19 +27809,19 @@
       </c>
       <c r="F30" t="str">
         <f>IF(C30=0,"-",IF(C30&gt;E30,"W",IF(C30&lt;E30,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A30)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D30)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A30)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D30)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A30)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D30)-'Picks Detail'!E41),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G30">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H30">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27804,7 +27841,7 @@
       </c>
       <c r="E31">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(8,A$21:A$32,0)),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="str">
         <f>IF(C31=0,"-",IF(C31&gt;E31,"W",IF(C31&lt;E31,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A31)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D31)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A31)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D31)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A31)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D31)-'Picks Detail'!E41),"L","T")),"T"))))</f>
@@ -27833,30 +27870,30 @@
       </c>
       <c r="C32" s="3">
         <f>SUMPRODUCT(('Picks Detail'!Q25:Q40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!Q25:Q40='Picks Detail'!E25:E40))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32">
         <v>7</v>
       </c>
       <c r="E32">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(7,A$21:A$32,0)),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" t="str">
         <f>IF(C32=0,"-",IF(C32&gt;E32,"W",IF(C32&lt;E32,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A32)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D32)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A32)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D32)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A32)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D32)-'Picks Detail'!E41),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>T</v>
       </c>
       <c r="G32">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H32">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29743,17 +29780,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -32576,17 +32613,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -35409,19 +35446,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -35472,7 +35509,7 @@
       </c>
       <c r="D3">
         <f>Helper!D2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <f>Helper!E2</f>
@@ -35492,7 +35529,7 @@
       </c>
       <c r="I3">
         <f>Helper!I2</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3">
         <f>Helper!J2</f>
@@ -35517,7 +35554,7 @@
       </c>
       <c r="D4">
         <f>Helper!D3</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <f>Helper!E3</f>
@@ -35537,7 +35574,7 @@
       </c>
       <c r="I4">
         <f>Helper!I3</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <f>Helper!J3</f>
@@ -35607,7 +35644,7 @@
       </c>
       <c r="D6">
         <f>Helper!D5</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <f>Helper!E5</f>
@@ -35627,7 +35664,7 @@
       </c>
       <c r="I6">
         <f>Helper!I5</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <f>Helper!J5</f>
@@ -35652,7 +35689,7 @@
       </c>
       <c r="D7">
         <f>Helper!D6</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <f>Helper!E6</f>
@@ -35672,7 +35709,7 @@
       </c>
       <c r="I7">
         <f>Helper!I6</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J7">
         <f>Helper!J6</f>
@@ -35697,7 +35734,7 @@
       </c>
       <c r="D8">
         <f>Helper!D7</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <f>Helper!E7</f>
@@ -35717,7 +35754,7 @@
       </c>
       <c r="I8">
         <f>Helper!I7</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J8">
         <f>Helper!J7</f>
@@ -35742,7 +35779,7 @@
       </c>
       <c r="D9">
         <f>Helper!D8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9">
         <f>Helper!E8</f>
@@ -35762,7 +35799,7 @@
       </c>
       <c r="I9">
         <f>Helper!I8</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <f>Helper!J8</f>
@@ -35787,7 +35824,7 @@
       </c>
       <c r="D10">
         <f>Helper!D9</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <f>Helper!E9</f>
@@ -35807,7 +35844,7 @@
       </c>
       <c r="I10">
         <f>Helper!I9</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J10">
         <f>Helper!J9</f>
@@ -35877,7 +35914,7 @@
       </c>
       <c r="D12">
         <f>Helper!D11</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <f>Helper!E11</f>
@@ -35897,7 +35934,7 @@
       </c>
       <c r="I12">
         <f>Helper!I11</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J12">
         <f>Helper!J11</f>
@@ -35967,7 +36004,7 @@
       </c>
       <c r="D14">
         <f>Helper!D13</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <f>Helper!E13</f>
@@ -35987,7 +36024,7 @@
       </c>
       <c r="I14">
         <f>Helper!I13</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J14">
         <f>Helper!J13</f>
@@ -35999,19 +36036,19 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="23" t="s">
         <v>217</v>
       </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
@@ -36589,19 +36626,19 @@
       </c>
     </row>
     <row r="31" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="28"/>
-      <c r="J31" s="28"/>
-      <c r="K31" s="28"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="24"/>
+      <c r="K31" s="24"/>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
@@ -37264,16 +37301,16 @@
       </c>
     </row>
     <row r="55" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="29" t="s">
+      <c r="A55" s="25" t="s">
         <v>235</v>
       </c>
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="29"/>
-      <c r="E55" s="29"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="25"/>
+      <c r="D55" s="25"/>
+      <c r="E55" s="25"/>
+      <c r="F55" s="25"/>
+      <c r="G55" s="25"/>
+      <c r="H55" s="25"/>
     </row>
     <row r="56" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
@@ -37311,7 +37348,7 @@
       </c>
       <c r="C57">
         <f>Helper!I2</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D57">
         <f>Helper!R2</f>
@@ -37323,11 +37360,11 @@
       </c>
       <c r="F57">
         <f>Helper!AE2</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G57">
         <f>Helper!K2</f>
-        <v>5.0000999999999998</v>
+        <v>6.0000999999999998</v>
       </c>
       <c r="H57">
         <f>Helper!T2</f>
@@ -37344,7 +37381,7 @@
       </c>
       <c r="C58">
         <f>Helper!I3</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D58">
         <f>Helper!R3</f>
@@ -37356,11 +37393,11 @@
       </c>
       <c r="F58">
         <f>Helper!AE3</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G58">
         <f>Helper!K3</f>
-        <v>7.0002000000000004</v>
+        <v>8.0001999999999995</v>
       </c>
       <c r="H58">
         <f>Helper!T3</f>
@@ -37410,7 +37447,7 @@
       </c>
       <c r="C60">
         <f>Helper!I5</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D60">
         <f>Helper!R5</f>
@@ -37422,11 +37459,11 @@
       </c>
       <c r="F60">
         <f>Helper!AE5</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G60">
         <f>Helper!K5</f>
-        <v>6.0004</v>
+        <v>7.0004</v>
       </c>
       <c r="H60">
         <f>Helper!T5</f>
@@ -37443,7 +37480,7 @@
       </c>
       <c r="C61">
         <f>Helper!I6</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D61">
         <f>Helper!R6</f>
@@ -37455,11 +37492,11 @@
       </c>
       <c r="F61">
         <f>Helper!AE6</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G61">
         <f>Helper!K6</f>
-        <v>16.000499999999999</v>
+        <v>17.000499999999999</v>
       </c>
       <c r="H61">
         <f>Helper!T6</f>
@@ -37476,7 +37513,7 @@
       </c>
       <c r="C62">
         <f>Helper!I7</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D62">
         <f>Helper!R7</f>
@@ -37488,11 +37525,11 @@
       </c>
       <c r="F62">
         <f>Helper!AE7</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G62">
         <f>Helper!K7</f>
-        <v>13.0006</v>
+        <v>14.0006</v>
       </c>
       <c r="H62">
         <f>Helper!T7</f>
@@ -37509,7 +37546,7 @@
       </c>
       <c r="C63">
         <f>Helper!I8</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D63">
         <f>Helper!R8</f>
@@ -37521,11 +37558,11 @@
       </c>
       <c r="F63">
         <f>Helper!AE8</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G63">
         <f>Helper!K8</f>
-        <v>7.0007000000000001</v>
+        <v>8.0007000000000001</v>
       </c>
       <c r="H63">
         <f>Helper!T8</f>
@@ -37542,7 +37579,7 @@
       </c>
       <c r="C64">
         <f>Helper!I9</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D64">
         <f>Helper!R9</f>
@@ -37554,11 +37591,11 @@
       </c>
       <c r="F64">
         <f>Helper!AE9</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G64">
         <f>Helper!K9</f>
-        <v>8.0007999999999999</v>
+        <v>9.0007999999999999</v>
       </c>
       <c r="H64">
         <f>Helper!T9</f>
@@ -37608,7 +37645,7 @@
       </c>
       <c r="C66">
         <f>Helper!I11</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D66">
         <f>Helper!R11</f>
@@ -37620,11 +37657,11 @@
       </c>
       <c r="F66">
         <f>Helper!AE11</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G66">
         <f>Helper!K11</f>
-        <v>17.001000000000001</v>
+        <v>18.001000000000001</v>
       </c>
       <c r="H66">
         <f>Helper!T11</f>
@@ -37674,7 +37711,7 @@
       </c>
       <c r="C68">
         <f>Helper!I13</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D68">
         <f>Helper!R13</f>
@@ -37686,11 +37723,11 @@
       </c>
       <c r="F68">
         <f>Helper!AE13</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G68">
         <f>Helper!K13</f>
-        <v>15.001200000000001</v>
+        <v>16.001200000000001</v>
       </c>
       <c r="H68">
         <f>Helper!T13</f>
@@ -37932,7 +37969,7 @@
       </c>
       <c r="C13">
         <f>INDEX(I$40:I$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
         <v>263</v>
@@ -38408,7 +38445,7 @@
       </c>
       <c r="I40">
         <f>Helper!AE2</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J40" t="b">
         <f t="shared" ref="J40:J51" si="1">OR(H40=$E$5,H40=$E$6,H40=$E$7,H40=$E$8,H40=$E$9)</f>
@@ -38416,7 +38453,7 @@
       </c>
       <c r="K40">
         <f>IF(J40,-1,I40+0.00001)</f>
-        <v>5.0000099999999996</v>
+        <v>6.0000099999999996</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38426,7 +38463,7 @@
       </c>
       <c r="I41">
         <f>Helper!AE3</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J41" t="b">
         <f t="shared" si="1"/>
@@ -38434,7 +38471,7 @@
       </c>
       <c r="K41">
         <f>IF(J41,-1,I41+0.00002)</f>
-        <v>7.0000200000000001</v>
+        <v>8.0000199999999992</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38462,7 +38499,7 @@
       </c>
       <c r="I43">
         <f>Helper!AE5</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J43" t="b">
         <f t="shared" si="1"/>
@@ -38480,7 +38517,7 @@
       </c>
       <c r="I44">
         <f>Helper!AE6</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J44" t="b">
         <f t="shared" si="1"/>
@@ -38488,7 +38525,7 @@
       </c>
       <c r="K44">
         <f>IF(J44,-1,I44+0.00005)</f>
-        <v>16.000050000000002</v>
+        <v>17.000050000000002</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38498,7 +38535,7 @@
       </c>
       <c r="I45">
         <f>Helper!AE7</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J45" t="b">
         <f t="shared" si="1"/>
@@ -38506,7 +38543,7 @@
       </c>
       <c r="K45">
         <f>IF(J45,-1,I45+0.00006)</f>
-        <v>13.00006</v>
+        <v>14.00006</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38516,7 +38553,7 @@
       </c>
       <c r="I46">
         <f>Helper!AE8</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J46" t="b">
         <f t="shared" si="1"/>
@@ -38524,7 +38561,7 @@
       </c>
       <c r="K46">
         <f>IF(J46,-1,I46+0.00007)</f>
-        <v>7.00007</v>
+        <v>8.0000699999999991</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38534,7 +38571,7 @@
       </c>
       <c r="I47">
         <f>Helper!AE9</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J47" t="b">
         <f t="shared" si="1"/>
@@ -38570,7 +38607,7 @@
       </c>
       <c r="I49">
         <f>Helper!AE11</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J49" t="b">
         <f t="shared" si="1"/>
@@ -38606,7 +38643,7 @@
       </c>
       <c r="I51">
         <f>Helper!AE13</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J51" t="b">
         <f t="shared" si="1"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26ECA4AB-7CAB-409D-9E8D-B317035D7FAE}"/>
+  <xr:revisionPtr revIDLastSave="279" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE57D085-3487-4B92-B33E-763ED9AC5FC2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3419" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3587" uniqueCount="346">
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -1378,15 +1378,15 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1665,12 +1665,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
+      <c r="A1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="D2">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H21,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G21,0)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E2">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H36,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G36,0)</f>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I13" si="0">SUM(C2:H2)</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J2">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F6="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F21="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F36="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F51="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F66="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F81="W"),1,0)</f>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="K2">
         <f>I2+0.0001</f>
-        <v>6.0000999999999998</v>
+        <v>13.0001</v>
       </c>
       <c r="L2">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H6,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G6,0)</f>
@@ -2957,11 +2957,11 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE13" si="2">I2+R2+AC2</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AF2">
         <f>AE2+0.0001</f>
-        <v>6.0000999999999998</v>
+        <v>13.0001</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="D3">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H22,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G22,0)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E3">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H37,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G37,0)</f>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="I3">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J3">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F7="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F22="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F37="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F52="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F67="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F82="W"),1,0)</f>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="K3">
         <f>I3+0.0002</f>
-        <v>8.0001999999999995</v>
+        <v>14.0002</v>
       </c>
       <c r="L3">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H7,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G7,0)</f>
@@ -3086,11 +3086,11 @@
       </c>
       <c r="AE3">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AF3">
         <f>AE3+0.0002</f>
-        <v>8.0001999999999995</v>
+        <v>14.0002</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="D4">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H23,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G23,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H38,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G38,0)</f>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J4">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F8="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F23="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F38="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F53="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F68="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F83="W"),1,0)</f>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="K4">
         <f>I4+0.0003</f>
-        <v>14.000299999999999</v>
+        <v>20.000299999999999</v>
       </c>
       <c r="L4">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H8,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G8,0)</f>
@@ -3215,11 +3215,11 @@
       </c>
       <c r="AE4">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AF4">
         <f>AE4+0.0003</f>
-        <v>14.000299999999999</v>
+        <v>20.000299999999999</v>
       </c>
     </row>
     <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="D5">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H24,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G24,0)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E5">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H39,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G39,0)</f>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="I5">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J5">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F9="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F24="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F39="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F54="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F69="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F84="W"),1,0)</f>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="K5">
         <f>I5+0.0004</f>
-        <v>7.0004</v>
+        <v>14.000400000000001</v>
       </c>
       <c r="L5">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H9,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G9,0)</f>
@@ -3344,11 +3344,11 @@
       </c>
       <c r="AE5">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AF5">
         <f>AE5+0.0004</f>
-        <v>7.0004</v>
+        <v>14.000400000000001</v>
       </c>
     </row>
     <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="D6">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H25,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G25,0)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H40,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G40,0)</f>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J6">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F10="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F25="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F40="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F55="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F70="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F85="W"),1,0)</f>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="K6">
         <f>I6+0.0005</f>
-        <v>17.000499999999999</v>
+        <v>22.000499999999999</v>
       </c>
       <c r="L6">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H10,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G10,0)</f>
@@ -3473,11 +3473,11 @@
       </c>
       <c r="AE6">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AF6">
         <f>AE6+0.0005</f>
-        <v>17.000499999999999</v>
+        <v>22.000499999999999</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="D7">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H26,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G26,0)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E7">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H41,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G41,0)</f>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J7">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F11="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F26="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F41="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F56="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F71="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F86="W"),1,0)</f>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="K7">
         <f>I7+0.0006</f>
-        <v>14.0006</v>
+        <v>19.000599999999999</v>
       </c>
       <c r="L7">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H11,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G11,0)</f>
@@ -3602,11 +3602,11 @@
       </c>
       <c r="AE7">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AF7">
         <f>AE7+0.0006</f>
-        <v>14.0006</v>
+        <v>19.000599999999999</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="D8">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H27,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G27,0)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E8">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H42,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G42,0)</f>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J8">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F12="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F27="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F42="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F57="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F72="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F87="W"),1,0)</f>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="K8">
         <f>I8+0.0007</f>
-        <v>8.0007000000000001</v>
+        <v>12.0007</v>
       </c>
       <c r="L8">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H12,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G12,0)</f>
@@ -3731,11 +3731,11 @@
       </c>
       <c r="AE8">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AF8">
         <f>AE8+0.0007</f>
-        <v>8.0007000000000001</v>
+        <v>12.0007</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="D9">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H28,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G28,0)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E9">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H43,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G43,0)</f>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J9">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F13="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F28="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F43="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F58="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F73="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F88="W"),1,0)</f>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="K9">
         <f>I9+0.0008</f>
-        <v>9.0007999999999999</v>
+        <v>12.0008</v>
       </c>
       <c r="L9">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H13,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G13,0)</f>
@@ -3860,11 +3860,11 @@
       </c>
       <c r="AE9">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AF9">
         <f>AE9+0.0008</f>
-        <v>9.0007999999999999</v>
+        <v>12.0008</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="D10">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H29,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G29,0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E10">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H44,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G44,0)</f>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="I10">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J10">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F14="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F29="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F44="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F59="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F74="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F89="W"),1,0)</f>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="K10">
         <f>I10+0.0009</f>
-        <v>8.0008999999999997</v>
+        <v>15.0009</v>
       </c>
       <c r="L10">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H14,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G14,0)</f>
@@ -3989,11 +3989,11 @@
       </c>
       <c r="AE10">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AF10">
         <f>AE10+0.0009</f>
-        <v>8.0008999999999997</v>
+        <v>15.0009</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D11">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H30,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G30,0)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E11">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H45,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G45,0)</f>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="I11">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J11">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F15="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F30="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F45="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F60="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F75="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F90="W"),1,0)</f>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="K11">
         <f>I11+0.001</f>
-        <v>18.001000000000001</v>
+        <v>25.001000000000001</v>
       </c>
       <c r="L11">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H15,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G15,0)</f>
@@ -4118,11 +4118,11 @@
       </c>
       <c r="AE11">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AF11">
         <f>AE11+0.001</f>
-        <v>18.001000000000001</v>
+        <v>25.001000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="D12">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H31,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G31,0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E12">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H46,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G46,0)</f>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="I12">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J12">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F16="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F31="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F46="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F61="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F76="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F91="W"),1,0)</f>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="K12">
         <f>I12+0.0011</f>
-        <v>16.001100000000001</v>
+        <v>21.001100000000001</v>
       </c>
       <c r="L12">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H16,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G16,0)</f>
@@ -4247,11 +4247,11 @@
       </c>
       <c r="AE12">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AF12">
         <f>AE12+0.0011</f>
-        <v>16.001100000000001</v>
+        <v>21.001100000000001</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="D13">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H32,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G32,0)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E13">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H47,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G47,0)</f>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="I13">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J13">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F17="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F32="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F47="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F62="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F77="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F92="W"),1,0)</f>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="K13">
         <f>I13+0.0012</f>
-        <v>16.001200000000001</v>
+        <v>19.001200000000001</v>
       </c>
       <c r="L13">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H17,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G17,0)</f>
@@ -4376,11 +4376,11 @@
       </c>
       <c r="AE13">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AF13">
         <f>AE13+0.0012</f>
-        <v>16.001200000000001</v>
+        <v>19.001200000000001</v>
       </c>
     </row>
   </sheetData>
@@ -7285,67 +7285,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8313,25 +8313,25 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="24"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="24"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -8455,20 +8455,44 @@
       </c>
       <c r="E26" s="9" t="str">
         <f>'NFL Schedule'!J23</f>
-        <v/>
-      </c>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10"/>
-      <c r="O26" s="10"/>
-      <c r="P26" s="10"/>
-      <c r="Q26" s="10"/>
+        <v>CAR</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="L26" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="M26" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="N26" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="O26" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="P26" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q26" s="10" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="27" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
@@ -8485,20 +8509,44 @@
       </c>
       <c r="E27" s="9" t="str">
         <f>'NFL Schedule'!J24</f>
-        <v/>
-      </c>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="10"/>
-      <c r="O27" s="10"/>
-      <c r="P27" s="10"/>
-      <c r="Q27" s="10"/>
+        <v>NO</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="L27" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="M27" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="N27" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="O27" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="P27" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q27" s="10" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
@@ -8515,20 +8563,44 @@
       </c>
       <c r="E28" s="9" t="str">
         <f>'NFL Schedule'!J25</f>
-        <v/>
-      </c>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="10"/>
-      <c r="O28" s="10"/>
-      <c r="P28" s="10"/>
-      <c r="Q28" s="10"/>
+        <v>MIN</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K28" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="L28" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M28" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="N28" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="O28" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="P28" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q28" s="10" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
@@ -8545,20 +8617,44 @@
       </c>
       <c r="E29" s="9" t="str">
         <f>'NFL Schedule'!J26</f>
-        <v/>
-      </c>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="10"/>
-      <c r="P29" s="10"/>
-      <c r="Q29" s="10"/>
+        <v>CIN</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="M29" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="N29" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="O29" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="P29" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q29" s="10" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
@@ -8575,20 +8671,44 @@
       </c>
       <c r="E30" s="9" t="str">
         <f>'NFL Schedule'!J27</f>
-        <v/>
-      </c>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="10"/>
-      <c r="O30" s="10"/>
-      <c r="P30" s="10"/>
-      <c r="Q30" s="10"/>
+        <v>NE</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="L30" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M30" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="N30" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="O30" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P30" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q30" s="10" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7">
@@ -8605,20 +8725,44 @@
       </c>
       <c r="E31" s="9" t="str">
         <f>'NFL Schedule'!J28</f>
-        <v/>
-      </c>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
-      <c r="O31" s="10"/>
-      <c r="P31" s="10"/>
-      <c r="Q31" s="10"/>
+        <v>NYJ</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="K31" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="L31" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="N31" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="O31" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="P31" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q31" s="10" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7">
@@ -8635,20 +8779,44 @@
       </c>
       <c r="E32" s="9" t="str">
         <f>'NFL Schedule'!J29</f>
-        <v/>
-      </c>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10"/>
-      <c r="O32" s="10"/>
-      <c r="P32" s="10"/>
-      <c r="Q32" s="10"/>
+        <v>CLE</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="L32" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="M32" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="N32" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="O32" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="P32" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q32" s="10" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="33" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7">
@@ -8665,20 +8833,44 @@
       </c>
       <c r="E33" s="9" t="str">
         <f>'NFL Schedule'!J30</f>
-        <v/>
-      </c>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10"/>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="10"/>
-      <c r="O33" s="10"/>
-      <c r="P33" s="10"/>
-      <c r="Q33" s="10"/>
+        <v>TEN</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="L33" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="M33" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="N33" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="O33" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="P33" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q33" s="10" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
@@ -8695,20 +8887,44 @@
       </c>
       <c r="E34" s="9" t="str">
         <f>'NFL Schedule'!J31</f>
-        <v/>
-      </c>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
-      <c r="N34" s="10"/>
-      <c r="O34" s="10"/>
-      <c r="P34" s="10"/>
-      <c r="Q34" s="10"/>
+        <v>DEN</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="K34" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="L34" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="M34" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="N34" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="O34" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="P34" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q34" s="10" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7">
@@ -8725,20 +8941,44 @@
       </c>
       <c r="E35" s="9" t="str">
         <f>'NFL Schedule'!J32</f>
-        <v/>
-      </c>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
-      <c r="O35" s="10"/>
-      <c r="P35" s="10"/>
-      <c r="Q35" s="10"/>
+        <v>LV</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="L35" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="M35" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="N35" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="O35" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="P35" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q35" s="10" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="36" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
@@ -8755,20 +8995,44 @@
       </c>
       <c r="E36" s="9" t="str">
         <f>'NFL Schedule'!J33</f>
-        <v/>
-      </c>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
-      <c r="N36" s="10"/>
-      <c r="O36" s="10"/>
-      <c r="P36" s="10"/>
-      <c r="Q36" s="10"/>
+        <v>SEA</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="K36" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="L36" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="M36" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="N36" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="O36" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="P36" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q36" s="10" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="37" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
@@ -8785,20 +9049,44 @@
       </c>
       <c r="E37" s="9" t="str">
         <f>'NFL Schedule'!J34</f>
-        <v/>
-      </c>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
-      <c r="O37" s="10"/>
-      <c r="P37" s="10"/>
-      <c r="Q37" s="10"/>
+        <v>DAL</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K37" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="L37" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="M37" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="N37" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="O37" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="P37" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q37" s="10" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
@@ -8815,20 +9103,44 @@
       </c>
       <c r="E38" s="9" t="str">
         <f>'NFL Schedule'!J35</f>
-        <v/>
-      </c>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="10"/>
-      <c r="O38" s="10"/>
-      <c r="P38" s="10"/>
-      <c r="Q38" s="10"/>
+        <v>SF</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="K38" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="L38" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="M38" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="N38" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="O38" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="P38" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q38" s="10" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="39" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
@@ -8845,20 +9157,44 @@
       </c>
       <c r="E39" s="9" t="str">
         <f>'NFL Schedule'!J36</f>
-        <v/>
-      </c>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
-      <c r="N39" s="10"/>
-      <c r="O39" s="10"/>
-      <c r="P39" s="10"/>
-      <c r="Q39" s="10"/>
+        <v>IND</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K39" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="L39" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="M39" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="N39" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="O39" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="P39" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q39" s="10" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
@@ -8915,25 +9251,25 @@
       <c r="Q41" s="14"/>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="29" t="s">
+      <c r="A42" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="29"/>
-      <c r="C42" s="29"/>
-      <c r="D42" s="29"/>
-      <c r="E42" s="29"/>
-      <c r="F42" s="29"/>
-      <c r="G42" s="29"/>
-      <c r="H42" s="29"/>
-      <c r="I42" s="29"/>
-      <c r="J42" s="29"/>
-      <c r="K42" s="29"/>
-      <c r="L42" s="29"/>
-      <c r="M42" s="29"/>
-      <c r="N42" s="29"/>
-      <c r="O42" s="29"/>
-      <c r="P42" s="29"/>
-      <c r="Q42" s="29"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="24"/>
+      <c r="N42" s="24"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="24"/>
+      <c r="Q42" s="24"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -9493,25 +9829,25 @@
       <c r="Q60" s="14"/>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="29" t="s">
+      <c r="A61" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
-      <c r="F61" s="29"/>
-      <c r="G61" s="29"/>
-      <c r="H61" s="29"/>
-      <c r="I61" s="29"/>
-      <c r="J61" s="29"/>
-      <c r="K61" s="29"/>
-      <c r="L61" s="29"/>
-      <c r="M61" s="29"/>
-      <c r="N61" s="29"/>
-      <c r="O61" s="29"/>
-      <c r="P61" s="29"/>
-      <c r="Q61" s="29"/>
+      <c r="B61" s="24"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="24"/>
+      <c r="J61" s="24"/>
+      <c r="K61" s="24"/>
+      <c r="L61" s="24"/>
+      <c r="M61" s="24"/>
+      <c r="N61" s="24"/>
+      <c r="O61" s="24"/>
+      <c r="P61" s="24"/>
+      <c r="Q61" s="24"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -10071,25 +10407,25 @@
       <c r="Q79" s="14"/>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="29" t="s">
+      <c r="A80" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="29"/>
-      <c r="C80" s="29"/>
-      <c r="D80" s="29"/>
-      <c r="E80" s="29"/>
-      <c r="F80" s="29"/>
-      <c r="G80" s="29"/>
-      <c r="H80" s="29"/>
-      <c r="I80" s="29"/>
-      <c r="J80" s="29"/>
-      <c r="K80" s="29"/>
-      <c r="L80" s="29"/>
-      <c r="M80" s="29"/>
-      <c r="N80" s="29"/>
-      <c r="O80" s="29"/>
-      <c r="P80" s="29"/>
-      <c r="Q80" s="29"/>
+      <c r="B80" s="24"/>
+      <c r="C80" s="24"/>
+      <c r="D80" s="24"/>
+      <c r="E80" s="24"/>
+      <c r="F80" s="24"/>
+      <c r="G80" s="24"/>
+      <c r="H80" s="24"/>
+      <c r="I80" s="24"/>
+      <c r="J80" s="24"/>
+      <c r="K80" s="24"/>
+      <c r="L80" s="24"/>
+      <c r="M80" s="24"/>
+      <c r="N80" s="24"/>
+      <c r="O80" s="24"/>
+      <c r="P80" s="24"/>
+      <c r="Q80" s="24"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -10619,25 +10955,25 @@
       <c r="Q97" s="14"/>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="29" t="s">
+      <c r="A98" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="29"/>
-      <c r="C98" s="29"/>
-      <c r="D98" s="29"/>
-      <c r="E98" s="29"/>
-      <c r="F98" s="29"/>
-      <c r="G98" s="29"/>
-      <c r="H98" s="29"/>
-      <c r="I98" s="29"/>
-      <c r="J98" s="29"/>
-      <c r="K98" s="29"/>
-      <c r="L98" s="29"/>
-      <c r="M98" s="29"/>
-      <c r="N98" s="29"/>
-      <c r="O98" s="29"/>
-      <c r="P98" s="29"/>
-      <c r="Q98" s="29"/>
+      <c r="B98" s="24"/>
+      <c r="C98" s="24"/>
+      <c r="D98" s="24"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24"/>
+      <c r="H98" s="24"/>
+      <c r="I98" s="24"/>
+      <c r="J98" s="24"/>
+      <c r="K98" s="24"/>
+      <c r="L98" s="24"/>
+      <c r="M98" s="24"/>
+      <c r="N98" s="24"/>
+      <c r="O98" s="24"/>
+      <c r="P98" s="24"/>
+      <c r="Q98" s="24"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -11137,25 +11473,25 @@
       <c r="Q114" s="14"/>
     </row>
     <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="29" t="s">
+      <c r="A115" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="29"/>
-      <c r="C115" s="29"/>
-      <c r="D115" s="29"/>
-      <c r="E115" s="29"/>
-      <c r="F115" s="29"/>
-      <c r="G115" s="29"/>
-      <c r="H115" s="29"/>
-      <c r="I115" s="29"/>
-      <c r="J115" s="29"/>
-      <c r="K115" s="29"/>
-      <c r="L115" s="29"/>
-      <c r="M115" s="29"/>
-      <c r="N115" s="29"/>
-      <c r="O115" s="29"/>
-      <c r="P115" s="29"/>
-      <c r="Q115" s="29"/>
+      <c r="B115" s="24"/>
+      <c r="C115" s="24"/>
+      <c r="D115" s="24"/>
+      <c r="E115" s="24"/>
+      <c r="F115" s="24"/>
+      <c r="G115" s="24"/>
+      <c r="H115" s="24"/>
+      <c r="I115" s="24"/>
+      <c r="J115" s="24"/>
+      <c r="K115" s="24"/>
+      <c r="L115" s="24"/>
+      <c r="M115" s="24"/>
+      <c r="N115" s="24"/>
+      <c r="O115" s="24"/>
+      <c r="P115" s="24"/>
+      <c r="Q115" s="24"/>
     </row>
     <row r="116" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -11655,25 +11991,25 @@
       <c r="Q131" s="14"/>
     </row>
     <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="29" t="s">
+      <c r="A132" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="B132" s="29"/>
-      <c r="C132" s="29"/>
-      <c r="D132" s="29"/>
-      <c r="E132" s="29"/>
-      <c r="F132" s="29"/>
-      <c r="G132" s="29"/>
-      <c r="H132" s="29"/>
-      <c r="I132" s="29"/>
-      <c r="J132" s="29"/>
-      <c r="K132" s="29"/>
-      <c r="L132" s="29"/>
-      <c r="M132" s="29"/>
-      <c r="N132" s="29"/>
-      <c r="O132" s="29"/>
-      <c r="P132" s="29"/>
-      <c r="Q132" s="29"/>
+      <c r="B132" s="24"/>
+      <c r="C132" s="24"/>
+      <c r="D132" s="24"/>
+      <c r="E132" s="24"/>
+      <c r="F132" s="24"/>
+      <c r="G132" s="24"/>
+      <c r="H132" s="24"/>
+      <c r="I132" s="24"/>
+      <c r="J132" s="24"/>
+      <c r="K132" s="24"/>
+      <c r="L132" s="24"/>
+      <c r="M132" s="24"/>
+      <c r="N132" s="24"/>
+      <c r="O132" s="24"/>
+      <c r="P132" s="24"/>
+      <c r="Q132" s="24"/>
     </row>
     <row r="133" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -12173,25 +12509,25 @@
       <c r="Q148" s="14"/>
     </row>
     <row r="149" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="29" t="s">
+      <c r="A149" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="B149" s="29"/>
-      <c r="C149" s="29"/>
-      <c r="D149" s="29"/>
-      <c r="E149" s="29"/>
-      <c r="F149" s="29"/>
-      <c r="G149" s="29"/>
-      <c r="H149" s="29"/>
-      <c r="I149" s="29"/>
-      <c r="J149" s="29"/>
-      <c r="K149" s="29"/>
-      <c r="L149" s="29"/>
-      <c r="M149" s="29"/>
-      <c r="N149" s="29"/>
-      <c r="O149" s="29"/>
-      <c r="P149" s="29"/>
-      <c r="Q149" s="29"/>
+      <c r="B149" s="24"/>
+      <c r="C149" s="24"/>
+      <c r="D149" s="24"/>
+      <c r="E149" s="24"/>
+      <c r="F149" s="24"/>
+      <c r="G149" s="24"/>
+      <c r="H149" s="24"/>
+      <c r="I149" s="24"/>
+      <c r="J149" s="24"/>
+      <c r="K149" s="24"/>
+      <c r="L149" s="24"/>
+      <c r="M149" s="24"/>
+      <c r="N149" s="24"/>
+      <c r="O149" s="24"/>
+      <c r="P149" s="24"/>
+      <c r="Q149" s="24"/>
     </row>
     <row r="150" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -12721,25 +13057,25 @@
       <c r="Q166" s="14"/>
     </row>
     <row r="167" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="29" t="s">
+      <c r="A167" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="B167" s="29"/>
-      <c r="C167" s="29"/>
-      <c r="D167" s="29"/>
-      <c r="E167" s="29"/>
-      <c r="F167" s="29"/>
-      <c r="G167" s="29"/>
-      <c r="H167" s="29"/>
-      <c r="I167" s="29"/>
-      <c r="J167" s="29"/>
-      <c r="K167" s="29"/>
-      <c r="L167" s="29"/>
-      <c r="M167" s="29"/>
-      <c r="N167" s="29"/>
-      <c r="O167" s="29"/>
-      <c r="P167" s="29"/>
-      <c r="Q167" s="29"/>
+      <c r="B167" s="24"/>
+      <c r="C167" s="24"/>
+      <c r="D167" s="24"/>
+      <c r="E167" s="24"/>
+      <c r="F167" s="24"/>
+      <c r="G167" s="24"/>
+      <c r="H167" s="24"/>
+      <c r="I167" s="24"/>
+      <c r="J167" s="24"/>
+      <c r="K167" s="24"/>
+      <c r="L167" s="24"/>
+      <c r="M167" s="24"/>
+      <c r="N167" s="24"/>
+      <c r="O167" s="24"/>
+      <c r="P167" s="24"/>
+      <c r="Q167" s="24"/>
     </row>
     <row r="168" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -13239,25 +13575,25 @@
       <c r="Q183" s="14"/>
     </row>
     <row r="184" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="29" t="s">
+      <c r="A184" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="B184" s="29"/>
-      <c r="C184" s="29"/>
-      <c r="D184" s="29"/>
-      <c r="E184" s="29"/>
-      <c r="F184" s="29"/>
-      <c r="G184" s="29"/>
-      <c r="H184" s="29"/>
-      <c r="I184" s="29"/>
-      <c r="J184" s="29"/>
-      <c r="K184" s="29"/>
-      <c r="L184" s="29"/>
-      <c r="M184" s="29"/>
-      <c r="N184" s="29"/>
-      <c r="O184" s="29"/>
-      <c r="P184" s="29"/>
-      <c r="Q184" s="29"/>
+      <c r="B184" s="24"/>
+      <c r="C184" s="24"/>
+      <c r="D184" s="24"/>
+      <c r="E184" s="24"/>
+      <c r="F184" s="24"/>
+      <c r="G184" s="24"/>
+      <c r="H184" s="24"/>
+      <c r="I184" s="24"/>
+      <c r="J184" s="24"/>
+      <c r="K184" s="24"/>
+      <c r="L184" s="24"/>
+      <c r="M184" s="24"/>
+      <c r="N184" s="24"/>
+      <c r="O184" s="24"/>
+      <c r="P184" s="24"/>
+      <c r="Q184" s="24"/>
     </row>
     <row r="185" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -13727,25 +14063,25 @@
       <c r="Q199" s="14"/>
     </row>
     <row r="200" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="29" t="s">
+      <c r="A200" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="B200" s="29"/>
-      <c r="C200" s="29"/>
-      <c r="D200" s="29"/>
-      <c r="E200" s="29"/>
-      <c r="F200" s="29"/>
-      <c r="G200" s="29"/>
-      <c r="H200" s="29"/>
-      <c r="I200" s="29"/>
-      <c r="J200" s="29"/>
-      <c r="K200" s="29"/>
-      <c r="L200" s="29"/>
-      <c r="M200" s="29"/>
-      <c r="N200" s="29"/>
-      <c r="O200" s="29"/>
-      <c r="P200" s="29"/>
-      <c r="Q200" s="29"/>
+      <c r="B200" s="24"/>
+      <c r="C200" s="24"/>
+      <c r="D200" s="24"/>
+      <c r="E200" s="24"/>
+      <c r="F200" s="24"/>
+      <c r="G200" s="24"/>
+      <c r="H200" s="24"/>
+      <c r="I200" s="24"/>
+      <c r="J200" s="24"/>
+      <c r="K200" s="24"/>
+      <c r="L200" s="24"/>
+      <c r="M200" s="24"/>
+      <c r="N200" s="24"/>
+      <c r="O200" s="24"/>
+      <c r="P200" s="24"/>
+      <c r="Q200" s="24"/>
     </row>
     <row r="201" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -14305,25 +14641,25 @@
       <c r="Q218" s="14"/>
     </row>
     <row r="219" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="29" t="s">
+      <c r="A219" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="B219" s="29"/>
-      <c r="C219" s="29"/>
-      <c r="D219" s="29"/>
-      <c r="E219" s="29"/>
-      <c r="F219" s="29"/>
-      <c r="G219" s="29"/>
-      <c r="H219" s="29"/>
-      <c r="I219" s="29"/>
-      <c r="J219" s="29"/>
-      <c r="K219" s="29"/>
-      <c r="L219" s="29"/>
-      <c r="M219" s="29"/>
-      <c r="N219" s="29"/>
-      <c r="O219" s="29"/>
-      <c r="P219" s="29"/>
-      <c r="Q219" s="29"/>
+      <c r="B219" s="24"/>
+      <c r="C219" s="24"/>
+      <c r="D219" s="24"/>
+      <c r="E219" s="24"/>
+      <c r="F219" s="24"/>
+      <c r="G219" s="24"/>
+      <c r="H219" s="24"/>
+      <c r="I219" s="24"/>
+      <c r="J219" s="24"/>
+      <c r="K219" s="24"/>
+      <c r="L219" s="24"/>
+      <c r="M219" s="24"/>
+      <c r="N219" s="24"/>
+      <c r="O219" s="24"/>
+      <c r="P219" s="24"/>
+      <c r="Q219" s="24"/>
     </row>
     <row r="220" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -14823,25 +15159,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="29" t="s">
+      <c r="A236" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B236" s="29"/>
-      <c r="C236" s="29"/>
-      <c r="D236" s="29"/>
-      <c r="E236" s="29"/>
-      <c r="F236" s="29"/>
-      <c r="G236" s="29"/>
-      <c r="H236" s="29"/>
-      <c r="I236" s="29"/>
-      <c r="J236" s="29"/>
-      <c r="K236" s="29"/>
-      <c r="L236" s="29"/>
-      <c r="M236" s="29"/>
-      <c r="N236" s="29"/>
-      <c r="O236" s="29"/>
-      <c r="P236" s="29"/>
-      <c r="Q236" s="29"/>
+      <c r="B236" s="24"/>
+      <c r="C236" s="24"/>
+      <c r="D236" s="24"/>
+      <c r="E236" s="24"/>
+      <c r="F236" s="24"/>
+      <c r="G236" s="24"/>
+      <c r="H236" s="24"/>
+      <c r="I236" s="24"/>
+      <c r="J236" s="24"/>
+      <c r="K236" s="24"/>
+      <c r="L236" s="24"/>
+      <c r="M236" s="24"/>
+      <c r="N236" s="24"/>
+      <c r="O236" s="24"/>
+      <c r="P236" s="24"/>
+      <c r="Q236" s="24"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -15371,25 +15707,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="29" t="s">
+      <c r="A254" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="B254" s="29"/>
-      <c r="C254" s="29"/>
-      <c r="D254" s="29"/>
-      <c r="E254" s="29"/>
-      <c r="F254" s="29"/>
-      <c r="G254" s="29"/>
-      <c r="H254" s="29"/>
-      <c r="I254" s="29"/>
-      <c r="J254" s="29"/>
-      <c r="K254" s="29"/>
-      <c r="L254" s="29"/>
-      <c r="M254" s="29"/>
-      <c r="N254" s="29"/>
-      <c r="O254" s="29"/>
-      <c r="P254" s="29"/>
-      <c r="Q254" s="29"/>
+      <c r="B254" s="24"/>
+      <c r="C254" s="24"/>
+      <c r="D254" s="24"/>
+      <c r="E254" s="24"/>
+      <c r="F254" s="24"/>
+      <c r="G254" s="24"/>
+      <c r="H254" s="24"/>
+      <c r="I254" s="24"/>
+      <c r="J254" s="24"/>
+      <c r="K254" s="24"/>
+      <c r="L254" s="24"/>
+      <c r="M254" s="24"/>
+      <c r="N254" s="24"/>
+      <c r="O254" s="24"/>
+      <c r="P254" s="24"/>
+      <c r="Q254" s="24"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -15949,25 +16285,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="29" t="s">
+      <c r="A273" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="B273" s="29"/>
-      <c r="C273" s="29"/>
-      <c r="D273" s="29"/>
-      <c r="E273" s="29"/>
-      <c r="F273" s="29"/>
-      <c r="G273" s="29"/>
-      <c r="H273" s="29"/>
-      <c r="I273" s="29"/>
-      <c r="J273" s="29"/>
-      <c r="K273" s="29"/>
-      <c r="L273" s="29"/>
-      <c r="M273" s="29"/>
-      <c r="N273" s="29"/>
-      <c r="O273" s="29"/>
-      <c r="P273" s="29"/>
-      <c r="Q273" s="29"/>
+      <c r="B273" s="24"/>
+      <c r="C273" s="24"/>
+      <c r="D273" s="24"/>
+      <c r="E273" s="24"/>
+      <c r="F273" s="24"/>
+      <c r="G273" s="24"/>
+      <c r="H273" s="24"/>
+      <c r="I273" s="24"/>
+      <c r="J273" s="24"/>
+      <c r="K273" s="24"/>
+      <c r="L273" s="24"/>
+      <c r="M273" s="24"/>
+      <c r="N273" s="24"/>
+      <c r="O273" s="24"/>
+      <c r="P273" s="24"/>
+      <c r="Q273" s="24"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -16527,25 +16863,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="29" t="s">
+      <c r="A292" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="B292" s="29"/>
-      <c r="C292" s="29"/>
-      <c r="D292" s="29"/>
-      <c r="E292" s="29"/>
-      <c r="F292" s="29"/>
-      <c r="G292" s="29"/>
-      <c r="H292" s="29"/>
-      <c r="I292" s="29"/>
-      <c r="J292" s="29"/>
-      <c r="K292" s="29"/>
-      <c r="L292" s="29"/>
-      <c r="M292" s="29"/>
-      <c r="N292" s="29"/>
-      <c r="O292" s="29"/>
-      <c r="P292" s="29"/>
-      <c r="Q292" s="29"/>
+      <c r="B292" s="24"/>
+      <c r="C292" s="24"/>
+      <c r="D292" s="24"/>
+      <c r="E292" s="24"/>
+      <c r="F292" s="24"/>
+      <c r="G292" s="24"/>
+      <c r="H292" s="24"/>
+      <c r="I292" s="24"/>
+      <c r="J292" s="24"/>
+      <c r="K292" s="24"/>
+      <c r="L292" s="24"/>
+      <c r="M292" s="24"/>
+      <c r="N292" s="24"/>
+      <c r="O292" s="24"/>
+      <c r="P292" s="24"/>
+      <c r="Q292" s="24"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -17105,25 +17441,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="29" t="s">
+      <c r="A311" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="B311" s="29"/>
-      <c r="C311" s="29"/>
-      <c r="D311" s="29"/>
-      <c r="E311" s="29"/>
-      <c r="F311" s="29"/>
-      <c r="G311" s="29"/>
-      <c r="H311" s="29"/>
-      <c r="I311" s="29"/>
-      <c r="J311" s="29"/>
-      <c r="K311" s="29"/>
-      <c r="L311" s="29"/>
-      <c r="M311" s="29"/>
-      <c r="N311" s="29"/>
-      <c r="O311" s="29"/>
-      <c r="P311" s="29"/>
-      <c r="Q311" s="29"/>
+      <c r="B311" s="24"/>
+      <c r="C311" s="24"/>
+      <c r="D311" s="24"/>
+      <c r="E311" s="24"/>
+      <c r="F311" s="24"/>
+      <c r="G311" s="24"/>
+      <c r="H311" s="24"/>
+      <c r="I311" s="24"/>
+      <c r="J311" s="24"/>
+      <c r="K311" s="24"/>
+      <c r="L311" s="24"/>
+      <c r="M311" s="24"/>
+      <c r="N311" s="24"/>
+      <c r="O311" s="24"/>
+      <c r="P311" s="24"/>
+      <c r="Q311" s="24"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -17684,26 +18020,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A23:Q23"/>
+    <mergeCell ref="A42:Q42"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="A132:Q132"/>
+    <mergeCell ref="A149:Q149"/>
+    <mergeCell ref="A167:Q167"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A219:Q219"/>
     <mergeCell ref="A236:Q236"/>
     <mergeCell ref="A254:Q254"/>
     <mergeCell ref="A273:Q273"/>
     <mergeCell ref="A292:Q292"/>
     <mergeCell ref="A311:Q311"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A167:Q167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="A23:Q23"/>
-    <mergeCell ref="A42:Q42"/>
   </mergeCells>
   <dataValidations count="268">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or SEA" promptTitle="ATS Pick" prompt="Pick NE or SEA" sqref="F6:Q6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -19466,16 +19802,25 @@
       <c r="D23" t="s">
         <v>62</v>
       </c>
+      <c r="E23">
+        <v>34</v>
+      </c>
       <c r="F23" t="s">
         <v>73</v>
       </c>
+      <c r="G23">
+        <v>3</v>
+      </c>
+      <c r="H23">
+        <v>-1.5</v>
+      </c>
       <c r="I23" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>CAR</v>
       </c>
       <c r="J23" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>CAR</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19491,16 +19836,25 @@
       <c r="D24" t="s">
         <v>65</v>
       </c>
+      <c r="E24">
+        <v>24</v>
+      </c>
       <c r="F24" t="s">
         <v>69</v>
       </c>
+      <c r="G24">
+        <v>17</v>
+      </c>
+      <c r="H24">
+        <v>8.5</v>
+      </c>
       <c r="I24" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>NO</v>
       </c>
       <c r="J24" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>NO</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19516,16 +19870,25 @@
       <c r="D25" t="s">
         <v>82</v>
       </c>
+      <c r="E25">
+        <v>9</v>
+      </c>
       <c r="F25" t="s">
         <v>61</v>
       </c>
+      <c r="G25">
+        <v>3</v>
+      </c>
+      <c r="H25">
+        <v>5.5</v>
+      </c>
       <c r="I25" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>MIN</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>MIN</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19541,16 +19904,25 @@
       <c r="D26" t="s">
         <v>64</v>
       </c>
+      <c r="E26">
+        <v>20</v>
+      </c>
       <c r="F26" t="s">
         <v>68</v>
       </c>
+      <c r="G26">
+        <v>6</v>
+      </c>
+      <c r="H26">
+        <v>2.5</v>
+      </c>
       <c r="I26" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>CIN</v>
       </c>
       <c r="J26" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>CIN</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19566,16 +19938,25 @@
       <c r="D27" t="s">
         <v>74</v>
       </c>
+      <c r="E27">
+        <v>3</v>
+      </c>
       <c r="F27" t="s">
         <v>57</v>
       </c>
+      <c r="G27">
+        <v>20</v>
+      </c>
+      <c r="H27">
+        <v>5.5</v>
+      </c>
       <c r="I27" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>NE</v>
       </c>
       <c r="J27" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>NE</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19591,16 +19972,25 @@
       <c r="D28" t="s">
         <v>81</v>
       </c>
+      <c r="E28">
+        <v>20</v>
+      </c>
       <c r="F28" t="s">
         <v>75</v>
       </c>
+      <c r="G28">
+        <v>17</v>
+      </c>
+      <c r="H28">
+        <v>-3.5</v>
+      </c>
       <c r="I28" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>GB</v>
       </c>
       <c r="J28" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>NYJ</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19616,16 +20006,25 @@
       <c r="D29" t="s">
         <v>71</v>
       </c>
+      <c r="E29">
+        <v>23</v>
+      </c>
       <c r="F29" t="s">
         <v>63</v>
       </c>
+      <c r="G29">
+        <v>19</v>
+      </c>
+      <c r="H29">
+        <v>8.5</v>
+      </c>
       <c r="I29" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>CLE</v>
       </c>
       <c r="J29" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>CLE</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19641,16 +20040,25 @@
       <c r="D30" t="s">
         <v>84</v>
       </c>
+      <c r="E30">
+        <v>24</v>
+      </c>
       <c r="F30" t="s">
         <v>76</v>
       </c>
+      <c r="G30">
+        <v>20</v>
+      </c>
+      <c r="H30">
+        <v>-7.5</v>
+      </c>
       <c r="I30" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>PHI</v>
       </c>
       <c r="J30" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>TEN</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19666,16 +20074,25 @@
       <c r="D31" t="s">
         <v>72</v>
       </c>
+      <c r="E31">
+        <v>13</v>
+      </c>
       <c r="F31" t="s">
         <v>87</v>
       </c>
+      <c r="G31">
+        <v>20</v>
+      </c>
+      <c r="H31">
+        <v>2.5</v>
+      </c>
       <c r="I31" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>DEN</v>
       </c>
       <c r="J31" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>DEN</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19691,16 +20108,25 @@
       <c r="D32" t="s">
         <v>80</v>
       </c>
+      <c r="E32">
+        <v>26</v>
+      </c>
       <c r="F32" t="s">
         <v>78</v>
       </c>
+      <c r="G32">
+        <v>14</v>
+      </c>
+      <c r="H32">
+        <v>6.5</v>
+      </c>
       <c r="I32" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>LV</v>
       </c>
       <c r="J32" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>LV</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19716,16 +20142,25 @@
       <c r="D33" t="s">
         <v>58</v>
       </c>
+      <c r="E33">
+        <v>31</v>
+      </c>
       <c r="F33" t="s">
         <v>77</v>
       </c>
+      <c r="G33">
+        <v>7</v>
+      </c>
+      <c r="H33">
+        <v>-3.5</v>
+      </c>
       <c r="I33" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>SEA</v>
       </c>
       <c r="J33" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>SEA</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19741,16 +20176,25 @@
       <c r="D34" t="s">
         <v>83</v>
       </c>
+      <c r="E34">
+        <v>20</v>
+      </c>
       <c r="F34" t="s">
         <v>85</v>
       </c>
+      <c r="G34">
+        <v>37</v>
+      </c>
+      <c r="H34">
+        <v>3.5</v>
+      </c>
       <c r="I34" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>DAL</v>
       </c>
       <c r="J34" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>DAL</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19766,16 +20210,25 @@
       <c r="D35" t="s">
         <v>79</v>
       </c>
+      <c r="E35">
+        <v>13</v>
+      </c>
       <c r="F35" t="s">
         <v>59</v>
       </c>
+      <c r="G35">
+        <v>35</v>
+      </c>
+      <c r="H35">
+        <v>13.5</v>
+      </c>
       <c r="I35" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>SF</v>
       </c>
       <c r="J35" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>SF</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19791,16 +20244,25 @@
       <c r="D36" t="s">
         <v>70</v>
       </c>
+      <c r="E36">
+        <v>30</v>
+      </c>
       <c r="F36" t="s">
         <v>88</v>
       </c>
+      <c r="G36">
+        <v>33</v>
+      </c>
+      <c r="H36">
+        <v>6.5</v>
+      </c>
       <c r="I36" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>KC</v>
       </c>
       <c r="J36" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>IND</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27474,30 +27936,30 @@
       </c>
       <c r="C21" s="3">
         <f>SUMPRODUCT(('Picks Detail'!F25:F40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!F25:F40='Picks Detail'!E25:E40))</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D21">
         <v>6</v>
       </c>
       <c r="E21">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(6,A$21:A$32,0)),0)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F21" t="str">
         <f>IF(C21=0,"-",IF(C21&gt;E21,"W",IF(C21&lt;E21,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A21)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D21)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A21)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D21)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A21)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D21)-'Picks Detail'!E41),"L","T")),"T"))))</f>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="G21">
         <f t="shared" ref="G21:G32" si="3">IF(F21="W",6,IF(F21="T",3,0))</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H21">
         <f t="shared" ref="H21:H32" si="4">IF(C21="",0,C21)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <f t="shared" ref="I21:I32" si="5">G21+H21</f>
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27510,30 +27972,30 @@
       </c>
       <c r="C22" s="3">
         <f>SUMPRODUCT(('Picks Detail'!G25:G40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!G25:G40='Picks Detail'!E25:E40))</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D22">
         <v>5</v>
       </c>
       <c r="E22">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(5,A$21:A$32,0)),0)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F22" t="str">
         <f>IF(C22=0,"-",IF(C22&gt;E22,"W",IF(C22&lt;E22,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A22)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D22)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A22)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D22)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A22)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D22)-'Picks Detail'!E41),"L","T")),"T"))))</f>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="G22">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H22">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I22">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27546,18 +28008,18 @@
       </c>
       <c r="C23" s="3">
         <f>SUMPRODUCT(('Picks Detail'!H25:H40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!H25:H40='Picks Detail'!E25:E40))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <v>10</v>
       </c>
       <c r="E23">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(10,A$21:A$32,0)),0)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F23" t="str">
         <f>IF(C23=0,"-",IF(C23&gt;E23,"W",IF(C23&lt;E23,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A23)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D23)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A23)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D23)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A23)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D23)-'Picks Detail'!E41),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G23">
         <f t="shared" si="3"/>
@@ -27565,11 +28027,11 @@
       </c>
       <c r="H23">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I23">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27582,14 +28044,14 @@
       </c>
       <c r="C24" s="3">
         <f>SUMPRODUCT(('Picks Detail'!I25:I40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!I25:I40='Picks Detail'!E25:E40))</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D24">
         <v>9</v>
       </c>
       <c r="E24">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(9,A$21:A$32,0)),0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F24" t="str">
         <f>IF(C24=0,"-",IF(C24&gt;E24,"W",IF(C24&lt;E24,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A24)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D24)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A24)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D24)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A24)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D24)-'Picks Detail'!E41),"L","T")),"T"))))</f>
@@ -27601,11 +28063,11 @@
       </c>
       <c r="H24">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I24">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27618,30 +28080,30 @@
       </c>
       <c r="C25" s="3">
         <f>SUMPRODUCT(('Picks Detail'!J25:J40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!J25:J40='Picks Detail'!E25:E40))</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D25">
         <v>2</v>
       </c>
       <c r="E25">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(2,A$21:A$32,0)),0)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F25" t="str">
         <f>IF(C25=0,"-",IF(C25&gt;E25,"W",IF(C25&lt;E25,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A25)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D25)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A25)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D25)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A25)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D25)-'Picks Detail'!E41),"L","T")),"T"))))</f>
-        <v>T</v>
+        <v>L</v>
       </c>
       <c r="G25">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H25">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I25">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27654,30 +28116,30 @@
       </c>
       <c r="C26" s="3">
         <f>SUMPRODUCT(('Picks Detail'!K25:K40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!K25:K40='Picks Detail'!E25:E40))</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(1,A$21:A$32,0)),0)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F26" t="str">
         <f>IF(C26=0,"-",IF(C26&gt;E26,"W",IF(C26&lt;E26,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A26)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D26)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A26)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D26)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A26)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D26)-'Picks Detail'!E41),"L","T")),"T"))))</f>
-        <v>T</v>
+        <v>L</v>
       </c>
       <c r="G26">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H26">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I26">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27690,30 +28152,30 @@
       </c>
       <c r="C27" s="3">
         <f>SUMPRODUCT(('Picks Detail'!L25:L40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!L25:L40='Picks Detail'!E25:E40))</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D27">
         <v>12</v>
       </c>
       <c r="E27">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(12,A$21:A$32,0)),0)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F27" t="str">
         <f>IF(C27=0,"-",IF(C27&gt;E27,"W",IF(C27&lt;E27,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A27)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D27)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A27)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D27)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A27)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D27)-'Picks Detail'!E41),"L","T")),"T"))))</f>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="G27">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H27">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I27">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27726,30 +28188,30 @@
       </c>
       <c r="C28" s="3">
         <f>SUMPRODUCT(('Picks Detail'!M25:M40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!M25:M40='Picks Detail'!E25:E40))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28">
         <v>11</v>
       </c>
       <c r="E28">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(11,A$21:A$32,0)),0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F28" t="str">
         <f>IF(C28=0,"-",IF(C28&gt;E28,"W",IF(C28&lt;E28,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A28)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D28)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A28)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D28)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A28)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D28)-'Picks Detail'!E41),"L","T")),"T"))))</f>
-        <v>W</v>
+        <v>L</v>
       </c>
       <c r="G28">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I28">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27762,18 +28224,18 @@
       </c>
       <c r="C29" s="3">
         <f>SUMPRODUCT(('Picks Detail'!N25:N40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!N25:N40='Picks Detail'!E25:E40))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D29">
         <v>4</v>
       </c>
       <c r="E29">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(4,A$21:A$32,0)),0)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F29" t="str">
         <f>IF(C29=0,"-",IF(C29&gt;E29,"W",IF(C29&lt;E29,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A29)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D29)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A29)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D29)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A29)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D29)-'Picks Detail'!E41),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G29">
         <f t="shared" si="3"/>
@@ -27781,11 +28243,11 @@
       </c>
       <c r="H29">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I29">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27798,14 +28260,14 @@
       </c>
       <c r="C30" s="3">
         <f>SUMPRODUCT(('Picks Detail'!O25:O40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!O25:O40='Picks Detail'!E25:E40))</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D30">
         <v>3</v>
       </c>
       <c r="E30">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(3,A$21:A$32,0)),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F30" t="str">
         <f>IF(C30=0,"-",IF(C30&gt;E30,"W",IF(C30&lt;E30,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A30)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D30)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A30)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D30)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A30)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D30)-'Picks Detail'!E41),"L","T")),"T"))))</f>
@@ -27817,11 +28279,11 @@
       </c>
       <c r="H30">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I30">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27834,30 +28296,30 @@
       </c>
       <c r="C31" s="3">
         <f>SUMPRODUCT(('Picks Detail'!P25:P40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!P25:P40='Picks Detail'!E25:E40))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D31">
         <v>8</v>
       </c>
       <c r="E31">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(8,A$21:A$32,0)),0)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F31" t="str">
         <f>IF(C31=0,"-",IF(C31&gt;E31,"W",IF(C31&lt;E31,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A31)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D31)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A31)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D31)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A31)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D31)-'Picks Detail'!E41),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G31">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H31">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I31">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27870,26 +28332,26 @@
       </c>
       <c r="C32" s="3">
         <f>SUMPRODUCT(('Picks Detail'!Q25:Q40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!Q25:Q40='Picks Detail'!E25:E40))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D32">
         <v>7</v>
       </c>
       <c r="E32">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(7,A$21:A$32,0)),0)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F32" t="str">
         <f>IF(C32=0,"-",IF(C32&gt;E32,"W",IF(C32&lt;E32,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A32)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D32)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A32)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D32)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A32)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D32)-'Picks Detail'!E41),"L","T")),"T"))))</f>
-        <v>T</v>
+        <v>L</v>
       </c>
       <c r="G32">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H32">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I32">
         <f t="shared" si="5"/>
@@ -35509,7 +35971,7 @@
       </c>
       <c r="D3">
         <f>Helper!D2</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <f>Helper!E2</f>
@@ -35529,7 +35991,7 @@
       </c>
       <c r="I3">
         <f>Helper!I2</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J3">
         <f>Helper!J2</f>
@@ -35537,7 +35999,7 @@
       </c>
       <c r="K3">
         <f>MAX(Helper!C2:H2)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35554,7 +36016,7 @@
       </c>
       <c r="D4">
         <f>Helper!D3</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <f>Helper!E3</f>
@@ -35574,7 +36036,7 @@
       </c>
       <c r="I4">
         <f>Helper!I3</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J4">
         <f>Helper!J3</f>
@@ -35599,7 +36061,7 @@
       </c>
       <c r="D5">
         <f>Helper!D4</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <f>Helper!E4</f>
@@ -35619,7 +36081,7 @@
       </c>
       <c r="I5">
         <f>Helper!I4</f>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J5">
         <f>Helper!J4</f>
@@ -35644,7 +36106,7 @@
       </c>
       <c r="D6">
         <f>Helper!D5</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <f>Helper!E5</f>
@@ -35664,7 +36126,7 @@
       </c>
       <c r="I6">
         <f>Helper!I5</f>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J6">
         <f>Helper!J5</f>
@@ -35672,7 +36134,7 @@
       </c>
       <c r="K6">
         <f>MAX(Helper!C5:H5)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35689,7 +36151,7 @@
       </c>
       <c r="D7">
         <f>Helper!D6</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E7">
         <f>Helper!E6</f>
@@ -35709,7 +36171,7 @@
       </c>
       <c r="I7">
         <f>Helper!I6</f>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J7">
         <f>Helper!J6</f>
@@ -35734,7 +36196,7 @@
       </c>
       <c r="D8">
         <f>Helper!D7</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E8">
         <f>Helper!E7</f>
@@ -35754,7 +36216,7 @@
       </c>
       <c r="I8">
         <f>Helper!I7</f>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J8">
         <f>Helper!J7</f>
@@ -35779,7 +36241,7 @@
       </c>
       <c r="D9">
         <f>Helper!D8</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E9">
         <f>Helper!E8</f>
@@ -35799,7 +36261,7 @@
       </c>
       <c r="I9">
         <f>Helper!I8</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J9">
         <f>Helper!J8</f>
@@ -35824,7 +36286,7 @@
       </c>
       <c r="D10">
         <f>Helper!D9</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E10">
         <f>Helper!E9</f>
@@ -35844,7 +36306,7 @@
       </c>
       <c r="I10">
         <f>Helper!I9</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J10">
         <f>Helper!J9</f>
@@ -35869,7 +36331,7 @@
       </c>
       <c r="D11">
         <f>Helper!D10</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E11">
         <f>Helper!E10</f>
@@ -35889,7 +36351,7 @@
       </c>
       <c r="I11">
         <f>Helper!I10</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J11">
         <f>Helper!J10</f>
@@ -35914,7 +36376,7 @@
       </c>
       <c r="D12">
         <f>Helper!D11</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <f>Helper!E11</f>
@@ -35934,7 +36396,7 @@
       </c>
       <c r="I12">
         <f>Helper!I11</f>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J12">
         <f>Helper!J11</f>
@@ -35959,7 +36421,7 @@
       </c>
       <c r="D13">
         <f>Helper!D12</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <f>Helper!E12</f>
@@ -35979,7 +36441,7 @@
       </c>
       <c r="I13">
         <f>Helper!I12</f>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J13">
         <f>Helper!J12</f>
@@ -36004,7 +36466,7 @@
       </c>
       <c r="D14">
         <f>Helper!D13</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E14">
         <f>Helper!E13</f>
@@ -36024,7 +36486,7 @@
       </c>
       <c r="I14">
         <f>Helper!I13</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J14">
         <f>Helper!J13</f>
@@ -36036,19 +36498,19 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
@@ -36626,19 +37088,19 @@
       </c>
     </row>
     <row r="31" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="24" t="s">
+      <c r="A31" s="28" t="s">
         <v>224</v>
       </c>
-      <c r="B31" s="24"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-      <c r="I31" s="24"/>
-      <c r="J31" s="24"/>
-      <c r="K31" s="24"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="28"/>
+      <c r="J31" s="28"/>
+      <c r="K31" s="28"/>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
@@ -37301,16 +37763,16 @@
       </c>
     </row>
     <row r="55" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="25" t="s">
+      <c r="A55" s="29" t="s">
         <v>235</v>
       </c>
-      <c r="B55" s="25"/>
-      <c r="C55" s="25"/>
-      <c r="D55" s="25"/>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="25"/>
+      <c r="B55" s="29"/>
+      <c r="C55" s="29"/>
+      <c r="D55" s="29"/>
+      <c r="E55" s="29"/>
+      <c r="F55" s="29"/>
+      <c r="G55" s="29"/>
+      <c r="H55" s="29"/>
     </row>
     <row r="56" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
@@ -37348,7 +37810,7 @@
       </c>
       <c r="C57">
         <f>Helper!I2</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D57">
         <f>Helper!R2</f>
@@ -37360,11 +37822,11 @@
       </c>
       <c r="F57">
         <f>Helper!AE2</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G57">
         <f>Helper!K2</f>
-        <v>6.0000999999999998</v>
+        <v>13.0001</v>
       </c>
       <c r="H57">
         <f>Helper!T2</f>
@@ -37381,7 +37843,7 @@
       </c>
       <c r="C58">
         <f>Helper!I3</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D58">
         <f>Helper!R3</f>
@@ -37393,11 +37855,11 @@
       </c>
       <c r="F58">
         <f>Helper!AE3</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G58">
         <f>Helper!K3</f>
-        <v>8.0001999999999995</v>
+        <v>14.0002</v>
       </c>
       <c r="H58">
         <f>Helper!T3</f>
@@ -37414,7 +37876,7 @@
       </c>
       <c r="C59">
         <f>Helper!I4</f>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D59">
         <f>Helper!R4</f>
@@ -37426,11 +37888,11 @@
       </c>
       <c r="F59">
         <f>Helper!AE4</f>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G59">
         <f>Helper!K4</f>
-        <v>14.000299999999999</v>
+        <v>20.000299999999999</v>
       </c>
       <c r="H59">
         <f>Helper!T4</f>
@@ -37447,7 +37909,7 @@
       </c>
       <c r="C60">
         <f>Helper!I5</f>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D60">
         <f>Helper!R5</f>
@@ -37459,11 +37921,11 @@
       </c>
       <c r="F60">
         <f>Helper!AE5</f>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G60">
         <f>Helper!K5</f>
-        <v>7.0004</v>
+        <v>14.000400000000001</v>
       </c>
       <c r="H60">
         <f>Helper!T5</f>
@@ -37480,7 +37942,7 @@
       </c>
       <c r="C61">
         <f>Helper!I6</f>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D61">
         <f>Helper!R6</f>
@@ -37492,11 +37954,11 @@
       </c>
       <c r="F61">
         <f>Helper!AE6</f>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G61">
         <f>Helper!K6</f>
-        <v>17.000499999999999</v>
+        <v>22.000499999999999</v>
       </c>
       <c r="H61">
         <f>Helper!T6</f>
@@ -37513,7 +37975,7 @@
       </c>
       <c r="C62">
         <f>Helper!I7</f>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D62">
         <f>Helper!R7</f>
@@ -37525,11 +37987,11 @@
       </c>
       <c r="F62">
         <f>Helper!AE7</f>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G62">
         <f>Helper!K7</f>
-        <v>14.0006</v>
+        <v>19.000599999999999</v>
       </c>
       <c r="H62">
         <f>Helper!T7</f>
@@ -37546,7 +38008,7 @@
       </c>
       <c r="C63">
         <f>Helper!I8</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D63">
         <f>Helper!R8</f>
@@ -37558,11 +38020,11 @@
       </c>
       <c r="F63">
         <f>Helper!AE8</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G63">
         <f>Helper!K8</f>
-        <v>8.0007000000000001</v>
+        <v>12.0007</v>
       </c>
       <c r="H63">
         <f>Helper!T8</f>
@@ -37579,7 +38041,7 @@
       </c>
       <c r="C64">
         <f>Helper!I9</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D64">
         <f>Helper!R9</f>
@@ -37591,11 +38053,11 @@
       </c>
       <c r="F64">
         <f>Helper!AE9</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G64">
         <f>Helper!K9</f>
-        <v>9.0007999999999999</v>
+        <v>12.0008</v>
       </c>
       <c r="H64">
         <f>Helper!T9</f>
@@ -37612,7 +38074,7 @@
       </c>
       <c r="C65">
         <f>Helper!I10</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D65">
         <f>Helper!R10</f>
@@ -37624,11 +38086,11 @@
       </c>
       <c r="F65">
         <f>Helper!AE10</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G65">
         <f>Helper!K10</f>
-        <v>8.0008999999999997</v>
+        <v>15.0009</v>
       </c>
       <c r="H65">
         <f>Helper!T10</f>
@@ -37645,7 +38107,7 @@
       </c>
       <c r="C66">
         <f>Helper!I11</f>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D66">
         <f>Helper!R11</f>
@@ -37657,11 +38119,11 @@
       </c>
       <c r="F66">
         <f>Helper!AE11</f>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G66">
         <f>Helper!K11</f>
-        <v>18.001000000000001</v>
+        <v>25.001000000000001</v>
       </c>
       <c r="H66">
         <f>Helper!T11</f>
@@ -37678,7 +38140,7 @@
       </c>
       <c r="C67">
         <f>Helper!I12</f>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D67">
         <f>Helper!R12</f>
@@ -37690,11 +38152,11 @@
       </c>
       <c r="F67">
         <f>Helper!AE12</f>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G67">
         <f>Helper!K12</f>
-        <v>16.001100000000001</v>
+        <v>21.001100000000001</v>
       </c>
       <c r="H67">
         <f>Helper!T12</f>
@@ -37711,7 +38173,7 @@
       </c>
       <c r="C68">
         <f>Helper!I13</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D68">
         <f>Helper!R13</f>
@@ -37723,11 +38185,11 @@
       </c>
       <c r="F68">
         <f>Helper!AE13</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G68">
         <f>Helper!K13</f>
-        <v>16.001200000000001</v>
+        <v>19.001200000000001</v>
       </c>
       <c r="H68">
         <f>Helper!T13</f>
@@ -37969,7 +38431,7 @@
       </c>
       <c r="C13">
         <f>INDEX(I$40:I$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
         <v>263</v>
@@ -38445,7 +38907,7 @@
       </c>
       <c r="I40">
         <f>Helper!AE2</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J40" t="b">
         <f t="shared" ref="J40:J51" si="1">OR(H40=$E$5,H40=$E$6,H40=$E$7,H40=$E$8,H40=$E$9)</f>
@@ -38453,7 +38915,7 @@
       </c>
       <c r="K40">
         <f>IF(J40,-1,I40+0.00001)</f>
-        <v>6.0000099999999996</v>
+        <v>13.00001</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38463,7 +38925,7 @@
       </c>
       <c r="I41">
         <f>Helper!AE3</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J41" t="b">
         <f t="shared" si="1"/>
@@ -38471,7 +38933,7 @@
       </c>
       <c r="K41">
         <f>IF(J41,-1,I41+0.00002)</f>
-        <v>8.0000199999999992</v>
+        <v>14.000019999999999</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38481,7 +38943,7 @@
       </c>
       <c r="I42">
         <f>Helper!AE4</f>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J42" t="b">
         <f t="shared" si="1"/>
@@ -38489,7 +38951,7 @@
       </c>
       <c r="K42">
         <f>IF(J42,-1,I42+0.00003)</f>
-        <v>14.000030000000001</v>
+        <v>20.000029999999999</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38499,7 +38961,7 @@
       </c>
       <c r="I43">
         <f>Helper!AE5</f>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J43" t="b">
         <f t="shared" si="1"/>
@@ -38517,7 +38979,7 @@
       </c>
       <c r="I44">
         <f>Helper!AE6</f>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J44" t="b">
         <f t="shared" si="1"/>
@@ -38525,7 +38987,7 @@
       </c>
       <c r="K44">
         <f>IF(J44,-1,I44+0.00005)</f>
-        <v>17.000050000000002</v>
+        <v>22.000050000000002</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38535,7 +38997,7 @@
       </c>
       <c r="I45">
         <f>Helper!AE7</f>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J45" t="b">
         <f t="shared" si="1"/>
@@ -38543,7 +39005,7 @@
       </c>
       <c r="K45">
         <f>IF(J45,-1,I45+0.00006)</f>
-        <v>14.00006</v>
+        <v>19.000060000000001</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38553,7 +39015,7 @@
       </c>
       <c r="I46">
         <f>Helper!AE8</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J46" t="b">
         <f t="shared" si="1"/>
@@ -38561,7 +39023,7 @@
       </c>
       <c r="K46">
         <f>IF(J46,-1,I46+0.00007)</f>
-        <v>8.0000699999999991</v>
+        <v>12.000069999999999</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38571,7 +39033,7 @@
       </c>
       <c r="I47">
         <f>Helper!AE9</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J47" t="b">
         <f t="shared" si="1"/>
@@ -38589,7 +39051,7 @@
       </c>
       <c r="I48">
         <f>Helper!AE10</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J48" t="b">
         <f t="shared" si="1"/>
@@ -38597,7 +39059,7 @@
       </c>
       <c r="K48">
         <f>IF(J48,-1,I48+0.00009)</f>
-        <v>8.0000900000000001</v>
+        <v>15.00009</v>
       </c>
     </row>
     <row r="49" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38607,7 +39069,7 @@
       </c>
       <c r="I49">
         <f>Helper!AE11</f>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J49" t="b">
         <f t="shared" si="1"/>
@@ -38625,7 +39087,7 @@
       </c>
       <c r="I50">
         <f>Helper!AE12</f>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J50" t="b">
         <f t="shared" si="1"/>
@@ -38643,7 +39105,7 @@
       </c>
       <c r="I51">
         <f>Helper!AE13</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J51" t="b">
         <f t="shared" si="1"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="279" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE57D085-3487-4B92-B33E-763ED9AC5FC2}"/>
+  <xr:revisionPtr revIDLastSave="306" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1EE7F45-5C00-4AFF-BC1F-F1B4159A4152}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3587" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3599" uniqueCount="346">
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -1377,13 +1377,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1665,12 +1665,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="D3">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H22,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G22,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H37,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G37,0)</f>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="I3">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J3">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F7="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F22="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F37="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F52="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F67="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F82="W"),1,0)</f>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="K3">
         <f>I3+0.0002</f>
-        <v>14.0002</v>
+        <v>15.0002</v>
       </c>
       <c r="L3">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H7,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G7,0)</f>
@@ -3086,11 +3086,11 @@
       </c>
       <c r="AE3">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF3">
         <f>AE3+0.0002</f>
-        <v>14.0002</v>
+        <v>15.0002</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="D7">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H26,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G26,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H41,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G41,0)</f>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F11="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F26="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F41="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F56="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F71="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F86="W"),1,0)</f>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="K7">
         <f>I7+0.0006</f>
-        <v>19.000599999999999</v>
+        <v>20.000599999999999</v>
       </c>
       <c r="L7">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H11,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G11,0)</f>
@@ -3602,11 +3602,11 @@
       </c>
       <c r="AE7">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF7">
         <f>AE7+0.0006</f>
-        <v>19.000599999999999</v>
+        <v>20.000599999999999</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="D8">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H27,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G27,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H42,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G42,0)</f>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J8">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F12="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F27="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F42="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F57="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F72="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F87="W"),1,0)</f>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="K8">
         <f>I8+0.0007</f>
-        <v>12.0007</v>
+        <v>13.0007</v>
       </c>
       <c r="L8">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H12,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G12,0)</f>
@@ -3731,11 +3731,11 @@
       </c>
       <c r="AE8">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF8">
         <f>AE8+0.0007</f>
-        <v>12.0007</v>
+        <v>13.0007</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="D12">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H31,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G31,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H46,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G46,0)</f>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="I12">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J12">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F16="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F31="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F46="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F61="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F76="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F91="W"),1,0)</f>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="K12">
         <f>I12+0.0011</f>
-        <v>21.001100000000001</v>
+        <v>22.001100000000001</v>
       </c>
       <c r="L12">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H16,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G16,0)</f>
@@ -4247,11 +4247,11 @@
       </c>
       <c r="AE12">
         <f t="shared" si="2"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF12">
         <f>AE12+0.0011</f>
-        <v>21.001100000000001</v>
+        <v>22.001100000000001</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4402,14 +4402,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -5354,14 +5354,14 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="22" t="s">
+      <c r="A56" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="22"/>
-      <c r="C56" s="22"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
@@ -6306,14 +6306,14 @@
       </c>
     </row>
     <row r="111" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="22" t="s">
+      <c r="A111" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B111" s="22"/>
-      <c r="C111" s="22"/>
-      <c r="D111" s="22"/>
-      <c r="E111" s="22"/>
-      <c r="F111" s="22"/>
+      <c r="B111" s="23"/>
+      <c r="C111" s="23"/>
+      <c r="D111" s="23"/>
+      <c r="E111" s="23"/>
+      <c r="F111" s="23"/>
     </row>
     <row r="112" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
@@ -7285,67 +7285,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="24"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8313,25 +8313,25 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="24"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -9211,20 +9211,44 @@
       </c>
       <c r="E40" s="9" t="str">
         <f>'NFL Schedule'!J37</f>
-        <v/>
-      </c>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
-      <c r="N40" s="10"/>
-      <c r="O40" s="10"/>
-      <c r="P40" s="10"/>
-      <c r="Q40" s="10"/>
+        <v>LAR</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="J40" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K40" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="L40" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="M40" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="N40" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="O40" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="P40" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q40" s="10" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
@@ -9233,43 +9257,67 @@
       <c r="B41" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="E41" s="13" t="str">
+      <c r="E41" s="13">
         <f>'NFL Schedule'!E38</f>
-        <v/>
-      </c>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="14"/>
-      <c r="J41" s="14"/>
-      <c r="K41" s="14"/>
-      <c r="L41" s="14"/>
-      <c r="M41" s="14"/>
-      <c r="N41" s="14"/>
-      <c r="O41" s="14"/>
-      <c r="P41" s="14"/>
-      <c r="Q41" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="F41" s="14">
+        <v>48</v>
+      </c>
+      <c r="G41" s="14">
+        <v>47</v>
+      </c>
+      <c r="H41" s="14">
+        <v>42</v>
+      </c>
+      <c r="I41" s="14">
+        <v>40</v>
+      </c>
+      <c r="J41" s="14">
+        <v>35</v>
+      </c>
+      <c r="K41" s="14">
+        <v>45</v>
+      </c>
+      <c r="L41" s="14">
+        <v>52</v>
+      </c>
+      <c r="M41" s="14">
+        <v>45</v>
+      </c>
+      <c r="N41" s="14">
+        <v>48</v>
+      </c>
+      <c r="O41" s="14">
+        <v>42</v>
+      </c>
+      <c r="P41" s="14">
+        <v>48</v>
+      </c>
+      <c r="Q41" s="14">
+        <v>51</v>
+      </c>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+      <c r="A42" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="24"/>
-      <c r="K42" s="24"/>
-      <c r="L42" s="24"/>
-      <c r="M42" s="24"/>
-      <c r="N42" s="24"/>
-      <c r="O42" s="24"/>
-      <c r="P42" s="24"/>
-      <c r="Q42" s="24"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="26"/>
+      <c r="Q42" s="26"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -9829,25 +9877,25 @@
       <c r="Q60" s="14"/>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="24" t="s">
+      <c r="A61" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="24"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="24"/>
-      <c r="J61" s="24"/>
-      <c r="K61" s="24"/>
-      <c r="L61" s="24"/>
-      <c r="M61" s="24"/>
-      <c r="N61" s="24"/>
-      <c r="O61" s="24"/>
-      <c r="P61" s="24"/>
-      <c r="Q61" s="24"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="26"/>
+      <c r="J61" s="26"/>
+      <c r="K61" s="26"/>
+      <c r="L61" s="26"/>
+      <c r="M61" s="26"/>
+      <c r="N61" s="26"/>
+      <c r="O61" s="26"/>
+      <c r="P61" s="26"/>
+      <c r="Q61" s="26"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -10407,25 +10455,25 @@
       <c r="Q79" s="14"/>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="24" t="s">
+      <c r="A80" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="24"/>
-      <c r="C80" s="24"/>
-      <c r="D80" s="24"/>
-      <c r="E80" s="24"/>
-      <c r="F80" s="24"/>
-      <c r="G80" s="24"/>
-      <c r="H80" s="24"/>
-      <c r="I80" s="24"/>
-      <c r="J80" s="24"/>
-      <c r="K80" s="24"/>
-      <c r="L80" s="24"/>
-      <c r="M80" s="24"/>
-      <c r="N80" s="24"/>
-      <c r="O80" s="24"/>
-      <c r="P80" s="24"/>
-      <c r="Q80" s="24"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
+      <c r="I80" s="26"/>
+      <c r="J80" s="26"/>
+      <c r="K80" s="26"/>
+      <c r="L80" s="26"/>
+      <c r="M80" s="26"/>
+      <c r="N80" s="26"/>
+      <c r="O80" s="26"/>
+      <c r="P80" s="26"/>
+      <c r="Q80" s="26"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -10955,25 +11003,25 @@
       <c r="Q97" s="14"/>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="24" t="s">
+      <c r="A98" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="24"/>
-      <c r="C98" s="24"/>
-      <c r="D98" s="24"/>
-      <c r="E98" s="24"/>
-      <c r="F98" s="24"/>
-      <c r="G98" s="24"/>
-      <c r="H98" s="24"/>
-      <c r="I98" s="24"/>
-      <c r="J98" s="24"/>
-      <c r="K98" s="24"/>
-      <c r="L98" s="24"/>
-      <c r="M98" s="24"/>
-      <c r="N98" s="24"/>
-      <c r="O98" s="24"/>
-      <c r="P98" s="24"/>
-      <c r="Q98" s="24"/>
+      <c r="B98" s="26"/>
+      <c r="C98" s="26"/>
+      <c r="D98" s="26"/>
+      <c r="E98" s="26"/>
+      <c r="F98" s="26"/>
+      <c r="G98" s="26"/>
+      <c r="H98" s="26"/>
+      <c r="I98" s="26"/>
+      <c r="J98" s="26"/>
+      <c r="K98" s="26"/>
+      <c r="L98" s="26"/>
+      <c r="M98" s="26"/>
+      <c r="N98" s="26"/>
+      <c r="O98" s="26"/>
+      <c r="P98" s="26"/>
+      <c r="Q98" s="26"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -11473,25 +11521,25 @@
       <c r="Q114" s="14"/>
     </row>
     <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="24" t="s">
+      <c r="A115" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="24"/>
-      <c r="C115" s="24"/>
-      <c r="D115" s="24"/>
-      <c r="E115" s="24"/>
-      <c r="F115" s="24"/>
-      <c r="G115" s="24"/>
-      <c r="H115" s="24"/>
-      <c r="I115" s="24"/>
-      <c r="J115" s="24"/>
-      <c r="K115" s="24"/>
-      <c r="L115" s="24"/>
-      <c r="M115" s="24"/>
-      <c r="N115" s="24"/>
-      <c r="O115" s="24"/>
-      <c r="P115" s="24"/>
-      <c r="Q115" s="24"/>
+      <c r="B115" s="26"/>
+      <c r="C115" s="26"/>
+      <c r="D115" s="26"/>
+      <c r="E115" s="26"/>
+      <c r="F115" s="26"/>
+      <c r="G115" s="26"/>
+      <c r="H115" s="26"/>
+      <c r="I115" s="26"/>
+      <c r="J115" s="26"/>
+      <c r="K115" s="26"/>
+      <c r="L115" s="26"/>
+      <c r="M115" s="26"/>
+      <c r="N115" s="26"/>
+      <c r="O115" s="26"/>
+      <c r="P115" s="26"/>
+      <c r="Q115" s="26"/>
     </row>
     <row r="116" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -11991,25 +12039,25 @@
       <c r="Q131" s="14"/>
     </row>
     <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="24" t="s">
+      <c r="A132" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="B132" s="24"/>
-      <c r="C132" s="24"/>
-      <c r="D132" s="24"/>
-      <c r="E132" s="24"/>
-      <c r="F132" s="24"/>
-      <c r="G132" s="24"/>
-      <c r="H132" s="24"/>
-      <c r="I132" s="24"/>
-      <c r="J132" s="24"/>
-      <c r="K132" s="24"/>
-      <c r="L132" s="24"/>
-      <c r="M132" s="24"/>
-      <c r="N132" s="24"/>
-      <c r="O132" s="24"/>
-      <c r="P132" s="24"/>
-      <c r="Q132" s="24"/>
+      <c r="B132" s="26"/>
+      <c r="C132" s="26"/>
+      <c r="D132" s="26"/>
+      <c r="E132" s="26"/>
+      <c r="F132" s="26"/>
+      <c r="G132" s="26"/>
+      <c r="H132" s="26"/>
+      <c r="I132" s="26"/>
+      <c r="J132" s="26"/>
+      <c r="K132" s="26"/>
+      <c r="L132" s="26"/>
+      <c r="M132" s="26"/>
+      <c r="N132" s="26"/>
+      <c r="O132" s="26"/>
+      <c r="P132" s="26"/>
+      <c r="Q132" s="26"/>
     </row>
     <row r="133" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -12509,25 +12557,25 @@
       <c r="Q148" s="14"/>
     </row>
     <row r="149" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="24" t="s">
+      <c r="A149" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="B149" s="24"/>
-      <c r="C149" s="24"/>
-      <c r="D149" s="24"/>
-      <c r="E149" s="24"/>
-      <c r="F149" s="24"/>
-      <c r="G149" s="24"/>
-      <c r="H149" s="24"/>
-      <c r="I149" s="24"/>
-      <c r="J149" s="24"/>
-      <c r="K149" s="24"/>
-      <c r="L149" s="24"/>
-      <c r="M149" s="24"/>
-      <c r="N149" s="24"/>
-      <c r="O149" s="24"/>
-      <c r="P149" s="24"/>
-      <c r="Q149" s="24"/>
+      <c r="B149" s="26"/>
+      <c r="C149" s="26"/>
+      <c r="D149" s="26"/>
+      <c r="E149" s="26"/>
+      <c r="F149" s="26"/>
+      <c r="G149" s="26"/>
+      <c r="H149" s="26"/>
+      <c r="I149" s="26"/>
+      <c r="J149" s="26"/>
+      <c r="K149" s="26"/>
+      <c r="L149" s="26"/>
+      <c r="M149" s="26"/>
+      <c r="N149" s="26"/>
+      <c r="O149" s="26"/>
+      <c r="P149" s="26"/>
+      <c r="Q149" s="26"/>
     </row>
     <row r="150" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -13057,25 +13105,25 @@
       <c r="Q166" s="14"/>
     </row>
     <row r="167" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="24" t="s">
+      <c r="A167" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="B167" s="24"/>
-      <c r="C167" s="24"/>
-      <c r="D167" s="24"/>
-      <c r="E167" s="24"/>
-      <c r="F167" s="24"/>
-      <c r="G167" s="24"/>
-      <c r="H167" s="24"/>
-      <c r="I167" s="24"/>
-      <c r="J167" s="24"/>
-      <c r="K167" s="24"/>
-      <c r="L167" s="24"/>
-      <c r="M167" s="24"/>
-      <c r="N167" s="24"/>
-      <c r="O167" s="24"/>
-      <c r="P167" s="24"/>
-      <c r="Q167" s="24"/>
+      <c r="B167" s="26"/>
+      <c r="C167" s="26"/>
+      <c r="D167" s="26"/>
+      <c r="E167" s="26"/>
+      <c r="F167" s="26"/>
+      <c r="G167" s="26"/>
+      <c r="H167" s="26"/>
+      <c r="I167" s="26"/>
+      <c r="J167" s="26"/>
+      <c r="K167" s="26"/>
+      <c r="L167" s="26"/>
+      <c r="M167" s="26"/>
+      <c r="N167" s="26"/>
+      <c r="O167" s="26"/>
+      <c r="P167" s="26"/>
+      <c r="Q167" s="26"/>
     </row>
     <row r="168" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -13575,25 +13623,25 @@
       <c r="Q183" s="14"/>
     </row>
     <row r="184" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="24" t="s">
+      <c r="A184" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="B184" s="24"/>
-      <c r="C184" s="24"/>
-      <c r="D184" s="24"/>
-      <c r="E184" s="24"/>
-      <c r="F184" s="24"/>
-      <c r="G184" s="24"/>
-      <c r="H184" s="24"/>
-      <c r="I184" s="24"/>
-      <c r="J184" s="24"/>
-      <c r="K184" s="24"/>
-      <c r="L184" s="24"/>
-      <c r="M184" s="24"/>
-      <c r="N184" s="24"/>
-      <c r="O184" s="24"/>
-      <c r="P184" s="24"/>
-      <c r="Q184" s="24"/>
+      <c r="B184" s="26"/>
+      <c r="C184" s="26"/>
+      <c r="D184" s="26"/>
+      <c r="E184" s="26"/>
+      <c r="F184" s="26"/>
+      <c r="G184" s="26"/>
+      <c r="H184" s="26"/>
+      <c r="I184" s="26"/>
+      <c r="J184" s="26"/>
+      <c r="K184" s="26"/>
+      <c r="L184" s="26"/>
+      <c r="M184" s="26"/>
+      <c r="N184" s="26"/>
+      <c r="O184" s="26"/>
+      <c r="P184" s="26"/>
+      <c r="Q184" s="26"/>
     </row>
     <row r="185" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -14063,25 +14111,25 @@
       <c r="Q199" s="14"/>
     </row>
     <row r="200" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="24" t="s">
+      <c r="A200" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="B200" s="24"/>
-      <c r="C200" s="24"/>
-      <c r="D200" s="24"/>
-      <c r="E200" s="24"/>
-      <c r="F200" s="24"/>
-      <c r="G200" s="24"/>
-      <c r="H200" s="24"/>
-      <c r="I200" s="24"/>
-      <c r="J200" s="24"/>
-      <c r="K200" s="24"/>
-      <c r="L200" s="24"/>
-      <c r="M200" s="24"/>
-      <c r="N200" s="24"/>
-      <c r="O200" s="24"/>
-      <c r="P200" s="24"/>
-      <c r="Q200" s="24"/>
+      <c r="B200" s="26"/>
+      <c r="C200" s="26"/>
+      <c r="D200" s="26"/>
+      <c r="E200" s="26"/>
+      <c r="F200" s="26"/>
+      <c r="G200" s="26"/>
+      <c r="H200" s="26"/>
+      <c r="I200" s="26"/>
+      <c r="J200" s="26"/>
+      <c r="K200" s="26"/>
+      <c r="L200" s="26"/>
+      <c r="M200" s="26"/>
+      <c r="N200" s="26"/>
+      <c r="O200" s="26"/>
+      <c r="P200" s="26"/>
+      <c r="Q200" s="26"/>
     </row>
     <row r="201" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -14641,25 +14689,25 @@
       <c r="Q218" s="14"/>
     </row>
     <row r="219" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="24" t="s">
+      <c r="A219" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="B219" s="24"/>
-      <c r="C219" s="24"/>
-      <c r="D219" s="24"/>
-      <c r="E219" s="24"/>
-      <c r="F219" s="24"/>
-      <c r="G219" s="24"/>
-      <c r="H219" s="24"/>
-      <c r="I219" s="24"/>
-      <c r="J219" s="24"/>
-      <c r="K219" s="24"/>
-      <c r="L219" s="24"/>
-      <c r="M219" s="24"/>
-      <c r="N219" s="24"/>
-      <c r="O219" s="24"/>
-      <c r="P219" s="24"/>
-      <c r="Q219" s="24"/>
+      <c r="B219" s="26"/>
+      <c r="C219" s="26"/>
+      <c r="D219" s="26"/>
+      <c r="E219" s="26"/>
+      <c r="F219" s="26"/>
+      <c r="G219" s="26"/>
+      <c r="H219" s="26"/>
+      <c r="I219" s="26"/>
+      <c r="J219" s="26"/>
+      <c r="K219" s="26"/>
+      <c r="L219" s="26"/>
+      <c r="M219" s="26"/>
+      <c r="N219" s="26"/>
+      <c r="O219" s="26"/>
+      <c r="P219" s="26"/>
+      <c r="Q219" s="26"/>
     </row>
     <row r="220" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -15159,25 +15207,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="24" t="s">
+      <c r="A236" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="B236" s="24"/>
-      <c r="C236" s="24"/>
-      <c r="D236" s="24"/>
-      <c r="E236" s="24"/>
-      <c r="F236" s="24"/>
-      <c r="G236" s="24"/>
-      <c r="H236" s="24"/>
-      <c r="I236" s="24"/>
-      <c r="J236" s="24"/>
-      <c r="K236" s="24"/>
-      <c r="L236" s="24"/>
-      <c r="M236" s="24"/>
-      <c r="N236" s="24"/>
-      <c r="O236" s="24"/>
-      <c r="P236" s="24"/>
-      <c r="Q236" s="24"/>
+      <c r="B236" s="26"/>
+      <c r="C236" s="26"/>
+      <c r="D236" s="26"/>
+      <c r="E236" s="26"/>
+      <c r="F236" s="26"/>
+      <c r="G236" s="26"/>
+      <c r="H236" s="26"/>
+      <c r="I236" s="26"/>
+      <c r="J236" s="26"/>
+      <c r="K236" s="26"/>
+      <c r="L236" s="26"/>
+      <c r="M236" s="26"/>
+      <c r="N236" s="26"/>
+      <c r="O236" s="26"/>
+      <c r="P236" s="26"/>
+      <c r="Q236" s="26"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -15707,25 +15755,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="24" t="s">
+      <c r="A254" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="B254" s="24"/>
-      <c r="C254" s="24"/>
-      <c r="D254" s="24"/>
-      <c r="E254" s="24"/>
-      <c r="F254" s="24"/>
-      <c r="G254" s="24"/>
-      <c r="H254" s="24"/>
-      <c r="I254" s="24"/>
-      <c r="J254" s="24"/>
-      <c r="K254" s="24"/>
-      <c r="L254" s="24"/>
-      <c r="M254" s="24"/>
-      <c r="N254" s="24"/>
-      <c r="O254" s="24"/>
-      <c r="P254" s="24"/>
-      <c r="Q254" s="24"/>
+      <c r="B254" s="26"/>
+      <c r="C254" s="26"/>
+      <c r="D254" s="26"/>
+      <c r="E254" s="26"/>
+      <c r="F254" s="26"/>
+      <c r="G254" s="26"/>
+      <c r="H254" s="26"/>
+      <c r="I254" s="26"/>
+      <c r="J254" s="26"/>
+      <c r="K254" s="26"/>
+      <c r="L254" s="26"/>
+      <c r="M254" s="26"/>
+      <c r="N254" s="26"/>
+      <c r="O254" s="26"/>
+      <c r="P254" s="26"/>
+      <c r="Q254" s="26"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -16285,25 +16333,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="24" t="s">
+      <c r="A273" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="B273" s="24"/>
-      <c r="C273" s="24"/>
-      <c r="D273" s="24"/>
-      <c r="E273" s="24"/>
-      <c r="F273" s="24"/>
-      <c r="G273" s="24"/>
-      <c r="H273" s="24"/>
-      <c r="I273" s="24"/>
-      <c r="J273" s="24"/>
-      <c r="K273" s="24"/>
-      <c r="L273" s="24"/>
-      <c r="M273" s="24"/>
-      <c r="N273" s="24"/>
-      <c r="O273" s="24"/>
-      <c r="P273" s="24"/>
-      <c r="Q273" s="24"/>
+      <c r="B273" s="26"/>
+      <c r="C273" s="26"/>
+      <c r="D273" s="26"/>
+      <c r="E273" s="26"/>
+      <c r="F273" s="26"/>
+      <c r="G273" s="26"/>
+      <c r="H273" s="26"/>
+      <c r="I273" s="26"/>
+      <c r="J273" s="26"/>
+      <c r="K273" s="26"/>
+      <c r="L273" s="26"/>
+      <c r="M273" s="26"/>
+      <c r="N273" s="26"/>
+      <c r="O273" s="26"/>
+      <c r="P273" s="26"/>
+      <c r="Q273" s="26"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -16863,25 +16911,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="24" t="s">
+      <c r="A292" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="B292" s="24"/>
-      <c r="C292" s="24"/>
-      <c r="D292" s="24"/>
-      <c r="E292" s="24"/>
-      <c r="F292" s="24"/>
-      <c r="G292" s="24"/>
-      <c r="H292" s="24"/>
-      <c r="I292" s="24"/>
-      <c r="J292" s="24"/>
-      <c r="K292" s="24"/>
-      <c r="L292" s="24"/>
-      <c r="M292" s="24"/>
-      <c r="N292" s="24"/>
-      <c r="O292" s="24"/>
-      <c r="P292" s="24"/>
-      <c r="Q292" s="24"/>
+      <c r="B292" s="26"/>
+      <c r="C292" s="26"/>
+      <c r="D292" s="26"/>
+      <c r="E292" s="26"/>
+      <c r="F292" s="26"/>
+      <c r="G292" s="26"/>
+      <c r="H292" s="26"/>
+      <c r="I292" s="26"/>
+      <c r="J292" s="26"/>
+      <c r="K292" s="26"/>
+      <c r="L292" s="26"/>
+      <c r="M292" s="26"/>
+      <c r="N292" s="26"/>
+      <c r="O292" s="26"/>
+      <c r="P292" s="26"/>
+      <c r="Q292" s="26"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -17441,25 +17489,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="24" t="s">
+      <c r="A311" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="B311" s="24"/>
-      <c r="C311" s="24"/>
-      <c r="D311" s="24"/>
-      <c r="E311" s="24"/>
-      <c r="F311" s="24"/>
-      <c r="G311" s="24"/>
-      <c r="H311" s="24"/>
-      <c r="I311" s="24"/>
-      <c r="J311" s="24"/>
-      <c r="K311" s="24"/>
-      <c r="L311" s="24"/>
-      <c r="M311" s="24"/>
-      <c r="N311" s="24"/>
-      <c r="O311" s="24"/>
-      <c r="P311" s="24"/>
-      <c r="Q311" s="24"/>
+      <c r="B311" s="26"/>
+      <c r="C311" s="26"/>
+      <c r="D311" s="26"/>
+      <c r="E311" s="26"/>
+      <c r="F311" s="26"/>
+      <c r="G311" s="26"/>
+      <c r="H311" s="26"/>
+      <c r="I311" s="26"/>
+      <c r="J311" s="26"/>
+      <c r="K311" s="26"/>
+      <c r="L311" s="26"/>
+      <c r="M311" s="26"/>
+      <c r="N311" s="26"/>
+      <c r="O311" s="26"/>
+      <c r="P311" s="26"/>
+      <c r="Q311" s="26"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -18020,26 +18068,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A236:Q236"/>
+    <mergeCell ref="A254:Q254"/>
+    <mergeCell ref="A273:Q273"/>
+    <mergeCell ref="A292:Q292"/>
+    <mergeCell ref="A311:Q311"/>
+    <mergeCell ref="A149:Q149"/>
+    <mergeCell ref="A167:Q167"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A219:Q219"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="A132:Q132"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A4:Q4"/>
     <mergeCell ref="A23:Q23"/>
     <mergeCell ref="A42:Q42"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A167:Q167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A236:Q236"/>
-    <mergeCell ref="A254:Q254"/>
-    <mergeCell ref="A273:Q273"/>
-    <mergeCell ref="A292:Q292"/>
-    <mergeCell ref="A311:Q311"/>
   </mergeCells>
   <dataValidations count="268">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or SEA" promptTitle="ATS Pick" prompt="Pick NE or SEA" sqref="F6:Q6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -20278,25 +20326,34 @@
       <c r="D37" t="s">
         <v>86</v>
       </c>
+      <c r="E37">
+        <v>6</v>
+      </c>
       <c r="F37" t="s">
         <v>60</v>
       </c>
+      <c r="G37">
+        <v>28</v>
+      </c>
+      <c r="H37">
+        <v>7.5</v>
+      </c>
       <c r="I37" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>LAR</v>
       </c>
       <c r="J37" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>LAR</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D38" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="E38" s="16" t="str">
+      <c r="E38" s="16">
         <f>IF(AND(E37&lt;&gt;"",G37&lt;&gt;""),E37+G37,"")</f>
-        <v/>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27409,17 +27466,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -27943,7 +28000,7 @@
       </c>
       <c r="E21">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(6,A$21:A$32,0)),0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" t="str">
         <f>IF(C21=0,"-",IF(C21&gt;E21,"W",IF(C21&lt;E21,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A21)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D21)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A21)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D21)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A21)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D21)-'Picks Detail'!E41),"L","T")),"T"))))</f>
@@ -27972,7 +28029,7 @@
       </c>
       <c r="C22" s="3">
         <f>SUMPRODUCT(('Picks Detail'!G25:G40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!G25:G40='Picks Detail'!E25:E40))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D22">
         <v>5</v>
@@ -27991,11 +28048,11 @@
       </c>
       <c r="H22">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I22">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28087,7 +28144,7 @@
       </c>
       <c r="E25">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(2,A$21:A$32,0)),0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F25" t="str">
         <f>IF(C25=0,"-",IF(C25&gt;E25,"W",IF(C25&lt;E25,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A25)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D25)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A25)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D25)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A25)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D25)-'Picks Detail'!E41),"L","T")),"T"))))</f>
@@ -28116,7 +28173,7 @@
       </c>
       <c r="C26" s="3">
         <f>SUMPRODUCT(('Picks Detail'!K25:K40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!K25:K40='Picks Detail'!E25:E40))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -28135,11 +28192,11 @@
       </c>
       <c r="H26">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I26">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28152,7 +28209,7 @@
       </c>
       <c r="C27" s="3">
         <f>SUMPRODUCT(('Picks Detail'!L25:L40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!L25:L40='Picks Detail'!E25:E40))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27">
         <v>12</v>
@@ -28171,11 +28228,11 @@
       </c>
       <c r="H27">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I27">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28195,7 +28252,7 @@
       </c>
       <c r="E28">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(11,A$21:A$32,0)),0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F28" t="str">
         <f>IF(C28=0,"-",IF(C28&gt;E28,"W",IF(C28&lt;E28,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A28)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D28)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A28)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D28)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A28)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D28)-'Picks Detail'!E41),"L","T")),"T"))))</f>
@@ -28296,7 +28353,7 @@
       </c>
       <c r="C31" s="3">
         <f>SUMPRODUCT(('Picks Detail'!P25:P40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!P25:P40='Picks Detail'!E25:E40))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D31">
         <v>8</v>
@@ -28315,11 +28372,11 @@
       </c>
       <c r="H31">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I31">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28339,7 +28396,7 @@
       </c>
       <c r="E32">
         <f>IFERROR(INDEX(C$21:C$32,MATCH(7,A$21:A$32,0)),0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F32" t="str">
         <f>IF(C32=0,"-",IF(C32&gt;E32,"W",IF(C32&lt;E32,"L",IF(AND('Picks Detail'!E41&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,A32)&lt;&gt;"",INDEX('Picks Detail'!F41:Q41,1,D32)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A32)-'Picks Detail'!E41)&lt;ABS(INDEX('Picks Detail'!F41:Q41,1,D32)-'Picks Detail'!E41),"W",IF(ABS(INDEX('Picks Detail'!F41:Q41,1,A32)-'Picks Detail'!E41)&gt;ABS(INDEX('Picks Detail'!F41:Q41,1,D32)-'Picks Detail'!E41),"L","T")),"T"))))</f>
@@ -30242,17 +30299,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -33075,17 +33132,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -35908,19 +35965,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -36016,7 +36073,7 @@
       </c>
       <c r="D4">
         <f>Helper!D3</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <f>Helper!E3</f>
@@ -36036,7 +36093,7 @@
       </c>
       <c r="I4">
         <f>Helper!I3</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J4">
         <f>Helper!J3</f>
@@ -36044,7 +36101,7 @@
       </c>
       <c r="K4">
         <f>MAX(Helper!C3:H3)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36196,7 +36253,7 @@
       </c>
       <c r="D8">
         <f>Helper!D7</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8">
         <f>Helper!E7</f>
@@ -36216,7 +36273,7 @@
       </c>
       <c r="I8">
         <f>Helper!I7</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J8">
         <f>Helper!J7</f>
@@ -36241,7 +36298,7 @@
       </c>
       <c r="D9">
         <f>Helper!D8</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <f>Helper!E8</f>
@@ -36261,7 +36318,7 @@
       </c>
       <c r="I9">
         <f>Helper!I8</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J9">
         <f>Helper!J8</f>
@@ -36421,7 +36478,7 @@
       </c>
       <c r="D13">
         <f>Helper!D12</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13">
         <f>Helper!E12</f>
@@ -36441,7 +36498,7 @@
       </c>
       <c r="I13">
         <f>Helper!I12</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J13">
         <f>Helper!J12</f>
@@ -37843,7 +37900,7 @@
       </c>
       <c r="C58">
         <f>Helper!I3</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D58">
         <f>Helper!R3</f>
@@ -37855,11 +37912,11 @@
       </c>
       <c r="F58">
         <f>Helper!AE3</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G58">
         <f>Helper!K3</f>
-        <v>14.0002</v>
+        <v>15.0002</v>
       </c>
       <c r="H58">
         <f>Helper!T3</f>
@@ -37975,7 +38032,7 @@
       </c>
       <c r="C62">
         <f>Helper!I7</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D62">
         <f>Helper!R7</f>
@@ -37987,11 +38044,11 @@
       </c>
       <c r="F62">
         <f>Helper!AE7</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G62">
         <f>Helper!K7</f>
-        <v>19.000599999999999</v>
+        <v>20.000599999999999</v>
       </c>
       <c r="H62">
         <f>Helper!T7</f>
@@ -38008,7 +38065,7 @@
       </c>
       <c r="C63">
         <f>Helper!I8</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D63">
         <f>Helper!R8</f>
@@ -38020,11 +38077,11 @@
       </c>
       <c r="F63">
         <f>Helper!AE8</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G63">
         <f>Helper!K8</f>
-        <v>12.0007</v>
+        <v>13.0007</v>
       </c>
       <c r="H63">
         <f>Helper!T8</f>
@@ -38140,7 +38197,7 @@
       </c>
       <c r="C67">
         <f>Helper!I12</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D67">
         <f>Helper!R12</f>
@@ -38152,11 +38209,11 @@
       </c>
       <c r="F67">
         <f>Helper!AE12</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G67">
         <f>Helper!K12</f>
-        <v>21.001100000000001</v>
+        <v>22.001100000000001</v>
       </c>
       <c r="H67">
         <f>Helper!T12</f>
@@ -38925,7 +38982,7 @@
       </c>
       <c r="I41">
         <f>Helper!AE3</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J41" t="b">
         <f t="shared" si="1"/>
@@ -38933,7 +38990,7 @@
       </c>
       <c r="K41">
         <f>IF(J41,-1,I41+0.00002)</f>
-        <v>14.000019999999999</v>
+        <v>15.000019999999999</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38997,7 +39054,7 @@
       </c>
       <c r="I45">
         <f>Helper!AE7</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J45" t="b">
         <f t="shared" si="1"/>
@@ -39005,7 +39062,7 @@
       </c>
       <c r="K45">
         <f>IF(J45,-1,I45+0.00006)</f>
-        <v>19.000060000000001</v>
+        <v>20.000060000000001</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39015,7 +39072,7 @@
       </c>
       <c r="I46">
         <f>Helper!AE8</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J46" t="b">
         <f t="shared" si="1"/>
@@ -39023,7 +39080,7 @@
       </c>
       <c r="K46">
         <f>IF(J46,-1,I46+0.00007)</f>
-        <v>12.000069999999999</v>
+        <v>13.000069999999999</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39087,7 +39144,7 @@
       </c>
       <c r="I50">
         <f>Helper!AE12</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J50" t="b">
         <f t="shared" si="1"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="306" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1EE7F45-5C00-4AFF-BC1F-F1B4159A4152}"/>
+  <xr:revisionPtr revIDLastSave="307" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBE74F20-650C-4E5C-BC64-8F1646B794E3}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1377,13 +1377,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1665,12 +1665,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="A1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1859,7 +1859,7 @@
         <v>23</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="D2">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H21,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G21,0)</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E2">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H36,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G36,0)</f>
@@ -2869,15 +2869,15 @@
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I13" si="0">SUM(C2:H2)</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J2">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F6="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F21="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F36="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F51="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F66="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F81="W"),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <f>I2+0.0001</f>
-        <v>13.0001</v>
+        <v>19.0001</v>
       </c>
       <c r="L2">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H6,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G6,0)</f>
@@ -2957,11 +2957,11 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE13" si="2">I2+R2+AC2</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AF2">
         <f>AE2+0.0001</f>
-        <v>13.0001</v>
+        <v>19.0001</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="D3">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H22,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G22,0)</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E3">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H37,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G37,0)</f>
@@ -2998,15 +2998,15 @@
       </c>
       <c r="I3">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J3">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F7="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F22="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F37="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F52="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F67="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F82="W"),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <f>I3+0.0002</f>
-        <v>15.0002</v>
+        <v>21.0002</v>
       </c>
       <c r="L3">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H7,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G7,0)</f>
@@ -3086,11 +3086,11 @@
       </c>
       <c r="AE3">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AF3">
         <f>AE3+0.0002</f>
-        <v>15.0002</v>
+        <v>21.0002</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="D5">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H24,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G24,0)</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E5">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H39,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G39,0)</f>
@@ -3256,15 +3256,15 @@
       </c>
       <c r="I5">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J5">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F9="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F24="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F39="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F54="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F69="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F84="W"),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <f>I5+0.0004</f>
-        <v>14.000400000000001</v>
+        <v>20.000399999999999</v>
       </c>
       <c r="L5">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H9,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G9,0)</f>
@@ -3344,11 +3344,11 @@
       </c>
       <c r="AE5">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AF5">
         <f>AE5+0.0004</f>
-        <v>14.000400000000001</v>
+        <v>20.000399999999999</v>
       </c>
     </row>
     <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="D8">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H27,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G27,0)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E8">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H42,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G42,0)</f>
@@ -3643,15 +3643,15 @@
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J8">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F12="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F27="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F42="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F57="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F72="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F87="W"),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
         <f>I8+0.0007</f>
-        <v>13.0007</v>
+        <v>19.000699999999998</v>
       </c>
       <c r="L8">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H12,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G12,0)</f>
@@ -3731,11 +3731,11 @@
       </c>
       <c r="AE8">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AF8">
         <f>AE8+0.0007</f>
-        <v>13.0007</v>
+        <v>19.000699999999998</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D11">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H30,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G30,0)</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E11">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H45,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G45,0)</f>
@@ -4030,15 +4030,15 @@
       </c>
       <c r="I11">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J11">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F15="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F30="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F45="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F60="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F75="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F90="W"),1,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11">
         <f>I11+0.001</f>
-        <v>25.001000000000001</v>
+        <v>31.001000000000001</v>
       </c>
       <c r="L11">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H15,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G15,0)</f>
@@ -4118,11 +4118,11 @@
       </c>
       <c r="AE11">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="AF11">
         <f>AE11+0.001</f>
-        <v>25.001000000000001</v>
+        <v>31.001000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="D12">
         <f>IF(Roster!$B$16&gt;=2,'Wk 1-6 Input'!H31,0)+IF(Roster!$B$16&gt;2,'Wk 1-6 Input'!G31,0)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E12">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H46,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G46,0)</f>
@@ -4159,15 +4159,15 @@
       </c>
       <c r="I12">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J12">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F16="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F31="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F46="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F61="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F76="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F91="W"),1,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12">
         <f>I12+0.0011</f>
-        <v>22.001100000000001</v>
+        <v>28.001100000000001</v>
       </c>
       <c r="L12">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H16,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G16,0)</f>
@@ -4247,11 +4247,11 @@
       </c>
       <c r="AE12">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AF12">
         <f>AE12+0.0011</f>
-        <v>22.001100000000001</v>
+        <v>28.001100000000001</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4402,14 +4402,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -5354,14 +5354,14 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
@@ -6306,14 +6306,14 @@
       </c>
     </row>
     <row r="111" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="23" t="s">
+      <c r="A111" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B111" s="23"/>
-      <c r="C111" s="23"/>
-      <c r="D111" s="23"/>
-      <c r="E111" s="23"/>
-      <c r="F111" s="23"/>
+      <c r="B111" s="22"/>
+      <c r="C111" s="22"/>
+      <c r="D111" s="22"/>
+      <c r="E111" s="22"/>
+      <c r="F111" s="22"/>
     </row>
     <row r="112" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
@@ -7285,67 +7285,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8313,25 +8313,25 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="26"/>
-      <c r="P23" s="26"/>
-      <c r="Q23" s="26"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="24"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="24"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -9299,25 +9299,25 @@
       </c>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="26" t="s">
+      <c r="A42" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="26"/>
-      <c r="L42" s="26"/>
-      <c r="M42" s="26"/>
-      <c r="N42" s="26"/>
-      <c r="O42" s="26"/>
-      <c r="P42" s="26"/>
-      <c r="Q42" s="26"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="24"/>
+      <c r="N42" s="24"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="24"/>
+      <c r="Q42" s="24"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -9877,25 +9877,25 @@
       <c r="Q60" s="14"/>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="26" t="s">
+      <c r="A61" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="26"/>
-      <c r="C61" s="26"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="26"/>
-      <c r="F61" s="26"/>
-      <c r="G61" s="26"/>
-      <c r="H61" s="26"/>
-      <c r="I61" s="26"/>
-      <c r="J61" s="26"/>
-      <c r="K61" s="26"/>
-      <c r="L61" s="26"/>
-      <c r="M61" s="26"/>
-      <c r="N61" s="26"/>
-      <c r="O61" s="26"/>
-      <c r="P61" s="26"/>
-      <c r="Q61" s="26"/>
+      <c r="B61" s="24"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="24"/>
+      <c r="J61" s="24"/>
+      <c r="K61" s="24"/>
+      <c r="L61" s="24"/>
+      <c r="M61" s="24"/>
+      <c r="N61" s="24"/>
+      <c r="O61" s="24"/>
+      <c r="P61" s="24"/>
+      <c r="Q61" s="24"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -10455,25 +10455,25 @@
       <c r="Q79" s="14"/>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="26" t="s">
+      <c r="A80" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="26"/>
-      <c r="C80" s="26"/>
-      <c r="D80" s="26"/>
-      <c r="E80" s="26"/>
-      <c r="F80" s="26"/>
-      <c r="G80" s="26"/>
-      <c r="H80" s="26"/>
-      <c r="I80" s="26"/>
-      <c r="J80" s="26"/>
-      <c r="K80" s="26"/>
-      <c r="L80" s="26"/>
-      <c r="M80" s="26"/>
-      <c r="N80" s="26"/>
-      <c r="O80" s="26"/>
-      <c r="P80" s="26"/>
-      <c r="Q80" s="26"/>
+      <c r="B80" s="24"/>
+      <c r="C80" s="24"/>
+      <c r="D80" s="24"/>
+      <c r="E80" s="24"/>
+      <c r="F80" s="24"/>
+      <c r="G80" s="24"/>
+      <c r="H80" s="24"/>
+      <c r="I80" s="24"/>
+      <c r="J80" s="24"/>
+      <c r="K80" s="24"/>
+      <c r="L80" s="24"/>
+      <c r="M80" s="24"/>
+      <c r="N80" s="24"/>
+      <c r="O80" s="24"/>
+      <c r="P80" s="24"/>
+      <c r="Q80" s="24"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -11003,25 +11003,25 @@
       <c r="Q97" s="14"/>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="26" t="s">
+      <c r="A98" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="26"/>
-      <c r="C98" s="26"/>
-      <c r="D98" s="26"/>
-      <c r="E98" s="26"/>
-      <c r="F98" s="26"/>
-      <c r="G98" s="26"/>
-      <c r="H98" s="26"/>
-      <c r="I98" s="26"/>
-      <c r="J98" s="26"/>
-      <c r="K98" s="26"/>
-      <c r="L98" s="26"/>
-      <c r="M98" s="26"/>
-      <c r="N98" s="26"/>
-      <c r="O98" s="26"/>
-      <c r="P98" s="26"/>
-      <c r="Q98" s="26"/>
+      <c r="B98" s="24"/>
+      <c r="C98" s="24"/>
+      <c r="D98" s="24"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24"/>
+      <c r="H98" s="24"/>
+      <c r="I98" s="24"/>
+      <c r="J98" s="24"/>
+      <c r="K98" s="24"/>
+      <c r="L98" s="24"/>
+      <c r="M98" s="24"/>
+      <c r="N98" s="24"/>
+      <c r="O98" s="24"/>
+      <c r="P98" s="24"/>
+      <c r="Q98" s="24"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -11521,25 +11521,25 @@
       <c r="Q114" s="14"/>
     </row>
     <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="26" t="s">
+      <c r="A115" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="26"/>
-      <c r="C115" s="26"/>
-      <c r="D115" s="26"/>
-      <c r="E115" s="26"/>
-      <c r="F115" s="26"/>
-      <c r="G115" s="26"/>
-      <c r="H115" s="26"/>
-      <c r="I115" s="26"/>
-      <c r="J115" s="26"/>
-      <c r="K115" s="26"/>
-      <c r="L115" s="26"/>
-      <c r="M115" s="26"/>
-      <c r="N115" s="26"/>
-      <c r="O115" s="26"/>
-      <c r="P115" s="26"/>
-      <c r="Q115" s="26"/>
+      <c r="B115" s="24"/>
+      <c r="C115" s="24"/>
+      <c r="D115" s="24"/>
+      <c r="E115" s="24"/>
+      <c r="F115" s="24"/>
+      <c r="G115" s="24"/>
+      <c r="H115" s="24"/>
+      <c r="I115" s="24"/>
+      <c r="J115" s="24"/>
+      <c r="K115" s="24"/>
+      <c r="L115" s="24"/>
+      <c r="M115" s="24"/>
+      <c r="N115" s="24"/>
+      <c r="O115" s="24"/>
+      <c r="P115" s="24"/>
+      <c r="Q115" s="24"/>
     </row>
     <row r="116" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -12039,25 +12039,25 @@
       <c r="Q131" s="14"/>
     </row>
     <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="26" t="s">
+      <c r="A132" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="B132" s="26"/>
-      <c r="C132" s="26"/>
-      <c r="D132" s="26"/>
-      <c r="E132" s="26"/>
-      <c r="F132" s="26"/>
-      <c r="G132" s="26"/>
-      <c r="H132" s="26"/>
-      <c r="I132" s="26"/>
-      <c r="J132" s="26"/>
-      <c r="K132" s="26"/>
-      <c r="L132" s="26"/>
-      <c r="M132" s="26"/>
-      <c r="N132" s="26"/>
-      <c r="O132" s="26"/>
-      <c r="P132" s="26"/>
-      <c r="Q132" s="26"/>
+      <c r="B132" s="24"/>
+      <c r="C132" s="24"/>
+      <c r="D132" s="24"/>
+      <c r="E132" s="24"/>
+      <c r="F132" s="24"/>
+      <c r="G132" s="24"/>
+      <c r="H132" s="24"/>
+      <c r="I132" s="24"/>
+      <c r="J132" s="24"/>
+      <c r="K132" s="24"/>
+      <c r="L132" s="24"/>
+      <c r="M132" s="24"/>
+      <c r="N132" s="24"/>
+      <c r="O132" s="24"/>
+      <c r="P132" s="24"/>
+      <c r="Q132" s="24"/>
     </row>
     <row r="133" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -12557,25 +12557,25 @@
       <c r="Q148" s="14"/>
     </row>
     <row r="149" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="26" t="s">
+      <c r="A149" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="B149" s="26"/>
-      <c r="C149" s="26"/>
-      <c r="D149" s="26"/>
-      <c r="E149" s="26"/>
-      <c r="F149" s="26"/>
-      <c r="G149" s="26"/>
-      <c r="H149" s="26"/>
-      <c r="I149" s="26"/>
-      <c r="J149" s="26"/>
-      <c r="K149" s="26"/>
-      <c r="L149" s="26"/>
-      <c r="M149" s="26"/>
-      <c r="N149" s="26"/>
-      <c r="O149" s="26"/>
-      <c r="P149" s="26"/>
-      <c r="Q149" s="26"/>
+      <c r="B149" s="24"/>
+      <c r="C149" s="24"/>
+      <c r="D149" s="24"/>
+      <c r="E149" s="24"/>
+      <c r="F149" s="24"/>
+      <c r="G149" s="24"/>
+      <c r="H149" s="24"/>
+      <c r="I149" s="24"/>
+      <c r="J149" s="24"/>
+      <c r="K149" s="24"/>
+      <c r="L149" s="24"/>
+      <c r="M149" s="24"/>
+      <c r="N149" s="24"/>
+      <c r="O149" s="24"/>
+      <c r="P149" s="24"/>
+      <c r="Q149" s="24"/>
     </row>
     <row r="150" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -13105,25 +13105,25 @@
       <c r="Q166" s="14"/>
     </row>
     <row r="167" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="26" t="s">
+      <c r="A167" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="B167" s="26"/>
-      <c r="C167" s="26"/>
-      <c r="D167" s="26"/>
-      <c r="E167" s="26"/>
-      <c r="F167" s="26"/>
-      <c r="G167" s="26"/>
-      <c r="H167" s="26"/>
-      <c r="I167" s="26"/>
-      <c r="J167" s="26"/>
-      <c r="K167" s="26"/>
-      <c r="L167" s="26"/>
-      <c r="M167" s="26"/>
-      <c r="N167" s="26"/>
-      <c r="O167" s="26"/>
-      <c r="P167" s="26"/>
-      <c r="Q167" s="26"/>
+      <c r="B167" s="24"/>
+      <c r="C167" s="24"/>
+      <c r="D167" s="24"/>
+      <c r="E167" s="24"/>
+      <c r="F167" s="24"/>
+      <c r="G167" s="24"/>
+      <c r="H167" s="24"/>
+      <c r="I167" s="24"/>
+      <c r="J167" s="24"/>
+      <c r="K167" s="24"/>
+      <c r="L167" s="24"/>
+      <c r="M167" s="24"/>
+      <c r="N167" s="24"/>
+      <c r="O167" s="24"/>
+      <c r="P167" s="24"/>
+      <c r="Q167" s="24"/>
     </row>
     <row r="168" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -13623,25 +13623,25 @@
       <c r="Q183" s="14"/>
     </row>
     <row r="184" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="26" t="s">
+      <c r="A184" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="B184" s="26"/>
-      <c r="C184" s="26"/>
-      <c r="D184" s="26"/>
-      <c r="E184" s="26"/>
-      <c r="F184" s="26"/>
-      <c r="G184" s="26"/>
-      <c r="H184" s="26"/>
-      <c r="I184" s="26"/>
-      <c r="J184" s="26"/>
-      <c r="K184" s="26"/>
-      <c r="L184" s="26"/>
-      <c r="M184" s="26"/>
-      <c r="N184" s="26"/>
-      <c r="O184" s="26"/>
-      <c r="P184" s="26"/>
-      <c r="Q184" s="26"/>
+      <c r="B184" s="24"/>
+      <c r="C184" s="24"/>
+      <c r="D184" s="24"/>
+      <c r="E184" s="24"/>
+      <c r="F184" s="24"/>
+      <c r="G184" s="24"/>
+      <c r="H184" s="24"/>
+      <c r="I184" s="24"/>
+      <c r="J184" s="24"/>
+      <c r="K184" s="24"/>
+      <c r="L184" s="24"/>
+      <c r="M184" s="24"/>
+      <c r="N184" s="24"/>
+      <c r="O184" s="24"/>
+      <c r="P184" s="24"/>
+      <c r="Q184" s="24"/>
     </row>
     <row r="185" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -14111,25 +14111,25 @@
       <c r="Q199" s="14"/>
     </row>
     <row r="200" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="26" t="s">
+      <c r="A200" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="B200" s="26"/>
-      <c r="C200" s="26"/>
-      <c r="D200" s="26"/>
-      <c r="E200" s="26"/>
-      <c r="F200" s="26"/>
-      <c r="G200" s="26"/>
-      <c r="H200" s="26"/>
-      <c r="I200" s="26"/>
-      <c r="J200" s="26"/>
-      <c r="K200" s="26"/>
-      <c r="L200" s="26"/>
-      <c r="M200" s="26"/>
-      <c r="N200" s="26"/>
-      <c r="O200" s="26"/>
-      <c r="P200" s="26"/>
-      <c r="Q200" s="26"/>
+      <c r="B200" s="24"/>
+      <c r="C200" s="24"/>
+      <c r="D200" s="24"/>
+      <c r="E200" s="24"/>
+      <c r="F200" s="24"/>
+      <c r="G200" s="24"/>
+      <c r="H200" s="24"/>
+      <c r="I200" s="24"/>
+      <c r="J200" s="24"/>
+      <c r="K200" s="24"/>
+      <c r="L200" s="24"/>
+      <c r="M200" s="24"/>
+      <c r="N200" s="24"/>
+      <c r="O200" s="24"/>
+      <c r="P200" s="24"/>
+      <c r="Q200" s="24"/>
     </row>
     <row r="201" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -14689,25 +14689,25 @@
       <c r="Q218" s="14"/>
     </row>
     <row r="219" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="26" t="s">
+      <c r="A219" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="B219" s="26"/>
-      <c r="C219" s="26"/>
-      <c r="D219" s="26"/>
-      <c r="E219" s="26"/>
-      <c r="F219" s="26"/>
-      <c r="G219" s="26"/>
-      <c r="H219" s="26"/>
-      <c r="I219" s="26"/>
-      <c r="J219" s="26"/>
-      <c r="K219" s="26"/>
-      <c r="L219" s="26"/>
-      <c r="M219" s="26"/>
-      <c r="N219" s="26"/>
-      <c r="O219" s="26"/>
-      <c r="P219" s="26"/>
-      <c r="Q219" s="26"/>
+      <c r="B219" s="24"/>
+      <c r="C219" s="24"/>
+      <c r="D219" s="24"/>
+      <c r="E219" s="24"/>
+      <c r="F219" s="24"/>
+      <c r="G219" s="24"/>
+      <c r="H219" s="24"/>
+      <c r="I219" s="24"/>
+      <c r="J219" s="24"/>
+      <c r="K219" s="24"/>
+      <c r="L219" s="24"/>
+      <c r="M219" s="24"/>
+      <c r="N219" s="24"/>
+      <c r="O219" s="24"/>
+      <c r="P219" s="24"/>
+      <c r="Q219" s="24"/>
     </row>
     <row r="220" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -15207,25 +15207,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="26" t="s">
+      <c r="A236" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B236" s="26"/>
-      <c r="C236" s="26"/>
-      <c r="D236" s="26"/>
-      <c r="E236" s="26"/>
-      <c r="F236" s="26"/>
-      <c r="G236" s="26"/>
-      <c r="H236" s="26"/>
-      <c r="I236" s="26"/>
-      <c r="J236" s="26"/>
-      <c r="K236" s="26"/>
-      <c r="L236" s="26"/>
-      <c r="M236" s="26"/>
-      <c r="N236" s="26"/>
-      <c r="O236" s="26"/>
-      <c r="P236" s="26"/>
-      <c r="Q236" s="26"/>
+      <c r="B236" s="24"/>
+      <c r="C236" s="24"/>
+      <c r="D236" s="24"/>
+      <c r="E236" s="24"/>
+      <c r="F236" s="24"/>
+      <c r="G236" s="24"/>
+      <c r="H236" s="24"/>
+      <c r="I236" s="24"/>
+      <c r="J236" s="24"/>
+      <c r="K236" s="24"/>
+      <c r="L236" s="24"/>
+      <c r="M236" s="24"/>
+      <c r="N236" s="24"/>
+      <c r="O236" s="24"/>
+      <c r="P236" s="24"/>
+      <c r="Q236" s="24"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -15755,25 +15755,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="26" t="s">
+      <c r="A254" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="B254" s="26"/>
-      <c r="C254" s="26"/>
-      <c r="D254" s="26"/>
-      <c r="E254" s="26"/>
-      <c r="F254" s="26"/>
-      <c r="G254" s="26"/>
-      <c r="H254" s="26"/>
-      <c r="I254" s="26"/>
-      <c r="J254" s="26"/>
-      <c r="K254" s="26"/>
-      <c r="L254" s="26"/>
-      <c r="M254" s="26"/>
-      <c r="N254" s="26"/>
-      <c r="O254" s="26"/>
-      <c r="P254" s="26"/>
-      <c r="Q254" s="26"/>
+      <c r="B254" s="24"/>
+      <c r="C254" s="24"/>
+      <c r="D254" s="24"/>
+      <c r="E254" s="24"/>
+      <c r="F254" s="24"/>
+      <c r="G254" s="24"/>
+      <c r="H254" s="24"/>
+      <c r="I254" s="24"/>
+      <c r="J254" s="24"/>
+      <c r="K254" s="24"/>
+      <c r="L254" s="24"/>
+      <c r="M254" s="24"/>
+      <c r="N254" s="24"/>
+      <c r="O254" s="24"/>
+      <c r="P254" s="24"/>
+      <c r="Q254" s="24"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -16333,25 +16333,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="26" t="s">
+      <c r="A273" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="B273" s="26"/>
-      <c r="C273" s="26"/>
-      <c r="D273" s="26"/>
-      <c r="E273" s="26"/>
-      <c r="F273" s="26"/>
-      <c r="G273" s="26"/>
-      <c r="H273" s="26"/>
-      <c r="I273" s="26"/>
-      <c r="J273" s="26"/>
-      <c r="K273" s="26"/>
-      <c r="L273" s="26"/>
-      <c r="M273" s="26"/>
-      <c r="N273" s="26"/>
-      <c r="O273" s="26"/>
-      <c r="P273" s="26"/>
-      <c r="Q273" s="26"/>
+      <c r="B273" s="24"/>
+      <c r="C273" s="24"/>
+      <c r="D273" s="24"/>
+      <c r="E273" s="24"/>
+      <c r="F273" s="24"/>
+      <c r="G273" s="24"/>
+      <c r="H273" s="24"/>
+      <c r="I273" s="24"/>
+      <c r="J273" s="24"/>
+      <c r="K273" s="24"/>
+      <c r="L273" s="24"/>
+      <c r="M273" s="24"/>
+      <c r="N273" s="24"/>
+      <c r="O273" s="24"/>
+      <c r="P273" s="24"/>
+      <c r="Q273" s="24"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -16911,25 +16911,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="26" t="s">
+      <c r="A292" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="B292" s="26"/>
-      <c r="C292" s="26"/>
-      <c r="D292" s="26"/>
-      <c r="E292" s="26"/>
-      <c r="F292" s="26"/>
-      <c r="G292" s="26"/>
-      <c r="H292" s="26"/>
-      <c r="I292" s="26"/>
-      <c r="J292" s="26"/>
-      <c r="K292" s="26"/>
-      <c r="L292" s="26"/>
-      <c r="M292" s="26"/>
-      <c r="N292" s="26"/>
-      <c r="O292" s="26"/>
-      <c r="P292" s="26"/>
-      <c r="Q292" s="26"/>
+      <c r="B292" s="24"/>
+      <c r="C292" s="24"/>
+      <c r="D292" s="24"/>
+      <c r="E292" s="24"/>
+      <c r="F292" s="24"/>
+      <c r="G292" s="24"/>
+      <c r="H292" s="24"/>
+      <c r="I292" s="24"/>
+      <c r="J292" s="24"/>
+      <c r="K292" s="24"/>
+      <c r="L292" s="24"/>
+      <c r="M292" s="24"/>
+      <c r="N292" s="24"/>
+      <c r="O292" s="24"/>
+      <c r="P292" s="24"/>
+      <c r="Q292" s="24"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -17489,25 +17489,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="26" t="s">
+      <c r="A311" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="B311" s="26"/>
-      <c r="C311" s="26"/>
-      <c r="D311" s="26"/>
-      <c r="E311" s="26"/>
-      <c r="F311" s="26"/>
-      <c r="G311" s="26"/>
-      <c r="H311" s="26"/>
-      <c r="I311" s="26"/>
-      <c r="J311" s="26"/>
-      <c r="K311" s="26"/>
-      <c r="L311" s="26"/>
-      <c r="M311" s="26"/>
-      <c r="N311" s="26"/>
-      <c r="O311" s="26"/>
-      <c r="P311" s="26"/>
-      <c r="Q311" s="26"/>
+      <c r="B311" s="24"/>
+      <c r="C311" s="24"/>
+      <c r="D311" s="24"/>
+      <c r="E311" s="24"/>
+      <c r="F311" s="24"/>
+      <c r="G311" s="24"/>
+      <c r="H311" s="24"/>
+      <c r="I311" s="24"/>
+      <c r="J311" s="24"/>
+      <c r="K311" s="24"/>
+      <c r="L311" s="24"/>
+      <c r="M311" s="24"/>
+      <c r="N311" s="24"/>
+      <c r="O311" s="24"/>
+      <c r="P311" s="24"/>
+      <c r="Q311" s="24"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -18068,26 +18068,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A23:Q23"/>
+    <mergeCell ref="A42:Q42"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="A132:Q132"/>
+    <mergeCell ref="A149:Q149"/>
+    <mergeCell ref="A167:Q167"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A219:Q219"/>
     <mergeCell ref="A236:Q236"/>
     <mergeCell ref="A254:Q254"/>
     <mergeCell ref="A273:Q273"/>
     <mergeCell ref="A292:Q292"/>
     <mergeCell ref="A311:Q311"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A167:Q167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="A23:Q23"/>
-    <mergeCell ref="A42:Q42"/>
   </mergeCells>
   <dataValidations count="268">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or SEA" promptTitle="ATS Pick" prompt="Pick NE or SEA" sqref="F6:Q6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -27466,17 +27466,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -30299,17 +30299,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -33132,17 +33132,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -35965,19 +35965,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -36028,7 +36028,7 @@
       </c>
       <c r="D3">
         <f>Helper!D2</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E3">
         <f>Helper!E2</f>
@@ -36048,15 +36048,15 @@
       </c>
       <c r="I3">
         <f>Helper!I2</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J3">
         <f>Helper!J2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <f>MAX(Helper!C2:H2)</f>
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36073,7 +36073,7 @@
       </c>
       <c r="D4">
         <f>Helper!D3</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E4">
         <f>Helper!E3</f>
@@ -36093,15 +36093,15 @@
       </c>
       <c r="I4">
         <f>Helper!I3</f>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J4">
         <f>Helper!J3</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <f>MAX(Helper!C3:H3)</f>
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36163,7 +36163,7 @@
       </c>
       <c r="D6">
         <f>Helper!D5</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <f>Helper!E5</f>
@@ -36183,15 +36183,15 @@
       </c>
       <c r="I6">
         <f>Helper!I5</f>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J6">
         <f>Helper!J5</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
         <f>MAX(Helper!C5:H5)</f>
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36298,7 +36298,7 @@
       </c>
       <c r="D9">
         <f>Helper!D8</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E9">
         <f>Helper!E8</f>
@@ -36318,15 +36318,15 @@
       </c>
       <c r="I9">
         <f>Helper!I8</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J9">
         <f>Helper!J8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9">
         <f>MAX(Helper!C8:H8)</f>
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36433,7 +36433,7 @@
       </c>
       <c r="D12">
         <f>Helper!D11</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E12">
         <f>Helper!E11</f>
@@ -36453,11 +36453,11 @@
       </c>
       <c r="I12">
         <f>Helper!I11</f>
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J12">
         <f>Helper!J11</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12">
         <f>MAX(Helper!C11:H11)</f>
@@ -36478,7 +36478,7 @@
       </c>
       <c r="D13">
         <f>Helper!D12</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E13">
         <f>Helper!E12</f>
@@ -36498,11 +36498,11 @@
       </c>
       <c r="I13">
         <f>Helper!I12</f>
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J13">
         <f>Helper!J12</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13">
         <f>MAX(Helper!C12:H12)</f>
@@ -37867,7 +37867,7 @@
       </c>
       <c r="C57">
         <f>Helper!I2</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D57">
         <f>Helper!R2</f>
@@ -37879,11 +37879,11 @@
       </c>
       <c r="F57">
         <f>Helper!AE2</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G57">
         <f>Helper!K2</f>
-        <v>13.0001</v>
+        <v>19.0001</v>
       </c>
       <c r="H57">
         <f>Helper!T2</f>
@@ -37900,7 +37900,7 @@
       </c>
       <c r="C58">
         <f>Helper!I3</f>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D58">
         <f>Helper!R3</f>
@@ -37912,11 +37912,11 @@
       </c>
       <c r="F58">
         <f>Helper!AE3</f>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G58">
         <f>Helper!K3</f>
-        <v>15.0002</v>
+        <v>21.0002</v>
       </c>
       <c r="H58">
         <f>Helper!T3</f>
@@ -37966,7 +37966,7 @@
       </c>
       <c r="C60">
         <f>Helper!I5</f>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D60">
         <f>Helper!R5</f>
@@ -37978,11 +37978,11 @@
       </c>
       <c r="F60">
         <f>Helper!AE5</f>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G60">
         <f>Helper!K5</f>
-        <v>14.000400000000001</v>
+        <v>20.000399999999999</v>
       </c>
       <c r="H60">
         <f>Helper!T5</f>
@@ -38065,7 +38065,7 @@
       </c>
       <c r="C63">
         <f>Helper!I8</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D63">
         <f>Helper!R8</f>
@@ -38077,11 +38077,11 @@
       </c>
       <c r="F63">
         <f>Helper!AE8</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G63">
         <f>Helper!K8</f>
-        <v>13.0007</v>
+        <v>19.000699999999998</v>
       </c>
       <c r="H63">
         <f>Helper!T8</f>
@@ -38164,7 +38164,7 @@
       </c>
       <c r="C66">
         <f>Helper!I11</f>
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D66">
         <f>Helper!R11</f>
@@ -38176,11 +38176,11 @@
       </c>
       <c r="F66">
         <f>Helper!AE11</f>
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G66">
         <f>Helper!K11</f>
-        <v>25.001000000000001</v>
+        <v>31.001000000000001</v>
       </c>
       <c r="H66">
         <f>Helper!T11</f>
@@ -38197,7 +38197,7 @@
       </c>
       <c r="C67">
         <f>Helper!I12</f>
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D67">
         <f>Helper!R12</f>
@@ -38209,11 +38209,11 @@
       </c>
       <c r="F67">
         <f>Helper!AE12</f>
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G67">
         <f>Helper!K12</f>
-        <v>22.001100000000001</v>
+        <v>28.001100000000001</v>
       </c>
       <c r="H67">
         <f>Helper!T12</f>
@@ -38964,7 +38964,7 @@
       </c>
       <c r="I40">
         <f>Helper!AE2</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J40" t="b">
         <f t="shared" ref="J40:J51" si="1">OR(H40=$E$5,H40=$E$6,H40=$E$7,H40=$E$8,H40=$E$9)</f>
@@ -38972,7 +38972,7 @@
       </c>
       <c r="K40">
         <f>IF(J40,-1,I40+0.00001)</f>
-        <v>13.00001</v>
+        <v>19.00001</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38982,7 +38982,7 @@
       </c>
       <c r="I41">
         <f>Helper!AE3</f>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J41" t="b">
         <f t="shared" si="1"/>
@@ -38990,7 +38990,7 @@
       </c>
       <c r="K41">
         <f>IF(J41,-1,I41+0.00002)</f>
-        <v>15.000019999999999</v>
+        <v>21.000019999999999</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39018,7 +39018,7 @@
       </c>
       <c r="I43">
         <f>Helper!AE5</f>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J43" t="b">
         <f t="shared" si="1"/>
@@ -39072,7 +39072,7 @@
       </c>
       <c r="I46">
         <f>Helper!AE8</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J46" t="b">
         <f t="shared" si="1"/>
@@ -39080,7 +39080,7 @@
       </c>
       <c r="K46">
         <f>IF(J46,-1,I46+0.00007)</f>
-        <v>13.000069999999999</v>
+        <v>19.000070000000001</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39126,7 +39126,7 @@
       </c>
       <c r="I49">
         <f>Helper!AE11</f>
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J49" t="b">
         <f t="shared" si="1"/>
@@ -39144,7 +39144,7 @@
       </c>
       <c r="I50">
         <f>Helper!AE12</f>
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J50" t="b">
         <f t="shared" si="1"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="307" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBE74F20-650C-4E5C-BC64-8F1646B794E3}"/>
+  <xr:revisionPtr revIDLastSave="319" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3156F26F-43EA-4881-9CAA-AE5B07250BA9}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3599" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="346">
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -1377,13 +1377,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1665,12 +1665,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="E2">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H36,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G36,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H51,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G51,0)</f>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I13" si="0">SUM(C2:H2)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F6="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F21="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F36="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F51="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F66="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F81="W"),1,0)</f>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="K2">
         <f>I2+0.0001</f>
-        <v>19.0001</v>
+        <v>20.0001</v>
       </c>
       <c r="L2">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H6,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G6,0)</f>
@@ -2957,11 +2957,11 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE13" si="2">I2+R2+AC2</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF2">
         <f>AE2+0.0001</f>
-        <v>19.0001</v>
+        <v>20.0001</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E4">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H38,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G38,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H53,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G53,0)</f>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J4">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F8="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F23="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F38="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F53="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F68="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F83="W"),1,0)</f>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="K4">
         <f>I4+0.0003</f>
-        <v>20.000299999999999</v>
+        <v>21.000299999999999</v>
       </c>
       <c r="L4">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H8,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G8,0)</f>
@@ -3215,11 +3215,11 @@
       </c>
       <c r="AE4">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF4">
         <f>AE4+0.0003</f>
-        <v>20.000299999999999</v>
+        <v>21.000299999999999</v>
       </c>
     </row>
     <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4402,14 +4402,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -5354,14 +5354,14 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="22" t="s">
+      <c r="A56" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="22"/>
-      <c r="C56" s="22"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
@@ -6306,14 +6306,14 @@
       </c>
     </row>
     <row r="111" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="22" t="s">
+      <c r="A111" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B111" s="22"/>
-      <c r="C111" s="22"/>
-      <c r="D111" s="22"/>
-      <c r="E111" s="22"/>
-      <c r="F111" s="22"/>
+      <c r="B111" s="23"/>
+      <c r="C111" s="23"/>
+      <c r="D111" s="23"/>
+      <c r="E111" s="23"/>
+      <c r="F111" s="23"/>
     </row>
     <row r="112" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
@@ -7285,67 +7285,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="24"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8313,25 +8313,25 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="24"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -9299,25 +9299,25 @@
       </c>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+      <c r="A42" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="24"/>
-      <c r="K42" s="24"/>
-      <c r="L42" s="24"/>
-      <c r="M42" s="24"/>
-      <c r="N42" s="24"/>
-      <c r="O42" s="24"/>
-      <c r="P42" s="24"/>
-      <c r="Q42" s="24"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="26"/>
+      <c r="Q42" s="26"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -9387,18 +9387,36 @@
       </c>
       <c r="E44" s="9" t="str">
         <f>'NFL Schedule'!J41</f>
-        <v/>
-      </c>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
+        <v>ATL</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="10"/>
-      <c r="O44" s="10"/>
+      <c r="J44" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="K44" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="L44" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="M44" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="N44" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="O44" s="10" t="s">
+        <v>81</v>
+      </c>
       <c r="P44" s="10"/>
       <c r="Q44" s="10"/>
     </row>
@@ -9877,25 +9895,25 @@
       <c r="Q60" s="14"/>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="24" t="s">
+      <c r="A61" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="24"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="24"/>
-      <c r="J61" s="24"/>
-      <c r="K61" s="24"/>
-      <c r="L61" s="24"/>
-      <c r="M61" s="24"/>
-      <c r="N61" s="24"/>
-      <c r="O61" s="24"/>
-      <c r="P61" s="24"/>
-      <c r="Q61" s="24"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="26"/>
+      <c r="J61" s="26"/>
+      <c r="K61" s="26"/>
+      <c r="L61" s="26"/>
+      <c r="M61" s="26"/>
+      <c r="N61" s="26"/>
+      <c r="O61" s="26"/>
+      <c r="P61" s="26"/>
+      <c r="Q61" s="26"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -10455,25 +10473,25 @@
       <c r="Q79" s="14"/>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="24" t="s">
+      <c r="A80" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="24"/>
-      <c r="C80" s="24"/>
-      <c r="D80" s="24"/>
-      <c r="E80" s="24"/>
-      <c r="F80" s="24"/>
-      <c r="G80" s="24"/>
-      <c r="H80" s="24"/>
-      <c r="I80" s="24"/>
-      <c r="J80" s="24"/>
-      <c r="K80" s="24"/>
-      <c r="L80" s="24"/>
-      <c r="M80" s="24"/>
-      <c r="N80" s="24"/>
-      <c r="O80" s="24"/>
-      <c r="P80" s="24"/>
-      <c r="Q80" s="24"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
+      <c r="I80" s="26"/>
+      <c r="J80" s="26"/>
+      <c r="K80" s="26"/>
+      <c r="L80" s="26"/>
+      <c r="M80" s="26"/>
+      <c r="N80" s="26"/>
+      <c r="O80" s="26"/>
+      <c r="P80" s="26"/>
+      <c r="Q80" s="26"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -11003,25 +11021,25 @@
       <c r="Q97" s="14"/>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="24" t="s">
+      <c r="A98" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="24"/>
-      <c r="C98" s="24"/>
-      <c r="D98" s="24"/>
-      <c r="E98" s="24"/>
-      <c r="F98" s="24"/>
-      <c r="G98" s="24"/>
-      <c r="H98" s="24"/>
-      <c r="I98" s="24"/>
-      <c r="J98" s="24"/>
-      <c r="K98" s="24"/>
-      <c r="L98" s="24"/>
-      <c r="M98" s="24"/>
-      <c r="N98" s="24"/>
-      <c r="O98" s="24"/>
-      <c r="P98" s="24"/>
-      <c r="Q98" s="24"/>
+      <c r="B98" s="26"/>
+      <c r="C98" s="26"/>
+      <c r="D98" s="26"/>
+      <c r="E98" s="26"/>
+      <c r="F98" s="26"/>
+      <c r="G98" s="26"/>
+      <c r="H98" s="26"/>
+      <c r="I98" s="26"/>
+      <c r="J98" s="26"/>
+      <c r="K98" s="26"/>
+      <c r="L98" s="26"/>
+      <c r="M98" s="26"/>
+      <c r="N98" s="26"/>
+      <c r="O98" s="26"/>
+      <c r="P98" s="26"/>
+      <c r="Q98" s="26"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -11521,25 +11539,25 @@
       <c r="Q114" s="14"/>
     </row>
     <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="24" t="s">
+      <c r="A115" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="24"/>
-      <c r="C115" s="24"/>
-      <c r="D115" s="24"/>
-      <c r="E115" s="24"/>
-      <c r="F115" s="24"/>
-      <c r="G115" s="24"/>
-      <c r="H115" s="24"/>
-      <c r="I115" s="24"/>
-      <c r="J115" s="24"/>
-      <c r="K115" s="24"/>
-      <c r="L115" s="24"/>
-      <c r="M115" s="24"/>
-      <c r="N115" s="24"/>
-      <c r="O115" s="24"/>
-      <c r="P115" s="24"/>
-      <c r="Q115" s="24"/>
+      <c r="B115" s="26"/>
+      <c r="C115" s="26"/>
+      <c r="D115" s="26"/>
+      <c r="E115" s="26"/>
+      <c r="F115" s="26"/>
+      <c r="G115" s="26"/>
+      <c r="H115" s="26"/>
+      <c r="I115" s="26"/>
+      <c r="J115" s="26"/>
+      <c r="K115" s="26"/>
+      <c r="L115" s="26"/>
+      <c r="M115" s="26"/>
+      <c r="N115" s="26"/>
+      <c r="O115" s="26"/>
+      <c r="P115" s="26"/>
+      <c r="Q115" s="26"/>
     </row>
     <row r="116" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -12039,25 +12057,25 @@
       <c r="Q131" s="14"/>
     </row>
     <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="24" t="s">
+      <c r="A132" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="B132" s="24"/>
-      <c r="C132" s="24"/>
-      <c r="D132" s="24"/>
-      <c r="E132" s="24"/>
-      <c r="F132" s="24"/>
-      <c r="G132" s="24"/>
-      <c r="H132" s="24"/>
-      <c r="I132" s="24"/>
-      <c r="J132" s="24"/>
-      <c r="K132" s="24"/>
-      <c r="L132" s="24"/>
-      <c r="M132" s="24"/>
-      <c r="N132" s="24"/>
-      <c r="O132" s="24"/>
-      <c r="P132" s="24"/>
-      <c r="Q132" s="24"/>
+      <c r="B132" s="26"/>
+      <c r="C132" s="26"/>
+      <c r="D132" s="26"/>
+      <c r="E132" s="26"/>
+      <c r="F132" s="26"/>
+      <c r="G132" s="26"/>
+      <c r="H132" s="26"/>
+      <c r="I132" s="26"/>
+      <c r="J132" s="26"/>
+      <c r="K132" s="26"/>
+      <c r="L132" s="26"/>
+      <c r="M132" s="26"/>
+      <c r="N132" s="26"/>
+      <c r="O132" s="26"/>
+      <c r="P132" s="26"/>
+      <c r="Q132" s="26"/>
     </row>
     <row r="133" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -12557,25 +12575,25 @@
       <c r="Q148" s="14"/>
     </row>
     <row r="149" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="24" t="s">
+      <c r="A149" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="B149" s="24"/>
-      <c r="C149" s="24"/>
-      <c r="D149" s="24"/>
-      <c r="E149" s="24"/>
-      <c r="F149" s="24"/>
-      <c r="G149" s="24"/>
-      <c r="H149" s="24"/>
-      <c r="I149" s="24"/>
-      <c r="J149" s="24"/>
-      <c r="K149" s="24"/>
-      <c r="L149" s="24"/>
-      <c r="M149" s="24"/>
-      <c r="N149" s="24"/>
-      <c r="O149" s="24"/>
-      <c r="P149" s="24"/>
-      <c r="Q149" s="24"/>
+      <c r="B149" s="26"/>
+      <c r="C149" s="26"/>
+      <c r="D149" s="26"/>
+      <c r="E149" s="26"/>
+      <c r="F149" s="26"/>
+      <c r="G149" s="26"/>
+      <c r="H149" s="26"/>
+      <c r="I149" s="26"/>
+      <c r="J149" s="26"/>
+      <c r="K149" s="26"/>
+      <c r="L149" s="26"/>
+      <c r="M149" s="26"/>
+      <c r="N149" s="26"/>
+      <c r="O149" s="26"/>
+      <c r="P149" s="26"/>
+      <c r="Q149" s="26"/>
     </row>
     <row r="150" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -13105,25 +13123,25 @@
       <c r="Q166" s="14"/>
     </row>
     <row r="167" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="24" t="s">
+      <c r="A167" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="B167" s="24"/>
-      <c r="C167" s="24"/>
-      <c r="D167" s="24"/>
-      <c r="E167" s="24"/>
-      <c r="F167" s="24"/>
-      <c r="G167" s="24"/>
-      <c r="H167" s="24"/>
-      <c r="I167" s="24"/>
-      <c r="J167" s="24"/>
-      <c r="K167" s="24"/>
-      <c r="L167" s="24"/>
-      <c r="M167" s="24"/>
-      <c r="N167" s="24"/>
-      <c r="O167" s="24"/>
-      <c r="P167" s="24"/>
-      <c r="Q167" s="24"/>
+      <c r="B167" s="26"/>
+      <c r="C167" s="26"/>
+      <c r="D167" s="26"/>
+      <c r="E167" s="26"/>
+      <c r="F167" s="26"/>
+      <c r="G167" s="26"/>
+      <c r="H167" s="26"/>
+      <c r="I167" s="26"/>
+      <c r="J167" s="26"/>
+      <c r="K167" s="26"/>
+      <c r="L167" s="26"/>
+      <c r="M167" s="26"/>
+      <c r="N167" s="26"/>
+      <c r="O167" s="26"/>
+      <c r="P167" s="26"/>
+      <c r="Q167" s="26"/>
     </row>
     <row r="168" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -13623,25 +13641,25 @@
       <c r="Q183" s="14"/>
     </row>
     <row r="184" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="24" t="s">
+      <c r="A184" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="B184" s="24"/>
-      <c r="C184" s="24"/>
-      <c r="D184" s="24"/>
-      <c r="E184" s="24"/>
-      <c r="F184" s="24"/>
-      <c r="G184" s="24"/>
-      <c r="H184" s="24"/>
-      <c r="I184" s="24"/>
-      <c r="J184" s="24"/>
-      <c r="K184" s="24"/>
-      <c r="L184" s="24"/>
-      <c r="M184" s="24"/>
-      <c r="N184" s="24"/>
-      <c r="O184" s="24"/>
-      <c r="P184" s="24"/>
-      <c r="Q184" s="24"/>
+      <c r="B184" s="26"/>
+      <c r="C184" s="26"/>
+      <c r="D184" s="26"/>
+      <c r="E184" s="26"/>
+      <c r="F184" s="26"/>
+      <c r="G184" s="26"/>
+      <c r="H184" s="26"/>
+      <c r="I184" s="26"/>
+      <c r="J184" s="26"/>
+      <c r="K184" s="26"/>
+      <c r="L184" s="26"/>
+      <c r="M184" s="26"/>
+      <c r="N184" s="26"/>
+      <c r="O184" s="26"/>
+      <c r="P184" s="26"/>
+      <c r="Q184" s="26"/>
     </row>
     <row r="185" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -14111,25 +14129,25 @@
       <c r="Q199" s="14"/>
     </row>
     <row r="200" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="24" t="s">
+      <c r="A200" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="B200" s="24"/>
-      <c r="C200" s="24"/>
-      <c r="D200" s="24"/>
-      <c r="E200" s="24"/>
-      <c r="F200" s="24"/>
-      <c r="G200" s="24"/>
-      <c r="H200" s="24"/>
-      <c r="I200" s="24"/>
-      <c r="J200" s="24"/>
-      <c r="K200" s="24"/>
-      <c r="L200" s="24"/>
-      <c r="M200" s="24"/>
-      <c r="N200" s="24"/>
-      <c r="O200" s="24"/>
-      <c r="P200" s="24"/>
-      <c r="Q200" s="24"/>
+      <c r="B200" s="26"/>
+      <c r="C200" s="26"/>
+      <c r="D200" s="26"/>
+      <c r="E200" s="26"/>
+      <c r="F200" s="26"/>
+      <c r="G200" s="26"/>
+      <c r="H200" s="26"/>
+      <c r="I200" s="26"/>
+      <c r="J200" s="26"/>
+      <c r="K200" s="26"/>
+      <c r="L200" s="26"/>
+      <c r="M200" s="26"/>
+      <c r="N200" s="26"/>
+      <c r="O200" s="26"/>
+      <c r="P200" s="26"/>
+      <c r="Q200" s="26"/>
     </row>
     <row r="201" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -14689,25 +14707,25 @@
       <c r="Q218" s="14"/>
     </row>
     <row r="219" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="24" t="s">
+      <c r="A219" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="B219" s="24"/>
-      <c r="C219" s="24"/>
-      <c r="D219" s="24"/>
-      <c r="E219" s="24"/>
-      <c r="F219" s="24"/>
-      <c r="G219" s="24"/>
-      <c r="H219" s="24"/>
-      <c r="I219" s="24"/>
-      <c r="J219" s="24"/>
-      <c r="K219" s="24"/>
-      <c r="L219" s="24"/>
-      <c r="M219" s="24"/>
-      <c r="N219" s="24"/>
-      <c r="O219" s="24"/>
-      <c r="P219" s="24"/>
-      <c r="Q219" s="24"/>
+      <c r="B219" s="26"/>
+      <c r="C219" s="26"/>
+      <c r="D219" s="26"/>
+      <c r="E219" s="26"/>
+      <c r="F219" s="26"/>
+      <c r="G219" s="26"/>
+      <c r="H219" s="26"/>
+      <c r="I219" s="26"/>
+      <c r="J219" s="26"/>
+      <c r="K219" s="26"/>
+      <c r="L219" s="26"/>
+      <c r="M219" s="26"/>
+      <c r="N219" s="26"/>
+      <c r="O219" s="26"/>
+      <c r="P219" s="26"/>
+      <c r="Q219" s="26"/>
     </row>
     <row r="220" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -15207,25 +15225,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="24" t="s">
+      <c r="A236" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="B236" s="24"/>
-      <c r="C236" s="24"/>
-      <c r="D236" s="24"/>
-      <c r="E236" s="24"/>
-      <c r="F236" s="24"/>
-      <c r="G236" s="24"/>
-      <c r="H236" s="24"/>
-      <c r="I236" s="24"/>
-      <c r="J236" s="24"/>
-      <c r="K236" s="24"/>
-      <c r="L236" s="24"/>
-      <c r="M236" s="24"/>
-      <c r="N236" s="24"/>
-      <c r="O236" s="24"/>
-      <c r="P236" s="24"/>
-      <c r="Q236" s="24"/>
+      <c r="B236" s="26"/>
+      <c r="C236" s="26"/>
+      <c r="D236" s="26"/>
+      <c r="E236" s="26"/>
+      <c r="F236" s="26"/>
+      <c r="G236" s="26"/>
+      <c r="H236" s="26"/>
+      <c r="I236" s="26"/>
+      <c r="J236" s="26"/>
+      <c r="K236" s="26"/>
+      <c r="L236" s="26"/>
+      <c r="M236" s="26"/>
+      <c r="N236" s="26"/>
+      <c r="O236" s="26"/>
+      <c r="P236" s="26"/>
+      <c r="Q236" s="26"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -15755,25 +15773,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="24" t="s">
+      <c r="A254" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="B254" s="24"/>
-      <c r="C254" s="24"/>
-      <c r="D254" s="24"/>
-      <c r="E254" s="24"/>
-      <c r="F254" s="24"/>
-      <c r="G254" s="24"/>
-      <c r="H254" s="24"/>
-      <c r="I254" s="24"/>
-      <c r="J254" s="24"/>
-      <c r="K254" s="24"/>
-      <c r="L254" s="24"/>
-      <c r="M254" s="24"/>
-      <c r="N254" s="24"/>
-      <c r="O254" s="24"/>
-      <c r="P254" s="24"/>
-      <c r="Q254" s="24"/>
+      <c r="B254" s="26"/>
+      <c r="C254" s="26"/>
+      <c r="D254" s="26"/>
+      <c r="E254" s="26"/>
+      <c r="F254" s="26"/>
+      <c r="G254" s="26"/>
+      <c r="H254" s="26"/>
+      <c r="I254" s="26"/>
+      <c r="J254" s="26"/>
+      <c r="K254" s="26"/>
+      <c r="L254" s="26"/>
+      <c r="M254" s="26"/>
+      <c r="N254" s="26"/>
+      <c r="O254" s="26"/>
+      <c r="P254" s="26"/>
+      <c r="Q254" s="26"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -16333,25 +16351,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="24" t="s">
+      <c r="A273" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="B273" s="24"/>
-      <c r="C273" s="24"/>
-      <c r="D273" s="24"/>
-      <c r="E273" s="24"/>
-      <c r="F273" s="24"/>
-      <c r="G273" s="24"/>
-      <c r="H273" s="24"/>
-      <c r="I273" s="24"/>
-      <c r="J273" s="24"/>
-      <c r="K273" s="24"/>
-      <c r="L273" s="24"/>
-      <c r="M273" s="24"/>
-      <c r="N273" s="24"/>
-      <c r="O273" s="24"/>
-      <c r="P273" s="24"/>
-      <c r="Q273" s="24"/>
+      <c r="B273" s="26"/>
+      <c r="C273" s="26"/>
+      <c r="D273" s="26"/>
+      <c r="E273" s="26"/>
+      <c r="F273" s="26"/>
+      <c r="G273" s="26"/>
+      <c r="H273" s="26"/>
+      <c r="I273" s="26"/>
+      <c r="J273" s="26"/>
+      <c r="K273" s="26"/>
+      <c r="L273" s="26"/>
+      <c r="M273" s="26"/>
+      <c r="N273" s="26"/>
+      <c r="O273" s="26"/>
+      <c r="P273" s="26"/>
+      <c r="Q273" s="26"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -16911,25 +16929,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="24" t="s">
+      <c r="A292" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="B292" s="24"/>
-      <c r="C292" s="24"/>
-      <c r="D292" s="24"/>
-      <c r="E292" s="24"/>
-      <c r="F292" s="24"/>
-      <c r="G292" s="24"/>
-      <c r="H292" s="24"/>
-      <c r="I292" s="24"/>
-      <c r="J292" s="24"/>
-      <c r="K292" s="24"/>
-      <c r="L292" s="24"/>
-      <c r="M292" s="24"/>
-      <c r="N292" s="24"/>
-      <c r="O292" s="24"/>
-      <c r="P292" s="24"/>
-      <c r="Q292" s="24"/>
+      <c r="B292" s="26"/>
+      <c r="C292" s="26"/>
+      <c r="D292" s="26"/>
+      <c r="E292" s="26"/>
+      <c r="F292" s="26"/>
+      <c r="G292" s="26"/>
+      <c r="H292" s="26"/>
+      <c r="I292" s="26"/>
+      <c r="J292" s="26"/>
+      <c r="K292" s="26"/>
+      <c r="L292" s="26"/>
+      <c r="M292" s="26"/>
+      <c r="N292" s="26"/>
+      <c r="O292" s="26"/>
+      <c r="P292" s="26"/>
+      <c r="Q292" s="26"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -17489,25 +17507,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="24" t="s">
+      <c r="A311" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="B311" s="24"/>
-      <c r="C311" s="24"/>
-      <c r="D311" s="24"/>
-      <c r="E311" s="24"/>
-      <c r="F311" s="24"/>
-      <c r="G311" s="24"/>
-      <c r="H311" s="24"/>
-      <c r="I311" s="24"/>
-      <c r="J311" s="24"/>
-      <c r="K311" s="24"/>
-      <c r="L311" s="24"/>
-      <c r="M311" s="24"/>
-      <c r="N311" s="24"/>
-      <c r="O311" s="24"/>
-      <c r="P311" s="24"/>
-      <c r="Q311" s="24"/>
+      <c r="B311" s="26"/>
+      <c r="C311" s="26"/>
+      <c r="D311" s="26"/>
+      <c r="E311" s="26"/>
+      <c r="F311" s="26"/>
+      <c r="G311" s="26"/>
+      <c r="H311" s="26"/>
+      <c r="I311" s="26"/>
+      <c r="J311" s="26"/>
+      <c r="K311" s="26"/>
+      <c r="L311" s="26"/>
+      <c r="M311" s="26"/>
+      <c r="N311" s="26"/>
+      <c r="O311" s="26"/>
+      <c r="P311" s="26"/>
+      <c r="Q311" s="26"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -18068,26 +18086,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A236:Q236"/>
+    <mergeCell ref="A254:Q254"/>
+    <mergeCell ref="A273:Q273"/>
+    <mergeCell ref="A292:Q292"/>
+    <mergeCell ref="A311:Q311"/>
+    <mergeCell ref="A149:Q149"/>
+    <mergeCell ref="A167:Q167"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A219:Q219"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="A132:Q132"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A4:Q4"/>
     <mergeCell ref="A23:Q23"/>
     <mergeCell ref="A42:Q42"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A167:Q167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A236:Q236"/>
-    <mergeCell ref="A254:Q254"/>
-    <mergeCell ref="A273:Q273"/>
-    <mergeCell ref="A292:Q292"/>
-    <mergeCell ref="A311:Q311"/>
   </mergeCells>
   <dataValidations count="268">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or SEA" promptTitle="ATS Pick" prompt="Pick NE or SEA" sqref="F6:Q6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -20406,16 +20424,25 @@
       <c r="D41" t="s">
         <v>73</v>
       </c>
+      <c r="E41">
+        <v>35</v>
+      </c>
       <c r="F41" t="s">
         <v>81</v>
       </c>
+      <c r="G41">
+        <v>14</v>
+      </c>
+      <c r="H41">
+        <v>6.5</v>
+      </c>
       <c r="I41" t="str">
         <f t="shared" ref="I41:I56" si="4">IF(OR(E41="",G41=""),"",IF(E41&gt;G41,D41,IF(G41&gt;E41,F41,"TIE")))</f>
-        <v/>
+        <v>ATL</v>
       </c>
       <c r="J41" t="str">
         <f t="shared" ref="J41:J56" si="5">IF(OR(E41="",G41="",H41=""),"",IF(E41+H41&gt;G41,D41,IF(E41+H41&lt;G41,F41,"PUSH")))</f>
-        <v/>
+        <v>ATL</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27466,17 +27493,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -28459,7 +28486,7 @@
       </c>
       <c r="C36" s="3">
         <f>SUMPRODUCT(('Picks Detail'!F44:F59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!F44:F59='Picks Detail'!E44:E59))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36">
         <v>7</v>
@@ -28470,19 +28497,19 @@
       </c>
       <c r="F36" t="str">
         <f>IF(C36=0,"-",IF(C36&gt;E36,"W",IF(C36&lt;E36,"L",IF(AND('Picks Detail'!E60&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,A36)&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,D36)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A36)-'Picks Detail'!E60)&lt;ABS(INDEX('Picks Detail'!F60:Q60,1,D36)-'Picks Detail'!E60),"W",IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A36)-'Picks Detail'!E60)&gt;ABS(INDEX('Picks Detail'!F60:Q60,1,D36)-'Picks Detail'!E60),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G36">
         <f t="shared" ref="G36:G47" si="6">IF(F36="W",6,IF(F36="T",3,0))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H36">
         <f t="shared" ref="H36:H47" si="7">IF(C36="",0,C36)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36">
         <f t="shared" ref="I36:I47" si="8">G36+H36</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28531,7 +28558,7 @@
       </c>
       <c r="C38" s="3">
         <f>SUMPRODUCT(('Picks Detail'!H44:H59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!H44:H59='Picks Detail'!E44:E59))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38">
         <v>11</v>
@@ -28542,19 +28569,19 @@
       </c>
       <c r="F38" t="str">
         <f>IF(C38=0,"-",IF(C38&gt;E38,"W",IF(C38&lt;E38,"L",IF(AND('Picks Detail'!E60&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,A38)&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,D38)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A38)-'Picks Detail'!E60)&lt;ABS(INDEX('Picks Detail'!F60:Q60,1,D38)-'Picks Detail'!E60),"W",IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A38)-'Picks Detail'!E60)&gt;ABS(INDEX('Picks Detail'!F60:Q60,1,D38)-'Picks Detail'!E60),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G38">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H38">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28682,7 +28709,7 @@
       </c>
       <c r="E42">
         <f>IFERROR(INDEX(C$36:C$47,MATCH(1,A$36:A$47,0)),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="str">
         <f>IF(C42=0,"-",IF(C42&gt;E42,"W",IF(C42&lt;E42,"L",IF(AND('Picks Detail'!E60&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,A42)&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,D42)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A42)-'Picks Detail'!E60)&lt;ABS(INDEX('Picks Detail'!F60:Q60,1,D42)-'Picks Detail'!E60),"W",IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A42)-'Picks Detail'!E60)&gt;ABS(INDEX('Picks Detail'!F60:Q60,1,D42)-'Picks Detail'!E60),"L","T")),"T"))))</f>
@@ -28826,7 +28853,7 @@
       </c>
       <c r="E46">
         <f>IFERROR(INDEX(C$36:C$47,MATCH(3,A$36:A$47,0)),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="str">
         <f>IF(C46=0,"-",IF(C46&gt;E46,"W",IF(C46&lt;E46,"L",IF(AND('Picks Detail'!E60&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,A46)&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,D46)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A46)-'Picks Detail'!E60)&lt;ABS(INDEX('Picks Detail'!F60:Q60,1,D46)-'Picks Detail'!E60),"W",IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A46)-'Picks Detail'!E60)&gt;ABS(INDEX('Picks Detail'!F60:Q60,1,D46)-'Picks Detail'!E60),"L","T")),"T"))))</f>
@@ -30299,17 +30326,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -33132,17 +33159,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -35965,19 +35992,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -36032,7 +36059,7 @@
       </c>
       <c r="E3">
         <f>Helper!E2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <f>Helper!F2</f>
@@ -36048,7 +36075,7 @@
       </c>
       <c r="I3">
         <f>Helper!I2</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J3">
         <f>Helper!J2</f>
@@ -36122,7 +36149,7 @@
       </c>
       <c r="E5">
         <f>Helper!E4</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <f>Helper!F4</f>
@@ -36138,7 +36165,7 @@
       </c>
       <c r="I5">
         <f>Helper!I4</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J5">
         <f>Helper!J4</f>
@@ -37867,7 +37894,7 @@
       </c>
       <c r="C57">
         <f>Helper!I2</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D57">
         <f>Helper!R2</f>
@@ -37879,11 +37906,11 @@
       </c>
       <c r="F57">
         <f>Helper!AE2</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G57">
         <f>Helper!K2</f>
-        <v>19.0001</v>
+        <v>20.0001</v>
       </c>
       <c r="H57">
         <f>Helper!T2</f>
@@ -37933,7 +37960,7 @@
       </c>
       <c r="C59">
         <f>Helper!I4</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D59">
         <f>Helper!R4</f>
@@ -37945,11 +37972,11 @@
       </c>
       <c r="F59">
         <f>Helper!AE4</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G59">
         <f>Helper!K4</f>
-        <v>20.000299999999999</v>
+        <v>21.000299999999999</v>
       </c>
       <c r="H59">
         <f>Helper!T4</f>
@@ -38964,7 +38991,7 @@
       </c>
       <c r="I40">
         <f>Helper!AE2</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J40" t="b">
         <f t="shared" ref="J40:J51" si="1">OR(H40=$E$5,H40=$E$6,H40=$E$7,H40=$E$8,H40=$E$9)</f>
@@ -38972,7 +38999,7 @@
       </c>
       <c r="K40">
         <f>IF(J40,-1,I40+0.00001)</f>
-        <v>19.00001</v>
+        <v>20.00001</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39000,7 +39027,7 @@
       </c>
       <c r="I42">
         <f>Helper!AE4</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J42" t="b">
         <f t="shared" si="1"/>
@@ -39008,7 +39035,7 @@
       </c>
       <c r="K42">
         <f>IF(J42,-1,I42+0.00003)</f>
-        <v>20.000029999999999</v>
+        <v>21.000029999999999</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="319" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3156F26F-43EA-4881-9CAA-AE5B07250BA9}"/>
+  <xr:revisionPtr revIDLastSave="524" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39672356-66BB-48EC-AD0B-D993EDFFC30C}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3762" uniqueCount="346">
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -1377,13 +1377,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1665,12 +1665,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="A1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B5" t="str">
         <f>'Playoff Picture'!B17</f>
-        <v>Zach Zarra</v>
+        <v>Jeffrey Loeser</v>
       </c>
       <c r="C5" s="3">
         <v>6</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="B9" t="str">
         <f>'Playoff Picture'!B21</f>
-        <v>Jeffrey Loeser</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="C9" s="3">
         <v>2</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="B14" t="str">
         <f>INDEX($B$5:$B$10,MATCH(LARGE($H$5:$H$10,1),$H$5:$H$10,0))</f>
-        <v>Zach Zarra</v>
+        <v>Jeffrey Loeser</v>
       </c>
       <c r="C14">
         <f>INDEX($C$5:$C$10,MATCH(LARGE($H$5:$H$10,1),$H$5:$H$10,0))</f>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B18" t="str">
         <f>INDEX($B$5:$B$10,MATCH(LARGE($H$5:$H$10,5),$H$5:$H$10,0))</f>
-        <v>Jeffrey Loeser</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="C18">
         <f>INDEX($C$5:$C$10,MATCH(LARGE($H$5:$H$10,5),$H$5:$H$10,0))</f>
@@ -2281,7 +2281,7 @@
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>'Playoff Wild Card'!B14</f>
-        <v>Zach Zarra</v>
+        <v>Jeffrey Loeser</v>
       </c>
       <c r="B6">
         <f>'Playoff Wild Card'!C14</f>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="B13" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>Zach Zarra</v>
+        <v>Jeffrey Loeser</v>
       </c>
       <c r="C13">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
@@ -2632,7 +2632,7 @@
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>A6</f>
-        <v>Zach Zarra</v>
+        <v>Jeffrey Loeser</v>
       </c>
       <c r="B22" s="3">
         <v>0</v>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="E2">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H36,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G36,0)</f>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F2">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H51,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G51,0)</f>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I13" si="0">SUM(C2:H2)</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J2">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F6="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F21="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F36="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F51="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F66="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F81="W"),1,0)</f>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="K2">
         <f>I2+0.0001</f>
-        <v>20.0001</v>
+        <v>30.0001</v>
       </c>
       <c r="L2">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H6,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G6,0)</f>
@@ -2957,11 +2957,11 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE13" si="2">I2+R2+AC2</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AF2">
         <f>AE2+0.0001</f>
-        <v>20.0001</v>
+        <v>30.0001</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="E3">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H37,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G37,0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H52,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G52,0)</f>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="I3">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J3">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F7="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F22="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F37="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F52="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F67="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F82="W"),1,0)</f>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="K3">
         <f>I3+0.0002</f>
-        <v>21.0002</v>
+        <v>29.0002</v>
       </c>
       <c r="L3">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H7,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G7,0)</f>
@@ -3086,11 +3086,11 @@
       </c>
       <c r="AE3">
         <f t="shared" si="2"/>
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AF3">
         <f>AE3+0.0002</f>
-        <v>21.0002</v>
+        <v>29.0002</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E4">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H38,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G38,0)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H53,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G53,0)</f>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J4">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F8="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F23="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F38="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F53="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F68="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F83="W"),1,0)</f>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="K4">
         <f>I4+0.0003</f>
-        <v>21.000299999999999</v>
+        <v>28.000299999999999</v>
       </c>
       <c r="L4">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H8,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G8,0)</f>
@@ -3215,11 +3215,11 @@
       </c>
       <c r="AE4">
         <f t="shared" si="2"/>
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AF4">
         <f>AE4+0.0003</f>
-        <v>21.000299999999999</v>
+        <v>28.000299999999999</v>
       </c>
     </row>
     <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="E6">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H40,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G40,0)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F6">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H55,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G55,0)</f>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J6">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F10="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F25="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F40="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F55="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F70="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F85="W"),1,0)</f>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="K6">
         <f>I6+0.0005</f>
-        <v>22.000499999999999</v>
+        <v>31.000499999999999</v>
       </c>
       <c r="L6">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H10,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G10,0)</f>
@@ -3473,11 +3473,11 @@
       </c>
       <c r="AE6">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="AF6">
         <f>AE6+0.0005</f>
-        <v>22.000499999999999</v>
+        <v>31.000499999999999</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="E7">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H41,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G41,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F7">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H56,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G56,0)</f>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J7">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F11="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F26="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F41="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F56="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F71="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F86="W"),1,0)</f>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="K7">
         <f>I7+0.0006</f>
-        <v>20.000599999999999</v>
+        <v>26.000599999999999</v>
       </c>
       <c r="L7">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H11,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G11,0)</f>
@@ -3602,11 +3602,11 @@
       </c>
       <c r="AE7">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AF7">
         <f>AE7+0.0006</f>
-        <v>20.000599999999999</v>
+        <v>26.000599999999999</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="E8">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H42,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G42,0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F8">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H57,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G57,0)</f>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J8">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F12="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F27="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F42="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F57="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F72="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F87="W"),1,0)</f>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="K8">
         <f>I8+0.0007</f>
-        <v>19.000699999999998</v>
+        <v>27.000699999999998</v>
       </c>
       <c r="L8">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H12,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G12,0)</f>
@@ -3731,11 +3731,11 @@
       </c>
       <c r="AE8">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="AF8">
         <f>AE8+0.0007</f>
-        <v>19.000699999999998</v>
+        <v>27.000699999999998</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="E9">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H43,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G43,0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F9">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H58,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G58,0)</f>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J9">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F13="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F28="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F43="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F58="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F73="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F88="W"),1,0)</f>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="K9">
         <f>I9+0.0008</f>
-        <v>12.0008</v>
+        <v>19.000800000000002</v>
       </c>
       <c r="L9">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H13,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G13,0)</f>
@@ -3860,11 +3860,11 @@
       </c>
       <c r="AE9">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AF9">
         <f>AE9+0.0008</f>
-        <v>12.0008</v>
+        <v>19.000800000000002</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="E10">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H44,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G44,0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F10">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H59,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G59,0)</f>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="I10">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J10">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F14="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F29="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F44="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F59="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F74="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F89="W"),1,0)</f>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="K10">
         <f>I10+0.0009</f>
-        <v>15.0009</v>
+        <v>23.000900000000001</v>
       </c>
       <c r="L10">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H14,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G14,0)</f>
@@ -3989,11 +3989,11 @@
       </c>
       <c r="AE10">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AF10">
         <f>AE10+0.0009</f>
-        <v>15.0009</v>
+        <v>23.000900000000001</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="E11">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H45,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G45,0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F11">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H60,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G60,0)</f>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="I11">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J11">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F15="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F30="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F45="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F60="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F75="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F90="W"),1,0)</f>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="K11">
         <f>I11+0.001</f>
-        <v>31.001000000000001</v>
+        <v>36.000999999999998</v>
       </c>
       <c r="L11">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H15,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G15,0)</f>
@@ -4118,11 +4118,11 @@
       </c>
       <c r="AE11">
         <f t="shared" si="2"/>
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="AF11">
         <f>AE11+0.001</f>
-        <v>31.001000000000001</v>
+        <v>36.000999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="E12">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H46,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G46,0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F12">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H61,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G61,0)</f>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="I12">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J12">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F16="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F31="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F46="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F61="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F76="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F91="W"),1,0)</f>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="K12">
         <f>I12+0.0011</f>
-        <v>28.001100000000001</v>
+        <v>36.001100000000001</v>
       </c>
       <c r="L12">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H16,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G16,0)</f>
@@ -4247,11 +4247,11 @@
       </c>
       <c r="AE12">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AF12">
         <f>AE12+0.0011</f>
-        <v>28.001100000000001</v>
+        <v>36.001100000000001</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="E13">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H47,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G47,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F13">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H62,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G62,0)</f>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="I13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J13">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F17="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F32="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F47="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F62="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F77="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F92="W"),1,0)</f>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="K13">
         <f>I13+0.0012</f>
-        <v>19.001200000000001</v>
+        <v>25.001200000000001</v>
       </c>
       <c r="L13">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H17,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G17,0)</f>
@@ -4376,11 +4376,11 @@
       </c>
       <c r="AE13">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AF13">
         <f>AE13+0.0012</f>
-        <v>19.001200000000001</v>
+        <v>25.001200000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4402,14 +4402,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -5354,14 +5354,14 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
@@ -6306,14 +6306,14 @@
       </c>
     </row>
     <row r="111" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="23" t="s">
+      <c r="A111" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B111" s="23"/>
-      <c r="C111" s="23"/>
-      <c r="D111" s="23"/>
-      <c r="E111" s="23"/>
-      <c r="F111" s="23"/>
+      <c r="B111" s="22"/>
+      <c r="C111" s="22"/>
+      <c r="D111" s="22"/>
+      <c r="E111" s="22"/>
+      <c r="F111" s="22"/>
     </row>
     <row r="112" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
@@ -7285,67 +7285,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8313,25 +8313,25 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="26"/>
-      <c r="P23" s="26"/>
-      <c r="Q23" s="26"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="24"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="24"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -9299,25 +9299,25 @@
       </c>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="26" t="s">
+      <c r="A42" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="26"/>
-      <c r="L42" s="26"/>
-      <c r="M42" s="26"/>
-      <c r="N42" s="26"/>
-      <c r="O42" s="26"/>
-      <c r="P42" s="26"/>
-      <c r="Q42" s="26"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="24"/>
+      <c r="N42" s="24"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="24"/>
+      <c r="Q42" s="24"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -9435,20 +9435,42 @@
       </c>
       <c r="E45" s="9" t="str">
         <f>'NFL Schedule'!J42</f>
-        <v/>
-      </c>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
+        <v>BUF</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>67</v>
+      </c>
       <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
-      <c r="N45" s="10"/>
-      <c r="O45" s="10"/>
-      <c r="P45" s="10"/>
-      <c r="Q45" s="10"/>
+      <c r="J45" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K45" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L45" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="M45" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="N45" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="O45" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="P45" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q45" s="10" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7">
@@ -9465,20 +9487,42 @@
       </c>
       <c r="E46" s="9" t="str">
         <f>'NFL Schedule'!J43</f>
-        <v/>
-      </c>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
+        <v>CLE</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>62</v>
+      </c>
       <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
-      <c r="N46" s="10"/>
-      <c r="O46" s="10"/>
-      <c r="P46" s="10"/>
-      <c r="Q46" s="10"/>
+      <c r="J46" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="K46" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="L46" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="M46" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="N46" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="O46" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="P46" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q46" s="10" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7">
@@ -9495,20 +9539,42 @@
       </c>
       <c r="E47" s="9" t="str">
         <f>'NFL Schedule'!J44</f>
-        <v/>
-      </c>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
+        <v>DET</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>66</v>
+      </c>
       <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10"/>
-      <c r="N47" s="10"/>
-      <c r="O47" s="10"/>
-      <c r="P47" s="10"/>
-      <c r="Q47" s="10"/>
+      <c r="J47" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K47" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="L47" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="M47" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="N47" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="O47" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="P47" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q47" s="10" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7">
@@ -9525,20 +9591,42 @@
       </c>
       <c r="E48" s="9" t="str">
         <f>'NFL Schedule'!J45</f>
-        <v/>
-      </c>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
+        <v>IND</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>70</v>
+      </c>
       <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10"/>
-      <c r="M48" s="10"/>
-      <c r="N48" s="10"/>
-      <c r="O48" s="10"/>
-      <c r="P48" s="10"/>
-      <c r="Q48" s="10"/>
+      <c r="J48" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K48" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="L48" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="M48" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="N48" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="O48" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="P48" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q48" s="10" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="49" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7">
@@ -9555,20 +9643,42 @@
       </c>
       <c r="E49" s="9" t="str">
         <f>'NFL Schedule'!J46</f>
-        <v/>
-      </c>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
+        <v>KC</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>88</v>
+      </c>
       <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="10"/>
-      <c r="M49" s="10"/>
-      <c r="N49" s="10"/>
-      <c r="O49" s="10"/>
-      <c r="P49" s="10"/>
-      <c r="Q49" s="10"/>
+      <c r="J49" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="K49" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="L49" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="M49" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="N49" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="O49" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="P49" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q49" s="10" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="50" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7">
@@ -9585,20 +9695,42 @@
       </c>
       <c r="E50" s="9" t="str">
         <f>'NFL Schedule'!J47</f>
-        <v/>
-      </c>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
+        <v>NYG</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="10"/>
-      <c r="M50" s="10"/>
-      <c r="N50" s="10"/>
-      <c r="O50" s="10"/>
-      <c r="P50" s="10"/>
-      <c r="Q50" s="10"/>
+      <c r="J50" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="K50" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="L50" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="M50" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="N50" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="O50" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="P50" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q50" s="10" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="51" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7">
@@ -9615,20 +9747,42 @@
       </c>
       <c r="E51" s="9" t="str">
         <f>'NFL Schedule'!J48</f>
-        <v/>
-      </c>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
+        <v>PIT</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>64</v>
+      </c>
       <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
-      <c r="N51" s="10"/>
-      <c r="O51" s="10"/>
-      <c r="P51" s="10"/>
-      <c r="Q51" s="10"/>
+      <c r="J51" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K51" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="L51" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="M51" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="N51" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="O51" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="P51" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q51" s="10" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="52" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="7">
@@ -9645,20 +9799,42 @@
       </c>
       <c r="E52" s="9" t="str">
         <f>'NFL Schedule'!J49</f>
-        <v/>
-      </c>
-      <c r="F52" s="10"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
+        <v>WAS</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H52" s="10" t="s">
+        <v>58</v>
+      </c>
       <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
-      <c r="K52" s="10"/>
-      <c r="L52" s="10"/>
-      <c r="M52" s="10"/>
-      <c r="N52" s="10"/>
-      <c r="O52" s="10"/>
-      <c r="P52" s="10"/>
-      <c r="Q52" s="10"/>
+      <c r="J52" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="K52" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="L52" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="M52" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="N52" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O52" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="P52" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q52" s="10" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="53" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="7">
@@ -9675,20 +9851,42 @@
       </c>
       <c r="E53" s="9" t="str">
         <f>'NFL Schedule'!J50</f>
-        <v/>
-      </c>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
+        <v>JAX</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
-      <c r="K53" s="10"/>
-      <c r="L53" s="10"/>
-      <c r="M53" s="10"/>
-      <c r="N53" s="10"/>
-      <c r="O53" s="10"/>
-      <c r="P53" s="10"/>
-      <c r="Q53" s="10"/>
+      <c r="J53" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="K53" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="L53" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M53" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="N53" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="O53" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P53" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q53" s="10" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="54" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="7">
@@ -9705,20 +9903,42 @@
       </c>
       <c r="E54" s="9" t="str">
         <f>'NFL Schedule'!J51</f>
-        <v/>
-      </c>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
+        <v>ARI</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H54" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
-      <c r="N54" s="10"/>
-      <c r="O54" s="10"/>
-      <c r="P54" s="10"/>
-      <c r="Q54" s="10"/>
+      <c r="J54" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="K54" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="L54" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="M54" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="N54" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="O54" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="P54" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q54" s="10" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="55" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="7">
@@ -9735,20 +9955,42 @@
       </c>
       <c r="E55" s="9" t="str">
         <f>'NFL Schedule'!J52</f>
-        <v/>
-      </c>
-      <c r="F55" s="10"/>
-      <c r="G55" s="10"/>
-      <c r="H55" s="10"/>
+        <v>MIN</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>82</v>
+      </c>
       <c r="I55" s="10"/>
-      <c r="J55" s="10"/>
-      <c r="K55" s="10"/>
-      <c r="L55" s="10"/>
-      <c r="M55" s="10"/>
-      <c r="N55" s="10"/>
-      <c r="O55" s="10"/>
-      <c r="P55" s="10"/>
-      <c r="Q55" s="10"/>
+      <c r="J55" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="K55" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="L55" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="M55" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="N55" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="O55" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="P55" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q55" s="10" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="56" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="7">
@@ -9765,20 +10007,42 @@
       </c>
       <c r="E56" s="9" t="str">
         <f>'NFL Schedule'!J53</f>
-        <v/>
-      </c>
-      <c r="F56" s="10"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="10"/>
+        <v>BAL</v>
+      </c>
+      <c r="F56" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H56" s="10" t="s">
+        <v>85</v>
+      </c>
       <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
-      <c r="K56" s="10"/>
-      <c r="L56" s="10"/>
-      <c r="M56" s="10"/>
-      <c r="N56" s="10"/>
-      <c r="O56" s="10"/>
-      <c r="P56" s="10"/>
-      <c r="Q56" s="10"/>
+      <c r="J56" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K56" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="L56" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="M56" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="N56" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="O56" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="P56" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q56" s="10" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="57" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="7">
@@ -9795,20 +10059,42 @@
       </c>
       <c r="E57" s="9" t="str">
         <f>'NFL Schedule'!J54</f>
-        <v/>
-      </c>
-      <c r="F57" s="10"/>
-      <c r="G57" s="10"/>
-      <c r="H57" s="10"/>
+        <v>LV</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>80</v>
+      </c>
       <c r="I57" s="10"/>
-      <c r="J57" s="10"/>
-      <c r="K57" s="10"/>
-      <c r="L57" s="10"/>
-      <c r="M57" s="10"/>
-      <c r="N57" s="10"/>
-      <c r="O57" s="10"/>
-      <c r="P57" s="10"/>
-      <c r="Q57" s="10"/>
+      <c r="J57" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="K57" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="L57" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="M57" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="N57" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="O57" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="P57" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q57" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="58" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="7">
@@ -9825,20 +10111,42 @@
       </c>
       <c r="E58" s="9" t="str">
         <f>'NFL Schedule'!J55</f>
-        <v/>
-      </c>
-      <c r="F58" s="10"/>
-      <c r="G58" s="10"/>
-      <c r="H58" s="10"/>
+        <v>DEN</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>60</v>
+      </c>
       <c r="I58" s="10"/>
-      <c r="J58" s="10"/>
-      <c r="K58" s="10"/>
-      <c r="L58" s="10"/>
-      <c r="M58" s="10"/>
-      <c r="N58" s="10"/>
-      <c r="O58" s="10"/>
-      <c r="P58" s="10"/>
-      <c r="Q58" s="10"/>
+      <c r="J58" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="K58" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="L58" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="M58" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="N58" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="O58" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="P58" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q58" s="10" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="59" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="7">
@@ -9895,25 +10203,25 @@
       <c r="Q60" s="14"/>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="26" t="s">
+      <c r="A61" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="26"/>
-      <c r="C61" s="26"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="26"/>
-      <c r="F61" s="26"/>
-      <c r="G61" s="26"/>
-      <c r="H61" s="26"/>
-      <c r="I61" s="26"/>
-      <c r="J61" s="26"/>
-      <c r="K61" s="26"/>
-      <c r="L61" s="26"/>
-      <c r="M61" s="26"/>
-      <c r="N61" s="26"/>
-      <c r="O61" s="26"/>
-      <c r="P61" s="26"/>
-      <c r="Q61" s="26"/>
+      <c r="B61" s="24"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="24"/>
+      <c r="J61" s="24"/>
+      <c r="K61" s="24"/>
+      <c r="L61" s="24"/>
+      <c r="M61" s="24"/>
+      <c r="N61" s="24"/>
+      <c r="O61" s="24"/>
+      <c r="P61" s="24"/>
+      <c r="Q61" s="24"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -10473,25 +10781,25 @@
       <c r="Q79" s="14"/>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="26" t="s">
+      <c r="A80" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="26"/>
-      <c r="C80" s="26"/>
-      <c r="D80" s="26"/>
-      <c r="E80" s="26"/>
-      <c r="F80" s="26"/>
-      <c r="G80" s="26"/>
-      <c r="H80" s="26"/>
-      <c r="I80" s="26"/>
-      <c r="J80" s="26"/>
-      <c r="K80" s="26"/>
-      <c r="L80" s="26"/>
-      <c r="M80" s="26"/>
-      <c r="N80" s="26"/>
-      <c r="O80" s="26"/>
-      <c r="P80" s="26"/>
-      <c r="Q80" s="26"/>
+      <c r="B80" s="24"/>
+      <c r="C80" s="24"/>
+      <c r="D80" s="24"/>
+      <c r="E80" s="24"/>
+      <c r="F80" s="24"/>
+      <c r="G80" s="24"/>
+      <c r="H80" s="24"/>
+      <c r="I80" s="24"/>
+      <c r="J80" s="24"/>
+      <c r="K80" s="24"/>
+      <c r="L80" s="24"/>
+      <c r="M80" s="24"/>
+      <c r="N80" s="24"/>
+      <c r="O80" s="24"/>
+      <c r="P80" s="24"/>
+      <c r="Q80" s="24"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -11021,25 +11329,25 @@
       <c r="Q97" s="14"/>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="26" t="s">
+      <c r="A98" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="26"/>
-      <c r="C98" s="26"/>
-      <c r="D98" s="26"/>
-      <c r="E98" s="26"/>
-      <c r="F98" s="26"/>
-      <c r="G98" s="26"/>
-      <c r="H98" s="26"/>
-      <c r="I98" s="26"/>
-      <c r="J98" s="26"/>
-      <c r="K98" s="26"/>
-      <c r="L98" s="26"/>
-      <c r="M98" s="26"/>
-      <c r="N98" s="26"/>
-      <c r="O98" s="26"/>
-      <c r="P98" s="26"/>
-      <c r="Q98" s="26"/>
+      <c r="B98" s="24"/>
+      <c r="C98" s="24"/>
+      <c r="D98" s="24"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24"/>
+      <c r="H98" s="24"/>
+      <c r="I98" s="24"/>
+      <c r="J98" s="24"/>
+      <c r="K98" s="24"/>
+      <c r="L98" s="24"/>
+      <c r="M98" s="24"/>
+      <c r="N98" s="24"/>
+      <c r="O98" s="24"/>
+      <c r="P98" s="24"/>
+      <c r="Q98" s="24"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -11539,25 +11847,25 @@
       <c r="Q114" s="14"/>
     </row>
     <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="26" t="s">
+      <c r="A115" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="26"/>
-      <c r="C115" s="26"/>
-      <c r="D115" s="26"/>
-      <c r="E115" s="26"/>
-      <c r="F115" s="26"/>
-      <c r="G115" s="26"/>
-      <c r="H115" s="26"/>
-      <c r="I115" s="26"/>
-      <c r="J115" s="26"/>
-      <c r="K115" s="26"/>
-      <c r="L115" s="26"/>
-      <c r="M115" s="26"/>
-      <c r="N115" s="26"/>
-      <c r="O115" s="26"/>
-      <c r="P115" s="26"/>
-      <c r="Q115" s="26"/>
+      <c r="B115" s="24"/>
+      <c r="C115" s="24"/>
+      <c r="D115" s="24"/>
+      <c r="E115" s="24"/>
+      <c r="F115" s="24"/>
+      <c r="G115" s="24"/>
+      <c r="H115" s="24"/>
+      <c r="I115" s="24"/>
+      <c r="J115" s="24"/>
+      <c r="K115" s="24"/>
+      <c r="L115" s="24"/>
+      <c r="M115" s="24"/>
+      <c r="N115" s="24"/>
+      <c r="O115" s="24"/>
+      <c r="P115" s="24"/>
+      <c r="Q115" s="24"/>
     </row>
     <row r="116" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -12057,25 +12365,25 @@
       <c r="Q131" s="14"/>
     </row>
     <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="26" t="s">
+      <c r="A132" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="B132" s="26"/>
-      <c r="C132" s="26"/>
-      <c r="D132" s="26"/>
-      <c r="E132" s="26"/>
-      <c r="F132" s="26"/>
-      <c r="G132" s="26"/>
-      <c r="H132" s="26"/>
-      <c r="I132" s="26"/>
-      <c r="J132" s="26"/>
-      <c r="K132" s="26"/>
-      <c r="L132" s="26"/>
-      <c r="M132" s="26"/>
-      <c r="N132" s="26"/>
-      <c r="O132" s="26"/>
-      <c r="P132" s="26"/>
-      <c r="Q132" s="26"/>
+      <c r="B132" s="24"/>
+      <c r="C132" s="24"/>
+      <c r="D132" s="24"/>
+      <c r="E132" s="24"/>
+      <c r="F132" s="24"/>
+      <c r="G132" s="24"/>
+      <c r="H132" s="24"/>
+      <c r="I132" s="24"/>
+      <c r="J132" s="24"/>
+      <c r="K132" s="24"/>
+      <c r="L132" s="24"/>
+      <c r="M132" s="24"/>
+      <c r="N132" s="24"/>
+      <c r="O132" s="24"/>
+      <c r="P132" s="24"/>
+      <c r="Q132" s="24"/>
     </row>
     <row r="133" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -12575,25 +12883,25 @@
       <c r="Q148" s="14"/>
     </row>
     <row r="149" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="26" t="s">
+      <c r="A149" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="B149" s="26"/>
-      <c r="C149" s="26"/>
-      <c r="D149" s="26"/>
-      <c r="E149" s="26"/>
-      <c r="F149" s="26"/>
-      <c r="G149" s="26"/>
-      <c r="H149" s="26"/>
-      <c r="I149" s="26"/>
-      <c r="J149" s="26"/>
-      <c r="K149" s="26"/>
-      <c r="L149" s="26"/>
-      <c r="M149" s="26"/>
-      <c r="N149" s="26"/>
-      <c r="O149" s="26"/>
-      <c r="P149" s="26"/>
-      <c r="Q149" s="26"/>
+      <c r="B149" s="24"/>
+      <c r="C149" s="24"/>
+      <c r="D149" s="24"/>
+      <c r="E149" s="24"/>
+      <c r="F149" s="24"/>
+      <c r="G149" s="24"/>
+      <c r="H149" s="24"/>
+      <c r="I149" s="24"/>
+      <c r="J149" s="24"/>
+      <c r="K149" s="24"/>
+      <c r="L149" s="24"/>
+      <c r="M149" s="24"/>
+      <c r="N149" s="24"/>
+      <c r="O149" s="24"/>
+      <c r="P149" s="24"/>
+      <c r="Q149" s="24"/>
     </row>
     <row r="150" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -13123,25 +13431,25 @@
       <c r="Q166" s="14"/>
     </row>
     <row r="167" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="26" t="s">
+      <c r="A167" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="B167" s="26"/>
-      <c r="C167" s="26"/>
-      <c r="D167" s="26"/>
-      <c r="E167" s="26"/>
-      <c r="F167" s="26"/>
-      <c r="G167" s="26"/>
-      <c r="H167" s="26"/>
-      <c r="I167" s="26"/>
-      <c r="J167" s="26"/>
-      <c r="K167" s="26"/>
-      <c r="L167" s="26"/>
-      <c r="M167" s="26"/>
-      <c r="N167" s="26"/>
-      <c r="O167" s="26"/>
-      <c r="P167" s="26"/>
-      <c r="Q167" s="26"/>
+      <c r="B167" s="24"/>
+      <c r="C167" s="24"/>
+      <c r="D167" s="24"/>
+      <c r="E167" s="24"/>
+      <c r="F167" s="24"/>
+      <c r="G167" s="24"/>
+      <c r="H167" s="24"/>
+      <c r="I167" s="24"/>
+      <c r="J167" s="24"/>
+      <c r="K167" s="24"/>
+      <c r="L167" s="24"/>
+      <c r="M167" s="24"/>
+      <c r="N167" s="24"/>
+      <c r="O167" s="24"/>
+      <c r="P167" s="24"/>
+      <c r="Q167" s="24"/>
     </row>
     <row r="168" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -13641,25 +13949,25 @@
       <c r="Q183" s="14"/>
     </row>
     <row r="184" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="26" t="s">
+      <c r="A184" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="B184" s="26"/>
-      <c r="C184" s="26"/>
-      <c r="D184" s="26"/>
-      <c r="E184" s="26"/>
-      <c r="F184" s="26"/>
-      <c r="G184" s="26"/>
-      <c r="H184" s="26"/>
-      <c r="I184" s="26"/>
-      <c r="J184" s="26"/>
-      <c r="K184" s="26"/>
-      <c r="L184" s="26"/>
-      <c r="M184" s="26"/>
-      <c r="N184" s="26"/>
-      <c r="O184" s="26"/>
-      <c r="P184" s="26"/>
-      <c r="Q184" s="26"/>
+      <c r="B184" s="24"/>
+      <c r="C184" s="24"/>
+      <c r="D184" s="24"/>
+      <c r="E184" s="24"/>
+      <c r="F184" s="24"/>
+      <c r="G184" s="24"/>
+      <c r="H184" s="24"/>
+      <c r="I184" s="24"/>
+      <c r="J184" s="24"/>
+      <c r="K184" s="24"/>
+      <c r="L184" s="24"/>
+      <c r="M184" s="24"/>
+      <c r="N184" s="24"/>
+      <c r="O184" s="24"/>
+      <c r="P184" s="24"/>
+      <c r="Q184" s="24"/>
     </row>
     <row r="185" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -14129,25 +14437,25 @@
       <c r="Q199" s="14"/>
     </row>
     <row r="200" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="26" t="s">
+      <c r="A200" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="B200" s="26"/>
-      <c r="C200" s="26"/>
-      <c r="D200" s="26"/>
-      <c r="E200" s="26"/>
-      <c r="F200" s="26"/>
-      <c r="G200" s="26"/>
-      <c r="H200" s="26"/>
-      <c r="I200" s="26"/>
-      <c r="J200" s="26"/>
-      <c r="K200" s="26"/>
-      <c r="L200" s="26"/>
-      <c r="M200" s="26"/>
-      <c r="N200" s="26"/>
-      <c r="O200" s="26"/>
-      <c r="P200" s="26"/>
-      <c r="Q200" s="26"/>
+      <c r="B200" s="24"/>
+      <c r="C200" s="24"/>
+      <c r="D200" s="24"/>
+      <c r="E200" s="24"/>
+      <c r="F200" s="24"/>
+      <c r="G200" s="24"/>
+      <c r="H200" s="24"/>
+      <c r="I200" s="24"/>
+      <c r="J200" s="24"/>
+      <c r="K200" s="24"/>
+      <c r="L200" s="24"/>
+      <c r="M200" s="24"/>
+      <c r="N200" s="24"/>
+      <c r="O200" s="24"/>
+      <c r="P200" s="24"/>
+      <c r="Q200" s="24"/>
     </row>
     <row r="201" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -14707,25 +15015,25 @@
       <c r="Q218" s="14"/>
     </row>
     <row r="219" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="26" t="s">
+      <c r="A219" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="B219" s="26"/>
-      <c r="C219" s="26"/>
-      <c r="D219" s="26"/>
-      <c r="E219" s="26"/>
-      <c r="F219" s="26"/>
-      <c r="G219" s="26"/>
-      <c r="H219" s="26"/>
-      <c r="I219" s="26"/>
-      <c r="J219" s="26"/>
-      <c r="K219" s="26"/>
-      <c r="L219" s="26"/>
-      <c r="M219" s="26"/>
-      <c r="N219" s="26"/>
-      <c r="O219" s="26"/>
-      <c r="P219" s="26"/>
-      <c r="Q219" s="26"/>
+      <c r="B219" s="24"/>
+      <c r="C219" s="24"/>
+      <c r="D219" s="24"/>
+      <c r="E219" s="24"/>
+      <c r="F219" s="24"/>
+      <c r="G219" s="24"/>
+      <c r="H219" s="24"/>
+      <c r="I219" s="24"/>
+      <c r="J219" s="24"/>
+      <c r="K219" s="24"/>
+      <c r="L219" s="24"/>
+      <c r="M219" s="24"/>
+      <c r="N219" s="24"/>
+      <c r="O219" s="24"/>
+      <c r="P219" s="24"/>
+      <c r="Q219" s="24"/>
     </row>
     <row r="220" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -15225,25 +15533,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="26" t="s">
+      <c r="A236" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B236" s="26"/>
-      <c r="C236" s="26"/>
-      <c r="D236" s="26"/>
-      <c r="E236" s="26"/>
-      <c r="F236" s="26"/>
-      <c r="G236" s="26"/>
-      <c r="H236" s="26"/>
-      <c r="I236" s="26"/>
-      <c r="J236" s="26"/>
-      <c r="K236" s="26"/>
-      <c r="L236" s="26"/>
-      <c r="M236" s="26"/>
-      <c r="N236" s="26"/>
-      <c r="O236" s="26"/>
-      <c r="P236" s="26"/>
-      <c r="Q236" s="26"/>
+      <c r="B236" s="24"/>
+      <c r="C236" s="24"/>
+      <c r="D236" s="24"/>
+      <c r="E236" s="24"/>
+      <c r="F236" s="24"/>
+      <c r="G236" s="24"/>
+      <c r="H236" s="24"/>
+      <c r="I236" s="24"/>
+      <c r="J236" s="24"/>
+      <c r="K236" s="24"/>
+      <c r="L236" s="24"/>
+      <c r="M236" s="24"/>
+      <c r="N236" s="24"/>
+      <c r="O236" s="24"/>
+      <c r="P236" s="24"/>
+      <c r="Q236" s="24"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -15773,25 +16081,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="26" t="s">
+      <c r="A254" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="B254" s="26"/>
-      <c r="C254" s="26"/>
-      <c r="D254" s="26"/>
-      <c r="E254" s="26"/>
-      <c r="F254" s="26"/>
-      <c r="G254" s="26"/>
-      <c r="H254" s="26"/>
-      <c r="I254" s="26"/>
-      <c r="J254" s="26"/>
-      <c r="K254" s="26"/>
-      <c r="L254" s="26"/>
-      <c r="M254" s="26"/>
-      <c r="N254" s="26"/>
-      <c r="O254" s="26"/>
-      <c r="P254" s="26"/>
-      <c r="Q254" s="26"/>
+      <c r="B254" s="24"/>
+      <c r="C254" s="24"/>
+      <c r="D254" s="24"/>
+      <c r="E254" s="24"/>
+      <c r="F254" s="24"/>
+      <c r="G254" s="24"/>
+      <c r="H254" s="24"/>
+      <c r="I254" s="24"/>
+      <c r="J254" s="24"/>
+      <c r="K254" s="24"/>
+      <c r="L254" s="24"/>
+      <c r="M254" s="24"/>
+      <c r="N254" s="24"/>
+      <c r="O254" s="24"/>
+      <c r="P254" s="24"/>
+      <c r="Q254" s="24"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -16351,25 +16659,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="26" t="s">
+      <c r="A273" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="B273" s="26"/>
-      <c r="C273" s="26"/>
-      <c r="D273" s="26"/>
-      <c r="E273" s="26"/>
-      <c r="F273" s="26"/>
-      <c r="G273" s="26"/>
-      <c r="H273" s="26"/>
-      <c r="I273" s="26"/>
-      <c r="J273" s="26"/>
-      <c r="K273" s="26"/>
-      <c r="L273" s="26"/>
-      <c r="M273" s="26"/>
-      <c r="N273" s="26"/>
-      <c r="O273" s="26"/>
-      <c r="P273" s="26"/>
-      <c r="Q273" s="26"/>
+      <c r="B273" s="24"/>
+      <c r="C273" s="24"/>
+      <c r="D273" s="24"/>
+      <c r="E273" s="24"/>
+      <c r="F273" s="24"/>
+      <c r="G273" s="24"/>
+      <c r="H273" s="24"/>
+      <c r="I273" s="24"/>
+      <c r="J273" s="24"/>
+      <c r="K273" s="24"/>
+      <c r="L273" s="24"/>
+      <c r="M273" s="24"/>
+      <c r="N273" s="24"/>
+      <c r="O273" s="24"/>
+      <c r="P273" s="24"/>
+      <c r="Q273" s="24"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -16929,25 +17237,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="26" t="s">
+      <c r="A292" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="B292" s="26"/>
-      <c r="C292" s="26"/>
-      <c r="D292" s="26"/>
-      <c r="E292" s="26"/>
-      <c r="F292" s="26"/>
-      <c r="G292" s="26"/>
-      <c r="H292" s="26"/>
-      <c r="I292" s="26"/>
-      <c r="J292" s="26"/>
-      <c r="K292" s="26"/>
-      <c r="L292" s="26"/>
-      <c r="M292" s="26"/>
-      <c r="N292" s="26"/>
-      <c r="O292" s="26"/>
-      <c r="P292" s="26"/>
-      <c r="Q292" s="26"/>
+      <c r="B292" s="24"/>
+      <c r="C292" s="24"/>
+      <c r="D292" s="24"/>
+      <c r="E292" s="24"/>
+      <c r="F292" s="24"/>
+      <c r="G292" s="24"/>
+      <c r="H292" s="24"/>
+      <c r="I292" s="24"/>
+      <c r="J292" s="24"/>
+      <c r="K292" s="24"/>
+      <c r="L292" s="24"/>
+      <c r="M292" s="24"/>
+      <c r="N292" s="24"/>
+      <c r="O292" s="24"/>
+      <c r="P292" s="24"/>
+      <c r="Q292" s="24"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -17507,25 +17815,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="26" t="s">
+      <c r="A311" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="B311" s="26"/>
-      <c r="C311" s="26"/>
-      <c r="D311" s="26"/>
-      <c r="E311" s="26"/>
-      <c r="F311" s="26"/>
-      <c r="G311" s="26"/>
-      <c r="H311" s="26"/>
-      <c r="I311" s="26"/>
-      <c r="J311" s="26"/>
-      <c r="K311" s="26"/>
-      <c r="L311" s="26"/>
-      <c r="M311" s="26"/>
-      <c r="N311" s="26"/>
-      <c r="O311" s="26"/>
-      <c r="P311" s="26"/>
-      <c r="Q311" s="26"/>
+      <c r="B311" s="24"/>
+      <c r="C311" s="24"/>
+      <c r="D311" s="24"/>
+      <c r="E311" s="24"/>
+      <c r="F311" s="24"/>
+      <c r="G311" s="24"/>
+      <c r="H311" s="24"/>
+      <c r="I311" s="24"/>
+      <c r="J311" s="24"/>
+      <c r="K311" s="24"/>
+      <c r="L311" s="24"/>
+      <c r="M311" s="24"/>
+      <c r="N311" s="24"/>
+      <c r="O311" s="24"/>
+      <c r="P311" s="24"/>
+      <c r="Q311" s="24"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -18086,26 +18394,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A23:Q23"/>
+    <mergeCell ref="A42:Q42"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="A132:Q132"/>
+    <mergeCell ref="A149:Q149"/>
+    <mergeCell ref="A167:Q167"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A219:Q219"/>
     <mergeCell ref="A236:Q236"/>
     <mergeCell ref="A254:Q254"/>
     <mergeCell ref="A273:Q273"/>
     <mergeCell ref="A292:Q292"/>
     <mergeCell ref="A311:Q311"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A167:Q167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="A23:Q23"/>
-    <mergeCell ref="A42:Q42"/>
   </mergeCells>
   <dataValidations count="268">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or SEA" promptTitle="ATS Pick" prompt="Pick NE or SEA" sqref="F6:Q6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -20458,16 +20766,25 @@
       <c r="D42" t="s">
         <v>78</v>
       </c>
+      <c r="E42">
+        <v>16</v>
+      </c>
       <c r="F42" t="s">
         <v>67</v>
       </c>
+      <c r="G42">
+        <v>24</v>
+      </c>
+      <c r="H42">
+        <v>7.5</v>
+      </c>
       <c r="I42" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>BUF</v>
       </c>
       <c r="J42" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>BUF</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20483,16 +20800,25 @@
       <c r="D43" t="s">
         <v>62</v>
       </c>
+      <c r="E43">
+        <v>18</v>
+      </c>
       <c r="F43" t="s">
         <v>71</v>
       </c>
+      <c r="G43">
+        <v>21</v>
+      </c>
+      <c r="H43">
+        <v>-2.5</v>
+      </c>
       <c r="I43" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>CLE</v>
       </c>
       <c r="J43" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>CLE</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20508,16 +20834,25 @@
       <c r="D44" t="s">
         <v>75</v>
       </c>
+      <c r="E44">
+        <v>24</v>
+      </c>
       <c r="F44" t="s">
         <v>66</v>
       </c>
+      <c r="G44">
+        <v>31</v>
+      </c>
+      <c r="H44">
+        <v>6.5</v>
+      </c>
       <c r="I44" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>DET</v>
       </c>
       <c r="J44" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>DET</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20533,16 +20868,25 @@
       <c r="D45" t="s">
         <v>68</v>
       </c>
+      <c r="E45">
+        <v>17</v>
+      </c>
       <c r="F45" t="s">
         <v>70</v>
       </c>
+      <c r="G45">
+        <v>19</v>
+      </c>
+      <c r="H45">
+        <v>-2.5</v>
+      </c>
       <c r="I45" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>IND</v>
       </c>
       <c r="J45" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>IND</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20558,16 +20902,25 @@
       <c r="D46" t="s">
         <v>88</v>
       </c>
+      <c r="E46">
+        <v>24</v>
+      </c>
       <c r="F46" t="s">
         <v>79</v>
       </c>
+      <c r="G46">
+        <v>10</v>
+      </c>
+      <c r="H46">
+        <v>-11.5</v>
+      </c>
       <c r="I46" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>KC</v>
       </c>
       <c r="J46" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>KC</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20583,16 +20936,25 @@
       <c r="D47" t="s">
         <v>76</v>
       </c>
+      <c r="E47">
+        <v>7</v>
+      </c>
       <c r="F47" t="s">
         <v>86</v>
       </c>
+      <c r="G47">
+        <v>12</v>
+      </c>
+      <c r="H47">
+        <v>3.5</v>
+      </c>
       <c r="I47" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>NYG</v>
       </c>
       <c r="J47" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>NYG</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20608,16 +20970,25 @@
       <c r="D48" t="s">
         <v>64</v>
       </c>
+      <c r="E48">
+        <v>27</v>
+      </c>
       <c r="F48" t="s">
         <v>74</v>
       </c>
+      <c r="G48">
+        <v>30</v>
+      </c>
+      <c r="H48">
+        <v>-3.5</v>
+      </c>
       <c r="I48" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>PIT</v>
       </c>
       <c r="J48" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>PIT</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20633,16 +21004,25 @@
       <c r="D49" t="s">
         <v>58</v>
       </c>
+      <c r="E49">
+        <v>31</v>
+      </c>
       <c r="F49" t="s">
         <v>83</v>
       </c>
+      <c r="G49">
+        <v>33</v>
+      </c>
+      <c r="H49">
+        <v>-7.5</v>
+      </c>
       <c r="I49" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>WAS</v>
       </c>
       <c r="J49" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>WAS</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20658,16 +21038,25 @@
       <c r="D50" t="s">
         <v>57</v>
       </c>
+      <c r="E50">
+        <v>6</v>
+      </c>
       <c r="F50" t="s">
         <v>72</v>
       </c>
+      <c r="G50">
+        <v>35</v>
+      </c>
+      <c r="H50">
+        <v>2.5</v>
+      </c>
       <c r="I50" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>JAX</v>
       </c>
       <c r="J50" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>JAX</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20683,16 +21072,25 @@
       <c r="D51" t="s">
         <v>77</v>
       </c>
+      <c r="E51">
+        <v>30</v>
+      </c>
       <c r="F51" t="s">
         <v>59</v>
       </c>
+      <c r="G51">
+        <v>36</v>
+      </c>
+      <c r="H51">
+        <v>8.5</v>
+      </c>
       <c r="I51" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>SF</v>
       </c>
       <c r="J51" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>ARI</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20708,16 +21106,25 @@
       <c r="D52" t="s">
         <v>82</v>
       </c>
+      <c r="E52">
+        <v>23</v>
+      </c>
       <c r="F52" t="s">
         <v>63</v>
       </c>
+      <c r="G52">
+        <v>16</v>
+      </c>
+      <c r="H52">
+        <v>-1.5</v>
+      </c>
       <c r="I52" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>MIN</v>
       </c>
       <c r="J52" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>MIN</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20733,16 +21140,25 @@
       <c r="D53" t="s">
         <v>69</v>
       </c>
+      <c r="E53">
+        <v>34</v>
+      </c>
       <c r="F53" t="s">
         <v>85</v>
       </c>
+      <c r="G53">
+        <v>31</v>
+      </c>
+      <c r="H53">
+        <v>-2.5</v>
+      </c>
       <c r="I53" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>BAL</v>
       </c>
       <c r="J53" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>BAL</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20758,16 +21174,25 @@
       <c r="D54" t="s">
         <v>80</v>
       </c>
+      <c r="E54">
+        <v>35</v>
+      </c>
       <c r="F54" t="s">
         <v>65</v>
       </c>
+      <c r="G54">
+        <v>27</v>
+      </c>
+      <c r="H54">
+        <v>3.5</v>
+      </c>
       <c r="I54" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>LV</v>
       </c>
       <c r="J54" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>LV</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20783,16 +21208,25 @@
       <c r="D55" t="s">
         <v>60</v>
       </c>
+      <c r="E55">
+        <v>26</v>
+      </c>
       <c r="F55" t="s">
         <v>87</v>
       </c>
+      <c r="G55">
+        <v>30</v>
+      </c>
+      <c r="H55">
+        <v>-2.5</v>
+      </c>
       <c r="I55" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>DEN</v>
       </c>
       <c r="J55" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>DEN</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27493,17 +27927,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -28486,14 +28920,14 @@
       </c>
       <c r="C36" s="3">
         <f>SUMPRODUCT(('Picks Detail'!F44:F59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!F44:F59='Picks Detail'!E44:E59))</f>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D36">
         <v>7</v>
       </c>
       <c r="E36">
         <f>IFERROR(INDEX(C$36:C$47,MATCH(7,A$36:A$47,0)),0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F36" t="str">
         <f>IF(C36=0,"-",IF(C36&gt;E36,"W",IF(C36&lt;E36,"L",IF(AND('Picks Detail'!E60&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,A36)&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,D36)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A36)-'Picks Detail'!E60)&lt;ABS(INDEX('Picks Detail'!F60:Q60,1,D36)-'Picks Detail'!E60),"W",IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A36)-'Picks Detail'!E60)&gt;ABS(INDEX('Picks Detail'!F60:Q60,1,D36)-'Picks Detail'!E60),"L","T")),"T"))))</f>
@@ -28505,11 +28939,11 @@
       </c>
       <c r="H36">
         <f t="shared" ref="H36:H47" si="7">IF(C36="",0,C36)</f>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I36">
         <f t="shared" ref="I36:I47" si="8">G36+H36</f>
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28522,30 +28956,30 @@
       </c>
       <c r="C37" s="3">
         <f>SUMPRODUCT(('Picks Detail'!G44:G59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!G44:G59='Picks Detail'!E44:E59))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D37">
         <v>8</v>
       </c>
       <c r="E37">
         <f>IFERROR(INDEX(C$36:C$47,MATCH(8,A$36:A$47,0)),0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F37" t="str">
         <f>IF(C37=0,"-",IF(C37&gt;E37,"W",IF(C37&lt;E37,"L",IF(AND('Picks Detail'!E60&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,A37)&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,D37)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A37)-'Picks Detail'!E60)&lt;ABS(INDEX('Picks Detail'!F60:Q60,1,D37)-'Picks Detail'!E60),"W",IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A37)-'Picks Detail'!E60)&gt;ABS(INDEX('Picks Detail'!F60:Q60,1,D37)-'Picks Detail'!E60),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G37">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H37">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I37">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28558,30 +28992,30 @@
       </c>
       <c r="C38" s="3">
         <f>SUMPRODUCT(('Picks Detail'!H44:H59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!H44:H59='Picks Detail'!E44:E59))</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D38">
         <v>11</v>
       </c>
       <c r="E38">
         <f>IFERROR(INDEX(C$36:C$47,MATCH(11,A$36:A$47,0)),0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F38" t="str">
         <f>IF(C38=0,"-",IF(C38&gt;E38,"W",IF(C38&lt;E38,"L",IF(AND('Picks Detail'!E60&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,A38)&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,D38)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A38)-'Picks Detail'!E60)&lt;ABS(INDEX('Picks Detail'!F60:Q60,1,D38)-'Picks Detail'!E60),"W",IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A38)-'Picks Detail'!E60)&gt;ABS(INDEX('Picks Detail'!F60:Q60,1,D38)-'Picks Detail'!E60),"L","T")),"T"))))</f>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="G38">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H38">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I38">
         <f t="shared" si="8"/>
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28601,7 +29035,7 @@
       </c>
       <c r="E39">
         <f>IFERROR(INDEX(C$36:C$47,MATCH(12,A$36:A$47,0)),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F39" t="str">
         <f>IF(C39=0,"-",IF(C39&gt;E39,"W",IF(C39&lt;E39,"L",IF(AND('Picks Detail'!E60&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,A39)&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,D39)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A39)-'Picks Detail'!E60)&lt;ABS(INDEX('Picks Detail'!F60:Q60,1,D39)-'Picks Detail'!E60),"W",IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A39)-'Picks Detail'!E60)&gt;ABS(INDEX('Picks Detail'!F60:Q60,1,D39)-'Picks Detail'!E60),"L","T")),"T"))))</f>
@@ -28630,30 +29064,30 @@
       </c>
       <c r="C40" s="3">
         <f>SUMPRODUCT(('Picks Detail'!J44:J59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!J44:J59='Picks Detail'!E44:E59))</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D40">
         <v>9</v>
       </c>
       <c r="E40">
         <f>IFERROR(INDEX(C$36:C$47,MATCH(9,A$36:A$47,0)),0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F40" t="str">
         <f>IF(C40=0,"-",IF(C40&gt;E40,"W",IF(C40&lt;E40,"L",IF(AND('Picks Detail'!E60&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,A40)&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,D40)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A40)-'Picks Detail'!E60)&lt;ABS(INDEX('Picks Detail'!F60:Q60,1,D40)-'Picks Detail'!E60),"W",IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A40)-'Picks Detail'!E60)&gt;ABS(INDEX('Picks Detail'!F60:Q60,1,D40)-'Picks Detail'!E60),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H40">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I40">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28666,30 +29100,30 @@
       </c>
       <c r="C41" s="3">
         <f>SUMPRODUCT(('Picks Detail'!K44:K59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!K44:K59='Picks Detail'!E44:E59))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D41">
         <v>10</v>
       </c>
       <c r="E41">
         <f>IFERROR(INDEX(C$36:C$47,MATCH(10,A$36:A$47,0)),0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F41" t="str">
         <f>IF(C41=0,"-",IF(C41&gt;E41,"W",IF(C41&lt;E41,"L",IF(AND('Picks Detail'!E60&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,A41)&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,D41)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A41)-'Picks Detail'!E60)&lt;ABS(INDEX('Picks Detail'!F60:Q60,1,D41)-'Picks Detail'!E60),"W",IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A41)-'Picks Detail'!E60)&gt;ABS(INDEX('Picks Detail'!F60:Q60,1,D41)-'Picks Detail'!E60),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G41">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H41">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I41">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28702,18 +29136,18 @@
       </c>
       <c r="C42" s="3">
         <f>SUMPRODUCT(('Picks Detail'!L44:L59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!L44:L59='Picks Detail'!E44:E59))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D42">
         <v>1</v>
       </c>
       <c r="E42">
         <f>IFERROR(INDEX(C$36:C$47,MATCH(1,A$36:A$47,0)),0)</f>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F42" t="str">
         <f>IF(C42=0,"-",IF(C42&gt;E42,"W",IF(C42&lt;E42,"L",IF(AND('Picks Detail'!E60&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,A42)&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,D42)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A42)-'Picks Detail'!E60)&lt;ABS(INDEX('Picks Detail'!F60:Q60,1,D42)-'Picks Detail'!E60),"W",IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A42)-'Picks Detail'!E60)&gt;ABS(INDEX('Picks Detail'!F60:Q60,1,D42)-'Picks Detail'!E60),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G42">
         <f t="shared" si="6"/>
@@ -28721,11 +29155,11 @@
       </c>
       <c r="H42">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I42">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28738,18 +29172,18 @@
       </c>
       <c r="C43" s="3">
         <f>SUMPRODUCT(('Picks Detail'!M44:M59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!M44:M59='Picks Detail'!E44:E59))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D43">
         <v>2</v>
       </c>
       <c r="E43">
         <f>IFERROR(INDEX(C$36:C$47,MATCH(2,A$36:A$47,0)),0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F43" t="str">
         <f>IF(C43=0,"-",IF(C43&gt;E43,"W",IF(C43&lt;E43,"L",IF(AND('Picks Detail'!E60&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,A43)&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,D43)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A43)-'Picks Detail'!E60)&lt;ABS(INDEX('Picks Detail'!F60:Q60,1,D43)-'Picks Detail'!E60),"W",IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A43)-'Picks Detail'!E60)&gt;ABS(INDEX('Picks Detail'!F60:Q60,1,D43)-'Picks Detail'!E60),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G43">
         <f t="shared" si="6"/>
@@ -28757,11 +29191,11 @@
       </c>
       <c r="H43">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I43">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28774,18 +29208,18 @@
       </c>
       <c r="C44" s="3">
         <f>SUMPRODUCT(('Picks Detail'!N44:N59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!N44:N59='Picks Detail'!E44:E59))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D44">
         <v>5</v>
       </c>
       <c r="E44">
         <f>IFERROR(INDEX(C$36:C$47,MATCH(5,A$36:A$47,0)),0)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F44" t="str">
         <f>IF(C44=0,"-",IF(C44&gt;E44,"W",IF(C44&lt;E44,"L",IF(AND('Picks Detail'!E60&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,A44)&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,D44)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A44)-'Picks Detail'!E60)&lt;ABS(INDEX('Picks Detail'!F60:Q60,1,D44)-'Picks Detail'!E60),"W",IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A44)-'Picks Detail'!E60)&gt;ABS(INDEX('Picks Detail'!F60:Q60,1,D44)-'Picks Detail'!E60),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G44">
         <f t="shared" si="6"/>
@@ -28793,11 +29227,11 @@
       </c>
       <c r="H44">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I44">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28810,18 +29244,18 @@
       </c>
       <c r="C45" s="3">
         <f>SUMPRODUCT(('Picks Detail'!O44:O59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!O44:O59='Picks Detail'!E44:E59))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D45">
         <v>6</v>
       </c>
       <c r="E45">
         <f>IFERROR(INDEX(C$36:C$47,MATCH(6,A$36:A$47,0)),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F45" t="str">
         <f>IF(C45=0,"-",IF(C45&gt;E45,"W",IF(C45&lt;E45,"L",IF(AND('Picks Detail'!E60&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,A45)&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,D45)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A45)-'Picks Detail'!E60)&lt;ABS(INDEX('Picks Detail'!F60:Q60,1,D45)-'Picks Detail'!E60),"W",IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A45)-'Picks Detail'!E60)&gt;ABS(INDEX('Picks Detail'!F60:Q60,1,D45)-'Picks Detail'!E60),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G45">
         <f t="shared" si="6"/>
@@ -28829,11 +29263,11 @@
       </c>
       <c r="H45">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I45">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28846,30 +29280,30 @@
       </c>
       <c r="C46" s="3">
         <f>SUMPRODUCT(('Picks Detail'!P44:P59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!P44:P59='Picks Detail'!E44:E59))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D46">
         <v>3</v>
       </c>
       <c r="E46">
         <f>IFERROR(INDEX(C$36:C$47,MATCH(3,A$36:A$47,0)),0)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F46" t="str">
         <f>IF(C46=0,"-",IF(C46&gt;E46,"W",IF(C46&lt;E46,"L",IF(AND('Picks Detail'!E60&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,A46)&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,D46)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A46)-'Picks Detail'!E60)&lt;ABS(INDEX('Picks Detail'!F60:Q60,1,D46)-'Picks Detail'!E60),"W",IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A46)-'Picks Detail'!E60)&gt;ABS(INDEX('Picks Detail'!F60:Q60,1,D46)-'Picks Detail'!E60),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>T</v>
       </c>
       <c r="G46">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H46">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I46">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28882,7 +29316,7 @@
       </c>
       <c r="C47" s="3">
         <f>SUMPRODUCT(('Picks Detail'!Q44:Q59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!Q44:Q59='Picks Detail'!E44:E59))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D47">
         <v>4</v>
@@ -28893,19 +29327,19 @@
       </c>
       <c r="F47" t="str">
         <f>IF(C47=0,"-",IF(C47&gt;E47,"W",IF(C47&lt;E47,"L",IF(AND('Picks Detail'!E60&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,A47)&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,D47)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A47)-'Picks Detail'!E60)&lt;ABS(INDEX('Picks Detail'!F60:Q60,1,D47)-'Picks Detail'!E60),"W",IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A47)-'Picks Detail'!E60)&gt;ABS(INDEX('Picks Detail'!F60:Q60,1,D47)-'Picks Detail'!E60),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G47">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H47">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I47">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30326,17 +30760,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -33159,17 +33593,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -35992,19 +36426,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -36059,7 +36493,7 @@
       </c>
       <c r="E3">
         <f>Helper!E2</f>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <f>Helper!F2</f>
@@ -36075,7 +36509,7 @@
       </c>
       <c r="I3">
         <f>Helper!I2</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J3">
         <f>Helper!J2</f>
@@ -36104,7 +36538,7 @@
       </c>
       <c r="E4">
         <f>Helper!E3</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <f>Helper!F3</f>
@@ -36120,7 +36554,7 @@
       </c>
       <c r="I4">
         <f>Helper!I3</f>
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J4">
         <f>Helper!J3</f>
@@ -36149,7 +36583,7 @@
       </c>
       <c r="E5">
         <f>Helper!E4</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F5">
         <f>Helper!F4</f>
@@ -36165,7 +36599,7 @@
       </c>
       <c r="I5">
         <f>Helper!I4</f>
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J5">
         <f>Helper!J4</f>
@@ -36239,7 +36673,7 @@
       </c>
       <c r="E7">
         <f>Helper!E6</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F7">
         <f>Helper!F6</f>
@@ -36255,7 +36689,7 @@
       </c>
       <c r="I7">
         <f>Helper!I6</f>
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J7">
         <f>Helper!J6</f>
@@ -36284,7 +36718,7 @@
       </c>
       <c r="E8">
         <f>Helper!E7</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F8">
         <f>Helper!F7</f>
@@ -36300,7 +36734,7 @@
       </c>
       <c r="I8">
         <f>Helper!I7</f>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J8">
         <f>Helper!J7</f>
@@ -36329,7 +36763,7 @@
       </c>
       <c r="E9">
         <f>Helper!E8</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F9">
         <f>Helper!F8</f>
@@ -36345,7 +36779,7 @@
       </c>
       <c r="I9">
         <f>Helper!I8</f>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J9">
         <f>Helper!J8</f>
@@ -36374,7 +36808,7 @@
       </c>
       <c r="E10">
         <f>Helper!E9</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F10">
         <f>Helper!F9</f>
@@ -36390,7 +36824,7 @@
       </c>
       <c r="I10">
         <f>Helper!I9</f>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J10">
         <f>Helper!J9</f>
@@ -36419,7 +36853,7 @@
       </c>
       <c r="E11">
         <f>Helper!E10</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F11">
         <f>Helper!F10</f>
@@ -36435,7 +36869,7 @@
       </c>
       <c r="I11">
         <f>Helper!I10</f>
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J11">
         <f>Helper!J10</f>
@@ -36464,7 +36898,7 @@
       </c>
       <c r="E12">
         <f>Helper!E11</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F12">
         <f>Helper!F11</f>
@@ -36480,7 +36914,7 @@
       </c>
       <c r="I12">
         <f>Helper!I11</f>
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J12">
         <f>Helper!J11</f>
@@ -36509,7 +36943,7 @@
       </c>
       <c r="E13">
         <f>Helper!E12</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F13">
         <f>Helper!F12</f>
@@ -36525,7 +36959,7 @@
       </c>
       <c r="I13">
         <f>Helper!I12</f>
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J13">
         <f>Helper!J12</f>
@@ -36554,7 +36988,7 @@
       </c>
       <c r="E14">
         <f>Helper!E13</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F14">
         <f>Helper!F13</f>
@@ -36570,7 +37004,7 @@
       </c>
       <c r="I14">
         <f>Helper!I13</f>
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J14">
         <f>Helper!J13</f>
@@ -37894,7 +38328,7 @@
       </c>
       <c r="C57">
         <f>Helper!I2</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D57">
         <f>Helper!R2</f>
@@ -37906,11 +38340,11 @@
       </c>
       <c r="F57">
         <f>Helper!AE2</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G57">
         <f>Helper!K2</f>
-        <v>20.0001</v>
+        <v>30.0001</v>
       </c>
       <c r="H57">
         <f>Helper!T2</f>
@@ -37927,7 +38361,7 @@
       </c>
       <c r="C58">
         <f>Helper!I3</f>
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D58">
         <f>Helper!R3</f>
@@ -37939,11 +38373,11 @@
       </c>
       <c r="F58">
         <f>Helper!AE3</f>
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G58">
         <f>Helper!K3</f>
-        <v>21.0002</v>
+        <v>29.0002</v>
       </c>
       <c r="H58">
         <f>Helper!T3</f>
@@ -37960,7 +38394,7 @@
       </c>
       <c r="C59">
         <f>Helper!I4</f>
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D59">
         <f>Helper!R4</f>
@@ -37972,11 +38406,11 @@
       </c>
       <c r="F59">
         <f>Helper!AE4</f>
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G59">
         <f>Helper!K4</f>
-        <v>21.000299999999999</v>
+        <v>28.000299999999999</v>
       </c>
       <c r="H59">
         <f>Helper!T4</f>
@@ -38026,7 +38460,7 @@
       </c>
       <c r="C61">
         <f>Helper!I6</f>
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D61">
         <f>Helper!R6</f>
@@ -38038,11 +38472,11 @@
       </c>
       <c r="F61">
         <f>Helper!AE6</f>
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G61">
         <f>Helper!K6</f>
-        <v>22.000499999999999</v>
+        <v>31.000499999999999</v>
       </c>
       <c r="H61">
         <f>Helper!T6</f>
@@ -38059,7 +38493,7 @@
       </c>
       <c r="C62">
         <f>Helper!I7</f>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D62">
         <f>Helper!R7</f>
@@ -38071,11 +38505,11 @@
       </c>
       <c r="F62">
         <f>Helper!AE7</f>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G62">
         <f>Helper!K7</f>
-        <v>20.000599999999999</v>
+        <v>26.000599999999999</v>
       </c>
       <c r="H62">
         <f>Helper!T7</f>
@@ -38092,7 +38526,7 @@
       </c>
       <c r="C63">
         <f>Helper!I8</f>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D63">
         <f>Helper!R8</f>
@@ -38104,11 +38538,11 @@
       </c>
       <c r="F63">
         <f>Helper!AE8</f>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G63">
         <f>Helper!K8</f>
-        <v>19.000699999999998</v>
+        <v>27.000699999999998</v>
       </c>
       <c r="H63">
         <f>Helper!T8</f>
@@ -38125,7 +38559,7 @@
       </c>
       <c r="C64">
         <f>Helper!I9</f>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D64">
         <f>Helper!R9</f>
@@ -38137,11 +38571,11 @@
       </c>
       <c r="F64">
         <f>Helper!AE9</f>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G64">
         <f>Helper!K9</f>
-        <v>12.0008</v>
+        <v>19.000800000000002</v>
       </c>
       <c r="H64">
         <f>Helper!T9</f>
@@ -38158,7 +38592,7 @@
       </c>
       <c r="C65">
         <f>Helper!I10</f>
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D65">
         <f>Helper!R10</f>
@@ -38170,11 +38604,11 @@
       </c>
       <c r="F65">
         <f>Helper!AE10</f>
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G65">
         <f>Helper!K10</f>
-        <v>15.0009</v>
+        <v>23.000900000000001</v>
       </c>
       <c r="H65">
         <f>Helper!T10</f>
@@ -38191,7 +38625,7 @@
       </c>
       <c r="C66">
         <f>Helper!I11</f>
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D66">
         <f>Helper!R11</f>
@@ -38203,11 +38637,11 @@
       </c>
       <c r="F66">
         <f>Helper!AE11</f>
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G66">
         <f>Helper!K11</f>
-        <v>31.001000000000001</v>
+        <v>36.000999999999998</v>
       </c>
       <c r="H66">
         <f>Helper!T11</f>
@@ -38224,7 +38658,7 @@
       </c>
       <c r="C67">
         <f>Helper!I12</f>
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D67">
         <f>Helper!R12</f>
@@ -38236,11 +38670,11 @@
       </c>
       <c r="F67">
         <f>Helper!AE12</f>
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G67">
         <f>Helper!K12</f>
-        <v>28.001100000000001</v>
+        <v>36.001100000000001</v>
       </c>
       <c r="H67">
         <f>Helper!T12</f>
@@ -38257,7 +38691,7 @@
       </c>
       <c r="C68">
         <f>Helper!I13</f>
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D68">
         <f>Helper!R13</f>
@@ -38269,11 +38703,11 @@
       </c>
       <c r="F68">
         <f>Helper!AE13</f>
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G68">
         <f>Helper!K13</f>
-        <v>19.001200000000001</v>
+        <v>25.001200000000001</v>
       </c>
       <c r="H68">
         <f>Helper!T13</f>
@@ -38343,7 +38777,7 @@
       </c>
       <c r="B5" t="str">
         <f>INDEX(Helper!B$2:B$13,MATCH(MAX(Helper!K$2:K$13),Helper!K$2:K$13,0))</f>
-        <v>Zach Zarra</v>
+        <v>Jeffrey Loeser</v>
       </c>
       <c r="C5" t="s">
         <v>252</v>
@@ -38353,7 +38787,7 @@
       </c>
       <c r="E5" t="str">
         <f>B5</f>
-        <v>Zach Zarra</v>
+        <v>Jeffrey Loeser</v>
       </c>
       <c r="F5" t="str">
         <f>IF(B5="","—","QUALIFIED")</f>
@@ -38461,11 +38895,11 @@
       </c>
       <c r="E9" t="str">
         <f>IF(AND(H13&lt;&gt;$E$5,H13&lt;&gt;$E$6,H13&lt;&gt;$E$7,H13&lt;&gt;$E$8),H13,IF(AND(H14&lt;&gt;$E$5,H14&lt;&gt;$E$6,H14&lt;&gt;$E$7,H14&lt;&gt;$E$8),H14,IF(AND(H15&lt;&gt;$E$5,H15&lt;&gt;$E$6,H15&lt;&gt;$E$7,H15&lt;&gt;$E$8),H15,H16)))</f>
-        <v>Jeffrey Loeser</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="F9" t="str">
         <f>IF(E9=B9,"QUALIFIED","PASS → "&amp;E9)</f>
-        <v>PASS → Jeffrey Loeser</v>
+        <v>PASS → Zach Zarra</v>
       </c>
       <c r="H9" t="str">
         <f>INDEX(Helper!B$6:B$9,MATCH(LARGE(Helper!AD$6:AD$9,1),Helper!AD$6:AD$9,0))</f>
@@ -38515,7 +38949,7 @@
       </c>
       <c r="C13">
         <f>INDEX(I$40:I$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
         <v>263</v>
@@ -38561,7 +38995,7 @@
       </c>
       <c r="B17" t="str">
         <f>E5</f>
-        <v>Zach Zarra</v>
+        <v>Jeffrey Loeser</v>
       </c>
       <c r="C17" t="str">
         <f>D5</f>
@@ -38613,7 +39047,7 @@
       </c>
       <c r="B21" t="str">
         <f>E9</f>
-        <v>Jeffrey Loeser</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="C21" t="str">
         <f>"Div C"</f>
@@ -38991,7 +39425,7 @@
       </c>
       <c r="I40">
         <f>Helper!AE2</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J40" t="b">
         <f t="shared" ref="J40:J51" si="1">OR(H40=$E$5,H40=$E$6,H40=$E$7,H40=$E$8,H40=$E$9)</f>
@@ -38999,7 +39433,7 @@
       </c>
       <c r="K40">
         <f>IF(J40,-1,I40+0.00001)</f>
-        <v>20.00001</v>
+        <v>30.00001</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39009,7 +39443,7 @@
       </c>
       <c r="I41">
         <f>Helper!AE3</f>
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J41" t="b">
         <f t="shared" si="1"/>
@@ -39017,7 +39451,7 @@
       </c>
       <c r="K41">
         <f>IF(J41,-1,I41+0.00002)</f>
-        <v>21.000019999999999</v>
+        <v>29.000019999999999</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39027,7 +39461,7 @@
       </c>
       <c r="I42">
         <f>Helper!AE4</f>
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J42" t="b">
         <f t="shared" si="1"/>
@@ -39035,7 +39469,7 @@
       </c>
       <c r="K42">
         <f>IF(J42,-1,I42+0.00003)</f>
-        <v>21.000029999999999</v>
+        <v>28.000029999999999</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39063,7 +39497,7 @@
       </c>
       <c r="I44">
         <f>Helper!AE6</f>
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J44" t="b">
         <f t="shared" si="1"/>
@@ -39071,7 +39505,7 @@
       </c>
       <c r="K44">
         <f>IF(J44,-1,I44+0.00005)</f>
-        <v>22.000050000000002</v>
+        <v>31.000050000000002</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39081,7 +39515,7 @@
       </c>
       <c r="I45">
         <f>Helper!AE7</f>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J45" t="b">
         <f t="shared" si="1"/>
@@ -39089,7 +39523,7 @@
       </c>
       <c r="K45">
         <f>IF(J45,-1,I45+0.00006)</f>
-        <v>20.000060000000001</v>
+        <v>26.000060000000001</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39099,7 +39533,7 @@
       </c>
       <c r="I46">
         <f>Helper!AE8</f>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J46" t="b">
         <f t="shared" si="1"/>
@@ -39107,7 +39541,7 @@
       </c>
       <c r="K46">
         <f>IF(J46,-1,I46+0.00007)</f>
-        <v>19.000070000000001</v>
+        <v>27.000070000000001</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39117,7 +39551,7 @@
       </c>
       <c r="I47">
         <f>Helper!AE9</f>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J47" t="b">
         <f t="shared" si="1"/>
@@ -39135,7 +39569,7 @@
       </c>
       <c r="I48">
         <f>Helper!AE10</f>
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J48" t="b">
         <f t="shared" si="1"/>
@@ -39143,7 +39577,7 @@
       </c>
       <c r="K48">
         <f>IF(J48,-1,I48+0.00009)</f>
-        <v>15.00009</v>
+        <v>23.00009</v>
       </c>
     </row>
     <row r="49" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39153,7 +39587,7 @@
       </c>
       <c r="I49">
         <f>Helper!AE11</f>
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J49" t="b">
         <f t="shared" si="1"/>
@@ -39171,7 +39605,7 @@
       </c>
       <c r="I50">
         <f>Helper!AE12</f>
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J50" t="b">
         <f t="shared" si="1"/>
@@ -39189,7 +39623,7 @@
       </c>
       <c r="I51">
         <f>Helper!AE13</f>
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J51" t="b">
         <f t="shared" si="1"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="524" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39672356-66BB-48EC-AD0B-D993EDFFC30C}"/>
+  <xr:revisionPtr revIDLastSave="549" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6BC745A-6631-45F7-9E5A-9D8EACB226A9}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3762" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3773" uniqueCount="346">
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -1377,13 +1377,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1665,12 +1665,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="E2">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H36,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G36,0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H51,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G51,0)</f>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I13" si="0">SUM(C2:H2)</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J2">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F6="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F21="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F36="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F51="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F66="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F81="W"),1,0)</f>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="K2">
         <f>I2+0.0001</f>
-        <v>30.0001</v>
+        <v>31.0001</v>
       </c>
       <c r="L2">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H6,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G6,0)</f>
@@ -2957,11 +2957,11 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE13" si="2">I2+R2+AC2</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AF2">
         <f>AE2+0.0001</f>
-        <v>30.0001</v>
+        <v>31.0001</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="E7">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H41,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G41,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H56,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G56,0)</f>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J7">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F11="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F26="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F41="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F56="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F71="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F86="W"),1,0)</f>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="K7">
         <f>I7+0.0006</f>
-        <v>26.000599999999999</v>
+        <v>27.000599999999999</v>
       </c>
       <c r="L7">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H11,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G11,0)</f>
@@ -3602,11 +3602,11 @@
       </c>
       <c r="AE7">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF7">
         <f>AE7+0.0006</f>
-        <v>26.000599999999999</v>
+        <v>27.000599999999999</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4402,14 +4402,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -5354,14 +5354,14 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="22" t="s">
+      <c r="A56" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="22"/>
-      <c r="C56" s="22"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
@@ -6306,14 +6306,14 @@
       </c>
     </row>
     <row r="111" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="22" t="s">
+      <c r="A111" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B111" s="22"/>
-      <c r="C111" s="22"/>
-      <c r="D111" s="22"/>
-      <c r="E111" s="22"/>
-      <c r="F111" s="22"/>
+      <c r="B111" s="23"/>
+      <c r="C111" s="23"/>
+      <c r="D111" s="23"/>
+      <c r="E111" s="23"/>
+      <c r="F111" s="23"/>
     </row>
     <row r="112" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
@@ -7285,67 +7285,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="24"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8313,25 +8313,25 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="24"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -9299,25 +9299,25 @@
       </c>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+      <c r="A42" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="24"/>
-      <c r="K42" s="24"/>
-      <c r="L42" s="24"/>
-      <c r="M42" s="24"/>
-      <c r="N42" s="24"/>
-      <c r="O42" s="24"/>
-      <c r="P42" s="24"/>
-      <c r="Q42" s="24"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="26"/>
+      <c r="Q42" s="26"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -10163,20 +10163,42 @@
       </c>
       <c r="E59" s="9" t="str">
         <f>'NFL Schedule'!J56</f>
-        <v/>
-      </c>
-      <c r="F59" s="10"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
+        <v>CHI</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>84</v>
+      </c>
       <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
-      <c r="K59" s="10"/>
-      <c r="L59" s="10"/>
-      <c r="M59" s="10"/>
-      <c r="N59" s="10"/>
-      <c r="O59" s="10"/>
-      <c r="P59" s="10"/>
-      <c r="Q59" s="10"/>
+      <c r="J59" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="K59" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="L59" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="M59" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="N59" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="O59" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="P59" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q59" s="10" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
@@ -10185,43 +10207,65 @@
       <c r="B60" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="E60" s="13" t="str">
+      <c r="E60" s="13">
         <f>'NFL Schedule'!E57</f>
-        <v/>
-      </c>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="F60" s="14">
+        <v>44</v>
+      </c>
+      <c r="G60" s="14">
+        <v>40</v>
+      </c>
+      <c r="H60" s="14">
+        <v>48</v>
+      </c>
       <c r="I60" s="14"/>
-      <c r="J60" s="14"/>
-      <c r="K60" s="14"/>
-      <c r="L60" s="14"/>
-      <c r="M60" s="14"/>
-      <c r="N60" s="14"/>
-      <c r="O60" s="14"/>
-      <c r="P60" s="14"/>
-      <c r="Q60" s="14"/>
+      <c r="J60" s="14">
+        <v>45</v>
+      </c>
+      <c r="K60" s="14">
+        <v>43</v>
+      </c>
+      <c r="L60" s="14">
+        <v>42</v>
+      </c>
+      <c r="M60" s="14">
+        <v>43</v>
+      </c>
+      <c r="N60" s="14">
+        <v>41</v>
+      </c>
+      <c r="O60" s="14">
+        <v>42</v>
+      </c>
+      <c r="P60" s="14">
+        <v>53</v>
+      </c>
+      <c r="Q60" s="14">
+        <v>42</v>
+      </c>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="24" t="s">
+      <c r="A61" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="24"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="24"/>
-      <c r="J61" s="24"/>
-      <c r="K61" s="24"/>
-      <c r="L61" s="24"/>
-      <c r="M61" s="24"/>
-      <c r="N61" s="24"/>
-      <c r="O61" s="24"/>
-      <c r="P61" s="24"/>
-      <c r="Q61" s="24"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="26"/>
+      <c r="J61" s="26"/>
+      <c r="K61" s="26"/>
+      <c r="L61" s="26"/>
+      <c r="M61" s="26"/>
+      <c r="N61" s="26"/>
+      <c r="O61" s="26"/>
+      <c r="P61" s="26"/>
+      <c r="Q61" s="26"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -10781,25 +10825,25 @@
       <c r="Q79" s="14"/>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="24" t="s">
+      <c r="A80" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="24"/>
-      <c r="C80" s="24"/>
-      <c r="D80" s="24"/>
-      <c r="E80" s="24"/>
-      <c r="F80" s="24"/>
-      <c r="G80" s="24"/>
-      <c r="H80" s="24"/>
-      <c r="I80" s="24"/>
-      <c r="J80" s="24"/>
-      <c r="K80" s="24"/>
-      <c r="L80" s="24"/>
-      <c r="M80" s="24"/>
-      <c r="N80" s="24"/>
-      <c r="O80" s="24"/>
-      <c r="P80" s="24"/>
-      <c r="Q80" s="24"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
+      <c r="I80" s="26"/>
+      <c r="J80" s="26"/>
+      <c r="K80" s="26"/>
+      <c r="L80" s="26"/>
+      <c r="M80" s="26"/>
+      <c r="N80" s="26"/>
+      <c r="O80" s="26"/>
+      <c r="P80" s="26"/>
+      <c r="Q80" s="26"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -11329,25 +11373,25 @@
       <c r="Q97" s="14"/>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="24" t="s">
+      <c r="A98" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="24"/>
-      <c r="C98" s="24"/>
-      <c r="D98" s="24"/>
-      <c r="E98" s="24"/>
-      <c r="F98" s="24"/>
-      <c r="G98" s="24"/>
-      <c r="H98" s="24"/>
-      <c r="I98" s="24"/>
-      <c r="J98" s="24"/>
-      <c r="K98" s="24"/>
-      <c r="L98" s="24"/>
-      <c r="M98" s="24"/>
-      <c r="N98" s="24"/>
-      <c r="O98" s="24"/>
-      <c r="P98" s="24"/>
-      <c r="Q98" s="24"/>
+      <c r="B98" s="26"/>
+      <c r="C98" s="26"/>
+      <c r="D98" s="26"/>
+      <c r="E98" s="26"/>
+      <c r="F98" s="26"/>
+      <c r="G98" s="26"/>
+      <c r="H98" s="26"/>
+      <c r="I98" s="26"/>
+      <c r="J98" s="26"/>
+      <c r="K98" s="26"/>
+      <c r="L98" s="26"/>
+      <c r="M98" s="26"/>
+      <c r="N98" s="26"/>
+      <c r="O98" s="26"/>
+      <c r="P98" s="26"/>
+      <c r="Q98" s="26"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -11847,25 +11891,25 @@
       <c r="Q114" s="14"/>
     </row>
     <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="24" t="s">
+      <c r="A115" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="24"/>
-      <c r="C115" s="24"/>
-      <c r="D115" s="24"/>
-      <c r="E115" s="24"/>
-      <c r="F115" s="24"/>
-      <c r="G115" s="24"/>
-      <c r="H115" s="24"/>
-      <c r="I115" s="24"/>
-      <c r="J115" s="24"/>
-      <c r="K115" s="24"/>
-      <c r="L115" s="24"/>
-      <c r="M115" s="24"/>
-      <c r="N115" s="24"/>
-      <c r="O115" s="24"/>
-      <c r="P115" s="24"/>
-      <c r="Q115" s="24"/>
+      <c r="B115" s="26"/>
+      <c r="C115" s="26"/>
+      <c r="D115" s="26"/>
+      <c r="E115" s="26"/>
+      <c r="F115" s="26"/>
+      <c r="G115" s="26"/>
+      <c r="H115" s="26"/>
+      <c r="I115" s="26"/>
+      <c r="J115" s="26"/>
+      <c r="K115" s="26"/>
+      <c r="L115" s="26"/>
+      <c r="M115" s="26"/>
+      <c r="N115" s="26"/>
+      <c r="O115" s="26"/>
+      <c r="P115" s="26"/>
+      <c r="Q115" s="26"/>
     </row>
     <row r="116" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -12365,25 +12409,25 @@
       <c r="Q131" s="14"/>
     </row>
     <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="24" t="s">
+      <c r="A132" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="B132" s="24"/>
-      <c r="C132" s="24"/>
-      <c r="D132" s="24"/>
-      <c r="E132" s="24"/>
-      <c r="F132" s="24"/>
-      <c r="G132" s="24"/>
-      <c r="H132" s="24"/>
-      <c r="I132" s="24"/>
-      <c r="J132" s="24"/>
-      <c r="K132" s="24"/>
-      <c r="L132" s="24"/>
-      <c r="M132" s="24"/>
-      <c r="N132" s="24"/>
-      <c r="O132" s="24"/>
-      <c r="P132" s="24"/>
-      <c r="Q132" s="24"/>
+      <c r="B132" s="26"/>
+      <c r="C132" s="26"/>
+      <c r="D132" s="26"/>
+      <c r="E132" s="26"/>
+      <c r="F132" s="26"/>
+      <c r="G132" s="26"/>
+      <c r="H132" s="26"/>
+      <c r="I132" s="26"/>
+      <c r="J132" s="26"/>
+      <c r="K132" s="26"/>
+      <c r="L132" s="26"/>
+      <c r="M132" s="26"/>
+      <c r="N132" s="26"/>
+      <c r="O132" s="26"/>
+      <c r="P132" s="26"/>
+      <c r="Q132" s="26"/>
     </row>
     <row r="133" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -12883,25 +12927,25 @@
       <c r="Q148" s="14"/>
     </row>
     <row r="149" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="24" t="s">
+      <c r="A149" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="B149" s="24"/>
-      <c r="C149" s="24"/>
-      <c r="D149" s="24"/>
-      <c r="E149" s="24"/>
-      <c r="F149" s="24"/>
-      <c r="G149" s="24"/>
-      <c r="H149" s="24"/>
-      <c r="I149" s="24"/>
-      <c r="J149" s="24"/>
-      <c r="K149" s="24"/>
-      <c r="L149" s="24"/>
-      <c r="M149" s="24"/>
-      <c r="N149" s="24"/>
-      <c r="O149" s="24"/>
-      <c r="P149" s="24"/>
-      <c r="Q149" s="24"/>
+      <c r="B149" s="26"/>
+      <c r="C149" s="26"/>
+      <c r="D149" s="26"/>
+      <c r="E149" s="26"/>
+      <c r="F149" s="26"/>
+      <c r="G149" s="26"/>
+      <c r="H149" s="26"/>
+      <c r="I149" s="26"/>
+      <c r="J149" s="26"/>
+      <c r="K149" s="26"/>
+      <c r="L149" s="26"/>
+      <c r="M149" s="26"/>
+      <c r="N149" s="26"/>
+      <c r="O149" s="26"/>
+      <c r="P149" s="26"/>
+      <c r="Q149" s="26"/>
     </row>
     <row r="150" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -13431,25 +13475,25 @@
       <c r="Q166" s="14"/>
     </row>
     <row r="167" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="24" t="s">
+      <c r="A167" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="B167" s="24"/>
-      <c r="C167" s="24"/>
-      <c r="D167" s="24"/>
-      <c r="E167" s="24"/>
-      <c r="F167" s="24"/>
-      <c r="G167" s="24"/>
-      <c r="H167" s="24"/>
-      <c r="I167" s="24"/>
-      <c r="J167" s="24"/>
-      <c r="K167" s="24"/>
-      <c r="L167" s="24"/>
-      <c r="M167" s="24"/>
-      <c r="N167" s="24"/>
-      <c r="O167" s="24"/>
-      <c r="P167" s="24"/>
-      <c r="Q167" s="24"/>
+      <c r="B167" s="26"/>
+      <c r="C167" s="26"/>
+      <c r="D167" s="26"/>
+      <c r="E167" s="26"/>
+      <c r="F167" s="26"/>
+      <c r="G167" s="26"/>
+      <c r="H167" s="26"/>
+      <c r="I167" s="26"/>
+      <c r="J167" s="26"/>
+      <c r="K167" s="26"/>
+      <c r="L167" s="26"/>
+      <c r="M167" s="26"/>
+      <c r="N167" s="26"/>
+      <c r="O167" s="26"/>
+      <c r="P167" s="26"/>
+      <c r="Q167" s="26"/>
     </row>
     <row r="168" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -13949,25 +13993,25 @@
       <c r="Q183" s="14"/>
     </row>
     <row r="184" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="24" t="s">
+      <c r="A184" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="B184" s="24"/>
-      <c r="C184" s="24"/>
-      <c r="D184" s="24"/>
-      <c r="E184" s="24"/>
-      <c r="F184" s="24"/>
-      <c r="G184" s="24"/>
-      <c r="H184" s="24"/>
-      <c r="I184" s="24"/>
-      <c r="J184" s="24"/>
-      <c r="K184" s="24"/>
-      <c r="L184" s="24"/>
-      <c r="M184" s="24"/>
-      <c r="N184" s="24"/>
-      <c r="O184" s="24"/>
-      <c r="P184" s="24"/>
-      <c r="Q184" s="24"/>
+      <c r="B184" s="26"/>
+      <c r="C184" s="26"/>
+      <c r="D184" s="26"/>
+      <c r="E184" s="26"/>
+      <c r="F184" s="26"/>
+      <c r="G184" s="26"/>
+      <c r="H184" s="26"/>
+      <c r="I184" s="26"/>
+      <c r="J184" s="26"/>
+      <c r="K184" s="26"/>
+      <c r="L184" s="26"/>
+      <c r="M184" s="26"/>
+      <c r="N184" s="26"/>
+      <c r="O184" s="26"/>
+      <c r="P184" s="26"/>
+      <c r="Q184" s="26"/>
     </row>
     <row r="185" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -14437,25 +14481,25 @@
       <c r="Q199" s="14"/>
     </row>
     <row r="200" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="24" t="s">
+      <c r="A200" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="B200" s="24"/>
-      <c r="C200" s="24"/>
-      <c r="D200" s="24"/>
-      <c r="E200" s="24"/>
-      <c r="F200" s="24"/>
-      <c r="G200" s="24"/>
-      <c r="H200" s="24"/>
-      <c r="I200" s="24"/>
-      <c r="J200" s="24"/>
-      <c r="K200" s="24"/>
-      <c r="L200" s="24"/>
-      <c r="M200" s="24"/>
-      <c r="N200" s="24"/>
-      <c r="O200" s="24"/>
-      <c r="P200" s="24"/>
-      <c r="Q200" s="24"/>
+      <c r="B200" s="26"/>
+      <c r="C200" s="26"/>
+      <c r="D200" s="26"/>
+      <c r="E200" s="26"/>
+      <c r="F200" s="26"/>
+      <c r="G200" s="26"/>
+      <c r="H200" s="26"/>
+      <c r="I200" s="26"/>
+      <c r="J200" s="26"/>
+      <c r="K200" s="26"/>
+      <c r="L200" s="26"/>
+      <c r="M200" s="26"/>
+      <c r="N200" s="26"/>
+      <c r="O200" s="26"/>
+      <c r="P200" s="26"/>
+      <c r="Q200" s="26"/>
     </row>
     <row r="201" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -15015,25 +15059,25 @@
       <c r="Q218" s="14"/>
     </row>
     <row r="219" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="24" t="s">
+      <c r="A219" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="B219" s="24"/>
-      <c r="C219" s="24"/>
-      <c r="D219" s="24"/>
-      <c r="E219" s="24"/>
-      <c r="F219" s="24"/>
-      <c r="G219" s="24"/>
-      <c r="H219" s="24"/>
-      <c r="I219" s="24"/>
-      <c r="J219" s="24"/>
-      <c r="K219" s="24"/>
-      <c r="L219" s="24"/>
-      <c r="M219" s="24"/>
-      <c r="N219" s="24"/>
-      <c r="O219" s="24"/>
-      <c r="P219" s="24"/>
-      <c r="Q219" s="24"/>
+      <c r="B219" s="26"/>
+      <c r="C219" s="26"/>
+      <c r="D219" s="26"/>
+      <c r="E219" s="26"/>
+      <c r="F219" s="26"/>
+      <c r="G219" s="26"/>
+      <c r="H219" s="26"/>
+      <c r="I219" s="26"/>
+      <c r="J219" s="26"/>
+      <c r="K219" s="26"/>
+      <c r="L219" s="26"/>
+      <c r="M219" s="26"/>
+      <c r="N219" s="26"/>
+      <c r="O219" s="26"/>
+      <c r="P219" s="26"/>
+      <c r="Q219" s="26"/>
     </row>
     <row r="220" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -15533,25 +15577,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="24" t="s">
+      <c r="A236" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="B236" s="24"/>
-      <c r="C236" s="24"/>
-      <c r="D236" s="24"/>
-      <c r="E236" s="24"/>
-      <c r="F236" s="24"/>
-      <c r="G236" s="24"/>
-      <c r="H236" s="24"/>
-      <c r="I236" s="24"/>
-      <c r="J236" s="24"/>
-      <c r="K236" s="24"/>
-      <c r="L236" s="24"/>
-      <c r="M236" s="24"/>
-      <c r="N236" s="24"/>
-      <c r="O236" s="24"/>
-      <c r="P236" s="24"/>
-      <c r="Q236" s="24"/>
+      <c r="B236" s="26"/>
+      <c r="C236" s="26"/>
+      <c r="D236" s="26"/>
+      <c r="E236" s="26"/>
+      <c r="F236" s="26"/>
+      <c r="G236" s="26"/>
+      <c r="H236" s="26"/>
+      <c r="I236" s="26"/>
+      <c r="J236" s="26"/>
+      <c r="K236" s="26"/>
+      <c r="L236" s="26"/>
+      <c r="M236" s="26"/>
+      <c r="N236" s="26"/>
+      <c r="O236" s="26"/>
+      <c r="P236" s="26"/>
+      <c r="Q236" s="26"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -16081,25 +16125,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="24" t="s">
+      <c r="A254" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="B254" s="24"/>
-      <c r="C254" s="24"/>
-      <c r="D254" s="24"/>
-      <c r="E254" s="24"/>
-      <c r="F254" s="24"/>
-      <c r="G254" s="24"/>
-      <c r="H254" s="24"/>
-      <c r="I254" s="24"/>
-      <c r="J254" s="24"/>
-      <c r="K254" s="24"/>
-      <c r="L254" s="24"/>
-      <c r="M254" s="24"/>
-      <c r="N254" s="24"/>
-      <c r="O254" s="24"/>
-      <c r="P254" s="24"/>
-      <c r="Q254" s="24"/>
+      <c r="B254" s="26"/>
+      <c r="C254" s="26"/>
+      <c r="D254" s="26"/>
+      <c r="E254" s="26"/>
+      <c r="F254" s="26"/>
+      <c r="G254" s="26"/>
+      <c r="H254" s="26"/>
+      <c r="I254" s="26"/>
+      <c r="J254" s="26"/>
+      <c r="K254" s="26"/>
+      <c r="L254" s="26"/>
+      <c r="M254" s="26"/>
+      <c r="N254" s="26"/>
+      <c r="O254" s="26"/>
+      <c r="P254" s="26"/>
+      <c r="Q254" s="26"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -16659,25 +16703,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="24" t="s">
+      <c r="A273" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="B273" s="24"/>
-      <c r="C273" s="24"/>
-      <c r="D273" s="24"/>
-      <c r="E273" s="24"/>
-      <c r="F273" s="24"/>
-      <c r="G273" s="24"/>
-      <c r="H273" s="24"/>
-      <c r="I273" s="24"/>
-      <c r="J273" s="24"/>
-      <c r="K273" s="24"/>
-      <c r="L273" s="24"/>
-      <c r="M273" s="24"/>
-      <c r="N273" s="24"/>
-      <c r="O273" s="24"/>
-      <c r="P273" s="24"/>
-      <c r="Q273" s="24"/>
+      <c r="B273" s="26"/>
+      <c r="C273" s="26"/>
+      <c r="D273" s="26"/>
+      <c r="E273" s="26"/>
+      <c r="F273" s="26"/>
+      <c r="G273" s="26"/>
+      <c r="H273" s="26"/>
+      <c r="I273" s="26"/>
+      <c r="J273" s="26"/>
+      <c r="K273" s="26"/>
+      <c r="L273" s="26"/>
+      <c r="M273" s="26"/>
+      <c r="N273" s="26"/>
+      <c r="O273" s="26"/>
+      <c r="P273" s="26"/>
+      <c r="Q273" s="26"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -17237,25 +17281,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="24" t="s">
+      <c r="A292" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="B292" s="24"/>
-      <c r="C292" s="24"/>
-      <c r="D292" s="24"/>
-      <c r="E292" s="24"/>
-      <c r="F292" s="24"/>
-      <c r="G292" s="24"/>
-      <c r="H292" s="24"/>
-      <c r="I292" s="24"/>
-      <c r="J292" s="24"/>
-      <c r="K292" s="24"/>
-      <c r="L292" s="24"/>
-      <c r="M292" s="24"/>
-      <c r="N292" s="24"/>
-      <c r="O292" s="24"/>
-      <c r="P292" s="24"/>
-      <c r="Q292" s="24"/>
+      <c r="B292" s="26"/>
+      <c r="C292" s="26"/>
+      <c r="D292" s="26"/>
+      <c r="E292" s="26"/>
+      <c r="F292" s="26"/>
+      <c r="G292" s="26"/>
+      <c r="H292" s="26"/>
+      <c r="I292" s="26"/>
+      <c r="J292" s="26"/>
+      <c r="K292" s="26"/>
+      <c r="L292" s="26"/>
+      <c r="M292" s="26"/>
+      <c r="N292" s="26"/>
+      <c r="O292" s="26"/>
+      <c r="P292" s="26"/>
+      <c r="Q292" s="26"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -17815,25 +17859,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="24" t="s">
+      <c r="A311" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="B311" s="24"/>
-      <c r="C311" s="24"/>
-      <c r="D311" s="24"/>
-      <c r="E311" s="24"/>
-      <c r="F311" s="24"/>
-      <c r="G311" s="24"/>
-      <c r="H311" s="24"/>
-      <c r="I311" s="24"/>
-      <c r="J311" s="24"/>
-      <c r="K311" s="24"/>
-      <c r="L311" s="24"/>
-      <c r="M311" s="24"/>
-      <c r="N311" s="24"/>
-      <c r="O311" s="24"/>
-      <c r="P311" s="24"/>
-      <c r="Q311" s="24"/>
+      <c r="B311" s="26"/>
+      <c r="C311" s="26"/>
+      <c r="D311" s="26"/>
+      <c r="E311" s="26"/>
+      <c r="F311" s="26"/>
+      <c r="G311" s="26"/>
+      <c r="H311" s="26"/>
+      <c r="I311" s="26"/>
+      <c r="J311" s="26"/>
+      <c r="K311" s="26"/>
+      <c r="L311" s="26"/>
+      <c r="M311" s="26"/>
+      <c r="N311" s="26"/>
+      <c r="O311" s="26"/>
+      <c r="P311" s="26"/>
+      <c r="Q311" s="26"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -18394,26 +18438,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A236:Q236"/>
+    <mergeCell ref="A254:Q254"/>
+    <mergeCell ref="A273:Q273"/>
+    <mergeCell ref="A292:Q292"/>
+    <mergeCell ref="A311:Q311"/>
+    <mergeCell ref="A149:Q149"/>
+    <mergeCell ref="A167:Q167"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A219:Q219"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="A132:Q132"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A4:Q4"/>
     <mergeCell ref="A23:Q23"/>
     <mergeCell ref="A42:Q42"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A167:Q167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A236:Q236"/>
-    <mergeCell ref="A254:Q254"/>
-    <mergeCell ref="A273:Q273"/>
-    <mergeCell ref="A292:Q292"/>
-    <mergeCell ref="A311:Q311"/>
   </mergeCells>
   <dataValidations count="268">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or SEA" promptTitle="ATS Pick" prompt="Pick NE or SEA" sqref="F6:Q6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -21242,25 +21286,34 @@
       <c r="D56" t="s">
         <v>84</v>
       </c>
+      <c r="E56">
+        <v>7</v>
+      </c>
       <c r="F56" t="s">
         <v>61</v>
       </c>
+      <c r="G56">
+        <v>27</v>
+      </c>
+      <c r="H56">
+        <v>-3.5</v>
+      </c>
       <c r="I56" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>CHI</v>
       </c>
       <c r="J56" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>CHI</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D57" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="E57" s="16" t="str">
+      <c r="E57" s="16">
         <f>IF(AND(E56&lt;&gt;"",G56&lt;&gt;""),E56+G56,"")</f>
-        <v/>
+        <v>34</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27927,17 +27980,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -28920,7 +28973,7 @@
       </c>
       <c r="C36" s="3">
         <f>SUMPRODUCT(('Picks Detail'!F44:F59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!F44:F59='Picks Detail'!E44:E59))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D36">
         <v>7</v>
@@ -28939,11 +28992,11 @@
       </c>
       <c r="H36">
         <f t="shared" ref="H36:H47" si="7">IF(C36="",0,C36)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I36">
         <f t="shared" ref="I36:I47" si="8">G36+H36</f>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29003,11 +29056,11 @@
       </c>
       <c r="F38" t="str">
         <f>IF(C38=0,"-",IF(C38&gt;E38,"W",IF(C38&lt;E38,"L",IF(AND('Picks Detail'!E60&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,A38)&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,D38)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A38)-'Picks Detail'!E60)&lt;ABS(INDEX('Picks Detail'!F60:Q60,1,D38)-'Picks Detail'!E60),"W",IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A38)-'Picks Detail'!E60)&gt;ABS(INDEX('Picks Detail'!F60:Q60,1,D38)-'Picks Detail'!E60),"L","T")),"T"))))</f>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="G38">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H38">
         <f t="shared" si="7"/>
@@ -29015,7 +29068,7 @@
       </c>
       <c r="I38">
         <f t="shared" si="8"/>
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29100,7 +29153,7 @@
       </c>
       <c r="C41" s="3">
         <f>SUMPRODUCT(('Picks Detail'!K44:K59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!K44:K59='Picks Detail'!E44:E59))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D41">
         <v>10</v>
@@ -29119,11 +29172,11 @@
       </c>
       <c r="H41">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I41">
         <f t="shared" si="8"/>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29143,7 +29196,7 @@
       </c>
       <c r="E42">
         <f>IFERROR(INDEX(C$36:C$47,MATCH(1,A$36:A$47,0)),0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F42" t="str">
         <f>IF(C42=0,"-",IF(C42&gt;E42,"W",IF(C42&lt;E42,"L",IF(AND('Picks Detail'!E60&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,A42)&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,D42)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A42)-'Picks Detail'!E60)&lt;ABS(INDEX('Picks Detail'!F60:Q60,1,D42)-'Picks Detail'!E60),"W",IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A42)-'Picks Detail'!E60)&gt;ABS(INDEX('Picks Detail'!F60:Q60,1,D42)-'Picks Detail'!E60),"L","T")),"T"))))</f>
@@ -29251,7 +29304,7 @@
       </c>
       <c r="E45">
         <f>IFERROR(INDEX(C$36:C$47,MATCH(6,A$36:A$47,0)),0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F45" t="str">
         <f>IF(C45=0,"-",IF(C45&gt;E45,"W",IF(C45&lt;E45,"L",IF(AND('Picks Detail'!E60&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,A45)&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,D45)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A45)-'Picks Detail'!E60)&lt;ABS(INDEX('Picks Detail'!F60:Q60,1,D45)-'Picks Detail'!E60),"W",IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A45)-'Picks Detail'!E60)&gt;ABS(INDEX('Picks Detail'!F60:Q60,1,D45)-'Picks Detail'!E60),"L","T")),"T"))))</f>
@@ -29291,11 +29344,11 @@
       </c>
       <c r="F46" t="str">
         <f>IF(C46=0,"-",IF(C46&gt;E46,"W",IF(C46&lt;E46,"L",IF(AND('Picks Detail'!E60&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,A46)&lt;&gt;"",INDEX('Picks Detail'!F60:Q60,1,D46)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A46)-'Picks Detail'!E60)&lt;ABS(INDEX('Picks Detail'!F60:Q60,1,D46)-'Picks Detail'!E60),"W",IF(ABS(INDEX('Picks Detail'!F60:Q60,1,A46)-'Picks Detail'!E60)&gt;ABS(INDEX('Picks Detail'!F60:Q60,1,D46)-'Picks Detail'!E60),"L","T")),"T"))))</f>
-        <v>T</v>
+        <v>L</v>
       </c>
       <c r="G46">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H46">
         <f t="shared" si="7"/>
@@ -29303,7 +29356,7 @@
       </c>
       <c r="I46">
         <f t="shared" si="8"/>
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30760,17 +30813,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -33593,17 +33646,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -36426,19 +36479,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -36493,7 +36546,7 @@
       </c>
       <c r="E3">
         <f>Helper!E2</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3">
         <f>Helper!F2</f>
@@ -36509,7 +36562,7 @@
       </c>
       <c r="I3">
         <f>Helper!I2</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J3">
         <f>Helper!J2</f>
@@ -36718,7 +36771,7 @@
       </c>
       <c r="E8">
         <f>Helper!E7</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8">
         <f>Helper!F7</f>
@@ -36734,7 +36787,7 @@
       </c>
       <c r="I8">
         <f>Helper!I7</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J8">
         <f>Helper!J7</f>
@@ -38328,7 +38381,7 @@
       </c>
       <c r="C57">
         <f>Helper!I2</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D57">
         <f>Helper!R2</f>
@@ -38340,11 +38393,11 @@
       </c>
       <c r="F57">
         <f>Helper!AE2</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G57">
         <f>Helper!K2</f>
-        <v>30.0001</v>
+        <v>31.0001</v>
       </c>
       <c r="H57">
         <f>Helper!T2</f>
@@ -38493,7 +38546,7 @@
       </c>
       <c r="C62">
         <f>Helper!I7</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D62">
         <f>Helper!R7</f>
@@ -38505,11 +38558,11 @@
       </c>
       <c r="F62">
         <f>Helper!AE7</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G62">
         <f>Helper!K7</f>
-        <v>26.000599999999999</v>
+        <v>27.000599999999999</v>
       </c>
       <c r="H62">
         <f>Helper!T7</f>
@@ -39425,7 +39478,7 @@
       </c>
       <c r="I40">
         <f>Helper!AE2</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J40" t="b">
         <f t="shared" ref="J40:J51" si="1">OR(H40=$E$5,H40=$E$6,H40=$E$7,H40=$E$8,H40=$E$9)</f>
@@ -39433,7 +39486,7 @@
       </c>
       <c r="K40">
         <f>IF(J40,-1,I40+0.00001)</f>
-        <v>30.00001</v>
+        <v>31.00001</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39515,7 +39568,7 @@
       </c>
       <c r="I45">
         <f>Helper!AE7</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J45" t="b">
         <f t="shared" si="1"/>
@@ -39523,7 +39576,7 @@
       </c>
       <c r="K45">
         <f>IF(J45,-1,I45+0.00006)</f>
-        <v>26.000060000000001</v>
+        <v>27.000060000000001</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="549" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6BC745A-6631-45F7-9E5A-9D8EACB226A9}"/>
+  <xr:revisionPtr revIDLastSave="550" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2EF102E-CD51-419E-89CE-ADB3D724697C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1377,13 +1377,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1665,12 +1665,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1859,7 +1859,7 @@
         <v>23</v>
       </c>
       <c r="B16" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B5" t="str">
         <f>'Playoff Picture'!B17</f>
-        <v>Jeffrey Loeser</v>
+        <v>Mikayla Simmons</v>
       </c>
       <c r="C5" s="3">
         <v>6</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="B9" t="str">
         <f>'Playoff Picture'!B21</f>
-        <v>Zach Zarra</v>
+        <v>Jeffrey Loeser</v>
       </c>
       <c r="C9" s="3">
         <v>2</v>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="B10" t="str">
         <f>'Playoff Picture'!B22</f>
-        <v>Mikayla Simmons</v>
+        <v>Evan Loeser</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="B14" t="str">
         <f>INDEX($B$5:$B$10,MATCH(LARGE($H$5:$H$10,1),$H$5:$H$10,0))</f>
-        <v>Jeffrey Loeser</v>
+        <v>Mikayla Simmons</v>
       </c>
       <c r="C14">
         <f>INDEX($C$5:$C$10,MATCH(LARGE($H$5:$H$10,1),$H$5:$H$10,0))</f>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B18" t="str">
         <f>INDEX($B$5:$B$10,MATCH(LARGE($H$5:$H$10,5),$H$5:$H$10,0))</f>
-        <v>Zach Zarra</v>
+        <v>Jeffrey Loeser</v>
       </c>
       <c r="C18">
         <f>INDEX($C$5:$C$10,MATCH(LARGE($H$5:$H$10,5),$H$5:$H$10,0))</f>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="B19" t="str">
         <f>INDEX($B$5:$B$10,MATCH(LARGE($H$5:$H$10,6),$H$5:$H$10,0))</f>
-        <v>Mikayla Simmons</v>
+        <v>Evan Loeser</v>
       </c>
       <c r="C19">
         <f>INDEX($C$5:$C$10,MATCH(LARGE($H$5:$H$10,6),$H$5:$H$10,0))</f>
@@ -2281,7 +2281,7 @@
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>'Playoff Wild Card'!B14</f>
-        <v>Jeffrey Loeser</v>
+        <v>Mikayla Simmons</v>
       </c>
       <c r="B6">
         <f>'Playoff Wild Card'!C14</f>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="B13" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>Jeffrey Loeser</v>
+        <v>Mikayla Simmons</v>
       </c>
       <c r="C13">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
@@ -2632,7 +2632,7 @@
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>A6</f>
-        <v>Jeffrey Loeser</v>
+        <v>Mikayla Simmons</v>
       </c>
       <c r="B22" s="3">
         <v>0</v>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="E2">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H36,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G36,0)</f>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H51,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G51,0)</f>
@@ -2869,15 +2869,15 @@
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I13" si="0">SUM(C2:H2)</f>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J2">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F6="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F21="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F36="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F51="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F66="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F81="W"),1,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
         <f>I2+0.0001</f>
-        <v>31.0001</v>
+        <v>37.000100000000003</v>
       </c>
       <c r="L2">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H6,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G6,0)</f>
@@ -2957,11 +2957,11 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE13" si="2">I2+R2+AC2</f>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="AF2">
         <f>AE2+0.0001</f>
-        <v>31.0001</v>
+        <v>37.000100000000003</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="E3">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H37,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G37,0)</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H52,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G52,0)</f>
@@ -2998,15 +2998,15 @@
       </c>
       <c r="I3">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J3">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F7="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F22="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F37="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F52="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F67="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F82="W"),1,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <f>I3+0.0002</f>
-        <v>29.0002</v>
+        <v>35.0002</v>
       </c>
       <c r="L3">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H7,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G7,0)</f>
@@ -3086,11 +3086,11 @@
       </c>
       <c r="AE3">
         <f t="shared" si="2"/>
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="AF3">
         <f>AE3+0.0002</f>
-        <v>29.0002</v>
+        <v>35.0002</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E4">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H38,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G38,0)</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F4">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H53,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G53,0)</f>
@@ -3127,15 +3127,15 @@
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J4">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F8="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F23="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F38="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F53="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F68="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F83="W"),1,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4">
         <f>I4+0.0003</f>
-        <v>28.000299999999999</v>
+        <v>34.000300000000003</v>
       </c>
       <c r="L4">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H8,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G8,0)</f>
@@ -3215,11 +3215,11 @@
       </c>
       <c r="AE4">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AF4">
         <f>AE4+0.0003</f>
-        <v>28.000299999999999</v>
+        <v>34.000300000000003</v>
       </c>
     </row>
     <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="E6">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H40,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G40,0)</f>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F6">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H55,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G55,0)</f>
@@ -3385,15 +3385,15 @@
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J6">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F10="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F25="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F40="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F55="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F70="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F85="W"),1,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6">
         <f>I6+0.0005</f>
-        <v>31.000499999999999</v>
+        <v>37.000500000000002</v>
       </c>
       <c r="L6">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H10,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G10,0)</f>
@@ -3473,11 +3473,11 @@
       </c>
       <c r="AE6">
         <f t="shared" si="2"/>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="AF6">
         <f>AE6+0.0005</f>
-        <v>31.000499999999999</v>
+        <v>37.000500000000002</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="E7">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H41,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G41,0)</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F7">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H56,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G56,0)</f>
@@ -3514,15 +3514,15 @@
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J7">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F11="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F26="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F41="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F56="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F71="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F86="W"),1,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7">
         <f>I7+0.0006</f>
-        <v>27.000599999999999</v>
+        <v>33.000599999999999</v>
       </c>
       <c r="L7">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H11,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G11,0)</f>
@@ -3602,11 +3602,11 @@
       </c>
       <c r="AE7">
         <f t="shared" si="2"/>
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="AF7">
         <f>AE7+0.0006</f>
-        <v>27.000599999999999</v>
+        <v>33.000599999999999</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="E13">
         <f>IF(Roster!$B$16&gt;=3,'Wk 1-6 Input'!H47,0)+IF(Roster!$B$16&gt;3,'Wk 1-6 Input'!G47,0)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F13">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H62,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G62,0)</f>
@@ -4288,15 +4288,15 @@
       </c>
       <c r="I13">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J13">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F17="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F32="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F47="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F62="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F77="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F92="W"),1,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13">
         <f>I13+0.0012</f>
-        <v>25.001200000000001</v>
+        <v>31.001200000000001</v>
       </c>
       <c r="L13">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H17,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G17,0)</f>
@@ -4376,11 +4376,11 @@
       </c>
       <c r="AE13">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="AF13">
         <f>AE13+0.0012</f>
-        <v>25.001200000000001</v>
+        <v>31.001200000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4402,14 +4402,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -5354,14 +5354,14 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
+      <c r="B56" s="26"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
@@ -6306,14 +6306,14 @@
       </c>
     </row>
     <row r="111" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="23" t="s">
+      <c r="A111" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="B111" s="23"/>
-      <c r="C111" s="23"/>
-      <c r="D111" s="23"/>
-      <c r="E111" s="23"/>
-      <c r="F111" s="23"/>
+      <c r="B111" s="26"/>
+      <c r="C111" s="26"/>
+      <c r="D111" s="26"/>
+      <c r="E111" s="26"/>
+      <c r="F111" s="26"/>
     </row>
     <row r="112" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
@@ -7285,67 +7285,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8313,25 +8313,25 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="26"/>
-      <c r="P23" s="26"/>
-      <c r="Q23" s="26"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -9299,25 +9299,25 @@
       </c>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="26" t="s">
+      <c r="A42" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="26"/>
-      <c r="L42" s="26"/>
-      <c r="M42" s="26"/>
-      <c r="N42" s="26"/>
-      <c r="O42" s="26"/>
-      <c r="P42" s="26"/>
-      <c r="Q42" s="26"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="22"/>
+      <c r="N42" s="22"/>
+      <c r="O42" s="22"/>
+      <c r="P42" s="22"/>
+      <c r="Q42" s="22"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -10247,25 +10247,25 @@
       </c>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="26" t="s">
+      <c r="A61" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="26"/>
-      <c r="C61" s="26"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="26"/>
-      <c r="F61" s="26"/>
-      <c r="G61" s="26"/>
-      <c r="H61" s="26"/>
-      <c r="I61" s="26"/>
-      <c r="J61" s="26"/>
-      <c r="K61" s="26"/>
-      <c r="L61" s="26"/>
-      <c r="M61" s="26"/>
-      <c r="N61" s="26"/>
-      <c r="O61" s="26"/>
-      <c r="P61" s="26"/>
-      <c r="Q61" s="26"/>
+      <c r="B61" s="22"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="22"/>
+      <c r="I61" s="22"/>
+      <c r="J61" s="22"/>
+      <c r="K61" s="22"/>
+      <c r="L61" s="22"/>
+      <c r="M61" s="22"/>
+      <c r="N61" s="22"/>
+      <c r="O61" s="22"/>
+      <c r="P61" s="22"/>
+      <c r="Q61" s="22"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -10825,25 +10825,25 @@
       <c r="Q79" s="14"/>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="26" t="s">
+      <c r="A80" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="26"/>
-      <c r="C80" s="26"/>
-      <c r="D80" s="26"/>
-      <c r="E80" s="26"/>
-      <c r="F80" s="26"/>
-      <c r="G80" s="26"/>
-      <c r="H80" s="26"/>
-      <c r="I80" s="26"/>
-      <c r="J80" s="26"/>
-      <c r="K80" s="26"/>
-      <c r="L80" s="26"/>
-      <c r="M80" s="26"/>
-      <c r="N80" s="26"/>
-      <c r="O80" s="26"/>
-      <c r="P80" s="26"/>
-      <c r="Q80" s="26"/>
+      <c r="B80" s="22"/>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="F80" s="22"/>
+      <c r="G80" s="22"/>
+      <c r="H80" s="22"/>
+      <c r="I80" s="22"/>
+      <c r="J80" s="22"/>
+      <c r="K80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -11373,25 +11373,25 @@
       <c r="Q97" s="14"/>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="26" t="s">
+      <c r="A98" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="26"/>
-      <c r="C98" s="26"/>
-      <c r="D98" s="26"/>
-      <c r="E98" s="26"/>
-      <c r="F98" s="26"/>
-      <c r="G98" s="26"/>
-      <c r="H98" s="26"/>
-      <c r="I98" s="26"/>
-      <c r="J98" s="26"/>
-      <c r="K98" s="26"/>
-      <c r="L98" s="26"/>
-      <c r="M98" s="26"/>
-      <c r="N98" s="26"/>
-      <c r="O98" s="26"/>
-      <c r="P98" s="26"/>
-      <c r="Q98" s="26"/>
+      <c r="B98" s="22"/>
+      <c r="C98" s="22"/>
+      <c r="D98" s="22"/>
+      <c r="E98" s="22"/>
+      <c r="F98" s="22"/>
+      <c r="G98" s="22"/>
+      <c r="H98" s="22"/>
+      <c r="I98" s="22"/>
+      <c r="J98" s="22"/>
+      <c r="K98" s="22"/>
+      <c r="L98" s="22"/>
+      <c r="M98" s="22"/>
+      <c r="N98" s="22"/>
+      <c r="O98" s="22"/>
+      <c r="P98" s="22"/>
+      <c r="Q98" s="22"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -11891,25 +11891,25 @@
       <c r="Q114" s="14"/>
     </row>
     <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="26" t="s">
+      <c r="A115" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="26"/>
-      <c r="C115" s="26"/>
-      <c r="D115" s="26"/>
-      <c r="E115" s="26"/>
-      <c r="F115" s="26"/>
-      <c r="G115" s="26"/>
-      <c r="H115" s="26"/>
-      <c r="I115" s="26"/>
-      <c r="J115" s="26"/>
-      <c r="K115" s="26"/>
-      <c r="L115" s="26"/>
-      <c r="M115" s="26"/>
-      <c r="N115" s="26"/>
-      <c r="O115" s="26"/>
-      <c r="P115" s="26"/>
-      <c r="Q115" s="26"/>
+      <c r="B115" s="22"/>
+      <c r="C115" s="22"/>
+      <c r="D115" s="22"/>
+      <c r="E115" s="22"/>
+      <c r="F115" s="22"/>
+      <c r="G115" s="22"/>
+      <c r="H115" s="22"/>
+      <c r="I115" s="22"/>
+      <c r="J115" s="22"/>
+      <c r="K115" s="22"/>
+      <c r="L115" s="22"/>
+      <c r="M115" s="22"/>
+      <c r="N115" s="22"/>
+      <c r="O115" s="22"/>
+      <c r="P115" s="22"/>
+      <c r="Q115" s="22"/>
     </row>
     <row r="116" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -12409,25 +12409,25 @@
       <c r="Q131" s="14"/>
     </row>
     <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="26" t="s">
+      <c r="A132" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="B132" s="26"/>
-      <c r="C132" s="26"/>
-      <c r="D132" s="26"/>
-      <c r="E132" s="26"/>
-      <c r="F132" s="26"/>
-      <c r="G132" s="26"/>
-      <c r="H132" s="26"/>
-      <c r="I132" s="26"/>
-      <c r="J132" s="26"/>
-      <c r="K132" s="26"/>
-      <c r="L132" s="26"/>
-      <c r="M132" s="26"/>
-      <c r="N132" s="26"/>
-      <c r="O132" s="26"/>
-      <c r="P132" s="26"/>
-      <c r="Q132" s="26"/>
+      <c r="B132" s="22"/>
+      <c r="C132" s="22"/>
+      <c r="D132" s="22"/>
+      <c r="E132" s="22"/>
+      <c r="F132" s="22"/>
+      <c r="G132" s="22"/>
+      <c r="H132" s="22"/>
+      <c r="I132" s="22"/>
+      <c r="J132" s="22"/>
+      <c r="K132" s="22"/>
+      <c r="L132" s="22"/>
+      <c r="M132" s="22"/>
+      <c r="N132" s="22"/>
+      <c r="O132" s="22"/>
+      <c r="P132" s="22"/>
+      <c r="Q132" s="22"/>
     </row>
     <row r="133" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -12927,25 +12927,25 @@
       <c r="Q148" s="14"/>
     </row>
     <row r="149" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="26" t="s">
+      <c r="A149" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="B149" s="26"/>
-      <c r="C149" s="26"/>
-      <c r="D149" s="26"/>
-      <c r="E149" s="26"/>
-      <c r="F149" s="26"/>
-      <c r="G149" s="26"/>
-      <c r="H149" s="26"/>
-      <c r="I149" s="26"/>
-      <c r="J149" s="26"/>
-      <c r="K149" s="26"/>
-      <c r="L149" s="26"/>
-      <c r="M149" s="26"/>
-      <c r="N149" s="26"/>
-      <c r="O149" s="26"/>
-      <c r="P149" s="26"/>
-      <c r="Q149" s="26"/>
+      <c r="B149" s="22"/>
+      <c r="C149" s="22"/>
+      <c r="D149" s="22"/>
+      <c r="E149" s="22"/>
+      <c r="F149" s="22"/>
+      <c r="G149" s="22"/>
+      <c r="H149" s="22"/>
+      <c r="I149" s="22"/>
+      <c r="J149" s="22"/>
+      <c r="K149" s="22"/>
+      <c r="L149" s="22"/>
+      <c r="M149" s="22"/>
+      <c r="N149" s="22"/>
+      <c r="O149" s="22"/>
+      <c r="P149" s="22"/>
+      <c r="Q149" s="22"/>
     </row>
     <row r="150" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -13475,25 +13475,25 @@
       <c r="Q166" s="14"/>
     </row>
     <row r="167" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="26" t="s">
+      <c r="A167" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="B167" s="26"/>
-      <c r="C167" s="26"/>
-      <c r="D167" s="26"/>
-      <c r="E167" s="26"/>
-      <c r="F167" s="26"/>
-      <c r="G167" s="26"/>
-      <c r="H167" s="26"/>
-      <c r="I167" s="26"/>
-      <c r="J167" s="26"/>
-      <c r="K167" s="26"/>
-      <c r="L167" s="26"/>
-      <c r="M167" s="26"/>
-      <c r="N167" s="26"/>
-      <c r="O167" s="26"/>
-      <c r="P167" s="26"/>
-      <c r="Q167" s="26"/>
+      <c r="B167" s="22"/>
+      <c r="C167" s="22"/>
+      <c r="D167" s="22"/>
+      <c r="E167" s="22"/>
+      <c r="F167" s="22"/>
+      <c r="G167" s="22"/>
+      <c r="H167" s="22"/>
+      <c r="I167" s="22"/>
+      <c r="J167" s="22"/>
+      <c r="K167" s="22"/>
+      <c r="L167" s="22"/>
+      <c r="M167" s="22"/>
+      <c r="N167" s="22"/>
+      <c r="O167" s="22"/>
+      <c r="P167" s="22"/>
+      <c r="Q167" s="22"/>
     </row>
     <row r="168" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -13993,25 +13993,25 @@
       <c r="Q183" s="14"/>
     </row>
     <row r="184" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="26" t="s">
+      <c r="A184" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="B184" s="26"/>
-      <c r="C184" s="26"/>
-      <c r="D184" s="26"/>
-      <c r="E184" s="26"/>
-      <c r="F184" s="26"/>
-      <c r="G184" s="26"/>
-      <c r="H184" s="26"/>
-      <c r="I184" s="26"/>
-      <c r="J184" s="26"/>
-      <c r="K184" s="26"/>
-      <c r="L184" s="26"/>
-      <c r="M184" s="26"/>
-      <c r="N184" s="26"/>
-      <c r="O184" s="26"/>
-      <c r="P184" s="26"/>
-      <c r="Q184" s="26"/>
+      <c r="B184" s="22"/>
+      <c r="C184" s="22"/>
+      <c r="D184" s="22"/>
+      <c r="E184" s="22"/>
+      <c r="F184" s="22"/>
+      <c r="G184" s="22"/>
+      <c r="H184" s="22"/>
+      <c r="I184" s="22"/>
+      <c r="J184" s="22"/>
+      <c r="K184" s="22"/>
+      <c r="L184" s="22"/>
+      <c r="M184" s="22"/>
+      <c r="N184" s="22"/>
+      <c r="O184" s="22"/>
+      <c r="P184" s="22"/>
+      <c r="Q184" s="22"/>
     </row>
     <row r="185" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -14481,25 +14481,25 @@
       <c r="Q199" s="14"/>
     </row>
     <row r="200" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="26" t="s">
+      <c r="A200" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="B200" s="26"/>
-      <c r="C200" s="26"/>
-      <c r="D200" s="26"/>
-      <c r="E200" s="26"/>
-      <c r="F200" s="26"/>
-      <c r="G200" s="26"/>
-      <c r="H200" s="26"/>
-      <c r="I200" s="26"/>
-      <c r="J200" s="26"/>
-      <c r="K200" s="26"/>
-      <c r="L200" s="26"/>
-      <c r="M200" s="26"/>
-      <c r="N200" s="26"/>
-      <c r="O200" s="26"/>
-      <c r="P200" s="26"/>
-      <c r="Q200" s="26"/>
+      <c r="B200" s="22"/>
+      <c r="C200" s="22"/>
+      <c r="D200" s="22"/>
+      <c r="E200" s="22"/>
+      <c r="F200" s="22"/>
+      <c r="G200" s="22"/>
+      <c r="H200" s="22"/>
+      <c r="I200" s="22"/>
+      <c r="J200" s="22"/>
+      <c r="K200" s="22"/>
+      <c r="L200" s="22"/>
+      <c r="M200" s="22"/>
+      <c r="N200" s="22"/>
+      <c r="O200" s="22"/>
+      <c r="P200" s="22"/>
+      <c r="Q200" s="22"/>
     </row>
     <row r="201" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -15059,25 +15059,25 @@
       <c r="Q218" s="14"/>
     </row>
     <row r="219" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="26" t="s">
+      <c r="A219" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="B219" s="26"/>
-      <c r="C219" s="26"/>
-      <c r="D219" s="26"/>
-      <c r="E219" s="26"/>
-      <c r="F219" s="26"/>
-      <c r="G219" s="26"/>
-      <c r="H219" s="26"/>
-      <c r="I219" s="26"/>
-      <c r="J219" s="26"/>
-      <c r="K219" s="26"/>
-      <c r="L219" s="26"/>
-      <c r="M219" s="26"/>
-      <c r="N219" s="26"/>
-      <c r="O219" s="26"/>
-      <c r="P219" s="26"/>
-      <c r="Q219" s="26"/>
+      <c r="B219" s="22"/>
+      <c r="C219" s="22"/>
+      <c r="D219" s="22"/>
+      <c r="E219" s="22"/>
+      <c r="F219" s="22"/>
+      <c r="G219" s="22"/>
+      <c r="H219" s="22"/>
+      <c r="I219" s="22"/>
+      <c r="J219" s="22"/>
+      <c r="K219" s="22"/>
+      <c r="L219" s="22"/>
+      <c r="M219" s="22"/>
+      <c r="N219" s="22"/>
+      <c r="O219" s="22"/>
+      <c r="P219" s="22"/>
+      <c r="Q219" s="22"/>
     </row>
     <row r="220" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -15577,25 +15577,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="26" t="s">
+      <c r="A236" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="B236" s="26"/>
-      <c r="C236" s="26"/>
-      <c r="D236" s="26"/>
-      <c r="E236" s="26"/>
-      <c r="F236" s="26"/>
-      <c r="G236" s="26"/>
-      <c r="H236" s="26"/>
-      <c r="I236" s="26"/>
-      <c r="J236" s="26"/>
-      <c r="K236" s="26"/>
-      <c r="L236" s="26"/>
-      <c r="M236" s="26"/>
-      <c r="N236" s="26"/>
-      <c r="O236" s="26"/>
-      <c r="P236" s="26"/>
-      <c r="Q236" s="26"/>
+      <c r="B236" s="22"/>
+      <c r="C236" s="22"/>
+      <c r="D236" s="22"/>
+      <c r="E236" s="22"/>
+      <c r="F236" s="22"/>
+      <c r="G236" s="22"/>
+      <c r="H236" s="22"/>
+      <c r="I236" s="22"/>
+      <c r="J236" s="22"/>
+      <c r="K236" s="22"/>
+      <c r="L236" s="22"/>
+      <c r="M236" s="22"/>
+      <c r="N236" s="22"/>
+      <c r="O236" s="22"/>
+      <c r="P236" s="22"/>
+      <c r="Q236" s="22"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -16125,25 +16125,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="26" t="s">
+      <c r="A254" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="B254" s="26"/>
-      <c r="C254" s="26"/>
-      <c r="D254" s="26"/>
-      <c r="E254" s="26"/>
-      <c r="F254" s="26"/>
-      <c r="G254" s="26"/>
-      <c r="H254" s="26"/>
-      <c r="I254" s="26"/>
-      <c r="J254" s="26"/>
-      <c r="K254" s="26"/>
-      <c r="L254" s="26"/>
-      <c r="M254" s="26"/>
-      <c r="N254" s="26"/>
-      <c r="O254" s="26"/>
-      <c r="P254" s="26"/>
-      <c r="Q254" s="26"/>
+      <c r="B254" s="22"/>
+      <c r="C254" s="22"/>
+      <c r="D254" s="22"/>
+      <c r="E254" s="22"/>
+      <c r="F254" s="22"/>
+      <c r="G254" s="22"/>
+      <c r="H254" s="22"/>
+      <c r="I254" s="22"/>
+      <c r="J254" s="22"/>
+      <c r="K254" s="22"/>
+      <c r="L254" s="22"/>
+      <c r="M254" s="22"/>
+      <c r="N254" s="22"/>
+      <c r="O254" s="22"/>
+      <c r="P254" s="22"/>
+      <c r="Q254" s="22"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -16703,25 +16703,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="26" t="s">
+      <c r="A273" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="B273" s="26"/>
-      <c r="C273" s="26"/>
-      <c r="D273" s="26"/>
-      <c r="E273" s="26"/>
-      <c r="F273" s="26"/>
-      <c r="G273" s="26"/>
-      <c r="H273" s="26"/>
-      <c r="I273" s="26"/>
-      <c r="J273" s="26"/>
-      <c r="K273" s="26"/>
-      <c r="L273" s="26"/>
-      <c r="M273" s="26"/>
-      <c r="N273" s="26"/>
-      <c r="O273" s="26"/>
-      <c r="P273" s="26"/>
-      <c r="Q273" s="26"/>
+      <c r="B273" s="22"/>
+      <c r="C273" s="22"/>
+      <c r="D273" s="22"/>
+      <c r="E273" s="22"/>
+      <c r="F273" s="22"/>
+      <c r="G273" s="22"/>
+      <c r="H273" s="22"/>
+      <c r="I273" s="22"/>
+      <c r="J273" s="22"/>
+      <c r="K273" s="22"/>
+      <c r="L273" s="22"/>
+      <c r="M273" s="22"/>
+      <c r="N273" s="22"/>
+      <c r="O273" s="22"/>
+      <c r="P273" s="22"/>
+      <c r="Q273" s="22"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -17281,25 +17281,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="26" t="s">
+      <c r="A292" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="B292" s="26"/>
-      <c r="C292" s="26"/>
-      <c r="D292" s="26"/>
-      <c r="E292" s="26"/>
-      <c r="F292" s="26"/>
-      <c r="G292" s="26"/>
-      <c r="H292" s="26"/>
-      <c r="I292" s="26"/>
-      <c r="J292" s="26"/>
-      <c r="K292" s="26"/>
-      <c r="L292" s="26"/>
-      <c r="M292" s="26"/>
-      <c r="N292" s="26"/>
-      <c r="O292" s="26"/>
-      <c r="P292" s="26"/>
-      <c r="Q292" s="26"/>
+      <c r="B292" s="22"/>
+      <c r="C292" s="22"/>
+      <c r="D292" s="22"/>
+      <c r="E292" s="22"/>
+      <c r="F292" s="22"/>
+      <c r="G292" s="22"/>
+      <c r="H292" s="22"/>
+      <c r="I292" s="22"/>
+      <c r="J292" s="22"/>
+      <c r="K292" s="22"/>
+      <c r="L292" s="22"/>
+      <c r="M292" s="22"/>
+      <c r="N292" s="22"/>
+      <c r="O292" s="22"/>
+      <c r="P292" s="22"/>
+      <c r="Q292" s="22"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -17859,25 +17859,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="26" t="s">
+      <c r="A311" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="B311" s="26"/>
-      <c r="C311" s="26"/>
-      <c r="D311" s="26"/>
-      <c r="E311" s="26"/>
-      <c r="F311" s="26"/>
-      <c r="G311" s="26"/>
-      <c r="H311" s="26"/>
-      <c r="I311" s="26"/>
-      <c r="J311" s="26"/>
-      <c r="K311" s="26"/>
-      <c r="L311" s="26"/>
-      <c r="M311" s="26"/>
-      <c r="N311" s="26"/>
-      <c r="O311" s="26"/>
-      <c r="P311" s="26"/>
-      <c r="Q311" s="26"/>
+      <c r="B311" s="22"/>
+      <c r="C311" s="22"/>
+      <c r="D311" s="22"/>
+      <c r="E311" s="22"/>
+      <c r="F311" s="22"/>
+      <c r="G311" s="22"/>
+      <c r="H311" s="22"/>
+      <c r="I311" s="22"/>
+      <c r="J311" s="22"/>
+      <c r="K311" s="22"/>
+      <c r="L311" s="22"/>
+      <c r="M311" s="22"/>
+      <c r="N311" s="22"/>
+      <c r="O311" s="22"/>
+      <c r="P311" s="22"/>
+      <c r="Q311" s="22"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -18438,26 +18438,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A23:Q23"/>
+    <mergeCell ref="A42:Q42"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="A132:Q132"/>
+    <mergeCell ref="A149:Q149"/>
+    <mergeCell ref="A167:Q167"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A219:Q219"/>
     <mergeCell ref="A236:Q236"/>
     <mergeCell ref="A254:Q254"/>
     <mergeCell ref="A273:Q273"/>
     <mergeCell ref="A292:Q292"/>
     <mergeCell ref="A311:Q311"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A167:Q167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="A23:Q23"/>
-    <mergeCell ref="A42:Q42"/>
   </mergeCells>
   <dataValidations count="268">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or SEA" promptTitle="ATS Pick" prompt="Pick NE or SEA" sqref="F6:Q6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -27980,17 +27980,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -30813,17 +30813,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -33646,17 +33646,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -36479,19 +36479,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -36546,7 +36546,7 @@
       </c>
       <c r="E3">
         <f>Helper!E2</f>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <f>Helper!F2</f>
@@ -36562,15 +36562,15 @@
       </c>
       <c r="I3">
         <f>Helper!I2</f>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J3">
         <f>Helper!J2</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <f>MAX(Helper!C2:H2)</f>
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36591,7 +36591,7 @@
       </c>
       <c r="E4">
         <f>Helper!E3</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F4">
         <f>Helper!F3</f>
@@ -36607,11 +36607,11 @@
       </c>
       <c r="I4">
         <f>Helper!I3</f>
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J4">
         <f>Helper!J3</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4">
         <f>MAX(Helper!C3:H3)</f>
@@ -36636,7 +36636,7 @@
       </c>
       <c r="E5">
         <f>Helper!E4</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F5">
         <f>Helper!F4</f>
@@ -36652,11 +36652,11 @@
       </c>
       <c r="I5">
         <f>Helper!I4</f>
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J5">
         <f>Helper!J4</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5">
         <f>MAX(Helper!C4:H4)</f>
@@ -36726,7 +36726,7 @@
       </c>
       <c r="E7">
         <f>Helper!E6</f>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F7">
         <f>Helper!F6</f>
@@ -36742,11 +36742,11 @@
       </c>
       <c r="I7">
         <f>Helper!I6</f>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J7">
         <f>Helper!J6</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7">
         <f>MAX(Helper!C6:H6)</f>
@@ -36771,7 +36771,7 @@
       </c>
       <c r="E8">
         <f>Helper!E7</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F8">
         <f>Helper!F7</f>
@@ -36787,11 +36787,11 @@
       </c>
       <c r="I8">
         <f>Helper!I7</f>
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J8">
         <f>Helper!J7</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8">
         <f>MAX(Helper!C7:H7)</f>
@@ -37041,7 +37041,7 @@
       </c>
       <c r="E14">
         <f>Helper!E13</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F14">
         <f>Helper!F13</f>
@@ -37057,11 +37057,11 @@
       </c>
       <c r="I14">
         <f>Helper!I13</f>
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J14">
         <f>Helper!J13</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14">
         <f>MAX(Helper!C13:H13)</f>
@@ -38381,7 +38381,7 @@
       </c>
       <c r="C57">
         <f>Helper!I2</f>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D57">
         <f>Helper!R2</f>
@@ -38393,11 +38393,11 @@
       </c>
       <c r="F57">
         <f>Helper!AE2</f>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G57">
         <f>Helper!K2</f>
-        <v>31.0001</v>
+        <v>37.000100000000003</v>
       </c>
       <c r="H57">
         <f>Helper!T2</f>
@@ -38414,7 +38414,7 @@
       </c>
       <c r="C58">
         <f>Helper!I3</f>
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D58">
         <f>Helper!R3</f>
@@ -38426,11 +38426,11 @@
       </c>
       <c r="F58">
         <f>Helper!AE3</f>
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G58">
         <f>Helper!K3</f>
-        <v>29.0002</v>
+        <v>35.0002</v>
       </c>
       <c r="H58">
         <f>Helper!T3</f>
@@ -38447,7 +38447,7 @@
       </c>
       <c r="C59">
         <f>Helper!I4</f>
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D59">
         <f>Helper!R4</f>
@@ -38459,11 +38459,11 @@
       </c>
       <c r="F59">
         <f>Helper!AE4</f>
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G59">
         <f>Helper!K4</f>
-        <v>28.000299999999999</v>
+        <v>34.000300000000003</v>
       </c>
       <c r="H59">
         <f>Helper!T4</f>
@@ -38513,7 +38513,7 @@
       </c>
       <c r="C61">
         <f>Helper!I6</f>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D61">
         <f>Helper!R6</f>
@@ -38525,11 +38525,11 @@
       </c>
       <c r="F61">
         <f>Helper!AE6</f>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G61">
         <f>Helper!K6</f>
-        <v>31.000499999999999</v>
+        <v>37.000500000000002</v>
       </c>
       <c r="H61">
         <f>Helper!T6</f>
@@ -38546,7 +38546,7 @@
       </c>
       <c r="C62">
         <f>Helper!I7</f>
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D62">
         <f>Helper!R7</f>
@@ -38558,11 +38558,11 @@
       </c>
       <c r="F62">
         <f>Helper!AE7</f>
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G62">
         <f>Helper!K7</f>
-        <v>27.000599999999999</v>
+        <v>33.000599999999999</v>
       </c>
       <c r="H62">
         <f>Helper!T7</f>
@@ -38744,7 +38744,7 @@
       </c>
       <c r="C68">
         <f>Helper!I13</f>
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D68">
         <f>Helper!R13</f>
@@ -38756,11 +38756,11 @@
       </c>
       <c r="F68">
         <f>Helper!AE13</f>
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G68">
         <f>Helper!K13</f>
-        <v>25.001200000000001</v>
+        <v>31.001200000000001</v>
       </c>
       <c r="H68">
         <f>Helper!T13</f>
@@ -38830,7 +38830,7 @@
       </c>
       <c r="B5" t="str">
         <f>INDEX(Helper!B$2:B$13,MATCH(MAX(Helper!K$2:K$13),Helper!K$2:K$13,0))</f>
-        <v>Jeffrey Loeser</v>
+        <v>Mikayla Simmons</v>
       </c>
       <c r="C5" t="s">
         <v>252</v>
@@ -38840,7 +38840,7 @@
       </c>
       <c r="E5" t="str">
         <f>B5</f>
-        <v>Jeffrey Loeser</v>
+        <v>Mikayla Simmons</v>
       </c>
       <c r="F5" t="str">
         <f>IF(B5="","—","QUALIFIED")</f>
@@ -38948,11 +38948,11 @@
       </c>
       <c r="E9" t="str">
         <f>IF(AND(H13&lt;&gt;$E$5,H13&lt;&gt;$E$6,H13&lt;&gt;$E$7,H13&lt;&gt;$E$8),H13,IF(AND(H14&lt;&gt;$E$5,H14&lt;&gt;$E$6,H14&lt;&gt;$E$7,H14&lt;&gt;$E$8),H14,IF(AND(H15&lt;&gt;$E$5,H15&lt;&gt;$E$6,H15&lt;&gt;$E$7,H15&lt;&gt;$E$8),H15,H16)))</f>
-        <v>Zach Zarra</v>
+        <v>Jeffrey Loeser</v>
       </c>
       <c r="F9" t="str">
         <f>IF(E9=B9,"QUALIFIED","PASS → "&amp;E9)</f>
-        <v>PASS → Zach Zarra</v>
+        <v>PASS → Jeffrey Loeser</v>
       </c>
       <c r="H9" t="str">
         <f>INDEX(Helper!B$6:B$9,MATCH(LARGE(Helper!AD$6:AD$9,1),Helper!AD$6:AD$9,0))</f>
@@ -38998,11 +38998,11 @@
       </c>
       <c r="B13" t="str">
         <f>INDEX(H$40:H$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
-        <v>Mikayla Simmons</v>
+        <v>Evan Loeser</v>
       </c>
       <c r="C13">
         <f>INDEX(I$40:I$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
         <v>263</v>
@@ -39048,7 +39048,7 @@
       </c>
       <c r="B17" t="str">
         <f>E5</f>
-        <v>Jeffrey Loeser</v>
+        <v>Mikayla Simmons</v>
       </c>
       <c r="C17" t="str">
         <f>D5</f>
@@ -39100,7 +39100,7 @@
       </c>
       <c r="B21" t="str">
         <f>E9</f>
-        <v>Zach Zarra</v>
+        <v>Jeffrey Loeser</v>
       </c>
       <c r="C21" t="str">
         <f>"Div C"</f>
@@ -39113,7 +39113,7 @@
       </c>
       <c r="B22" t="str">
         <f>B13</f>
-        <v>Mikayla Simmons</v>
+        <v>Evan Loeser</v>
       </c>
       <c r="C22" t="str">
         <f>"Wild Card 1"</f>
@@ -39478,7 +39478,7 @@
       </c>
       <c r="I40">
         <f>Helper!AE2</f>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J40" t="b">
         <f t="shared" ref="J40:J51" si="1">OR(H40=$E$5,H40=$E$6,H40=$E$7,H40=$E$8,H40=$E$9)</f>
@@ -39486,7 +39486,7 @@
       </c>
       <c r="K40">
         <f>IF(J40,-1,I40+0.00001)</f>
-        <v>31.00001</v>
+        <v>37.000010000000003</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39496,7 +39496,7 @@
       </c>
       <c r="I41">
         <f>Helper!AE3</f>
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J41" t="b">
         <f t="shared" si="1"/>
@@ -39504,7 +39504,7 @@
       </c>
       <c r="K41">
         <f>IF(J41,-1,I41+0.00002)</f>
-        <v>29.000019999999999</v>
+        <v>35.000019999999999</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39514,7 +39514,7 @@
       </c>
       <c r="I42">
         <f>Helper!AE4</f>
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J42" t="b">
         <f t="shared" si="1"/>
@@ -39522,7 +39522,7 @@
       </c>
       <c r="K42">
         <f>IF(J42,-1,I42+0.00003)</f>
-        <v>28.000029999999999</v>
+        <v>34.000030000000002</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39550,15 +39550,15 @@
       </c>
       <c r="I44">
         <f>Helper!AE6</f>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J44" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44">
         <f>IF(J44,-1,I44+0.00005)</f>
-        <v>31.000050000000002</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39568,7 +39568,7 @@
       </c>
       <c r="I45">
         <f>Helper!AE7</f>
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J45" t="b">
         <f t="shared" si="1"/>
@@ -39576,7 +39576,7 @@
       </c>
       <c r="K45">
         <f>IF(J45,-1,I45+0.00006)</f>
-        <v>27.000060000000001</v>
+        <v>33.000059999999998</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39644,11 +39644,11 @@
       </c>
       <c r="J49" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49">
         <f>IF(J49,-1,I49+0.0001)</f>
-        <v>-1</v>
+        <v>36.000100000000003</v>
       </c>
     </row>
     <row r="50" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39676,7 +39676,7 @@
       </c>
       <c r="I51">
         <f>Helper!AE13</f>
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J51" t="b">
         <f t="shared" si="1"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="550" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2EF102E-CD51-419E-89CE-ADB3D724697C}"/>
+  <xr:revisionPtr revIDLastSave="783" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FFA0CC4-573D-467C-801F-A1805DD1329C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3773" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3953" uniqueCount="346">
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -1377,13 +1377,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1470,10 +1470,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1665,12 +1661,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1926,7 +1922,7 @@
       </c>
       <c r="B5" t="str">
         <f>'Playoff Picture'!B17</f>
-        <v>Mikayla Simmons</v>
+        <v>Evan Loeser</v>
       </c>
       <c r="C5" s="3">
         <v>6</v>
@@ -2071,7 +2067,7 @@
       </c>
       <c r="B10" t="str">
         <f>'Playoff Picture'!B22</f>
-        <v>Evan Loeser</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
@@ -2120,7 +2116,7 @@
       </c>
       <c r="B14" t="str">
         <f>INDEX($B$5:$B$10,MATCH(LARGE($H$5:$H$10,1),$H$5:$H$10,0))</f>
-        <v>Mikayla Simmons</v>
+        <v>Evan Loeser</v>
       </c>
       <c r="C14">
         <f>INDEX($C$5:$C$10,MATCH(LARGE($H$5:$H$10,1),$H$5:$H$10,0))</f>
@@ -2205,7 +2201,7 @@
       </c>
       <c r="B19" t="str">
         <f>INDEX($B$5:$B$10,MATCH(LARGE($H$5:$H$10,6),$H$5:$H$10,0))</f>
-        <v>Evan Loeser</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="C19">
         <f>INDEX($C$5:$C$10,MATCH(LARGE($H$5:$H$10,6),$H$5:$H$10,0))</f>
@@ -2281,7 +2277,7 @@
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>'Playoff Wild Card'!B14</f>
-        <v>Mikayla Simmons</v>
+        <v>Evan Loeser</v>
       </c>
       <c r="B6">
         <f>'Playoff Wild Card'!C14</f>
@@ -2483,7 +2479,7 @@
       </c>
       <c r="B13" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>Mikayla Simmons</v>
+        <v>Evan Loeser</v>
       </c>
       <c r="C13">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
@@ -2632,7 +2628,7 @@
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>A6</f>
-        <v>Mikayla Simmons</v>
+        <v>Evan Loeser</v>
       </c>
       <c r="B22" s="3">
         <v>0</v>
@@ -2857,7 +2853,7 @@
       </c>
       <c r="F2">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H51,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G51,0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G2">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H66,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G66,0)</f>
@@ -2869,7 +2865,7 @@
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I13" si="0">SUM(C2:H2)</f>
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="J2">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F6="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F21="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F36="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F51="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F66="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F81="W"),1,0)</f>
@@ -2877,7 +2873,7 @@
       </c>
       <c r="K2">
         <f>I2+0.0001</f>
-        <v>37.000100000000003</v>
+        <v>44.000100000000003</v>
       </c>
       <c r="L2">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H6,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G6,0)</f>
@@ -2957,11 +2953,11 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE13" si="2">I2+R2+AC2</f>
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AF2">
         <f>AE2+0.0001</f>
-        <v>37.000100000000003</v>
+        <v>44.000100000000003</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2986,7 +2982,7 @@
       </c>
       <c r="F3">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H52,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G52,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G3">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H67,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G67,0)</f>
@@ -2998,7 +2994,7 @@
       </c>
       <c r="I3">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J3">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F7="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F22="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F37="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F52="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F67="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F82="W"),1,0)</f>
@@ -3006,7 +3002,7 @@
       </c>
       <c r="K3">
         <f>I3+0.0002</f>
-        <v>35.0002</v>
+        <v>41.0002</v>
       </c>
       <c r="L3">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H7,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G7,0)</f>
@@ -3086,11 +3082,11 @@
       </c>
       <c r="AE3">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="AF3">
         <f>AE3+0.0002</f>
-        <v>35.0002</v>
+        <v>41.0002</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3115,7 +3111,7 @@
       </c>
       <c r="F4">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H53,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G53,0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G4">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H68,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G68,0)</f>
@@ -3127,7 +3123,7 @@
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="J4">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F8="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F23="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F38="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F53="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F68="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F83="W"),1,0)</f>
@@ -3135,7 +3131,7 @@
       </c>
       <c r="K4">
         <f>I4+0.0003</f>
-        <v>34.000300000000003</v>
+        <v>42.000300000000003</v>
       </c>
       <c r="L4">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H8,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G8,0)</f>
@@ -3215,11 +3211,11 @@
       </c>
       <c r="AE4">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AF4">
         <f>AE4+0.0003</f>
-        <v>34.000300000000003</v>
+        <v>42.000300000000003</v>
       </c>
     </row>
     <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3244,7 +3240,7 @@
       </c>
       <c r="F5">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H54,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G54,0)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H69,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G69,0)</f>
@@ -3256,7 +3252,7 @@
       </c>
       <c r="I5">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J5">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F9="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F24="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F39="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F54="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F69="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F84="W"),1,0)</f>
@@ -3264,7 +3260,7 @@
       </c>
       <c r="K5">
         <f>I5+0.0004</f>
-        <v>20.000399999999999</v>
+        <v>31.000399999999999</v>
       </c>
       <c r="L5">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H9,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G9,0)</f>
@@ -3344,11 +3340,11 @@
       </c>
       <c r="AE5">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="AF5">
         <f>AE5+0.0004</f>
-        <v>20.000399999999999</v>
+        <v>31.000399999999999</v>
       </c>
     </row>
     <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3373,7 +3369,7 @@
       </c>
       <c r="F6">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H55,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G55,0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H70,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G70,0)</f>
@@ -3385,7 +3381,7 @@
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J6">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F10="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F25="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F40="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F55="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F70="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F85="W"),1,0)</f>
@@ -3393,7 +3389,7 @@
       </c>
       <c r="K6">
         <f>I6+0.0005</f>
-        <v>37.000500000000002</v>
+        <v>42.000500000000002</v>
       </c>
       <c r="L6">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H10,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G10,0)</f>
@@ -3473,11 +3469,11 @@
       </c>
       <c r="AE6">
         <f t="shared" si="2"/>
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AF6">
         <f>AE6+0.0005</f>
-        <v>37.000500000000002</v>
+        <v>42.000500000000002</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3502,7 +3498,7 @@
       </c>
       <c r="F7">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H56,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G56,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G7">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H71,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G71,0)</f>
@@ -3514,7 +3510,7 @@
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J7">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F11="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F26="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F41="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F56="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F71="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F86="W"),1,0)</f>
@@ -3522,7 +3518,7 @@
       </c>
       <c r="K7">
         <f>I7+0.0006</f>
-        <v>33.000599999999999</v>
+        <v>39.000599999999999</v>
       </c>
       <c r="L7">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H11,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G11,0)</f>
@@ -3602,11 +3598,11 @@
       </c>
       <c r="AE7">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="AF7">
         <f>AE7+0.0006</f>
-        <v>33.000599999999999</v>
+        <v>39.000599999999999</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3631,7 +3627,7 @@
       </c>
       <c r="F8">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H57,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G57,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G8">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H72,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G72,0)</f>
@@ -3643,7 +3639,7 @@
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J8">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F12="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F27="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F42="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F57="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F72="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F87="W"),1,0)</f>
@@ -3651,7 +3647,7 @@
       </c>
       <c r="K8">
         <f>I8+0.0007</f>
-        <v>27.000699999999998</v>
+        <v>33.000700000000002</v>
       </c>
       <c r="L8">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H12,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G12,0)</f>
@@ -3731,11 +3727,11 @@
       </c>
       <c r="AE8">
         <f t="shared" si="2"/>
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="AF8">
         <f>AE8+0.0007</f>
-        <v>27.000699999999998</v>
+        <v>33.000700000000002</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3760,7 +3756,7 @@
       </c>
       <c r="F9">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H58,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G58,0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G9">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H73,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G73,0)</f>
@@ -3772,7 +3768,7 @@
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J9">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F13="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F28="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F43="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F58="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F73="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F88="W"),1,0)</f>
@@ -3780,7 +3776,7 @@
       </c>
       <c r="K9">
         <f>I9+0.0008</f>
-        <v>19.000800000000002</v>
+        <v>26.000800000000002</v>
       </c>
       <c r="L9">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H13,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G13,0)</f>
@@ -3860,11 +3856,11 @@
       </c>
       <c r="AE9">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AF9">
         <f>AE9+0.0008</f>
-        <v>19.000800000000002</v>
+        <v>26.000800000000002</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3889,7 +3885,7 @@
       </c>
       <c r="F10">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H59,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G59,0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G10">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H74,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G74,0)</f>
@@ -3901,7 +3897,7 @@
       </c>
       <c r="I10">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J10">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F14="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F29="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F44="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F59="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F74="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F89="W"),1,0)</f>
@@ -3909,7 +3905,7 @@
       </c>
       <c r="K10">
         <f>I10+0.0009</f>
-        <v>23.000900000000001</v>
+        <v>30.000900000000001</v>
       </c>
       <c r="L10">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H14,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G14,0)</f>
@@ -3989,11 +3985,11 @@
       </c>
       <c r="AE10">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AF10">
         <f>AE10+0.0009</f>
-        <v>23.000900000000001</v>
+        <v>30.000900000000001</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4018,7 +4014,7 @@
       </c>
       <c r="F11">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H60,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G60,0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G11">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H75,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G75,0)</f>
@@ -4030,7 +4026,7 @@
       </c>
       <c r="I11">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J11">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F15="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F30="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F45="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F60="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F75="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F90="W"),1,0)</f>
@@ -4038,7 +4034,7 @@
       </c>
       <c r="K11">
         <f>I11+0.001</f>
-        <v>36.000999999999998</v>
+        <v>43.000999999999998</v>
       </c>
       <c r="L11">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H15,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G15,0)</f>
@@ -4118,11 +4114,11 @@
       </c>
       <c r="AE11">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="AF11">
         <f>AE11+0.001</f>
-        <v>36.000999999999998</v>
+        <v>43.000999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4147,7 +4143,7 @@
       </c>
       <c r="F12">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H61,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G61,0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G12">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H76,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G76,0)</f>
@@ -4159,7 +4155,7 @@
       </c>
       <c r="I12">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J12">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F16="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F31="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F46="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F61="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F76="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F91="W"),1,0)</f>
@@ -4167,7 +4163,7 @@
       </c>
       <c r="K12">
         <f>I12+0.0011</f>
-        <v>36.001100000000001</v>
+        <v>43.001100000000001</v>
       </c>
       <c r="L12">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H16,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G16,0)</f>
@@ -4247,11 +4243,11 @@
       </c>
       <c r="AE12">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="AF12">
         <f>AE12+0.0011</f>
-        <v>36.001100000000001</v>
+        <v>43.001100000000001</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4276,7 +4272,7 @@
       </c>
       <c r="F13">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H62,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G62,0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G13">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H77,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G77,0)</f>
@@ -4288,7 +4284,7 @@
       </c>
       <c r="I13">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J13">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F17="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F32="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F47="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F62="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F77="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F92="W"),1,0)</f>
@@ -4296,7 +4292,7 @@
       </c>
       <c r="K13">
         <f>I13+0.0012</f>
-        <v>31.001200000000001</v>
+        <v>38.001199999999997</v>
       </c>
       <c r="L13">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H17,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G17,0)</f>
@@ -4376,11 +4372,11 @@
       </c>
       <c r="AE13">
         <f t="shared" si="2"/>
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="AF13">
         <f>AE13+0.0012</f>
-        <v>31.001200000000001</v>
+        <v>38.001199999999997</v>
       </c>
     </row>
   </sheetData>
@@ -4402,14 +4398,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -5354,14 +5350,14 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="26" t="s">
+      <c r="A56" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="26"/>
-      <c r="C56" s="26"/>
-      <c r="D56" s="26"/>
-      <c r="E56" s="26"/>
-      <c r="F56" s="26"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
@@ -6306,14 +6302,14 @@
       </c>
     </row>
     <row r="111" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="26" t="s">
+      <c r="A111" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B111" s="26"/>
-      <c r="C111" s="26"/>
-      <c r="D111" s="26"/>
-      <c r="E111" s="26"/>
-      <c r="F111" s="26"/>
+      <c r="B111" s="23"/>
+      <c r="C111" s="23"/>
+      <c r="D111" s="23"/>
+      <c r="E111" s="23"/>
+      <c r="F111" s="23"/>
     </row>
     <row r="112" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
@@ -7285,67 +7281,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8313,25 +8309,25 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="22"/>
-      <c r="O23" s="22"/>
-      <c r="P23" s="22"/>
-      <c r="Q23" s="22"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -9299,25 +9295,25 @@
       </c>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="22" t="s">
+      <c r="A42" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="22"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="22"/>
-      <c r="I42" s="22"/>
-      <c r="J42" s="22"/>
-      <c r="K42" s="22"/>
-      <c r="L42" s="22"/>
-      <c r="M42" s="22"/>
-      <c r="N42" s="22"/>
-      <c r="O42" s="22"/>
-      <c r="P42" s="22"/>
-      <c r="Q42" s="22"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="26"/>
+      <c r="Q42" s="26"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -10247,25 +10243,25 @@
       </c>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="22" t="s">
+      <c r="A61" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="22"/>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="22"/>
-      <c r="H61" s="22"/>
-      <c r="I61" s="22"/>
-      <c r="J61" s="22"/>
-      <c r="K61" s="22"/>
-      <c r="L61" s="22"/>
-      <c r="M61" s="22"/>
-      <c r="N61" s="22"/>
-      <c r="O61" s="22"/>
-      <c r="P61" s="22"/>
-      <c r="Q61" s="22"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="26"/>
+      <c r="J61" s="26"/>
+      <c r="K61" s="26"/>
+      <c r="L61" s="26"/>
+      <c r="M61" s="26"/>
+      <c r="N61" s="26"/>
+      <c r="O61" s="26"/>
+      <c r="P61" s="26"/>
+      <c r="Q61" s="26"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -10335,20 +10331,44 @@
       </c>
       <c r="E63" s="9" t="str">
         <f>'NFL Schedule'!J60</f>
-        <v/>
-      </c>
-      <c r="F63" s="10"/>
-      <c r="G63" s="10"/>
-      <c r="H63" s="10"/>
-      <c r="I63" s="10"/>
-      <c r="J63" s="10"/>
-      <c r="K63" s="10"/>
-      <c r="L63" s="10"/>
-      <c r="M63" s="10"/>
-      <c r="N63" s="10"/>
-      <c r="O63" s="10"/>
-      <c r="P63" s="10"/>
-      <c r="Q63" s="10"/>
+        <v>CLE</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="G63" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I63" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="J63" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K63" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="L63" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="M63" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="N63" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="O63" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="P63" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q63" s="10" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="64" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="7">
@@ -10365,20 +10385,44 @@
       </c>
       <c r="E64" s="9" t="str">
         <f>'NFL Schedule'!J61</f>
-        <v/>
-      </c>
-      <c r="F64" s="10"/>
-      <c r="G64" s="10"/>
-      <c r="H64" s="10"/>
-      <c r="I64" s="10"/>
-      <c r="J64" s="10"/>
-      <c r="K64" s="10"/>
-      <c r="L64" s="10"/>
-      <c r="M64" s="10"/>
-      <c r="N64" s="10"/>
-      <c r="O64" s="10"/>
-      <c r="P64" s="10"/>
-      <c r="Q64" s="10"/>
+        <v>IND</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="G64" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H64" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I64" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J64" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K64" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="L64" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="M64" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="N64" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="O64" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="P64" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q64" s="10" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="65" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="7">
@@ -10395,20 +10439,44 @@
       </c>
       <c r="E65" s="9" t="str">
         <f>'NFL Schedule'!J62</f>
-        <v/>
-      </c>
-      <c r="F65" s="10"/>
-      <c r="G65" s="10"/>
-      <c r="H65" s="10"/>
-      <c r="I65" s="10"/>
-      <c r="J65" s="10"/>
-      <c r="K65" s="10"/>
-      <c r="L65" s="10"/>
-      <c r="M65" s="10"/>
-      <c r="N65" s="10"/>
-      <c r="O65" s="10"/>
-      <c r="P65" s="10"/>
-      <c r="Q65" s="10"/>
+        <v>NE</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G65" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H65" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="I65" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="J65" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K65" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="L65" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="M65" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="N65" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="O65" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P65" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q65" s="10" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="66" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="7">
@@ -10425,20 +10493,44 @@
       </c>
       <c r="E66" s="9" t="str">
         <f>'NFL Schedule'!J63</f>
-        <v/>
-      </c>
-      <c r="F66" s="10"/>
-      <c r="G66" s="10"/>
-      <c r="H66" s="10"/>
-      <c r="I66" s="10"/>
-      <c r="J66" s="10"/>
-      <c r="K66" s="10"/>
-      <c r="L66" s="10"/>
-      <c r="M66" s="10"/>
-      <c r="N66" s="10"/>
-      <c r="O66" s="10"/>
-      <c r="P66" s="10"/>
-      <c r="Q66" s="10"/>
+        <v>CHI</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="G66" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H66" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I66" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="J66" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K66" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="L66" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M66" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="N66" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="O66" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="P66" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q66" s="10" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="67" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="7">
@@ -10455,20 +10547,44 @@
       </c>
       <c r="E67" s="9" t="str">
         <f>'NFL Schedule'!J64</f>
-        <v/>
-      </c>
-      <c r="F67" s="10"/>
-      <c r="G67" s="10"/>
-      <c r="H67" s="10"/>
-      <c r="I67" s="10"/>
-      <c r="J67" s="10"/>
-      <c r="K67" s="10"/>
-      <c r="L67" s="10"/>
-      <c r="M67" s="10"/>
-      <c r="N67" s="10"/>
-      <c r="O67" s="10"/>
-      <c r="P67" s="10"/>
-      <c r="Q67" s="10"/>
+        <v>JAX</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G67" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="I67" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="J67" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="K67" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="L67" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="M67" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="N67" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="O67" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="P67" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q67" s="10" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="68" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="7">
@@ -10485,20 +10601,44 @@
       </c>
       <c r="E68" s="9" t="str">
         <f>'NFL Schedule'!J65</f>
-        <v/>
-      </c>
-      <c r="F68" s="10"/>
-      <c r="G68" s="10"/>
-      <c r="H68" s="10"/>
-      <c r="I68" s="10"/>
-      <c r="J68" s="10"/>
-      <c r="K68" s="10"/>
-      <c r="L68" s="10"/>
-      <c r="M68" s="10"/>
-      <c r="N68" s="10"/>
-      <c r="O68" s="10"/>
-      <c r="P68" s="10"/>
-      <c r="Q68" s="10"/>
+        <v>NYG</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H68" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I68" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="J68" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K68" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="L68" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="M68" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="N68" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="O68" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="P68" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q68" s="10" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="69" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="7">
@@ -10515,20 +10655,44 @@
       </c>
       <c r="E69" s="9" t="str">
         <f>'NFL Schedule'!J66</f>
-        <v/>
-      </c>
-      <c r="F69" s="10"/>
-      <c r="G69" s="10"/>
-      <c r="H69" s="10"/>
-      <c r="I69" s="10"/>
-      <c r="J69" s="10"/>
-      <c r="K69" s="10"/>
-      <c r="L69" s="10"/>
-      <c r="M69" s="10"/>
-      <c r="N69" s="10"/>
-      <c r="O69" s="10"/>
-      <c r="P69" s="10"/>
-      <c r="Q69" s="10"/>
+        <v>LAR</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="H69" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="I69" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="J69" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="K69" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="L69" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="M69" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="N69" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="O69" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="P69" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q69" s="10" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="70" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="7">
@@ -10545,20 +10709,44 @@
       </c>
       <c r="E70" s="9" t="str">
         <f>'NFL Schedule'!J67</f>
-        <v/>
-      </c>
-      <c r="F70" s="10"/>
-      <c r="G70" s="10"/>
-      <c r="H70" s="10"/>
-      <c r="I70" s="10"/>
-      <c r="J70" s="10"/>
-      <c r="K70" s="10"/>
-      <c r="L70" s="10"/>
-      <c r="M70" s="10"/>
-      <c r="N70" s="10"/>
-      <c r="O70" s="10"/>
-      <c r="P70" s="10"/>
-      <c r="Q70" s="10"/>
+        <v>TB</v>
+      </c>
+      <c r="F70" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="H70" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="I70" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="J70" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="K70" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="L70" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="M70" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="N70" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="O70" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="P70" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q70" s="10" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="71" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="7">
@@ -10575,20 +10763,44 @@
       </c>
       <c r="E71" s="9" t="str">
         <f>'NFL Schedule'!J68</f>
-        <v/>
-      </c>
-      <c r="F71" s="10"/>
-      <c r="G71" s="10"/>
-      <c r="H71" s="10"/>
-      <c r="I71" s="10"/>
-      <c r="J71" s="10"/>
-      <c r="K71" s="10"/>
-      <c r="L71" s="10"/>
-      <c r="M71" s="10"/>
-      <c r="N71" s="10"/>
-      <c r="O71" s="10"/>
-      <c r="P71" s="10"/>
-      <c r="Q71" s="10"/>
+        <v>TEN</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G71" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H71" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I71" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="J71" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="K71" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="L71" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="M71" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="N71" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O71" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="P71" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q71" s="10" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="72" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="7">
@@ -10605,20 +10817,44 @@
       </c>
       <c r="E72" s="9" t="str">
         <f>'NFL Schedule'!J69</f>
-        <v/>
-      </c>
-      <c r="F72" s="10"/>
-      <c r="G72" s="10"/>
-      <c r="H72" s="10"/>
-      <c r="I72" s="10"/>
-      <c r="J72" s="10"/>
-      <c r="K72" s="10"/>
-      <c r="L72" s="10"/>
-      <c r="M72" s="10"/>
-      <c r="N72" s="10"/>
-      <c r="O72" s="10"/>
-      <c r="P72" s="10"/>
-      <c r="Q72" s="10"/>
+        <v>DAL</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H72" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I72" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="J72" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K72" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="L72" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="M72" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="N72" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="O72" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="P72" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q72" s="10" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="73" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="7">
@@ -10635,20 +10871,44 @@
       </c>
       <c r="E73" s="9" t="str">
         <f>'NFL Schedule'!J70</f>
-        <v/>
-      </c>
-      <c r="F73" s="10"/>
-      <c r="G73" s="10"/>
-      <c r="H73" s="10"/>
-      <c r="I73" s="10"/>
-      <c r="J73" s="10"/>
-      <c r="K73" s="10"/>
-      <c r="L73" s="10"/>
-      <c r="M73" s="10"/>
-      <c r="N73" s="10"/>
-      <c r="O73" s="10"/>
-      <c r="P73" s="10"/>
-      <c r="Q73" s="10"/>
+        <v>MIA</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H73" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="I73" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="J73" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="K73" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="L73" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="M73" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="N73" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="O73" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="P73" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q73" s="10" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="74" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="7">
@@ -10665,20 +10925,44 @@
       </c>
       <c r="E74" s="9" t="str">
         <f>'NFL Schedule'!J71</f>
-        <v/>
-      </c>
-      <c r="F74" s="10"/>
-      <c r="G74" s="10"/>
-      <c r="H74" s="10"/>
-      <c r="I74" s="10"/>
-      <c r="J74" s="10"/>
-      <c r="K74" s="10"/>
-      <c r="L74" s="10"/>
-      <c r="M74" s="10"/>
-      <c r="N74" s="10"/>
-      <c r="O74" s="10"/>
-      <c r="P74" s="10"/>
-      <c r="Q74" s="10"/>
+        <v>LV</v>
+      </c>
+      <c r="F74" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G74" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="H74" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="I74" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="J74" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="K74" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="L74" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="M74" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="N74" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="O74" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="P74" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q74" s="10" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="75" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="7">
@@ -10695,20 +10979,44 @@
       </c>
       <c r="E75" s="9" t="str">
         <f>'NFL Schedule'!J72</f>
-        <v/>
-      </c>
-      <c r="F75" s="10"/>
-      <c r="G75" s="10"/>
-      <c r="H75" s="10"/>
-      <c r="I75" s="10"/>
-      <c r="J75" s="10"/>
-      <c r="K75" s="10"/>
-      <c r="L75" s="10"/>
-      <c r="M75" s="10"/>
-      <c r="N75" s="10"/>
-      <c r="O75" s="10"/>
-      <c r="P75" s="10"/>
-      <c r="Q75" s="10"/>
+        <v>SF</v>
+      </c>
+      <c r="F75" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G75" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H75" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I75" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="J75" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="K75" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="L75" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="M75" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="N75" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="O75" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="P75" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q75" s="10" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="76" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="7">
@@ -10725,20 +11033,44 @@
       </c>
       <c r="E76" s="9" t="str">
         <f>'NFL Schedule'!J73</f>
-        <v/>
-      </c>
-      <c r="F76" s="10"/>
-      <c r="G76" s="10"/>
-      <c r="H76" s="10"/>
-      <c r="I76" s="10"/>
-      <c r="J76" s="10"/>
-      <c r="K76" s="10"/>
-      <c r="L76" s="10"/>
-      <c r="M76" s="10"/>
-      <c r="N76" s="10"/>
-      <c r="O76" s="10"/>
-      <c r="P76" s="10"/>
-      <c r="Q76" s="10"/>
+        <v>LAC</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G76" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="I76" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="J76" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="K76" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="L76" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="M76" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="N76" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O76" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="P76" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q76" s="10" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="77" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="7">
@@ -10755,20 +11087,44 @@
       </c>
       <c r="E77" s="9" t="str">
         <f>'NFL Schedule'!J74</f>
-        <v/>
-      </c>
-      <c r="F77" s="10"/>
-      <c r="G77" s="10"/>
-      <c r="H77" s="10"/>
-      <c r="I77" s="10"/>
-      <c r="J77" s="10"/>
-      <c r="K77" s="10"/>
-      <c r="L77" s="10"/>
-      <c r="M77" s="10"/>
-      <c r="N77" s="10"/>
-      <c r="O77" s="10"/>
-      <c r="P77" s="10"/>
-      <c r="Q77" s="10"/>
+        <v>CAR</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G77" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="I77" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J77" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K77" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="L77" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="M77" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="N77" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="O77" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="P77" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q77" s="10" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="78" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="7">
@@ -10825,25 +11181,25 @@
       <c r="Q79" s="14"/>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="22" t="s">
+      <c r="A80" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="22"/>
-      <c r="C80" s="22"/>
-      <c r="D80" s="22"/>
-      <c r="E80" s="22"/>
-      <c r="F80" s="22"/>
-      <c r="G80" s="22"/>
-      <c r="H80" s="22"/>
-      <c r="I80" s="22"/>
-      <c r="J80" s="22"/>
-      <c r="K80" s="22"/>
-      <c r="L80" s="22"/>
-      <c r="M80" s="22"/>
-      <c r="N80" s="22"/>
-      <c r="O80" s="22"/>
-      <c r="P80" s="22"/>
-      <c r="Q80" s="22"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
+      <c r="I80" s="26"/>
+      <c r="J80" s="26"/>
+      <c r="K80" s="26"/>
+      <c r="L80" s="26"/>
+      <c r="M80" s="26"/>
+      <c r="N80" s="26"/>
+      <c r="O80" s="26"/>
+      <c r="P80" s="26"/>
+      <c r="Q80" s="26"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -11373,25 +11729,25 @@
       <c r="Q97" s="14"/>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="22" t="s">
+      <c r="A98" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="22"/>
-      <c r="C98" s="22"/>
-      <c r="D98" s="22"/>
-      <c r="E98" s="22"/>
-      <c r="F98" s="22"/>
-      <c r="G98" s="22"/>
-      <c r="H98" s="22"/>
-      <c r="I98" s="22"/>
-      <c r="J98" s="22"/>
-      <c r="K98" s="22"/>
-      <c r="L98" s="22"/>
-      <c r="M98" s="22"/>
-      <c r="N98" s="22"/>
-      <c r="O98" s="22"/>
-      <c r="P98" s="22"/>
-      <c r="Q98" s="22"/>
+      <c r="B98" s="26"/>
+      <c r="C98" s="26"/>
+      <c r="D98" s="26"/>
+      <c r="E98" s="26"/>
+      <c r="F98" s="26"/>
+      <c r="G98" s="26"/>
+      <c r="H98" s="26"/>
+      <c r="I98" s="26"/>
+      <c r="J98" s="26"/>
+      <c r="K98" s="26"/>
+      <c r="L98" s="26"/>
+      <c r="M98" s="26"/>
+      <c r="N98" s="26"/>
+      <c r="O98" s="26"/>
+      <c r="P98" s="26"/>
+      <c r="Q98" s="26"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -11891,25 +12247,25 @@
       <c r="Q114" s="14"/>
     </row>
     <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="22" t="s">
+      <c r="A115" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="22"/>
-      <c r="C115" s="22"/>
-      <c r="D115" s="22"/>
-      <c r="E115" s="22"/>
-      <c r="F115" s="22"/>
-      <c r="G115" s="22"/>
-      <c r="H115" s="22"/>
-      <c r="I115" s="22"/>
-      <c r="J115" s="22"/>
-      <c r="K115" s="22"/>
-      <c r="L115" s="22"/>
-      <c r="M115" s="22"/>
-      <c r="N115" s="22"/>
-      <c r="O115" s="22"/>
-      <c r="P115" s="22"/>
-      <c r="Q115" s="22"/>
+      <c r="B115" s="26"/>
+      <c r="C115" s="26"/>
+      <c r="D115" s="26"/>
+      <c r="E115" s="26"/>
+      <c r="F115" s="26"/>
+      <c r="G115" s="26"/>
+      <c r="H115" s="26"/>
+      <c r="I115" s="26"/>
+      <c r="J115" s="26"/>
+      <c r="K115" s="26"/>
+      <c r="L115" s="26"/>
+      <c r="M115" s="26"/>
+      <c r="N115" s="26"/>
+      <c r="O115" s="26"/>
+      <c r="P115" s="26"/>
+      <c r="Q115" s="26"/>
     </row>
     <row r="116" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -12409,25 +12765,25 @@
       <c r="Q131" s="14"/>
     </row>
     <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="22" t="s">
+      <c r="A132" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="B132" s="22"/>
-      <c r="C132" s="22"/>
-      <c r="D132" s="22"/>
-      <c r="E132" s="22"/>
-      <c r="F132" s="22"/>
-      <c r="G132" s="22"/>
-      <c r="H132" s="22"/>
-      <c r="I132" s="22"/>
-      <c r="J132" s="22"/>
-      <c r="K132" s="22"/>
-      <c r="L132" s="22"/>
-      <c r="M132" s="22"/>
-      <c r="N132" s="22"/>
-      <c r="O132" s="22"/>
-      <c r="P132" s="22"/>
-      <c r="Q132" s="22"/>
+      <c r="B132" s="26"/>
+      <c r="C132" s="26"/>
+      <c r="D132" s="26"/>
+      <c r="E132" s="26"/>
+      <c r="F132" s="26"/>
+      <c r="G132" s="26"/>
+      <c r="H132" s="26"/>
+      <c r="I132" s="26"/>
+      <c r="J132" s="26"/>
+      <c r="K132" s="26"/>
+      <c r="L132" s="26"/>
+      <c r="M132" s="26"/>
+      <c r="N132" s="26"/>
+      <c r="O132" s="26"/>
+      <c r="P132" s="26"/>
+      <c r="Q132" s="26"/>
     </row>
     <row r="133" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -12927,25 +13283,25 @@
       <c r="Q148" s="14"/>
     </row>
     <row r="149" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="22" t="s">
+      <c r="A149" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="B149" s="22"/>
-      <c r="C149" s="22"/>
-      <c r="D149" s="22"/>
-      <c r="E149" s="22"/>
-      <c r="F149" s="22"/>
-      <c r="G149" s="22"/>
-      <c r="H149" s="22"/>
-      <c r="I149" s="22"/>
-      <c r="J149" s="22"/>
-      <c r="K149" s="22"/>
-      <c r="L149" s="22"/>
-      <c r="M149" s="22"/>
-      <c r="N149" s="22"/>
-      <c r="O149" s="22"/>
-      <c r="P149" s="22"/>
-      <c r="Q149" s="22"/>
+      <c r="B149" s="26"/>
+      <c r="C149" s="26"/>
+      <c r="D149" s="26"/>
+      <c r="E149" s="26"/>
+      <c r="F149" s="26"/>
+      <c r="G149" s="26"/>
+      <c r="H149" s="26"/>
+      <c r="I149" s="26"/>
+      <c r="J149" s="26"/>
+      <c r="K149" s="26"/>
+      <c r="L149" s="26"/>
+      <c r="M149" s="26"/>
+      <c r="N149" s="26"/>
+      <c r="O149" s="26"/>
+      <c r="P149" s="26"/>
+      <c r="Q149" s="26"/>
     </row>
     <row r="150" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -13475,25 +13831,25 @@
       <c r="Q166" s="14"/>
     </row>
     <row r="167" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="22" t="s">
+      <c r="A167" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="B167" s="22"/>
-      <c r="C167" s="22"/>
-      <c r="D167" s="22"/>
-      <c r="E167" s="22"/>
-      <c r="F167" s="22"/>
-      <c r="G167" s="22"/>
-      <c r="H167" s="22"/>
-      <c r="I167" s="22"/>
-      <c r="J167" s="22"/>
-      <c r="K167" s="22"/>
-      <c r="L167" s="22"/>
-      <c r="M167" s="22"/>
-      <c r="N167" s="22"/>
-      <c r="O167" s="22"/>
-      <c r="P167" s="22"/>
-      <c r="Q167" s="22"/>
+      <c r="B167" s="26"/>
+      <c r="C167" s="26"/>
+      <c r="D167" s="26"/>
+      <c r="E167" s="26"/>
+      <c r="F167" s="26"/>
+      <c r="G167" s="26"/>
+      <c r="H167" s="26"/>
+      <c r="I167" s="26"/>
+      <c r="J167" s="26"/>
+      <c r="K167" s="26"/>
+      <c r="L167" s="26"/>
+      <c r="M167" s="26"/>
+      <c r="N167" s="26"/>
+      <c r="O167" s="26"/>
+      <c r="P167" s="26"/>
+      <c r="Q167" s="26"/>
     </row>
     <row r="168" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -13993,25 +14349,25 @@
       <c r="Q183" s="14"/>
     </row>
     <row r="184" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="22" t="s">
+      <c r="A184" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="B184" s="22"/>
-      <c r="C184" s="22"/>
-      <c r="D184" s="22"/>
-      <c r="E184" s="22"/>
-      <c r="F184" s="22"/>
-      <c r="G184" s="22"/>
-      <c r="H184" s="22"/>
-      <c r="I184" s="22"/>
-      <c r="J184" s="22"/>
-      <c r="K184" s="22"/>
-      <c r="L184" s="22"/>
-      <c r="M184" s="22"/>
-      <c r="N184" s="22"/>
-      <c r="O184" s="22"/>
-      <c r="P184" s="22"/>
-      <c r="Q184" s="22"/>
+      <c r="B184" s="26"/>
+      <c r="C184" s="26"/>
+      <c r="D184" s="26"/>
+      <c r="E184" s="26"/>
+      <c r="F184" s="26"/>
+      <c r="G184" s="26"/>
+      <c r="H184" s="26"/>
+      <c r="I184" s="26"/>
+      <c r="J184" s="26"/>
+      <c r="K184" s="26"/>
+      <c r="L184" s="26"/>
+      <c r="M184" s="26"/>
+      <c r="N184" s="26"/>
+      <c r="O184" s="26"/>
+      <c r="P184" s="26"/>
+      <c r="Q184" s="26"/>
     </row>
     <row r="185" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -14481,25 +14837,25 @@
       <c r="Q199" s="14"/>
     </row>
     <row r="200" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="22" t="s">
+      <c r="A200" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="B200" s="22"/>
-      <c r="C200" s="22"/>
-      <c r="D200" s="22"/>
-      <c r="E200" s="22"/>
-      <c r="F200" s="22"/>
-      <c r="G200" s="22"/>
-      <c r="H200" s="22"/>
-      <c r="I200" s="22"/>
-      <c r="J200" s="22"/>
-      <c r="K200" s="22"/>
-      <c r="L200" s="22"/>
-      <c r="M200" s="22"/>
-      <c r="N200" s="22"/>
-      <c r="O200" s="22"/>
-      <c r="P200" s="22"/>
-      <c r="Q200" s="22"/>
+      <c r="B200" s="26"/>
+      <c r="C200" s="26"/>
+      <c r="D200" s="26"/>
+      <c r="E200" s="26"/>
+      <c r="F200" s="26"/>
+      <c r="G200" s="26"/>
+      <c r="H200" s="26"/>
+      <c r="I200" s="26"/>
+      <c r="J200" s="26"/>
+      <c r="K200" s="26"/>
+      <c r="L200" s="26"/>
+      <c r="M200" s="26"/>
+      <c r="N200" s="26"/>
+      <c r="O200" s="26"/>
+      <c r="P200" s="26"/>
+      <c r="Q200" s="26"/>
     </row>
     <row r="201" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -15059,25 +15415,25 @@
       <c r="Q218" s="14"/>
     </row>
     <row r="219" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="22" t="s">
+      <c r="A219" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="B219" s="22"/>
-      <c r="C219" s="22"/>
-      <c r="D219" s="22"/>
-      <c r="E219" s="22"/>
-      <c r="F219" s="22"/>
-      <c r="G219" s="22"/>
-      <c r="H219" s="22"/>
-      <c r="I219" s="22"/>
-      <c r="J219" s="22"/>
-      <c r="K219" s="22"/>
-      <c r="L219" s="22"/>
-      <c r="M219" s="22"/>
-      <c r="N219" s="22"/>
-      <c r="O219" s="22"/>
-      <c r="P219" s="22"/>
-      <c r="Q219" s="22"/>
+      <c r="B219" s="26"/>
+      <c r="C219" s="26"/>
+      <c r="D219" s="26"/>
+      <c r="E219" s="26"/>
+      <c r="F219" s="26"/>
+      <c r="G219" s="26"/>
+      <c r="H219" s="26"/>
+      <c r="I219" s="26"/>
+      <c r="J219" s="26"/>
+      <c r="K219" s="26"/>
+      <c r="L219" s="26"/>
+      <c r="M219" s="26"/>
+      <c r="N219" s="26"/>
+      <c r="O219" s="26"/>
+      <c r="P219" s="26"/>
+      <c r="Q219" s="26"/>
     </row>
     <row r="220" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -15577,25 +15933,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="22" t="s">
+      <c r="A236" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="B236" s="22"/>
-      <c r="C236" s="22"/>
-      <c r="D236" s="22"/>
-      <c r="E236" s="22"/>
-      <c r="F236" s="22"/>
-      <c r="G236" s="22"/>
-      <c r="H236" s="22"/>
-      <c r="I236" s="22"/>
-      <c r="J236" s="22"/>
-      <c r="K236" s="22"/>
-      <c r="L236" s="22"/>
-      <c r="M236" s="22"/>
-      <c r="N236" s="22"/>
-      <c r="O236" s="22"/>
-      <c r="P236" s="22"/>
-      <c r="Q236" s="22"/>
+      <c r="B236" s="26"/>
+      <c r="C236" s="26"/>
+      <c r="D236" s="26"/>
+      <c r="E236" s="26"/>
+      <c r="F236" s="26"/>
+      <c r="G236" s="26"/>
+      <c r="H236" s="26"/>
+      <c r="I236" s="26"/>
+      <c r="J236" s="26"/>
+      <c r="K236" s="26"/>
+      <c r="L236" s="26"/>
+      <c r="M236" s="26"/>
+      <c r="N236" s="26"/>
+      <c r="O236" s="26"/>
+      <c r="P236" s="26"/>
+      <c r="Q236" s="26"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -16125,25 +16481,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="22" t="s">
+      <c r="A254" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="B254" s="22"/>
-      <c r="C254" s="22"/>
-      <c r="D254" s="22"/>
-      <c r="E254" s="22"/>
-      <c r="F254" s="22"/>
-      <c r="G254" s="22"/>
-      <c r="H254" s="22"/>
-      <c r="I254" s="22"/>
-      <c r="J254" s="22"/>
-      <c r="K254" s="22"/>
-      <c r="L254" s="22"/>
-      <c r="M254" s="22"/>
-      <c r="N254" s="22"/>
-      <c r="O254" s="22"/>
-      <c r="P254" s="22"/>
-      <c r="Q254" s="22"/>
+      <c r="B254" s="26"/>
+      <c r="C254" s="26"/>
+      <c r="D254" s="26"/>
+      <c r="E254" s="26"/>
+      <c r="F254" s="26"/>
+      <c r="G254" s="26"/>
+      <c r="H254" s="26"/>
+      <c r="I254" s="26"/>
+      <c r="J254" s="26"/>
+      <c r="K254" s="26"/>
+      <c r="L254" s="26"/>
+      <c r="M254" s="26"/>
+      <c r="N254" s="26"/>
+      <c r="O254" s="26"/>
+      <c r="P254" s="26"/>
+      <c r="Q254" s="26"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -16703,25 +17059,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="22" t="s">
+      <c r="A273" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="B273" s="22"/>
-      <c r="C273" s="22"/>
-      <c r="D273" s="22"/>
-      <c r="E273" s="22"/>
-      <c r="F273" s="22"/>
-      <c r="G273" s="22"/>
-      <c r="H273" s="22"/>
-      <c r="I273" s="22"/>
-      <c r="J273" s="22"/>
-      <c r="K273" s="22"/>
-      <c r="L273" s="22"/>
-      <c r="M273" s="22"/>
-      <c r="N273" s="22"/>
-      <c r="O273" s="22"/>
-      <c r="P273" s="22"/>
-      <c r="Q273" s="22"/>
+      <c r="B273" s="26"/>
+      <c r="C273" s="26"/>
+      <c r="D273" s="26"/>
+      <c r="E273" s="26"/>
+      <c r="F273" s="26"/>
+      <c r="G273" s="26"/>
+      <c r="H273" s="26"/>
+      <c r="I273" s="26"/>
+      <c r="J273" s="26"/>
+      <c r="K273" s="26"/>
+      <c r="L273" s="26"/>
+      <c r="M273" s="26"/>
+      <c r="N273" s="26"/>
+      <c r="O273" s="26"/>
+      <c r="P273" s="26"/>
+      <c r="Q273" s="26"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -17281,25 +17637,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="22" t="s">
+      <c r="A292" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="B292" s="22"/>
-      <c r="C292" s="22"/>
-      <c r="D292" s="22"/>
-      <c r="E292" s="22"/>
-      <c r="F292" s="22"/>
-      <c r="G292" s="22"/>
-      <c r="H292" s="22"/>
-      <c r="I292" s="22"/>
-      <c r="J292" s="22"/>
-      <c r="K292" s="22"/>
-      <c r="L292" s="22"/>
-      <c r="M292" s="22"/>
-      <c r="N292" s="22"/>
-      <c r="O292" s="22"/>
-      <c r="P292" s="22"/>
-      <c r="Q292" s="22"/>
+      <c r="B292" s="26"/>
+      <c r="C292" s="26"/>
+      <c r="D292" s="26"/>
+      <c r="E292" s="26"/>
+      <c r="F292" s="26"/>
+      <c r="G292" s="26"/>
+      <c r="H292" s="26"/>
+      <c r="I292" s="26"/>
+      <c r="J292" s="26"/>
+      <c r="K292" s="26"/>
+      <c r="L292" s="26"/>
+      <c r="M292" s="26"/>
+      <c r="N292" s="26"/>
+      <c r="O292" s="26"/>
+      <c r="P292" s="26"/>
+      <c r="Q292" s="26"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -17859,25 +18215,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="22" t="s">
+      <c r="A311" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="B311" s="22"/>
-      <c r="C311" s="22"/>
-      <c r="D311" s="22"/>
-      <c r="E311" s="22"/>
-      <c r="F311" s="22"/>
-      <c r="G311" s="22"/>
-      <c r="H311" s="22"/>
-      <c r="I311" s="22"/>
-      <c r="J311" s="22"/>
-      <c r="K311" s="22"/>
-      <c r="L311" s="22"/>
-      <c r="M311" s="22"/>
-      <c r="N311" s="22"/>
-      <c r="O311" s="22"/>
-      <c r="P311" s="22"/>
-      <c r="Q311" s="22"/>
+      <c r="B311" s="26"/>
+      <c r="C311" s="26"/>
+      <c r="D311" s="26"/>
+      <c r="E311" s="26"/>
+      <c r="F311" s="26"/>
+      <c r="G311" s="26"/>
+      <c r="H311" s="26"/>
+      <c r="I311" s="26"/>
+      <c r="J311" s="26"/>
+      <c r="K311" s="26"/>
+      <c r="L311" s="26"/>
+      <c r="M311" s="26"/>
+      <c r="N311" s="26"/>
+      <c r="O311" s="26"/>
+      <c r="P311" s="26"/>
+      <c r="Q311" s="26"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -18438,26 +18794,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A236:Q236"/>
+    <mergeCell ref="A254:Q254"/>
+    <mergeCell ref="A273:Q273"/>
+    <mergeCell ref="A292:Q292"/>
+    <mergeCell ref="A311:Q311"/>
+    <mergeCell ref="A149:Q149"/>
+    <mergeCell ref="A167:Q167"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A219:Q219"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="A132:Q132"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A4:Q4"/>
     <mergeCell ref="A23:Q23"/>
     <mergeCell ref="A42:Q42"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A167:Q167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A236:Q236"/>
-    <mergeCell ref="A254:Q254"/>
-    <mergeCell ref="A273:Q273"/>
-    <mergeCell ref="A292:Q292"/>
-    <mergeCell ref="A311:Q311"/>
   </mergeCells>
   <dataValidations count="268">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or SEA" promptTitle="ATS Pick" prompt="Pick NE or SEA" sqref="F6:Q6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -21366,16 +21722,25 @@
       <c r="D60" t="s">
         <v>74</v>
       </c>
+      <c r="E60">
+        <v>24</v>
+      </c>
       <c r="F60" t="s">
         <v>71</v>
       </c>
+      <c r="G60">
+        <v>27</v>
+      </c>
+      <c r="H60">
+        <v>-2.5</v>
+      </c>
       <c r="I60" t="str">
         <f t="shared" ref="I60:I75" si="6">IF(OR(E60="",G60=""),"",IF(E60&gt;G60,D60,IF(G60&gt;E60,F60,"TIE")))</f>
-        <v/>
+        <v>CLE</v>
       </c>
       <c r="J60" t="str">
         <f t="shared" ref="J60:J75" si="7">IF(OR(E60="",G60="",H60=""),"",IF(E60+H60&gt;G60,D60,IF(E60+H60&lt;G60,F60,"PUSH")))</f>
-        <v/>
+        <v>CLE</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21391,16 +21756,25 @@
       <c r="D61" t="s">
         <v>70</v>
       </c>
+      <c r="E61">
+        <v>30</v>
+      </c>
       <c r="F61" t="s">
         <v>83</v>
       </c>
+      <c r="G61">
+        <v>13</v>
+      </c>
+      <c r="H61">
+        <v>-3.5</v>
+      </c>
       <c r="I61" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>IND</v>
       </c>
       <c r="J61" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>IND</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21416,16 +21790,25 @@
       <c r="D62" t="s">
         <v>57</v>
       </c>
+      <c r="E62">
+        <v>29</v>
+      </c>
       <c r="F62" t="s">
         <v>67</v>
       </c>
+      <c r="G62">
+        <v>26</v>
+      </c>
+      <c r="H62">
+        <v>6.5</v>
+      </c>
       <c r="I62" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>NE</v>
       </c>
       <c r="J62" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>NE</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21441,16 +21824,25 @@
       <c r="D63" t="s">
         <v>75</v>
       </c>
+      <c r="E63">
+        <v>12</v>
+      </c>
       <c r="F63" t="s">
         <v>61</v>
       </c>
+      <c r="G63">
+        <v>23</v>
+      </c>
+      <c r="H63">
+        <v>3.5</v>
+      </c>
       <c r="I63" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>CHI</v>
       </c>
       <c r="J63" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>CHI</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21466,16 +21858,25 @@
       <c r="D64" t="s">
         <v>72</v>
       </c>
+      <c r="E64">
+        <v>22</v>
+      </c>
       <c r="F64" t="s">
         <v>64</v>
       </c>
+      <c r="G64">
+        <v>17</v>
+      </c>
+      <c r="H64">
+        <v>2.5</v>
+      </c>
       <c r="I64" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>JAX</v>
       </c>
       <c r="J64" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>JAX</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21491,16 +21892,25 @@
       <c r="D65" t="s">
         <v>77</v>
       </c>
+      <c r="E65">
+        <v>24</v>
+      </c>
       <c r="F65" t="s">
         <v>86</v>
       </c>
+      <c r="G65">
+        <v>36</v>
+      </c>
+      <c r="H65">
+        <v>-0.5</v>
+      </c>
       <c r="I65" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>NYG</v>
       </c>
       <c r="J65" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>NYG</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21516,16 +21926,25 @@
       <c r="D66" t="s">
         <v>60</v>
       </c>
+      <c r="E66">
+        <v>24</v>
+      </c>
       <c r="F66" t="s">
         <v>84</v>
       </c>
+      <c r="G66">
+        <v>20</v>
+      </c>
+      <c r="H66">
+        <v>-2.5</v>
+      </c>
       <c r="I66" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>LAR</v>
       </c>
       <c r="J66" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>LAR</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21541,16 +21960,25 @@
       <c r="D67" t="s">
         <v>81</v>
       </c>
+      <c r="E67">
+        <v>17</v>
+      </c>
       <c r="F67" t="s">
         <v>63</v>
       </c>
+      <c r="G67">
+        <v>14</v>
+      </c>
+      <c r="H67">
+        <v>-3.5</v>
+      </c>
       <c r="I67" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>GB</v>
       </c>
       <c r="J67" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>TB</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21566,16 +21994,25 @@
       <c r="D68" t="s">
         <v>76</v>
       </c>
+      <c r="E68">
+        <v>18</v>
+      </c>
       <c r="F68" t="s">
         <v>69</v>
       </c>
+      <c r="G68">
+        <v>24</v>
+      </c>
+      <c r="H68">
+        <v>11.5</v>
+      </c>
       <c r="I68" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>BAL</v>
       </c>
       <c r="J68" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>TEN</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21591,16 +22028,25 @@
       <c r="D69" t="s">
         <v>85</v>
       </c>
+      <c r="E69">
+        <v>34</v>
+      </c>
       <c r="F69" t="s">
         <v>68</v>
       </c>
+      <c r="G69">
+        <v>30</v>
+      </c>
+      <c r="H69">
+        <v>-2.5</v>
+      </c>
       <c r="I69" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>DAL</v>
       </c>
       <c r="J69" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>DAL</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21616,16 +22062,25 @@
       <c r="D70" t="s">
         <v>79</v>
       </c>
+      <c r="E70">
+        <v>10</v>
+      </c>
       <c r="F70" t="s">
         <v>82</v>
       </c>
+      <c r="G70">
+        <v>15</v>
+      </c>
+      <c r="H70">
+        <v>11.5</v>
+      </c>
       <c r="I70" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>MIN</v>
       </c>
       <c r="J70" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>MIA</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21641,16 +22096,25 @@
       <c r="D71" t="s">
         <v>88</v>
       </c>
+      <c r="E71">
+        <v>30</v>
+      </c>
       <c r="F71" t="s">
         <v>80</v>
       </c>
+      <c r="G71">
+        <v>27</v>
+      </c>
+      <c r="H71">
+        <v>-4.5</v>
+      </c>
       <c r="I71" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>KC</v>
       </c>
       <c r="J71" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>LV</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21666,16 +22130,25 @@
       <c r="D72" t="s">
         <v>87</v>
       </c>
+      <c r="E72">
+        <v>14</v>
+      </c>
       <c r="F72" t="s">
         <v>59</v>
       </c>
+      <c r="G72">
+        <v>24</v>
+      </c>
+      <c r="H72">
+        <v>2.5</v>
+      </c>
       <c r="I72" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>SF</v>
       </c>
       <c r="J72" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>SF</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21691,16 +22164,25 @@
       <c r="D73" t="s">
         <v>78</v>
       </c>
+      <c r="E73">
+        <v>23</v>
+      </c>
       <c r="F73" t="s">
         <v>58</v>
       </c>
+      <c r="G73">
+        <v>30</v>
+      </c>
+      <c r="H73">
+        <v>7.5</v>
+      </c>
       <c r="I73" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>SEA</v>
       </c>
       <c r="J73" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>LAC</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21716,16 +22198,25 @@
       <c r="D74" t="s">
         <v>66</v>
       </c>
+      <c r="E74">
+        <v>26</v>
+      </c>
       <c r="F74" t="s">
         <v>62</v>
       </c>
+      <c r="G74">
+        <v>32</v>
+      </c>
+      <c r="H74">
+        <v>-3.5</v>
+      </c>
       <c r="I74" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>CAR</v>
       </c>
       <c r="J74" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>CAR</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27980,17 +28471,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -29439,30 +29930,30 @@
       </c>
       <c r="C51" s="3">
         <f>SUMPRODUCT(('Picks Detail'!F63:F78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!F63:F78='Picks Detail'!E63:E78))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D51">
         <v>8</v>
       </c>
       <c r="E51">
         <f>IFERROR(INDEX(C$51:C$62,MATCH(8,A$51:A$62,0)),0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F51" t="str">
         <f>IF(C51=0,"-",IF(C51&gt;E51,"W",IF(C51&lt;E51,"L",IF(AND('Picks Detail'!E79&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,A51)&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,D51)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A51)-'Picks Detail'!E79)&lt;ABS(INDEX('Picks Detail'!F79:Q79,1,D51)-'Picks Detail'!E79),"W",IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A51)-'Picks Detail'!E79)&gt;ABS(INDEX('Picks Detail'!F79:Q79,1,D51)-'Picks Detail'!E79),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>T</v>
       </c>
       <c r="G51">
         <f t="shared" ref="G51:G62" si="9">IF(F51="W",6,IF(F51="T",3,0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H51">
         <f t="shared" ref="H51:H62" si="10">IF(C51="",0,C51)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I51">
         <f t="shared" ref="I51:I62" si="11">G51+H51</f>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29475,30 +29966,30 @@
       </c>
       <c r="C52" s="3">
         <f>SUMPRODUCT(('Picks Detail'!G63:G78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!G63:G78='Picks Detail'!E63:E78))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D52">
         <v>7</v>
       </c>
       <c r="E52">
         <f>IFERROR(INDEX(C$51:C$62,MATCH(7,A$51:A$62,0)),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F52" t="str">
         <f>IF(C52=0,"-",IF(C52&gt;E52,"W",IF(C52&lt;E52,"L",IF(AND('Picks Detail'!E79&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,A52)&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,D52)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A52)-'Picks Detail'!E79)&lt;ABS(INDEX('Picks Detail'!F79:Q79,1,D52)-'Picks Detail'!E79),"W",IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A52)-'Picks Detail'!E79)&gt;ABS(INDEX('Picks Detail'!F79:Q79,1,D52)-'Picks Detail'!E79),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>T</v>
       </c>
       <c r="G52">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H52">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I52">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29511,30 +30002,30 @@
       </c>
       <c r="C53" s="3">
         <f>SUMPRODUCT(('Picks Detail'!H63:H78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!H63:H78='Picks Detail'!E63:E78))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D53">
         <v>12</v>
       </c>
       <c r="E53">
         <f>IFERROR(INDEX(C$51:C$62,MATCH(12,A$51:A$62,0)),0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F53" t="str">
         <f>IF(C53=0,"-",IF(C53&gt;E53,"W",IF(C53&lt;E53,"L",IF(AND('Picks Detail'!E79&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,A53)&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,D53)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A53)-'Picks Detail'!E79)&lt;ABS(INDEX('Picks Detail'!F79:Q79,1,D53)-'Picks Detail'!E79),"W",IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A53)-'Picks Detail'!E79)&gt;ABS(INDEX('Picks Detail'!F79:Q79,1,D53)-'Picks Detail'!E79),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G53">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H53">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I53">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29547,30 +30038,30 @@
       </c>
       <c r="C54" s="3">
         <f>SUMPRODUCT(('Picks Detail'!I63:I78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!I63:I78='Picks Detail'!E63:E78))</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D54">
         <v>11</v>
       </c>
       <c r="E54">
         <f>IFERROR(INDEX(C$51:C$62,MATCH(11,A$51:A$62,0)),0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F54" t="str">
         <f>IF(C54=0,"-",IF(C54&gt;E54,"W",IF(C54&lt;E54,"L",IF(AND('Picks Detail'!E79&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,A54)&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,D54)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A54)-'Picks Detail'!E79)&lt;ABS(INDEX('Picks Detail'!F79:Q79,1,D54)-'Picks Detail'!E79),"W",IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A54)-'Picks Detail'!E79)&gt;ABS(INDEX('Picks Detail'!F79:Q79,1,D54)-'Picks Detail'!E79),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G54">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H54">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I54">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29583,18 +30074,18 @@
       </c>
       <c r="C55" s="3">
         <f>SUMPRODUCT(('Picks Detail'!J63:J78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!J63:J78='Picks Detail'!E63:E78))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D55">
         <v>10</v>
       </c>
       <c r="E55">
         <f>IFERROR(INDEX(C$51:C$62,MATCH(10,A$51:A$62,0)),0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F55" t="str">
         <f>IF(C55=0,"-",IF(C55&gt;E55,"W",IF(C55&lt;E55,"L",IF(AND('Picks Detail'!E79&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,A55)&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,D55)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A55)-'Picks Detail'!E79)&lt;ABS(INDEX('Picks Detail'!F79:Q79,1,D55)-'Picks Detail'!E79),"W",IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A55)-'Picks Detail'!E79)&gt;ABS(INDEX('Picks Detail'!F79:Q79,1,D55)-'Picks Detail'!E79),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G55">
         <f t="shared" si="9"/>
@@ -29602,11 +30093,11 @@
       </c>
       <c r="H55">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I55">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29619,18 +30110,18 @@
       </c>
       <c r="C56" s="3">
         <f>SUMPRODUCT(('Picks Detail'!K63:K78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!K63:K78='Picks Detail'!E63:E78))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D56">
         <v>9</v>
       </c>
       <c r="E56">
         <f>IFERROR(INDEX(C$51:C$62,MATCH(9,A$51:A$62,0)),0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="str">
         <f>IF(C56=0,"-",IF(C56&gt;E56,"W",IF(C56&lt;E56,"L",IF(AND('Picks Detail'!E79&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,A56)&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,D56)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A56)-'Picks Detail'!E79)&lt;ABS(INDEX('Picks Detail'!F79:Q79,1,D56)-'Picks Detail'!E79),"W",IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A56)-'Picks Detail'!E79)&gt;ABS(INDEX('Picks Detail'!F79:Q79,1,D56)-'Picks Detail'!E79),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G56">
         <f t="shared" si="9"/>
@@ -29638,11 +30129,11 @@
       </c>
       <c r="H56">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I56">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29655,30 +30146,30 @@
       </c>
       <c r="C57" s="3">
         <f>SUMPRODUCT(('Picks Detail'!L63:L78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!L63:L78='Picks Detail'!E63:E78))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D57">
         <v>2</v>
       </c>
       <c r="E57">
         <f>IFERROR(INDEX(C$51:C$62,MATCH(2,A$51:A$62,0)),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F57" t="str">
         <f>IF(C57=0,"-",IF(C57&gt;E57,"W",IF(C57&lt;E57,"L",IF(AND('Picks Detail'!E79&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,A57)&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,D57)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A57)-'Picks Detail'!E79)&lt;ABS(INDEX('Picks Detail'!F79:Q79,1,D57)-'Picks Detail'!E79),"W",IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A57)-'Picks Detail'!E79)&gt;ABS(INDEX('Picks Detail'!F79:Q79,1,D57)-'Picks Detail'!E79),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>T</v>
       </c>
       <c r="G57">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H57">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I57">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29691,30 +30182,30 @@
       </c>
       <c r="C58" s="3">
         <f>SUMPRODUCT(('Picks Detail'!M63:M78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!M63:M78='Picks Detail'!E63:E78))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D58">
         <v>1</v>
       </c>
       <c r="E58">
         <f>IFERROR(INDEX(C$51:C$62,MATCH(1,A$51:A$62,0)),0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F58" t="str">
         <f>IF(C58=0,"-",IF(C58&gt;E58,"W",IF(C58&lt;E58,"L",IF(AND('Picks Detail'!E79&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,A58)&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,D58)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A58)-'Picks Detail'!E79)&lt;ABS(INDEX('Picks Detail'!F79:Q79,1,D58)-'Picks Detail'!E79),"W",IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A58)-'Picks Detail'!E79)&gt;ABS(INDEX('Picks Detail'!F79:Q79,1,D58)-'Picks Detail'!E79),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>T</v>
       </c>
       <c r="G58">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H58">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I58">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29727,30 +30218,30 @@
       </c>
       <c r="C59" s="3">
         <f>SUMPRODUCT(('Picks Detail'!N63:N78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!N63:N78='Picks Detail'!E63:E78))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D59">
         <v>6</v>
       </c>
       <c r="E59">
         <f>IFERROR(INDEX(C$51:C$62,MATCH(6,A$51:A$62,0)),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F59" t="str">
         <f>IF(C59=0,"-",IF(C59&gt;E59,"W",IF(C59&lt;E59,"L",IF(AND('Picks Detail'!E79&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,A59)&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,D59)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A59)-'Picks Detail'!E79)&lt;ABS(INDEX('Picks Detail'!F79:Q79,1,D59)-'Picks Detail'!E79),"W",IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A59)-'Picks Detail'!E79)&gt;ABS(INDEX('Picks Detail'!F79:Q79,1,D59)-'Picks Detail'!E79),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G59">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H59">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I59">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29763,30 +30254,30 @@
       </c>
       <c r="C60" s="3">
         <f>SUMPRODUCT(('Picks Detail'!O63:O78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!O63:O78='Picks Detail'!E63:E78))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D60">
         <v>5</v>
       </c>
       <c r="E60">
         <f>IFERROR(INDEX(C$51:C$62,MATCH(5,A$51:A$62,0)),0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F60" t="str">
         <f>IF(C60=0,"-",IF(C60&gt;E60,"W",IF(C60&lt;E60,"L",IF(AND('Picks Detail'!E79&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,A60)&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,D60)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A60)-'Picks Detail'!E79)&lt;ABS(INDEX('Picks Detail'!F79:Q79,1,D60)-'Picks Detail'!E79),"W",IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A60)-'Picks Detail'!E79)&gt;ABS(INDEX('Picks Detail'!F79:Q79,1,D60)-'Picks Detail'!E79),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G60">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H60">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I60">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29799,18 +30290,18 @@
       </c>
       <c r="C61" s="3">
         <f>SUMPRODUCT(('Picks Detail'!P63:P78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!P63:P78='Picks Detail'!E63:E78))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D61">
         <v>4</v>
       </c>
       <c r="E61">
         <f>IFERROR(INDEX(C$51:C$62,MATCH(4,A$51:A$62,0)),0)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F61" t="str">
         <f>IF(C61=0,"-",IF(C61&gt;E61,"W",IF(C61&lt;E61,"L",IF(AND('Picks Detail'!E79&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,A61)&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,D61)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A61)-'Picks Detail'!E79)&lt;ABS(INDEX('Picks Detail'!F79:Q79,1,D61)-'Picks Detail'!E79),"W",IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A61)-'Picks Detail'!E79)&gt;ABS(INDEX('Picks Detail'!F79:Q79,1,D61)-'Picks Detail'!E79),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G61">
         <f t="shared" si="9"/>
@@ -29818,11 +30309,11 @@
       </c>
       <c r="H61">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I61">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29835,18 +30326,18 @@
       </c>
       <c r="C62" s="3">
         <f>SUMPRODUCT(('Picks Detail'!Q63:Q78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!Q63:Q78='Picks Detail'!E63:E78))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D62">
         <v>3</v>
       </c>
       <c r="E62">
         <f>IFERROR(INDEX(C$51:C$62,MATCH(3,A$51:A$62,0)),0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F62" t="str">
         <f>IF(C62=0,"-",IF(C62&gt;E62,"W",IF(C62&lt;E62,"L",IF(AND('Picks Detail'!E79&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,A62)&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,D62)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A62)-'Picks Detail'!E79)&lt;ABS(INDEX('Picks Detail'!F79:Q79,1,D62)-'Picks Detail'!E79),"W",IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A62)-'Picks Detail'!E79)&gt;ABS(INDEX('Picks Detail'!F79:Q79,1,D62)-'Picks Detail'!E79),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G62">
         <f t="shared" si="9"/>
@@ -29854,11 +30345,11 @@
       </c>
       <c r="H62">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I62">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30813,17 +31304,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -33646,17 +34137,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -36479,19 +36970,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -36550,7 +37041,7 @@
       </c>
       <c r="F3">
         <f>Helper!F2</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G3">
         <f>Helper!G2</f>
@@ -36562,7 +37053,7 @@
       </c>
       <c r="I3">
         <f>Helper!I2</f>
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="J3">
         <f>Helper!J2</f>
@@ -36595,7 +37086,7 @@
       </c>
       <c r="F4">
         <f>Helper!F3</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <f>Helper!G3</f>
@@ -36607,7 +37098,7 @@
       </c>
       <c r="I4">
         <f>Helper!I3</f>
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J4">
         <f>Helper!J3</f>
@@ -36640,7 +37131,7 @@
       </c>
       <c r="F5">
         <f>Helper!F4</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G5">
         <f>Helper!G4</f>
@@ -36652,7 +37143,7 @@
       </c>
       <c r="I5">
         <f>Helper!I4</f>
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="J5">
         <f>Helper!J4</f>
@@ -36685,7 +37176,7 @@
       </c>
       <c r="F6">
         <f>Helper!F5</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <f>Helper!G5</f>
@@ -36697,7 +37188,7 @@
       </c>
       <c r="I6">
         <f>Helper!I5</f>
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J6">
         <f>Helper!J5</f>
@@ -36730,7 +37221,7 @@
       </c>
       <c r="F7">
         <f>Helper!F6</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <f>Helper!G6</f>
@@ -36742,7 +37233,7 @@
       </c>
       <c r="I7">
         <f>Helper!I6</f>
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J7">
         <f>Helper!J6</f>
@@ -36775,7 +37266,7 @@
       </c>
       <c r="F8">
         <f>Helper!F7</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G8">
         <f>Helper!G7</f>
@@ -36787,7 +37278,7 @@
       </c>
       <c r="I8">
         <f>Helper!I7</f>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J8">
         <f>Helper!J7</f>
@@ -36820,7 +37311,7 @@
       </c>
       <c r="F9">
         <f>Helper!F8</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G9">
         <f>Helper!G8</f>
@@ -36832,7 +37323,7 @@
       </c>
       <c r="I9">
         <f>Helper!I8</f>
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J9">
         <f>Helper!J8</f>
@@ -36865,7 +37356,7 @@
       </c>
       <c r="F10">
         <f>Helper!F9</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G10">
         <f>Helper!G9</f>
@@ -36877,7 +37368,7 @@
       </c>
       <c r="I10">
         <f>Helper!I9</f>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J10">
         <f>Helper!J9</f>
@@ -36910,7 +37401,7 @@
       </c>
       <c r="F11">
         <f>Helper!F10</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G11">
         <f>Helper!G10</f>
@@ -36922,7 +37413,7 @@
       </c>
       <c r="I11">
         <f>Helper!I10</f>
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J11">
         <f>Helper!J10</f>
@@ -36955,7 +37446,7 @@
       </c>
       <c r="F12">
         <f>Helper!F11</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G12">
         <f>Helper!G11</f>
@@ -36967,7 +37458,7 @@
       </c>
       <c r="I12">
         <f>Helper!I11</f>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J12">
         <f>Helper!J11</f>
@@ -37000,7 +37491,7 @@
       </c>
       <c r="F13">
         <f>Helper!F12</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G13">
         <f>Helper!G12</f>
@@ -37012,7 +37503,7 @@
       </c>
       <c r="I13">
         <f>Helper!I12</f>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J13">
         <f>Helper!J12</f>
@@ -37045,7 +37536,7 @@
       </c>
       <c r="F14">
         <f>Helper!F13</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G14">
         <f>Helper!G13</f>
@@ -37057,7 +37548,7 @@
       </c>
       <c r="I14">
         <f>Helper!I13</f>
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J14">
         <f>Helper!J13</f>
@@ -38381,7 +38872,7 @@
       </c>
       <c r="C57">
         <f>Helper!I2</f>
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D57">
         <f>Helper!R2</f>
@@ -38393,11 +38884,11 @@
       </c>
       <c r="F57">
         <f>Helper!AE2</f>
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G57">
         <f>Helper!K2</f>
-        <v>37.000100000000003</v>
+        <v>44.000100000000003</v>
       </c>
       <c r="H57">
         <f>Helper!T2</f>
@@ -38414,7 +38905,7 @@
       </c>
       <c r="C58">
         <f>Helper!I3</f>
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D58">
         <f>Helper!R3</f>
@@ -38426,11 +38917,11 @@
       </c>
       <c r="F58">
         <f>Helper!AE3</f>
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G58">
         <f>Helper!K3</f>
-        <v>35.0002</v>
+        <v>41.0002</v>
       </c>
       <c r="H58">
         <f>Helper!T3</f>
@@ -38447,7 +38938,7 @@
       </c>
       <c r="C59">
         <f>Helper!I4</f>
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D59">
         <f>Helper!R4</f>
@@ -38459,11 +38950,11 @@
       </c>
       <c r="F59">
         <f>Helper!AE4</f>
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G59">
         <f>Helper!K4</f>
-        <v>34.000300000000003</v>
+        <v>42.000300000000003</v>
       </c>
       <c r="H59">
         <f>Helper!T4</f>
@@ -38480,7 +38971,7 @@
       </c>
       <c r="C60">
         <f>Helper!I5</f>
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D60">
         <f>Helper!R5</f>
@@ -38492,11 +38983,11 @@
       </c>
       <c r="F60">
         <f>Helper!AE5</f>
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G60">
         <f>Helper!K5</f>
-        <v>20.000399999999999</v>
+        <v>31.000399999999999</v>
       </c>
       <c r="H60">
         <f>Helper!T5</f>
@@ -38513,7 +39004,7 @@
       </c>
       <c r="C61">
         <f>Helper!I6</f>
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D61">
         <f>Helper!R6</f>
@@ -38525,11 +39016,11 @@
       </c>
       <c r="F61">
         <f>Helper!AE6</f>
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G61">
         <f>Helper!K6</f>
-        <v>37.000500000000002</v>
+        <v>42.000500000000002</v>
       </c>
       <c r="H61">
         <f>Helper!T6</f>
@@ -38546,7 +39037,7 @@
       </c>
       <c r="C62">
         <f>Helper!I7</f>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D62">
         <f>Helper!R7</f>
@@ -38558,11 +39049,11 @@
       </c>
       <c r="F62">
         <f>Helper!AE7</f>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G62">
         <f>Helper!K7</f>
-        <v>33.000599999999999</v>
+        <v>39.000599999999999</v>
       </c>
       <c r="H62">
         <f>Helper!T7</f>
@@ -38579,7 +39070,7 @@
       </c>
       <c r="C63">
         <f>Helper!I8</f>
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D63">
         <f>Helper!R8</f>
@@ -38591,11 +39082,11 @@
       </c>
       <c r="F63">
         <f>Helper!AE8</f>
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G63">
         <f>Helper!K8</f>
-        <v>27.000699999999998</v>
+        <v>33.000700000000002</v>
       </c>
       <c r="H63">
         <f>Helper!T8</f>
@@ -38612,7 +39103,7 @@
       </c>
       <c r="C64">
         <f>Helper!I9</f>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D64">
         <f>Helper!R9</f>
@@ -38624,11 +39115,11 @@
       </c>
       <c r="F64">
         <f>Helper!AE9</f>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G64">
         <f>Helper!K9</f>
-        <v>19.000800000000002</v>
+        <v>26.000800000000002</v>
       </c>
       <c r="H64">
         <f>Helper!T9</f>
@@ -38645,7 +39136,7 @@
       </c>
       <c r="C65">
         <f>Helper!I10</f>
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D65">
         <f>Helper!R10</f>
@@ -38657,11 +39148,11 @@
       </c>
       <c r="F65">
         <f>Helper!AE10</f>
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G65">
         <f>Helper!K10</f>
-        <v>23.000900000000001</v>
+        <v>30.000900000000001</v>
       </c>
       <c r="H65">
         <f>Helper!T10</f>
@@ -38678,7 +39169,7 @@
       </c>
       <c r="C66">
         <f>Helper!I11</f>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D66">
         <f>Helper!R11</f>
@@ -38690,11 +39181,11 @@
       </c>
       <c r="F66">
         <f>Helper!AE11</f>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G66">
         <f>Helper!K11</f>
-        <v>36.000999999999998</v>
+        <v>43.000999999999998</v>
       </c>
       <c r="H66">
         <f>Helper!T11</f>
@@ -38711,7 +39202,7 @@
       </c>
       <c r="C67">
         <f>Helper!I12</f>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D67">
         <f>Helper!R12</f>
@@ -38723,11 +39214,11 @@
       </c>
       <c r="F67">
         <f>Helper!AE12</f>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G67">
         <f>Helper!K12</f>
-        <v>36.001100000000001</v>
+        <v>43.001100000000001</v>
       </c>
       <c r="H67">
         <f>Helper!T12</f>
@@ -38744,7 +39235,7 @@
       </c>
       <c r="C68">
         <f>Helper!I13</f>
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D68">
         <f>Helper!R13</f>
@@ -38756,11 +39247,11 @@
       </c>
       <c r="F68">
         <f>Helper!AE13</f>
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G68">
         <f>Helper!K13</f>
-        <v>31.001200000000001</v>
+        <v>38.001199999999997</v>
       </c>
       <c r="H68">
         <f>Helper!T13</f>
@@ -38830,7 +39321,7 @@
       </c>
       <c r="B5" t="str">
         <f>INDEX(Helper!B$2:B$13,MATCH(MAX(Helper!K$2:K$13),Helper!K$2:K$13,0))</f>
-        <v>Mikayla Simmons</v>
+        <v>Evan Loeser</v>
       </c>
       <c r="C5" t="s">
         <v>252</v>
@@ -38840,7 +39331,7 @@
       </c>
       <c r="E5" t="str">
         <f>B5</f>
-        <v>Mikayla Simmons</v>
+        <v>Evan Loeser</v>
       </c>
       <c r="F5" t="str">
         <f>IF(B5="","—","QUALIFIED")</f>
@@ -38998,11 +39489,11 @@
       </c>
       <c r="B13" t="str">
         <f>INDEX(H$40:H$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
-        <v>Evan Loeser</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="C13">
         <f>INDEX(I$40:I$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
         <v>263</v>
@@ -39048,7 +39539,7 @@
       </c>
       <c r="B17" t="str">
         <f>E5</f>
-        <v>Mikayla Simmons</v>
+        <v>Evan Loeser</v>
       </c>
       <c r="C17" t="str">
         <f>D5</f>
@@ -39113,7 +39604,7 @@
       </c>
       <c r="B22" t="str">
         <f>B13</f>
-        <v>Evan Loeser</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="C22" t="str">
         <f>"Wild Card 1"</f>
@@ -39478,15 +39969,15 @@
       </c>
       <c r="I40">
         <f>Helper!AE2</f>
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="J40" t="b">
         <f t="shared" ref="J40:J51" si="1">OR(H40=$E$5,H40=$E$6,H40=$E$7,H40=$E$8,H40=$E$9)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40">
         <f>IF(J40,-1,I40+0.00001)</f>
-        <v>37.000010000000003</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39496,7 +39987,7 @@
       </c>
       <c r="I41">
         <f>Helper!AE3</f>
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J41" t="b">
         <f t="shared" si="1"/>
@@ -39504,7 +39995,7 @@
       </c>
       <c r="K41">
         <f>IF(J41,-1,I41+0.00002)</f>
-        <v>35.000019999999999</v>
+        <v>41.000019999999999</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39514,7 +40005,7 @@
       </c>
       <c r="I42">
         <f>Helper!AE4</f>
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="J42" t="b">
         <f t="shared" si="1"/>
@@ -39522,7 +40013,7 @@
       </c>
       <c r="K42">
         <f>IF(J42,-1,I42+0.00003)</f>
-        <v>34.000030000000002</v>
+        <v>42.000030000000002</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39532,7 +40023,7 @@
       </c>
       <c r="I43">
         <f>Helper!AE5</f>
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J43" t="b">
         <f t="shared" si="1"/>
@@ -39550,15 +40041,15 @@
       </c>
       <c r="I44">
         <f>Helper!AE6</f>
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J44" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44">
         <f>IF(J44,-1,I44+0.00005)</f>
-        <v>-1</v>
+        <v>42.000050000000002</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39568,7 +40059,7 @@
       </c>
       <c r="I45">
         <f>Helper!AE7</f>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J45" t="b">
         <f t="shared" si="1"/>
@@ -39576,7 +40067,7 @@
       </c>
       <c r="K45">
         <f>IF(J45,-1,I45+0.00006)</f>
-        <v>33.000059999999998</v>
+        <v>39.000059999999998</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39586,7 +40077,7 @@
       </c>
       <c r="I46">
         <f>Helper!AE8</f>
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J46" t="b">
         <f t="shared" si="1"/>
@@ -39594,7 +40085,7 @@
       </c>
       <c r="K46">
         <f>IF(J46,-1,I46+0.00007)</f>
-        <v>27.000070000000001</v>
+        <v>33.000070000000001</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39604,7 +40095,7 @@
       </c>
       <c r="I47">
         <f>Helper!AE9</f>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J47" t="b">
         <f t="shared" si="1"/>
@@ -39622,7 +40113,7 @@
       </c>
       <c r="I48">
         <f>Helper!AE10</f>
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J48" t="b">
         <f t="shared" si="1"/>
@@ -39630,7 +40121,7 @@
       </c>
       <c r="K48">
         <f>IF(J48,-1,I48+0.00009)</f>
-        <v>23.00009</v>
+        <v>30.00009</v>
       </c>
     </row>
     <row r="49" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39640,7 +40131,7 @@
       </c>
       <c r="I49">
         <f>Helper!AE11</f>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J49" t="b">
         <f t="shared" si="1"/>
@@ -39648,7 +40139,7 @@
       </c>
       <c r="K49">
         <f>IF(J49,-1,I49+0.0001)</f>
-        <v>36.000100000000003</v>
+        <v>43.000100000000003</v>
       </c>
     </row>
     <row r="50" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39658,7 +40149,7 @@
       </c>
       <c r="I50">
         <f>Helper!AE12</f>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J50" t="b">
         <f t="shared" si="1"/>
@@ -39676,7 +40167,7 @@
       </c>
       <c r="I51">
         <f>Helper!AE13</f>
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J51" t="b">
         <f t="shared" si="1"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="783" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FFA0CC4-573D-467C-801F-A1805DD1329C}"/>
+  <xr:revisionPtr revIDLastSave="784" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67597EDC-2273-443C-8CFC-60F9110D7C63}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3953" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3954" uniqueCount="347">
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -1087,6 +1087,9 @@
   <si>
     <t>Season Adj</t>
   </si>
+  <si>
+    <t>One game away from completing the first month of the season. A 2 week push remains to complete segment 1</t>
+  </si>
 </sst>
 </file>
 
@@ -1377,13 +1380,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1470,6 +1473,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1661,12 +1668,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="A1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -2721,7 +2728,11 @@
         <v>315</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>346</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4398,14 +4409,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -5350,14 +5361,14 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
@@ -6302,14 +6313,14 @@
       </c>
     </row>
     <row r="111" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="23" t="s">
+      <c r="A111" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B111" s="23"/>
-      <c r="C111" s="23"/>
-      <c r="D111" s="23"/>
-      <c r="E111" s="23"/>
-      <c r="F111" s="23"/>
+      <c r="B111" s="22"/>
+      <c r="C111" s="22"/>
+      <c r="D111" s="22"/>
+      <c r="E111" s="22"/>
+      <c r="F111" s="22"/>
     </row>
     <row r="112" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
@@ -7281,67 +7292,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8309,25 +8320,25 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="26"/>
-      <c r="P23" s="26"/>
-      <c r="Q23" s="26"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="24"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="24"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -9295,25 +9306,25 @@
       </c>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="26" t="s">
+      <c r="A42" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="26"/>
-      <c r="L42" s="26"/>
-      <c r="M42" s="26"/>
-      <c r="N42" s="26"/>
-      <c r="O42" s="26"/>
-      <c r="P42" s="26"/>
-      <c r="Q42" s="26"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="24"/>
+      <c r="N42" s="24"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="24"/>
+      <c r="Q42" s="24"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -10243,25 +10254,25 @@
       </c>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="26" t="s">
+      <c r="A61" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="26"/>
-      <c r="C61" s="26"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="26"/>
-      <c r="F61" s="26"/>
-      <c r="G61" s="26"/>
-      <c r="H61" s="26"/>
-      <c r="I61" s="26"/>
-      <c r="J61" s="26"/>
-      <c r="K61" s="26"/>
-      <c r="L61" s="26"/>
-      <c r="M61" s="26"/>
-      <c r="N61" s="26"/>
-      <c r="O61" s="26"/>
-      <c r="P61" s="26"/>
-      <c r="Q61" s="26"/>
+      <c r="B61" s="24"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="24"/>
+      <c r="J61" s="24"/>
+      <c r="K61" s="24"/>
+      <c r="L61" s="24"/>
+      <c r="M61" s="24"/>
+      <c r="N61" s="24"/>
+      <c r="O61" s="24"/>
+      <c r="P61" s="24"/>
+      <c r="Q61" s="24"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -11181,25 +11192,25 @@
       <c r="Q79" s="14"/>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="26" t="s">
+      <c r="A80" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="26"/>
-      <c r="C80" s="26"/>
-      <c r="D80" s="26"/>
-      <c r="E80" s="26"/>
-      <c r="F80" s="26"/>
-      <c r="G80" s="26"/>
-      <c r="H80" s="26"/>
-      <c r="I80" s="26"/>
-      <c r="J80" s="26"/>
-      <c r="K80" s="26"/>
-      <c r="L80" s="26"/>
-      <c r="M80" s="26"/>
-      <c r="N80" s="26"/>
-      <c r="O80" s="26"/>
-      <c r="P80" s="26"/>
-      <c r="Q80" s="26"/>
+      <c r="B80" s="24"/>
+      <c r="C80" s="24"/>
+      <c r="D80" s="24"/>
+      <c r="E80" s="24"/>
+      <c r="F80" s="24"/>
+      <c r="G80" s="24"/>
+      <c r="H80" s="24"/>
+      <c r="I80" s="24"/>
+      <c r="J80" s="24"/>
+      <c r="K80" s="24"/>
+      <c r="L80" s="24"/>
+      <c r="M80" s="24"/>
+      <c r="N80" s="24"/>
+      <c r="O80" s="24"/>
+      <c r="P80" s="24"/>
+      <c r="Q80" s="24"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -11729,25 +11740,25 @@
       <c r="Q97" s="14"/>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="26" t="s">
+      <c r="A98" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="26"/>
-      <c r="C98" s="26"/>
-      <c r="D98" s="26"/>
-      <c r="E98" s="26"/>
-      <c r="F98" s="26"/>
-      <c r="G98" s="26"/>
-      <c r="H98" s="26"/>
-      <c r="I98" s="26"/>
-      <c r="J98" s="26"/>
-      <c r="K98" s="26"/>
-      <c r="L98" s="26"/>
-      <c r="M98" s="26"/>
-      <c r="N98" s="26"/>
-      <c r="O98" s="26"/>
-      <c r="P98" s="26"/>
-      <c r="Q98" s="26"/>
+      <c r="B98" s="24"/>
+      <c r="C98" s="24"/>
+      <c r="D98" s="24"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24"/>
+      <c r="H98" s="24"/>
+      <c r="I98" s="24"/>
+      <c r="J98" s="24"/>
+      <c r="K98" s="24"/>
+      <c r="L98" s="24"/>
+      <c r="M98" s="24"/>
+      <c r="N98" s="24"/>
+      <c r="O98" s="24"/>
+      <c r="P98" s="24"/>
+      <c r="Q98" s="24"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -12247,25 +12258,25 @@
       <c r="Q114" s="14"/>
     </row>
     <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="26" t="s">
+      <c r="A115" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="26"/>
-      <c r="C115" s="26"/>
-      <c r="D115" s="26"/>
-      <c r="E115" s="26"/>
-      <c r="F115" s="26"/>
-      <c r="G115" s="26"/>
-      <c r="H115" s="26"/>
-      <c r="I115" s="26"/>
-      <c r="J115" s="26"/>
-      <c r="K115" s="26"/>
-      <c r="L115" s="26"/>
-      <c r="M115" s="26"/>
-      <c r="N115" s="26"/>
-      <c r="O115" s="26"/>
-      <c r="P115" s="26"/>
-      <c r="Q115" s="26"/>
+      <c r="B115" s="24"/>
+      <c r="C115" s="24"/>
+      <c r="D115" s="24"/>
+      <c r="E115" s="24"/>
+      <c r="F115" s="24"/>
+      <c r="G115" s="24"/>
+      <c r="H115" s="24"/>
+      <c r="I115" s="24"/>
+      <c r="J115" s="24"/>
+      <c r="K115" s="24"/>
+      <c r="L115" s="24"/>
+      <c r="M115" s="24"/>
+      <c r="N115" s="24"/>
+      <c r="O115" s="24"/>
+      <c r="P115" s="24"/>
+      <c r="Q115" s="24"/>
     </row>
     <row r="116" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -12765,25 +12776,25 @@
       <c r="Q131" s="14"/>
     </row>
     <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="26" t="s">
+      <c r="A132" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="B132" s="26"/>
-      <c r="C132" s="26"/>
-      <c r="D132" s="26"/>
-      <c r="E132" s="26"/>
-      <c r="F132" s="26"/>
-      <c r="G132" s="26"/>
-      <c r="H132" s="26"/>
-      <c r="I132" s="26"/>
-      <c r="J132" s="26"/>
-      <c r="K132" s="26"/>
-      <c r="L132" s="26"/>
-      <c r="M132" s="26"/>
-      <c r="N132" s="26"/>
-      <c r="O132" s="26"/>
-      <c r="P132" s="26"/>
-      <c r="Q132" s="26"/>
+      <c r="B132" s="24"/>
+      <c r="C132" s="24"/>
+      <c r="D132" s="24"/>
+      <c r="E132" s="24"/>
+      <c r="F132" s="24"/>
+      <c r="G132" s="24"/>
+      <c r="H132" s="24"/>
+      <c r="I132" s="24"/>
+      <c r="J132" s="24"/>
+      <c r="K132" s="24"/>
+      <c r="L132" s="24"/>
+      <c r="M132" s="24"/>
+      <c r="N132" s="24"/>
+      <c r="O132" s="24"/>
+      <c r="P132" s="24"/>
+      <c r="Q132" s="24"/>
     </row>
     <row r="133" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -13283,25 +13294,25 @@
       <c r="Q148" s="14"/>
     </row>
     <row r="149" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="26" t="s">
+      <c r="A149" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="B149" s="26"/>
-      <c r="C149" s="26"/>
-      <c r="D149" s="26"/>
-      <c r="E149" s="26"/>
-      <c r="F149" s="26"/>
-      <c r="G149" s="26"/>
-      <c r="H149" s="26"/>
-      <c r="I149" s="26"/>
-      <c r="J149" s="26"/>
-      <c r="K149" s="26"/>
-      <c r="L149" s="26"/>
-      <c r="M149" s="26"/>
-      <c r="N149" s="26"/>
-      <c r="O149" s="26"/>
-      <c r="P149" s="26"/>
-      <c r="Q149" s="26"/>
+      <c r="B149" s="24"/>
+      <c r="C149" s="24"/>
+      <c r="D149" s="24"/>
+      <c r="E149" s="24"/>
+      <c r="F149" s="24"/>
+      <c r="G149" s="24"/>
+      <c r="H149" s="24"/>
+      <c r="I149" s="24"/>
+      <c r="J149" s="24"/>
+      <c r="K149" s="24"/>
+      <c r="L149" s="24"/>
+      <c r="M149" s="24"/>
+      <c r="N149" s="24"/>
+      <c r="O149" s="24"/>
+      <c r="P149" s="24"/>
+      <c r="Q149" s="24"/>
     </row>
     <row r="150" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -13831,25 +13842,25 @@
       <c r="Q166" s="14"/>
     </row>
     <row r="167" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="26" t="s">
+      <c r="A167" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="B167" s="26"/>
-      <c r="C167" s="26"/>
-      <c r="D167" s="26"/>
-      <c r="E167" s="26"/>
-      <c r="F167" s="26"/>
-      <c r="G167" s="26"/>
-      <c r="H167" s="26"/>
-      <c r="I167" s="26"/>
-      <c r="J167" s="26"/>
-      <c r="K167" s="26"/>
-      <c r="L167" s="26"/>
-      <c r="M167" s="26"/>
-      <c r="N167" s="26"/>
-      <c r="O167" s="26"/>
-      <c r="P167" s="26"/>
-      <c r="Q167" s="26"/>
+      <c r="B167" s="24"/>
+      <c r="C167" s="24"/>
+      <c r="D167" s="24"/>
+      <c r="E167" s="24"/>
+      <c r="F167" s="24"/>
+      <c r="G167" s="24"/>
+      <c r="H167" s="24"/>
+      <c r="I167" s="24"/>
+      <c r="J167" s="24"/>
+      <c r="K167" s="24"/>
+      <c r="L167" s="24"/>
+      <c r="M167" s="24"/>
+      <c r="N167" s="24"/>
+      <c r="O167" s="24"/>
+      <c r="P167" s="24"/>
+      <c r="Q167" s="24"/>
     </row>
     <row r="168" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -14349,25 +14360,25 @@
       <c r="Q183" s="14"/>
     </row>
     <row r="184" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="26" t="s">
+      <c r="A184" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="B184" s="26"/>
-      <c r="C184" s="26"/>
-      <c r="D184" s="26"/>
-      <c r="E184" s="26"/>
-      <c r="F184" s="26"/>
-      <c r="G184" s="26"/>
-      <c r="H184" s="26"/>
-      <c r="I184" s="26"/>
-      <c r="J184" s="26"/>
-      <c r="K184" s="26"/>
-      <c r="L184" s="26"/>
-      <c r="M184" s="26"/>
-      <c r="N184" s="26"/>
-      <c r="O184" s="26"/>
-      <c r="P184" s="26"/>
-      <c r="Q184" s="26"/>
+      <c r="B184" s="24"/>
+      <c r="C184" s="24"/>
+      <c r="D184" s="24"/>
+      <c r="E184" s="24"/>
+      <c r="F184" s="24"/>
+      <c r="G184" s="24"/>
+      <c r="H184" s="24"/>
+      <c r="I184" s="24"/>
+      <c r="J184" s="24"/>
+      <c r="K184" s="24"/>
+      <c r="L184" s="24"/>
+      <c r="M184" s="24"/>
+      <c r="N184" s="24"/>
+      <c r="O184" s="24"/>
+      <c r="P184" s="24"/>
+      <c r="Q184" s="24"/>
     </row>
     <row r="185" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -14837,25 +14848,25 @@
       <c r="Q199" s="14"/>
     </row>
     <row r="200" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="26" t="s">
+      <c r="A200" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="B200" s="26"/>
-      <c r="C200" s="26"/>
-      <c r="D200" s="26"/>
-      <c r="E200" s="26"/>
-      <c r="F200" s="26"/>
-      <c r="G200" s="26"/>
-      <c r="H200" s="26"/>
-      <c r="I200" s="26"/>
-      <c r="J200" s="26"/>
-      <c r="K200" s="26"/>
-      <c r="L200" s="26"/>
-      <c r="M200" s="26"/>
-      <c r="N200" s="26"/>
-      <c r="O200" s="26"/>
-      <c r="P200" s="26"/>
-      <c r="Q200" s="26"/>
+      <c r="B200" s="24"/>
+      <c r="C200" s="24"/>
+      <c r="D200" s="24"/>
+      <c r="E200" s="24"/>
+      <c r="F200" s="24"/>
+      <c r="G200" s="24"/>
+      <c r="H200" s="24"/>
+      <c r="I200" s="24"/>
+      <c r="J200" s="24"/>
+      <c r="K200" s="24"/>
+      <c r="L200" s="24"/>
+      <c r="M200" s="24"/>
+      <c r="N200" s="24"/>
+      <c r="O200" s="24"/>
+      <c r="P200" s="24"/>
+      <c r="Q200" s="24"/>
     </row>
     <row r="201" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -15415,25 +15426,25 @@
       <c r="Q218" s="14"/>
     </row>
     <row r="219" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="26" t="s">
+      <c r="A219" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="B219" s="26"/>
-      <c r="C219" s="26"/>
-      <c r="D219" s="26"/>
-      <c r="E219" s="26"/>
-      <c r="F219" s="26"/>
-      <c r="G219" s="26"/>
-      <c r="H219" s="26"/>
-      <c r="I219" s="26"/>
-      <c r="J219" s="26"/>
-      <c r="K219" s="26"/>
-      <c r="L219" s="26"/>
-      <c r="M219" s="26"/>
-      <c r="N219" s="26"/>
-      <c r="O219" s="26"/>
-      <c r="P219" s="26"/>
-      <c r="Q219" s="26"/>
+      <c r="B219" s="24"/>
+      <c r="C219" s="24"/>
+      <c r="D219" s="24"/>
+      <c r="E219" s="24"/>
+      <c r="F219" s="24"/>
+      <c r="G219" s="24"/>
+      <c r="H219" s="24"/>
+      <c r="I219" s="24"/>
+      <c r="J219" s="24"/>
+      <c r="K219" s="24"/>
+      <c r="L219" s="24"/>
+      <c r="M219" s="24"/>
+      <c r="N219" s="24"/>
+      <c r="O219" s="24"/>
+      <c r="P219" s="24"/>
+      <c r="Q219" s="24"/>
     </row>
     <row r="220" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -15933,25 +15944,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="26" t="s">
+      <c r="A236" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B236" s="26"/>
-      <c r="C236" s="26"/>
-      <c r="D236" s="26"/>
-      <c r="E236" s="26"/>
-      <c r="F236" s="26"/>
-      <c r="G236" s="26"/>
-      <c r="H236" s="26"/>
-      <c r="I236" s="26"/>
-      <c r="J236" s="26"/>
-      <c r="K236" s="26"/>
-      <c r="L236" s="26"/>
-      <c r="M236" s="26"/>
-      <c r="N236" s="26"/>
-      <c r="O236" s="26"/>
-      <c r="P236" s="26"/>
-      <c r="Q236" s="26"/>
+      <c r="B236" s="24"/>
+      <c r="C236" s="24"/>
+      <c r="D236" s="24"/>
+      <c r="E236" s="24"/>
+      <c r="F236" s="24"/>
+      <c r="G236" s="24"/>
+      <c r="H236" s="24"/>
+      <c r="I236" s="24"/>
+      <c r="J236" s="24"/>
+      <c r="K236" s="24"/>
+      <c r="L236" s="24"/>
+      <c r="M236" s="24"/>
+      <c r="N236" s="24"/>
+      <c r="O236" s="24"/>
+      <c r="P236" s="24"/>
+      <c r="Q236" s="24"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -16481,25 +16492,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="26" t="s">
+      <c r="A254" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="B254" s="26"/>
-      <c r="C254" s="26"/>
-      <c r="D254" s="26"/>
-      <c r="E254" s="26"/>
-      <c r="F254" s="26"/>
-      <c r="G254" s="26"/>
-      <c r="H254" s="26"/>
-      <c r="I254" s="26"/>
-      <c r="J254" s="26"/>
-      <c r="K254" s="26"/>
-      <c r="L254" s="26"/>
-      <c r="M254" s="26"/>
-      <c r="N254" s="26"/>
-      <c r="O254" s="26"/>
-      <c r="P254" s="26"/>
-      <c r="Q254" s="26"/>
+      <c r="B254" s="24"/>
+      <c r="C254" s="24"/>
+      <c r="D254" s="24"/>
+      <c r="E254" s="24"/>
+      <c r="F254" s="24"/>
+      <c r="G254" s="24"/>
+      <c r="H254" s="24"/>
+      <c r="I254" s="24"/>
+      <c r="J254" s="24"/>
+      <c r="K254" s="24"/>
+      <c r="L254" s="24"/>
+      <c r="M254" s="24"/>
+      <c r="N254" s="24"/>
+      <c r="O254" s="24"/>
+      <c r="P254" s="24"/>
+      <c r="Q254" s="24"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -17059,25 +17070,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="26" t="s">
+      <c r="A273" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="B273" s="26"/>
-      <c r="C273" s="26"/>
-      <c r="D273" s="26"/>
-      <c r="E273" s="26"/>
-      <c r="F273" s="26"/>
-      <c r="G273" s="26"/>
-      <c r="H273" s="26"/>
-      <c r="I273" s="26"/>
-      <c r="J273" s="26"/>
-      <c r="K273" s="26"/>
-      <c r="L273" s="26"/>
-      <c r="M273" s="26"/>
-      <c r="N273" s="26"/>
-      <c r="O273" s="26"/>
-      <c r="P273" s="26"/>
-      <c r="Q273" s="26"/>
+      <c r="B273" s="24"/>
+      <c r="C273" s="24"/>
+      <c r="D273" s="24"/>
+      <c r="E273" s="24"/>
+      <c r="F273" s="24"/>
+      <c r="G273" s="24"/>
+      <c r="H273" s="24"/>
+      <c r="I273" s="24"/>
+      <c r="J273" s="24"/>
+      <c r="K273" s="24"/>
+      <c r="L273" s="24"/>
+      <c r="M273" s="24"/>
+      <c r="N273" s="24"/>
+      <c r="O273" s="24"/>
+      <c r="P273" s="24"/>
+      <c r="Q273" s="24"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -17637,25 +17648,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="26" t="s">
+      <c r="A292" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="B292" s="26"/>
-      <c r="C292" s="26"/>
-      <c r="D292" s="26"/>
-      <c r="E292" s="26"/>
-      <c r="F292" s="26"/>
-      <c r="G292" s="26"/>
-      <c r="H292" s="26"/>
-      <c r="I292" s="26"/>
-      <c r="J292" s="26"/>
-      <c r="K292" s="26"/>
-      <c r="L292" s="26"/>
-      <c r="M292" s="26"/>
-      <c r="N292" s="26"/>
-      <c r="O292" s="26"/>
-      <c r="P292" s="26"/>
-      <c r="Q292" s="26"/>
+      <c r="B292" s="24"/>
+      <c r="C292" s="24"/>
+      <c r="D292" s="24"/>
+      <c r="E292" s="24"/>
+      <c r="F292" s="24"/>
+      <c r="G292" s="24"/>
+      <c r="H292" s="24"/>
+      <c r="I292" s="24"/>
+      <c r="J292" s="24"/>
+      <c r="K292" s="24"/>
+      <c r="L292" s="24"/>
+      <c r="M292" s="24"/>
+      <c r="N292" s="24"/>
+      <c r="O292" s="24"/>
+      <c r="P292" s="24"/>
+      <c r="Q292" s="24"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -18215,25 +18226,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="26" t="s">
+      <c r="A311" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="B311" s="26"/>
-      <c r="C311" s="26"/>
-      <c r="D311" s="26"/>
-      <c r="E311" s="26"/>
-      <c r="F311" s="26"/>
-      <c r="G311" s="26"/>
-      <c r="H311" s="26"/>
-      <c r="I311" s="26"/>
-      <c r="J311" s="26"/>
-      <c r="K311" s="26"/>
-      <c r="L311" s="26"/>
-      <c r="M311" s="26"/>
-      <c r="N311" s="26"/>
-      <c r="O311" s="26"/>
-      <c r="P311" s="26"/>
-      <c r="Q311" s="26"/>
+      <c r="B311" s="24"/>
+      <c r="C311" s="24"/>
+      <c r="D311" s="24"/>
+      <c r="E311" s="24"/>
+      <c r="F311" s="24"/>
+      <c r="G311" s="24"/>
+      <c r="H311" s="24"/>
+      <c r="I311" s="24"/>
+      <c r="J311" s="24"/>
+      <c r="K311" s="24"/>
+      <c r="L311" s="24"/>
+      <c r="M311" s="24"/>
+      <c r="N311" s="24"/>
+      <c r="O311" s="24"/>
+      <c r="P311" s="24"/>
+      <c r="Q311" s="24"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -18794,26 +18805,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A23:Q23"/>
+    <mergeCell ref="A42:Q42"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="A132:Q132"/>
+    <mergeCell ref="A149:Q149"/>
+    <mergeCell ref="A167:Q167"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A219:Q219"/>
     <mergeCell ref="A236:Q236"/>
     <mergeCell ref="A254:Q254"/>
     <mergeCell ref="A273:Q273"/>
     <mergeCell ref="A292:Q292"/>
     <mergeCell ref="A311:Q311"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A167:Q167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="A23:Q23"/>
-    <mergeCell ref="A42:Q42"/>
   </mergeCells>
   <dataValidations count="268">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or SEA" promptTitle="ATS Pick" prompt="Pick NE or SEA" sqref="F6:Q6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -28471,17 +28482,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -31304,17 +31315,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -34137,17 +34148,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -36970,19 +36981,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="784" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67597EDC-2273-443C-8CFC-60F9110D7C63}"/>
+  <xr:revisionPtr revIDLastSave="810" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFA93FC5-BED3-473F-B4A5-BFBE7A119BA7}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3954" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3965" uniqueCount="346">
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -1087,9 +1087,6 @@
   <si>
     <t>Season Adj</t>
   </si>
-  <si>
-    <t>One game away from completing the first month of the season. A 2 week push remains to complete segment 1</t>
-  </si>
 </sst>
 </file>
 
@@ -1380,13 +1377,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1473,10 +1470,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1668,12 +1661,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1862,7 +1855,7 @@
         <v>23</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1929,7 +1922,7 @@
       </c>
       <c r="B5" t="str">
         <f>'Playoff Picture'!B17</f>
-        <v>Evan Loeser</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="C5" s="3">
         <v>6</v>
@@ -2074,7 +2067,7 @@
       </c>
       <c r="B10" t="str">
         <f>'Playoff Picture'!B22</f>
-        <v>Zach Zarra</v>
+        <v>Jack Smith</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
@@ -2123,7 +2116,7 @@
       </c>
       <c r="B14" t="str">
         <f>INDEX($B$5:$B$10,MATCH(LARGE($H$5:$H$10,1),$H$5:$H$10,0))</f>
-        <v>Evan Loeser</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="C14">
         <f>INDEX($C$5:$C$10,MATCH(LARGE($H$5:$H$10,1),$H$5:$H$10,0))</f>
@@ -2208,7 +2201,7 @@
       </c>
       <c r="B19" t="str">
         <f>INDEX($B$5:$B$10,MATCH(LARGE($H$5:$H$10,6),$H$5:$H$10,0))</f>
-        <v>Zach Zarra</v>
+        <v>Jack Smith</v>
       </c>
       <c r="C19">
         <f>INDEX($C$5:$C$10,MATCH(LARGE($H$5:$H$10,6),$H$5:$H$10,0))</f>
@@ -2284,7 +2277,7 @@
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>'Playoff Wild Card'!B14</f>
-        <v>Evan Loeser</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="B6">
         <f>'Playoff Wild Card'!C14</f>
@@ -2486,7 +2479,7 @@
       </c>
       <c r="B13" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>Evan Loeser</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="C13">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
@@ -2635,7 +2628,7 @@
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>A6</f>
-        <v>Evan Loeser</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="B22" s="3">
         <v>0</v>
@@ -2728,11 +2721,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
-        <v>346</v>
-      </c>
-    </row>
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2864,7 +2853,7 @@
       </c>
       <c r="F2">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H51,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G51,0)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H66,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G66,0)</f>
@@ -2876,7 +2865,7 @@
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I13" si="0">SUM(C2:H2)</f>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J2">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F6="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F21="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F36="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F51="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F66="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F81="W"),1,0)</f>
@@ -2884,7 +2873,7 @@
       </c>
       <c r="K2">
         <f>I2+0.0001</f>
-        <v>44.000100000000003</v>
+        <v>47.000100000000003</v>
       </c>
       <c r="L2">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H6,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G6,0)</f>
@@ -2964,11 +2953,11 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE13" si="2">I2+R2+AC2</f>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AF2">
         <f>AE2+0.0001</f>
-        <v>44.000100000000003</v>
+        <v>47.000100000000003</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2993,7 +2982,7 @@
       </c>
       <c r="F3">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H52,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G52,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H67,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G67,0)</f>
@@ -3005,7 +2994,7 @@
       </c>
       <c r="I3">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J3">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F7="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F22="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F37="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F52="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F67="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F82="W"),1,0)</f>
@@ -3013,7 +3002,7 @@
       </c>
       <c r="K3">
         <f>I3+0.0002</f>
-        <v>41.0002</v>
+        <v>44.0002</v>
       </c>
       <c r="L3">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H7,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G7,0)</f>
@@ -3093,11 +3082,11 @@
       </c>
       <c r="AE3">
         <f t="shared" si="2"/>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AF3">
         <f>AE3+0.0002</f>
-        <v>41.0002</v>
+        <v>44.0002</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3122,7 +3111,7 @@
       </c>
       <c r="F4">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H53,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G53,0)</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H68,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G68,0)</f>
@@ -3134,15 +3123,15 @@
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J4">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F8="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F23="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F38="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F53="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F68="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F83="W"),1,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4">
         <f>I4+0.0003</f>
-        <v>42.000300000000003</v>
+        <v>48.000300000000003</v>
       </c>
       <c r="L4">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H8,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G8,0)</f>
@@ -3222,11 +3211,11 @@
       </c>
       <c r="AE4">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AF4">
         <f>AE4+0.0003</f>
-        <v>42.000300000000003</v>
+        <v>48.000300000000003</v>
       </c>
     </row>
     <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3251,7 +3240,7 @@
       </c>
       <c r="F5">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H54,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G54,0)</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G5">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H69,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G69,0)</f>
@@ -3263,15 +3252,15 @@
       </c>
       <c r="I5">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J5">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F9="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F24="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F39="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F54="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F69="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F84="W"),1,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5">
         <f>I5+0.0004</f>
-        <v>31.000399999999999</v>
+        <v>37.000399999999999</v>
       </c>
       <c r="L5">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H9,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G9,0)</f>
@@ -3351,11 +3340,11 @@
       </c>
       <c r="AE5">
         <f t="shared" si="2"/>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="AF5">
         <f>AE5+0.0004</f>
-        <v>31.000399999999999</v>
+        <v>37.000399999999999</v>
       </c>
     </row>
     <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3638,7 +3627,7 @@
       </c>
       <c r="F8">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H57,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G57,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H72,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G72,0)</f>
@@ -3650,7 +3639,7 @@
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J8">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F12="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F27="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F42="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F57="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F72="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F87="W"),1,0)</f>
@@ -3658,7 +3647,7 @@
       </c>
       <c r="K8">
         <f>I8+0.0007</f>
-        <v>33.000700000000002</v>
+        <v>36.000700000000002</v>
       </c>
       <c r="L8">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H12,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G12,0)</f>
@@ -3738,11 +3727,11 @@
       </c>
       <c r="AE8">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AF8">
         <f>AE8+0.0007</f>
-        <v>33.000700000000002</v>
+        <v>36.000700000000002</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3767,7 +3756,7 @@
       </c>
       <c r="F9">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H58,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G58,0)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H73,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G73,0)</f>
@@ -3779,7 +3768,7 @@
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J9">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F13="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F28="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F43="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F58="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F73="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F88="W"),1,0)</f>
@@ -3787,7 +3776,7 @@
       </c>
       <c r="K9">
         <f>I9+0.0008</f>
-        <v>26.000800000000002</v>
+        <v>29.000800000000002</v>
       </c>
       <c r="L9">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H13,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G13,0)</f>
@@ -3867,11 +3856,11 @@
       </c>
       <c r="AE9">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AF9">
         <f>AE9+0.0008</f>
-        <v>26.000800000000002</v>
+        <v>29.000800000000002</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3896,7 +3885,7 @@
       </c>
       <c r="F10">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H59,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G59,0)</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H74,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G74,0)</f>
@@ -3908,15 +3897,15 @@
       </c>
       <c r="I10">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J10">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F14="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F29="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F44="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F59="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F74="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F89="W"),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <f>I10+0.0009</f>
-        <v>30.000900000000001</v>
+        <v>36.000900000000001</v>
       </c>
       <c r="L10">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H14,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G14,0)</f>
@@ -3996,11 +3985,11 @@
       </c>
       <c r="AE10">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AF10">
         <f>AE10+0.0009</f>
-        <v>30.000900000000001</v>
+        <v>36.000900000000001</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4025,7 +4014,7 @@
       </c>
       <c r="F11">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H60,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G60,0)</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H75,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G75,0)</f>
@@ -4037,15 +4026,15 @@
       </c>
       <c r="I11">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J11">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F15="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F30="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F45="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F60="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F75="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F90="W"),1,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11">
         <f>I11+0.001</f>
-        <v>43.000999999999998</v>
+        <v>49.000999999999998</v>
       </c>
       <c r="L11">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H15,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G15,0)</f>
@@ -4125,11 +4114,11 @@
       </c>
       <c r="AE11">
         <f t="shared" si="2"/>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="AF11">
         <f>AE11+0.001</f>
-        <v>43.000999999999998</v>
+        <v>49.000999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4409,14 +4398,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -5361,14 +5350,14 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="22" t="s">
+      <c r="A56" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="22"/>
-      <c r="C56" s="22"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
@@ -6313,14 +6302,14 @@
       </c>
     </row>
     <row r="111" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="22" t="s">
+      <c r="A111" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B111" s="22"/>
-      <c r="C111" s="22"/>
-      <c r="D111" s="22"/>
-      <c r="E111" s="22"/>
-      <c r="F111" s="22"/>
+      <c r="B111" s="23"/>
+      <c r="C111" s="23"/>
+      <c r="D111" s="23"/>
+      <c r="E111" s="23"/>
+      <c r="F111" s="23"/>
     </row>
     <row r="112" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
@@ -7292,67 +7281,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="24"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8320,25 +8309,25 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="24"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -9306,25 +9295,25 @@
       </c>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+      <c r="A42" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="24"/>
-      <c r="K42" s="24"/>
-      <c r="L42" s="24"/>
-      <c r="M42" s="24"/>
-      <c r="N42" s="24"/>
-      <c r="O42" s="24"/>
-      <c r="P42" s="24"/>
-      <c r="Q42" s="24"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="26"/>
+      <c r="Q42" s="26"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -10254,25 +10243,25 @@
       </c>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="24" t="s">
+      <c r="A61" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="24"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="24"/>
-      <c r="J61" s="24"/>
-      <c r="K61" s="24"/>
-      <c r="L61" s="24"/>
-      <c r="M61" s="24"/>
-      <c r="N61" s="24"/>
-      <c r="O61" s="24"/>
-      <c r="P61" s="24"/>
-      <c r="Q61" s="24"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="26"/>
+      <c r="J61" s="26"/>
+      <c r="K61" s="26"/>
+      <c r="L61" s="26"/>
+      <c r="M61" s="26"/>
+      <c r="N61" s="26"/>
+      <c r="O61" s="26"/>
+      <c r="P61" s="26"/>
+      <c r="Q61" s="26"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -11154,18 +11143,42 @@
         <f>'NFL Schedule'!J75</f>
         <v/>
       </c>
-      <c r="F78" s="10"/>
-      <c r="G78" s="10"/>
-      <c r="H78" s="10"/>
-      <c r="I78" s="10"/>
-      <c r="J78" s="10"/>
-      <c r="K78" s="10"/>
-      <c r="L78" s="10"/>
-      <c r="M78" s="10"/>
-      <c r="N78" s="10"/>
-      <c r="O78" s="10"/>
-      <c r="P78" s="10"/>
-      <c r="Q78" s="10"/>
+      <c r="F78" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H78" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I78" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="J78" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="K78" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="L78" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="M78" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="N78" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="O78" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="P78" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q78" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
@@ -11178,39 +11191,63 @@
         <f>'NFL Schedule'!E76</f>
         <v/>
       </c>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-      <c r="I79" s="14"/>
-      <c r="J79" s="14"/>
-      <c r="K79" s="14"/>
-      <c r="L79" s="14"/>
-      <c r="M79" s="14"/>
-      <c r="N79" s="14"/>
-      <c r="O79" s="14"/>
-      <c r="P79" s="14"/>
-      <c r="Q79" s="14"/>
+      <c r="F79" s="14">
+        <v>45</v>
+      </c>
+      <c r="G79" s="14">
+        <v>45</v>
+      </c>
+      <c r="H79" s="14">
+        <v>51</v>
+      </c>
+      <c r="I79" s="14">
+        <v>40</v>
+      </c>
+      <c r="J79" s="14">
+        <v>32</v>
+      </c>
+      <c r="K79" s="14">
+        <v>42</v>
+      </c>
+      <c r="L79" s="14">
+        <v>42</v>
+      </c>
+      <c r="M79" s="14">
+        <v>45</v>
+      </c>
+      <c r="N79" s="14">
+        <v>49</v>
+      </c>
+      <c r="O79" s="14">
+        <v>42</v>
+      </c>
+      <c r="P79" s="14">
+        <v>41</v>
+      </c>
+      <c r="Q79" s="14">
+        <v>44</v>
+      </c>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="24" t="s">
+      <c r="A80" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="24"/>
-      <c r="C80" s="24"/>
-      <c r="D80" s="24"/>
-      <c r="E80" s="24"/>
-      <c r="F80" s="24"/>
-      <c r="G80" s="24"/>
-      <c r="H80" s="24"/>
-      <c r="I80" s="24"/>
-      <c r="J80" s="24"/>
-      <c r="K80" s="24"/>
-      <c r="L80" s="24"/>
-      <c r="M80" s="24"/>
-      <c r="N80" s="24"/>
-      <c r="O80" s="24"/>
-      <c r="P80" s="24"/>
-      <c r="Q80" s="24"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
+      <c r="I80" s="26"/>
+      <c r="J80" s="26"/>
+      <c r="K80" s="26"/>
+      <c r="L80" s="26"/>
+      <c r="M80" s="26"/>
+      <c r="N80" s="26"/>
+      <c r="O80" s="26"/>
+      <c r="P80" s="26"/>
+      <c r="Q80" s="26"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -11740,25 +11777,25 @@
       <c r="Q97" s="14"/>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="24" t="s">
+      <c r="A98" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="24"/>
-      <c r="C98" s="24"/>
-      <c r="D98" s="24"/>
-      <c r="E98" s="24"/>
-      <c r="F98" s="24"/>
-      <c r="G98" s="24"/>
-      <c r="H98" s="24"/>
-      <c r="I98" s="24"/>
-      <c r="J98" s="24"/>
-      <c r="K98" s="24"/>
-      <c r="L98" s="24"/>
-      <c r="M98" s="24"/>
-      <c r="N98" s="24"/>
-      <c r="O98" s="24"/>
-      <c r="P98" s="24"/>
-      <c r="Q98" s="24"/>
+      <c r="B98" s="26"/>
+      <c r="C98" s="26"/>
+      <c r="D98" s="26"/>
+      <c r="E98" s="26"/>
+      <c r="F98" s="26"/>
+      <c r="G98" s="26"/>
+      <c r="H98" s="26"/>
+      <c r="I98" s="26"/>
+      <c r="J98" s="26"/>
+      <c r="K98" s="26"/>
+      <c r="L98" s="26"/>
+      <c r="M98" s="26"/>
+      <c r="N98" s="26"/>
+      <c r="O98" s="26"/>
+      <c r="P98" s="26"/>
+      <c r="Q98" s="26"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -12258,25 +12295,25 @@
       <c r="Q114" s="14"/>
     </row>
     <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="24" t="s">
+      <c r="A115" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="24"/>
-      <c r="C115" s="24"/>
-      <c r="D115" s="24"/>
-      <c r="E115" s="24"/>
-      <c r="F115" s="24"/>
-      <c r="G115" s="24"/>
-      <c r="H115" s="24"/>
-      <c r="I115" s="24"/>
-      <c r="J115" s="24"/>
-      <c r="K115" s="24"/>
-      <c r="L115" s="24"/>
-      <c r="M115" s="24"/>
-      <c r="N115" s="24"/>
-      <c r="O115" s="24"/>
-      <c r="P115" s="24"/>
-      <c r="Q115" s="24"/>
+      <c r="B115" s="26"/>
+      <c r="C115" s="26"/>
+      <c r="D115" s="26"/>
+      <c r="E115" s="26"/>
+      <c r="F115" s="26"/>
+      <c r="G115" s="26"/>
+      <c r="H115" s="26"/>
+      <c r="I115" s="26"/>
+      <c r="J115" s="26"/>
+      <c r="K115" s="26"/>
+      <c r="L115" s="26"/>
+      <c r="M115" s="26"/>
+      <c r="N115" s="26"/>
+      <c r="O115" s="26"/>
+      <c r="P115" s="26"/>
+      <c r="Q115" s="26"/>
     </row>
     <row r="116" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -12776,25 +12813,25 @@
       <c r="Q131" s="14"/>
     </row>
     <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="24" t="s">
+      <c r="A132" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="B132" s="24"/>
-      <c r="C132" s="24"/>
-      <c r="D132" s="24"/>
-      <c r="E132" s="24"/>
-      <c r="F132" s="24"/>
-      <c r="G132" s="24"/>
-      <c r="H132" s="24"/>
-      <c r="I132" s="24"/>
-      <c r="J132" s="24"/>
-      <c r="K132" s="24"/>
-      <c r="L132" s="24"/>
-      <c r="M132" s="24"/>
-      <c r="N132" s="24"/>
-      <c r="O132" s="24"/>
-      <c r="P132" s="24"/>
-      <c r="Q132" s="24"/>
+      <c r="B132" s="26"/>
+      <c r="C132" s="26"/>
+      <c r="D132" s="26"/>
+      <c r="E132" s="26"/>
+      <c r="F132" s="26"/>
+      <c r="G132" s="26"/>
+      <c r="H132" s="26"/>
+      <c r="I132" s="26"/>
+      <c r="J132" s="26"/>
+      <c r="K132" s="26"/>
+      <c r="L132" s="26"/>
+      <c r="M132" s="26"/>
+      <c r="N132" s="26"/>
+      <c r="O132" s="26"/>
+      <c r="P132" s="26"/>
+      <c r="Q132" s="26"/>
     </row>
     <row r="133" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -13294,25 +13331,25 @@
       <c r="Q148" s="14"/>
     </row>
     <row r="149" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="24" t="s">
+      <c r="A149" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="B149" s="24"/>
-      <c r="C149" s="24"/>
-      <c r="D149" s="24"/>
-      <c r="E149" s="24"/>
-      <c r="F149" s="24"/>
-      <c r="G149" s="24"/>
-      <c r="H149" s="24"/>
-      <c r="I149" s="24"/>
-      <c r="J149" s="24"/>
-      <c r="K149" s="24"/>
-      <c r="L149" s="24"/>
-      <c r="M149" s="24"/>
-      <c r="N149" s="24"/>
-      <c r="O149" s="24"/>
-      <c r="P149" s="24"/>
-      <c r="Q149" s="24"/>
+      <c r="B149" s="26"/>
+      <c r="C149" s="26"/>
+      <c r="D149" s="26"/>
+      <c r="E149" s="26"/>
+      <c r="F149" s="26"/>
+      <c r="G149" s="26"/>
+      <c r="H149" s="26"/>
+      <c r="I149" s="26"/>
+      <c r="J149" s="26"/>
+      <c r="K149" s="26"/>
+      <c r="L149" s="26"/>
+      <c r="M149" s="26"/>
+      <c r="N149" s="26"/>
+      <c r="O149" s="26"/>
+      <c r="P149" s="26"/>
+      <c r="Q149" s="26"/>
     </row>
     <row r="150" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -13842,25 +13879,25 @@
       <c r="Q166" s="14"/>
     </row>
     <row r="167" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="24" t="s">
+      <c r="A167" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="B167" s="24"/>
-      <c r="C167" s="24"/>
-      <c r="D167" s="24"/>
-      <c r="E167" s="24"/>
-      <c r="F167" s="24"/>
-      <c r="G167" s="24"/>
-      <c r="H167" s="24"/>
-      <c r="I167" s="24"/>
-      <c r="J167" s="24"/>
-      <c r="K167" s="24"/>
-      <c r="L167" s="24"/>
-      <c r="M167" s="24"/>
-      <c r="N167" s="24"/>
-      <c r="O167" s="24"/>
-      <c r="P167" s="24"/>
-      <c r="Q167" s="24"/>
+      <c r="B167" s="26"/>
+      <c r="C167" s="26"/>
+      <c r="D167" s="26"/>
+      <c r="E167" s="26"/>
+      <c r="F167" s="26"/>
+      <c r="G167" s="26"/>
+      <c r="H167" s="26"/>
+      <c r="I167" s="26"/>
+      <c r="J167" s="26"/>
+      <c r="K167" s="26"/>
+      <c r="L167" s="26"/>
+      <c r="M167" s="26"/>
+      <c r="N167" s="26"/>
+      <c r="O167" s="26"/>
+      <c r="P167" s="26"/>
+      <c r="Q167" s="26"/>
     </row>
     <row r="168" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -14360,25 +14397,25 @@
       <c r="Q183" s="14"/>
     </row>
     <row r="184" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="24" t="s">
+      <c r="A184" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="B184" s="24"/>
-      <c r="C184" s="24"/>
-      <c r="D184" s="24"/>
-      <c r="E184" s="24"/>
-      <c r="F184" s="24"/>
-      <c r="G184" s="24"/>
-      <c r="H184" s="24"/>
-      <c r="I184" s="24"/>
-      <c r="J184" s="24"/>
-      <c r="K184" s="24"/>
-      <c r="L184" s="24"/>
-      <c r="M184" s="24"/>
-      <c r="N184" s="24"/>
-      <c r="O184" s="24"/>
-      <c r="P184" s="24"/>
-      <c r="Q184" s="24"/>
+      <c r="B184" s="26"/>
+      <c r="C184" s="26"/>
+      <c r="D184" s="26"/>
+      <c r="E184" s="26"/>
+      <c r="F184" s="26"/>
+      <c r="G184" s="26"/>
+      <c r="H184" s="26"/>
+      <c r="I184" s="26"/>
+      <c r="J184" s="26"/>
+      <c r="K184" s="26"/>
+      <c r="L184" s="26"/>
+      <c r="M184" s="26"/>
+      <c r="N184" s="26"/>
+      <c r="O184" s="26"/>
+      <c r="P184" s="26"/>
+      <c r="Q184" s="26"/>
     </row>
     <row r="185" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -14848,25 +14885,25 @@
       <c r="Q199" s="14"/>
     </row>
     <row r="200" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="24" t="s">
+      <c r="A200" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="B200" s="24"/>
-      <c r="C200" s="24"/>
-      <c r="D200" s="24"/>
-      <c r="E200" s="24"/>
-      <c r="F200" s="24"/>
-      <c r="G200" s="24"/>
-      <c r="H200" s="24"/>
-      <c r="I200" s="24"/>
-      <c r="J200" s="24"/>
-      <c r="K200" s="24"/>
-      <c r="L200" s="24"/>
-      <c r="M200" s="24"/>
-      <c r="N200" s="24"/>
-      <c r="O200" s="24"/>
-      <c r="P200" s="24"/>
-      <c r="Q200" s="24"/>
+      <c r="B200" s="26"/>
+      <c r="C200" s="26"/>
+      <c r="D200" s="26"/>
+      <c r="E200" s="26"/>
+      <c r="F200" s="26"/>
+      <c r="G200" s="26"/>
+      <c r="H200" s="26"/>
+      <c r="I200" s="26"/>
+      <c r="J200" s="26"/>
+      <c r="K200" s="26"/>
+      <c r="L200" s="26"/>
+      <c r="M200" s="26"/>
+      <c r="N200" s="26"/>
+      <c r="O200" s="26"/>
+      <c r="P200" s="26"/>
+      <c r="Q200" s="26"/>
     </row>
     <row r="201" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -15426,25 +15463,25 @@
       <c r="Q218" s="14"/>
     </row>
     <row r="219" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="24" t="s">
+      <c r="A219" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="B219" s="24"/>
-      <c r="C219" s="24"/>
-      <c r="D219" s="24"/>
-      <c r="E219" s="24"/>
-      <c r="F219" s="24"/>
-      <c r="G219" s="24"/>
-      <c r="H219" s="24"/>
-      <c r="I219" s="24"/>
-      <c r="J219" s="24"/>
-      <c r="K219" s="24"/>
-      <c r="L219" s="24"/>
-      <c r="M219" s="24"/>
-      <c r="N219" s="24"/>
-      <c r="O219" s="24"/>
-      <c r="P219" s="24"/>
-      <c r="Q219" s="24"/>
+      <c r="B219" s="26"/>
+      <c r="C219" s="26"/>
+      <c r="D219" s="26"/>
+      <c r="E219" s="26"/>
+      <c r="F219" s="26"/>
+      <c r="G219" s="26"/>
+      <c r="H219" s="26"/>
+      <c r="I219" s="26"/>
+      <c r="J219" s="26"/>
+      <c r="K219" s="26"/>
+      <c r="L219" s="26"/>
+      <c r="M219" s="26"/>
+      <c r="N219" s="26"/>
+      <c r="O219" s="26"/>
+      <c r="P219" s="26"/>
+      <c r="Q219" s="26"/>
     </row>
     <row r="220" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -15944,25 +15981,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="24" t="s">
+      <c r="A236" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="B236" s="24"/>
-      <c r="C236" s="24"/>
-      <c r="D236" s="24"/>
-      <c r="E236" s="24"/>
-      <c r="F236" s="24"/>
-      <c r="G236" s="24"/>
-      <c r="H236" s="24"/>
-      <c r="I236" s="24"/>
-      <c r="J236" s="24"/>
-      <c r="K236" s="24"/>
-      <c r="L236" s="24"/>
-      <c r="M236" s="24"/>
-      <c r="N236" s="24"/>
-      <c r="O236" s="24"/>
-      <c r="P236" s="24"/>
-      <c r="Q236" s="24"/>
+      <c r="B236" s="26"/>
+      <c r="C236" s="26"/>
+      <c r="D236" s="26"/>
+      <c r="E236" s="26"/>
+      <c r="F236" s="26"/>
+      <c r="G236" s="26"/>
+      <c r="H236" s="26"/>
+      <c r="I236" s="26"/>
+      <c r="J236" s="26"/>
+      <c r="K236" s="26"/>
+      <c r="L236" s="26"/>
+      <c r="M236" s="26"/>
+      <c r="N236" s="26"/>
+      <c r="O236" s="26"/>
+      <c r="P236" s="26"/>
+      <c r="Q236" s="26"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -16492,25 +16529,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="24" t="s">
+      <c r="A254" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="B254" s="24"/>
-      <c r="C254" s="24"/>
-      <c r="D254" s="24"/>
-      <c r="E254" s="24"/>
-      <c r="F254" s="24"/>
-      <c r="G254" s="24"/>
-      <c r="H254" s="24"/>
-      <c r="I254" s="24"/>
-      <c r="J254" s="24"/>
-      <c r="K254" s="24"/>
-      <c r="L254" s="24"/>
-      <c r="M254" s="24"/>
-      <c r="N254" s="24"/>
-      <c r="O254" s="24"/>
-      <c r="P254" s="24"/>
-      <c r="Q254" s="24"/>
+      <c r="B254" s="26"/>
+      <c r="C254" s="26"/>
+      <c r="D254" s="26"/>
+      <c r="E254" s="26"/>
+      <c r="F254" s="26"/>
+      <c r="G254" s="26"/>
+      <c r="H254" s="26"/>
+      <c r="I254" s="26"/>
+      <c r="J254" s="26"/>
+      <c r="K254" s="26"/>
+      <c r="L254" s="26"/>
+      <c r="M254" s="26"/>
+      <c r="N254" s="26"/>
+      <c r="O254" s="26"/>
+      <c r="P254" s="26"/>
+      <c r="Q254" s="26"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -17070,25 +17107,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="24" t="s">
+      <c r="A273" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="B273" s="24"/>
-      <c r="C273" s="24"/>
-      <c r="D273" s="24"/>
-      <c r="E273" s="24"/>
-      <c r="F273" s="24"/>
-      <c r="G273" s="24"/>
-      <c r="H273" s="24"/>
-      <c r="I273" s="24"/>
-      <c r="J273" s="24"/>
-      <c r="K273" s="24"/>
-      <c r="L273" s="24"/>
-      <c r="M273" s="24"/>
-      <c r="N273" s="24"/>
-      <c r="O273" s="24"/>
-      <c r="P273" s="24"/>
-      <c r="Q273" s="24"/>
+      <c r="B273" s="26"/>
+      <c r="C273" s="26"/>
+      <c r="D273" s="26"/>
+      <c r="E273" s="26"/>
+      <c r="F273" s="26"/>
+      <c r="G273" s="26"/>
+      <c r="H273" s="26"/>
+      <c r="I273" s="26"/>
+      <c r="J273" s="26"/>
+      <c r="K273" s="26"/>
+      <c r="L273" s="26"/>
+      <c r="M273" s="26"/>
+      <c r="N273" s="26"/>
+      <c r="O273" s="26"/>
+      <c r="P273" s="26"/>
+      <c r="Q273" s="26"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -17648,25 +17685,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="24" t="s">
+      <c r="A292" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="B292" s="24"/>
-      <c r="C292" s="24"/>
-      <c r="D292" s="24"/>
-      <c r="E292" s="24"/>
-      <c r="F292" s="24"/>
-      <c r="G292" s="24"/>
-      <c r="H292" s="24"/>
-      <c r="I292" s="24"/>
-      <c r="J292" s="24"/>
-      <c r="K292" s="24"/>
-      <c r="L292" s="24"/>
-      <c r="M292" s="24"/>
-      <c r="N292" s="24"/>
-      <c r="O292" s="24"/>
-      <c r="P292" s="24"/>
-      <c r="Q292" s="24"/>
+      <c r="B292" s="26"/>
+      <c r="C292" s="26"/>
+      <c r="D292" s="26"/>
+      <c r="E292" s="26"/>
+      <c r="F292" s="26"/>
+      <c r="G292" s="26"/>
+      <c r="H292" s="26"/>
+      <c r="I292" s="26"/>
+      <c r="J292" s="26"/>
+      <c r="K292" s="26"/>
+      <c r="L292" s="26"/>
+      <c r="M292" s="26"/>
+      <c r="N292" s="26"/>
+      <c r="O292" s="26"/>
+      <c r="P292" s="26"/>
+      <c r="Q292" s="26"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -18226,25 +18263,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="24" t="s">
+      <c r="A311" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="B311" s="24"/>
-      <c r="C311" s="24"/>
-      <c r="D311" s="24"/>
-      <c r="E311" s="24"/>
-      <c r="F311" s="24"/>
-      <c r="G311" s="24"/>
-      <c r="H311" s="24"/>
-      <c r="I311" s="24"/>
-      <c r="J311" s="24"/>
-      <c r="K311" s="24"/>
-      <c r="L311" s="24"/>
-      <c r="M311" s="24"/>
-      <c r="N311" s="24"/>
-      <c r="O311" s="24"/>
-      <c r="P311" s="24"/>
-      <c r="Q311" s="24"/>
+      <c r="B311" s="26"/>
+      <c r="C311" s="26"/>
+      <c r="D311" s="26"/>
+      <c r="E311" s="26"/>
+      <c r="F311" s="26"/>
+      <c r="G311" s="26"/>
+      <c r="H311" s="26"/>
+      <c r="I311" s="26"/>
+      <c r="J311" s="26"/>
+      <c r="K311" s="26"/>
+      <c r="L311" s="26"/>
+      <c r="M311" s="26"/>
+      <c r="N311" s="26"/>
+      <c r="O311" s="26"/>
+      <c r="P311" s="26"/>
+      <c r="Q311" s="26"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -18805,26 +18842,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A236:Q236"/>
+    <mergeCell ref="A254:Q254"/>
+    <mergeCell ref="A273:Q273"/>
+    <mergeCell ref="A292:Q292"/>
+    <mergeCell ref="A311:Q311"/>
+    <mergeCell ref="A149:Q149"/>
+    <mergeCell ref="A167:Q167"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A219:Q219"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="A132:Q132"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A4:Q4"/>
     <mergeCell ref="A23:Q23"/>
     <mergeCell ref="A42:Q42"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A167:Q167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A236:Q236"/>
-    <mergeCell ref="A254:Q254"/>
-    <mergeCell ref="A273:Q273"/>
-    <mergeCell ref="A292:Q292"/>
-    <mergeCell ref="A311:Q311"/>
   </mergeCells>
   <dataValidations count="268">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or SEA" promptTitle="ATS Pick" prompt="Pick NE or SEA" sqref="F6:Q6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -28482,17 +28519,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -31315,17 +31352,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -34148,17 +34185,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -36981,19 +37018,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -37052,7 +37089,7 @@
       </c>
       <c r="F3">
         <f>Helper!F2</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <f>Helper!G2</f>
@@ -37064,7 +37101,7 @@
       </c>
       <c r="I3">
         <f>Helper!I2</f>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J3">
         <f>Helper!J2</f>
@@ -37097,7 +37134,7 @@
       </c>
       <c r="F4">
         <f>Helper!F3</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <f>Helper!G3</f>
@@ -37109,7 +37146,7 @@
       </c>
       <c r="I4">
         <f>Helper!I3</f>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J4">
         <f>Helper!J3</f>
@@ -37142,7 +37179,7 @@
       </c>
       <c r="F5">
         <f>Helper!F4</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G5">
         <f>Helper!G4</f>
@@ -37154,11 +37191,11 @@
       </c>
       <c r="I5">
         <f>Helper!I4</f>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J5">
         <f>Helper!J4</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <f>MAX(Helper!C4:H4)</f>
@@ -37187,7 +37224,7 @@
       </c>
       <c r="F6">
         <f>Helper!F5</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G6">
         <f>Helper!G5</f>
@@ -37199,15 +37236,15 @@
       </c>
       <c r="I6">
         <f>Helper!I5</f>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J6">
         <f>Helper!J5</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6">
         <f>MAX(Helper!C5:H5)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37322,7 +37359,7 @@
       </c>
       <c r="F9">
         <f>Helper!F8</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G9">
         <f>Helper!G8</f>
@@ -37334,7 +37371,7 @@
       </c>
       <c r="I9">
         <f>Helper!I8</f>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J9">
         <f>Helper!J8</f>
@@ -37367,7 +37404,7 @@
       </c>
       <c r="F10">
         <f>Helper!F9</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <f>Helper!G9</f>
@@ -37379,7 +37416,7 @@
       </c>
       <c r="I10">
         <f>Helper!I9</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J10">
         <f>Helper!J9</f>
@@ -37387,7 +37424,7 @@
       </c>
       <c r="K10">
         <f>MAX(Helper!C9:H9)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37412,7 +37449,7 @@
       </c>
       <c r="F11">
         <f>Helper!F10</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <f>Helper!G10</f>
@@ -37424,15 +37461,15 @@
       </c>
       <c r="I11">
         <f>Helper!I10</f>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J11">
         <f>Helper!J10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <f>MAX(Helper!C10:H10)</f>
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37457,7 +37494,7 @@
       </c>
       <c r="F12">
         <f>Helper!F11</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <f>Helper!G11</f>
@@ -37469,11 +37506,11 @@
       </c>
       <c r="I12">
         <f>Helper!I11</f>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J12">
         <f>Helper!J11</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12">
         <f>MAX(Helper!C11:H11)</f>
@@ -38883,7 +38920,7 @@
       </c>
       <c r="C57">
         <f>Helper!I2</f>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D57">
         <f>Helper!R2</f>
@@ -38895,11 +38932,11 @@
       </c>
       <c r="F57">
         <f>Helper!AE2</f>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G57">
         <f>Helper!K2</f>
-        <v>44.000100000000003</v>
+        <v>47.000100000000003</v>
       </c>
       <c r="H57">
         <f>Helper!T2</f>
@@ -38916,7 +38953,7 @@
       </c>
       <c r="C58">
         <f>Helper!I3</f>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D58">
         <f>Helper!R3</f>
@@ -38928,11 +38965,11 @@
       </c>
       <c r="F58">
         <f>Helper!AE3</f>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G58">
         <f>Helper!K3</f>
-        <v>41.0002</v>
+        <v>44.0002</v>
       </c>
       <c r="H58">
         <f>Helper!T3</f>
@@ -38949,7 +38986,7 @@
       </c>
       <c r="C59">
         <f>Helper!I4</f>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D59">
         <f>Helper!R4</f>
@@ -38961,11 +38998,11 @@
       </c>
       <c r="F59">
         <f>Helper!AE4</f>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G59">
         <f>Helper!K4</f>
-        <v>42.000300000000003</v>
+        <v>48.000300000000003</v>
       </c>
       <c r="H59">
         <f>Helper!T4</f>
@@ -38982,7 +39019,7 @@
       </c>
       <c r="C60">
         <f>Helper!I5</f>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D60">
         <f>Helper!R5</f>
@@ -38994,11 +39031,11 @@
       </c>
       <c r="F60">
         <f>Helper!AE5</f>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G60">
         <f>Helper!K5</f>
-        <v>31.000399999999999</v>
+        <v>37.000399999999999</v>
       </c>
       <c r="H60">
         <f>Helper!T5</f>
@@ -39081,7 +39118,7 @@
       </c>
       <c r="C63">
         <f>Helper!I8</f>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D63">
         <f>Helper!R8</f>
@@ -39093,11 +39130,11 @@
       </c>
       <c r="F63">
         <f>Helper!AE8</f>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G63">
         <f>Helper!K8</f>
-        <v>33.000700000000002</v>
+        <v>36.000700000000002</v>
       </c>
       <c r="H63">
         <f>Helper!T8</f>
@@ -39114,7 +39151,7 @@
       </c>
       <c r="C64">
         <f>Helper!I9</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D64">
         <f>Helper!R9</f>
@@ -39126,11 +39163,11 @@
       </c>
       <c r="F64">
         <f>Helper!AE9</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G64">
         <f>Helper!K9</f>
-        <v>26.000800000000002</v>
+        <v>29.000800000000002</v>
       </c>
       <c r="H64">
         <f>Helper!T9</f>
@@ -39147,7 +39184,7 @@
       </c>
       <c r="C65">
         <f>Helper!I10</f>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D65">
         <f>Helper!R10</f>
@@ -39159,11 +39196,11 @@
       </c>
       <c r="F65">
         <f>Helper!AE10</f>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G65">
         <f>Helper!K10</f>
-        <v>30.000900000000001</v>
+        <v>36.000900000000001</v>
       </c>
       <c r="H65">
         <f>Helper!T10</f>
@@ -39180,7 +39217,7 @@
       </c>
       <c r="C66">
         <f>Helper!I11</f>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D66">
         <f>Helper!R11</f>
@@ -39192,11 +39229,11 @@
       </c>
       <c r="F66">
         <f>Helper!AE11</f>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G66">
         <f>Helper!K11</f>
-        <v>43.000999999999998</v>
+        <v>49.000999999999998</v>
       </c>
       <c r="H66">
         <f>Helper!T11</f>
@@ -39332,7 +39369,7 @@
       </c>
       <c r="B5" t="str">
         <f>INDEX(Helper!B$2:B$13,MATCH(MAX(Helper!K$2:K$13),Helper!K$2:K$13,0))</f>
-        <v>Evan Loeser</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="C5" t="s">
         <v>252</v>
@@ -39342,7 +39379,7 @@
       </c>
       <c r="E5" t="str">
         <f>B5</f>
-        <v>Evan Loeser</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="F5" t="str">
         <f>IF(B5="","—","QUALIFIED")</f>
@@ -39500,11 +39537,11 @@
       </c>
       <c r="B13" t="str">
         <f>INDEX(H$40:H$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
-        <v>Zach Zarra</v>
+        <v>Jack Smith</v>
       </c>
       <c r="C13">
         <f>INDEX(I$40:I$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
         <v>263</v>
@@ -39550,7 +39587,7 @@
       </c>
       <c r="B17" t="str">
         <f>E5</f>
-        <v>Evan Loeser</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="C17" t="str">
         <f>D5</f>
@@ -39615,7 +39652,7 @@
       </c>
       <c r="B22" t="str">
         <f>B13</f>
-        <v>Zach Zarra</v>
+        <v>Jack Smith</v>
       </c>
       <c r="C22" t="str">
         <f>"Wild Card 1"</f>
@@ -39980,15 +40017,15 @@
       </c>
       <c r="I40">
         <f>Helper!AE2</f>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J40" t="b">
         <f t="shared" ref="J40:J51" si="1">OR(H40=$E$5,H40=$E$6,H40=$E$7,H40=$E$8,H40=$E$9)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40">
         <f>IF(J40,-1,I40+0.00001)</f>
-        <v>-1</v>
+        <v>47.000010000000003</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39998,7 +40035,7 @@
       </c>
       <c r="I41">
         <f>Helper!AE3</f>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J41" t="b">
         <f t="shared" si="1"/>
@@ -40006,7 +40043,7 @@
       </c>
       <c r="K41">
         <f>IF(J41,-1,I41+0.00002)</f>
-        <v>41.000019999999999</v>
+        <v>44.000019999999999</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40016,7 +40053,7 @@
       </c>
       <c r="I42">
         <f>Helper!AE4</f>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J42" t="b">
         <f t="shared" si="1"/>
@@ -40024,7 +40061,7 @@
       </c>
       <c r="K42">
         <f>IF(J42,-1,I42+0.00003)</f>
-        <v>42.000030000000002</v>
+        <v>48.000030000000002</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40034,7 +40071,7 @@
       </c>
       <c r="I43">
         <f>Helper!AE5</f>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J43" t="b">
         <f t="shared" si="1"/>
@@ -40088,7 +40125,7 @@
       </c>
       <c r="I46">
         <f>Helper!AE8</f>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J46" t="b">
         <f t="shared" si="1"/>
@@ -40096,7 +40133,7 @@
       </c>
       <c r="K46">
         <f>IF(J46,-1,I46+0.00007)</f>
-        <v>33.000070000000001</v>
+        <v>36.000070000000001</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40106,7 +40143,7 @@
       </c>
       <c r="I47">
         <f>Helper!AE9</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J47" t="b">
         <f t="shared" si="1"/>
@@ -40124,7 +40161,7 @@
       </c>
       <c r="I48">
         <f>Helper!AE10</f>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J48" t="b">
         <f t="shared" si="1"/>
@@ -40132,7 +40169,7 @@
       </c>
       <c r="K48">
         <f>IF(J48,-1,I48+0.00009)</f>
-        <v>30.00009</v>
+        <v>36.00009</v>
       </c>
     </row>
     <row r="49" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40142,15 +40179,15 @@
       </c>
       <c r="I49">
         <f>Helper!AE11</f>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J49" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49">
         <f>IF(J49,-1,I49+0.0001)</f>
-        <v>43.000100000000003</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="50" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="810" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFA93FC5-BED3-473F-B4A5-BFBE7A119BA7}"/>
+  <xr:revisionPtr revIDLastSave="813" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E6797B9-7EE4-4C2E-9742-E2471831DF9D}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1381,9 +1381,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1470,6 +1470,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2853,7 +2857,7 @@
       </c>
       <c r="F2">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H51,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G51,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H66,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G66,0)</f>
@@ -2865,7 +2869,7 @@
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I13" si="0">SUM(C2:H2)</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F6="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F21="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F36="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F51="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F66="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F81="W"),1,0)</f>
@@ -2873,7 +2877,7 @@
       </c>
       <c r="K2">
         <f>I2+0.0001</f>
-        <v>47.000100000000003</v>
+        <v>48.000100000000003</v>
       </c>
       <c r="L2">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H6,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G6,0)</f>
@@ -2953,11 +2957,11 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE13" si="2">I2+R2+AC2</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF2">
         <f>AE2+0.0001</f>
-        <v>47.000100000000003</v>
+        <v>48.000100000000003</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2982,7 +2986,7 @@
       </c>
       <c r="F3">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H52,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G52,0)</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H67,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G67,0)</f>
@@ -2994,15 +2998,15 @@
       </c>
       <c r="I3">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J3">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F7="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F22="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F37="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F52="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F67="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F82="W"),1,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
         <f>I3+0.0002</f>
-        <v>44.0002</v>
+        <v>48.0002</v>
       </c>
       <c r="L3">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H7,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G7,0)</f>
@@ -3082,11 +3086,11 @@
       </c>
       <c r="AE3">
         <f t="shared" si="2"/>
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AF3">
         <f>AE3+0.0002</f>
-        <v>44.0002</v>
+        <v>48.0002</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3111,7 +3115,7 @@
       </c>
       <c r="F4">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H53,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G53,0)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H68,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G68,0)</f>
@@ -3123,7 +3127,7 @@
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J4">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F8="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F23="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F38="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F53="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F68="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F83="W"),1,0)</f>
@@ -3131,7 +3135,7 @@
       </c>
       <c r="K4">
         <f>I4+0.0003</f>
-        <v>48.000300000000003</v>
+        <v>49.000300000000003</v>
       </c>
       <c r="L4">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H8,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G8,0)</f>
@@ -3211,11 +3215,11 @@
       </c>
       <c r="AE4">
         <f t="shared" si="2"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AF4">
         <f>AE4+0.0003</f>
-        <v>48.000300000000003</v>
+        <v>49.000300000000003</v>
       </c>
     </row>
     <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3240,7 +3244,7 @@
       </c>
       <c r="F5">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H54,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G54,0)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H69,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G69,0)</f>
@@ -3252,7 +3256,7 @@
       </c>
       <c r="I5">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J5">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F9="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F24="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F39="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F54="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F69="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F84="W"),1,0)</f>
@@ -3260,7 +3264,7 @@
       </c>
       <c r="K5">
         <f>I5+0.0004</f>
-        <v>37.000399999999999</v>
+        <v>38.000399999999999</v>
       </c>
       <c r="L5">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H9,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G9,0)</f>
@@ -3340,11 +3344,11 @@
       </c>
       <c r="AE5">
         <f t="shared" si="2"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AF5">
         <f>AE5+0.0004</f>
-        <v>37.000399999999999</v>
+        <v>38.000399999999999</v>
       </c>
     </row>
     <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3369,7 +3373,7 @@
       </c>
       <c r="F6">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H55,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G55,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H70,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G70,0)</f>
@@ -3381,7 +3385,7 @@
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J6">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F10="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F25="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F40="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F55="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F70="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F85="W"),1,0)</f>
@@ -3389,7 +3393,7 @@
       </c>
       <c r="K6">
         <f>I6+0.0005</f>
-        <v>42.000500000000002</v>
+        <v>43.000500000000002</v>
       </c>
       <c r="L6">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H10,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G10,0)</f>
@@ -3469,11 +3473,11 @@
       </c>
       <c r="AE6">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AF6">
         <f>AE6+0.0005</f>
-        <v>42.000500000000002</v>
+        <v>43.000500000000002</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3498,7 +3502,7 @@
       </c>
       <c r="F7">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H56,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G56,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G7">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H71,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G71,0)</f>
@@ -3510,7 +3514,7 @@
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J7">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F11="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F26="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F41="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F56="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F71="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F86="W"),1,0)</f>
@@ -3518,7 +3522,7 @@
       </c>
       <c r="K7">
         <f>I7+0.0006</f>
-        <v>39.000599999999999</v>
+        <v>40.000599999999999</v>
       </c>
       <c r="L7">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H11,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G11,0)</f>
@@ -3598,11 +3602,11 @@
       </c>
       <c r="AE7">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AF7">
         <f>AE7+0.0006</f>
-        <v>39.000599999999999</v>
+        <v>40.000599999999999</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3627,7 +3631,7 @@
       </c>
       <c r="F8">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H57,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G57,0)</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G8">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H72,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G72,0)</f>
@@ -3639,7 +3643,7 @@
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J8">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F12="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F27="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F42="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F57="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F72="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F87="W"),1,0)</f>
@@ -3647,7 +3651,7 @@
       </c>
       <c r="K8">
         <f>I8+0.0007</f>
-        <v>36.000700000000002</v>
+        <v>33.000700000000002</v>
       </c>
       <c r="L8">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H12,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G12,0)</f>
@@ -3727,11 +3731,11 @@
       </c>
       <c r="AE8">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="AF8">
         <f>AE8+0.0007</f>
-        <v>36.000700000000002</v>
+        <v>33.000700000000002</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3756,7 +3760,7 @@
       </c>
       <c r="F9">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H58,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G58,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H73,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G73,0)</f>
@@ -3768,7 +3772,7 @@
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J9">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F13="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F28="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F43="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F58="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F73="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F88="W"),1,0)</f>
@@ -3776,7 +3780,7 @@
       </c>
       <c r="K9">
         <f>I9+0.0008</f>
-        <v>29.000800000000002</v>
+        <v>30.000800000000002</v>
       </c>
       <c r="L9">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H13,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G13,0)</f>
@@ -3856,11 +3860,11 @@
       </c>
       <c r="AE9">
         <f t="shared" si="2"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF9">
         <f>AE9+0.0008</f>
-        <v>29.000800000000002</v>
+        <v>30.000800000000002</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3885,7 +3889,7 @@
       </c>
       <c r="F10">
         <f>IF(Roster!$B$16&gt;=4,'Wk 1-6 Input'!H59,0)+IF(Roster!$B$16&gt;4,'Wk 1-6 Input'!G59,0)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H74,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G74,0)</f>
@@ -3897,7 +3901,7 @@
       </c>
       <c r="I10">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J10">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F14="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F29="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F44="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F59="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F74="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F89="W"),1,0)</f>
@@ -3905,7 +3909,7 @@
       </c>
       <c r="K10">
         <f>I10+0.0009</f>
-        <v>36.000900000000001</v>
+        <v>37.000900000000001</v>
       </c>
       <c r="L10">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H14,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G14,0)</f>
@@ -3985,11 +3989,11 @@
       </c>
       <c r="AE10">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AF10">
         <f>AE10+0.0009</f>
-        <v>36.000900000000001</v>
+        <v>37.000900000000001</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7281,67 +7285,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8309,25 +8313,25 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="26"/>
-      <c r="P23" s="26"/>
-      <c r="Q23" s="26"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="24"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="24"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -9295,25 +9299,25 @@
       </c>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="26" t="s">
+      <c r="A42" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="26"/>
-      <c r="L42" s="26"/>
-      <c r="M42" s="26"/>
-      <c r="N42" s="26"/>
-      <c r="O42" s="26"/>
-      <c r="P42" s="26"/>
-      <c r="Q42" s="26"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="24"/>
+      <c r="N42" s="24"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="24"/>
+      <c r="Q42" s="24"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -10243,25 +10247,25 @@
       </c>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="26" t="s">
+      <c r="A61" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="26"/>
-      <c r="C61" s="26"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="26"/>
-      <c r="F61" s="26"/>
-      <c r="G61" s="26"/>
-      <c r="H61" s="26"/>
-      <c r="I61" s="26"/>
-      <c r="J61" s="26"/>
-      <c r="K61" s="26"/>
-      <c r="L61" s="26"/>
-      <c r="M61" s="26"/>
-      <c r="N61" s="26"/>
-      <c r="O61" s="26"/>
-      <c r="P61" s="26"/>
-      <c r="Q61" s="26"/>
+      <c r="B61" s="24"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="24"/>
+      <c r="J61" s="24"/>
+      <c r="K61" s="24"/>
+      <c r="L61" s="24"/>
+      <c r="M61" s="24"/>
+      <c r="N61" s="24"/>
+      <c r="O61" s="24"/>
+      <c r="P61" s="24"/>
+      <c r="Q61" s="24"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -11141,7 +11145,7 @@
       </c>
       <c r="E78" s="9" t="str">
         <f>'NFL Schedule'!J75</f>
-        <v/>
+        <v>ATL</v>
       </c>
       <c r="F78" s="10" t="s">
         <v>73</v>
@@ -11187,9 +11191,9 @@
       <c r="B79" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="E79" s="13" t="str">
+      <c r="E79" s="13">
         <f>'NFL Schedule'!E76</f>
-        <v/>
+        <v>69</v>
       </c>
       <c r="F79" s="14">
         <v>45</v>
@@ -11229,25 +11233,25 @@
       </c>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="26" t="s">
+      <c r="A80" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="26"/>
-      <c r="C80" s="26"/>
-      <c r="D80" s="26"/>
-      <c r="E80" s="26"/>
-      <c r="F80" s="26"/>
-      <c r="G80" s="26"/>
-      <c r="H80" s="26"/>
-      <c r="I80" s="26"/>
-      <c r="J80" s="26"/>
-      <c r="K80" s="26"/>
-      <c r="L80" s="26"/>
-      <c r="M80" s="26"/>
-      <c r="N80" s="26"/>
-      <c r="O80" s="26"/>
-      <c r="P80" s="26"/>
-      <c r="Q80" s="26"/>
+      <c r="B80" s="24"/>
+      <c r="C80" s="24"/>
+      <c r="D80" s="24"/>
+      <c r="E80" s="24"/>
+      <c r="F80" s="24"/>
+      <c r="G80" s="24"/>
+      <c r="H80" s="24"/>
+      <c r="I80" s="24"/>
+      <c r="J80" s="24"/>
+      <c r="K80" s="24"/>
+      <c r="L80" s="24"/>
+      <c r="M80" s="24"/>
+      <c r="N80" s="24"/>
+      <c r="O80" s="24"/>
+      <c r="P80" s="24"/>
+      <c r="Q80" s="24"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -11777,25 +11781,25 @@
       <c r="Q97" s="14"/>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="26" t="s">
+      <c r="A98" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="26"/>
-      <c r="C98" s="26"/>
-      <c r="D98" s="26"/>
-      <c r="E98" s="26"/>
-      <c r="F98" s="26"/>
-      <c r="G98" s="26"/>
-      <c r="H98" s="26"/>
-      <c r="I98" s="26"/>
-      <c r="J98" s="26"/>
-      <c r="K98" s="26"/>
-      <c r="L98" s="26"/>
-      <c r="M98" s="26"/>
-      <c r="N98" s="26"/>
-      <c r="O98" s="26"/>
-      <c r="P98" s="26"/>
-      <c r="Q98" s="26"/>
+      <c r="B98" s="24"/>
+      <c r="C98" s="24"/>
+      <c r="D98" s="24"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24"/>
+      <c r="H98" s="24"/>
+      <c r="I98" s="24"/>
+      <c r="J98" s="24"/>
+      <c r="K98" s="24"/>
+      <c r="L98" s="24"/>
+      <c r="M98" s="24"/>
+      <c r="N98" s="24"/>
+      <c r="O98" s="24"/>
+      <c r="P98" s="24"/>
+      <c r="Q98" s="24"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -12295,25 +12299,25 @@
       <c r="Q114" s="14"/>
     </row>
     <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="26" t="s">
+      <c r="A115" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="26"/>
-      <c r="C115" s="26"/>
-      <c r="D115" s="26"/>
-      <c r="E115" s="26"/>
-      <c r="F115" s="26"/>
-      <c r="G115" s="26"/>
-      <c r="H115" s="26"/>
-      <c r="I115" s="26"/>
-      <c r="J115" s="26"/>
-      <c r="K115" s="26"/>
-      <c r="L115" s="26"/>
-      <c r="M115" s="26"/>
-      <c r="N115" s="26"/>
-      <c r="O115" s="26"/>
-      <c r="P115" s="26"/>
-      <c r="Q115" s="26"/>
+      <c r="B115" s="24"/>
+      <c r="C115" s="24"/>
+      <c r="D115" s="24"/>
+      <c r="E115" s="24"/>
+      <c r="F115" s="24"/>
+      <c r="G115" s="24"/>
+      <c r="H115" s="24"/>
+      <c r="I115" s="24"/>
+      <c r="J115" s="24"/>
+      <c r="K115" s="24"/>
+      <c r="L115" s="24"/>
+      <c r="M115" s="24"/>
+      <c r="N115" s="24"/>
+      <c r="O115" s="24"/>
+      <c r="P115" s="24"/>
+      <c r="Q115" s="24"/>
     </row>
     <row r="116" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -12813,25 +12817,25 @@
       <c r="Q131" s="14"/>
     </row>
     <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="26" t="s">
+      <c r="A132" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="B132" s="26"/>
-      <c r="C132" s="26"/>
-      <c r="D132" s="26"/>
-      <c r="E132" s="26"/>
-      <c r="F132" s="26"/>
-      <c r="G132" s="26"/>
-      <c r="H132" s="26"/>
-      <c r="I132" s="26"/>
-      <c r="J132" s="26"/>
-      <c r="K132" s="26"/>
-      <c r="L132" s="26"/>
-      <c r="M132" s="26"/>
-      <c r="N132" s="26"/>
-      <c r="O132" s="26"/>
-      <c r="P132" s="26"/>
-      <c r="Q132" s="26"/>
+      <c r="B132" s="24"/>
+      <c r="C132" s="24"/>
+      <c r="D132" s="24"/>
+      <c r="E132" s="24"/>
+      <c r="F132" s="24"/>
+      <c r="G132" s="24"/>
+      <c r="H132" s="24"/>
+      <c r="I132" s="24"/>
+      <c r="J132" s="24"/>
+      <c r="K132" s="24"/>
+      <c r="L132" s="24"/>
+      <c r="M132" s="24"/>
+      <c r="N132" s="24"/>
+      <c r="O132" s="24"/>
+      <c r="P132" s="24"/>
+      <c r="Q132" s="24"/>
     </row>
     <row r="133" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -13331,25 +13335,25 @@
       <c r="Q148" s="14"/>
     </row>
     <row r="149" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="26" t="s">
+      <c r="A149" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="B149" s="26"/>
-      <c r="C149" s="26"/>
-      <c r="D149" s="26"/>
-      <c r="E149" s="26"/>
-      <c r="F149" s="26"/>
-      <c r="G149" s="26"/>
-      <c r="H149" s="26"/>
-      <c r="I149" s="26"/>
-      <c r="J149" s="26"/>
-      <c r="K149" s="26"/>
-      <c r="L149" s="26"/>
-      <c r="M149" s="26"/>
-      <c r="N149" s="26"/>
-      <c r="O149" s="26"/>
-      <c r="P149" s="26"/>
-      <c r="Q149" s="26"/>
+      <c r="B149" s="24"/>
+      <c r="C149" s="24"/>
+      <c r="D149" s="24"/>
+      <c r="E149" s="24"/>
+      <c r="F149" s="24"/>
+      <c r="G149" s="24"/>
+      <c r="H149" s="24"/>
+      <c r="I149" s="24"/>
+      <c r="J149" s="24"/>
+      <c r="K149" s="24"/>
+      <c r="L149" s="24"/>
+      <c r="M149" s="24"/>
+      <c r="N149" s="24"/>
+      <c r="O149" s="24"/>
+      <c r="P149" s="24"/>
+      <c r="Q149" s="24"/>
     </row>
     <row r="150" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -13879,25 +13883,25 @@
       <c r="Q166" s="14"/>
     </row>
     <row r="167" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="26" t="s">
+      <c r="A167" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="B167" s="26"/>
-      <c r="C167" s="26"/>
-      <c r="D167" s="26"/>
-      <c r="E167" s="26"/>
-      <c r="F167" s="26"/>
-      <c r="G167" s="26"/>
-      <c r="H167" s="26"/>
-      <c r="I167" s="26"/>
-      <c r="J167" s="26"/>
-      <c r="K167" s="26"/>
-      <c r="L167" s="26"/>
-      <c r="M167" s="26"/>
-      <c r="N167" s="26"/>
-      <c r="O167" s="26"/>
-      <c r="P167" s="26"/>
-      <c r="Q167" s="26"/>
+      <c r="B167" s="24"/>
+      <c r="C167" s="24"/>
+      <c r="D167" s="24"/>
+      <c r="E167" s="24"/>
+      <c r="F167" s="24"/>
+      <c r="G167" s="24"/>
+      <c r="H167" s="24"/>
+      <c r="I167" s="24"/>
+      <c r="J167" s="24"/>
+      <c r="K167" s="24"/>
+      <c r="L167" s="24"/>
+      <c r="M167" s="24"/>
+      <c r="N167" s="24"/>
+      <c r="O167" s="24"/>
+      <c r="P167" s="24"/>
+      <c r="Q167" s="24"/>
     </row>
     <row r="168" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -14397,25 +14401,25 @@
       <c r="Q183" s="14"/>
     </row>
     <row r="184" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="26" t="s">
+      <c r="A184" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="B184" s="26"/>
-      <c r="C184" s="26"/>
-      <c r="D184" s="26"/>
-      <c r="E184" s="26"/>
-      <c r="F184" s="26"/>
-      <c r="G184" s="26"/>
-      <c r="H184" s="26"/>
-      <c r="I184" s="26"/>
-      <c r="J184" s="26"/>
-      <c r="K184" s="26"/>
-      <c r="L184" s="26"/>
-      <c r="M184" s="26"/>
-      <c r="N184" s="26"/>
-      <c r="O184" s="26"/>
-      <c r="P184" s="26"/>
-      <c r="Q184" s="26"/>
+      <c r="B184" s="24"/>
+      <c r="C184" s="24"/>
+      <c r="D184" s="24"/>
+      <c r="E184" s="24"/>
+      <c r="F184" s="24"/>
+      <c r="G184" s="24"/>
+      <c r="H184" s="24"/>
+      <c r="I184" s="24"/>
+      <c r="J184" s="24"/>
+      <c r="K184" s="24"/>
+      <c r="L184" s="24"/>
+      <c r="M184" s="24"/>
+      <c r="N184" s="24"/>
+      <c r="O184" s="24"/>
+      <c r="P184" s="24"/>
+      <c r="Q184" s="24"/>
     </row>
     <row r="185" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -14885,25 +14889,25 @@
       <c r="Q199" s="14"/>
     </row>
     <row r="200" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="26" t="s">
+      <c r="A200" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="B200" s="26"/>
-      <c r="C200" s="26"/>
-      <c r="D200" s="26"/>
-      <c r="E200" s="26"/>
-      <c r="F200" s="26"/>
-      <c r="G200" s="26"/>
-      <c r="H200" s="26"/>
-      <c r="I200" s="26"/>
-      <c r="J200" s="26"/>
-      <c r="K200" s="26"/>
-      <c r="L200" s="26"/>
-      <c r="M200" s="26"/>
-      <c r="N200" s="26"/>
-      <c r="O200" s="26"/>
-      <c r="P200" s="26"/>
-      <c r="Q200" s="26"/>
+      <c r="B200" s="24"/>
+      <c r="C200" s="24"/>
+      <c r="D200" s="24"/>
+      <c r="E200" s="24"/>
+      <c r="F200" s="24"/>
+      <c r="G200" s="24"/>
+      <c r="H200" s="24"/>
+      <c r="I200" s="24"/>
+      <c r="J200" s="24"/>
+      <c r="K200" s="24"/>
+      <c r="L200" s="24"/>
+      <c r="M200" s="24"/>
+      <c r="N200" s="24"/>
+      <c r="O200" s="24"/>
+      <c r="P200" s="24"/>
+      <c r="Q200" s="24"/>
     </row>
     <row r="201" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -15463,25 +15467,25 @@
       <c r="Q218" s="14"/>
     </row>
     <row r="219" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="26" t="s">
+      <c r="A219" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="B219" s="26"/>
-      <c r="C219" s="26"/>
-      <c r="D219" s="26"/>
-      <c r="E219" s="26"/>
-      <c r="F219" s="26"/>
-      <c r="G219" s="26"/>
-      <c r="H219" s="26"/>
-      <c r="I219" s="26"/>
-      <c r="J219" s="26"/>
-      <c r="K219" s="26"/>
-      <c r="L219" s="26"/>
-      <c r="M219" s="26"/>
-      <c r="N219" s="26"/>
-      <c r="O219" s="26"/>
-      <c r="P219" s="26"/>
-      <c r="Q219" s="26"/>
+      <c r="B219" s="24"/>
+      <c r="C219" s="24"/>
+      <c r="D219" s="24"/>
+      <c r="E219" s="24"/>
+      <c r="F219" s="24"/>
+      <c r="G219" s="24"/>
+      <c r="H219" s="24"/>
+      <c r="I219" s="24"/>
+      <c r="J219" s="24"/>
+      <c r="K219" s="24"/>
+      <c r="L219" s="24"/>
+      <c r="M219" s="24"/>
+      <c r="N219" s="24"/>
+      <c r="O219" s="24"/>
+      <c r="P219" s="24"/>
+      <c r="Q219" s="24"/>
     </row>
     <row r="220" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -15981,25 +15985,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="26" t="s">
+      <c r="A236" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B236" s="26"/>
-      <c r="C236" s="26"/>
-      <c r="D236" s="26"/>
-      <c r="E236" s="26"/>
-      <c r="F236" s="26"/>
-      <c r="G236" s="26"/>
-      <c r="H236" s="26"/>
-      <c r="I236" s="26"/>
-      <c r="J236" s="26"/>
-      <c r="K236" s="26"/>
-      <c r="L236" s="26"/>
-      <c r="M236" s="26"/>
-      <c r="N236" s="26"/>
-      <c r="O236" s="26"/>
-      <c r="P236" s="26"/>
-      <c r="Q236" s="26"/>
+      <c r="B236" s="24"/>
+      <c r="C236" s="24"/>
+      <c r="D236" s="24"/>
+      <c r="E236" s="24"/>
+      <c r="F236" s="24"/>
+      <c r="G236" s="24"/>
+      <c r="H236" s="24"/>
+      <c r="I236" s="24"/>
+      <c r="J236" s="24"/>
+      <c r="K236" s="24"/>
+      <c r="L236" s="24"/>
+      <c r="M236" s="24"/>
+      <c r="N236" s="24"/>
+      <c r="O236" s="24"/>
+      <c r="P236" s="24"/>
+      <c r="Q236" s="24"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -16529,25 +16533,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="26" t="s">
+      <c r="A254" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="B254" s="26"/>
-      <c r="C254" s="26"/>
-      <c r="D254" s="26"/>
-      <c r="E254" s="26"/>
-      <c r="F254" s="26"/>
-      <c r="G254" s="26"/>
-      <c r="H254" s="26"/>
-      <c r="I254" s="26"/>
-      <c r="J254" s="26"/>
-      <c r="K254" s="26"/>
-      <c r="L254" s="26"/>
-      <c r="M254" s="26"/>
-      <c r="N254" s="26"/>
-      <c r="O254" s="26"/>
-      <c r="P254" s="26"/>
-      <c r="Q254" s="26"/>
+      <c r="B254" s="24"/>
+      <c r="C254" s="24"/>
+      <c r="D254" s="24"/>
+      <c r="E254" s="24"/>
+      <c r="F254" s="24"/>
+      <c r="G254" s="24"/>
+      <c r="H254" s="24"/>
+      <c r="I254" s="24"/>
+      <c r="J254" s="24"/>
+      <c r="K254" s="24"/>
+      <c r="L254" s="24"/>
+      <c r="M254" s="24"/>
+      <c r="N254" s="24"/>
+      <c r="O254" s="24"/>
+      <c r="P254" s="24"/>
+      <c r="Q254" s="24"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -17107,25 +17111,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="26" t="s">
+      <c r="A273" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="B273" s="26"/>
-      <c r="C273" s="26"/>
-      <c r="D273" s="26"/>
-      <c r="E273" s="26"/>
-      <c r="F273" s="26"/>
-      <c r="G273" s="26"/>
-      <c r="H273" s="26"/>
-      <c r="I273" s="26"/>
-      <c r="J273" s="26"/>
-      <c r="K273" s="26"/>
-      <c r="L273" s="26"/>
-      <c r="M273" s="26"/>
-      <c r="N273" s="26"/>
-      <c r="O273" s="26"/>
-      <c r="P273" s="26"/>
-      <c r="Q273" s="26"/>
+      <c r="B273" s="24"/>
+      <c r="C273" s="24"/>
+      <c r="D273" s="24"/>
+      <c r="E273" s="24"/>
+      <c r="F273" s="24"/>
+      <c r="G273" s="24"/>
+      <c r="H273" s="24"/>
+      <c r="I273" s="24"/>
+      <c r="J273" s="24"/>
+      <c r="K273" s="24"/>
+      <c r="L273" s="24"/>
+      <c r="M273" s="24"/>
+      <c r="N273" s="24"/>
+      <c r="O273" s="24"/>
+      <c r="P273" s="24"/>
+      <c r="Q273" s="24"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -17685,25 +17689,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="26" t="s">
+      <c r="A292" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="B292" s="26"/>
-      <c r="C292" s="26"/>
-      <c r="D292" s="26"/>
-      <c r="E292" s="26"/>
-      <c r="F292" s="26"/>
-      <c r="G292" s="26"/>
-      <c r="H292" s="26"/>
-      <c r="I292" s="26"/>
-      <c r="J292" s="26"/>
-      <c r="K292" s="26"/>
-      <c r="L292" s="26"/>
-      <c r="M292" s="26"/>
-      <c r="N292" s="26"/>
-      <c r="O292" s="26"/>
-      <c r="P292" s="26"/>
-      <c r="Q292" s="26"/>
+      <c r="B292" s="24"/>
+      <c r="C292" s="24"/>
+      <c r="D292" s="24"/>
+      <c r="E292" s="24"/>
+      <c r="F292" s="24"/>
+      <c r="G292" s="24"/>
+      <c r="H292" s="24"/>
+      <c r="I292" s="24"/>
+      <c r="J292" s="24"/>
+      <c r="K292" s="24"/>
+      <c r="L292" s="24"/>
+      <c r="M292" s="24"/>
+      <c r="N292" s="24"/>
+      <c r="O292" s="24"/>
+      <c r="P292" s="24"/>
+      <c r="Q292" s="24"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -18263,25 +18267,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="26" t="s">
+      <c r="A311" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="B311" s="26"/>
-      <c r="C311" s="26"/>
-      <c r="D311" s="26"/>
-      <c r="E311" s="26"/>
-      <c r="F311" s="26"/>
-      <c r="G311" s="26"/>
-      <c r="H311" s="26"/>
-      <c r="I311" s="26"/>
-      <c r="J311" s="26"/>
-      <c r="K311" s="26"/>
-      <c r="L311" s="26"/>
-      <c r="M311" s="26"/>
-      <c r="N311" s="26"/>
-      <c r="O311" s="26"/>
-      <c r="P311" s="26"/>
-      <c r="Q311" s="26"/>
+      <c r="B311" s="24"/>
+      <c r="C311" s="24"/>
+      <c r="D311" s="24"/>
+      <c r="E311" s="24"/>
+      <c r="F311" s="24"/>
+      <c r="G311" s="24"/>
+      <c r="H311" s="24"/>
+      <c r="I311" s="24"/>
+      <c r="J311" s="24"/>
+      <c r="K311" s="24"/>
+      <c r="L311" s="24"/>
+      <c r="M311" s="24"/>
+      <c r="N311" s="24"/>
+      <c r="O311" s="24"/>
+      <c r="P311" s="24"/>
+      <c r="Q311" s="24"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -18842,26 +18846,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A23:Q23"/>
+    <mergeCell ref="A42:Q42"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="A132:Q132"/>
+    <mergeCell ref="A149:Q149"/>
+    <mergeCell ref="A167:Q167"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A219:Q219"/>
     <mergeCell ref="A236:Q236"/>
     <mergeCell ref="A254:Q254"/>
     <mergeCell ref="A273:Q273"/>
     <mergeCell ref="A292:Q292"/>
     <mergeCell ref="A311:Q311"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A167:Q167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="A23:Q23"/>
-    <mergeCell ref="A42:Q42"/>
   </mergeCells>
   <dataValidations count="268">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or SEA" promptTitle="ATS Pick" prompt="Pick NE or SEA" sqref="F6:Q6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -22280,25 +22284,34 @@
       <c r="D75" t="s">
         <v>73</v>
       </c>
+      <c r="E75">
+        <v>45</v>
+      </c>
       <c r="F75" t="s">
         <v>65</v>
       </c>
+      <c r="G75">
+        <v>24</v>
+      </c>
+      <c r="H75">
+        <v>2.5</v>
+      </c>
       <c r="I75" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>ATL</v>
       </c>
       <c r="J75" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>ATL</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D76" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="E76" s="16" t="str">
+      <c r="E76" s="16">
         <f>IF(AND(E75&lt;&gt;"",G75&lt;&gt;""),E75+G75,"")</f>
-        <v/>
+        <v>69</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29978,14 +29991,14 @@
       </c>
       <c r="C51" s="3">
         <f>SUMPRODUCT(('Picks Detail'!F63:F78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!F63:F78='Picks Detail'!E63:E78))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D51">
         <v>8</v>
       </c>
       <c r="E51">
         <f>IFERROR(INDEX(C$51:C$62,MATCH(8,A$51:A$62,0)),0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F51" t="str">
         <f>IF(C51=0,"-",IF(C51&gt;E51,"W",IF(C51&lt;E51,"L",IF(AND('Picks Detail'!E79&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,A51)&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,D51)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A51)-'Picks Detail'!E79)&lt;ABS(INDEX('Picks Detail'!F79:Q79,1,D51)-'Picks Detail'!E79),"W",IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A51)-'Picks Detail'!E79)&gt;ABS(INDEX('Picks Detail'!F79:Q79,1,D51)-'Picks Detail'!E79),"L","T")),"T"))))</f>
@@ -29997,11 +30010,11 @@
       </c>
       <c r="H51">
         <f t="shared" ref="H51:H62" si="10">IF(C51="",0,C51)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I51">
         <f t="shared" ref="I51:I62" si="11">G51+H51</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30014,7 +30027,7 @@
       </c>
       <c r="C52" s="3">
         <f>SUMPRODUCT(('Picks Detail'!G63:G78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!G63:G78='Picks Detail'!E63:E78))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D52">
         <v>7</v>
@@ -30025,19 +30038,19 @@
       </c>
       <c r="F52" t="str">
         <f>IF(C52=0,"-",IF(C52&gt;E52,"W",IF(C52&lt;E52,"L",IF(AND('Picks Detail'!E79&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,A52)&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,D52)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A52)-'Picks Detail'!E79)&lt;ABS(INDEX('Picks Detail'!F79:Q79,1,D52)-'Picks Detail'!E79),"W",IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A52)-'Picks Detail'!E79)&gt;ABS(INDEX('Picks Detail'!F79:Q79,1,D52)-'Picks Detail'!E79),"L","T")),"T"))))</f>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="G52">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H52">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I52">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30050,7 +30063,7 @@
       </c>
       <c r="C53" s="3">
         <f>SUMPRODUCT(('Picks Detail'!H63:H78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!H63:H78='Picks Detail'!E63:E78))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D53">
         <v>12</v>
@@ -30069,11 +30082,11 @@
       </c>
       <c r="H53">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I53">
         <f t="shared" si="11"/>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30086,7 +30099,7 @@
       </c>
       <c r="C54" s="3">
         <f>SUMPRODUCT(('Picks Detail'!I63:I78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!I63:I78='Picks Detail'!E63:E78))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D54">
         <v>11</v>
@@ -30105,11 +30118,11 @@
       </c>
       <c r="H54">
         <f t="shared" si="10"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I54">
         <f t="shared" si="11"/>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30122,7 +30135,7 @@
       </c>
       <c r="C55" s="3">
         <f>SUMPRODUCT(('Picks Detail'!J63:J78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!J63:J78='Picks Detail'!E63:E78))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D55">
         <v>10</v>
@@ -30141,11 +30154,11 @@
       </c>
       <c r="H55">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I55">
         <f t="shared" si="11"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30158,14 +30171,14 @@
       </c>
       <c r="C56" s="3">
         <f>SUMPRODUCT(('Picks Detail'!K63:K78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!K63:K78='Picks Detail'!E63:E78))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D56">
         <v>9</v>
       </c>
       <c r="E56">
         <f>IFERROR(INDEX(C$51:C$62,MATCH(9,A$51:A$62,0)),0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F56" t="str">
         <f>IF(C56=0,"-",IF(C56&gt;E56,"W",IF(C56&lt;E56,"L",IF(AND('Picks Detail'!E79&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,A56)&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,D56)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A56)-'Picks Detail'!E79)&lt;ABS(INDEX('Picks Detail'!F79:Q79,1,D56)-'Picks Detail'!E79),"W",IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A56)-'Picks Detail'!E79)&gt;ABS(INDEX('Picks Detail'!F79:Q79,1,D56)-'Picks Detail'!E79),"L","T")),"T"))))</f>
@@ -30177,11 +30190,11 @@
       </c>
       <c r="H56">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I56">
         <f t="shared" si="11"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30201,15 +30214,15 @@
       </c>
       <c r="E57">
         <f>IFERROR(INDEX(C$51:C$62,MATCH(2,A$51:A$62,0)),0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F57" t="str">
         <f>IF(C57=0,"-",IF(C57&gt;E57,"W",IF(C57&lt;E57,"L",IF(AND('Picks Detail'!E79&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,A57)&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,D57)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A57)-'Picks Detail'!E79)&lt;ABS(INDEX('Picks Detail'!F79:Q79,1,D57)-'Picks Detail'!E79),"W",IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A57)-'Picks Detail'!E79)&gt;ABS(INDEX('Picks Detail'!F79:Q79,1,D57)-'Picks Detail'!E79),"L","T")),"T"))))</f>
-        <v>T</v>
+        <v>L</v>
       </c>
       <c r="G57">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H57">
         <f t="shared" si="10"/>
@@ -30217,7 +30230,7 @@
       </c>
       <c r="I57">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30230,14 +30243,14 @@
       </c>
       <c r="C58" s="3">
         <f>SUMPRODUCT(('Picks Detail'!M63:M78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!M63:M78='Picks Detail'!E63:E78))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D58">
         <v>1</v>
       </c>
       <c r="E58">
         <f>IFERROR(INDEX(C$51:C$62,MATCH(1,A$51:A$62,0)),0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F58" t="str">
         <f>IF(C58=0,"-",IF(C58&gt;E58,"W",IF(C58&lt;E58,"L",IF(AND('Picks Detail'!E79&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,A58)&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,D58)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A58)-'Picks Detail'!E79)&lt;ABS(INDEX('Picks Detail'!F79:Q79,1,D58)-'Picks Detail'!E79),"W",IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A58)-'Picks Detail'!E79)&gt;ABS(INDEX('Picks Detail'!F79:Q79,1,D58)-'Picks Detail'!E79),"L","T")),"T"))))</f>
@@ -30249,11 +30262,11 @@
       </c>
       <c r="H58">
         <f t="shared" si="10"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I58">
         <f t="shared" si="11"/>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30266,14 +30279,14 @@
       </c>
       <c r="C59" s="3">
         <f>SUMPRODUCT(('Picks Detail'!N63:N78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!N63:N78='Picks Detail'!E63:E78))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D59">
         <v>6</v>
       </c>
       <c r="E59">
         <f>IFERROR(INDEX(C$51:C$62,MATCH(6,A$51:A$62,0)),0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F59" t="str">
         <f>IF(C59=0,"-",IF(C59&gt;E59,"W",IF(C59&lt;E59,"L",IF(AND('Picks Detail'!E79&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,A59)&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,D59)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A59)-'Picks Detail'!E79)&lt;ABS(INDEX('Picks Detail'!F79:Q79,1,D59)-'Picks Detail'!E79),"W",IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A59)-'Picks Detail'!E79)&gt;ABS(INDEX('Picks Detail'!F79:Q79,1,D59)-'Picks Detail'!E79),"L","T")),"T"))))</f>
@@ -30285,11 +30298,11 @@
       </c>
       <c r="H59">
         <f t="shared" si="10"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I59">
         <f t="shared" si="11"/>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30309,7 +30322,7 @@
       </c>
       <c r="E60">
         <f>IFERROR(INDEX(C$51:C$62,MATCH(5,A$51:A$62,0)),0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F60" t="str">
         <f>IF(C60=0,"-",IF(C60&gt;E60,"W",IF(C60&lt;E60,"L",IF(AND('Picks Detail'!E79&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,A60)&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,D60)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A60)-'Picks Detail'!E79)&lt;ABS(INDEX('Picks Detail'!F79:Q79,1,D60)-'Picks Detail'!E79),"W",IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A60)-'Picks Detail'!E79)&gt;ABS(INDEX('Picks Detail'!F79:Q79,1,D60)-'Picks Detail'!E79),"L","T")),"T"))))</f>
@@ -30345,7 +30358,7 @@
       </c>
       <c r="E61">
         <f>IFERROR(INDEX(C$51:C$62,MATCH(4,A$51:A$62,0)),0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F61" t="str">
         <f>IF(C61=0,"-",IF(C61&gt;E61,"W",IF(C61&lt;E61,"L",IF(AND('Picks Detail'!E79&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,A61)&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,D61)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A61)-'Picks Detail'!E79)&lt;ABS(INDEX('Picks Detail'!F79:Q79,1,D61)-'Picks Detail'!E79),"W",IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A61)-'Picks Detail'!E79)&gt;ABS(INDEX('Picks Detail'!F79:Q79,1,D61)-'Picks Detail'!E79),"L","T")),"T"))))</f>
@@ -30381,7 +30394,7 @@
       </c>
       <c r="E62">
         <f>IFERROR(INDEX(C$51:C$62,MATCH(3,A$51:A$62,0)),0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F62" t="str">
         <f>IF(C62=0,"-",IF(C62&gt;E62,"W",IF(C62&lt;E62,"L",IF(AND('Picks Detail'!E79&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,A62)&lt;&gt;"",INDEX('Picks Detail'!F79:Q79,1,D62)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A62)-'Picks Detail'!E79)&lt;ABS(INDEX('Picks Detail'!F79:Q79,1,D62)-'Picks Detail'!E79),"W",IF(ABS(INDEX('Picks Detail'!F79:Q79,1,A62)-'Picks Detail'!E79)&gt;ABS(INDEX('Picks Detail'!F79:Q79,1,D62)-'Picks Detail'!E79),"L","T")),"T"))))</f>
@@ -37089,7 +37102,7 @@
       </c>
       <c r="F3">
         <f>Helper!F2</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <f>Helper!G2</f>
@@ -37101,7 +37114,7 @@
       </c>
       <c r="I3">
         <f>Helper!I2</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J3">
         <f>Helper!J2</f>
@@ -37134,7 +37147,7 @@
       </c>
       <c r="F4">
         <f>Helper!F3</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <f>Helper!G3</f>
@@ -37146,11 +37159,11 @@
       </c>
       <c r="I4">
         <f>Helper!I3</f>
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J4">
         <f>Helper!J3</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4">
         <f>MAX(Helper!C3:H3)</f>
@@ -37179,7 +37192,7 @@
       </c>
       <c r="F5">
         <f>Helper!F4</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5">
         <f>Helper!G4</f>
@@ -37191,7 +37204,7 @@
       </c>
       <c r="I5">
         <f>Helper!I4</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J5">
         <f>Helper!J4</f>
@@ -37199,7 +37212,7 @@
       </c>
       <c r="K5">
         <f>MAX(Helper!C4:H4)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37224,7 +37237,7 @@
       </c>
       <c r="F6">
         <f>Helper!F5</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6">
         <f>Helper!G5</f>
@@ -37236,7 +37249,7 @@
       </c>
       <c r="I6">
         <f>Helper!I5</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J6">
         <f>Helper!J5</f>
@@ -37244,7 +37257,7 @@
       </c>
       <c r="K6">
         <f>MAX(Helper!C5:H5)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37269,7 +37282,7 @@
       </c>
       <c r="F7">
         <f>Helper!F6</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7">
         <f>Helper!G6</f>
@@ -37281,7 +37294,7 @@
       </c>
       <c r="I7">
         <f>Helper!I6</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J7">
         <f>Helper!J6</f>
@@ -37314,7 +37327,7 @@
       </c>
       <c r="F8">
         <f>Helper!F7</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G8">
         <f>Helper!G7</f>
@@ -37326,7 +37339,7 @@
       </c>
       <c r="I8">
         <f>Helper!I7</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J8">
         <f>Helper!J7</f>
@@ -37359,7 +37372,7 @@
       </c>
       <c r="F9">
         <f>Helper!F8</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G9">
         <f>Helper!G8</f>
@@ -37371,7 +37384,7 @@
       </c>
       <c r="I9">
         <f>Helper!I8</f>
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J9">
         <f>Helper!J8</f>
@@ -37404,7 +37417,7 @@
       </c>
       <c r="F10">
         <f>Helper!F9</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <f>Helper!G9</f>
@@ -37416,7 +37429,7 @@
       </c>
       <c r="I10">
         <f>Helper!I9</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J10">
         <f>Helper!J9</f>
@@ -37424,7 +37437,7 @@
       </c>
       <c r="K10">
         <f>MAX(Helper!C9:H9)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37449,7 +37462,7 @@
       </c>
       <c r="F11">
         <f>Helper!F10</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11">
         <f>Helper!G10</f>
@@ -37461,7 +37474,7 @@
       </c>
       <c r="I11">
         <f>Helper!I10</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J11">
         <f>Helper!J10</f>
@@ -37469,7 +37482,7 @@
       </c>
       <c r="K11">
         <f>MAX(Helper!C10:H10)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38920,7 +38933,7 @@
       </c>
       <c r="C57">
         <f>Helper!I2</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D57">
         <f>Helper!R2</f>
@@ -38932,11 +38945,11 @@
       </c>
       <c r="F57">
         <f>Helper!AE2</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G57">
         <f>Helper!K2</f>
-        <v>47.000100000000003</v>
+        <v>48.000100000000003</v>
       </c>
       <c r="H57">
         <f>Helper!T2</f>
@@ -38953,7 +38966,7 @@
       </c>
       <c r="C58">
         <f>Helper!I3</f>
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D58">
         <f>Helper!R3</f>
@@ -38965,11 +38978,11 @@
       </c>
       <c r="F58">
         <f>Helper!AE3</f>
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G58">
         <f>Helper!K3</f>
-        <v>44.0002</v>
+        <v>48.0002</v>
       </c>
       <c r="H58">
         <f>Helper!T3</f>
@@ -38986,7 +38999,7 @@
       </c>
       <c r="C59">
         <f>Helper!I4</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D59">
         <f>Helper!R4</f>
@@ -38998,11 +39011,11 @@
       </c>
       <c r="F59">
         <f>Helper!AE4</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G59">
         <f>Helper!K4</f>
-        <v>48.000300000000003</v>
+        <v>49.000300000000003</v>
       </c>
       <c r="H59">
         <f>Helper!T4</f>
@@ -39019,7 +39032,7 @@
       </c>
       <c r="C60">
         <f>Helper!I5</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D60">
         <f>Helper!R5</f>
@@ -39031,11 +39044,11 @@
       </c>
       <c r="F60">
         <f>Helper!AE5</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G60">
         <f>Helper!K5</f>
-        <v>37.000399999999999</v>
+        <v>38.000399999999999</v>
       </c>
       <c r="H60">
         <f>Helper!T5</f>
@@ -39052,7 +39065,7 @@
       </c>
       <c r="C61">
         <f>Helper!I6</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D61">
         <f>Helper!R6</f>
@@ -39064,11 +39077,11 @@
       </c>
       <c r="F61">
         <f>Helper!AE6</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G61">
         <f>Helper!K6</f>
-        <v>42.000500000000002</v>
+        <v>43.000500000000002</v>
       </c>
       <c r="H61">
         <f>Helper!T6</f>
@@ -39085,7 +39098,7 @@
       </c>
       <c r="C62">
         <f>Helper!I7</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D62">
         <f>Helper!R7</f>
@@ -39097,11 +39110,11 @@
       </c>
       <c r="F62">
         <f>Helper!AE7</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G62">
         <f>Helper!K7</f>
-        <v>39.000599999999999</v>
+        <v>40.000599999999999</v>
       </c>
       <c r="H62">
         <f>Helper!T7</f>
@@ -39118,7 +39131,7 @@
       </c>
       <c r="C63">
         <f>Helper!I8</f>
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D63">
         <f>Helper!R8</f>
@@ -39130,11 +39143,11 @@
       </c>
       <c r="F63">
         <f>Helper!AE8</f>
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G63">
         <f>Helper!K8</f>
-        <v>36.000700000000002</v>
+        <v>33.000700000000002</v>
       </c>
       <c r="H63">
         <f>Helper!T8</f>
@@ -39151,7 +39164,7 @@
       </c>
       <c r="C64">
         <f>Helper!I9</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D64">
         <f>Helper!R9</f>
@@ -39163,11 +39176,11 @@
       </c>
       <c r="F64">
         <f>Helper!AE9</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G64">
         <f>Helper!K9</f>
-        <v>29.000800000000002</v>
+        <v>30.000800000000002</v>
       </c>
       <c r="H64">
         <f>Helper!T9</f>
@@ -39184,7 +39197,7 @@
       </c>
       <c r="C65">
         <f>Helper!I10</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D65">
         <f>Helper!R10</f>
@@ -39196,11 +39209,11 @@
       </c>
       <c r="F65">
         <f>Helper!AE10</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G65">
         <f>Helper!K10</f>
-        <v>36.000900000000001</v>
+        <v>37.000900000000001</v>
       </c>
       <c r="H65">
         <f>Helper!T10</f>
@@ -39541,7 +39554,7 @@
       </c>
       <c r="C13">
         <f>INDEX(I$40:I$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
         <v>263</v>
@@ -40017,7 +40030,7 @@
       </c>
       <c r="I40">
         <f>Helper!AE2</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J40" t="b">
         <f t="shared" ref="J40:J51" si="1">OR(H40=$E$5,H40=$E$6,H40=$E$7,H40=$E$8,H40=$E$9)</f>
@@ -40025,7 +40038,7 @@
       </c>
       <c r="K40">
         <f>IF(J40,-1,I40+0.00001)</f>
-        <v>47.000010000000003</v>
+        <v>48.000010000000003</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40035,7 +40048,7 @@
       </c>
       <c r="I41">
         <f>Helper!AE3</f>
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J41" t="b">
         <f t="shared" si="1"/>
@@ -40043,7 +40056,7 @@
       </c>
       <c r="K41">
         <f>IF(J41,-1,I41+0.00002)</f>
-        <v>44.000019999999999</v>
+        <v>48.000019999999999</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40053,7 +40066,7 @@
       </c>
       <c r="I42">
         <f>Helper!AE4</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J42" t="b">
         <f t="shared" si="1"/>
@@ -40061,7 +40074,7 @@
       </c>
       <c r="K42">
         <f>IF(J42,-1,I42+0.00003)</f>
-        <v>48.000030000000002</v>
+        <v>49.000030000000002</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40071,7 +40084,7 @@
       </c>
       <c r="I43">
         <f>Helper!AE5</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J43" t="b">
         <f t="shared" si="1"/>
@@ -40089,7 +40102,7 @@
       </c>
       <c r="I44">
         <f>Helper!AE6</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J44" t="b">
         <f t="shared" si="1"/>
@@ -40097,7 +40110,7 @@
       </c>
       <c r="K44">
         <f>IF(J44,-1,I44+0.00005)</f>
-        <v>42.000050000000002</v>
+        <v>43.000050000000002</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40107,7 +40120,7 @@
       </c>
       <c r="I45">
         <f>Helper!AE7</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J45" t="b">
         <f t="shared" si="1"/>
@@ -40115,7 +40128,7 @@
       </c>
       <c r="K45">
         <f>IF(J45,-1,I45+0.00006)</f>
-        <v>39.000059999999998</v>
+        <v>40.000059999999998</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40125,7 +40138,7 @@
       </c>
       <c r="I46">
         <f>Helper!AE8</f>
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J46" t="b">
         <f t="shared" si="1"/>
@@ -40133,7 +40146,7 @@
       </c>
       <c r="K46">
         <f>IF(J46,-1,I46+0.00007)</f>
-        <v>36.000070000000001</v>
+        <v>33.000070000000001</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40143,7 +40156,7 @@
       </c>
       <c r="I47">
         <f>Helper!AE9</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J47" t="b">
         <f t="shared" si="1"/>
@@ -40161,7 +40174,7 @@
       </c>
       <c r="I48">
         <f>Helper!AE10</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J48" t="b">
         <f t="shared" si="1"/>
@@ -40169,7 +40182,7 @@
       </c>
       <c r="K48">
         <f>IF(J48,-1,I48+0.00009)</f>
-        <v>36.00009</v>
+        <v>37.00009</v>
       </c>
     </row>
     <row r="49" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="813" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E6797B9-7EE4-4C2E-9742-E2471831DF9D}"/>
+  <xr:revisionPtr revIDLastSave="828" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{437E1029-514C-4272-963F-E650A4A70D8A}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3965" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3973" uniqueCount="346">
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -1381,9 +1381,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="G2">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H66,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G66,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H81,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G81,0)</f>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I13" si="0">SUM(C2:H2)</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J2">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F6="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F21="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F36="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F51="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F66="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F81="W"),1,0)</f>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="K2">
         <f>I2+0.0001</f>
-        <v>48.000100000000003</v>
+        <v>49.000100000000003</v>
       </c>
       <c r="L2">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H6,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G6,0)</f>
@@ -2957,11 +2957,11 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE13" si="2">I2+R2+AC2</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AF2">
         <f>AE2+0.0001</f>
-        <v>48.000100000000003</v>
+        <v>49.000100000000003</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="G10">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H74,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G74,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H89,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G89,0)</f>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="I10">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J10">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F14="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F29="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F44="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F59="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F74="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F89="W"),1,0)</f>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="K10">
         <f>I10+0.0009</f>
-        <v>37.000900000000001</v>
+        <v>38.000900000000001</v>
       </c>
       <c r="L10">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H14,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G14,0)</f>
@@ -3989,11 +3989,11 @@
       </c>
       <c r="AE10">
         <f t="shared" si="2"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AF10">
         <f>AE10+0.0009</f>
-        <v>37.000900000000001</v>
+        <v>38.000900000000001</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7285,67 +7285,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="24"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8313,25 +8313,25 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="24"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -9299,25 +9299,25 @@
       </c>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+      <c r="A42" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="24"/>
-      <c r="K42" s="24"/>
-      <c r="L42" s="24"/>
-      <c r="M42" s="24"/>
-      <c r="N42" s="24"/>
-      <c r="O42" s="24"/>
-      <c r="P42" s="24"/>
-      <c r="Q42" s="24"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="26"/>
+      <c r="Q42" s="26"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -10247,25 +10247,25 @@
       </c>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="24" t="s">
+      <c r="A61" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="24"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="24"/>
-      <c r="J61" s="24"/>
-      <c r="K61" s="24"/>
-      <c r="L61" s="24"/>
-      <c r="M61" s="24"/>
-      <c r="N61" s="24"/>
-      <c r="O61" s="24"/>
-      <c r="P61" s="24"/>
-      <c r="Q61" s="24"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="26"/>
+      <c r="J61" s="26"/>
+      <c r="K61" s="26"/>
+      <c r="L61" s="26"/>
+      <c r="M61" s="26"/>
+      <c r="N61" s="26"/>
+      <c r="O61" s="26"/>
+      <c r="P61" s="26"/>
+      <c r="Q61" s="26"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -11233,25 +11233,25 @@
       </c>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="24" t="s">
+      <c r="A80" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="24"/>
-      <c r="C80" s="24"/>
-      <c r="D80" s="24"/>
-      <c r="E80" s="24"/>
-      <c r="F80" s="24"/>
-      <c r="G80" s="24"/>
-      <c r="H80" s="24"/>
-      <c r="I80" s="24"/>
-      <c r="J80" s="24"/>
-      <c r="K80" s="24"/>
-      <c r="L80" s="24"/>
-      <c r="M80" s="24"/>
-      <c r="N80" s="24"/>
-      <c r="O80" s="24"/>
-      <c r="P80" s="24"/>
-      <c r="Q80" s="24"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
+      <c r="I80" s="26"/>
+      <c r="J80" s="26"/>
+      <c r="K80" s="26"/>
+      <c r="L80" s="26"/>
+      <c r="M80" s="26"/>
+      <c r="N80" s="26"/>
+      <c r="O80" s="26"/>
+      <c r="P80" s="26"/>
+      <c r="Q80" s="26"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -11321,20 +11321,36 @@
       </c>
       <c r="E82" s="9" t="str">
         <f>'NFL Schedule'!J79</f>
-        <v/>
-      </c>
-      <c r="F82" s="10"/>
-      <c r="G82" s="10"/>
-      <c r="H82" s="10"/>
+        <v>TB</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>85</v>
+      </c>
       <c r="I82" s="10"/>
       <c r="J82" s="10"/>
-      <c r="K82" s="10"/>
-      <c r="L82" s="10"/>
-      <c r="M82" s="10"/>
-      <c r="N82" s="10"/>
+      <c r="K82" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="L82" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="M82" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="N82" s="10" t="s">
+        <v>63</v>
+      </c>
       <c r="O82" s="10"/>
       <c r="P82" s="10"/>
-      <c r="Q82" s="10"/>
+      <c r="Q82" s="10" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="83" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="7">
@@ -11781,25 +11797,25 @@
       <c r="Q97" s="14"/>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="24" t="s">
+      <c r="A98" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="24"/>
-      <c r="C98" s="24"/>
-      <c r="D98" s="24"/>
-      <c r="E98" s="24"/>
-      <c r="F98" s="24"/>
-      <c r="G98" s="24"/>
-      <c r="H98" s="24"/>
-      <c r="I98" s="24"/>
-      <c r="J98" s="24"/>
-      <c r="K98" s="24"/>
-      <c r="L98" s="24"/>
-      <c r="M98" s="24"/>
-      <c r="N98" s="24"/>
-      <c r="O98" s="24"/>
-      <c r="P98" s="24"/>
-      <c r="Q98" s="24"/>
+      <c r="B98" s="26"/>
+      <c r="C98" s="26"/>
+      <c r="D98" s="26"/>
+      <c r="E98" s="26"/>
+      <c r="F98" s="26"/>
+      <c r="G98" s="26"/>
+      <c r="H98" s="26"/>
+      <c r="I98" s="26"/>
+      <c r="J98" s="26"/>
+      <c r="K98" s="26"/>
+      <c r="L98" s="26"/>
+      <c r="M98" s="26"/>
+      <c r="N98" s="26"/>
+      <c r="O98" s="26"/>
+      <c r="P98" s="26"/>
+      <c r="Q98" s="26"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -12299,25 +12315,25 @@
       <c r="Q114" s="14"/>
     </row>
     <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="24" t="s">
+      <c r="A115" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="24"/>
-      <c r="C115" s="24"/>
-      <c r="D115" s="24"/>
-      <c r="E115" s="24"/>
-      <c r="F115" s="24"/>
-      <c r="G115" s="24"/>
-      <c r="H115" s="24"/>
-      <c r="I115" s="24"/>
-      <c r="J115" s="24"/>
-      <c r="K115" s="24"/>
-      <c r="L115" s="24"/>
-      <c r="M115" s="24"/>
-      <c r="N115" s="24"/>
-      <c r="O115" s="24"/>
-      <c r="P115" s="24"/>
-      <c r="Q115" s="24"/>
+      <c r="B115" s="26"/>
+      <c r="C115" s="26"/>
+      <c r="D115" s="26"/>
+      <c r="E115" s="26"/>
+      <c r="F115" s="26"/>
+      <c r="G115" s="26"/>
+      <c r="H115" s="26"/>
+      <c r="I115" s="26"/>
+      <c r="J115" s="26"/>
+      <c r="K115" s="26"/>
+      <c r="L115" s="26"/>
+      <c r="M115" s="26"/>
+      <c r="N115" s="26"/>
+      <c r="O115" s="26"/>
+      <c r="P115" s="26"/>
+      <c r="Q115" s="26"/>
     </row>
     <row r="116" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -12817,25 +12833,25 @@
       <c r="Q131" s="14"/>
     </row>
     <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="24" t="s">
+      <c r="A132" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="B132" s="24"/>
-      <c r="C132" s="24"/>
-      <c r="D132" s="24"/>
-      <c r="E132" s="24"/>
-      <c r="F132" s="24"/>
-      <c r="G132" s="24"/>
-      <c r="H132" s="24"/>
-      <c r="I132" s="24"/>
-      <c r="J132" s="24"/>
-      <c r="K132" s="24"/>
-      <c r="L132" s="24"/>
-      <c r="M132" s="24"/>
-      <c r="N132" s="24"/>
-      <c r="O132" s="24"/>
-      <c r="P132" s="24"/>
-      <c r="Q132" s="24"/>
+      <c r="B132" s="26"/>
+      <c r="C132" s="26"/>
+      <c r="D132" s="26"/>
+      <c r="E132" s="26"/>
+      <c r="F132" s="26"/>
+      <c r="G132" s="26"/>
+      <c r="H132" s="26"/>
+      <c r="I132" s="26"/>
+      <c r="J132" s="26"/>
+      <c r="K132" s="26"/>
+      <c r="L132" s="26"/>
+      <c r="M132" s="26"/>
+      <c r="N132" s="26"/>
+      <c r="O132" s="26"/>
+      <c r="P132" s="26"/>
+      <c r="Q132" s="26"/>
     </row>
     <row r="133" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -13335,25 +13351,25 @@
       <c r="Q148" s="14"/>
     </row>
     <row r="149" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="24" t="s">
+      <c r="A149" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="B149" s="24"/>
-      <c r="C149" s="24"/>
-      <c r="D149" s="24"/>
-      <c r="E149" s="24"/>
-      <c r="F149" s="24"/>
-      <c r="G149" s="24"/>
-      <c r="H149" s="24"/>
-      <c r="I149" s="24"/>
-      <c r="J149" s="24"/>
-      <c r="K149" s="24"/>
-      <c r="L149" s="24"/>
-      <c r="M149" s="24"/>
-      <c r="N149" s="24"/>
-      <c r="O149" s="24"/>
-      <c r="P149" s="24"/>
-      <c r="Q149" s="24"/>
+      <c r="B149" s="26"/>
+      <c r="C149" s="26"/>
+      <c r="D149" s="26"/>
+      <c r="E149" s="26"/>
+      <c r="F149" s="26"/>
+      <c r="G149" s="26"/>
+      <c r="H149" s="26"/>
+      <c r="I149" s="26"/>
+      <c r="J149" s="26"/>
+      <c r="K149" s="26"/>
+      <c r="L149" s="26"/>
+      <c r="M149" s="26"/>
+      <c r="N149" s="26"/>
+      <c r="O149" s="26"/>
+      <c r="P149" s="26"/>
+      <c r="Q149" s="26"/>
     </row>
     <row r="150" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -13883,25 +13899,25 @@
       <c r="Q166" s="14"/>
     </row>
     <row r="167" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="24" t="s">
+      <c r="A167" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="B167" s="24"/>
-      <c r="C167" s="24"/>
-      <c r="D167" s="24"/>
-      <c r="E167" s="24"/>
-      <c r="F167" s="24"/>
-      <c r="G167" s="24"/>
-      <c r="H167" s="24"/>
-      <c r="I167" s="24"/>
-      <c r="J167" s="24"/>
-      <c r="K167" s="24"/>
-      <c r="L167" s="24"/>
-      <c r="M167" s="24"/>
-      <c r="N167" s="24"/>
-      <c r="O167" s="24"/>
-      <c r="P167" s="24"/>
-      <c r="Q167" s="24"/>
+      <c r="B167" s="26"/>
+      <c r="C167" s="26"/>
+      <c r="D167" s="26"/>
+      <c r="E167" s="26"/>
+      <c r="F167" s="26"/>
+      <c r="G167" s="26"/>
+      <c r="H167" s="26"/>
+      <c r="I167" s="26"/>
+      <c r="J167" s="26"/>
+      <c r="K167" s="26"/>
+      <c r="L167" s="26"/>
+      <c r="M167" s="26"/>
+      <c r="N167" s="26"/>
+      <c r="O167" s="26"/>
+      <c r="P167" s="26"/>
+      <c r="Q167" s="26"/>
     </row>
     <row r="168" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -14401,25 +14417,25 @@
       <c r="Q183" s="14"/>
     </row>
     <row r="184" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="24" t="s">
+      <c r="A184" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="B184" s="24"/>
-      <c r="C184" s="24"/>
-      <c r="D184" s="24"/>
-      <c r="E184" s="24"/>
-      <c r="F184" s="24"/>
-      <c r="G184" s="24"/>
-      <c r="H184" s="24"/>
-      <c r="I184" s="24"/>
-      <c r="J184" s="24"/>
-      <c r="K184" s="24"/>
-      <c r="L184" s="24"/>
-      <c r="M184" s="24"/>
-      <c r="N184" s="24"/>
-      <c r="O184" s="24"/>
-      <c r="P184" s="24"/>
-      <c r="Q184" s="24"/>
+      <c r="B184" s="26"/>
+      <c r="C184" s="26"/>
+      <c r="D184" s="26"/>
+      <c r="E184" s="26"/>
+      <c r="F184" s="26"/>
+      <c r="G184" s="26"/>
+      <c r="H184" s="26"/>
+      <c r="I184" s="26"/>
+      <c r="J184" s="26"/>
+      <c r="K184" s="26"/>
+      <c r="L184" s="26"/>
+      <c r="M184" s="26"/>
+      <c r="N184" s="26"/>
+      <c r="O184" s="26"/>
+      <c r="P184" s="26"/>
+      <c r="Q184" s="26"/>
     </row>
     <row r="185" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -14889,25 +14905,25 @@
       <c r="Q199" s="14"/>
     </row>
     <row r="200" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="24" t="s">
+      <c r="A200" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="B200" s="24"/>
-      <c r="C200" s="24"/>
-      <c r="D200" s="24"/>
-      <c r="E200" s="24"/>
-      <c r="F200" s="24"/>
-      <c r="G200" s="24"/>
-      <c r="H200" s="24"/>
-      <c r="I200" s="24"/>
-      <c r="J200" s="24"/>
-      <c r="K200" s="24"/>
-      <c r="L200" s="24"/>
-      <c r="M200" s="24"/>
-      <c r="N200" s="24"/>
-      <c r="O200" s="24"/>
-      <c r="P200" s="24"/>
-      <c r="Q200" s="24"/>
+      <c r="B200" s="26"/>
+      <c r="C200" s="26"/>
+      <c r="D200" s="26"/>
+      <c r="E200" s="26"/>
+      <c r="F200" s="26"/>
+      <c r="G200" s="26"/>
+      <c r="H200" s="26"/>
+      <c r="I200" s="26"/>
+      <c r="J200" s="26"/>
+      <c r="K200" s="26"/>
+      <c r="L200" s="26"/>
+      <c r="M200" s="26"/>
+      <c r="N200" s="26"/>
+      <c r="O200" s="26"/>
+      <c r="P200" s="26"/>
+      <c r="Q200" s="26"/>
     </row>
     <row r="201" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -15467,25 +15483,25 @@
       <c r="Q218" s="14"/>
     </row>
     <row r="219" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="24" t="s">
+      <c r="A219" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="B219" s="24"/>
-      <c r="C219" s="24"/>
-      <c r="D219" s="24"/>
-      <c r="E219" s="24"/>
-      <c r="F219" s="24"/>
-      <c r="G219" s="24"/>
-      <c r="H219" s="24"/>
-      <c r="I219" s="24"/>
-      <c r="J219" s="24"/>
-      <c r="K219" s="24"/>
-      <c r="L219" s="24"/>
-      <c r="M219" s="24"/>
-      <c r="N219" s="24"/>
-      <c r="O219" s="24"/>
-      <c r="P219" s="24"/>
-      <c r="Q219" s="24"/>
+      <c r="B219" s="26"/>
+      <c r="C219" s="26"/>
+      <c r="D219" s="26"/>
+      <c r="E219" s="26"/>
+      <c r="F219" s="26"/>
+      <c r="G219" s="26"/>
+      <c r="H219" s="26"/>
+      <c r="I219" s="26"/>
+      <c r="J219" s="26"/>
+      <c r="K219" s="26"/>
+      <c r="L219" s="26"/>
+      <c r="M219" s="26"/>
+      <c r="N219" s="26"/>
+      <c r="O219" s="26"/>
+      <c r="P219" s="26"/>
+      <c r="Q219" s="26"/>
     </row>
     <row r="220" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -15985,25 +16001,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="24" t="s">
+      <c r="A236" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="B236" s="24"/>
-      <c r="C236" s="24"/>
-      <c r="D236" s="24"/>
-      <c r="E236" s="24"/>
-      <c r="F236" s="24"/>
-      <c r="G236" s="24"/>
-      <c r="H236" s="24"/>
-      <c r="I236" s="24"/>
-      <c r="J236" s="24"/>
-      <c r="K236" s="24"/>
-      <c r="L236" s="24"/>
-      <c r="M236" s="24"/>
-      <c r="N236" s="24"/>
-      <c r="O236" s="24"/>
-      <c r="P236" s="24"/>
-      <c r="Q236" s="24"/>
+      <c r="B236" s="26"/>
+      <c r="C236" s="26"/>
+      <c r="D236" s="26"/>
+      <c r="E236" s="26"/>
+      <c r="F236" s="26"/>
+      <c r="G236" s="26"/>
+      <c r="H236" s="26"/>
+      <c r="I236" s="26"/>
+      <c r="J236" s="26"/>
+      <c r="K236" s="26"/>
+      <c r="L236" s="26"/>
+      <c r="M236" s="26"/>
+      <c r="N236" s="26"/>
+      <c r="O236" s="26"/>
+      <c r="P236" s="26"/>
+      <c r="Q236" s="26"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -16533,25 +16549,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="24" t="s">
+      <c r="A254" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="B254" s="24"/>
-      <c r="C254" s="24"/>
-      <c r="D254" s="24"/>
-      <c r="E254" s="24"/>
-      <c r="F254" s="24"/>
-      <c r="G254" s="24"/>
-      <c r="H254" s="24"/>
-      <c r="I254" s="24"/>
-      <c r="J254" s="24"/>
-      <c r="K254" s="24"/>
-      <c r="L254" s="24"/>
-      <c r="M254" s="24"/>
-      <c r="N254" s="24"/>
-      <c r="O254" s="24"/>
-      <c r="P254" s="24"/>
-      <c r="Q254" s="24"/>
+      <c r="B254" s="26"/>
+      <c r="C254" s="26"/>
+      <c r="D254" s="26"/>
+      <c r="E254" s="26"/>
+      <c r="F254" s="26"/>
+      <c r="G254" s="26"/>
+      <c r="H254" s="26"/>
+      <c r="I254" s="26"/>
+      <c r="J254" s="26"/>
+      <c r="K254" s="26"/>
+      <c r="L254" s="26"/>
+      <c r="M254" s="26"/>
+      <c r="N254" s="26"/>
+      <c r="O254" s="26"/>
+      <c r="P254" s="26"/>
+      <c r="Q254" s="26"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -17111,25 +17127,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="24" t="s">
+      <c r="A273" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="B273" s="24"/>
-      <c r="C273" s="24"/>
-      <c r="D273" s="24"/>
-      <c r="E273" s="24"/>
-      <c r="F273" s="24"/>
-      <c r="G273" s="24"/>
-      <c r="H273" s="24"/>
-      <c r="I273" s="24"/>
-      <c r="J273" s="24"/>
-      <c r="K273" s="24"/>
-      <c r="L273" s="24"/>
-      <c r="M273" s="24"/>
-      <c r="N273" s="24"/>
-      <c r="O273" s="24"/>
-      <c r="P273" s="24"/>
-      <c r="Q273" s="24"/>
+      <c r="B273" s="26"/>
+      <c r="C273" s="26"/>
+      <c r="D273" s="26"/>
+      <c r="E273" s="26"/>
+      <c r="F273" s="26"/>
+      <c r="G273" s="26"/>
+      <c r="H273" s="26"/>
+      <c r="I273" s="26"/>
+      <c r="J273" s="26"/>
+      <c r="K273" s="26"/>
+      <c r="L273" s="26"/>
+      <c r="M273" s="26"/>
+      <c r="N273" s="26"/>
+      <c r="O273" s="26"/>
+      <c r="P273" s="26"/>
+      <c r="Q273" s="26"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -17689,25 +17705,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="24" t="s">
+      <c r="A292" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="B292" s="24"/>
-      <c r="C292" s="24"/>
-      <c r="D292" s="24"/>
-      <c r="E292" s="24"/>
-      <c r="F292" s="24"/>
-      <c r="G292" s="24"/>
-      <c r="H292" s="24"/>
-      <c r="I292" s="24"/>
-      <c r="J292" s="24"/>
-      <c r="K292" s="24"/>
-      <c r="L292" s="24"/>
-      <c r="M292" s="24"/>
-      <c r="N292" s="24"/>
-      <c r="O292" s="24"/>
-      <c r="P292" s="24"/>
-      <c r="Q292" s="24"/>
+      <c r="B292" s="26"/>
+      <c r="C292" s="26"/>
+      <c r="D292" s="26"/>
+      <c r="E292" s="26"/>
+      <c r="F292" s="26"/>
+      <c r="G292" s="26"/>
+      <c r="H292" s="26"/>
+      <c r="I292" s="26"/>
+      <c r="J292" s="26"/>
+      <c r="K292" s="26"/>
+      <c r="L292" s="26"/>
+      <c r="M292" s="26"/>
+      <c r="N292" s="26"/>
+      <c r="O292" s="26"/>
+      <c r="P292" s="26"/>
+      <c r="Q292" s="26"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -18267,25 +18283,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="24" t="s">
+      <c r="A311" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="B311" s="24"/>
-      <c r="C311" s="24"/>
-      <c r="D311" s="24"/>
-      <c r="E311" s="24"/>
-      <c r="F311" s="24"/>
-      <c r="G311" s="24"/>
-      <c r="H311" s="24"/>
-      <c r="I311" s="24"/>
-      <c r="J311" s="24"/>
-      <c r="K311" s="24"/>
-      <c r="L311" s="24"/>
-      <c r="M311" s="24"/>
-      <c r="N311" s="24"/>
-      <c r="O311" s="24"/>
-      <c r="P311" s="24"/>
-      <c r="Q311" s="24"/>
+      <c r="B311" s="26"/>
+      <c r="C311" s="26"/>
+      <c r="D311" s="26"/>
+      <c r="E311" s="26"/>
+      <c r="F311" s="26"/>
+      <c r="G311" s="26"/>
+      <c r="H311" s="26"/>
+      <c r="I311" s="26"/>
+      <c r="J311" s="26"/>
+      <c r="K311" s="26"/>
+      <c r="L311" s="26"/>
+      <c r="M311" s="26"/>
+      <c r="N311" s="26"/>
+      <c r="O311" s="26"/>
+      <c r="P311" s="26"/>
+      <c r="Q311" s="26"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -18846,26 +18862,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A236:Q236"/>
+    <mergeCell ref="A254:Q254"/>
+    <mergeCell ref="A273:Q273"/>
+    <mergeCell ref="A292:Q292"/>
+    <mergeCell ref="A311:Q311"/>
+    <mergeCell ref="A149:Q149"/>
+    <mergeCell ref="A167:Q167"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A219:Q219"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="A132:Q132"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A4:Q4"/>
     <mergeCell ref="A23:Q23"/>
     <mergeCell ref="A42:Q42"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A167:Q167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A236:Q236"/>
-    <mergeCell ref="A254:Q254"/>
-    <mergeCell ref="A273:Q273"/>
-    <mergeCell ref="A292:Q292"/>
-    <mergeCell ref="A311:Q311"/>
   </mergeCells>
   <dataValidations count="268">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or SEA" promptTitle="ATS Pick" prompt="Pick NE or SEA" sqref="F6:Q6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -22364,16 +22380,25 @@
       <c r="D79" t="s">
         <v>63</v>
       </c>
+      <c r="E79">
+        <v>24</v>
+      </c>
       <c r="F79" t="s">
         <v>85</v>
       </c>
+      <c r="G79">
+        <v>16</v>
+      </c>
+      <c r="H79">
+        <v>8.5</v>
+      </c>
       <c r="I79" t="str">
         <f t="shared" ref="I79:I93" si="8">IF(OR(E79="",G79=""),"",IF(E79&gt;G79,D79,IF(G79&gt;E79,F79,"TIE")))</f>
-        <v/>
+        <v>TB</v>
       </c>
       <c r="J79" t="str">
         <f t="shared" ref="J79:J93" si="9">IF(OR(E79="",G79="",H79=""),"",IF(E79+H79&gt;G79,D79,IF(E79+H79&lt;G79,F79,"PUSH")))</f>
-        <v/>
+        <v>TB</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30457,7 +30482,7 @@
       </c>
       <c r="C66" s="3">
         <f>SUMPRODUCT(('Picks Detail'!F82:F96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!F82:F96='Picks Detail'!E82:E96))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66">
         <v>11</v>
@@ -30468,19 +30493,19 @@
       </c>
       <c r="F66" t="str">
         <f>IF(C66=0,"-",IF(C66&gt;E66,"W",IF(C66&lt;E66,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A66)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D66)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A66)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D66)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A66)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D66)-'Picks Detail'!E97),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G66">
         <f t="shared" ref="G66:G77" si="12">IF(F66="W",6,IF(F66="T",3,0))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H66">
         <f t="shared" ref="H66:H77" si="13">IF(C66="",0,C66)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66">
         <f t="shared" ref="I66:I77" si="14">G66+H66</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30716,7 +30741,7 @@
       </c>
       <c r="E73">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(9,A$66:A$77,0)),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="str">
         <f>IF(C73=0,"-",IF(C73&gt;E73,"W",IF(C73&lt;E73,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A73)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D73)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A73)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D73)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A73)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D73)-'Picks Detail'!E97),"L","T")),"T"))))</f>
@@ -30745,7 +30770,7 @@
       </c>
       <c r="C74" s="3">
         <f>SUMPRODUCT(('Picks Detail'!N82:N96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!N82:N96='Picks Detail'!E82:E96))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D74">
         <v>8</v>
@@ -30756,19 +30781,19 @@
       </c>
       <c r="F74" t="str">
         <f>IF(C74=0,"-",IF(C74&gt;E74,"W",IF(C74&lt;E74,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A74)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D74)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A74)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D74)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A74)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D74)-'Picks Detail'!E97),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G74">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H74">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30824,7 +30849,7 @@
       </c>
       <c r="E76">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(1,A$66:A$77,0)),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" t="str">
         <f>IF(C76=0,"-",IF(C76&gt;E76,"W",IF(C76&lt;E76,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A76)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D76)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A76)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D76)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A76)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D76)-'Picks Detail'!E97),"L","T")),"T"))))</f>
@@ -37106,7 +37131,7 @@
       </c>
       <c r="G3">
         <f>Helper!G2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <f>Helper!H2</f>
@@ -37114,7 +37139,7 @@
       </c>
       <c r="I3">
         <f>Helper!I2</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J3">
         <f>Helper!J2</f>
@@ -37466,7 +37491,7 @@
       </c>
       <c r="G11">
         <f>Helper!G10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <f>Helper!H10</f>
@@ -37474,7 +37499,7 @@
       </c>
       <c r="I11">
         <f>Helper!I10</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J11">
         <f>Helper!J10</f>
@@ -38933,7 +38958,7 @@
       </c>
       <c r="C57">
         <f>Helper!I2</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D57">
         <f>Helper!R2</f>
@@ -38945,11 +38970,11 @@
       </c>
       <c r="F57">
         <f>Helper!AE2</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G57">
         <f>Helper!K2</f>
-        <v>48.000100000000003</v>
+        <v>49.000100000000003</v>
       </c>
       <c r="H57">
         <f>Helper!T2</f>
@@ -39197,7 +39222,7 @@
       </c>
       <c r="C65">
         <f>Helper!I10</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D65">
         <f>Helper!R10</f>
@@ -39209,11 +39234,11 @@
       </c>
       <c r="F65">
         <f>Helper!AE10</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G65">
         <f>Helper!K10</f>
-        <v>37.000900000000001</v>
+        <v>38.000900000000001</v>
       </c>
       <c r="H65">
         <f>Helper!T10</f>
@@ -40030,7 +40055,7 @@
       </c>
       <c r="I40">
         <f>Helper!AE2</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J40" t="b">
         <f t="shared" ref="J40:J51" si="1">OR(H40=$E$5,H40=$E$6,H40=$E$7,H40=$E$8,H40=$E$9)</f>
@@ -40038,7 +40063,7 @@
       </c>
       <c r="K40">
         <f>IF(J40,-1,I40+0.00001)</f>
-        <v>48.000010000000003</v>
+        <v>49.000010000000003</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40174,7 +40199,7 @@
       </c>
       <c r="I48">
         <f>Helper!AE10</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J48" t="b">
         <f t="shared" si="1"/>
@@ -40182,7 +40207,7 @@
       </c>
       <c r="K48">
         <f>IF(J48,-1,I48+0.00009)</f>
-        <v>37.00009</v>
+        <v>38.00009</v>
       </c>
     </row>
     <row r="49" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="828" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{437E1029-514C-4272-963F-E650A4A70D8A}"/>
+  <xr:revisionPtr revIDLastSave="1023" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8502DABB-D82F-4129-8B00-917C1A4AEDB8}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3973" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4115" uniqueCount="346">
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -1377,13 +1377,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1665,12 +1665,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="B10" t="str">
         <f>'Playoff Picture'!B22</f>
-        <v>Jack Smith</v>
+        <v>Chris Simmons</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="B19" t="str">
         <f>INDEX($B$5:$B$10,MATCH(LARGE($H$5:$H$10,6),$H$5:$H$10,0))</f>
-        <v>Jack Smith</v>
+        <v>Chris Simmons</v>
       </c>
       <c r="C19">
         <f>INDEX($C$5:$C$10,MATCH(LARGE($H$5:$H$10,6),$H$5:$H$10,0))</f>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="G2">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H66,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G66,0)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H2">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H81,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G81,0)</f>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I13" si="0">SUM(C2:H2)</f>
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="J2">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F6="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F21="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F36="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F51="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F66="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F81="W"),1,0)</f>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="K2">
         <f>I2+0.0001</f>
-        <v>49.000100000000003</v>
+        <v>56.000100000000003</v>
       </c>
       <c r="L2">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H6,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G6,0)</f>
@@ -2957,11 +2957,11 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE13" si="2">I2+R2+AC2</f>
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="AF2">
         <f>AE2+0.0001</f>
-        <v>49.000100000000003</v>
+        <v>56.000100000000003</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G3">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H67,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G67,0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H3">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H82,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G82,0)</f>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="I3">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="J3">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F7="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F22="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F37="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F52="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F67="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F82="W"),1,0)</f>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="K3">
         <f>I3+0.0002</f>
-        <v>48.0002</v>
+        <v>56.0002</v>
       </c>
       <c r="L3">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H7,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G7,0)</f>
@@ -3086,11 +3086,11 @@
       </c>
       <c r="AE3">
         <f t="shared" si="2"/>
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="AF3">
         <f>AE3+0.0002</f>
-        <v>48.0002</v>
+        <v>56.0002</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="G4">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H68,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G68,0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H4">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H83,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G83,0)</f>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J4">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F8="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F23="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F38="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F53="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F68="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F83="W"),1,0)</f>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="K4">
         <f>I4+0.0003</f>
-        <v>49.000300000000003</v>
+        <v>53.000300000000003</v>
       </c>
       <c r="L4">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H8,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G8,0)</f>
@@ -3215,11 +3215,11 @@
       </c>
       <c r="AE4">
         <f t="shared" si="2"/>
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="AF4">
         <f>AE4+0.0003</f>
-        <v>49.000300000000003</v>
+        <v>53.000300000000003</v>
       </c>
     </row>
     <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="G6">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H70,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G70,0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H85,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G85,0)</f>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="J6">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F10="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F25="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F40="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F55="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F70="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F85="W"),1,0)</f>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="K6">
         <f>I6+0.0005</f>
-        <v>43.000500000000002</v>
+        <v>51.000500000000002</v>
       </c>
       <c r="L6">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H10,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G10,0)</f>
@@ -3473,11 +3473,11 @@
       </c>
       <c r="AE6">
         <f t="shared" si="2"/>
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="AF6">
         <f>AE6+0.0005</f>
-        <v>43.000500000000002</v>
+        <v>51.000500000000002</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G7">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H71,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G71,0)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H7">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H86,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G86,0)</f>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="J7">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F11="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F26="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F41="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F56="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F71="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F86="W"),1,0)</f>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="K7">
         <f>I7+0.0006</f>
-        <v>40.000599999999999</v>
+        <v>49.000599999999999</v>
       </c>
       <c r="L7">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H11,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G11,0)</f>
@@ -3602,11 +3602,11 @@
       </c>
       <c r="AE7">
         <f t="shared" si="2"/>
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="AF7">
         <f>AE7+0.0006</f>
-        <v>40.000599999999999</v>
+        <v>49.000599999999999</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="G8">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H72,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G72,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H8">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H87,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G87,0)</f>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J8">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F12="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F27="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F42="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F57="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F72="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F87="W"),1,0)</f>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="K8">
         <f>I8+0.0007</f>
-        <v>33.000700000000002</v>
+        <v>39.000700000000002</v>
       </c>
       <c r="L8">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H12,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G12,0)</f>
@@ -3731,11 +3731,11 @@
       </c>
       <c r="AE8">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="AF8">
         <f>AE8+0.0007</f>
-        <v>33.000700000000002</v>
+        <v>39.000700000000002</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="G9">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H73,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G73,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H9">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H88,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G88,0)</f>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J9">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F13="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F28="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F43="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F58="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F73="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F88="W"),1,0)</f>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="K9">
         <f>I9+0.0008</f>
-        <v>30.000800000000002</v>
+        <v>36.000799999999998</v>
       </c>
       <c r="L9">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H13,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G13,0)</f>
@@ -3860,11 +3860,11 @@
       </c>
       <c r="AE9">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AF9">
         <f>AE9+0.0008</f>
-        <v>30.000800000000002</v>
+        <v>36.000799999999998</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="G10">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H74,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G74,0)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H10">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H89,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G89,0)</f>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="I10">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J10">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F14="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F29="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F44="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F59="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F74="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F89="W"),1,0)</f>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="K10">
         <f>I10+0.0009</f>
-        <v>38.000900000000001</v>
+        <v>42.000900000000001</v>
       </c>
       <c r="L10">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H14,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G14,0)</f>
@@ -3989,11 +3989,11 @@
       </c>
       <c r="AE10">
         <f t="shared" si="2"/>
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AF10">
         <f>AE10+0.0009</f>
-        <v>38.000900000000001</v>
+        <v>42.000900000000001</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G11">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H75,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G75,0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H11">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H90,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G90,0)</f>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="I11">
         <f t="shared" si="0"/>
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="J11">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F15="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F30="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F45="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F60="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F75="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F90="W"),1,0)</f>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="K11">
         <f>I11+0.001</f>
-        <v>49.000999999999998</v>
+        <v>56.000999999999998</v>
       </c>
       <c r="L11">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H15,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G15,0)</f>
@@ -4118,11 +4118,11 @@
       </c>
       <c r="AE11">
         <f t="shared" si="2"/>
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="AF11">
         <f>AE11+0.001</f>
-        <v>49.000999999999998</v>
+        <v>56.000999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="G12">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H76,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G76,0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H12">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H91,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G91,0)</f>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="I12">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J12">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F16="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F31="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F46="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F61="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F76="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F91="W"),1,0)</f>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="K12">
         <f>I12+0.0011</f>
-        <v>43.001100000000001</v>
+        <v>47.001100000000001</v>
       </c>
       <c r="L12">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H16,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G16,0)</f>
@@ -4247,11 +4247,11 @@
       </c>
       <c r="AE12">
         <f t="shared" si="2"/>
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="AF12">
         <f>AE12+0.0011</f>
-        <v>43.001100000000001</v>
+        <v>47.001100000000001</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="G13">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H77,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G77,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H92,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G92,0)</f>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="I13">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J13">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F17="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F32="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F47="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F62="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F77="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F92="W"),1,0)</f>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="K13">
         <f>I13+0.0012</f>
-        <v>38.001199999999997</v>
+        <v>41.001199999999997</v>
       </c>
       <c r="L13">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H17,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G17,0)</f>
@@ -4376,11 +4376,11 @@
       </c>
       <c r="AE13">
         <f t="shared" si="2"/>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="AF13">
         <f>AE13+0.0012</f>
-        <v>38.001199999999997</v>
+        <v>41.001199999999997</v>
       </c>
     </row>
   </sheetData>
@@ -4402,14 +4402,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -5354,14 +5354,14 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
+      <c r="B56" s="26"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
@@ -6306,14 +6306,14 @@
       </c>
     </row>
     <row r="111" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="23" t="s">
+      <c r="A111" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="B111" s="23"/>
-      <c r="C111" s="23"/>
-      <c r="D111" s="23"/>
-      <c r="E111" s="23"/>
-      <c r="F111" s="23"/>
+      <c r="B111" s="26"/>
+      <c r="C111" s="26"/>
+      <c r="D111" s="26"/>
+      <c r="E111" s="26"/>
+      <c r="F111" s="26"/>
     </row>
     <row r="112" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
@@ -7285,67 +7285,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8313,25 +8313,25 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="26"/>
-      <c r="P23" s="26"/>
-      <c r="Q23" s="26"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -9299,25 +9299,25 @@
       </c>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="26" t="s">
+      <c r="A42" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="26"/>
-      <c r="L42" s="26"/>
-      <c r="M42" s="26"/>
-      <c r="N42" s="26"/>
-      <c r="O42" s="26"/>
-      <c r="P42" s="26"/>
-      <c r="Q42" s="26"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="22"/>
+      <c r="N42" s="22"/>
+      <c r="O42" s="22"/>
+      <c r="P42" s="22"/>
+      <c r="Q42" s="22"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -10247,25 +10247,25 @@
       </c>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="26" t="s">
+      <c r="A61" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="26"/>
-      <c r="C61" s="26"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="26"/>
-      <c r="F61" s="26"/>
-      <c r="G61" s="26"/>
-      <c r="H61" s="26"/>
-      <c r="I61" s="26"/>
-      <c r="J61" s="26"/>
-      <c r="K61" s="26"/>
-      <c r="L61" s="26"/>
-      <c r="M61" s="26"/>
-      <c r="N61" s="26"/>
-      <c r="O61" s="26"/>
-      <c r="P61" s="26"/>
-      <c r="Q61" s="26"/>
+      <c r="B61" s="22"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="22"/>
+      <c r="I61" s="22"/>
+      <c r="J61" s="22"/>
+      <c r="K61" s="22"/>
+      <c r="L61" s="22"/>
+      <c r="M61" s="22"/>
+      <c r="N61" s="22"/>
+      <c r="O61" s="22"/>
+      <c r="P61" s="22"/>
+      <c r="Q61" s="22"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -11233,25 +11233,25 @@
       </c>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="26" t="s">
+      <c r="A80" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="26"/>
-      <c r="C80" s="26"/>
-      <c r="D80" s="26"/>
-      <c r="E80" s="26"/>
-      <c r="F80" s="26"/>
-      <c r="G80" s="26"/>
-      <c r="H80" s="26"/>
-      <c r="I80" s="26"/>
-      <c r="J80" s="26"/>
-      <c r="K80" s="26"/>
-      <c r="L80" s="26"/>
-      <c r="M80" s="26"/>
-      <c r="N80" s="26"/>
-      <c r="O80" s="26"/>
-      <c r="P80" s="26"/>
-      <c r="Q80" s="26"/>
+      <c r="B80" s="22"/>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="F80" s="22"/>
+      <c r="G80" s="22"/>
+      <c r="H80" s="22"/>
+      <c r="I80" s="22"/>
+      <c r="J80" s="22"/>
+      <c r="K80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -11367,20 +11367,42 @@
       </c>
       <c r="E83" s="9" t="str">
         <f>'NFL Schedule'!J80</f>
-        <v/>
-      </c>
-      <c r="F83" s="10"/>
-      <c r="G83" s="10"/>
-      <c r="H83" s="10"/>
+        <v>PHI</v>
+      </c>
+      <c r="F83" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I83" s="10"/>
-      <c r="J83" s="10"/>
-      <c r="K83" s="10"/>
-      <c r="L83" s="10"/>
-      <c r="M83" s="10"/>
-      <c r="N83" s="10"/>
-      <c r="O83" s="10"/>
-      <c r="P83" s="10"/>
-      <c r="Q83" s="10"/>
+      <c r="J83" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="K83" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="L83" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="M83" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="N83" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="O83" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="P83" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q83" s="10" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="84" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="7">
@@ -11397,19 +11419,39 @@
       </c>
       <c r="E84" s="9" t="str">
         <f>'NFL Schedule'!J81</f>
-        <v/>
-      </c>
-      <c r="F84" s="10"/>
-      <c r="G84" s="10"/>
-      <c r="H84" s="10"/>
+        <v>HOU</v>
+      </c>
+      <c r="F84" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G84" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I84" s="10"/>
-      <c r="J84" s="10"/>
-      <c r="K84" s="10"/>
-      <c r="L84" s="10"/>
-      <c r="M84" s="10"/>
-      <c r="N84" s="10"/>
-      <c r="O84" s="10"/>
-      <c r="P84" s="10"/>
+      <c r="J84" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="K84" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="L84" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="M84" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="N84" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="O84" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="P84" s="10" t="s">
+        <v>68</v>
+      </c>
       <c r="Q84" s="10"/>
     </row>
     <row r="85" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11427,20 +11469,42 @@
       </c>
       <c r="E85" s="9" t="str">
         <f>'NFL Schedule'!J82</f>
-        <v/>
-      </c>
-      <c r="F85" s="10"/>
-      <c r="G85" s="10"/>
-      <c r="H85" s="10"/>
+        <v>MIA</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>64</v>
+      </c>
       <c r="I85" s="10"/>
-      <c r="J85" s="10"/>
-      <c r="K85" s="10"/>
-      <c r="L85" s="10"/>
-      <c r="M85" s="10"/>
-      <c r="N85" s="10"/>
-      <c r="O85" s="10"/>
-      <c r="P85" s="10"/>
-      <c r="Q85" s="10"/>
+      <c r="J85" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K85" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="L85" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="M85" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="N85" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="O85" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="P85" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q85" s="10" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="86" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="7">
@@ -11457,20 +11521,42 @@
       </c>
       <c r="E86" s="9" t="str">
         <f>'NFL Schedule'!J83</f>
-        <v/>
-      </c>
-      <c r="F86" s="10"/>
-      <c r="G86" s="10"/>
-      <c r="H86" s="10"/>
+        <v>NE</v>
+      </c>
+      <c r="F86" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G86" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H86" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="I86" s="10"/>
-      <c r="J86" s="10"/>
-      <c r="K86" s="10"/>
-      <c r="L86" s="10"/>
-      <c r="M86" s="10"/>
-      <c r="N86" s="10"/>
-      <c r="O86" s="10"/>
-      <c r="P86" s="10"/>
-      <c r="Q86" s="10"/>
+      <c r="J86" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="K86" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="L86" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M86" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N86" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="O86" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P86" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q86" s="10" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="87" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="7">
@@ -11487,20 +11573,42 @@
       </c>
       <c r="E87" s="9" t="str">
         <f>'NFL Schedule'!J84</f>
-        <v/>
-      </c>
-      <c r="F87" s="10"/>
-      <c r="G87" s="10"/>
-      <c r="H87" s="10"/>
+        <v>MIN</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>65</v>
+      </c>
       <c r="I87" s="10"/>
-      <c r="J87" s="10"/>
-      <c r="K87" s="10"/>
-      <c r="L87" s="10"/>
-      <c r="M87" s="10"/>
-      <c r="N87" s="10"/>
-      <c r="O87" s="10"/>
-      <c r="P87" s="10"/>
-      <c r="Q87" s="10"/>
+      <c r="J87" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="K87" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="L87" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="M87" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="N87" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="O87" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="P87" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q87" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="88" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="7">
@@ -11517,20 +11625,42 @@
       </c>
       <c r="E88" s="9" t="str">
         <f>'NFL Schedule'!J85</f>
-        <v/>
-      </c>
-      <c r="F88" s="10"/>
-      <c r="G88" s="10"/>
-      <c r="H88" s="10"/>
+        <v>NYJ</v>
+      </c>
+      <c r="F88" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H88" s="10" t="s">
+        <v>71</v>
+      </c>
       <c r="I88" s="10"/>
-      <c r="J88" s="10"/>
-      <c r="K88" s="10"/>
-      <c r="L88" s="10"/>
-      <c r="M88" s="10"/>
-      <c r="N88" s="10"/>
-      <c r="O88" s="10"/>
-      <c r="P88" s="10"/>
-      <c r="Q88" s="10"/>
+      <c r="J88" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="K88" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="L88" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="M88" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="N88" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="O88" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="P88" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q88" s="10" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="89" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="7">
@@ -11547,20 +11677,42 @@
       </c>
       <c r="E89" s="9" t="str">
         <f>'NFL Schedule'!J86</f>
-        <v/>
-      </c>
-      <c r="F89" s="10"/>
-      <c r="G89" s="10"/>
-      <c r="H89" s="10"/>
+        <v>PIT</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>70</v>
+      </c>
       <c r="I89" s="10"/>
-      <c r="J89" s="10"/>
-      <c r="K89" s="10"/>
-      <c r="L89" s="10"/>
-      <c r="M89" s="10"/>
-      <c r="N89" s="10"/>
-      <c r="O89" s="10"/>
-      <c r="P89" s="10"/>
-      <c r="Q89" s="10"/>
+      <c r="J89" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K89" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="L89" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="M89" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="N89" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="O89" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="P89" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q89" s="10" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="90" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="7">
@@ -11577,20 +11729,42 @@
       </c>
       <c r="E90" s="9" t="str">
         <f>'NFL Schedule'!J87</f>
-        <v/>
-      </c>
-      <c r="F90" s="10"/>
-      <c r="G90" s="10"/>
-      <c r="H90" s="10"/>
+        <v>NYG</v>
+      </c>
+      <c r="F90" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="G90" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H90" s="10" t="s">
+        <v>86</v>
+      </c>
       <c r="I90" s="10"/>
-      <c r="J90" s="10"/>
-      <c r="K90" s="10"/>
-      <c r="L90" s="10"/>
-      <c r="M90" s="10"/>
-      <c r="N90" s="10"/>
-      <c r="O90" s="10"/>
-      <c r="P90" s="10"/>
-      <c r="Q90" s="10"/>
+      <c r="J90" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K90" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="L90" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="M90" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="N90" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="O90" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="P90" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q90" s="10" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="91" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="7">
@@ -11607,20 +11781,42 @@
       </c>
       <c r="E91" s="9" t="str">
         <f>'NFL Schedule'!J88</f>
-        <v/>
-      </c>
-      <c r="F91" s="10"/>
-      <c r="G91" s="10"/>
-      <c r="H91" s="10"/>
+        <v>DEN</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>87</v>
+      </c>
       <c r="I91" s="10"/>
-      <c r="J91" s="10"/>
-      <c r="K91" s="10"/>
-      <c r="L91" s="10"/>
-      <c r="M91" s="10"/>
-      <c r="N91" s="10"/>
-      <c r="O91" s="10"/>
-      <c r="P91" s="10"/>
-      <c r="Q91" s="10"/>
+      <c r="J91" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="K91" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="L91" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="M91" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="N91" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="O91" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="P91" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q91" s="10" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="92" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="7">
@@ -11637,20 +11833,42 @@
       </c>
       <c r="E92" s="9" t="str">
         <f>'NFL Schedule'!J89</f>
-        <v/>
-      </c>
-      <c r="F92" s="10"/>
-      <c r="G92" s="10"/>
-      <c r="H92" s="10"/>
+        <v>GB</v>
+      </c>
+      <c r="F92" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="G92" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H92" s="10" t="s">
+        <v>61</v>
+      </c>
       <c r="I92" s="10"/>
-      <c r="J92" s="10"/>
-      <c r="K92" s="10"/>
-      <c r="L92" s="10"/>
-      <c r="M92" s="10"/>
-      <c r="N92" s="10"/>
-      <c r="O92" s="10"/>
-      <c r="P92" s="10"/>
-      <c r="Q92" s="10"/>
+      <c r="J92" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="K92" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="L92" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M92" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="N92" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="O92" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="P92" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q92" s="10" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="93" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="7">
@@ -11667,20 +11885,42 @@
       </c>
       <c r="E93" s="9" t="str">
         <f>'NFL Schedule'!J90</f>
-        <v/>
-      </c>
-      <c r="F93" s="10"/>
-      <c r="G93" s="10"/>
-      <c r="H93" s="10"/>
+        <v>DET</v>
+      </c>
+      <c r="F93" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G93" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H93" s="10" t="s">
+        <v>66</v>
+      </c>
       <c r="I93" s="10"/>
-      <c r="J93" s="10"/>
-      <c r="K93" s="10"/>
-      <c r="L93" s="10"/>
-      <c r="M93" s="10"/>
-      <c r="N93" s="10"/>
-      <c r="O93" s="10"/>
-      <c r="P93" s="10"/>
-      <c r="Q93" s="10"/>
+      <c r="J93" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="K93" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="L93" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="M93" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="N93" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="O93" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="P93" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q93" s="10" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="94" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="7">
@@ -11697,20 +11937,42 @@
       </c>
       <c r="E94" s="9" t="str">
         <f>'NFL Schedule'!J91</f>
-        <v/>
-      </c>
-      <c r="F94" s="10"/>
-      <c r="G94" s="10"/>
-      <c r="H94" s="10"/>
+        <v>SF</v>
+      </c>
+      <c r="F94" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G94" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H94" s="10" t="s">
+        <v>58</v>
+      </c>
       <c r="I94" s="10"/>
-      <c r="J94" s="10"/>
-      <c r="K94" s="10"/>
-      <c r="L94" s="10"/>
-      <c r="M94" s="10"/>
-      <c r="N94" s="10"/>
-      <c r="O94" s="10"/>
-      <c r="P94" s="10"/>
-      <c r="Q94" s="10"/>
+      <c r="J94" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="K94" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="L94" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="M94" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="N94" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="O94" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="P94" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q94" s="10" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="95" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="7">
@@ -11727,20 +11989,42 @@
       </c>
       <c r="E95" s="9" t="str">
         <f>'NFL Schedule'!J92</f>
-        <v/>
-      </c>
-      <c r="F95" s="10"/>
-      <c r="G95" s="10"/>
-      <c r="H95" s="10"/>
+        <v>BAL</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G95" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I95" s="10"/>
-      <c r="J95" s="10"/>
-      <c r="K95" s="10"/>
-      <c r="L95" s="10"/>
-      <c r="M95" s="10"/>
-      <c r="N95" s="10"/>
-      <c r="O95" s="10"/>
-      <c r="P95" s="10"/>
-      <c r="Q95" s="10"/>
+      <c r="J95" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="K95" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="L95" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="M95" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="N95" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="O95" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P95" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q95" s="10" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="96" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="7">
@@ -11797,25 +12081,25 @@
       <c r="Q97" s="14"/>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="26" t="s">
+      <c r="A98" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="26"/>
-      <c r="C98" s="26"/>
-      <c r="D98" s="26"/>
-      <c r="E98" s="26"/>
-      <c r="F98" s="26"/>
-      <c r="G98" s="26"/>
-      <c r="H98" s="26"/>
-      <c r="I98" s="26"/>
-      <c r="J98" s="26"/>
-      <c r="K98" s="26"/>
-      <c r="L98" s="26"/>
-      <c r="M98" s="26"/>
-      <c r="N98" s="26"/>
-      <c r="O98" s="26"/>
-      <c r="P98" s="26"/>
-      <c r="Q98" s="26"/>
+      <c r="B98" s="22"/>
+      <c r="C98" s="22"/>
+      <c r="D98" s="22"/>
+      <c r="E98" s="22"/>
+      <c r="F98" s="22"/>
+      <c r="G98" s="22"/>
+      <c r="H98" s="22"/>
+      <c r="I98" s="22"/>
+      <c r="J98" s="22"/>
+      <c r="K98" s="22"/>
+      <c r="L98" s="22"/>
+      <c r="M98" s="22"/>
+      <c r="N98" s="22"/>
+      <c r="O98" s="22"/>
+      <c r="P98" s="22"/>
+      <c r="Q98" s="22"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -12315,25 +12599,25 @@
       <c r="Q114" s="14"/>
     </row>
     <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="26" t="s">
+      <c r="A115" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="26"/>
-      <c r="C115" s="26"/>
-      <c r="D115" s="26"/>
-      <c r="E115" s="26"/>
-      <c r="F115" s="26"/>
-      <c r="G115" s="26"/>
-      <c r="H115" s="26"/>
-      <c r="I115" s="26"/>
-      <c r="J115" s="26"/>
-      <c r="K115" s="26"/>
-      <c r="L115" s="26"/>
-      <c r="M115" s="26"/>
-      <c r="N115" s="26"/>
-      <c r="O115" s="26"/>
-      <c r="P115" s="26"/>
-      <c r="Q115" s="26"/>
+      <c r="B115" s="22"/>
+      <c r="C115" s="22"/>
+      <c r="D115" s="22"/>
+      <c r="E115" s="22"/>
+      <c r="F115" s="22"/>
+      <c r="G115" s="22"/>
+      <c r="H115" s="22"/>
+      <c r="I115" s="22"/>
+      <c r="J115" s="22"/>
+      <c r="K115" s="22"/>
+      <c r="L115" s="22"/>
+      <c r="M115" s="22"/>
+      <c r="N115" s="22"/>
+      <c r="O115" s="22"/>
+      <c r="P115" s="22"/>
+      <c r="Q115" s="22"/>
     </row>
     <row r="116" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -12833,25 +13117,25 @@
       <c r="Q131" s="14"/>
     </row>
     <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="26" t="s">
+      <c r="A132" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="B132" s="26"/>
-      <c r="C132" s="26"/>
-      <c r="D132" s="26"/>
-      <c r="E132" s="26"/>
-      <c r="F132" s="26"/>
-      <c r="G132" s="26"/>
-      <c r="H132" s="26"/>
-      <c r="I132" s="26"/>
-      <c r="J132" s="26"/>
-      <c r="K132" s="26"/>
-      <c r="L132" s="26"/>
-      <c r="M132" s="26"/>
-      <c r="N132" s="26"/>
-      <c r="O132" s="26"/>
-      <c r="P132" s="26"/>
-      <c r="Q132" s="26"/>
+      <c r="B132" s="22"/>
+      <c r="C132" s="22"/>
+      <c r="D132" s="22"/>
+      <c r="E132" s="22"/>
+      <c r="F132" s="22"/>
+      <c r="G132" s="22"/>
+      <c r="H132" s="22"/>
+      <c r="I132" s="22"/>
+      <c r="J132" s="22"/>
+      <c r="K132" s="22"/>
+      <c r="L132" s="22"/>
+      <c r="M132" s="22"/>
+      <c r="N132" s="22"/>
+      <c r="O132" s="22"/>
+      <c r="P132" s="22"/>
+      <c r="Q132" s="22"/>
     </row>
     <row r="133" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -13351,25 +13635,25 @@
       <c r="Q148" s="14"/>
     </row>
     <row r="149" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="26" t="s">
+      <c r="A149" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="B149" s="26"/>
-      <c r="C149" s="26"/>
-      <c r="D149" s="26"/>
-      <c r="E149" s="26"/>
-      <c r="F149" s="26"/>
-      <c r="G149" s="26"/>
-      <c r="H149" s="26"/>
-      <c r="I149" s="26"/>
-      <c r="J149" s="26"/>
-      <c r="K149" s="26"/>
-      <c r="L149" s="26"/>
-      <c r="M149" s="26"/>
-      <c r="N149" s="26"/>
-      <c r="O149" s="26"/>
-      <c r="P149" s="26"/>
-      <c r="Q149" s="26"/>
+      <c r="B149" s="22"/>
+      <c r="C149" s="22"/>
+      <c r="D149" s="22"/>
+      <c r="E149" s="22"/>
+      <c r="F149" s="22"/>
+      <c r="G149" s="22"/>
+      <c r="H149" s="22"/>
+      <c r="I149" s="22"/>
+      <c r="J149" s="22"/>
+      <c r="K149" s="22"/>
+      <c r="L149" s="22"/>
+      <c r="M149" s="22"/>
+      <c r="N149" s="22"/>
+      <c r="O149" s="22"/>
+      <c r="P149" s="22"/>
+      <c r="Q149" s="22"/>
     </row>
     <row r="150" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -13899,25 +14183,25 @@
       <c r="Q166" s="14"/>
     </row>
     <row r="167" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="26" t="s">
+      <c r="A167" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="B167" s="26"/>
-      <c r="C167" s="26"/>
-      <c r="D167" s="26"/>
-      <c r="E167" s="26"/>
-      <c r="F167" s="26"/>
-      <c r="G167" s="26"/>
-      <c r="H167" s="26"/>
-      <c r="I167" s="26"/>
-      <c r="J167" s="26"/>
-      <c r="K167" s="26"/>
-      <c r="L167" s="26"/>
-      <c r="M167" s="26"/>
-      <c r="N167" s="26"/>
-      <c r="O167" s="26"/>
-      <c r="P167" s="26"/>
-      <c r="Q167" s="26"/>
+      <c r="B167" s="22"/>
+      <c r="C167" s="22"/>
+      <c r="D167" s="22"/>
+      <c r="E167" s="22"/>
+      <c r="F167" s="22"/>
+      <c r="G167" s="22"/>
+      <c r="H167" s="22"/>
+      <c r="I167" s="22"/>
+      <c r="J167" s="22"/>
+      <c r="K167" s="22"/>
+      <c r="L167" s="22"/>
+      <c r="M167" s="22"/>
+      <c r="N167" s="22"/>
+      <c r="O167" s="22"/>
+      <c r="P167" s="22"/>
+      <c r="Q167" s="22"/>
     </row>
     <row r="168" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -14417,25 +14701,25 @@
       <c r="Q183" s="14"/>
     </row>
     <row r="184" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="26" t="s">
+      <c r="A184" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="B184" s="26"/>
-      <c r="C184" s="26"/>
-      <c r="D184" s="26"/>
-      <c r="E184" s="26"/>
-      <c r="F184" s="26"/>
-      <c r="G184" s="26"/>
-      <c r="H184" s="26"/>
-      <c r="I184" s="26"/>
-      <c r="J184" s="26"/>
-      <c r="K184" s="26"/>
-      <c r="L184" s="26"/>
-      <c r="M184" s="26"/>
-      <c r="N184" s="26"/>
-      <c r="O184" s="26"/>
-      <c r="P184" s="26"/>
-      <c r="Q184" s="26"/>
+      <c r="B184" s="22"/>
+      <c r="C184" s="22"/>
+      <c r="D184" s="22"/>
+      <c r="E184" s="22"/>
+      <c r="F184" s="22"/>
+      <c r="G184" s="22"/>
+      <c r="H184" s="22"/>
+      <c r="I184" s="22"/>
+      <c r="J184" s="22"/>
+      <c r="K184" s="22"/>
+      <c r="L184" s="22"/>
+      <c r="M184" s="22"/>
+      <c r="N184" s="22"/>
+      <c r="O184" s="22"/>
+      <c r="P184" s="22"/>
+      <c r="Q184" s="22"/>
     </row>
     <row r="185" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -14905,25 +15189,25 @@
       <c r="Q199" s="14"/>
     </row>
     <row r="200" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="26" t="s">
+      <c r="A200" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="B200" s="26"/>
-      <c r="C200" s="26"/>
-      <c r="D200" s="26"/>
-      <c r="E200" s="26"/>
-      <c r="F200" s="26"/>
-      <c r="G200" s="26"/>
-      <c r="H200" s="26"/>
-      <c r="I200" s="26"/>
-      <c r="J200" s="26"/>
-      <c r="K200" s="26"/>
-      <c r="L200" s="26"/>
-      <c r="M200" s="26"/>
-      <c r="N200" s="26"/>
-      <c r="O200" s="26"/>
-      <c r="P200" s="26"/>
-      <c r="Q200" s="26"/>
+      <c r="B200" s="22"/>
+      <c r="C200" s="22"/>
+      <c r="D200" s="22"/>
+      <c r="E200" s="22"/>
+      <c r="F200" s="22"/>
+      <c r="G200" s="22"/>
+      <c r="H200" s="22"/>
+      <c r="I200" s="22"/>
+      <c r="J200" s="22"/>
+      <c r="K200" s="22"/>
+      <c r="L200" s="22"/>
+      <c r="M200" s="22"/>
+      <c r="N200" s="22"/>
+      <c r="O200" s="22"/>
+      <c r="P200" s="22"/>
+      <c r="Q200" s="22"/>
     </row>
     <row r="201" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -15483,25 +15767,25 @@
       <c r="Q218" s="14"/>
     </row>
     <row r="219" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="26" t="s">
+      <c r="A219" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="B219" s="26"/>
-      <c r="C219" s="26"/>
-      <c r="D219" s="26"/>
-      <c r="E219" s="26"/>
-      <c r="F219" s="26"/>
-      <c r="G219" s="26"/>
-      <c r="H219" s="26"/>
-      <c r="I219" s="26"/>
-      <c r="J219" s="26"/>
-      <c r="K219" s="26"/>
-      <c r="L219" s="26"/>
-      <c r="M219" s="26"/>
-      <c r="N219" s="26"/>
-      <c r="O219" s="26"/>
-      <c r="P219" s="26"/>
-      <c r="Q219" s="26"/>
+      <c r="B219" s="22"/>
+      <c r="C219" s="22"/>
+      <c r="D219" s="22"/>
+      <c r="E219" s="22"/>
+      <c r="F219" s="22"/>
+      <c r="G219" s="22"/>
+      <c r="H219" s="22"/>
+      <c r="I219" s="22"/>
+      <c r="J219" s="22"/>
+      <c r="K219" s="22"/>
+      <c r="L219" s="22"/>
+      <c r="M219" s="22"/>
+      <c r="N219" s="22"/>
+      <c r="O219" s="22"/>
+      <c r="P219" s="22"/>
+      <c r="Q219" s="22"/>
     </row>
     <row r="220" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -16001,25 +16285,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="26" t="s">
+      <c r="A236" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="B236" s="26"/>
-      <c r="C236" s="26"/>
-      <c r="D236" s="26"/>
-      <c r="E236" s="26"/>
-      <c r="F236" s="26"/>
-      <c r="G236" s="26"/>
-      <c r="H236" s="26"/>
-      <c r="I236" s="26"/>
-      <c r="J236" s="26"/>
-      <c r="K236" s="26"/>
-      <c r="L236" s="26"/>
-      <c r="M236" s="26"/>
-      <c r="N236" s="26"/>
-      <c r="O236" s="26"/>
-      <c r="P236" s="26"/>
-      <c r="Q236" s="26"/>
+      <c r="B236" s="22"/>
+      <c r="C236" s="22"/>
+      <c r="D236" s="22"/>
+      <c r="E236" s="22"/>
+      <c r="F236" s="22"/>
+      <c r="G236" s="22"/>
+      <c r="H236" s="22"/>
+      <c r="I236" s="22"/>
+      <c r="J236" s="22"/>
+      <c r="K236" s="22"/>
+      <c r="L236" s="22"/>
+      <c r="M236" s="22"/>
+      <c r="N236" s="22"/>
+      <c r="O236" s="22"/>
+      <c r="P236" s="22"/>
+      <c r="Q236" s="22"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -16549,25 +16833,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="26" t="s">
+      <c r="A254" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="B254" s="26"/>
-      <c r="C254" s="26"/>
-      <c r="D254" s="26"/>
-      <c r="E254" s="26"/>
-      <c r="F254" s="26"/>
-      <c r="G254" s="26"/>
-      <c r="H254" s="26"/>
-      <c r="I254" s="26"/>
-      <c r="J254" s="26"/>
-      <c r="K254" s="26"/>
-      <c r="L254" s="26"/>
-      <c r="M254" s="26"/>
-      <c r="N254" s="26"/>
-      <c r="O254" s="26"/>
-      <c r="P254" s="26"/>
-      <c r="Q254" s="26"/>
+      <c r="B254" s="22"/>
+      <c r="C254" s="22"/>
+      <c r="D254" s="22"/>
+      <c r="E254" s="22"/>
+      <c r="F254" s="22"/>
+      <c r="G254" s="22"/>
+      <c r="H254" s="22"/>
+      <c r="I254" s="22"/>
+      <c r="J254" s="22"/>
+      <c r="K254" s="22"/>
+      <c r="L254" s="22"/>
+      <c r="M254" s="22"/>
+      <c r="N254" s="22"/>
+      <c r="O254" s="22"/>
+      <c r="P254" s="22"/>
+      <c r="Q254" s="22"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -17127,25 +17411,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="26" t="s">
+      <c r="A273" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="B273" s="26"/>
-      <c r="C273" s="26"/>
-      <c r="D273" s="26"/>
-      <c r="E273" s="26"/>
-      <c r="F273" s="26"/>
-      <c r="G273" s="26"/>
-      <c r="H273" s="26"/>
-      <c r="I273" s="26"/>
-      <c r="J273" s="26"/>
-      <c r="K273" s="26"/>
-      <c r="L273" s="26"/>
-      <c r="M273" s="26"/>
-      <c r="N273" s="26"/>
-      <c r="O273" s="26"/>
-      <c r="P273" s="26"/>
-      <c r="Q273" s="26"/>
+      <c r="B273" s="22"/>
+      <c r="C273" s="22"/>
+      <c r="D273" s="22"/>
+      <c r="E273" s="22"/>
+      <c r="F273" s="22"/>
+      <c r="G273" s="22"/>
+      <c r="H273" s="22"/>
+      <c r="I273" s="22"/>
+      <c r="J273" s="22"/>
+      <c r="K273" s="22"/>
+      <c r="L273" s="22"/>
+      <c r="M273" s="22"/>
+      <c r="N273" s="22"/>
+      <c r="O273" s="22"/>
+      <c r="P273" s="22"/>
+      <c r="Q273" s="22"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -17705,25 +17989,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="26" t="s">
+      <c r="A292" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="B292" s="26"/>
-      <c r="C292" s="26"/>
-      <c r="D292" s="26"/>
-      <c r="E292" s="26"/>
-      <c r="F292" s="26"/>
-      <c r="G292" s="26"/>
-      <c r="H292" s="26"/>
-      <c r="I292" s="26"/>
-      <c r="J292" s="26"/>
-      <c r="K292" s="26"/>
-      <c r="L292" s="26"/>
-      <c r="M292" s="26"/>
-      <c r="N292" s="26"/>
-      <c r="O292" s="26"/>
-      <c r="P292" s="26"/>
-      <c r="Q292" s="26"/>
+      <c r="B292" s="22"/>
+      <c r="C292" s="22"/>
+      <c r="D292" s="22"/>
+      <c r="E292" s="22"/>
+      <c r="F292" s="22"/>
+      <c r="G292" s="22"/>
+      <c r="H292" s="22"/>
+      <c r="I292" s="22"/>
+      <c r="J292" s="22"/>
+      <c r="K292" s="22"/>
+      <c r="L292" s="22"/>
+      <c r="M292" s="22"/>
+      <c r="N292" s="22"/>
+      <c r="O292" s="22"/>
+      <c r="P292" s="22"/>
+      <c r="Q292" s="22"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -18283,25 +18567,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="26" t="s">
+      <c r="A311" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="B311" s="26"/>
-      <c r="C311" s="26"/>
-      <c r="D311" s="26"/>
-      <c r="E311" s="26"/>
-      <c r="F311" s="26"/>
-      <c r="G311" s="26"/>
-      <c r="H311" s="26"/>
-      <c r="I311" s="26"/>
-      <c r="J311" s="26"/>
-      <c r="K311" s="26"/>
-      <c r="L311" s="26"/>
-      <c r="M311" s="26"/>
-      <c r="N311" s="26"/>
-      <c r="O311" s="26"/>
-      <c r="P311" s="26"/>
-      <c r="Q311" s="26"/>
+      <c r="B311" s="22"/>
+      <c r="C311" s="22"/>
+      <c r="D311" s="22"/>
+      <c r="E311" s="22"/>
+      <c r="F311" s="22"/>
+      <c r="G311" s="22"/>
+      <c r="H311" s="22"/>
+      <c r="I311" s="22"/>
+      <c r="J311" s="22"/>
+      <c r="K311" s="22"/>
+      <c r="L311" s="22"/>
+      <c r="M311" s="22"/>
+      <c r="N311" s="22"/>
+      <c r="O311" s="22"/>
+      <c r="P311" s="22"/>
+      <c r="Q311" s="22"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -18862,26 +19146,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A23:Q23"/>
+    <mergeCell ref="A42:Q42"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="A132:Q132"/>
+    <mergeCell ref="A149:Q149"/>
+    <mergeCell ref="A167:Q167"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A219:Q219"/>
     <mergeCell ref="A236:Q236"/>
     <mergeCell ref="A254:Q254"/>
     <mergeCell ref="A273:Q273"/>
     <mergeCell ref="A292:Q292"/>
     <mergeCell ref="A311:Q311"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A167:Q167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="A23:Q23"/>
-    <mergeCell ref="A42:Q42"/>
   </mergeCells>
   <dataValidations count="268">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or SEA" promptTitle="ATS Pick" prompt="Pick NE or SEA" sqref="F6:Q6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -22414,16 +22698,25 @@
       <c r="D80" t="s">
         <v>84</v>
       </c>
+      <c r="E80">
+        <v>17</v>
+      </c>
       <c r="F80" t="s">
         <v>72</v>
       </c>
+      <c r="G80">
+        <v>19</v>
+      </c>
+      <c r="H80">
+        <v>6.5</v>
+      </c>
       <c r="I80" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>JAX</v>
       </c>
       <c r="J80" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>PHI</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22439,16 +22732,25 @@
       <c r="D81" t="s">
         <v>68</v>
       </c>
+      <c r="E81">
+        <v>26</v>
+      </c>
       <c r="F81" t="s">
         <v>76</v>
       </c>
+      <c r="G81">
+        <v>3</v>
+      </c>
+      <c r="H81">
+        <v>-7.5</v>
+      </c>
       <c r="I81" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>HOU</v>
       </c>
       <c r="J81" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>HOU</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22464,16 +22766,25 @@
       <c r="D82" t="s">
         <v>64</v>
       </c>
+      <c r="E82">
+        <v>31</v>
+      </c>
       <c r="F82" t="s">
         <v>79</v>
       </c>
+      <c r="G82">
+        <v>24</v>
+      </c>
+      <c r="H82">
+        <v>-7.5</v>
+      </c>
       <c r="I82" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>CIN</v>
       </c>
       <c r="J82" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>MIA</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22489,16 +22800,25 @@
       <c r="D83" t="s">
         <v>80</v>
       </c>
+      <c r="E83">
+        <v>17</v>
+      </c>
       <c r="F83" t="s">
         <v>57</v>
       </c>
+      <c r="G83">
+        <v>45</v>
+      </c>
+      <c r="H83">
+        <v>3.5</v>
+      </c>
       <c r="I83" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>NE</v>
       </c>
       <c r="J83" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>NE</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22514,16 +22834,25 @@
       <c r="D84" t="s">
         <v>82</v>
       </c>
+      <c r="E84">
+        <v>23</v>
+      </c>
       <c r="F84" t="s">
         <v>65</v>
       </c>
+      <c r="G84">
+        <v>13</v>
+      </c>
+      <c r="H84">
+        <v>-1.5</v>
+      </c>
       <c r="I84" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>MIN</v>
       </c>
       <c r="J84" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>MIN</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22539,16 +22868,25 @@
       <c r="D85" t="s">
         <v>71</v>
       </c>
+      <c r="E85">
+        <v>12</v>
+      </c>
       <c r="F85" t="s">
         <v>75</v>
       </c>
+      <c r="G85">
+        <v>17</v>
+      </c>
+      <c r="H85">
+        <v>2.5</v>
+      </c>
       <c r="I85" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>NYJ</v>
       </c>
       <c r="J85" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>NYJ</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22564,16 +22902,25 @@
       <c r="D86" t="s">
         <v>70</v>
       </c>
+      <c r="E86">
+        <v>22</v>
+      </c>
       <c r="F86" t="s">
         <v>74</v>
       </c>
+      <c r="G86">
+        <v>34</v>
+      </c>
+      <c r="H86">
+        <v>2.5</v>
+      </c>
       <c r="I86" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>PIT</v>
       </c>
       <c r="J86" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>PIT</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22589,16 +22936,25 @@
       <c r="D87" t="s">
         <v>86</v>
       </c>
+      <c r="E87">
+        <v>27</v>
+      </c>
       <c r="F87" t="s">
         <v>83</v>
       </c>
+      <c r="G87">
+        <v>27</v>
+      </c>
+      <c r="H87">
+        <v>3.5</v>
+      </c>
       <c r="I87" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>TIE</v>
       </c>
       <c r="J87" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>NYG</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22614,16 +22970,25 @@
       <c r="D88" t="s">
         <v>87</v>
       </c>
+      <c r="E88">
+        <v>23</v>
+      </c>
       <c r="F88" t="s">
         <v>78</v>
       </c>
+      <c r="G88">
+        <v>17</v>
+      </c>
+      <c r="H88">
+        <v>-3.5</v>
+      </c>
       <c r="I88" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>DEN</v>
       </c>
       <c r="J88" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>DEN</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22639,16 +23004,25 @@
       <c r="D89" t="s">
         <v>61</v>
       </c>
+      <c r="E89">
+        <v>7</v>
+      </c>
       <c r="F89" t="s">
         <v>81</v>
       </c>
+      <c r="G89">
+        <v>31</v>
+      </c>
+      <c r="H89">
+        <v>-2.5</v>
+      </c>
       <c r="I89" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>GB</v>
       </c>
       <c r="J89" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>GB</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22664,16 +23038,25 @@
       <c r="D90" t="s">
         <v>66</v>
       </c>
+      <c r="E90">
+        <v>45</v>
+      </c>
       <c r="F90" t="s">
         <v>77</v>
       </c>
+      <c r="G90">
+        <v>21</v>
+      </c>
+      <c r="H90">
+        <v>-4.5</v>
+      </c>
       <c r="I90" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>DET</v>
       </c>
       <c r="J90" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>DET</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22689,16 +23072,25 @@
       <c r="D91" t="s">
         <v>59</v>
       </c>
+      <c r="E91">
+        <v>32</v>
+      </c>
       <c r="F91" t="s">
         <v>58</v>
       </c>
+      <c r="G91">
+        <v>29</v>
+      </c>
+      <c r="H91">
+        <v>2.5</v>
+      </c>
       <c r="I91" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>SF</v>
       </c>
       <c r="J91" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>SF</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22714,16 +23106,25 @@
       <c r="D92" t="s">
         <v>69</v>
       </c>
+      <c r="E92">
+        <v>30</v>
+      </c>
       <c r="F92" t="s">
         <v>73</v>
       </c>
+      <c r="G92">
+        <v>23</v>
+      </c>
+      <c r="H92">
+        <v>2.5</v>
+      </c>
       <c r="I92" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>BAL</v>
       </c>
       <c r="J92" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>BAL</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28557,17 +28958,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -30482,14 +30883,14 @@
       </c>
       <c r="C66" s="3">
         <f>SUMPRODUCT(('Picks Detail'!F82:F96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!F82:F96='Picks Detail'!E82:E96))</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D66">
         <v>11</v>
       </c>
       <c r="E66">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(11,A$66:A$77,0)),0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F66" t="str">
         <f>IF(C66=0,"-",IF(C66&gt;E66,"W",IF(C66&lt;E66,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A66)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D66)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A66)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D66)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A66)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D66)-'Picks Detail'!E97),"L","T")),"T"))))</f>
@@ -30501,11 +30902,11 @@
       </c>
       <c r="H66">
         <f t="shared" ref="H66:H77" si="13">IF(C66="",0,C66)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I66">
         <f t="shared" ref="I66:I77" si="14">G66+H66</f>
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30518,30 +30919,30 @@
       </c>
       <c r="C67" s="3">
         <f>SUMPRODUCT(('Picks Detail'!G82:G96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!G82:G96='Picks Detail'!E82:E96))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D67">
         <v>12</v>
       </c>
       <c r="E67">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(12,A$66:A$77,0)),0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F67" t="str">
         <f>IF(C67=0,"-",IF(C67&gt;E67,"W",IF(C67&lt;E67,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A67)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D67)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A67)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D67)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A67)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D67)-'Picks Detail'!E97),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G67">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H67">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I67">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30554,18 +30955,18 @@
       </c>
       <c r="C68" s="3">
         <f>SUMPRODUCT(('Picks Detail'!H82:H96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!H82:H96='Picks Detail'!E82:E96))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D68">
         <v>5</v>
       </c>
       <c r="E68">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(5,A$66:A$77,0)),0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F68" t="str">
         <f>IF(C68=0,"-",IF(C68&gt;E68,"W",IF(C68&lt;E68,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A68)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D68)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A68)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D68)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A68)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D68)-'Picks Detail'!E97),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G68">
         <f t="shared" si="12"/>
@@ -30573,11 +30974,11 @@
       </c>
       <c r="H68">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I68">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30597,7 +30998,7 @@
       </c>
       <c r="E69">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(6,A$66:A$77,0)),0)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F69" t="str">
         <f>IF(C69=0,"-",IF(C69&gt;E69,"W",IF(C69&lt;E69,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A69)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D69)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A69)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D69)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A69)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D69)-'Picks Detail'!E97),"L","T")),"T"))))</f>
@@ -30626,30 +31027,30 @@
       </c>
       <c r="C70" s="3">
         <f>SUMPRODUCT(('Picks Detail'!J82:J96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!J82:J96='Picks Detail'!E82:E96))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D70">
         <v>3</v>
       </c>
       <c r="E70">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(3,A$66:A$77,0)),0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F70" t="str">
         <f>IF(C70=0,"-",IF(C70&gt;E70,"W",IF(C70&lt;E70,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A70)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D70)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A70)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D70)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A70)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D70)-'Picks Detail'!E97),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G70">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H70">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I70">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30662,7 +31063,7 @@
       </c>
       <c r="C71" s="3">
         <f>SUMPRODUCT(('Picks Detail'!K82:K96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!K82:K96='Picks Detail'!E82:E96))</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D71">
         <v>4</v>
@@ -30673,19 +31074,19 @@
       </c>
       <c r="F71" t="str">
         <f>IF(C71=0,"-",IF(C71&gt;E71,"W",IF(C71&lt;E71,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A71)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D71)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A71)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D71)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A71)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D71)-'Picks Detail'!E97),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G71">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H71">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I71">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30698,18 +31099,18 @@
       </c>
       <c r="C72" s="3">
         <f>SUMPRODUCT(('Picks Detail'!L82:L96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!L82:L96='Picks Detail'!E82:E96))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D72">
         <v>10</v>
       </c>
       <c r="E72">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(10,A$66:A$77,0)),0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F72" t="str">
         <f>IF(C72=0,"-",IF(C72&gt;E72,"W",IF(C72&lt;E72,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A72)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D72)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A72)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D72)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A72)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D72)-'Picks Detail'!E97),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G72">
         <f t="shared" si="12"/>
@@ -30717,11 +31118,11 @@
       </c>
       <c r="H72">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I72">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30734,30 +31135,30 @@
       </c>
       <c r="C73" s="3">
         <f>SUMPRODUCT(('Picks Detail'!M82:M96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!M82:M96='Picks Detail'!E82:E96))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D73">
         <v>9</v>
       </c>
       <c r="E73">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(9,A$66:A$77,0)),0)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F73" t="str">
         <f>IF(C73=0,"-",IF(C73&gt;E73,"W",IF(C73&lt;E73,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A73)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D73)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A73)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D73)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A73)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D73)-'Picks Detail'!E97),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G73">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H73">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I73">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30770,30 +31171,30 @@
       </c>
       <c r="C74" s="3">
         <f>SUMPRODUCT(('Picks Detail'!N82:N96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!N82:N96='Picks Detail'!E82:E96))</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D74">
         <v>8</v>
       </c>
       <c r="E74">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(8,A$66:A$77,0)),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F74" t="str">
         <f>IF(C74=0,"-",IF(C74&gt;E74,"W",IF(C74&lt;E74,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A74)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D74)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A74)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D74)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A74)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D74)-'Picks Detail'!E97),"L","T")),"T"))))</f>
-        <v>W</v>
+        <v>L</v>
       </c>
       <c r="G74">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H74">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I74">
         <f t="shared" si="14"/>
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30806,30 +31207,30 @@
       </c>
       <c r="C75" s="3">
         <f>SUMPRODUCT(('Picks Detail'!O82:O96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!O82:O96='Picks Detail'!E82:E96))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D75">
         <v>7</v>
       </c>
       <c r="E75">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(7,A$66:A$77,0)),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F75" t="str">
         <f>IF(C75=0,"-",IF(C75&gt;E75,"W",IF(C75&lt;E75,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A75)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D75)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A75)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D75)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A75)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D75)-'Picks Detail'!E97),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G75">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H75">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I75">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30842,18 +31243,18 @@
       </c>
       <c r="C76" s="3">
         <f>SUMPRODUCT(('Picks Detail'!P82:P96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!P82:P96='Picks Detail'!E82:E96))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D76">
         <v>1</v>
       </c>
       <c r="E76">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(1,A$66:A$77,0)),0)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F76" t="str">
         <f>IF(C76=0,"-",IF(C76&gt;E76,"W",IF(C76&lt;E76,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A76)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D76)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A76)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D76)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A76)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D76)-'Picks Detail'!E97),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G76">
         <f t="shared" si="12"/>
@@ -30861,11 +31262,11 @@
       </c>
       <c r="H76">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I76">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30878,18 +31279,18 @@
       </c>
       <c r="C77" s="3">
         <f>SUMPRODUCT(('Picks Detail'!Q82:Q96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!Q82:Q96='Picks Detail'!E82:E96))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D77">
         <v>2</v>
       </c>
       <c r="E77">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(2,A$66:A$77,0)),0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F77" t="str">
         <f>IF(C77=0,"-",IF(C77&gt;E77,"W",IF(C77&lt;E77,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A77)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D77)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A77)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D77)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A77)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D77)-'Picks Detail'!E97),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G77">
         <f t="shared" si="12"/>
@@ -30897,11 +31298,11 @@
       </c>
       <c r="H77">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I77">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31390,17 +31791,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -34223,17 +34624,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -37056,19 +37457,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -37131,7 +37532,7 @@
       </c>
       <c r="G3">
         <f>Helper!G2</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H3">
         <f>Helper!H2</f>
@@ -37139,7 +37540,7 @@
       </c>
       <c r="I3">
         <f>Helper!I2</f>
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="J3">
         <f>Helper!J2</f>
@@ -37176,7 +37577,7 @@
       </c>
       <c r="G4">
         <f>Helper!G3</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H4">
         <f>Helper!H3</f>
@@ -37184,7 +37585,7 @@
       </c>
       <c r="I4">
         <f>Helper!I3</f>
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="J4">
         <f>Helper!J3</f>
@@ -37221,7 +37622,7 @@
       </c>
       <c r="G5">
         <f>Helper!G4</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H5">
         <f>Helper!H4</f>
@@ -37229,7 +37630,7 @@
       </c>
       <c r="I5">
         <f>Helper!I4</f>
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J5">
         <f>Helper!J4</f>
@@ -37311,7 +37712,7 @@
       </c>
       <c r="G7">
         <f>Helper!G6</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H7">
         <f>Helper!H6</f>
@@ -37319,7 +37720,7 @@
       </c>
       <c r="I7">
         <f>Helper!I6</f>
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="J7">
         <f>Helper!J6</f>
@@ -37356,7 +37757,7 @@
       </c>
       <c r="G8">
         <f>Helper!G7</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H8">
         <f>Helper!H7</f>
@@ -37364,7 +37765,7 @@
       </c>
       <c r="I8">
         <f>Helper!I7</f>
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="J8">
         <f>Helper!J7</f>
@@ -37401,7 +37802,7 @@
       </c>
       <c r="G9">
         <f>Helper!G8</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H9">
         <f>Helper!H8</f>
@@ -37409,7 +37810,7 @@
       </c>
       <c r="I9">
         <f>Helper!I8</f>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J9">
         <f>Helper!J8</f>
@@ -37446,7 +37847,7 @@
       </c>
       <c r="G10">
         <f>Helper!G9</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H10">
         <f>Helper!H9</f>
@@ -37454,7 +37855,7 @@
       </c>
       <c r="I10">
         <f>Helper!I9</f>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J10">
         <f>Helper!J9</f>
@@ -37491,7 +37892,7 @@
       </c>
       <c r="G11">
         <f>Helper!G10</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H11">
         <f>Helper!H10</f>
@@ -37499,7 +37900,7 @@
       </c>
       <c r="I11">
         <f>Helper!I10</f>
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J11">
         <f>Helper!J10</f>
@@ -37536,7 +37937,7 @@
       </c>
       <c r="G12">
         <f>Helper!G11</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H12">
         <f>Helper!H11</f>
@@ -37544,7 +37945,7 @@
       </c>
       <c r="I12">
         <f>Helper!I11</f>
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="J12">
         <f>Helper!J11</f>
@@ -37581,7 +37982,7 @@
       </c>
       <c r="G13">
         <f>Helper!G12</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H13">
         <f>Helper!H12</f>
@@ -37589,7 +37990,7 @@
       </c>
       <c r="I13">
         <f>Helper!I12</f>
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J13">
         <f>Helper!J12</f>
@@ -37626,7 +38027,7 @@
       </c>
       <c r="G14">
         <f>Helper!G13</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14">
         <f>Helper!H13</f>
@@ -37634,7 +38035,7 @@
       </c>
       <c r="I14">
         <f>Helper!I13</f>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J14">
         <f>Helper!J13</f>
@@ -38958,7 +39359,7 @@
       </c>
       <c r="C57">
         <f>Helper!I2</f>
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D57">
         <f>Helper!R2</f>
@@ -38970,11 +39371,11 @@
       </c>
       <c r="F57">
         <f>Helper!AE2</f>
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G57">
         <f>Helper!K2</f>
-        <v>49.000100000000003</v>
+        <v>56.000100000000003</v>
       </c>
       <c r="H57">
         <f>Helper!T2</f>
@@ -38991,7 +39392,7 @@
       </c>
       <c r="C58">
         <f>Helper!I3</f>
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D58">
         <f>Helper!R3</f>
@@ -39003,11 +39404,11 @@
       </c>
       <c r="F58">
         <f>Helper!AE3</f>
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G58">
         <f>Helper!K3</f>
-        <v>48.0002</v>
+        <v>56.0002</v>
       </c>
       <c r="H58">
         <f>Helper!T3</f>
@@ -39024,7 +39425,7 @@
       </c>
       <c r="C59">
         <f>Helper!I4</f>
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D59">
         <f>Helper!R4</f>
@@ -39036,11 +39437,11 @@
       </c>
       <c r="F59">
         <f>Helper!AE4</f>
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G59">
         <f>Helper!K4</f>
-        <v>49.000300000000003</v>
+        <v>53.000300000000003</v>
       </c>
       <c r="H59">
         <f>Helper!T4</f>
@@ -39090,7 +39491,7 @@
       </c>
       <c r="C61">
         <f>Helper!I6</f>
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D61">
         <f>Helper!R6</f>
@@ -39102,11 +39503,11 @@
       </c>
       <c r="F61">
         <f>Helper!AE6</f>
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G61">
         <f>Helper!K6</f>
-        <v>43.000500000000002</v>
+        <v>51.000500000000002</v>
       </c>
       <c r="H61">
         <f>Helper!T6</f>
@@ -39123,7 +39524,7 @@
       </c>
       <c r="C62">
         <f>Helper!I7</f>
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D62">
         <f>Helper!R7</f>
@@ -39135,11 +39536,11 @@
       </c>
       <c r="F62">
         <f>Helper!AE7</f>
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G62">
         <f>Helper!K7</f>
-        <v>40.000599999999999</v>
+        <v>49.000599999999999</v>
       </c>
       <c r="H62">
         <f>Helper!T7</f>
@@ -39156,7 +39557,7 @@
       </c>
       <c r="C63">
         <f>Helper!I8</f>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D63">
         <f>Helper!R8</f>
@@ -39168,11 +39569,11 @@
       </c>
       <c r="F63">
         <f>Helper!AE8</f>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G63">
         <f>Helper!K8</f>
-        <v>33.000700000000002</v>
+        <v>39.000700000000002</v>
       </c>
       <c r="H63">
         <f>Helper!T8</f>
@@ -39189,7 +39590,7 @@
       </c>
       <c r="C64">
         <f>Helper!I9</f>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D64">
         <f>Helper!R9</f>
@@ -39201,11 +39602,11 @@
       </c>
       <c r="F64">
         <f>Helper!AE9</f>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G64">
         <f>Helper!K9</f>
-        <v>30.000800000000002</v>
+        <v>36.000799999999998</v>
       </c>
       <c r="H64">
         <f>Helper!T9</f>
@@ -39222,7 +39623,7 @@
       </c>
       <c r="C65">
         <f>Helper!I10</f>
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D65">
         <f>Helper!R10</f>
@@ -39234,11 +39635,11 @@
       </c>
       <c r="F65">
         <f>Helper!AE10</f>
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G65">
         <f>Helper!K10</f>
-        <v>38.000900000000001</v>
+        <v>42.000900000000001</v>
       </c>
       <c r="H65">
         <f>Helper!T10</f>
@@ -39255,7 +39656,7 @@
       </c>
       <c r="C66">
         <f>Helper!I11</f>
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D66">
         <f>Helper!R11</f>
@@ -39267,11 +39668,11 @@
       </c>
       <c r="F66">
         <f>Helper!AE11</f>
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G66">
         <f>Helper!K11</f>
-        <v>49.000999999999998</v>
+        <v>56.000999999999998</v>
       </c>
       <c r="H66">
         <f>Helper!T11</f>
@@ -39288,7 +39689,7 @@
       </c>
       <c r="C67">
         <f>Helper!I12</f>
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D67">
         <f>Helper!R12</f>
@@ -39300,11 +39701,11 @@
       </c>
       <c r="F67">
         <f>Helper!AE12</f>
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G67">
         <f>Helper!K12</f>
-        <v>43.001100000000001</v>
+        <v>47.001100000000001</v>
       </c>
       <c r="H67">
         <f>Helper!T12</f>
@@ -39321,7 +39722,7 @@
       </c>
       <c r="C68">
         <f>Helper!I13</f>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D68">
         <f>Helper!R13</f>
@@ -39333,11 +39734,11 @@
       </c>
       <c r="F68">
         <f>Helper!AE13</f>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G68">
         <f>Helper!K13</f>
-        <v>38.001199999999997</v>
+        <v>41.001199999999997</v>
       </c>
       <c r="H68">
         <f>Helper!T13</f>
@@ -39575,11 +39976,11 @@
       </c>
       <c r="B13" t="str">
         <f>INDEX(H$40:H$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
-        <v>Jack Smith</v>
+        <v>Chris Simmons</v>
       </c>
       <c r="C13">
         <f>INDEX(I$40:I$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
         <v>263</v>
@@ -39690,7 +40091,7 @@
       </c>
       <c r="B22" t="str">
         <f>B13</f>
-        <v>Jack Smith</v>
+        <v>Chris Simmons</v>
       </c>
       <c r="C22" t="str">
         <f>"Wild Card 1"</f>
@@ -40055,7 +40456,7 @@
       </c>
       <c r="I40">
         <f>Helper!AE2</f>
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="J40" t="b">
         <f t="shared" ref="J40:J51" si="1">OR(H40=$E$5,H40=$E$6,H40=$E$7,H40=$E$8,H40=$E$9)</f>
@@ -40063,7 +40464,7 @@
       </c>
       <c r="K40">
         <f>IF(J40,-1,I40+0.00001)</f>
-        <v>49.000010000000003</v>
+        <v>56.000010000000003</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40073,7 +40474,7 @@
       </c>
       <c r="I41">
         <f>Helper!AE3</f>
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="J41" t="b">
         <f t="shared" si="1"/>
@@ -40081,7 +40482,7 @@
       </c>
       <c r="K41">
         <f>IF(J41,-1,I41+0.00002)</f>
-        <v>48.000019999999999</v>
+        <v>56.000019999999999</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40091,7 +40492,7 @@
       </c>
       <c r="I42">
         <f>Helper!AE4</f>
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J42" t="b">
         <f t="shared" si="1"/>
@@ -40099,7 +40500,7 @@
       </c>
       <c r="K42">
         <f>IF(J42,-1,I42+0.00003)</f>
-        <v>49.000030000000002</v>
+        <v>53.000030000000002</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40127,7 +40528,7 @@
       </c>
       <c r="I44">
         <f>Helper!AE6</f>
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="J44" t="b">
         <f t="shared" si="1"/>
@@ -40135,7 +40536,7 @@
       </c>
       <c r="K44">
         <f>IF(J44,-1,I44+0.00005)</f>
-        <v>43.000050000000002</v>
+        <v>51.000050000000002</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40145,7 +40546,7 @@
       </c>
       <c r="I45">
         <f>Helper!AE7</f>
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="J45" t="b">
         <f t="shared" si="1"/>
@@ -40153,7 +40554,7 @@
       </c>
       <c r="K45">
         <f>IF(J45,-1,I45+0.00006)</f>
-        <v>40.000059999999998</v>
+        <v>49.000059999999998</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40163,7 +40564,7 @@
       </c>
       <c r="I46">
         <f>Helper!AE8</f>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J46" t="b">
         <f t="shared" si="1"/>
@@ -40171,7 +40572,7 @@
       </c>
       <c r="K46">
         <f>IF(J46,-1,I46+0.00007)</f>
-        <v>33.000070000000001</v>
+        <v>39.000070000000001</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40181,7 +40582,7 @@
       </c>
       <c r="I47">
         <f>Helper!AE9</f>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J47" t="b">
         <f t="shared" si="1"/>
@@ -40199,7 +40600,7 @@
       </c>
       <c r="I48">
         <f>Helper!AE10</f>
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J48" t="b">
         <f t="shared" si="1"/>
@@ -40207,7 +40608,7 @@
       </c>
       <c r="K48">
         <f>IF(J48,-1,I48+0.00009)</f>
-        <v>38.00009</v>
+        <v>42.00009</v>
       </c>
     </row>
     <row r="49" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40217,7 +40618,7 @@
       </c>
       <c r="I49">
         <f>Helper!AE11</f>
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="J49" t="b">
         <f t="shared" si="1"/>
@@ -40235,7 +40636,7 @@
       </c>
       <c r="I50">
         <f>Helper!AE12</f>
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J50" t="b">
         <f t="shared" si="1"/>
@@ -40253,7 +40654,7 @@
       </c>
       <c r="I51">
         <f>Helper!AE13</f>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J51" t="b">
         <f t="shared" si="1"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1023" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8502DABB-D82F-4129-8B00-917C1A4AEDB8}"/>
+  <xr:revisionPtr revIDLastSave="1048" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25747702-C5A7-483A-8745-289FE83B87E2}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4115" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4126" uniqueCount="346">
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -1377,13 +1377,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1470,10 +1470,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1665,12 +1661,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
+      <c r="A1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1926,7 +1922,7 @@
       </c>
       <c r="B5" t="str">
         <f>'Playoff Picture'!B17</f>
-        <v>Zach Zarra</v>
+        <v>Chris Simmons</v>
       </c>
       <c r="C5" s="3">
         <v>6</v>
@@ -2071,7 +2067,7 @@
       </c>
       <c r="B10" t="str">
         <f>'Playoff Picture'!B22</f>
-        <v>Chris Simmons</v>
+        <v>Evan Loeser</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
@@ -2120,7 +2116,7 @@
       </c>
       <c r="B14" t="str">
         <f>INDEX($B$5:$B$10,MATCH(LARGE($H$5:$H$10,1),$H$5:$H$10,0))</f>
-        <v>Zach Zarra</v>
+        <v>Chris Simmons</v>
       </c>
       <c r="C14">
         <f>INDEX($C$5:$C$10,MATCH(LARGE($H$5:$H$10,1),$H$5:$H$10,0))</f>
@@ -2205,7 +2201,7 @@
       </c>
       <c r="B19" t="str">
         <f>INDEX($B$5:$B$10,MATCH(LARGE($H$5:$H$10,6),$H$5:$H$10,0))</f>
-        <v>Chris Simmons</v>
+        <v>Evan Loeser</v>
       </c>
       <c r="C19">
         <f>INDEX($C$5:$C$10,MATCH(LARGE($H$5:$H$10,6),$H$5:$H$10,0))</f>
@@ -2281,7 +2277,7 @@
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>'Playoff Wild Card'!B14</f>
-        <v>Zach Zarra</v>
+        <v>Chris Simmons</v>
       </c>
       <c r="B6">
         <f>'Playoff Wild Card'!C14</f>
@@ -2483,7 +2479,7 @@
       </c>
       <c r="B13" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>Zach Zarra</v>
+        <v>Chris Simmons</v>
       </c>
       <c r="C13">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
@@ -2632,7 +2628,7 @@
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>A6</f>
-        <v>Zach Zarra</v>
+        <v>Chris Simmons</v>
       </c>
       <c r="B22" s="3">
         <v>0</v>
@@ -2861,7 +2857,7 @@
       </c>
       <c r="G2">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H66,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G66,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H81,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G81,0)</f>
@@ -2869,7 +2865,7 @@
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I13" si="0">SUM(C2:H2)</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J2">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F6="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F21="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F36="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F51="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F66="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F81="W"),1,0)</f>
@@ -2877,7 +2873,7 @@
       </c>
       <c r="K2">
         <f>I2+0.0001</f>
-        <v>56.000100000000003</v>
+        <v>57.000100000000003</v>
       </c>
       <c r="L2">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H6,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G6,0)</f>
@@ -2957,11 +2953,11 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE13" si="2">I2+R2+AC2</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AF2">
         <f>AE2+0.0001</f>
-        <v>56.000100000000003</v>
+        <v>57.000100000000003</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2990,7 +2986,7 @@
       </c>
       <c r="G3">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H67,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G67,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H82,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G82,0)</f>
@@ -2998,7 +2994,7 @@
       </c>
       <c r="I3">
         <f t="shared" si="0"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J3">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F7="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F22="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F37="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F52="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F67="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F82="W"),1,0)</f>
@@ -3006,7 +3002,7 @@
       </c>
       <c r="K3">
         <f>I3+0.0002</f>
-        <v>56.0002</v>
+        <v>57.0002</v>
       </c>
       <c r="L3">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H7,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G7,0)</f>
@@ -3086,11 +3082,11 @@
       </c>
       <c r="AE3">
         <f t="shared" si="2"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AF3">
         <f>AE3+0.0002</f>
-        <v>56.0002</v>
+        <v>57.0002</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3119,7 +3115,7 @@
       </c>
       <c r="G4">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H68,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G68,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H83,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G83,0)</f>
@@ -3127,7 +3123,7 @@
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J4">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F8="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F23="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F38="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F53="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F68="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F83="W"),1,0)</f>
@@ -3135,7 +3131,7 @@
       </c>
       <c r="K4">
         <f>I4+0.0003</f>
-        <v>53.000300000000003</v>
+        <v>54.000300000000003</v>
       </c>
       <c r="L4">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H8,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G8,0)</f>
@@ -3215,11 +3211,11 @@
       </c>
       <c r="AE4">
         <f t="shared" si="2"/>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AF4">
         <f>AE4+0.0003</f>
-        <v>53.000300000000003</v>
+        <v>54.000300000000003</v>
       </c>
     </row>
     <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3377,7 +3373,7 @@
       </c>
       <c r="G6">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H70,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G70,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H85,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G85,0)</f>
@@ -3385,7 +3381,7 @@
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J6">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F10="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F25="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F40="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F55="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F70="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F85="W"),1,0)</f>
@@ -3393,7 +3389,7 @@
       </c>
       <c r="K6">
         <f>I6+0.0005</f>
-        <v>51.000500000000002</v>
+        <v>52.000500000000002</v>
       </c>
       <c r="L6">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H10,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G10,0)</f>
@@ -3473,11 +3469,11 @@
       </c>
       <c r="AE6">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AF6">
         <f>AE6+0.0005</f>
-        <v>51.000500000000002</v>
+        <v>52.000500000000002</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3506,7 +3502,7 @@
       </c>
       <c r="G7">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H71,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G71,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H7">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H86,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G86,0)</f>
@@ -3514,7 +3510,7 @@
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J7">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F11="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F26="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F41="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F56="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F71="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F86="W"),1,0)</f>
@@ -3522,7 +3518,7 @@
       </c>
       <c r="K7">
         <f>I7+0.0006</f>
-        <v>49.000599999999999</v>
+        <v>50.000599999999999</v>
       </c>
       <c r="L7">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H11,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G11,0)</f>
@@ -3602,11 +3598,11 @@
       </c>
       <c r="AE7">
         <f t="shared" si="2"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF7">
         <f>AE7+0.0006</f>
-        <v>49.000599999999999</v>
+        <v>50.000599999999999</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3635,7 +3631,7 @@
       </c>
       <c r="G8">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H72,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G72,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H87,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G87,0)</f>
@@ -3643,7 +3639,7 @@
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J8">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F12="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F27="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F42="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F57="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F72="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F87="W"),1,0)</f>
@@ -3651,7 +3647,7 @@
       </c>
       <c r="K8">
         <f>I8+0.0007</f>
-        <v>39.000700000000002</v>
+        <v>40.000700000000002</v>
       </c>
       <c r="L8">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H12,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G12,0)</f>
@@ -3731,11 +3727,11 @@
       </c>
       <c r="AE8">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AF8">
         <f>AE8+0.0007</f>
-        <v>39.000700000000002</v>
+        <v>40.000700000000002</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3764,7 +3760,7 @@
       </c>
       <c r="G9">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H73,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G73,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H88,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G88,0)</f>
@@ -3772,7 +3768,7 @@
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J9">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F13="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F28="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F43="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F58="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F73="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F88="W"),1,0)</f>
@@ -3780,7 +3776,7 @@
       </c>
       <c r="K9">
         <f>I9+0.0008</f>
-        <v>36.000799999999998</v>
+        <v>37.000799999999998</v>
       </c>
       <c r="L9">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H13,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G13,0)</f>
@@ -3860,11 +3856,11 @@
       </c>
       <c r="AE9">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AF9">
         <f>AE9+0.0008</f>
-        <v>36.000799999999998</v>
+        <v>37.000799999999998</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3893,7 +3889,7 @@
       </c>
       <c r="G10">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H74,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G74,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H89,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G89,0)</f>
@@ -3901,7 +3897,7 @@
       </c>
       <c r="I10">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J10">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F14="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F29="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F44="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F59="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F74="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F89="W"),1,0)</f>
@@ -3909,7 +3905,7 @@
       </c>
       <c r="K10">
         <f>I10+0.0009</f>
-        <v>42.000900000000001</v>
+        <v>43.000900000000001</v>
       </c>
       <c r="L10">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H14,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G14,0)</f>
@@ -3989,11 +3985,11 @@
       </c>
       <c r="AE10">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AF10">
         <f>AE10+0.0009</f>
-        <v>42.000900000000001</v>
+        <v>43.000900000000001</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4151,7 +4147,7 @@
       </c>
       <c r="G12">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H76,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G76,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H91,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G91,0)</f>
@@ -4159,7 +4155,7 @@
       </c>
       <c r="I12">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J12">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F16="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F31="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F46="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F61="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F76="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F91="W"),1,0)</f>
@@ -4167,7 +4163,7 @@
       </c>
       <c r="K12">
         <f>I12+0.0011</f>
-        <v>47.001100000000001</v>
+        <v>48.001100000000001</v>
       </c>
       <c r="L12">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H16,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G16,0)</f>
@@ -4247,11 +4243,11 @@
       </c>
       <c r="AE12">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF12">
         <f>AE12+0.0011</f>
-        <v>47.001100000000001</v>
+        <v>48.001100000000001</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4280,7 +4276,7 @@
       </c>
       <c r="G13">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H77,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G77,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H92,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G92,0)</f>
@@ -4288,7 +4284,7 @@
       </c>
       <c r="I13">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J13">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F17="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F32="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F47="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F62="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F77="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F92="W"),1,0)</f>
@@ -4296,7 +4292,7 @@
       </c>
       <c r="K13">
         <f>I13+0.0012</f>
-        <v>41.001199999999997</v>
+        <v>42.001199999999997</v>
       </c>
       <c r="L13">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H17,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G17,0)</f>
@@ -4376,11 +4372,11 @@
       </c>
       <c r="AE13">
         <f t="shared" si="2"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AF13">
         <f>AE13+0.0012</f>
-        <v>41.001199999999997</v>
+        <v>42.001199999999997</v>
       </c>
     </row>
   </sheetData>
@@ -4402,14 +4398,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -5354,14 +5350,14 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="26" t="s">
+      <c r="A56" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="26"/>
-      <c r="C56" s="26"/>
-      <c r="D56" s="26"/>
-      <c r="E56" s="26"/>
-      <c r="F56" s="26"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
@@ -6306,14 +6302,14 @@
       </c>
     </row>
     <row r="111" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="26" t="s">
+      <c r="A111" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B111" s="26"/>
-      <c r="C111" s="26"/>
-      <c r="D111" s="26"/>
-      <c r="E111" s="26"/>
-      <c r="F111" s="26"/>
+      <c r="B111" s="22"/>
+      <c r="C111" s="22"/>
+      <c r="D111" s="22"/>
+      <c r="E111" s="22"/>
+      <c r="F111" s="22"/>
     </row>
     <row r="112" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
@@ -7285,67 +7281,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8313,25 +8309,25 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="22"/>
-      <c r="O23" s="22"/>
-      <c r="P23" s="22"/>
-      <c r="Q23" s="22"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -9299,25 +9295,25 @@
       </c>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="22" t="s">
+      <c r="A42" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="22"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="22"/>
-      <c r="I42" s="22"/>
-      <c r="J42" s="22"/>
-      <c r="K42" s="22"/>
-      <c r="L42" s="22"/>
-      <c r="M42" s="22"/>
-      <c r="N42" s="22"/>
-      <c r="O42" s="22"/>
-      <c r="P42" s="22"/>
-      <c r="Q42" s="22"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="26"/>
+      <c r="Q42" s="26"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -10247,25 +10243,25 @@
       </c>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="22" t="s">
+      <c r="A61" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="22"/>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="22"/>
-      <c r="H61" s="22"/>
-      <c r="I61" s="22"/>
-      <c r="J61" s="22"/>
-      <c r="K61" s="22"/>
-      <c r="L61" s="22"/>
-      <c r="M61" s="22"/>
-      <c r="N61" s="22"/>
-      <c r="O61" s="22"/>
-      <c r="P61" s="22"/>
-      <c r="Q61" s="22"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="26"/>
+      <c r="J61" s="26"/>
+      <c r="K61" s="26"/>
+      <c r="L61" s="26"/>
+      <c r="M61" s="26"/>
+      <c r="N61" s="26"/>
+      <c r="O61" s="26"/>
+      <c r="P61" s="26"/>
+      <c r="Q61" s="26"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -11233,25 +11229,25 @@
       </c>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="22" t="s">
+      <c r="A80" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="22"/>
-      <c r="C80" s="22"/>
-      <c r="D80" s="22"/>
-      <c r="E80" s="22"/>
-      <c r="F80" s="22"/>
-      <c r="G80" s="22"/>
-      <c r="H80" s="22"/>
-      <c r="I80" s="22"/>
-      <c r="J80" s="22"/>
-      <c r="K80" s="22"/>
-      <c r="L80" s="22"/>
-      <c r="M80" s="22"/>
-      <c r="N80" s="22"/>
-      <c r="O80" s="22"/>
-      <c r="P80" s="22"/>
-      <c r="Q80" s="22"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
+      <c r="I80" s="26"/>
+      <c r="J80" s="26"/>
+      <c r="K80" s="26"/>
+      <c r="L80" s="26"/>
+      <c r="M80" s="26"/>
+      <c r="N80" s="26"/>
+      <c r="O80" s="26"/>
+      <c r="P80" s="26"/>
+      <c r="Q80" s="26"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -12041,20 +12037,42 @@
       </c>
       <c r="E96" s="9" t="str">
         <f>'NFL Schedule'!J93</f>
-        <v/>
-      </c>
-      <c r="F96" s="10"/>
-      <c r="G96" s="10"/>
-      <c r="H96" s="10"/>
+        <v>BUF</v>
+      </c>
+      <c r="F96" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G96" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H96" s="10" t="s">
+        <v>67</v>
+      </c>
       <c r="I96" s="10"/>
-      <c r="J96" s="10"/>
-      <c r="K96" s="10"/>
-      <c r="L96" s="10"/>
-      <c r="M96" s="10"/>
-      <c r="N96" s="10"/>
-      <c r="O96" s="10"/>
-      <c r="P96" s="10"/>
-      <c r="Q96" s="10"/>
+      <c r="J96" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K96" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L96" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="M96" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="N96" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="O96" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="P96" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q96" s="10" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
@@ -12063,43 +12081,65 @@
       <c r="B97" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="E97" s="13" t="str">
+      <c r="E97" s="13">
         <f>'NFL Schedule'!E94</f>
-        <v/>
-      </c>
-      <c r="F97" s="14"/>
-      <c r="G97" s="14"/>
-      <c r="H97" s="14"/>
+        <v>71</v>
+      </c>
+      <c r="F97" s="14">
+        <v>51</v>
+      </c>
+      <c r="G97" s="14">
+        <v>52</v>
+      </c>
+      <c r="H97" s="14">
+        <v>43</v>
+      </c>
       <c r="I97" s="14"/>
-      <c r="J97" s="14"/>
-      <c r="K97" s="14"/>
-      <c r="L97" s="14"/>
-      <c r="M97" s="14"/>
-      <c r="N97" s="14"/>
-      <c r="O97" s="14"/>
-      <c r="P97" s="14"/>
-      <c r="Q97" s="14"/>
+      <c r="J97" s="14">
+        <v>45</v>
+      </c>
+      <c r="K97" s="14">
+        <v>42</v>
+      </c>
+      <c r="L97" s="14">
+        <v>52</v>
+      </c>
+      <c r="M97" s="14">
+        <v>45</v>
+      </c>
+      <c r="N97" s="14">
+        <v>55</v>
+      </c>
+      <c r="O97" s="14">
+        <v>50</v>
+      </c>
+      <c r="P97" s="14">
+        <v>52</v>
+      </c>
+      <c r="Q97" s="14">
+        <v>51</v>
+      </c>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="22" t="s">
+      <c r="A98" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="22"/>
-      <c r="C98" s="22"/>
-      <c r="D98" s="22"/>
-      <c r="E98" s="22"/>
-      <c r="F98" s="22"/>
-      <c r="G98" s="22"/>
-      <c r="H98" s="22"/>
-      <c r="I98" s="22"/>
-      <c r="J98" s="22"/>
-      <c r="K98" s="22"/>
-      <c r="L98" s="22"/>
-      <c r="M98" s="22"/>
-      <c r="N98" s="22"/>
-      <c r="O98" s="22"/>
-      <c r="P98" s="22"/>
-      <c r="Q98" s="22"/>
+      <c r="B98" s="26"/>
+      <c r="C98" s="26"/>
+      <c r="D98" s="26"/>
+      <c r="E98" s="26"/>
+      <c r="F98" s="26"/>
+      <c r="G98" s="26"/>
+      <c r="H98" s="26"/>
+      <c r="I98" s="26"/>
+      <c r="J98" s="26"/>
+      <c r="K98" s="26"/>
+      <c r="L98" s="26"/>
+      <c r="M98" s="26"/>
+      <c r="N98" s="26"/>
+      <c r="O98" s="26"/>
+      <c r="P98" s="26"/>
+      <c r="Q98" s="26"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -12599,25 +12639,25 @@
       <c r="Q114" s="14"/>
     </row>
     <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="22" t="s">
+      <c r="A115" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="22"/>
-      <c r="C115" s="22"/>
-      <c r="D115" s="22"/>
-      <c r="E115" s="22"/>
-      <c r="F115" s="22"/>
-      <c r="G115" s="22"/>
-      <c r="H115" s="22"/>
-      <c r="I115" s="22"/>
-      <c r="J115" s="22"/>
-      <c r="K115" s="22"/>
-      <c r="L115" s="22"/>
-      <c r="M115" s="22"/>
-      <c r="N115" s="22"/>
-      <c r="O115" s="22"/>
-      <c r="P115" s="22"/>
-      <c r="Q115" s="22"/>
+      <c r="B115" s="26"/>
+      <c r="C115" s="26"/>
+      <c r="D115" s="26"/>
+      <c r="E115" s="26"/>
+      <c r="F115" s="26"/>
+      <c r="G115" s="26"/>
+      <c r="H115" s="26"/>
+      <c r="I115" s="26"/>
+      <c r="J115" s="26"/>
+      <c r="K115" s="26"/>
+      <c r="L115" s="26"/>
+      <c r="M115" s="26"/>
+      <c r="N115" s="26"/>
+      <c r="O115" s="26"/>
+      <c r="P115" s="26"/>
+      <c r="Q115" s="26"/>
     </row>
     <row r="116" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -13117,25 +13157,25 @@
       <c r="Q131" s="14"/>
     </row>
     <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="22" t="s">
+      <c r="A132" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="B132" s="22"/>
-      <c r="C132" s="22"/>
-      <c r="D132" s="22"/>
-      <c r="E132" s="22"/>
-      <c r="F132" s="22"/>
-      <c r="G132" s="22"/>
-      <c r="H132" s="22"/>
-      <c r="I132" s="22"/>
-      <c r="J132" s="22"/>
-      <c r="K132" s="22"/>
-      <c r="L132" s="22"/>
-      <c r="M132" s="22"/>
-      <c r="N132" s="22"/>
-      <c r="O132" s="22"/>
-      <c r="P132" s="22"/>
-      <c r="Q132" s="22"/>
+      <c r="B132" s="26"/>
+      <c r="C132" s="26"/>
+      <c r="D132" s="26"/>
+      <c r="E132" s="26"/>
+      <c r="F132" s="26"/>
+      <c r="G132" s="26"/>
+      <c r="H132" s="26"/>
+      <c r="I132" s="26"/>
+      <c r="J132" s="26"/>
+      <c r="K132" s="26"/>
+      <c r="L132" s="26"/>
+      <c r="M132" s="26"/>
+      <c r="N132" s="26"/>
+      <c r="O132" s="26"/>
+      <c r="P132" s="26"/>
+      <c r="Q132" s="26"/>
     </row>
     <row r="133" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -13635,25 +13675,25 @@
       <c r="Q148" s="14"/>
     </row>
     <row r="149" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="22" t="s">
+      <c r="A149" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="B149" s="22"/>
-      <c r="C149" s="22"/>
-      <c r="D149" s="22"/>
-      <c r="E149" s="22"/>
-      <c r="F149" s="22"/>
-      <c r="G149" s="22"/>
-      <c r="H149" s="22"/>
-      <c r="I149" s="22"/>
-      <c r="J149" s="22"/>
-      <c r="K149" s="22"/>
-      <c r="L149" s="22"/>
-      <c r="M149" s="22"/>
-      <c r="N149" s="22"/>
-      <c r="O149" s="22"/>
-      <c r="P149" s="22"/>
-      <c r="Q149" s="22"/>
+      <c r="B149" s="26"/>
+      <c r="C149" s="26"/>
+      <c r="D149" s="26"/>
+      <c r="E149" s="26"/>
+      <c r="F149" s="26"/>
+      <c r="G149" s="26"/>
+      <c r="H149" s="26"/>
+      <c r="I149" s="26"/>
+      <c r="J149" s="26"/>
+      <c r="K149" s="26"/>
+      <c r="L149" s="26"/>
+      <c r="M149" s="26"/>
+      <c r="N149" s="26"/>
+      <c r="O149" s="26"/>
+      <c r="P149" s="26"/>
+      <c r="Q149" s="26"/>
     </row>
     <row r="150" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -14183,25 +14223,25 @@
       <c r="Q166" s="14"/>
     </row>
     <row r="167" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="22" t="s">
+      <c r="A167" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="B167" s="22"/>
-      <c r="C167" s="22"/>
-      <c r="D167" s="22"/>
-      <c r="E167" s="22"/>
-      <c r="F167" s="22"/>
-      <c r="G167" s="22"/>
-      <c r="H167" s="22"/>
-      <c r="I167" s="22"/>
-      <c r="J167" s="22"/>
-      <c r="K167" s="22"/>
-      <c r="L167" s="22"/>
-      <c r="M167" s="22"/>
-      <c r="N167" s="22"/>
-      <c r="O167" s="22"/>
-      <c r="P167" s="22"/>
-      <c r="Q167" s="22"/>
+      <c r="B167" s="26"/>
+      <c r="C167" s="26"/>
+      <c r="D167" s="26"/>
+      <c r="E167" s="26"/>
+      <c r="F167" s="26"/>
+      <c r="G167" s="26"/>
+      <c r="H167" s="26"/>
+      <c r="I167" s="26"/>
+      <c r="J167" s="26"/>
+      <c r="K167" s="26"/>
+      <c r="L167" s="26"/>
+      <c r="M167" s="26"/>
+      <c r="N167" s="26"/>
+      <c r="O167" s="26"/>
+      <c r="P167" s="26"/>
+      <c r="Q167" s="26"/>
     </row>
     <row r="168" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -14701,25 +14741,25 @@
       <c r="Q183" s="14"/>
     </row>
     <row r="184" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="22" t="s">
+      <c r="A184" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="B184" s="22"/>
-      <c r="C184" s="22"/>
-      <c r="D184" s="22"/>
-      <c r="E184" s="22"/>
-      <c r="F184" s="22"/>
-      <c r="G184" s="22"/>
-      <c r="H184" s="22"/>
-      <c r="I184" s="22"/>
-      <c r="J184" s="22"/>
-      <c r="K184" s="22"/>
-      <c r="L184" s="22"/>
-      <c r="M184" s="22"/>
-      <c r="N184" s="22"/>
-      <c r="O184" s="22"/>
-      <c r="P184" s="22"/>
-      <c r="Q184" s="22"/>
+      <c r="B184" s="26"/>
+      <c r="C184" s="26"/>
+      <c r="D184" s="26"/>
+      <c r="E184" s="26"/>
+      <c r="F184" s="26"/>
+      <c r="G184" s="26"/>
+      <c r="H184" s="26"/>
+      <c r="I184" s="26"/>
+      <c r="J184" s="26"/>
+      <c r="K184" s="26"/>
+      <c r="L184" s="26"/>
+      <c r="M184" s="26"/>
+      <c r="N184" s="26"/>
+      <c r="O184" s="26"/>
+      <c r="P184" s="26"/>
+      <c r="Q184" s="26"/>
     </row>
     <row r="185" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -15189,25 +15229,25 @@
       <c r="Q199" s="14"/>
     </row>
     <row r="200" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="22" t="s">
+      <c r="A200" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="B200" s="22"/>
-      <c r="C200" s="22"/>
-      <c r="D200" s="22"/>
-      <c r="E200" s="22"/>
-      <c r="F200" s="22"/>
-      <c r="G200" s="22"/>
-      <c r="H200" s="22"/>
-      <c r="I200" s="22"/>
-      <c r="J200" s="22"/>
-      <c r="K200" s="22"/>
-      <c r="L200" s="22"/>
-      <c r="M200" s="22"/>
-      <c r="N200" s="22"/>
-      <c r="O200" s="22"/>
-      <c r="P200" s="22"/>
-      <c r="Q200" s="22"/>
+      <c r="B200" s="26"/>
+      <c r="C200" s="26"/>
+      <c r="D200" s="26"/>
+      <c r="E200" s="26"/>
+      <c r="F200" s="26"/>
+      <c r="G200" s="26"/>
+      <c r="H200" s="26"/>
+      <c r="I200" s="26"/>
+      <c r="J200" s="26"/>
+      <c r="K200" s="26"/>
+      <c r="L200" s="26"/>
+      <c r="M200" s="26"/>
+      <c r="N200" s="26"/>
+      <c r="O200" s="26"/>
+      <c r="P200" s="26"/>
+      <c r="Q200" s="26"/>
     </row>
     <row r="201" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -15767,25 +15807,25 @@
       <c r="Q218" s="14"/>
     </row>
     <row r="219" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="22" t="s">
+      <c r="A219" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="B219" s="22"/>
-      <c r="C219" s="22"/>
-      <c r="D219" s="22"/>
-      <c r="E219" s="22"/>
-      <c r="F219" s="22"/>
-      <c r="G219" s="22"/>
-      <c r="H219" s="22"/>
-      <c r="I219" s="22"/>
-      <c r="J219" s="22"/>
-      <c r="K219" s="22"/>
-      <c r="L219" s="22"/>
-      <c r="M219" s="22"/>
-      <c r="N219" s="22"/>
-      <c r="O219" s="22"/>
-      <c r="P219" s="22"/>
-      <c r="Q219" s="22"/>
+      <c r="B219" s="26"/>
+      <c r="C219" s="26"/>
+      <c r="D219" s="26"/>
+      <c r="E219" s="26"/>
+      <c r="F219" s="26"/>
+      <c r="G219" s="26"/>
+      <c r="H219" s="26"/>
+      <c r="I219" s="26"/>
+      <c r="J219" s="26"/>
+      <c r="K219" s="26"/>
+      <c r="L219" s="26"/>
+      <c r="M219" s="26"/>
+      <c r="N219" s="26"/>
+      <c r="O219" s="26"/>
+      <c r="P219" s="26"/>
+      <c r="Q219" s="26"/>
     </row>
     <row r="220" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -16285,25 +16325,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="22" t="s">
+      <c r="A236" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="B236" s="22"/>
-      <c r="C236" s="22"/>
-      <c r="D236" s="22"/>
-      <c r="E236" s="22"/>
-      <c r="F236" s="22"/>
-      <c r="G236" s="22"/>
-      <c r="H236" s="22"/>
-      <c r="I236" s="22"/>
-      <c r="J236" s="22"/>
-      <c r="K236" s="22"/>
-      <c r="L236" s="22"/>
-      <c r="M236" s="22"/>
-      <c r="N236" s="22"/>
-      <c r="O236" s="22"/>
-      <c r="P236" s="22"/>
-      <c r="Q236" s="22"/>
+      <c r="B236" s="26"/>
+      <c r="C236" s="26"/>
+      <c r="D236" s="26"/>
+      <c r="E236" s="26"/>
+      <c r="F236" s="26"/>
+      <c r="G236" s="26"/>
+      <c r="H236" s="26"/>
+      <c r="I236" s="26"/>
+      <c r="J236" s="26"/>
+      <c r="K236" s="26"/>
+      <c r="L236" s="26"/>
+      <c r="M236" s="26"/>
+      <c r="N236" s="26"/>
+      <c r="O236" s="26"/>
+      <c r="P236" s="26"/>
+      <c r="Q236" s="26"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -16833,25 +16873,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="22" t="s">
+      <c r="A254" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="B254" s="22"/>
-      <c r="C254" s="22"/>
-      <c r="D254" s="22"/>
-      <c r="E254" s="22"/>
-      <c r="F254" s="22"/>
-      <c r="G254" s="22"/>
-      <c r="H254" s="22"/>
-      <c r="I254" s="22"/>
-      <c r="J254" s="22"/>
-      <c r="K254" s="22"/>
-      <c r="L254" s="22"/>
-      <c r="M254" s="22"/>
-      <c r="N254" s="22"/>
-      <c r="O254" s="22"/>
-      <c r="P254" s="22"/>
-      <c r="Q254" s="22"/>
+      <c r="B254" s="26"/>
+      <c r="C254" s="26"/>
+      <c r="D254" s="26"/>
+      <c r="E254" s="26"/>
+      <c r="F254" s="26"/>
+      <c r="G254" s="26"/>
+      <c r="H254" s="26"/>
+      <c r="I254" s="26"/>
+      <c r="J254" s="26"/>
+      <c r="K254" s="26"/>
+      <c r="L254" s="26"/>
+      <c r="M254" s="26"/>
+      <c r="N254" s="26"/>
+      <c r="O254" s="26"/>
+      <c r="P254" s="26"/>
+      <c r="Q254" s="26"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -17411,25 +17451,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="22" t="s">
+      <c r="A273" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="B273" s="22"/>
-      <c r="C273" s="22"/>
-      <c r="D273" s="22"/>
-      <c r="E273" s="22"/>
-      <c r="F273" s="22"/>
-      <c r="G273" s="22"/>
-      <c r="H273" s="22"/>
-      <c r="I273" s="22"/>
-      <c r="J273" s="22"/>
-      <c r="K273" s="22"/>
-      <c r="L273" s="22"/>
-      <c r="M273" s="22"/>
-      <c r="N273" s="22"/>
-      <c r="O273" s="22"/>
-      <c r="P273" s="22"/>
-      <c r="Q273" s="22"/>
+      <c r="B273" s="26"/>
+      <c r="C273" s="26"/>
+      <c r="D273" s="26"/>
+      <c r="E273" s="26"/>
+      <c r="F273" s="26"/>
+      <c r="G273" s="26"/>
+      <c r="H273" s="26"/>
+      <c r="I273" s="26"/>
+      <c r="J273" s="26"/>
+      <c r="K273" s="26"/>
+      <c r="L273" s="26"/>
+      <c r="M273" s="26"/>
+      <c r="N273" s="26"/>
+      <c r="O273" s="26"/>
+      <c r="P273" s="26"/>
+      <c r="Q273" s="26"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -17989,25 +18029,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="22" t="s">
+      <c r="A292" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="B292" s="22"/>
-      <c r="C292" s="22"/>
-      <c r="D292" s="22"/>
-      <c r="E292" s="22"/>
-      <c r="F292" s="22"/>
-      <c r="G292" s="22"/>
-      <c r="H292" s="22"/>
-      <c r="I292" s="22"/>
-      <c r="J292" s="22"/>
-      <c r="K292" s="22"/>
-      <c r="L292" s="22"/>
-      <c r="M292" s="22"/>
-      <c r="N292" s="22"/>
-      <c r="O292" s="22"/>
-      <c r="P292" s="22"/>
-      <c r="Q292" s="22"/>
+      <c r="B292" s="26"/>
+      <c r="C292" s="26"/>
+      <c r="D292" s="26"/>
+      <c r="E292" s="26"/>
+      <c r="F292" s="26"/>
+      <c r="G292" s="26"/>
+      <c r="H292" s="26"/>
+      <c r="I292" s="26"/>
+      <c r="J292" s="26"/>
+      <c r="K292" s="26"/>
+      <c r="L292" s="26"/>
+      <c r="M292" s="26"/>
+      <c r="N292" s="26"/>
+      <c r="O292" s="26"/>
+      <c r="P292" s="26"/>
+      <c r="Q292" s="26"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -18567,25 +18607,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="22" t="s">
+      <c r="A311" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="B311" s="22"/>
-      <c r="C311" s="22"/>
-      <c r="D311" s="22"/>
-      <c r="E311" s="22"/>
-      <c r="F311" s="22"/>
-      <c r="G311" s="22"/>
-      <c r="H311" s="22"/>
-      <c r="I311" s="22"/>
-      <c r="J311" s="22"/>
-      <c r="K311" s="22"/>
-      <c r="L311" s="22"/>
-      <c r="M311" s="22"/>
-      <c r="N311" s="22"/>
-      <c r="O311" s="22"/>
-      <c r="P311" s="22"/>
-      <c r="Q311" s="22"/>
+      <c r="B311" s="26"/>
+      <c r="C311" s="26"/>
+      <c r="D311" s="26"/>
+      <c r="E311" s="26"/>
+      <c r="F311" s="26"/>
+      <c r="G311" s="26"/>
+      <c r="H311" s="26"/>
+      <c r="I311" s="26"/>
+      <c r="J311" s="26"/>
+      <c r="K311" s="26"/>
+      <c r="L311" s="26"/>
+      <c r="M311" s="26"/>
+      <c r="N311" s="26"/>
+      <c r="O311" s="26"/>
+      <c r="P311" s="26"/>
+      <c r="Q311" s="26"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -19146,26 +19186,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A236:Q236"/>
+    <mergeCell ref="A254:Q254"/>
+    <mergeCell ref="A273:Q273"/>
+    <mergeCell ref="A292:Q292"/>
+    <mergeCell ref="A311:Q311"/>
+    <mergeCell ref="A149:Q149"/>
+    <mergeCell ref="A167:Q167"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A219:Q219"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="A132:Q132"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A4:Q4"/>
     <mergeCell ref="A23:Q23"/>
     <mergeCell ref="A42:Q42"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A167:Q167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A236:Q236"/>
-    <mergeCell ref="A254:Q254"/>
-    <mergeCell ref="A273:Q273"/>
-    <mergeCell ref="A292:Q292"/>
-    <mergeCell ref="A311:Q311"/>
   </mergeCells>
   <dataValidations count="268">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or SEA" promptTitle="ATS Pick" prompt="Pick NE or SEA" sqref="F6:Q6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -23140,25 +23180,34 @@
       <c r="D93" t="s">
         <v>67</v>
       </c>
+      <c r="E93">
+        <v>37</v>
+      </c>
       <c r="F93" t="s">
         <v>60</v>
       </c>
+      <c r="G93">
+        <v>34</v>
+      </c>
+      <c r="H93">
+        <v>2.5</v>
+      </c>
       <c r="I93" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>BUF</v>
       </c>
       <c r="J93" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>BUF</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D94" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="E94" s="16" t="str">
+      <c r="E94" s="16">
         <f>IF(AND(E93&lt;&gt;"",G93&lt;&gt;""),E93+G93,"")</f>
-        <v/>
+        <v>71</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28958,17 +29007,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -30883,14 +30932,14 @@
       </c>
       <c r="C66" s="3">
         <f>SUMPRODUCT(('Picks Detail'!F82:F96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!F82:F96='Picks Detail'!E82:E96))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D66">
         <v>11</v>
       </c>
       <c r="E66">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(11,A$66:A$77,0)),0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F66" t="str">
         <f>IF(C66=0,"-",IF(C66&gt;E66,"W",IF(C66&lt;E66,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A66)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D66)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A66)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D66)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A66)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D66)-'Picks Detail'!E97),"L","T")),"T"))))</f>
@@ -30902,11 +30951,11 @@
       </c>
       <c r="H66">
         <f t="shared" ref="H66:H77" si="13">IF(C66="",0,C66)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I66">
         <f t="shared" ref="I66:I77" si="14">G66+H66</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30919,14 +30968,14 @@
       </c>
       <c r="C67" s="3">
         <f>SUMPRODUCT(('Picks Detail'!G82:G96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!G82:G96='Picks Detail'!E82:E96))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D67">
         <v>12</v>
       </c>
       <c r="E67">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(12,A$66:A$77,0)),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F67" t="str">
         <f>IF(C67=0,"-",IF(C67&gt;E67,"W",IF(C67&lt;E67,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A67)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D67)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A67)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D67)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A67)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D67)-'Picks Detail'!E97),"L","T")),"T"))))</f>
@@ -30938,11 +30987,11 @@
       </c>
       <c r="H67">
         <f t="shared" si="13"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I67">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30955,14 +31004,14 @@
       </c>
       <c r="C68" s="3">
         <f>SUMPRODUCT(('Picks Detail'!H82:H96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!H82:H96='Picks Detail'!E82:E96))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D68">
         <v>5</v>
       </c>
       <c r="E68">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(5,A$66:A$77,0)),0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F68" t="str">
         <f>IF(C68=0,"-",IF(C68&gt;E68,"W",IF(C68&lt;E68,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A68)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D68)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A68)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D68)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A68)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D68)-'Picks Detail'!E97),"L","T")),"T"))))</f>
@@ -30974,11 +31023,11 @@
       </c>
       <c r="H68">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I68">
         <f t="shared" si="14"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30998,7 +31047,7 @@
       </c>
       <c r="E69">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(6,A$66:A$77,0)),0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F69" t="str">
         <f>IF(C69=0,"-",IF(C69&gt;E69,"W",IF(C69&lt;E69,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A69)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D69)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A69)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D69)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A69)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D69)-'Picks Detail'!E97),"L","T")),"T"))))</f>
@@ -31027,14 +31076,14 @@
       </c>
       <c r="C70" s="3">
         <f>SUMPRODUCT(('Picks Detail'!J82:J96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!J82:J96='Picks Detail'!E82:E96))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D70">
         <v>3</v>
       </c>
       <c r="E70">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(3,A$66:A$77,0)),0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F70" t="str">
         <f>IF(C70=0,"-",IF(C70&gt;E70,"W",IF(C70&lt;E70,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A70)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D70)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A70)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D70)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A70)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D70)-'Picks Detail'!E97),"L","T")),"T"))))</f>
@@ -31046,11 +31095,11 @@
       </c>
       <c r="H70">
         <f t="shared" si="13"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I70">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31063,7 +31112,7 @@
       </c>
       <c r="C71" s="3">
         <f>SUMPRODUCT(('Picks Detail'!K82:K96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!K82:K96='Picks Detail'!E82:E96))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D71">
         <v>4</v>
@@ -31082,11 +31131,11 @@
       </c>
       <c r="H71">
         <f t="shared" si="13"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I71">
         <f t="shared" si="14"/>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31099,7 +31148,7 @@
       </c>
       <c r="C72" s="3">
         <f>SUMPRODUCT(('Picks Detail'!L82:L96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!L82:L96='Picks Detail'!E82:E96))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D72">
         <v>10</v>
@@ -31110,19 +31159,19 @@
       </c>
       <c r="F72" t="str">
         <f>IF(C72=0,"-",IF(C72&gt;E72,"W",IF(C72&lt;E72,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A72)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D72)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A72)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D72)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A72)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D72)-'Picks Detail'!E97),"L","T")),"T"))))</f>
-        <v>L</v>
+        <v>W</v>
       </c>
       <c r="G72">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H72">
         <f t="shared" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I72">
         <f t="shared" si="14"/>
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31135,14 +31184,14 @@
       </c>
       <c r="C73" s="3">
         <f>SUMPRODUCT(('Picks Detail'!M82:M96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!M82:M96='Picks Detail'!E82:E96))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D73">
         <v>9</v>
       </c>
       <c r="E73">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(9,A$66:A$77,0)),0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="str">
         <f>IF(C73=0,"-",IF(C73&gt;E73,"W",IF(C73&lt;E73,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A73)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D73)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A73)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D73)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A73)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D73)-'Picks Detail'!E97),"L","T")),"T"))))</f>
@@ -31154,11 +31203,11 @@
       </c>
       <c r="H73">
         <f t="shared" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I73">
         <f t="shared" si="14"/>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31171,14 +31220,14 @@
       </c>
       <c r="C74" s="3">
         <f>SUMPRODUCT(('Picks Detail'!N82:N96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!N82:N96='Picks Detail'!E82:E96))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D74">
         <v>8</v>
       </c>
       <c r="E74">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(8,A$66:A$77,0)),0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F74" t="str">
         <f>IF(C74=0,"-",IF(C74&gt;E74,"W",IF(C74&lt;E74,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A74)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D74)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A74)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D74)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A74)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D74)-'Picks Detail'!E97),"L","T")),"T"))))</f>
@@ -31190,11 +31239,11 @@
       </c>
       <c r="H74">
         <f t="shared" si="13"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I74">
         <f t="shared" si="14"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31214,15 +31263,15 @@
       </c>
       <c r="E75">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(7,A$66:A$77,0)),0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F75" t="str">
         <f>IF(C75=0,"-",IF(C75&gt;E75,"W",IF(C75&lt;E75,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A75)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D75)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A75)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D75)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A75)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D75)-'Picks Detail'!E97),"L","T")),"T"))))</f>
-        <v>W</v>
+        <v>L</v>
       </c>
       <c r="G75">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H75">
         <f t="shared" si="13"/>
@@ -31230,7 +31279,7 @@
       </c>
       <c r="I75">
         <f t="shared" si="14"/>
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31243,14 +31292,14 @@
       </c>
       <c r="C76" s="3">
         <f>SUMPRODUCT(('Picks Detail'!P82:P96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!P82:P96='Picks Detail'!E82:E96))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D76">
         <v>1</v>
       </c>
       <c r="E76">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(1,A$66:A$77,0)),0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F76" t="str">
         <f>IF(C76=0,"-",IF(C76&gt;E76,"W",IF(C76&lt;E76,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A76)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D76)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A76)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D76)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A76)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D76)-'Picks Detail'!E97),"L","T")),"T"))))</f>
@@ -31262,11 +31311,11 @@
       </c>
       <c r="H76">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I76">
         <f t="shared" si="14"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31279,14 +31328,14 @@
       </c>
       <c r="C77" s="3">
         <f>SUMPRODUCT(('Picks Detail'!Q82:Q96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!Q82:Q96='Picks Detail'!E82:E96))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D77">
         <v>2</v>
       </c>
       <c r="E77">
         <f>IFERROR(INDEX(C$66:C$77,MATCH(2,A$66:A$77,0)),0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F77" t="str">
         <f>IF(C77=0,"-",IF(C77&gt;E77,"W",IF(C77&lt;E77,"L",IF(AND('Picks Detail'!E97&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,A77)&lt;&gt;"",INDEX('Picks Detail'!F97:Q97,1,D77)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A77)-'Picks Detail'!E97)&lt;ABS(INDEX('Picks Detail'!F97:Q97,1,D77)-'Picks Detail'!E97),"W",IF(ABS(INDEX('Picks Detail'!F97:Q97,1,A77)-'Picks Detail'!E97)&gt;ABS(INDEX('Picks Detail'!F97:Q97,1,D77)-'Picks Detail'!E97),"L","T")),"T"))))</f>
@@ -31298,11 +31347,11 @@
       </c>
       <c r="H77">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I77">
         <f t="shared" si="14"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31791,17 +31840,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="22" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -34624,17 +34673,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -37457,19 +37506,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -37532,7 +37581,7 @@
       </c>
       <c r="G3">
         <f>Helper!G2</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3">
         <f>Helper!H2</f>
@@ -37540,7 +37589,7 @@
       </c>
       <c r="I3">
         <f>Helper!I2</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J3">
         <f>Helper!J2</f>
@@ -37577,7 +37626,7 @@
       </c>
       <c r="G4">
         <f>Helper!G3</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4">
         <f>Helper!H3</f>
@@ -37585,7 +37634,7 @@
       </c>
       <c r="I4">
         <f>Helper!I3</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J4">
         <f>Helper!J3</f>
@@ -37622,7 +37671,7 @@
       </c>
       <c r="G5">
         <f>Helper!G4</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <f>Helper!H4</f>
@@ -37630,7 +37679,7 @@
       </c>
       <c r="I5">
         <f>Helper!I4</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J5">
         <f>Helper!J4</f>
@@ -37712,7 +37761,7 @@
       </c>
       <c r="G7">
         <f>Helper!G6</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7">
         <f>Helper!H6</f>
@@ -37720,7 +37769,7 @@
       </c>
       <c r="I7">
         <f>Helper!I6</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J7">
         <f>Helper!J6</f>
@@ -37757,7 +37806,7 @@
       </c>
       <c r="G8">
         <f>Helper!G7</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H8">
         <f>Helper!H7</f>
@@ -37765,7 +37814,7 @@
       </c>
       <c r="I8">
         <f>Helper!I7</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J8">
         <f>Helper!J7</f>
@@ -37802,7 +37851,7 @@
       </c>
       <c r="G9">
         <f>Helper!G8</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9">
         <f>Helper!H8</f>
@@ -37810,7 +37859,7 @@
       </c>
       <c r="I9">
         <f>Helper!I8</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J9">
         <f>Helper!J8</f>
@@ -37847,7 +37896,7 @@
       </c>
       <c r="G10">
         <f>Helper!G9</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H10">
         <f>Helper!H9</f>
@@ -37855,7 +37904,7 @@
       </c>
       <c r="I10">
         <f>Helper!I9</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J10">
         <f>Helper!J9</f>
@@ -37892,7 +37941,7 @@
       </c>
       <c r="G11">
         <f>Helper!G10</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H11">
         <f>Helper!H10</f>
@@ -37900,7 +37949,7 @@
       </c>
       <c r="I11">
         <f>Helper!I10</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J11">
         <f>Helper!J10</f>
@@ -37982,7 +38031,7 @@
       </c>
       <c r="G13">
         <f>Helper!G12</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H13">
         <f>Helper!H12</f>
@@ -37990,7 +38039,7 @@
       </c>
       <c r="I13">
         <f>Helper!I12</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J13">
         <f>Helper!J12</f>
@@ -38027,7 +38076,7 @@
       </c>
       <c r="G14">
         <f>Helper!G13</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14">
         <f>Helper!H13</f>
@@ -38035,7 +38084,7 @@
       </c>
       <c r="I14">
         <f>Helper!I13</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J14">
         <f>Helper!J13</f>
@@ -39359,7 +39408,7 @@
       </c>
       <c r="C57">
         <f>Helper!I2</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D57">
         <f>Helper!R2</f>
@@ -39371,11 +39420,11 @@
       </c>
       <c r="F57">
         <f>Helper!AE2</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G57">
         <f>Helper!K2</f>
-        <v>56.000100000000003</v>
+        <v>57.000100000000003</v>
       </c>
       <c r="H57">
         <f>Helper!T2</f>
@@ -39392,7 +39441,7 @@
       </c>
       <c r="C58">
         <f>Helper!I3</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D58">
         <f>Helper!R3</f>
@@ -39404,11 +39453,11 @@
       </c>
       <c r="F58">
         <f>Helper!AE3</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G58">
         <f>Helper!K3</f>
-        <v>56.0002</v>
+        <v>57.0002</v>
       </c>
       <c r="H58">
         <f>Helper!T3</f>
@@ -39425,7 +39474,7 @@
       </c>
       <c r="C59">
         <f>Helper!I4</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D59">
         <f>Helper!R4</f>
@@ -39437,11 +39486,11 @@
       </c>
       <c r="F59">
         <f>Helper!AE4</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G59">
         <f>Helper!K4</f>
-        <v>53.000300000000003</v>
+        <v>54.000300000000003</v>
       </c>
       <c r="H59">
         <f>Helper!T4</f>
@@ -39491,7 +39540,7 @@
       </c>
       <c r="C61">
         <f>Helper!I6</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D61">
         <f>Helper!R6</f>
@@ -39503,11 +39552,11 @@
       </c>
       <c r="F61">
         <f>Helper!AE6</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G61">
         <f>Helper!K6</f>
-        <v>51.000500000000002</v>
+        <v>52.000500000000002</v>
       </c>
       <c r="H61">
         <f>Helper!T6</f>
@@ -39524,7 +39573,7 @@
       </c>
       <c r="C62">
         <f>Helper!I7</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D62">
         <f>Helper!R7</f>
@@ -39536,11 +39585,11 @@
       </c>
       <c r="F62">
         <f>Helper!AE7</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G62">
         <f>Helper!K7</f>
-        <v>49.000599999999999</v>
+        <v>50.000599999999999</v>
       </c>
       <c r="H62">
         <f>Helper!T7</f>
@@ -39557,7 +39606,7 @@
       </c>
       <c r="C63">
         <f>Helper!I8</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D63">
         <f>Helper!R8</f>
@@ -39569,11 +39618,11 @@
       </c>
       <c r="F63">
         <f>Helper!AE8</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G63">
         <f>Helper!K8</f>
-        <v>39.000700000000002</v>
+        <v>40.000700000000002</v>
       </c>
       <c r="H63">
         <f>Helper!T8</f>
@@ -39590,7 +39639,7 @@
       </c>
       <c r="C64">
         <f>Helper!I9</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D64">
         <f>Helper!R9</f>
@@ -39602,11 +39651,11 @@
       </c>
       <c r="F64">
         <f>Helper!AE9</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G64">
         <f>Helper!K9</f>
-        <v>36.000799999999998</v>
+        <v>37.000799999999998</v>
       </c>
       <c r="H64">
         <f>Helper!T9</f>
@@ -39623,7 +39672,7 @@
       </c>
       <c r="C65">
         <f>Helper!I10</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D65">
         <f>Helper!R10</f>
@@ -39635,11 +39684,11 @@
       </c>
       <c r="F65">
         <f>Helper!AE10</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G65">
         <f>Helper!K10</f>
-        <v>42.000900000000001</v>
+        <v>43.000900000000001</v>
       </c>
       <c r="H65">
         <f>Helper!T10</f>
@@ -39689,7 +39738,7 @@
       </c>
       <c r="C67">
         <f>Helper!I12</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D67">
         <f>Helper!R12</f>
@@ -39701,11 +39750,11 @@
       </c>
       <c r="F67">
         <f>Helper!AE12</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G67">
         <f>Helper!K12</f>
-        <v>47.001100000000001</v>
+        <v>48.001100000000001</v>
       </c>
       <c r="H67">
         <f>Helper!T12</f>
@@ -39722,7 +39771,7 @@
       </c>
       <c r="C68">
         <f>Helper!I13</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D68">
         <f>Helper!R13</f>
@@ -39734,11 +39783,11 @@
       </c>
       <c r="F68">
         <f>Helper!AE13</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G68">
         <f>Helper!K13</f>
-        <v>41.001199999999997</v>
+        <v>42.001199999999997</v>
       </c>
       <c r="H68">
         <f>Helper!T13</f>
@@ -39808,7 +39857,7 @@
       </c>
       <c r="B5" t="str">
         <f>INDEX(Helper!B$2:B$13,MATCH(MAX(Helper!K$2:K$13),Helper!K$2:K$13,0))</f>
-        <v>Zach Zarra</v>
+        <v>Chris Simmons</v>
       </c>
       <c r="C5" t="s">
         <v>252</v>
@@ -39818,7 +39867,7 @@
       </c>
       <c r="E5" t="str">
         <f>B5</f>
-        <v>Zach Zarra</v>
+        <v>Chris Simmons</v>
       </c>
       <c r="F5" t="str">
         <f>IF(B5="","—","QUALIFIED")</f>
@@ -39976,11 +40025,11 @@
       </c>
       <c r="B13" t="str">
         <f>INDEX(H$40:H$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
-        <v>Chris Simmons</v>
+        <v>Evan Loeser</v>
       </c>
       <c r="C13">
         <f>INDEX(I$40:I$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
         <v>263</v>
@@ -40026,7 +40075,7 @@
       </c>
       <c r="B17" t="str">
         <f>E5</f>
-        <v>Zach Zarra</v>
+        <v>Chris Simmons</v>
       </c>
       <c r="C17" t="str">
         <f>D5</f>
@@ -40091,7 +40140,7 @@
       </c>
       <c r="B22" t="str">
         <f>B13</f>
-        <v>Chris Simmons</v>
+        <v>Evan Loeser</v>
       </c>
       <c r="C22" t="str">
         <f>"Wild Card 1"</f>
@@ -40456,7 +40505,7 @@
       </c>
       <c r="I40">
         <f>Helper!AE2</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J40" t="b">
         <f t="shared" ref="J40:J51" si="1">OR(H40=$E$5,H40=$E$6,H40=$E$7,H40=$E$8,H40=$E$9)</f>
@@ -40464,7 +40513,7 @@
       </c>
       <c r="K40">
         <f>IF(J40,-1,I40+0.00001)</f>
-        <v>56.000010000000003</v>
+        <v>57.000010000000003</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40474,15 +40523,15 @@
       </c>
       <c r="I41">
         <f>Helper!AE3</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J41" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41">
         <f>IF(J41,-1,I41+0.00002)</f>
-        <v>56.000019999999999</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40492,7 +40541,7 @@
       </c>
       <c r="I42">
         <f>Helper!AE4</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J42" t="b">
         <f t="shared" si="1"/>
@@ -40500,7 +40549,7 @@
       </c>
       <c r="K42">
         <f>IF(J42,-1,I42+0.00003)</f>
-        <v>53.000030000000002</v>
+        <v>54.000030000000002</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40528,7 +40577,7 @@
       </c>
       <c r="I44">
         <f>Helper!AE6</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J44" t="b">
         <f t="shared" si="1"/>
@@ -40536,7 +40585,7 @@
       </c>
       <c r="K44">
         <f>IF(J44,-1,I44+0.00005)</f>
-        <v>51.000050000000002</v>
+        <v>52.000050000000002</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40546,7 +40595,7 @@
       </c>
       <c r="I45">
         <f>Helper!AE7</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J45" t="b">
         <f t="shared" si="1"/>
@@ -40554,7 +40603,7 @@
       </c>
       <c r="K45">
         <f>IF(J45,-1,I45+0.00006)</f>
-        <v>49.000059999999998</v>
+        <v>50.000059999999998</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40564,7 +40613,7 @@
       </c>
       <c r="I46">
         <f>Helper!AE8</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J46" t="b">
         <f t="shared" si="1"/>
@@ -40572,7 +40621,7 @@
       </c>
       <c r="K46">
         <f>IF(J46,-1,I46+0.00007)</f>
-        <v>39.000070000000001</v>
+        <v>40.000070000000001</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40582,7 +40631,7 @@
       </c>
       <c r="I47">
         <f>Helper!AE9</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J47" t="b">
         <f t="shared" si="1"/>
@@ -40600,7 +40649,7 @@
       </c>
       <c r="I48">
         <f>Helper!AE10</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J48" t="b">
         <f t="shared" si="1"/>
@@ -40608,7 +40657,7 @@
       </c>
       <c r="K48">
         <f>IF(J48,-1,I48+0.00009)</f>
-        <v>42.00009</v>
+        <v>43.00009</v>
       </c>
     </row>
     <row r="49" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40622,11 +40671,11 @@
       </c>
       <c r="J49" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49">
         <f>IF(J49,-1,I49+0.0001)</f>
-        <v>-1</v>
+        <v>56.000100000000003</v>
       </c>
     </row>
     <row r="50" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40636,7 +40685,7 @@
       </c>
       <c r="I50">
         <f>Helper!AE12</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J50" t="b">
         <f t="shared" si="1"/>
@@ -40654,7 +40703,7 @@
       </c>
       <c r="I51">
         <f>Helper!AE13</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J51" t="b">
         <f t="shared" si="1"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1048" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25747702-C5A7-483A-8745-289FE83B87E2}"/>
+  <xr:revisionPtr revIDLastSave="1049" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{645F2539-8A24-413C-9B72-3A9AB5D00601}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1381,9 +1381,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1470,6 +1470,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1855,7 +1859,7 @@
         <v>23</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2857,7 +2861,7 @@
       </c>
       <c r="G2">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H66,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G66,0)</f>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H2">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H81,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G81,0)</f>
@@ -2865,15 +2869,15 @@
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I13" si="0">SUM(C2:H2)</f>
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J2">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F6="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F21="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F36="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F51="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F66="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F81="W"),1,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <f>I2+0.0001</f>
-        <v>57.000100000000003</v>
+        <v>63.000100000000003</v>
       </c>
       <c r="L2">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H6,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G6,0)</f>
@@ -2953,11 +2957,11 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE13" si="2">I2+R2+AC2</f>
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AF2">
         <f>AE2+0.0001</f>
-        <v>57.000100000000003</v>
+        <v>63.000100000000003</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2986,7 +2990,7 @@
       </c>
       <c r="G3">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H67,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G67,0)</f>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H3">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H82,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G82,0)</f>
@@ -2994,15 +2998,15 @@
       </c>
       <c r="I3">
         <f t="shared" si="0"/>
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J3">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F7="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F22="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F37="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F52="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F67="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F82="W"),1,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3">
         <f>I3+0.0002</f>
-        <v>57.0002</v>
+        <v>63.0002</v>
       </c>
       <c r="L3">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H7,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G7,0)</f>
@@ -3082,11 +3086,11 @@
       </c>
       <c r="AE3">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AF3">
         <f>AE3+0.0002</f>
-        <v>57.0002</v>
+        <v>63.0002</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3373,7 +3377,7 @@
       </c>
       <c r="G6">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H70,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G70,0)</f>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H6">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H85,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G85,0)</f>
@@ -3381,15 +3385,15 @@
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J6">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F10="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F25="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F40="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F55="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F70="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F85="W"),1,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6">
         <f>I6+0.0005</f>
-        <v>52.000500000000002</v>
+        <v>58.000500000000002</v>
       </c>
       <c r="L6">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H10,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G10,0)</f>
@@ -3469,11 +3473,11 @@
       </c>
       <c r="AE6">
         <f t="shared" si="2"/>
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AF6">
         <f>AE6+0.0005</f>
-        <v>52.000500000000002</v>
+        <v>58.000500000000002</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3502,7 +3506,7 @@
       </c>
       <c r="G7">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H71,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G71,0)</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H7">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H86,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G86,0)</f>
@@ -3510,15 +3514,15 @@
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J7">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F11="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F26="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F41="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F56="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F71="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F86="W"),1,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7">
         <f>I7+0.0006</f>
-        <v>50.000599999999999</v>
+        <v>56.000599999999999</v>
       </c>
       <c r="L7">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H11,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G11,0)</f>
@@ -3598,11 +3602,11 @@
       </c>
       <c r="AE7">
         <f t="shared" si="2"/>
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AF7">
         <f>AE7+0.0006</f>
-        <v>50.000599999999999</v>
+        <v>56.000599999999999</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3631,7 +3635,7 @@
       </c>
       <c r="G8">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H72,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G72,0)</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H8">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H87,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G87,0)</f>
@@ -3639,15 +3643,15 @@
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J8">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F12="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F27="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F42="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F57="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F72="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F87="W"),1,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8">
         <f>I8+0.0007</f>
-        <v>40.000700000000002</v>
+        <v>46.000700000000002</v>
       </c>
       <c r="L8">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H12,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G12,0)</f>
@@ -3727,11 +3731,11 @@
       </c>
       <c r="AE8">
         <f t="shared" si="2"/>
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AF8">
         <f>AE8+0.0007</f>
-        <v>40.000700000000002</v>
+        <v>46.000700000000002</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3760,7 +3764,7 @@
       </c>
       <c r="G9">
         <f>IF(Roster!$B$16&gt;=5,'Wk 1-6 Input'!H73,0)+IF(Roster!$B$16&gt;5,'Wk 1-6 Input'!G73,0)</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H9">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H88,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G88,0)</f>
@@ -3768,15 +3772,15 @@
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J9">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F13="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F28="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F43="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F58="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F73="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F88="W"),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9">
         <f>I9+0.0008</f>
-        <v>37.000799999999998</v>
+        <v>43.000799999999998</v>
       </c>
       <c r="L9">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H13,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G13,0)</f>
@@ -3856,11 +3860,11 @@
       </c>
       <c r="AE9">
         <f t="shared" si="2"/>
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="AF9">
         <f>AE9+0.0008</f>
-        <v>37.000799999999998</v>
+        <v>43.000799999999998</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7281,67 +7285,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8309,25 +8313,25 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="26"/>
-      <c r="P23" s="26"/>
-      <c r="Q23" s="26"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="24"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="24"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -9295,25 +9299,25 @@
       </c>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="26" t="s">
+      <c r="A42" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="26"/>
-      <c r="L42" s="26"/>
-      <c r="M42" s="26"/>
-      <c r="N42" s="26"/>
-      <c r="O42" s="26"/>
-      <c r="P42" s="26"/>
-      <c r="Q42" s="26"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="24"/>
+      <c r="N42" s="24"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="24"/>
+      <c r="Q42" s="24"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -10243,25 +10247,25 @@
       </c>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="26" t="s">
+      <c r="A61" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="26"/>
-      <c r="C61" s="26"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="26"/>
-      <c r="F61" s="26"/>
-      <c r="G61" s="26"/>
-      <c r="H61" s="26"/>
-      <c r="I61" s="26"/>
-      <c r="J61" s="26"/>
-      <c r="K61" s="26"/>
-      <c r="L61" s="26"/>
-      <c r="M61" s="26"/>
-      <c r="N61" s="26"/>
-      <c r="O61" s="26"/>
-      <c r="P61" s="26"/>
-      <c r="Q61" s="26"/>
+      <c r="B61" s="24"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="24"/>
+      <c r="J61" s="24"/>
+      <c r="K61" s="24"/>
+      <c r="L61" s="24"/>
+      <c r="M61" s="24"/>
+      <c r="N61" s="24"/>
+      <c r="O61" s="24"/>
+      <c r="P61" s="24"/>
+      <c r="Q61" s="24"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -11229,25 +11233,25 @@
       </c>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="26" t="s">
+      <c r="A80" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="26"/>
-      <c r="C80" s="26"/>
-      <c r="D80" s="26"/>
-      <c r="E80" s="26"/>
-      <c r="F80" s="26"/>
-      <c r="G80" s="26"/>
-      <c r="H80" s="26"/>
-      <c r="I80" s="26"/>
-      <c r="J80" s="26"/>
-      <c r="K80" s="26"/>
-      <c r="L80" s="26"/>
-      <c r="M80" s="26"/>
-      <c r="N80" s="26"/>
-      <c r="O80" s="26"/>
-      <c r="P80" s="26"/>
-      <c r="Q80" s="26"/>
+      <c r="B80" s="24"/>
+      <c r="C80" s="24"/>
+      <c r="D80" s="24"/>
+      <c r="E80" s="24"/>
+      <c r="F80" s="24"/>
+      <c r="G80" s="24"/>
+      <c r="H80" s="24"/>
+      <c r="I80" s="24"/>
+      <c r="J80" s="24"/>
+      <c r="K80" s="24"/>
+      <c r="L80" s="24"/>
+      <c r="M80" s="24"/>
+      <c r="N80" s="24"/>
+      <c r="O80" s="24"/>
+      <c r="P80" s="24"/>
+      <c r="Q80" s="24"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -12121,25 +12125,25 @@
       </c>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="26" t="s">
+      <c r="A98" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="26"/>
-      <c r="C98" s="26"/>
-      <c r="D98" s="26"/>
-      <c r="E98" s="26"/>
-      <c r="F98" s="26"/>
-      <c r="G98" s="26"/>
-      <c r="H98" s="26"/>
-      <c r="I98" s="26"/>
-      <c r="J98" s="26"/>
-      <c r="K98" s="26"/>
-      <c r="L98" s="26"/>
-      <c r="M98" s="26"/>
-      <c r="N98" s="26"/>
-      <c r="O98" s="26"/>
-      <c r="P98" s="26"/>
-      <c r="Q98" s="26"/>
+      <c r="B98" s="24"/>
+      <c r="C98" s="24"/>
+      <c r="D98" s="24"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24"/>
+      <c r="H98" s="24"/>
+      <c r="I98" s="24"/>
+      <c r="J98" s="24"/>
+      <c r="K98" s="24"/>
+      <c r="L98" s="24"/>
+      <c r="M98" s="24"/>
+      <c r="N98" s="24"/>
+      <c r="O98" s="24"/>
+      <c r="P98" s="24"/>
+      <c r="Q98" s="24"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -12639,25 +12643,25 @@
       <c r="Q114" s="14"/>
     </row>
     <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="26" t="s">
+      <c r="A115" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="26"/>
-      <c r="C115" s="26"/>
-      <c r="D115" s="26"/>
-      <c r="E115" s="26"/>
-      <c r="F115" s="26"/>
-      <c r="G115" s="26"/>
-      <c r="H115" s="26"/>
-      <c r="I115" s="26"/>
-      <c r="J115" s="26"/>
-      <c r="K115" s="26"/>
-      <c r="L115" s="26"/>
-      <c r="M115" s="26"/>
-      <c r="N115" s="26"/>
-      <c r="O115" s="26"/>
-      <c r="P115" s="26"/>
-      <c r="Q115" s="26"/>
+      <c r="B115" s="24"/>
+      <c r="C115" s="24"/>
+      <c r="D115" s="24"/>
+      <c r="E115" s="24"/>
+      <c r="F115" s="24"/>
+      <c r="G115" s="24"/>
+      <c r="H115" s="24"/>
+      <c r="I115" s="24"/>
+      <c r="J115" s="24"/>
+      <c r="K115" s="24"/>
+      <c r="L115" s="24"/>
+      <c r="M115" s="24"/>
+      <c r="N115" s="24"/>
+      <c r="O115" s="24"/>
+      <c r="P115" s="24"/>
+      <c r="Q115" s="24"/>
     </row>
     <row r="116" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -13157,25 +13161,25 @@
       <c r="Q131" s="14"/>
     </row>
     <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="26" t="s">
+      <c r="A132" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="B132" s="26"/>
-      <c r="C132" s="26"/>
-      <c r="D132" s="26"/>
-      <c r="E132" s="26"/>
-      <c r="F132" s="26"/>
-      <c r="G132" s="26"/>
-      <c r="H132" s="26"/>
-      <c r="I132" s="26"/>
-      <c r="J132" s="26"/>
-      <c r="K132" s="26"/>
-      <c r="L132" s="26"/>
-      <c r="M132" s="26"/>
-      <c r="N132" s="26"/>
-      <c r="O132" s="26"/>
-      <c r="P132" s="26"/>
-      <c r="Q132" s="26"/>
+      <c r="B132" s="24"/>
+      <c r="C132" s="24"/>
+      <c r="D132" s="24"/>
+      <c r="E132" s="24"/>
+      <c r="F132" s="24"/>
+      <c r="G132" s="24"/>
+      <c r="H132" s="24"/>
+      <c r="I132" s="24"/>
+      <c r="J132" s="24"/>
+      <c r="K132" s="24"/>
+      <c r="L132" s="24"/>
+      <c r="M132" s="24"/>
+      <c r="N132" s="24"/>
+      <c r="O132" s="24"/>
+      <c r="P132" s="24"/>
+      <c r="Q132" s="24"/>
     </row>
     <row r="133" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -13675,25 +13679,25 @@
       <c r="Q148" s="14"/>
     </row>
     <row r="149" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="26" t="s">
+      <c r="A149" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="B149" s="26"/>
-      <c r="C149" s="26"/>
-      <c r="D149" s="26"/>
-      <c r="E149" s="26"/>
-      <c r="F149" s="26"/>
-      <c r="G149" s="26"/>
-      <c r="H149" s="26"/>
-      <c r="I149" s="26"/>
-      <c r="J149" s="26"/>
-      <c r="K149" s="26"/>
-      <c r="L149" s="26"/>
-      <c r="M149" s="26"/>
-      <c r="N149" s="26"/>
-      <c r="O149" s="26"/>
-      <c r="P149" s="26"/>
-      <c r="Q149" s="26"/>
+      <c r="B149" s="24"/>
+      <c r="C149" s="24"/>
+      <c r="D149" s="24"/>
+      <c r="E149" s="24"/>
+      <c r="F149" s="24"/>
+      <c r="G149" s="24"/>
+      <c r="H149" s="24"/>
+      <c r="I149" s="24"/>
+      <c r="J149" s="24"/>
+      <c r="K149" s="24"/>
+      <c r="L149" s="24"/>
+      <c r="M149" s="24"/>
+      <c r="N149" s="24"/>
+      <c r="O149" s="24"/>
+      <c r="P149" s="24"/>
+      <c r="Q149" s="24"/>
     </row>
     <row r="150" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -14223,25 +14227,25 @@
       <c r="Q166" s="14"/>
     </row>
     <row r="167" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="26" t="s">
+      <c r="A167" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="B167" s="26"/>
-      <c r="C167" s="26"/>
-      <c r="D167" s="26"/>
-      <c r="E167" s="26"/>
-      <c r="F167" s="26"/>
-      <c r="G167" s="26"/>
-      <c r="H167" s="26"/>
-      <c r="I167" s="26"/>
-      <c r="J167" s="26"/>
-      <c r="K167" s="26"/>
-      <c r="L167" s="26"/>
-      <c r="M167" s="26"/>
-      <c r="N167" s="26"/>
-      <c r="O167" s="26"/>
-      <c r="P167" s="26"/>
-      <c r="Q167" s="26"/>
+      <c r="B167" s="24"/>
+      <c r="C167" s="24"/>
+      <c r="D167" s="24"/>
+      <c r="E167" s="24"/>
+      <c r="F167" s="24"/>
+      <c r="G167" s="24"/>
+      <c r="H167" s="24"/>
+      <c r="I167" s="24"/>
+      <c r="J167" s="24"/>
+      <c r="K167" s="24"/>
+      <c r="L167" s="24"/>
+      <c r="M167" s="24"/>
+      <c r="N167" s="24"/>
+      <c r="O167" s="24"/>
+      <c r="P167" s="24"/>
+      <c r="Q167" s="24"/>
     </row>
     <row r="168" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -14741,25 +14745,25 @@
       <c r="Q183" s="14"/>
     </row>
     <row r="184" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="26" t="s">
+      <c r="A184" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="B184" s="26"/>
-      <c r="C184" s="26"/>
-      <c r="D184" s="26"/>
-      <c r="E184" s="26"/>
-      <c r="F184" s="26"/>
-      <c r="G184" s="26"/>
-      <c r="H184" s="26"/>
-      <c r="I184" s="26"/>
-      <c r="J184" s="26"/>
-      <c r="K184" s="26"/>
-      <c r="L184" s="26"/>
-      <c r="M184" s="26"/>
-      <c r="N184" s="26"/>
-      <c r="O184" s="26"/>
-      <c r="P184" s="26"/>
-      <c r="Q184" s="26"/>
+      <c r="B184" s="24"/>
+      <c r="C184" s="24"/>
+      <c r="D184" s="24"/>
+      <c r="E184" s="24"/>
+      <c r="F184" s="24"/>
+      <c r="G184" s="24"/>
+      <c r="H184" s="24"/>
+      <c r="I184" s="24"/>
+      <c r="J184" s="24"/>
+      <c r="K184" s="24"/>
+      <c r="L184" s="24"/>
+      <c r="M184" s="24"/>
+      <c r="N184" s="24"/>
+      <c r="O184" s="24"/>
+      <c r="P184" s="24"/>
+      <c r="Q184" s="24"/>
     </row>
     <row r="185" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -15229,25 +15233,25 @@
       <c r="Q199" s="14"/>
     </row>
     <row r="200" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="26" t="s">
+      <c r="A200" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="B200" s="26"/>
-      <c r="C200" s="26"/>
-      <c r="D200" s="26"/>
-      <c r="E200" s="26"/>
-      <c r="F200" s="26"/>
-      <c r="G200" s="26"/>
-      <c r="H200" s="26"/>
-      <c r="I200" s="26"/>
-      <c r="J200" s="26"/>
-      <c r="K200" s="26"/>
-      <c r="L200" s="26"/>
-      <c r="M200" s="26"/>
-      <c r="N200" s="26"/>
-      <c r="O200" s="26"/>
-      <c r="P200" s="26"/>
-      <c r="Q200" s="26"/>
+      <c r="B200" s="24"/>
+      <c r="C200" s="24"/>
+      <c r="D200" s="24"/>
+      <c r="E200" s="24"/>
+      <c r="F200" s="24"/>
+      <c r="G200" s="24"/>
+      <c r="H200" s="24"/>
+      <c r="I200" s="24"/>
+      <c r="J200" s="24"/>
+      <c r="K200" s="24"/>
+      <c r="L200" s="24"/>
+      <c r="M200" s="24"/>
+      <c r="N200" s="24"/>
+      <c r="O200" s="24"/>
+      <c r="P200" s="24"/>
+      <c r="Q200" s="24"/>
     </row>
     <row r="201" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -15807,25 +15811,25 @@
       <c r="Q218" s="14"/>
     </row>
     <row r="219" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="26" t="s">
+      <c r="A219" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="B219" s="26"/>
-      <c r="C219" s="26"/>
-      <c r="D219" s="26"/>
-      <c r="E219" s="26"/>
-      <c r="F219" s="26"/>
-      <c r="G219" s="26"/>
-      <c r="H219" s="26"/>
-      <c r="I219" s="26"/>
-      <c r="J219" s="26"/>
-      <c r="K219" s="26"/>
-      <c r="L219" s="26"/>
-      <c r="M219" s="26"/>
-      <c r="N219" s="26"/>
-      <c r="O219" s="26"/>
-      <c r="P219" s="26"/>
-      <c r="Q219" s="26"/>
+      <c r="B219" s="24"/>
+      <c r="C219" s="24"/>
+      <c r="D219" s="24"/>
+      <c r="E219" s="24"/>
+      <c r="F219" s="24"/>
+      <c r="G219" s="24"/>
+      <c r="H219" s="24"/>
+      <c r="I219" s="24"/>
+      <c r="J219" s="24"/>
+      <c r="K219" s="24"/>
+      <c r="L219" s="24"/>
+      <c r="M219" s="24"/>
+      <c r="N219" s="24"/>
+      <c r="O219" s="24"/>
+      <c r="P219" s="24"/>
+      <c r="Q219" s="24"/>
     </row>
     <row r="220" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -16325,25 +16329,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="26" t="s">
+      <c r="A236" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B236" s="26"/>
-      <c r="C236" s="26"/>
-      <c r="D236" s="26"/>
-      <c r="E236" s="26"/>
-      <c r="F236" s="26"/>
-      <c r="G236" s="26"/>
-      <c r="H236" s="26"/>
-      <c r="I236" s="26"/>
-      <c r="J236" s="26"/>
-      <c r="K236" s="26"/>
-      <c r="L236" s="26"/>
-      <c r="M236" s="26"/>
-      <c r="N236" s="26"/>
-      <c r="O236" s="26"/>
-      <c r="P236" s="26"/>
-      <c r="Q236" s="26"/>
+      <c r="B236" s="24"/>
+      <c r="C236" s="24"/>
+      <c r="D236" s="24"/>
+      <c r="E236" s="24"/>
+      <c r="F236" s="24"/>
+      <c r="G236" s="24"/>
+      <c r="H236" s="24"/>
+      <c r="I236" s="24"/>
+      <c r="J236" s="24"/>
+      <c r="K236" s="24"/>
+      <c r="L236" s="24"/>
+      <c r="M236" s="24"/>
+      <c r="N236" s="24"/>
+      <c r="O236" s="24"/>
+      <c r="P236" s="24"/>
+      <c r="Q236" s="24"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -16873,25 +16877,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="26" t="s">
+      <c r="A254" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="B254" s="26"/>
-      <c r="C254" s="26"/>
-      <c r="D254" s="26"/>
-      <c r="E254" s="26"/>
-      <c r="F254" s="26"/>
-      <c r="G254" s="26"/>
-      <c r="H254" s="26"/>
-      <c r="I254" s="26"/>
-      <c r="J254" s="26"/>
-      <c r="K254" s="26"/>
-      <c r="L254" s="26"/>
-      <c r="M254" s="26"/>
-      <c r="N254" s="26"/>
-      <c r="O254" s="26"/>
-      <c r="P254" s="26"/>
-      <c r="Q254" s="26"/>
+      <c r="B254" s="24"/>
+      <c r="C254" s="24"/>
+      <c r="D254" s="24"/>
+      <c r="E254" s="24"/>
+      <c r="F254" s="24"/>
+      <c r="G254" s="24"/>
+      <c r="H254" s="24"/>
+      <c r="I254" s="24"/>
+      <c r="J254" s="24"/>
+      <c r="K254" s="24"/>
+      <c r="L254" s="24"/>
+      <c r="M254" s="24"/>
+      <c r="N254" s="24"/>
+      <c r="O254" s="24"/>
+      <c r="P254" s="24"/>
+      <c r="Q254" s="24"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -17451,25 +17455,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="26" t="s">
+      <c r="A273" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="B273" s="26"/>
-      <c r="C273" s="26"/>
-      <c r="D273" s="26"/>
-      <c r="E273" s="26"/>
-      <c r="F273" s="26"/>
-      <c r="G273" s="26"/>
-      <c r="H273" s="26"/>
-      <c r="I273" s="26"/>
-      <c r="J273" s="26"/>
-      <c r="K273" s="26"/>
-      <c r="L273" s="26"/>
-      <c r="M273" s="26"/>
-      <c r="N273" s="26"/>
-      <c r="O273" s="26"/>
-      <c r="P273" s="26"/>
-      <c r="Q273" s="26"/>
+      <c r="B273" s="24"/>
+      <c r="C273" s="24"/>
+      <c r="D273" s="24"/>
+      <c r="E273" s="24"/>
+      <c r="F273" s="24"/>
+      <c r="G273" s="24"/>
+      <c r="H273" s="24"/>
+      <c r="I273" s="24"/>
+      <c r="J273" s="24"/>
+      <c r="K273" s="24"/>
+      <c r="L273" s="24"/>
+      <c r="M273" s="24"/>
+      <c r="N273" s="24"/>
+      <c r="O273" s="24"/>
+      <c r="P273" s="24"/>
+      <c r="Q273" s="24"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -18029,25 +18033,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="26" t="s">
+      <c r="A292" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="B292" s="26"/>
-      <c r="C292" s="26"/>
-      <c r="D292" s="26"/>
-      <c r="E292" s="26"/>
-      <c r="F292" s="26"/>
-      <c r="G292" s="26"/>
-      <c r="H292" s="26"/>
-      <c r="I292" s="26"/>
-      <c r="J292" s="26"/>
-      <c r="K292" s="26"/>
-      <c r="L292" s="26"/>
-      <c r="M292" s="26"/>
-      <c r="N292" s="26"/>
-      <c r="O292" s="26"/>
-      <c r="P292" s="26"/>
-      <c r="Q292" s="26"/>
+      <c r="B292" s="24"/>
+      <c r="C292" s="24"/>
+      <c r="D292" s="24"/>
+      <c r="E292" s="24"/>
+      <c r="F292" s="24"/>
+      <c r="G292" s="24"/>
+      <c r="H292" s="24"/>
+      <c r="I292" s="24"/>
+      <c r="J292" s="24"/>
+      <c r="K292" s="24"/>
+      <c r="L292" s="24"/>
+      <c r="M292" s="24"/>
+      <c r="N292" s="24"/>
+      <c r="O292" s="24"/>
+      <c r="P292" s="24"/>
+      <c r="Q292" s="24"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -18607,25 +18611,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="26" t="s">
+      <c r="A311" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="B311" s="26"/>
-      <c r="C311" s="26"/>
-      <c r="D311" s="26"/>
-      <c r="E311" s="26"/>
-      <c r="F311" s="26"/>
-      <c r="G311" s="26"/>
-      <c r="H311" s="26"/>
-      <c r="I311" s="26"/>
-      <c r="J311" s="26"/>
-      <c r="K311" s="26"/>
-      <c r="L311" s="26"/>
-      <c r="M311" s="26"/>
-      <c r="N311" s="26"/>
-      <c r="O311" s="26"/>
-      <c r="P311" s="26"/>
-      <c r="Q311" s="26"/>
+      <c r="B311" s="24"/>
+      <c r="C311" s="24"/>
+      <c r="D311" s="24"/>
+      <c r="E311" s="24"/>
+      <c r="F311" s="24"/>
+      <c r="G311" s="24"/>
+      <c r="H311" s="24"/>
+      <c r="I311" s="24"/>
+      <c r="J311" s="24"/>
+      <c r="K311" s="24"/>
+      <c r="L311" s="24"/>
+      <c r="M311" s="24"/>
+      <c r="N311" s="24"/>
+      <c r="O311" s="24"/>
+      <c r="P311" s="24"/>
+      <c r="Q311" s="24"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -19186,26 +19190,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A23:Q23"/>
+    <mergeCell ref="A42:Q42"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="A132:Q132"/>
+    <mergeCell ref="A149:Q149"/>
+    <mergeCell ref="A167:Q167"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A219:Q219"/>
     <mergeCell ref="A236:Q236"/>
     <mergeCell ref="A254:Q254"/>
     <mergeCell ref="A273:Q273"/>
     <mergeCell ref="A292:Q292"/>
     <mergeCell ref="A311:Q311"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A167:Q167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="A23:Q23"/>
-    <mergeCell ref="A42:Q42"/>
   </mergeCells>
   <dataValidations count="268">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or SEA" promptTitle="ATS Pick" prompt="Pick NE or SEA" sqref="F6:Q6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -37581,7 +37585,7 @@
       </c>
       <c r="G3">
         <f>Helper!G2</f>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H3">
         <f>Helper!H2</f>
@@ -37589,11 +37593,11 @@
       </c>
       <c r="I3">
         <f>Helper!I2</f>
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J3">
         <f>Helper!J2</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
         <f>MAX(Helper!C2:H2)</f>
@@ -37626,7 +37630,7 @@
       </c>
       <c r="G4">
         <f>Helper!G3</f>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H4">
         <f>Helper!H3</f>
@@ -37634,15 +37638,15 @@
       </c>
       <c r="I4">
         <f>Helper!I3</f>
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J4">
         <f>Helper!J3</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4">
         <f>MAX(Helper!C3:H3)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37761,7 +37765,7 @@
       </c>
       <c r="G7">
         <f>Helper!G6</f>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H7">
         <f>Helper!H6</f>
@@ -37769,11 +37773,11 @@
       </c>
       <c r="I7">
         <f>Helper!I6</f>
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J7">
         <f>Helper!J6</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7">
         <f>MAX(Helper!C6:H6)</f>
@@ -37806,7 +37810,7 @@
       </c>
       <c r="G8">
         <f>Helper!G7</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H8">
         <f>Helper!H7</f>
@@ -37814,15 +37818,15 @@
       </c>
       <c r="I8">
         <f>Helper!I7</f>
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J8">
         <f>Helper!J7</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8">
         <f>MAX(Helper!C7:H7)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37851,7 +37855,7 @@
       </c>
       <c r="G9">
         <f>Helper!G8</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H9">
         <f>Helper!H8</f>
@@ -37859,15 +37863,15 @@
       </c>
       <c r="I9">
         <f>Helper!I8</f>
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J9">
         <f>Helper!J8</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9">
         <f>MAX(Helper!C8:H8)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37896,7 +37900,7 @@
       </c>
       <c r="G10">
         <f>Helper!G9</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H10">
         <f>Helper!H9</f>
@@ -37904,15 +37908,15 @@
       </c>
       <c r="I10">
         <f>Helper!I9</f>
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J10">
         <f>Helper!J9</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <f>MAX(Helper!C9:H9)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39408,7 +39412,7 @@
       </c>
       <c r="C57">
         <f>Helper!I2</f>
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D57">
         <f>Helper!R2</f>
@@ -39420,11 +39424,11 @@
       </c>
       <c r="F57">
         <f>Helper!AE2</f>
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G57">
         <f>Helper!K2</f>
-        <v>57.000100000000003</v>
+        <v>63.000100000000003</v>
       </c>
       <c r="H57">
         <f>Helper!T2</f>
@@ -39441,7 +39445,7 @@
       </c>
       <c r="C58">
         <f>Helper!I3</f>
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D58">
         <f>Helper!R3</f>
@@ -39453,11 +39457,11 @@
       </c>
       <c r="F58">
         <f>Helper!AE3</f>
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G58">
         <f>Helper!K3</f>
-        <v>57.0002</v>
+        <v>63.0002</v>
       </c>
       <c r="H58">
         <f>Helper!T3</f>
@@ -39540,7 +39544,7 @@
       </c>
       <c r="C61">
         <f>Helper!I6</f>
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D61">
         <f>Helper!R6</f>
@@ -39552,11 +39556,11 @@
       </c>
       <c r="F61">
         <f>Helper!AE6</f>
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G61">
         <f>Helper!K6</f>
-        <v>52.000500000000002</v>
+        <v>58.000500000000002</v>
       </c>
       <c r="H61">
         <f>Helper!T6</f>
@@ -39573,7 +39577,7 @@
       </c>
       <c r="C62">
         <f>Helper!I7</f>
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D62">
         <f>Helper!R7</f>
@@ -39585,11 +39589,11 @@
       </c>
       <c r="F62">
         <f>Helper!AE7</f>
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G62">
         <f>Helper!K7</f>
-        <v>50.000599999999999</v>
+        <v>56.000599999999999</v>
       </c>
       <c r="H62">
         <f>Helper!T7</f>
@@ -39606,7 +39610,7 @@
       </c>
       <c r="C63">
         <f>Helper!I8</f>
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D63">
         <f>Helper!R8</f>
@@ -39618,11 +39622,11 @@
       </c>
       <c r="F63">
         <f>Helper!AE8</f>
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G63">
         <f>Helper!K8</f>
-        <v>40.000700000000002</v>
+        <v>46.000700000000002</v>
       </c>
       <c r="H63">
         <f>Helper!T8</f>
@@ -39639,7 +39643,7 @@
       </c>
       <c r="C64">
         <f>Helper!I9</f>
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D64">
         <f>Helper!R9</f>
@@ -39651,11 +39655,11 @@
       </c>
       <c r="F64">
         <f>Helper!AE9</f>
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G64">
         <f>Helper!K9</f>
-        <v>37.000799999999998</v>
+        <v>43.000799999999998</v>
       </c>
       <c r="H64">
         <f>Helper!T9</f>
@@ -40029,7 +40033,7 @@
       </c>
       <c r="C13">
         <f>INDEX(I$40:I$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
         <v>263</v>
@@ -40505,7 +40509,7 @@
       </c>
       <c r="I40">
         <f>Helper!AE2</f>
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J40" t="b">
         <f t="shared" ref="J40:J51" si="1">OR(H40=$E$5,H40=$E$6,H40=$E$7,H40=$E$8,H40=$E$9)</f>
@@ -40513,7 +40517,7 @@
       </c>
       <c r="K40">
         <f>IF(J40,-1,I40+0.00001)</f>
-        <v>57.000010000000003</v>
+        <v>63.000010000000003</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40523,7 +40527,7 @@
       </c>
       <c r="I41">
         <f>Helper!AE3</f>
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J41" t="b">
         <f t="shared" si="1"/>
@@ -40577,7 +40581,7 @@
       </c>
       <c r="I44">
         <f>Helper!AE6</f>
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J44" t="b">
         <f t="shared" si="1"/>
@@ -40585,7 +40589,7 @@
       </c>
       <c r="K44">
         <f>IF(J44,-1,I44+0.00005)</f>
-        <v>52.000050000000002</v>
+        <v>58.000050000000002</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40595,7 +40599,7 @@
       </c>
       <c r="I45">
         <f>Helper!AE7</f>
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J45" t="b">
         <f t="shared" si="1"/>
@@ -40603,7 +40607,7 @@
       </c>
       <c r="K45">
         <f>IF(J45,-1,I45+0.00006)</f>
-        <v>50.000059999999998</v>
+        <v>56.000059999999998</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40613,7 +40617,7 @@
       </c>
       <c r="I46">
         <f>Helper!AE8</f>
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J46" t="b">
         <f t="shared" si="1"/>
@@ -40621,7 +40625,7 @@
       </c>
       <c r="K46">
         <f>IF(J46,-1,I46+0.00007)</f>
-        <v>40.000070000000001</v>
+        <v>46.000070000000001</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40631,7 +40635,7 @@
       </c>
       <c r="I47">
         <f>Helper!AE9</f>
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J47" t="b">
         <f t="shared" si="1"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1049" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{645F2539-8A24-413C-9B72-3A9AB5D00601}"/>
+  <xr:revisionPtr revIDLastSave="1235" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C564DB2-2A58-4BAF-9FA9-2BD664CF96C2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="857" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29400" yWindow="-120" windowWidth="28320" windowHeight="16440" tabRatio="911" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4126" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4266" uniqueCount="346">
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -1377,13 +1377,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1665,12 +1665,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -2865,11 +2865,11 @@
       </c>
       <c r="H2">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H81,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G81,0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I13" si="0">SUM(C2:H2)</f>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J2">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F6="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F21="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F36="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F51="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F66="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F81="W"),1,0)</f>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="K2">
         <f>I2+0.0001</f>
-        <v>63.000100000000003</v>
+        <v>68.000100000000003</v>
       </c>
       <c r="L2">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H6,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G6,0)</f>
@@ -2957,11 +2957,11 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE13" si="2">I2+R2+AC2</f>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="AF2">
         <f>AE2+0.0001</f>
-        <v>63.000100000000003</v>
+        <v>68.000100000000003</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2994,11 +2994,11 @@
       </c>
       <c r="H3">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H82,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G82,0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I3">
         <f t="shared" si="0"/>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J3">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F7="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F22="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F37="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F52="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F67="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F82="W"),1,0)</f>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="K3">
         <f>I3+0.0002</f>
-        <v>63.0002</v>
+        <v>68.000200000000007</v>
       </c>
       <c r="L3">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H7,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G7,0)</f>
@@ -3086,11 +3086,11 @@
       </c>
       <c r="AE3">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="AF3">
         <f>AE3+0.0002</f>
-        <v>63.0002</v>
+        <v>68.000200000000007</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3123,11 +3123,11 @@
       </c>
       <c r="H4">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H83,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G83,0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="J4">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F8="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F23="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F38="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F53="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F68="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F83="W"),1,0)</f>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="K4">
         <f>I4+0.0003</f>
-        <v>54.000300000000003</v>
+        <v>61.000300000000003</v>
       </c>
       <c r="L4">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H8,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G8,0)</f>
@@ -3215,11 +3215,11 @@
       </c>
       <c r="AE4">
         <f t="shared" si="2"/>
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="AF4">
         <f>AE4+0.0003</f>
-        <v>54.000300000000003</v>
+        <v>61.000300000000003</v>
       </c>
     </row>
     <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3381,11 +3381,11 @@
       </c>
       <c r="H6">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H85,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G85,0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="J6">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F10="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F25="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F40="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F55="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F70="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F85="W"),1,0)</f>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="K6">
         <f>I6+0.0005</f>
-        <v>58.000500000000002</v>
+        <v>65.000500000000002</v>
       </c>
       <c r="L6">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H10,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G10,0)</f>
@@ -3473,11 +3473,11 @@
       </c>
       <c r="AE6">
         <f t="shared" si="2"/>
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="AF6">
         <f>AE6+0.0005</f>
-        <v>58.000500000000002</v>
+        <v>65.000500000000002</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3510,11 +3510,11 @@
       </c>
       <c r="H7">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H86,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G86,0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J7">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F11="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F26="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F41="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F56="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F71="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F86="W"),1,0)</f>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="K7">
         <f>I7+0.0006</f>
-        <v>56.000599999999999</v>
+        <v>60.000599999999999</v>
       </c>
       <c r="L7">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H11,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G11,0)</f>
@@ -3602,11 +3602,11 @@
       </c>
       <c r="AE7">
         <f t="shared" si="2"/>
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="AF7">
         <f>AE7+0.0006</f>
-        <v>56.000599999999999</v>
+        <v>60.000599999999999</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3639,11 +3639,11 @@
       </c>
       <c r="H8">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H87,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G87,0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="J8">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F12="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F27="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F42="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F57="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F72="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F87="W"),1,0)</f>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="K8">
         <f>I8+0.0007</f>
-        <v>46.000700000000002</v>
+        <v>53.000700000000002</v>
       </c>
       <c r="L8">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H12,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G12,0)</f>
@@ -3731,11 +3731,11 @@
       </c>
       <c r="AE8">
         <f t="shared" si="2"/>
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="AF8">
         <f>AE8+0.0007</f>
-        <v>46.000700000000002</v>
+        <v>53.000700000000002</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3768,11 +3768,11 @@
       </c>
       <c r="H9">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H88,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G88,0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J9">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F13="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F28="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F43="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F58="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F73="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F88="W"),1,0)</f>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="K9">
         <f>I9+0.0008</f>
-        <v>43.000799999999998</v>
+        <v>50.000799999999998</v>
       </c>
       <c r="L9">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H13,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G13,0)</f>
@@ -3860,11 +3860,11 @@
       </c>
       <c r="AE9">
         <f t="shared" si="2"/>
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="AF9">
         <f>AE9+0.0008</f>
-        <v>43.000799999999998</v>
+        <v>50.000799999999998</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3897,11 +3897,11 @@
       </c>
       <c r="H10">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H89,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G89,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I10">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J10">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F14="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F29="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F44="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F59="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F74="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F89="W"),1,0)</f>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="K10">
         <f>I10+0.0009</f>
-        <v>43.000900000000001</v>
+        <v>49.000900000000001</v>
       </c>
       <c r="L10">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H14,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G14,0)</f>
@@ -3989,11 +3989,11 @@
       </c>
       <c r="AE10">
         <f t="shared" si="2"/>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="AF10">
         <f>AE10+0.0009</f>
-        <v>43.000900000000001</v>
+        <v>49.000900000000001</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4026,11 +4026,11 @@
       </c>
       <c r="H11">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H90,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G90,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <f t="shared" si="0"/>
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="J11">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F15="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F30="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F45="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F60="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F75="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F90="W"),1,0)</f>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="K11">
         <f>I11+0.001</f>
-        <v>56.000999999999998</v>
+        <v>62.000999999999998</v>
       </c>
       <c r="L11">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H15,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G15,0)</f>
@@ -4118,11 +4118,11 @@
       </c>
       <c r="AE11">
         <f t="shared" si="2"/>
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="AF11">
         <f>AE11+0.001</f>
-        <v>56.000999999999998</v>
+        <v>62.000999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4155,11 +4155,11 @@
       </c>
       <c r="H12">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H91,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G91,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J12">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F16="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F31="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F46="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F61="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F76="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F91="W"),1,0)</f>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="K12">
         <f>I12+0.0011</f>
-        <v>48.001100000000001</v>
+        <v>54.001100000000001</v>
       </c>
       <c r="L12">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H16,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G16,0)</f>
@@ -4247,11 +4247,11 @@
       </c>
       <c r="AE12">
         <f t="shared" si="2"/>
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="AF12">
         <f>AE12+0.0011</f>
-        <v>48.001100000000001</v>
+        <v>54.001100000000001</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4284,11 +4284,11 @@
       </c>
       <c r="H13">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H92,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G92,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J13">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F17="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F32="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F47="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F62="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F77="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F92="W"),1,0)</f>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="K13">
         <f>I13+0.0012</f>
-        <v>42.001199999999997</v>
+        <v>48.001199999999997</v>
       </c>
       <c r="L13">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H17,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G17,0)</f>
@@ -4376,11 +4376,11 @@
       </c>
       <c r="AE13">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AF13">
         <f>AE13+0.0012</f>
-        <v>42.001199999999997</v>
+        <v>48.001199999999997</v>
       </c>
     </row>
   </sheetData>
@@ -4402,14 +4402,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -5354,14 +5354,14 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="22" t="s">
+      <c r="A56" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="22"/>
-      <c r="C56" s="22"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
@@ -6306,14 +6306,14 @@
       </c>
     </row>
     <row r="111" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="22" t="s">
+      <c r="A111" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B111" s="22"/>
-      <c r="C111" s="22"/>
-      <c r="D111" s="22"/>
-      <c r="E111" s="22"/>
-      <c r="F111" s="22"/>
+      <c r="B111" s="23"/>
+      <c r="C111" s="23"/>
+      <c r="D111" s="23"/>
+      <c r="E111" s="23"/>
+      <c r="F111" s="23"/>
     </row>
     <row r="112" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
@@ -7285,67 +7285,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="24"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8313,25 +8313,25 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="24"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -9299,25 +9299,25 @@
       </c>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+      <c r="A42" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="24"/>
-      <c r="K42" s="24"/>
-      <c r="L42" s="24"/>
-      <c r="M42" s="24"/>
-      <c r="N42" s="24"/>
-      <c r="O42" s="24"/>
-      <c r="P42" s="24"/>
-      <c r="Q42" s="24"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="26"/>
+      <c r="Q42" s="26"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -10247,25 +10247,25 @@
       </c>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="24" t="s">
+      <c r="A61" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="24"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="24"/>
-      <c r="J61" s="24"/>
-      <c r="K61" s="24"/>
-      <c r="L61" s="24"/>
-      <c r="M61" s="24"/>
-      <c r="N61" s="24"/>
-      <c r="O61" s="24"/>
-      <c r="P61" s="24"/>
-      <c r="Q61" s="24"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="26"/>
+      <c r="J61" s="26"/>
+      <c r="K61" s="26"/>
+      <c r="L61" s="26"/>
+      <c r="M61" s="26"/>
+      <c r="N61" s="26"/>
+      <c r="O61" s="26"/>
+      <c r="P61" s="26"/>
+      <c r="Q61" s="26"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -11233,25 +11233,25 @@
       </c>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="24" t="s">
+      <c r="A80" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="24"/>
-      <c r="C80" s="24"/>
-      <c r="D80" s="24"/>
-      <c r="E80" s="24"/>
-      <c r="F80" s="24"/>
-      <c r="G80" s="24"/>
-      <c r="H80" s="24"/>
-      <c r="I80" s="24"/>
-      <c r="J80" s="24"/>
-      <c r="K80" s="24"/>
-      <c r="L80" s="24"/>
-      <c r="M80" s="24"/>
-      <c r="N80" s="24"/>
-      <c r="O80" s="24"/>
-      <c r="P80" s="24"/>
-      <c r="Q80" s="24"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
+      <c r="I80" s="26"/>
+      <c r="J80" s="26"/>
+      <c r="K80" s="26"/>
+      <c r="L80" s="26"/>
+      <c r="M80" s="26"/>
+      <c r="N80" s="26"/>
+      <c r="O80" s="26"/>
+      <c r="P80" s="26"/>
+      <c r="Q80" s="26"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -12125,25 +12125,25 @@
       </c>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="24" t="s">
+      <c r="A98" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="24"/>
-      <c r="C98" s="24"/>
-      <c r="D98" s="24"/>
-      <c r="E98" s="24"/>
-      <c r="F98" s="24"/>
-      <c r="G98" s="24"/>
-      <c r="H98" s="24"/>
-      <c r="I98" s="24"/>
-      <c r="J98" s="24"/>
-      <c r="K98" s="24"/>
-      <c r="L98" s="24"/>
-      <c r="M98" s="24"/>
-      <c r="N98" s="24"/>
-      <c r="O98" s="24"/>
-      <c r="P98" s="24"/>
-      <c r="Q98" s="24"/>
+      <c r="B98" s="26"/>
+      <c r="C98" s="26"/>
+      <c r="D98" s="26"/>
+      <c r="E98" s="26"/>
+      <c r="F98" s="26"/>
+      <c r="G98" s="26"/>
+      <c r="H98" s="26"/>
+      <c r="I98" s="26"/>
+      <c r="J98" s="26"/>
+      <c r="K98" s="26"/>
+      <c r="L98" s="26"/>
+      <c r="M98" s="26"/>
+      <c r="N98" s="26"/>
+      <c r="O98" s="26"/>
+      <c r="P98" s="26"/>
+      <c r="Q98" s="26"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -12213,18 +12213,34 @@
       </c>
       <c r="E100" s="9" t="str">
         <f>'NFL Schedule'!J97</f>
-        <v/>
-      </c>
-      <c r="F100" s="10"/>
-      <c r="G100" s="10"/>
-      <c r="H100" s="10"/>
+        <v>DEN</v>
+      </c>
+      <c r="F100" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="G100" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H100" s="10" t="s">
+        <v>58</v>
+      </c>
       <c r="I100" s="10"/>
       <c r="J100" s="10"/>
-      <c r="K100" s="10"/>
-      <c r="L100" s="10"/>
-      <c r="M100" s="10"/>
-      <c r="N100" s="10"/>
-      <c r="O100" s="10"/>
+      <c r="K100" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="L100" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="M100" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="N100" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O100" s="10" t="s">
+        <v>58</v>
+      </c>
       <c r="P100" s="10"/>
       <c r="Q100" s="10"/>
     </row>
@@ -12243,20 +12259,42 @@
       </c>
       <c r="E101" s="9" t="str">
         <f>'NFL Schedule'!J98</f>
-        <v/>
-      </c>
-      <c r="F101" s="10"/>
-      <c r="G101" s="10"/>
-      <c r="H101" s="10"/>
+        <v>HOU</v>
+      </c>
+      <c r="F101" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G101" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H101" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I101" s="10"/>
-      <c r="J101" s="10"/>
-      <c r="K101" s="10"/>
-      <c r="L101" s="10"/>
-      <c r="M101" s="10"/>
-      <c r="N101" s="10"/>
-      <c r="O101" s="10"/>
-      <c r="P101" s="10"/>
-      <c r="Q101" s="10"/>
+      <c r="J101" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="K101" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="L101" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="M101" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="N101" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="O101" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="P101" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q101" s="10" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="102" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="7">
@@ -12273,20 +12311,42 @@
       </c>
       <c r="E102" s="9" t="str">
         <f>'NFL Schedule'!J99</f>
-        <v/>
-      </c>
-      <c r="F102" s="10"/>
-      <c r="G102" s="10"/>
-      <c r="H102" s="10"/>
+        <v>CHI</v>
+      </c>
+      <c r="F102" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G102" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H102" s="10" t="s">
+        <v>61</v>
+      </c>
       <c r="I102" s="10"/>
-      <c r="J102" s="10"/>
-      <c r="K102" s="10"/>
-      <c r="L102" s="10"/>
-      <c r="M102" s="10"/>
-      <c r="N102" s="10"/>
-      <c r="O102" s="10"/>
-      <c r="P102" s="10"/>
-      <c r="Q102" s="10"/>
+      <c r="J102" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K102" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="L102" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M102" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="N102" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="O102" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="P102" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q102" s="10" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="103" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="7">
@@ -12303,20 +12363,42 @@
       </c>
       <c r="E103" s="9" t="str">
         <f>'NFL Schedule'!J100</f>
-        <v/>
-      </c>
-      <c r="F103" s="10"/>
-      <c r="G103" s="10"/>
-      <c r="H103" s="10"/>
+        <v>CLE</v>
+      </c>
+      <c r="F103" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G103" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>71</v>
+      </c>
       <c r="I103" s="10"/>
-      <c r="J103" s="10"/>
-      <c r="K103" s="10"/>
-      <c r="L103" s="10"/>
-      <c r="M103" s="10"/>
-      <c r="N103" s="10"/>
-      <c r="O103" s="10"/>
-      <c r="P103" s="10"/>
-      <c r="Q103" s="10"/>
+      <c r="J103" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="K103" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="L103" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="M103" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="N103" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O103" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="P103" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q103" s="10" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="104" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="7">
@@ -12333,20 +12415,42 @@
       </c>
       <c r="E104" s="9" t="str">
         <f>'NFL Schedule'!J101</f>
-        <v/>
-      </c>
-      <c r="F104" s="10"/>
-      <c r="G104" s="10"/>
-      <c r="H104" s="10"/>
+        <v>TEN</v>
+      </c>
+      <c r="F104" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G104" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H104" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="I104" s="10"/>
-      <c r="J104" s="10"/>
-      <c r="K104" s="10"/>
-      <c r="L104" s="10"/>
-      <c r="M104" s="10"/>
-      <c r="N104" s="10"/>
-      <c r="O104" s="10"/>
-      <c r="P104" s="10"/>
-      <c r="Q104" s="10"/>
+      <c r="J104" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K104" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="L104" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="M104" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="N104" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="O104" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="P104" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q104" s="10" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="105" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="7">
@@ -12363,20 +12467,42 @@
       </c>
       <c r="E105" s="9" t="str">
         <f>'NFL Schedule'!J102</f>
-        <v/>
-      </c>
-      <c r="F105" s="10"/>
-      <c r="G105" s="10"/>
-      <c r="H105" s="10"/>
+        <v>NYJ</v>
+      </c>
+      <c r="F105" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G105" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H105" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="I105" s="10"/>
-      <c r="J105" s="10"/>
-      <c r="K105" s="10"/>
-      <c r="L105" s="10"/>
-      <c r="M105" s="10"/>
-      <c r="N105" s="10"/>
-      <c r="O105" s="10"/>
-      <c r="P105" s="10"/>
-      <c r="Q105" s="10"/>
+      <c r="J105" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="K105" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="L105" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="M105" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N105" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="O105" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P105" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q105" s="10" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="106" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="7">
@@ -12393,20 +12519,42 @@
       </c>
       <c r="E106" s="9" t="str">
         <f>'NFL Schedule'!J103</f>
-        <v/>
-      </c>
-      <c r="F106" s="10"/>
-      <c r="G106" s="10"/>
-      <c r="H106" s="10"/>
+        <v>NO</v>
+      </c>
+      <c r="F106" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="G106" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H106" s="10" t="s">
+        <v>86</v>
+      </c>
       <c r="I106" s="10"/>
-      <c r="J106" s="10"/>
-      <c r="K106" s="10"/>
-      <c r="L106" s="10"/>
-      <c r="M106" s="10"/>
-      <c r="N106" s="10"/>
-      <c r="O106" s="10"/>
-      <c r="P106" s="10"/>
-      <c r="Q106" s="10"/>
+      <c r="J106" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K106" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="L106" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="M106" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="N106" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="O106" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="P106" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q106" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="107" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="7">
@@ -12423,20 +12571,42 @@
       </c>
       <c r="E107" s="9" t="str">
         <f>'NFL Schedule'!J104</f>
-        <v/>
-      </c>
-      <c r="F107" s="10"/>
-      <c r="G107" s="10"/>
-      <c r="H107" s="10"/>
+        <v>CAR</v>
+      </c>
+      <c r="F107" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G107" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H107" s="10" t="s">
+        <v>62</v>
+      </c>
       <c r="I107" s="10"/>
-      <c r="J107" s="10"/>
-      <c r="K107" s="10"/>
-      <c r="L107" s="10"/>
-      <c r="M107" s="10"/>
-      <c r="N107" s="10"/>
-      <c r="O107" s="10"/>
-      <c r="P107" s="10"/>
-      <c r="Q107" s="10"/>
+      <c r="J107" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="K107" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="L107" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="M107" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="N107" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="O107" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="P107" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q107" s="10" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="108" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="7">
@@ -12453,20 +12623,42 @@
       </c>
       <c r="E108" s="9" t="str">
         <f>'NFL Schedule'!J105</f>
-        <v/>
-      </c>
-      <c r="F108" s="10"/>
-      <c r="G108" s="10"/>
-      <c r="H108" s="10"/>
+        <v>PIT</v>
+      </c>
+      <c r="F108" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G108" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H108" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="I108" s="10"/>
-      <c r="J108" s="10"/>
-      <c r="K108" s="10"/>
-      <c r="L108" s="10"/>
-      <c r="M108" s="10"/>
-      <c r="N108" s="10"/>
-      <c r="O108" s="10"/>
-      <c r="P108" s="10"/>
-      <c r="Q108" s="10"/>
+      <c r="J108" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K108" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="L108" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="M108" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="N108" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="O108" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="P108" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q108" s="10" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="109" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="7">
@@ -12479,31 +12671,53 @@
         <v>54</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E109" s="9" t="str">
         <f>'NFL Schedule'!J106</f>
-        <v/>
-      </c>
-      <c r="F109" s="10"/>
-      <c r="G109" s="10"/>
-      <c r="H109" s="10"/>
+        <v>ARI</v>
+      </c>
+      <c r="F109" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G109" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H109" s="10" t="s">
+        <v>77</v>
+      </c>
       <c r="I109" s="10"/>
-      <c r="J109" s="10"/>
-      <c r="K109" s="10"/>
-      <c r="L109" s="10"/>
-      <c r="M109" s="10"/>
-      <c r="N109" s="10"/>
-      <c r="O109" s="10"/>
-      <c r="P109" s="10"/>
-      <c r="Q109" s="10"/>
+      <c r="J109" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="K109" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="L109" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="M109" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="N109" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="O109" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="P109" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q109" s="10" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="110" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="7">
         <v>11</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="C110" s="8" t="s">
         <v>54</v>
@@ -12513,20 +12727,42 @@
       </c>
       <c r="E110" s="9" t="str">
         <f>'NFL Schedule'!J107</f>
-        <v/>
-      </c>
-      <c r="F110" s="10"/>
-      <c r="G110" s="10"/>
-      <c r="H110" s="10"/>
+        <v>KC</v>
+      </c>
+      <c r="F110" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G110" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="H110" s="10" t="s">
+        <v>60</v>
+      </c>
       <c r="I110" s="10"/>
-      <c r="J110" s="10"/>
-      <c r="K110" s="10"/>
-      <c r="L110" s="10"/>
-      <c r="M110" s="10"/>
-      <c r="N110" s="10"/>
-      <c r="O110" s="10"/>
-      <c r="P110" s="10"/>
-      <c r="Q110" s="10"/>
+      <c r="J110" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="K110" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="L110" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="M110" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="N110" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="O110" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="P110" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q110" s="10" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="111" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="7">
@@ -12543,20 +12779,42 @@
       </c>
       <c r="E111" s="9" t="str">
         <f>'NFL Schedule'!J108</f>
-        <v/>
-      </c>
-      <c r="F111" s="10"/>
-      <c r="G111" s="10"/>
-      <c r="H111" s="10"/>
+        <v>LV</v>
+      </c>
+      <c r="F111" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G111" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H111" s="10" t="s">
+        <v>67</v>
+      </c>
       <c r="I111" s="10"/>
-      <c r="J111" s="10"/>
-      <c r="K111" s="10"/>
-      <c r="L111" s="10"/>
-      <c r="M111" s="10"/>
-      <c r="N111" s="10"/>
-      <c r="O111" s="10"/>
-      <c r="P111" s="10"/>
-      <c r="Q111" s="10"/>
+      <c r="J111" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K111" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L111" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="M111" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="N111" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="O111" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="P111" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q111" s="10" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="112" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="7">
@@ -12573,20 +12831,42 @@
       </c>
       <c r="E112" s="9" t="str">
         <f>'NFL Schedule'!J109</f>
-        <v/>
-      </c>
-      <c r="F112" s="10"/>
-      <c r="G112" s="10"/>
-      <c r="H112" s="10"/>
+        <v>GB</v>
+      </c>
+      <c r="F112" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G112" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H112" s="10" t="s">
+        <v>81</v>
+      </c>
       <c r="I112" s="10"/>
-      <c r="J112" s="10"/>
-      <c r="K112" s="10"/>
-      <c r="L112" s="10"/>
-      <c r="M112" s="10"/>
-      <c r="N112" s="10"/>
-      <c r="O112" s="10"/>
-      <c r="P112" s="10"/>
-      <c r="Q112" s="10"/>
+      <c r="J112" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="K112" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="L112" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="M112" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="N112" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="O112" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="P112" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q112" s="10" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="113" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="7">
@@ -12643,25 +12923,25 @@
       <c r="Q114" s="14"/>
     </row>
     <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="24" t="s">
+      <c r="A115" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="24"/>
-      <c r="C115" s="24"/>
-      <c r="D115" s="24"/>
-      <c r="E115" s="24"/>
-      <c r="F115" s="24"/>
-      <c r="G115" s="24"/>
-      <c r="H115" s="24"/>
-      <c r="I115" s="24"/>
-      <c r="J115" s="24"/>
-      <c r="K115" s="24"/>
-      <c r="L115" s="24"/>
-      <c r="M115" s="24"/>
-      <c r="N115" s="24"/>
-      <c r="O115" s="24"/>
-      <c r="P115" s="24"/>
-      <c r="Q115" s="24"/>
+      <c r="B115" s="26"/>
+      <c r="C115" s="26"/>
+      <c r="D115" s="26"/>
+      <c r="E115" s="26"/>
+      <c r="F115" s="26"/>
+      <c r="G115" s="26"/>
+      <c r="H115" s="26"/>
+      <c r="I115" s="26"/>
+      <c r="J115" s="26"/>
+      <c r="K115" s="26"/>
+      <c r="L115" s="26"/>
+      <c r="M115" s="26"/>
+      <c r="N115" s="26"/>
+      <c r="O115" s="26"/>
+      <c r="P115" s="26"/>
+      <c r="Q115" s="26"/>
     </row>
     <row r="116" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -13161,25 +13441,25 @@
       <c r="Q131" s="14"/>
     </row>
     <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="24" t="s">
+      <c r="A132" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="B132" s="24"/>
-      <c r="C132" s="24"/>
-      <c r="D132" s="24"/>
-      <c r="E132" s="24"/>
-      <c r="F132" s="24"/>
-      <c r="G132" s="24"/>
-      <c r="H132" s="24"/>
-      <c r="I132" s="24"/>
-      <c r="J132" s="24"/>
-      <c r="K132" s="24"/>
-      <c r="L132" s="24"/>
-      <c r="M132" s="24"/>
-      <c r="N132" s="24"/>
-      <c r="O132" s="24"/>
-      <c r="P132" s="24"/>
-      <c r="Q132" s="24"/>
+      <c r="B132" s="26"/>
+      <c r="C132" s="26"/>
+      <c r="D132" s="26"/>
+      <c r="E132" s="26"/>
+      <c r="F132" s="26"/>
+      <c r="G132" s="26"/>
+      <c r="H132" s="26"/>
+      <c r="I132" s="26"/>
+      <c r="J132" s="26"/>
+      <c r="K132" s="26"/>
+      <c r="L132" s="26"/>
+      <c r="M132" s="26"/>
+      <c r="N132" s="26"/>
+      <c r="O132" s="26"/>
+      <c r="P132" s="26"/>
+      <c r="Q132" s="26"/>
     </row>
     <row r="133" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -13679,25 +13959,25 @@
       <c r="Q148" s="14"/>
     </row>
     <row r="149" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="24" t="s">
+      <c r="A149" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="B149" s="24"/>
-      <c r="C149" s="24"/>
-      <c r="D149" s="24"/>
-      <c r="E149" s="24"/>
-      <c r="F149" s="24"/>
-      <c r="G149" s="24"/>
-      <c r="H149" s="24"/>
-      <c r="I149" s="24"/>
-      <c r="J149" s="24"/>
-      <c r="K149" s="24"/>
-      <c r="L149" s="24"/>
-      <c r="M149" s="24"/>
-      <c r="N149" s="24"/>
-      <c r="O149" s="24"/>
-      <c r="P149" s="24"/>
-      <c r="Q149" s="24"/>
+      <c r="B149" s="26"/>
+      <c r="C149" s="26"/>
+      <c r="D149" s="26"/>
+      <c r="E149" s="26"/>
+      <c r="F149" s="26"/>
+      <c r="G149" s="26"/>
+      <c r="H149" s="26"/>
+      <c r="I149" s="26"/>
+      <c r="J149" s="26"/>
+      <c r="K149" s="26"/>
+      <c r="L149" s="26"/>
+      <c r="M149" s="26"/>
+      <c r="N149" s="26"/>
+      <c r="O149" s="26"/>
+      <c r="P149" s="26"/>
+      <c r="Q149" s="26"/>
     </row>
     <row r="150" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -14227,25 +14507,25 @@
       <c r="Q166" s="14"/>
     </row>
     <row r="167" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="24" t="s">
+      <c r="A167" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="B167" s="24"/>
-      <c r="C167" s="24"/>
-      <c r="D167" s="24"/>
-      <c r="E167" s="24"/>
-      <c r="F167" s="24"/>
-      <c r="G167" s="24"/>
-      <c r="H167" s="24"/>
-      <c r="I167" s="24"/>
-      <c r="J167" s="24"/>
-      <c r="K167" s="24"/>
-      <c r="L167" s="24"/>
-      <c r="M167" s="24"/>
-      <c r="N167" s="24"/>
-      <c r="O167" s="24"/>
-      <c r="P167" s="24"/>
-      <c r="Q167" s="24"/>
+      <c r="B167" s="26"/>
+      <c r="C167" s="26"/>
+      <c r="D167" s="26"/>
+      <c r="E167" s="26"/>
+      <c r="F167" s="26"/>
+      <c r="G167" s="26"/>
+      <c r="H167" s="26"/>
+      <c r="I167" s="26"/>
+      <c r="J167" s="26"/>
+      <c r="K167" s="26"/>
+      <c r="L167" s="26"/>
+      <c r="M167" s="26"/>
+      <c r="N167" s="26"/>
+      <c r="O167" s="26"/>
+      <c r="P167" s="26"/>
+      <c r="Q167" s="26"/>
     </row>
     <row r="168" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -14745,25 +15025,25 @@
       <c r="Q183" s="14"/>
     </row>
     <row r="184" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="24" t="s">
+      <c r="A184" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="B184" s="24"/>
-      <c r="C184" s="24"/>
-      <c r="D184" s="24"/>
-      <c r="E184" s="24"/>
-      <c r="F184" s="24"/>
-      <c r="G184" s="24"/>
-      <c r="H184" s="24"/>
-      <c r="I184" s="24"/>
-      <c r="J184" s="24"/>
-      <c r="K184" s="24"/>
-      <c r="L184" s="24"/>
-      <c r="M184" s="24"/>
-      <c r="N184" s="24"/>
-      <c r="O184" s="24"/>
-      <c r="P184" s="24"/>
-      <c r="Q184" s="24"/>
+      <c r="B184" s="26"/>
+      <c r="C184" s="26"/>
+      <c r="D184" s="26"/>
+      <c r="E184" s="26"/>
+      <c r="F184" s="26"/>
+      <c r="G184" s="26"/>
+      <c r="H184" s="26"/>
+      <c r="I184" s="26"/>
+      <c r="J184" s="26"/>
+      <c r="K184" s="26"/>
+      <c r="L184" s="26"/>
+      <c r="M184" s="26"/>
+      <c r="N184" s="26"/>
+      <c r="O184" s="26"/>
+      <c r="P184" s="26"/>
+      <c r="Q184" s="26"/>
     </row>
     <row r="185" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -15233,25 +15513,25 @@
       <c r="Q199" s="14"/>
     </row>
     <row r="200" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="24" t="s">
+      <c r="A200" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="B200" s="24"/>
-      <c r="C200" s="24"/>
-      <c r="D200" s="24"/>
-      <c r="E200" s="24"/>
-      <c r="F200" s="24"/>
-      <c r="G200" s="24"/>
-      <c r="H200" s="24"/>
-      <c r="I200" s="24"/>
-      <c r="J200" s="24"/>
-      <c r="K200" s="24"/>
-      <c r="L200" s="24"/>
-      <c r="M200" s="24"/>
-      <c r="N200" s="24"/>
-      <c r="O200" s="24"/>
-      <c r="P200" s="24"/>
-      <c r="Q200" s="24"/>
+      <c r="B200" s="26"/>
+      <c r="C200" s="26"/>
+      <c r="D200" s="26"/>
+      <c r="E200" s="26"/>
+      <c r="F200" s="26"/>
+      <c r="G200" s="26"/>
+      <c r="H200" s="26"/>
+      <c r="I200" s="26"/>
+      <c r="J200" s="26"/>
+      <c r="K200" s="26"/>
+      <c r="L200" s="26"/>
+      <c r="M200" s="26"/>
+      <c r="N200" s="26"/>
+      <c r="O200" s="26"/>
+      <c r="P200" s="26"/>
+      <c r="Q200" s="26"/>
     </row>
     <row r="201" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -15811,25 +16091,25 @@
       <c r="Q218" s="14"/>
     </row>
     <row r="219" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="24" t="s">
+      <c r="A219" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="B219" s="24"/>
-      <c r="C219" s="24"/>
-      <c r="D219" s="24"/>
-      <c r="E219" s="24"/>
-      <c r="F219" s="24"/>
-      <c r="G219" s="24"/>
-      <c r="H219" s="24"/>
-      <c r="I219" s="24"/>
-      <c r="J219" s="24"/>
-      <c r="K219" s="24"/>
-      <c r="L219" s="24"/>
-      <c r="M219" s="24"/>
-      <c r="N219" s="24"/>
-      <c r="O219" s="24"/>
-      <c r="P219" s="24"/>
-      <c r="Q219" s="24"/>
+      <c r="B219" s="26"/>
+      <c r="C219" s="26"/>
+      <c r="D219" s="26"/>
+      <c r="E219" s="26"/>
+      <c r="F219" s="26"/>
+      <c r="G219" s="26"/>
+      <c r="H219" s="26"/>
+      <c r="I219" s="26"/>
+      <c r="J219" s="26"/>
+      <c r="K219" s="26"/>
+      <c r="L219" s="26"/>
+      <c r="M219" s="26"/>
+      <c r="N219" s="26"/>
+      <c r="O219" s="26"/>
+      <c r="P219" s="26"/>
+      <c r="Q219" s="26"/>
     </row>
     <row r="220" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -16329,25 +16609,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="24" t="s">
+      <c r="A236" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="B236" s="24"/>
-      <c r="C236" s="24"/>
-      <c r="D236" s="24"/>
-      <c r="E236" s="24"/>
-      <c r="F236" s="24"/>
-      <c r="G236" s="24"/>
-      <c r="H236" s="24"/>
-      <c r="I236" s="24"/>
-      <c r="J236" s="24"/>
-      <c r="K236" s="24"/>
-      <c r="L236" s="24"/>
-      <c r="M236" s="24"/>
-      <c r="N236" s="24"/>
-      <c r="O236" s="24"/>
-      <c r="P236" s="24"/>
-      <c r="Q236" s="24"/>
+      <c r="B236" s="26"/>
+      <c r="C236" s="26"/>
+      <c r="D236" s="26"/>
+      <c r="E236" s="26"/>
+      <c r="F236" s="26"/>
+      <c r="G236" s="26"/>
+      <c r="H236" s="26"/>
+      <c r="I236" s="26"/>
+      <c r="J236" s="26"/>
+      <c r="K236" s="26"/>
+      <c r="L236" s="26"/>
+      <c r="M236" s="26"/>
+      <c r="N236" s="26"/>
+      <c r="O236" s="26"/>
+      <c r="P236" s="26"/>
+      <c r="Q236" s="26"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -16877,25 +17157,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="24" t="s">
+      <c r="A254" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="B254" s="24"/>
-      <c r="C254" s="24"/>
-      <c r="D254" s="24"/>
-      <c r="E254" s="24"/>
-      <c r="F254" s="24"/>
-      <c r="G254" s="24"/>
-      <c r="H254" s="24"/>
-      <c r="I254" s="24"/>
-      <c r="J254" s="24"/>
-      <c r="K254" s="24"/>
-      <c r="L254" s="24"/>
-      <c r="M254" s="24"/>
-      <c r="N254" s="24"/>
-      <c r="O254" s="24"/>
-      <c r="P254" s="24"/>
-      <c r="Q254" s="24"/>
+      <c r="B254" s="26"/>
+      <c r="C254" s="26"/>
+      <c r="D254" s="26"/>
+      <c r="E254" s="26"/>
+      <c r="F254" s="26"/>
+      <c r="G254" s="26"/>
+      <c r="H254" s="26"/>
+      <c r="I254" s="26"/>
+      <c r="J254" s="26"/>
+      <c r="K254" s="26"/>
+      <c r="L254" s="26"/>
+      <c r="M254" s="26"/>
+      <c r="N254" s="26"/>
+      <c r="O254" s="26"/>
+      <c r="P254" s="26"/>
+      <c r="Q254" s="26"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -17455,25 +17735,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="24" t="s">
+      <c r="A273" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="B273" s="24"/>
-      <c r="C273" s="24"/>
-      <c r="D273" s="24"/>
-      <c r="E273" s="24"/>
-      <c r="F273" s="24"/>
-      <c r="G273" s="24"/>
-      <c r="H273" s="24"/>
-      <c r="I273" s="24"/>
-      <c r="J273" s="24"/>
-      <c r="K273" s="24"/>
-      <c r="L273" s="24"/>
-      <c r="M273" s="24"/>
-      <c r="N273" s="24"/>
-      <c r="O273" s="24"/>
-      <c r="P273" s="24"/>
-      <c r="Q273" s="24"/>
+      <c r="B273" s="26"/>
+      <c r="C273" s="26"/>
+      <c r="D273" s="26"/>
+      <c r="E273" s="26"/>
+      <c r="F273" s="26"/>
+      <c r="G273" s="26"/>
+      <c r="H273" s="26"/>
+      <c r="I273" s="26"/>
+      <c r="J273" s="26"/>
+      <c r="K273" s="26"/>
+      <c r="L273" s="26"/>
+      <c r="M273" s="26"/>
+      <c r="N273" s="26"/>
+      <c r="O273" s="26"/>
+      <c r="P273" s="26"/>
+      <c r="Q273" s="26"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -18033,25 +18313,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="24" t="s">
+      <c r="A292" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="B292" s="24"/>
-      <c r="C292" s="24"/>
-      <c r="D292" s="24"/>
-      <c r="E292" s="24"/>
-      <c r="F292" s="24"/>
-      <c r="G292" s="24"/>
-      <c r="H292" s="24"/>
-      <c r="I292" s="24"/>
-      <c r="J292" s="24"/>
-      <c r="K292" s="24"/>
-      <c r="L292" s="24"/>
-      <c r="M292" s="24"/>
-      <c r="N292" s="24"/>
-      <c r="O292" s="24"/>
-      <c r="P292" s="24"/>
-      <c r="Q292" s="24"/>
+      <c r="B292" s="26"/>
+      <c r="C292" s="26"/>
+      <c r="D292" s="26"/>
+      <c r="E292" s="26"/>
+      <c r="F292" s="26"/>
+      <c r="G292" s="26"/>
+      <c r="H292" s="26"/>
+      <c r="I292" s="26"/>
+      <c r="J292" s="26"/>
+      <c r="K292" s="26"/>
+      <c r="L292" s="26"/>
+      <c r="M292" s="26"/>
+      <c r="N292" s="26"/>
+      <c r="O292" s="26"/>
+      <c r="P292" s="26"/>
+      <c r="Q292" s="26"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -18611,25 +18891,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="24" t="s">
+      <c r="A311" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="B311" s="24"/>
-      <c r="C311" s="24"/>
-      <c r="D311" s="24"/>
-      <c r="E311" s="24"/>
-      <c r="F311" s="24"/>
-      <c r="G311" s="24"/>
-      <c r="H311" s="24"/>
-      <c r="I311" s="24"/>
-      <c r="J311" s="24"/>
-      <c r="K311" s="24"/>
-      <c r="L311" s="24"/>
-      <c r="M311" s="24"/>
-      <c r="N311" s="24"/>
-      <c r="O311" s="24"/>
-      <c r="P311" s="24"/>
-      <c r="Q311" s="24"/>
+      <c r="B311" s="26"/>
+      <c r="C311" s="26"/>
+      <c r="D311" s="26"/>
+      <c r="E311" s="26"/>
+      <c r="F311" s="26"/>
+      <c r="G311" s="26"/>
+      <c r="H311" s="26"/>
+      <c r="I311" s="26"/>
+      <c r="J311" s="26"/>
+      <c r="K311" s="26"/>
+      <c r="L311" s="26"/>
+      <c r="M311" s="26"/>
+      <c r="N311" s="26"/>
+      <c r="O311" s="26"/>
+      <c r="P311" s="26"/>
+      <c r="Q311" s="26"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -19190,26 +19470,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A236:Q236"/>
+    <mergeCell ref="A254:Q254"/>
+    <mergeCell ref="A273:Q273"/>
+    <mergeCell ref="A292:Q292"/>
+    <mergeCell ref="A311:Q311"/>
+    <mergeCell ref="A149:Q149"/>
+    <mergeCell ref="A167:Q167"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A219:Q219"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="A132:Q132"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A4:Q4"/>
     <mergeCell ref="A23:Q23"/>
     <mergeCell ref="A42:Q42"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A167:Q167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A236:Q236"/>
-    <mergeCell ref="A254:Q254"/>
-    <mergeCell ref="A273:Q273"/>
-    <mergeCell ref="A292:Q292"/>
-    <mergeCell ref="A311:Q311"/>
   </mergeCells>
   <dataValidations count="268">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or SEA" promptTitle="ATS Pick" prompt="Pick NE or SEA" sqref="F6:Q6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -23264,16 +23544,25 @@
       <c r="D97" t="s">
         <v>58</v>
       </c>
+      <c r="E97">
+        <v>14</v>
+      </c>
       <c r="F97" t="s">
         <v>87</v>
       </c>
+      <c r="G97">
+        <v>17</v>
+      </c>
+      <c r="H97">
+        <v>-2.5</v>
+      </c>
       <c r="I97" t="str">
         <f t="shared" ref="I97:I110" si="10">IF(OR(E97="",G97=""),"",IF(E97&gt;G97,D97,IF(G97&gt;E97,F97,"TIE")))</f>
-        <v/>
+        <v>DEN</v>
       </c>
       <c r="J97" t="str">
         <f t="shared" ref="J97:J110" si="11">IF(OR(E97="",G97="",H97=""),"",IF(E97+H97&gt;G97,D97,IF(E97+H97&lt;G97,F97,"PUSH")))</f>
-        <v/>
+        <v>DEN</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23289,16 +23578,25 @@
       <c r="D98" t="s">
         <v>68</v>
       </c>
+      <c r="E98">
+        <v>34</v>
+      </c>
       <c r="F98" t="s">
         <v>72</v>
       </c>
+      <c r="G98">
+        <v>31</v>
+      </c>
+      <c r="H98">
+        <v>2.5</v>
+      </c>
       <c r="I98" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>HOU</v>
       </c>
       <c r="J98" t="str">
         <f t="shared" si="11"/>
-        <v/>
+        <v>HOU</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23314,16 +23612,25 @@
       <c r="D99" t="s">
         <v>61</v>
       </c>
+      <c r="E99">
+        <v>31</v>
+      </c>
       <c r="F99" t="s">
         <v>73</v>
       </c>
+      <c r="G99">
+        <v>23</v>
+      </c>
+      <c r="H99">
+        <v>-3.5</v>
+      </c>
       <c r="I99" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>CHI</v>
       </c>
       <c r="J99" t="str">
         <f t="shared" si="11"/>
-        <v/>
+        <v>CHI</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23339,16 +23646,25 @@
       <c r="D100" t="s">
         <v>69</v>
       </c>
+      <c r="E100">
+        <v>10</v>
+      </c>
       <c r="F100" t="s">
         <v>71</v>
       </c>
+      <c r="G100">
+        <v>13</v>
+      </c>
+      <c r="H100">
+        <v>-4.5</v>
+      </c>
       <c r="I100" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>CLE</v>
       </c>
       <c r="J100" t="str">
         <f t="shared" si="11"/>
-        <v/>
+        <v>CLE</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23364,16 +23680,25 @@
       <c r="D101" t="s">
         <v>76</v>
       </c>
+      <c r="E101">
+        <v>26</v>
+      </c>
       <c r="F101" t="s">
         <v>70</v>
       </c>
+      <c r="G101">
+        <v>20</v>
+      </c>
+      <c r="H101">
+        <v>6.5</v>
+      </c>
       <c r="I101" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>TEN</v>
       </c>
       <c r="J101" t="str">
         <f t="shared" si="11"/>
-        <v/>
+        <v>TEN</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23389,16 +23714,25 @@
       <c r="D102" t="s">
         <v>75</v>
       </c>
+      <c r="E102">
+        <v>19</v>
+      </c>
       <c r="F102" t="s">
         <v>57</v>
       </c>
+      <c r="G102">
+        <v>26</v>
+      </c>
+      <c r="H102">
+        <v>7.5</v>
+      </c>
       <c r="I102" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>NE</v>
       </c>
       <c r="J102" t="str">
         <f t="shared" si="11"/>
-        <v/>
+        <v>NYJ</v>
       </c>
     </row>
     <row r="103" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23414,16 +23748,25 @@
       <c r="D103" t="s">
         <v>65</v>
       </c>
+      <c r="E103">
+        <v>34</v>
+      </c>
       <c r="F103" t="s">
         <v>86</v>
       </c>
+      <c r="G103">
+        <v>27</v>
+      </c>
+      <c r="H103">
+        <v>1.5</v>
+      </c>
       <c r="I103" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>NO</v>
       </c>
       <c r="J103" t="str">
         <f t="shared" si="11"/>
-        <v/>
+        <v>NO</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23439,16 +23782,25 @@
       <c r="D104" t="s">
         <v>62</v>
       </c>
+      <c r="E104">
+        <v>25</v>
+      </c>
       <c r="F104" t="s">
         <v>84</v>
       </c>
+      <c r="G104">
+        <v>14</v>
+      </c>
+      <c r="H104">
+        <v>1.5</v>
+      </c>
       <c r="I104" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>CAR</v>
       </c>
       <c r="J104" t="str">
         <f t="shared" si="11"/>
-        <v/>
+        <v>CAR</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23464,16 +23816,25 @@
       <c r="D105" t="s">
         <v>74</v>
       </c>
+      <c r="E105">
+        <v>26</v>
+      </c>
       <c r="F105" t="s">
         <v>63</v>
       </c>
+      <c r="G105">
+        <v>19</v>
+      </c>
+      <c r="H105">
+        <v>-2.5</v>
+      </c>
       <c r="I105" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>PIT</v>
       </c>
       <c r="J105" t="str">
         <f t="shared" si="11"/>
-        <v/>
+        <v>PIT</v>
       </c>
     </row>
     <row r="106" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23489,16 +23850,25 @@
       <c r="D106" t="s">
         <v>77</v>
       </c>
+      <c r="E106">
+        <v>18</v>
+      </c>
       <c r="F106" t="s">
-        <v>78</v>
+        <v>60</v>
+      </c>
+      <c r="G106">
+        <v>16</v>
+      </c>
+      <c r="H106">
+        <v>13.5</v>
       </c>
       <c r="I106" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>ARI</v>
       </c>
       <c r="J106" t="str">
         <f t="shared" si="11"/>
-        <v/>
+        <v>ARI</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23512,18 +23882,27 @@
         <v>121</v>
       </c>
       <c r="D107" t="s">
-        <v>60</v>
+        <v>78</v>
+      </c>
+      <c r="E107">
+        <v>6</v>
       </c>
       <c r="F107" t="s">
         <v>88</v>
       </c>
+      <c r="G107">
+        <v>22</v>
+      </c>
+      <c r="H107">
+        <v>8.5</v>
+      </c>
       <c r="I107" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>KC</v>
       </c>
       <c r="J107" t="str">
         <f t="shared" si="11"/>
-        <v/>
+        <v>KC</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23539,16 +23918,25 @@
       <c r="D108" t="s">
         <v>67</v>
       </c>
+      <c r="E108">
+        <v>33</v>
+      </c>
       <c r="F108" t="s">
         <v>80</v>
       </c>
+      <c r="G108">
+        <v>30</v>
+      </c>
+      <c r="H108">
+        <v>-5.5</v>
+      </c>
       <c r="I108" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>BUF</v>
       </c>
       <c r="J108" t="str">
         <f t="shared" si="11"/>
-        <v/>
+        <v>LV</v>
       </c>
     </row>
     <row r="109" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23564,16 +23952,25 @@
       <c r="D109" t="s">
         <v>85</v>
       </c>
+      <c r="E109">
+        <v>13</v>
+      </c>
       <c r="F109" t="s">
         <v>81</v>
       </c>
+      <c r="G109">
+        <v>23</v>
+      </c>
+      <c r="H109">
+        <v>1.5</v>
+      </c>
       <c r="I109" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>GB</v>
       </c>
       <c r="J109" t="str">
         <f t="shared" si="11"/>
-        <v/>
+        <v>GB</v>
       </c>
     </row>
     <row r="110" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29011,17 +29408,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -31402,18 +31799,18 @@
       </c>
       <c r="C81" s="3">
         <f>SUMPRODUCT(('Picks Detail'!F100:F113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!F100:F113='Picks Detail'!E100:E113))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D81">
         <v>9</v>
       </c>
       <c r="E81">
         <f>IFERROR(INDEX(C$81:C$92,MATCH(9,A$81:A$92,0)),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F81" t="str">
         <f>IF(C81=0,"-",IF(C81&gt;E81,"W",IF(C81&lt;E81,"L",IF(AND('Picks Detail'!E114&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,A81)&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,D81)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A81)-'Picks Detail'!E114)&lt;ABS(INDEX('Picks Detail'!F114:Q114,1,D81)-'Picks Detail'!E114),"W",IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A81)-'Picks Detail'!E114)&gt;ABS(INDEX('Picks Detail'!F114:Q114,1,D81)-'Picks Detail'!E114),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G81">
         <f t="shared" ref="G81:G92" si="15">IF(F81="W",6,IF(F81="T",3,0))</f>
@@ -31421,11 +31818,11 @@
       </c>
       <c r="H81">
         <f t="shared" ref="H81:H92" si="16">IF(C81="",0,C81)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I81">
         <f t="shared" ref="I81:I92" si="17">G81+H81</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31438,18 +31835,18 @@
       </c>
       <c r="C82" s="3">
         <f>SUMPRODUCT(('Picks Detail'!G100:G113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!G100:G113='Picks Detail'!E100:E113))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D82">
         <v>10</v>
       </c>
       <c r="E82">
         <f>IFERROR(INDEX(C$81:C$92,MATCH(10,A$81:A$92,0)),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F82" t="str">
         <f>IF(C82=0,"-",IF(C82&gt;E82,"W",IF(C82&lt;E82,"L",IF(AND('Picks Detail'!E114&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,A82)&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,D82)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A82)-'Picks Detail'!E114)&lt;ABS(INDEX('Picks Detail'!F114:Q114,1,D82)-'Picks Detail'!E114),"W",IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A82)-'Picks Detail'!E114)&gt;ABS(INDEX('Picks Detail'!F114:Q114,1,D82)-'Picks Detail'!E114),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G82">
         <f t="shared" si="15"/>
@@ -31457,11 +31854,11 @@
       </c>
       <c r="H82">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I82">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31474,30 +31871,30 @@
       </c>
       <c r="C83" s="3">
         <f>SUMPRODUCT(('Picks Detail'!H100:H113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!H100:H113='Picks Detail'!E100:E113))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D83">
         <v>7</v>
       </c>
       <c r="E83">
         <f>IFERROR(INDEX(C$81:C$92,MATCH(7,A$81:A$92,0)),0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F83" t="str">
         <f>IF(C83=0,"-",IF(C83&gt;E83,"W",IF(C83&lt;E83,"L",IF(AND('Picks Detail'!E114&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,A83)&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,D83)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A83)-'Picks Detail'!E114)&lt;ABS(INDEX('Picks Detail'!F114:Q114,1,D83)-'Picks Detail'!E114),"W",IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A83)-'Picks Detail'!E114)&gt;ABS(INDEX('Picks Detail'!F114:Q114,1,D83)-'Picks Detail'!E114),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>T</v>
       </c>
       <c r="G83">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H83">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I83">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31517,7 +31914,7 @@
       </c>
       <c r="E84">
         <f>IFERROR(INDEX(C$81:C$92,MATCH(8,A$81:A$92,0)),0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F84" t="str">
         <f>IF(C84=0,"-",IF(C84&gt;E84,"W",IF(C84&lt;E84,"L",IF(AND('Picks Detail'!E114&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,A84)&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,D84)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A84)-'Picks Detail'!E114)&lt;ABS(INDEX('Picks Detail'!F114:Q114,1,D84)-'Picks Detail'!E114),"W",IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A84)-'Picks Detail'!E114)&gt;ABS(INDEX('Picks Detail'!F114:Q114,1,D84)-'Picks Detail'!E114),"L","T")),"T"))))</f>
@@ -31546,30 +31943,30 @@
       </c>
       <c r="C85" s="3">
         <f>SUMPRODUCT(('Picks Detail'!J100:J113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!J100:J113='Picks Detail'!E100:E113))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D85">
         <v>12</v>
       </c>
       <c r="E85">
         <f>IFERROR(INDEX(C$81:C$92,MATCH(12,A$81:A$92,0)),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F85" t="str">
         <f>IF(C85=0,"-",IF(C85&gt;E85,"W",IF(C85&lt;E85,"L",IF(AND('Picks Detail'!E114&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,A85)&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,D85)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A85)-'Picks Detail'!E114)&lt;ABS(INDEX('Picks Detail'!F114:Q114,1,D85)-'Picks Detail'!E114),"W",IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A85)-'Picks Detail'!E114)&gt;ABS(INDEX('Picks Detail'!F114:Q114,1,D85)-'Picks Detail'!E114),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G85">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H85">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I85">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31582,18 +31979,18 @@
       </c>
       <c r="C86" s="3">
         <f>SUMPRODUCT(('Picks Detail'!K100:K113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!K100:K113='Picks Detail'!E100:E113))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D86">
         <v>11</v>
       </c>
       <c r="E86">
         <f>IFERROR(INDEX(C$81:C$92,MATCH(11,A$81:A$92,0)),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F86" t="str">
         <f>IF(C86=0,"-",IF(C86&gt;E86,"W",IF(C86&lt;E86,"L",IF(AND('Picks Detail'!E114&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,A86)&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,D86)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A86)-'Picks Detail'!E114)&lt;ABS(INDEX('Picks Detail'!F114:Q114,1,D86)-'Picks Detail'!E114),"W",IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A86)-'Picks Detail'!E114)&gt;ABS(INDEX('Picks Detail'!F114:Q114,1,D86)-'Picks Detail'!E114),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G86">
         <f t="shared" si="15"/>
@@ -31601,11 +31998,11 @@
       </c>
       <c r="H86">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I86">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31618,30 +32015,30 @@
       </c>
       <c r="C87" s="3">
         <f>SUMPRODUCT(('Picks Detail'!L100:L113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!L100:L113='Picks Detail'!E100:E113))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D87">
         <v>3</v>
       </c>
       <c r="E87">
         <f>IFERROR(INDEX(C$81:C$92,MATCH(3,A$81:A$92,0)),0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F87" t="str">
         <f>IF(C87=0,"-",IF(C87&gt;E87,"W",IF(C87&lt;E87,"L",IF(AND('Picks Detail'!E114&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,A87)&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,D87)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A87)-'Picks Detail'!E114)&lt;ABS(INDEX('Picks Detail'!F114:Q114,1,D87)-'Picks Detail'!E114),"W",IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A87)-'Picks Detail'!E114)&gt;ABS(INDEX('Picks Detail'!F114:Q114,1,D87)-'Picks Detail'!E114),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>T</v>
       </c>
       <c r="G87">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H87">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I87">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31654,7 +32051,7 @@
       </c>
       <c r="C88" s="3">
         <f>SUMPRODUCT(('Picks Detail'!M100:M113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!M100:M113='Picks Detail'!E100:E113))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D88">
         <v>4</v>
@@ -31665,19 +32062,19 @@
       </c>
       <c r="F88" t="str">
         <f>IF(C88=0,"-",IF(C88&gt;E88,"W",IF(C88&lt;E88,"L",IF(AND('Picks Detail'!E114&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,A88)&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,D88)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A88)-'Picks Detail'!E114)&lt;ABS(INDEX('Picks Detail'!F114:Q114,1,D88)-'Picks Detail'!E114),"W",IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A88)-'Picks Detail'!E114)&gt;ABS(INDEX('Picks Detail'!F114:Q114,1,D88)-'Picks Detail'!E114),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G88">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H88">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I88">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31690,30 +32087,30 @@
       </c>
       <c r="C89" s="3">
         <f>SUMPRODUCT(('Picks Detail'!N100:N113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!N100:N113='Picks Detail'!E100:E113))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D89">
         <v>1</v>
       </c>
       <c r="E89">
         <f>IFERROR(INDEX(C$81:C$92,MATCH(1,A$81:A$92,0)),0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F89" t="str">
         <f>IF(C89=0,"-",IF(C89&gt;E89,"W",IF(C89&lt;E89,"L",IF(AND('Picks Detail'!E114&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,A89)&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,D89)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A89)-'Picks Detail'!E114)&lt;ABS(INDEX('Picks Detail'!F114:Q114,1,D89)-'Picks Detail'!E114),"W",IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A89)-'Picks Detail'!E114)&gt;ABS(INDEX('Picks Detail'!F114:Q114,1,D89)-'Picks Detail'!E114),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G89">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H89">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I89">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31726,30 +32123,30 @@
       </c>
       <c r="C90" s="3">
         <f>SUMPRODUCT(('Picks Detail'!O100:O113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!O100:O113='Picks Detail'!E100:E113))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D90">
         <v>2</v>
       </c>
       <c r="E90">
         <f>IFERROR(INDEX(C$81:C$92,MATCH(2,A$81:A$92,0)),0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F90" t="str">
         <f>IF(C90=0,"-",IF(C90&gt;E90,"W",IF(C90&lt;E90,"L",IF(AND('Picks Detail'!E114&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,A90)&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,D90)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A90)-'Picks Detail'!E114)&lt;ABS(INDEX('Picks Detail'!F114:Q114,1,D90)-'Picks Detail'!E114),"W",IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A90)-'Picks Detail'!E114)&gt;ABS(INDEX('Picks Detail'!F114:Q114,1,D90)-'Picks Detail'!E114),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G90">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H90">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I90">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31762,30 +32159,30 @@
       </c>
       <c r="C91" s="3">
         <f>SUMPRODUCT(('Picks Detail'!P100:P113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!P100:P113='Picks Detail'!E100:E113))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D91">
         <v>6</v>
       </c>
       <c r="E91">
         <f>IFERROR(INDEX(C$81:C$92,MATCH(6,A$81:A$92,0)),0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F91" t="str">
         <f>IF(C91=0,"-",IF(C91&gt;E91,"W",IF(C91&lt;E91,"L",IF(AND('Picks Detail'!E114&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,A91)&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,D91)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A91)-'Picks Detail'!E114)&lt;ABS(INDEX('Picks Detail'!F114:Q114,1,D91)-'Picks Detail'!E114),"W",IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A91)-'Picks Detail'!E114)&gt;ABS(INDEX('Picks Detail'!F114:Q114,1,D91)-'Picks Detail'!E114),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G91">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H91">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I91">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31798,18 +32195,18 @@
       </c>
       <c r="C92" s="3">
         <f>SUMPRODUCT(('Picks Detail'!Q100:Q113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!Q100:Q113='Picks Detail'!E100:E113))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D92">
         <v>5</v>
       </c>
       <c r="E92">
         <f>IFERROR(INDEX(C$81:C$92,MATCH(5,A$81:A$92,0)),0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F92" t="str">
         <f>IF(C92=0,"-",IF(C92&gt;E92,"W",IF(C92&lt;E92,"L",IF(AND('Picks Detail'!E114&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,A92)&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,D92)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A92)-'Picks Detail'!E114)&lt;ABS(INDEX('Picks Detail'!F114:Q114,1,D92)-'Picks Detail'!E114),"W",IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A92)-'Picks Detail'!E114)&gt;ABS(INDEX('Picks Detail'!F114:Q114,1,D92)-'Picks Detail'!E114),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G92">
         <f t="shared" si="15"/>
@@ -31817,11 +32214,11 @@
       </c>
       <c r="H92">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I92">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -31844,17 +32241,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -34677,17 +35074,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -37510,19 +37907,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -37589,11 +37986,11 @@
       </c>
       <c r="H3">
         <f>Helper!H2</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I3">
         <f>Helper!I2</f>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J3">
         <f>Helper!J2</f>
@@ -37634,11 +38031,11 @@
       </c>
       <c r="H4">
         <f>Helper!H3</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <f>Helper!I3</f>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J4">
         <f>Helper!J3</f>
@@ -37679,11 +38076,11 @@
       </c>
       <c r="H5">
         <f>Helper!H4</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <f>Helper!I4</f>
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="J5">
         <f>Helper!J4</f>
@@ -37769,11 +38166,11 @@
       </c>
       <c r="H7">
         <f>Helper!H6</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <f>Helper!I6</f>
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="J7">
         <f>Helper!J6</f>
@@ -37814,11 +38211,11 @@
       </c>
       <c r="H8">
         <f>Helper!H7</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I8">
         <f>Helper!I7</f>
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J8">
         <f>Helper!J7</f>
@@ -37859,11 +38256,11 @@
       </c>
       <c r="H9">
         <f>Helper!H8</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I9">
         <f>Helper!I8</f>
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="J9">
         <f>Helper!J8</f>
@@ -37904,11 +38301,11 @@
       </c>
       <c r="H10">
         <f>Helper!H9</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <f>Helper!I9</f>
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J10">
         <f>Helper!J9</f>
@@ -37949,11 +38346,11 @@
       </c>
       <c r="H11">
         <f>Helper!H10</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <f>Helper!I10</f>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J11">
         <f>Helper!J10</f>
@@ -37994,11 +38391,11 @@
       </c>
       <c r="H12">
         <f>Helper!H11</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <f>Helper!I11</f>
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="J12">
         <f>Helper!J11</f>
@@ -38039,11 +38436,11 @@
       </c>
       <c r="H13">
         <f>Helper!H12</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <f>Helper!I12</f>
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J13">
         <f>Helper!J12</f>
@@ -38084,11 +38481,11 @@
       </c>
       <c r="H14">
         <f>Helper!H13</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <f>Helper!I13</f>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J14">
         <f>Helper!J13</f>
@@ -39412,7 +39809,7 @@
       </c>
       <c r="C57">
         <f>Helper!I2</f>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D57">
         <f>Helper!R2</f>
@@ -39424,11 +39821,11 @@
       </c>
       <c r="F57">
         <f>Helper!AE2</f>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G57">
         <f>Helper!K2</f>
-        <v>63.000100000000003</v>
+        <v>68.000100000000003</v>
       </c>
       <c r="H57">
         <f>Helper!T2</f>
@@ -39445,7 +39842,7 @@
       </c>
       <c r="C58">
         <f>Helper!I3</f>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D58">
         <f>Helper!R3</f>
@@ -39457,11 +39854,11 @@
       </c>
       <c r="F58">
         <f>Helper!AE3</f>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G58">
         <f>Helper!K3</f>
-        <v>63.0002</v>
+        <v>68.000200000000007</v>
       </c>
       <c r="H58">
         <f>Helper!T3</f>
@@ -39478,7 +39875,7 @@
       </c>
       <c r="C59">
         <f>Helper!I4</f>
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D59">
         <f>Helper!R4</f>
@@ -39490,11 +39887,11 @@
       </c>
       <c r="F59">
         <f>Helper!AE4</f>
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G59">
         <f>Helper!K4</f>
-        <v>54.000300000000003</v>
+        <v>61.000300000000003</v>
       </c>
       <c r="H59">
         <f>Helper!T4</f>
@@ -39544,7 +39941,7 @@
       </c>
       <c r="C61">
         <f>Helper!I6</f>
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D61">
         <f>Helper!R6</f>
@@ -39556,11 +39953,11 @@
       </c>
       <c r="F61">
         <f>Helper!AE6</f>
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G61">
         <f>Helper!K6</f>
-        <v>58.000500000000002</v>
+        <v>65.000500000000002</v>
       </c>
       <c r="H61">
         <f>Helper!T6</f>
@@ -39577,7 +39974,7 @@
       </c>
       <c r="C62">
         <f>Helper!I7</f>
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D62">
         <f>Helper!R7</f>
@@ -39589,11 +39986,11 @@
       </c>
       <c r="F62">
         <f>Helper!AE7</f>
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G62">
         <f>Helper!K7</f>
-        <v>56.000599999999999</v>
+        <v>60.000599999999999</v>
       </c>
       <c r="H62">
         <f>Helper!T7</f>
@@ -39610,7 +40007,7 @@
       </c>
       <c r="C63">
         <f>Helper!I8</f>
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D63">
         <f>Helper!R8</f>
@@ -39622,11 +40019,11 @@
       </c>
       <c r="F63">
         <f>Helper!AE8</f>
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G63">
         <f>Helper!K8</f>
-        <v>46.000700000000002</v>
+        <v>53.000700000000002</v>
       </c>
       <c r="H63">
         <f>Helper!T8</f>
@@ -39643,7 +40040,7 @@
       </c>
       <c r="C64">
         <f>Helper!I9</f>
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D64">
         <f>Helper!R9</f>
@@ -39655,11 +40052,11 @@
       </c>
       <c r="F64">
         <f>Helper!AE9</f>
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G64">
         <f>Helper!K9</f>
-        <v>43.000799999999998</v>
+        <v>50.000799999999998</v>
       </c>
       <c r="H64">
         <f>Helper!T9</f>
@@ -39676,7 +40073,7 @@
       </c>
       <c r="C65">
         <f>Helper!I10</f>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D65">
         <f>Helper!R10</f>
@@ -39688,11 +40085,11 @@
       </c>
       <c r="F65">
         <f>Helper!AE10</f>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G65">
         <f>Helper!K10</f>
-        <v>43.000900000000001</v>
+        <v>49.000900000000001</v>
       </c>
       <c r="H65">
         <f>Helper!T10</f>
@@ -39709,7 +40106,7 @@
       </c>
       <c r="C66">
         <f>Helper!I11</f>
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D66">
         <f>Helper!R11</f>
@@ -39721,11 +40118,11 @@
       </c>
       <c r="F66">
         <f>Helper!AE11</f>
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G66">
         <f>Helper!K11</f>
-        <v>56.000999999999998</v>
+        <v>62.000999999999998</v>
       </c>
       <c r="H66">
         <f>Helper!T11</f>
@@ -39742,7 +40139,7 @@
       </c>
       <c r="C67">
         <f>Helper!I12</f>
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D67">
         <f>Helper!R12</f>
@@ -39754,11 +40151,11 @@
       </c>
       <c r="F67">
         <f>Helper!AE12</f>
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G67">
         <f>Helper!K12</f>
-        <v>48.001100000000001</v>
+        <v>54.001100000000001</v>
       </c>
       <c r="H67">
         <f>Helper!T12</f>
@@ -39775,7 +40172,7 @@
       </c>
       <c r="C68">
         <f>Helper!I13</f>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D68">
         <f>Helper!R13</f>
@@ -39787,11 +40184,11 @@
       </c>
       <c r="F68">
         <f>Helper!AE13</f>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G68">
         <f>Helper!K13</f>
-        <v>42.001199999999997</v>
+        <v>48.001199999999997</v>
       </c>
       <c r="H68">
         <f>Helper!T13</f>
@@ -40033,7 +40430,7 @@
       </c>
       <c r="C13">
         <f>INDEX(I$40:I$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
         <v>263</v>
@@ -40509,7 +40906,7 @@
       </c>
       <c r="I40">
         <f>Helper!AE2</f>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J40" t="b">
         <f t="shared" ref="J40:J51" si="1">OR(H40=$E$5,H40=$E$6,H40=$E$7,H40=$E$8,H40=$E$9)</f>
@@ -40517,7 +40914,7 @@
       </c>
       <c r="K40">
         <f>IF(J40,-1,I40+0.00001)</f>
-        <v>63.000010000000003</v>
+        <v>68.000010000000003</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40527,7 +40924,7 @@
       </c>
       <c r="I41">
         <f>Helper!AE3</f>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J41" t="b">
         <f t="shared" si="1"/>
@@ -40545,7 +40942,7 @@
       </c>
       <c r="I42">
         <f>Helper!AE4</f>
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="J42" t="b">
         <f t="shared" si="1"/>
@@ -40553,7 +40950,7 @@
       </c>
       <c r="K42">
         <f>IF(J42,-1,I42+0.00003)</f>
-        <v>54.000030000000002</v>
+        <v>61.000030000000002</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40581,7 +40978,7 @@
       </c>
       <c r="I44">
         <f>Helper!AE6</f>
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="J44" t="b">
         <f t="shared" si="1"/>
@@ -40589,7 +40986,7 @@
       </c>
       <c r="K44">
         <f>IF(J44,-1,I44+0.00005)</f>
-        <v>58.000050000000002</v>
+        <v>65.000050000000002</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40599,7 +40996,7 @@
       </c>
       <c r="I45">
         <f>Helper!AE7</f>
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J45" t="b">
         <f t="shared" si="1"/>
@@ -40607,7 +41004,7 @@
       </c>
       <c r="K45">
         <f>IF(J45,-1,I45+0.00006)</f>
-        <v>56.000059999999998</v>
+        <v>60.000059999999998</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40617,7 +41014,7 @@
       </c>
       <c r="I46">
         <f>Helper!AE8</f>
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="J46" t="b">
         <f t="shared" si="1"/>
@@ -40625,7 +41022,7 @@
       </c>
       <c r="K46">
         <f>IF(J46,-1,I46+0.00007)</f>
-        <v>46.000070000000001</v>
+        <v>53.000070000000001</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40635,7 +41032,7 @@
       </c>
       <c r="I47">
         <f>Helper!AE9</f>
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J47" t="b">
         <f t="shared" si="1"/>
@@ -40653,7 +41050,7 @@
       </c>
       <c r="I48">
         <f>Helper!AE10</f>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J48" t="b">
         <f t="shared" si="1"/>
@@ -40661,7 +41058,7 @@
       </c>
       <c r="K48">
         <f>IF(J48,-1,I48+0.00009)</f>
-        <v>43.00009</v>
+        <v>49.00009</v>
       </c>
     </row>
     <row r="49" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40671,7 +41068,7 @@
       </c>
       <c r="I49">
         <f>Helper!AE11</f>
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="J49" t="b">
         <f t="shared" si="1"/>
@@ -40679,7 +41076,7 @@
       </c>
       <c r="K49">
         <f>IF(J49,-1,I49+0.0001)</f>
-        <v>56.000100000000003</v>
+        <v>62.000100000000003</v>
       </c>
     </row>
     <row r="50" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40689,7 +41086,7 @@
       </c>
       <c r="I50">
         <f>Helper!AE12</f>
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J50" t="b">
         <f t="shared" si="1"/>
@@ -40707,7 +41104,7 @@
       </c>
       <c r="I51">
         <f>Helper!AE13</f>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J51" t="b">
         <f t="shared" si="1"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -12678,10 +12678,10 @@
         <v>ARI</v>
       </c>
       <c r="F109" s="10" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="H109" s="10" t="s">
         <v>77</v>
@@ -12691,13 +12691,13 @@
         <v>77</v>
       </c>
       <c r="K109" s="10" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="L109" s="10" t="s">
         <v>77</v>
       </c>
       <c r="M109" s="10" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="N109" s="10" t="s">
         <v>77</v>
@@ -12706,10 +12706,10 @@
         <v>77</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="Q109" s="10" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
     </row>
     <row r="110" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12730,13 +12730,13 @@
         <v>KC</v>
       </c>
       <c r="F110" s="10" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="G110" s="10" t="s">
         <v>88</v>
       </c>
       <c r="H110" s="10" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="I110" s="10"/>
       <c r="J110" s="10" t="s">
@@ -12752,7 +12752,7 @@
         <v>88</v>
       </c>
       <c r="N110" s="10" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="O110" s="10" t="s">
         <v>88</v>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1235" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C564DB2-2A58-4BAF-9FA9-2BD664CF96C2}"/>
+  <xr:revisionPtr revIDLastSave="1261" documentId="11_C5FB6D5EBB7DB41C9C4944A345A03722CFCA9995" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9B34C42-023A-4C01-9AA6-7366B77DFF44}"/>
   <bookViews>
-    <workbookView xWindow="29400" yWindow="-120" windowWidth="28320" windowHeight="16440" tabRatio="911" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28200" yWindow="-120" windowWidth="28320" windowHeight="16440" tabRatio="911" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4266" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4277" uniqueCount="346">
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -1377,13 +1377,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1470,10 +1470,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1665,12 +1661,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="A1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1859,7 +1855,7 @@
         <v>23</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1926,7 +1922,7 @@
       </c>
       <c r="B5" t="str">
         <f>'Playoff Picture'!B17</f>
-        <v>Chris Simmons</v>
+        <v>Mikayla Simmons</v>
       </c>
       <c r="C5" s="3">
         <v>6</v>
@@ -2071,7 +2067,7 @@
       </c>
       <c r="B10" t="str">
         <f>'Playoff Picture'!B22</f>
-        <v>Evan Loeser</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
@@ -2120,7 +2116,7 @@
       </c>
       <c r="B14" t="str">
         <f>INDEX($B$5:$B$10,MATCH(LARGE($H$5:$H$10,1),$H$5:$H$10,0))</f>
-        <v>Chris Simmons</v>
+        <v>Mikayla Simmons</v>
       </c>
       <c r="C14">
         <f>INDEX($C$5:$C$10,MATCH(LARGE($H$5:$H$10,1),$H$5:$H$10,0))</f>
@@ -2205,7 +2201,7 @@
       </c>
       <c r="B19" t="str">
         <f>INDEX($B$5:$B$10,MATCH(LARGE($H$5:$H$10,6),$H$5:$H$10,0))</f>
-        <v>Evan Loeser</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="C19">
         <f>INDEX($C$5:$C$10,MATCH(LARGE($H$5:$H$10,6),$H$5:$H$10,0))</f>
@@ -2281,7 +2277,7 @@
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>'Playoff Wild Card'!B14</f>
-        <v>Chris Simmons</v>
+        <v>Mikayla Simmons</v>
       </c>
       <c r="B6">
         <f>'Playoff Wild Card'!C14</f>
@@ -2483,7 +2479,7 @@
       </c>
       <c r="B13" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>Chris Simmons</v>
+        <v>Mikayla Simmons</v>
       </c>
       <c r="C13">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
@@ -2632,7 +2628,7 @@
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>A6</f>
-        <v>Chris Simmons</v>
+        <v>Mikayla Simmons</v>
       </c>
       <c r="B22" s="3">
         <v>0</v>
@@ -3381,19 +3377,19 @@
       </c>
       <c r="H6">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H85,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G85,0)</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J6">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F10="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F25="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F40="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F55="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F70="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F85="W"),1,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <f>I6+0.0005</f>
-        <v>65.000500000000002</v>
+        <v>71.000500000000002</v>
       </c>
       <c r="L6">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H10,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G10,0)</f>
@@ -3473,11 +3469,11 @@
       </c>
       <c r="AE6">
         <f t="shared" si="2"/>
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="AF6">
         <f>AE6+0.0005</f>
-        <v>65.000500000000002</v>
+        <v>71.000500000000002</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3639,19 +3635,19 @@
       </c>
       <c r="H8">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H87,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G87,0)</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="J8">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F12="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F27="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F42="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F57="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F72="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F87="W"),1,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8">
         <f>I8+0.0007</f>
-        <v>53.000700000000002</v>
+        <v>59.000700000000002</v>
       </c>
       <c r="L8">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H12,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G12,0)</f>
@@ -3731,11 +3727,11 @@
       </c>
       <c r="AE8">
         <f t="shared" si="2"/>
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="AF8">
         <f>AE8+0.0007</f>
-        <v>53.000700000000002</v>
+        <v>59.000700000000002</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3768,19 +3764,19 @@
       </c>
       <c r="H9">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H88,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G88,0)</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J9">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F13="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F28="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F43="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F58="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F73="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F88="W"),1,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9">
         <f>I9+0.0008</f>
-        <v>50.000799999999998</v>
+        <v>56.000799999999998</v>
       </c>
       <c r="L9">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H13,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G13,0)</f>
@@ -3860,11 +3856,11 @@
       </c>
       <c r="AE9">
         <f t="shared" si="2"/>
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AF9">
         <f>AE9+0.0008</f>
-        <v>50.000799999999998</v>
+        <v>56.000799999999998</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3897,19 +3893,19 @@
       </c>
       <c r="H10">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H89,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G89,0)</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I10">
         <f t="shared" si="0"/>
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="J10">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F14="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F29="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F44="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F59="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F74="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F89="W"),1,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10">
         <f>I10+0.0009</f>
-        <v>49.000900000000001</v>
+        <v>56.000900000000001</v>
       </c>
       <c r="L10">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H14,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G14,0)</f>
@@ -3989,11 +3985,11 @@
       </c>
       <c r="AE10">
         <f t="shared" si="2"/>
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="AF10">
         <f>AE10+0.0009</f>
-        <v>49.000900000000001</v>
+        <v>56.000900000000001</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4026,19 +4022,19 @@
       </c>
       <c r="H11">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H90,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G90,0)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I11">
         <f t="shared" si="0"/>
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="J11">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F15="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F30="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F45="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F60="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F75="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F90="W"),1,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11">
         <f>I11+0.001</f>
-        <v>62.000999999999998</v>
+        <v>68.001000000000005</v>
       </c>
       <c r="L11">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H15,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G15,0)</f>
@@ -4118,11 +4114,11 @@
       </c>
       <c r="AE11">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="AF11">
         <f>AE11+0.001</f>
-        <v>62.000999999999998</v>
+        <v>68.001000000000005</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4155,19 +4151,19 @@
       </c>
       <c r="H12">
         <f>IF(Roster!$B$16&gt;=6,'Wk 1-6 Input'!H91,0)+IF(Roster!$B$16&gt;6,'Wk 1-6 Input'!G91,0)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I12">
         <f t="shared" si="0"/>
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J12">
         <f>IF(AND(Roster!$B$16&gt;1,'Wk 1-6 Input'!F16="W"),1,0)+IF(AND(Roster!$B$16&gt;2,'Wk 1-6 Input'!F31="W"),1,0)+IF(AND(Roster!$B$16&gt;3,'Wk 1-6 Input'!F46="W"),1,0)+IF(AND(Roster!$B$16&gt;4,'Wk 1-6 Input'!F61="W"),1,0)+IF(AND(Roster!$B$16&gt;5,'Wk 1-6 Input'!F76="W"),1,0)+IF(AND(Roster!$B$16&gt;6,'Wk 1-6 Input'!F91="W"),1,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12">
         <f>I12+0.0011</f>
-        <v>54.001100000000001</v>
+        <v>60.001100000000001</v>
       </c>
       <c r="L12">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H16,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G16,0)</f>
@@ -4247,11 +4243,11 @@
       </c>
       <c r="AE12">
         <f t="shared" si="2"/>
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="AF12">
         <f>AE12+0.0011</f>
-        <v>54.001100000000001</v>
+        <v>60.001100000000001</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4402,14 +4398,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -5354,14 +5350,14 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
@@ -6306,14 +6302,14 @@
       </c>
     </row>
     <row r="111" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="23" t="s">
+      <c r="A111" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B111" s="23"/>
-      <c r="C111" s="23"/>
-      <c r="D111" s="23"/>
-      <c r="E111" s="23"/>
-      <c r="F111" s="23"/>
+      <c r="B111" s="22"/>
+      <c r="C111" s="22"/>
+      <c r="D111" s="22"/>
+      <c r="E111" s="22"/>
+      <c r="F111" s="22"/>
     </row>
     <row r="112" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
@@ -7285,67 +7281,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8313,25 +8309,25 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="26"/>
-      <c r="P23" s="26"/>
-      <c r="Q23" s="26"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="24"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="24"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -9299,25 +9295,25 @@
       </c>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="26" t="s">
+      <c r="A42" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="26"/>
-      <c r="L42" s="26"/>
-      <c r="M42" s="26"/>
-      <c r="N42" s="26"/>
-      <c r="O42" s="26"/>
-      <c r="P42" s="26"/>
-      <c r="Q42" s="26"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="24"/>
+      <c r="N42" s="24"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="24"/>
+      <c r="Q42" s="24"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -10247,25 +10243,25 @@
       </c>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="26" t="s">
+      <c r="A61" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="26"/>
-      <c r="C61" s="26"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="26"/>
-      <c r="F61" s="26"/>
-      <c r="G61" s="26"/>
-      <c r="H61" s="26"/>
-      <c r="I61" s="26"/>
-      <c r="J61" s="26"/>
-      <c r="K61" s="26"/>
-      <c r="L61" s="26"/>
-      <c r="M61" s="26"/>
-      <c r="N61" s="26"/>
-      <c r="O61" s="26"/>
-      <c r="P61" s="26"/>
-      <c r="Q61" s="26"/>
+      <c r="B61" s="24"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="24"/>
+      <c r="J61" s="24"/>
+      <c r="K61" s="24"/>
+      <c r="L61" s="24"/>
+      <c r="M61" s="24"/>
+      <c r="N61" s="24"/>
+      <c r="O61" s="24"/>
+      <c r="P61" s="24"/>
+      <c r="Q61" s="24"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -11233,25 +11229,25 @@
       </c>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="26" t="s">
+      <c r="A80" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="26"/>
-      <c r="C80" s="26"/>
-      <c r="D80" s="26"/>
-      <c r="E80" s="26"/>
-      <c r="F80" s="26"/>
-      <c r="G80" s="26"/>
-      <c r="H80" s="26"/>
-      <c r="I80" s="26"/>
-      <c r="J80" s="26"/>
-      <c r="K80" s="26"/>
-      <c r="L80" s="26"/>
-      <c r="M80" s="26"/>
-      <c r="N80" s="26"/>
-      <c r="O80" s="26"/>
-      <c r="P80" s="26"/>
-      <c r="Q80" s="26"/>
+      <c r="B80" s="24"/>
+      <c r="C80" s="24"/>
+      <c r="D80" s="24"/>
+      <c r="E80" s="24"/>
+      <c r="F80" s="24"/>
+      <c r="G80" s="24"/>
+      <c r="H80" s="24"/>
+      <c r="I80" s="24"/>
+      <c r="J80" s="24"/>
+      <c r="K80" s="24"/>
+      <c r="L80" s="24"/>
+      <c r="M80" s="24"/>
+      <c r="N80" s="24"/>
+      <c r="O80" s="24"/>
+      <c r="P80" s="24"/>
+      <c r="Q80" s="24"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -12125,25 +12121,25 @@
       </c>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="26" t="s">
+      <c r="A98" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="26"/>
-      <c r="C98" s="26"/>
-      <c r="D98" s="26"/>
-      <c r="E98" s="26"/>
-      <c r="F98" s="26"/>
-      <c r="G98" s="26"/>
-      <c r="H98" s="26"/>
-      <c r="I98" s="26"/>
-      <c r="J98" s="26"/>
-      <c r="K98" s="26"/>
-      <c r="L98" s="26"/>
-      <c r="M98" s="26"/>
-      <c r="N98" s="26"/>
-      <c r="O98" s="26"/>
-      <c r="P98" s="26"/>
-      <c r="Q98" s="26"/>
+      <c r="B98" s="24"/>
+      <c r="C98" s="24"/>
+      <c r="D98" s="24"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24"/>
+      <c r="H98" s="24"/>
+      <c r="I98" s="24"/>
+      <c r="J98" s="24"/>
+      <c r="K98" s="24"/>
+      <c r="L98" s="24"/>
+      <c r="M98" s="24"/>
+      <c r="N98" s="24"/>
+      <c r="O98" s="24"/>
+      <c r="P98" s="24"/>
+      <c r="Q98" s="24"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -12883,20 +12879,42 @@
       </c>
       <c r="E113" s="9" t="str">
         <f>'NFL Schedule'!J110</f>
-        <v/>
-      </c>
-      <c r="F113" s="10"/>
-      <c r="G113" s="10"/>
-      <c r="H113" s="10"/>
+        <v>WAS</v>
+      </c>
+      <c r="F113" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G113" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H113" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="I113" s="10"/>
-      <c r="J113" s="10"/>
-      <c r="K113" s="10"/>
-      <c r="L113" s="10"/>
-      <c r="M113" s="10"/>
-      <c r="N113" s="10"/>
-      <c r="O113" s="10"/>
-      <c r="P113" s="10"/>
-      <c r="Q113" s="10"/>
+      <c r="J113" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="K113" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="L113" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="M113" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="N113" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="O113" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="P113" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q113" s="10" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="11" t="s">
@@ -12905,43 +12923,65 @@
       <c r="B114" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="E114" s="13" t="str">
+      <c r="E114" s="13">
         <f>'NFL Schedule'!E111</f>
-        <v/>
-      </c>
-      <c r="F114" s="14"/>
-      <c r="G114" s="14"/>
-      <c r="H114" s="14"/>
+        <v>40</v>
+      </c>
+      <c r="F114" s="14">
+        <v>46</v>
+      </c>
+      <c r="G114" s="14">
+        <v>52</v>
+      </c>
+      <c r="H114" s="14">
+        <v>49</v>
+      </c>
       <c r="I114" s="14"/>
-      <c r="J114" s="14"/>
-      <c r="K114" s="14"/>
-      <c r="L114" s="14"/>
-      <c r="M114" s="14"/>
-      <c r="N114" s="14"/>
-      <c r="O114" s="14"/>
-      <c r="P114" s="14"/>
-      <c r="Q114" s="14"/>
+      <c r="J114" s="14">
+        <v>50</v>
+      </c>
+      <c r="K114" s="14">
+        <v>42</v>
+      </c>
+      <c r="L114" s="14">
+        <v>42</v>
+      </c>
+      <c r="M114" s="14">
+        <v>47</v>
+      </c>
+      <c r="N114" s="14">
+        <v>50</v>
+      </c>
+      <c r="O114" s="14">
+        <v>45</v>
+      </c>
+      <c r="P114" s="14">
+        <v>43</v>
+      </c>
+      <c r="Q114" s="14">
+        <v>51</v>
+      </c>
     </row>
     <row r="115" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="26" t="s">
+      <c r="A115" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="26"/>
-      <c r="C115" s="26"/>
-      <c r="D115" s="26"/>
-      <c r="E115" s="26"/>
-      <c r="F115" s="26"/>
-      <c r="G115" s="26"/>
-      <c r="H115" s="26"/>
-      <c r="I115" s="26"/>
-      <c r="J115" s="26"/>
-      <c r="K115" s="26"/>
-      <c r="L115" s="26"/>
-      <c r="M115" s="26"/>
-      <c r="N115" s="26"/>
-      <c r="O115" s="26"/>
-      <c r="P115" s="26"/>
-      <c r="Q115" s="26"/>
+      <c r="B115" s="24"/>
+      <c r="C115" s="24"/>
+      <c r="D115" s="24"/>
+      <c r="E115" s="24"/>
+      <c r="F115" s="24"/>
+      <c r="G115" s="24"/>
+      <c r="H115" s="24"/>
+      <c r="I115" s="24"/>
+      <c r="J115" s="24"/>
+      <c r="K115" s="24"/>
+      <c r="L115" s="24"/>
+      <c r="M115" s="24"/>
+      <c r="N115" s="24"/>
+      <c r="O115" s="24"/>
+      <c r="P115" s="24"/>
+      <c r="Q115" s="24"/>
     </row>
     <row r="116" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -13441,25 +13481,25 @@
       <c r="Q131" s="14"/>
     </row>
     <row r="132" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="26" t="s">
+      <c r="A132" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="B132" s="26"/>
-      <c r="C132" s="26"/>
-      <c r="D132" s="26"/>
-      <c r="E132" s="26"/>
-      <c r="F132" s="26"/>
-      <c r="G132" s="26"/>
-      <c r="H132" s="26"/>
-      <c r="I132" s="26"/>
-      <c r="J132" s="26"/>
-      <c r="K132" s="26"/>
-      <c r="L132" s="26"/>
-      <c r="M132" s="26"/>
-      <c r="N132" s="26"/>
-      <c r="O132" s="26"/>
-      <c r="P132" s="26"/>
-      <c r="Q132" s="26"/>
+      <c r="B132" s="24"/>
+      <c r="C132" s="24"/>
+      <c r="D132" s="24"/>
+      <c r="E132" s="24"/>
+      <c r="F132" s="24"/>
+      <c r="G132" s="24"/>
+      <c r="H132" s="24"/>
+      <c r="I132" s="24"/>
+      <c r="J132" s="24"/>
+      <c r="K132" s="24"/>
+      <c r="L132" s="24"/>
+      <c r="M132" s="24"/>
+      <c r="N132" s="24"/>
+      <c r="O132" s="24"/>
+      <c r="P132" s="24"/>
+      <c r="Q132" s="24"/>
     </row>
     <row r="133" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -13959,25 +13999,25 @@
       <c r="Q148" s="14"/>
     </row>
     <row r="149" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="26" t="s">
+      <c r="A149" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="B149" s="26"/>
-      <c r="C149" s="26"/>
-      <c r="D149" s="26"/>
-      <c r="E149" s="26"/>
-      <c r="F149" s="26"/>
-      <c r="G149" s="26"/>
-      <c r="H149" s="26"/>
-      <c r="I149" s="26"/>
-      <c r="J149" s="26"/>
-      <c r="K149" s="26"/>
-      <c r="L149" s="26"/>
-      <c r="M149" s="26"/>
-      <c r="N149" s="26"/>
-      <c r="O149" s="26"/>
-      <c r="P149" s="26"/>
-      <c r="Q149" s="26"/>
+      <c r="B149" s="24"/>
+      <c r="C149" s="24"/>
+      <c r="D149" s="24"/>
+      <c r="E149" s="24"/>
+      <c r="F149" s="24"/>
+      <c r="G149" s="24"/>
+      <c r="H149" s="24"/>
+      <c r="I149" s="24"/>
+      <c r="J149" s="24"/>
+      <c r="K149" s="24"/>
+      <c r="L149" s="24"/>
+      <c r="M149" s="24"/>
+      <c r="N149" s="24"/>
+      <c r="O149" s="24"/>
+      <c r="P149" s="24"/>
+      <c r="Q149" s="24"/>
     </row>
     <row r="150" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -14507,25 +14547,25 @@
       <c r="Q166" s="14"/>
     </row>
     <row r="167" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="26" t="s">
+      <c r="A167" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="B167" s="26"/>
-      <c r="C167" s="26"/>
-      <c r="D167" s="26"/>
-      <c r="E167" s="26"/>
-      <c r="F167" s="26"/>
-      <c r="G167" s="26"/>
-      <c r="H167" s="26"/>
-      <c r="I167" s="26"/>
-      <c r="J167" s="26"/>
-      <c r="K167" s="26"/>
-      <c r="L167" s="26"/>
-      <c r="M167" s="26"/>
-      <c r="N167" s="26"/>
-      <c r="O167" s="26"/>
-      <c r="P167" s="26"/>
-      <c r="Q167" s="26"/>
+      <c r="B167" s="24"/>
+      <c r="C167" s="24"/>
+      <c r="D167" s="24"/>
+      <c r="E167" s="24"/>
+      <c r="F167" s="24"/>
+      <c r="G167" s="24"/>
+      <c r="H167" s="24"/>
+      <c r="I167" s="24"/>
+      <c r="J167" s="24"/>
+      <c r="K167" s="24"/>
+      <c r="L167" s="24"/>
+      <c r="M167" s="24"/>
+      <c r="N167" s="24"/>
+      <c r="O167" s="24"/>
+      <c r="P167" s="24"/>
+      <c r="Q167" s="24"/>
     </row>
     <row r="168" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -15025,25 +15065,25 @@
       <c r="Q183" s="14"/>
     </row>
     <row r="184" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="26" t="s">
+      <c r="A184" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="B184" s="26"/>
-      <c r="C184" s="26"/>
-      <c r="D184" s="26"/>
-      <c r="E184" s="26"/>
-      <c r="F184" s="26"/>
-      <c r="G184" s="26"/>
-      <c r="H184" s="26"/>
-      <c r="I184" s="26"/>
-      <c r="J184" s="26"/>
-      <c r="K184" s="26"/>
-      <c r="L184" s="26"/>
-      <c r="M184" s="26"/>
-      <c r="N184" s="26"/>
-      <c r="O184" s="26"/>
-      <c r="P184" s="26"/>
-      <c r="Q184" s="26"/>
+      <c r="B184" s="24"/>
+      <c r="C184" s="24"/>
+      <c r="D184" s="24"/>
+      <c r="E184" s="24"/>
+      <c r="F184" s="24"/>
+      <c r="G184" s="24"/>
+      <c r="H184" s="24"/>
+      <c r="I184" s="24"/>
+      <c r="J184" s="24"/>
+      <c r="K184" s="24"/>
+      <c r="L184" s="24"/>
+      <c r="M184" s="24"/>
+      <c r="N184" s="24"/>
+      <c r="O184" s="24"/>
+      <c r="P184" s="24"/>
+      <c r="Q184" s="24"/>
     </row>
     <row r="185" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -15513,25 +15553,25 @@
       <c r="Q199" s="14"/>
     </row>
     <row r="200" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="26" t="s">
+      <c r="A200" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="B200" s="26"/>
-      <c r="C200" s="26"/>
-      <c r="D200" s="26"/>
-      <c r="E200" s="26"/>
-      <c r="F200" s="26"/>
-      <c r="G200" s="26"/>
-      <c r="H200" s="26"/>
-      <c r="I200" s="26"/>
-      <c r="J200" s="26"/>
-      <c r="K200" s="26"/>
-      <c r="L200" s="26"/>
-      <c r="M200" s="26"/>
-      <c r="N200" s="26"/>
-      <c r="O200" s="26"/>
-      <c r="P200" s="26"/>
-      <c r="Q200" s="26"/>
+      <c r="B200" s="24"/>
+      <c r="C200" s="24"/>
+      <c r="D200" s="24"/>
+      <c r="E200" s="24"/>
+      <c r="F200" s="24"/>
+      <c r="G200" s="24"/>
+      <c r="H200" s="24"/>
+      <c r="I200" s="24"/>
+      <c r="J200" s="24"/>
+      <c r="K200" s="24"/>
+      <c r="L200" s="24"/>
+      <c r="M200" s="24"/>
+      <c r="N200" s="24"/>
+      <c r="O200" s="24"/>
+      <c r="P200" s="24"/>
+      <c r="Q200" s="24"/>
     </row>
     <row r="201" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -16091,25 +16131,25 @@
       <c r="Q218" s="14"/>
     </row>
     <row r="219" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="26" t="s">
+      <c r="A219" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="B219" s="26"/>
-      <c r="C219" s="26"/>
-      <c r="D219" s="26"/>
-      <c r="E219" s="26"/>
-      <c r="F219" s="26"/>
-      <c r="G219" s="26"/>
-      <c r="H219" s="26"/>
-      <c r="I219" s="26"/>
-      <c r="J219" s="26"/>
-      <c r="K219" s="26"/>
-      <c r="L219" s="26"/>
-      <c r="M219" s="26"/>
-      <c r="N219" s="26"/>
-      <c r="O219" s="26"/>
-      <c r="P219" s="26"/>
-      <c r="Q219" s="26"/>
+      <c r="B219" s="24"/>
+      <c r="C219" s="24"/>
+      <c r="D219" s="24"/>
+      <c r="E219" s="24"/>
+      <c r="F219" s="24"/>
+      <c r="G219" s="24"/>
+      <c r="H219" s="24"/>
+      <c r="I219" s="24"/>
+      <c r="J219" s="24"/>
+      <c r="K219" s="24"/>
+      <c r="L219" s="24"/>
+      <c r="M219" s="24"/>
+      <c r="N219" s="24"/>
+      <c r="O219" s="24"/>
+      <c r="P219" s="24"/>
+      <c r="Q219" s="24"/>
     </row>
     <row r="220" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -16609,25 +16649,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="26" t="s">
+      <c r="A236" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B236" s="26"/>
-      <c r="C236" s="26"/>
-      <c r="D236" s="26"/>
-      <c r="E236" s="26"/>
-      <c r="F236" s="26"/>
-      <c r="G236" s="26"/>
-      <c r="H236" s="26"/>
-      <c r="I236" s="26"/>
-      <c r="J236" s="26"/>
-      <c r="K236" s="26"/>
-      <c r="L236" s="26"/>
-      <c r="M236" s="26"/>
-      <c r="N236" s="26"/>
-      <c r="O236" s="26"/>
-      <c r="P236" s="26"/>
-      <c r="Q236" s="26"/>
+      <c r="B236" s="24"/>
+      <c r="C236" s="24"/>
+      <c r="D236" s="24"/>
+      <c r="E236" s="24"/>
+      <c r="F236" s="24"/>
+      <c r="G236" s="24"/>
+      <c r="H236" s="24"/>
+      <c r="I236" s="24"/>
+      <c r="J236" s="24"/>
+      <c r="K236" s="24"/>
+      <c r="L236" s="24"/>
+      <c r="M236" s="24"/>
+      <c r="N236" s="24"/>
+      <c r="O236" s="24"/>
+      <c r="P236" s="24"/>
+      <c r="Q236" s="24"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -17157,25 +17197,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="26" t="s">
+      <c r="A254" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="B254" s="26"/>
-      <c r="C254" s="26"/>
-      <c r="D254" s="26"/>
-      <c r="E254" s="26"/>
-      <c r="F254" s="26"/>
-      <c r="G254" s="26"/>
-      <c r="H254" s="26"/>
-      <c r="I254" s="26"/>
-      <c r="J254" s="26"/>
-      <c r="K254" s="26"/>
-      <c r="L254" s="26"/>
-      <c r="M254" s="26"/>
-      <c r="N254" s="26"/>
-      <c r="O254" s="26"/>
-      <c r="P254" s="26"/>
-      <c r="Q254" s="26"/>
+      <c r="B254" s="24"/>
+      <c r="C254" s="24"/>
+      <c r="D254" s="24"/>
+      <c r="E254" s="24"/>
+      <c r="F254" s="24"/>
+      <c r="G254" s="24"/>
+      <c r="H254" s="24"/>
+      <c r="I254" s="24"/>
+      <c r="J254" s="24"/>
+      <c r="K254" s="24"/>
+      <c r="L254" s="24"/>
+      <c r="M254" s="24"/>
+      <c r="N254" s="24"/>
+      <c r="O254" s="24"/>
+      <c r="P254" s="24"/>
+      <c r="Q254" s="24"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -17735,25 +17775,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="26" t="s">
+      <c r="A273" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="B273" s="26"/>
-      <c r="C273" s="26"/>
-      <c r="D273" s="26"/>
-      <c r="E273" s="26"/>
-      <c r="F273" s="26"/>
-      <c r="G273" s="26"/>
-      <c r="H273" s="26"/>
-      <c r="I273" s="26"/>
-      <c r="J273" s="26"/>
-      <c r="K273" s="26"/>
-      <c r="L273" s="26"/>
-      <c r="M273" s="26"/>
-      <c r="N273" s="26"/>
-      <c r="O273" s="26"/>
-      <c r="P273" s="26"/>
-      <c r="Q273" s="26"/>
+      <c r="B273" s="24"/>
+      <c r="C273" s="24"/>
+      <c r="D273" s="24"/>
+      <c r="E273" s="24"/>
+      <c r="F273" s="24"/>
+      <c r="G273" s="24"/>
+      <c r="H273" s="24"/>
+      <c r="I273" s="24"/>
+      <c r="J273" s="24"/>
+      <c r="K273" s="24"/>
+      <c r="L273" s="24"/>
+      <c r="M273" s="24"/>
+      <c r="N273" s="24"/>
+      <c r="O273" s="24"/>
+      <c r="P273" s="24"/>
+      <c r="Q273" s="24"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -18313,25 +18353,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="26" t="s">
+      <c r="A292" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="B292" s="26"/>
-      <c r="C292" s="26"/>
-      <c r="D292" s="26"/>
-      <c r="E292" s="26"/>
-      <c r="F292" s="26"/>
-      <c r="G292" s="26"/>
-      <c r="H292" s="26"/>
-      <c r="I292" s="26"/>
-      <c r="J292" s="26"/>
-      <c r="K292" s="26"/>
-      <c r="L292" s="26"/>
-      <c r="M292" s="26"/>
-      <c r="N292" s="26"/>
-      <c r="O292" s="26"/>
-      <c r="P292" s="26"/>
-      <c r="Q292" s="26"/>
+      <c r="B292" s="24"/>
+      <c r="C292" s="24"/>
+      <c r="D292" s="24"/>
+      <c r="E292" s="24"/>
+      <c r="F292" s="24"/>
+      <c r="G292" s="24"/>
+      <c r="H292" s="24"/>
+      <c r="I292" s="24"/>
+      <c r="J292" s="24"/>
+      <c r="K292" s="24"/>
+      <c r="L292" s="24"/>
+      <c r="M292" s="24"/>
+      <c r="N292" s="24"/>
+      <c r="O292" s="24"/>
+      <c r="P292" s="24"/>
+      <c r="Q292" s="24"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -18891,25 +18931,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="26" t="s">
+      <c r="A311" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="B311" s="26"/>
-      <c r="C311" s="26"/>
-      <c r="D311" s="26"/>
-      <c r="E311" s="26"/>
-      <c r="F311" s="26"/>
-      <c r="G311" s="26"/>
-      <c r="H311" s="26"/>
-      <c r="I311" s="26"/>
-      <c r="J311" s="26"/>
-      <c r="K311" s="26"/>
-      <c r="L311" s="26"/>
-      <c r="M311" s="26"/>
-      <c r="N311" s="26"/>
-      <c r="O311" s="26"/>
-      <c r="P311" s="26"/>
-      <c r="Q311" s="26"/>
+      <c r="B311" s="24"/>
+      <c r="C311" s="24"/>
+      <c r="D311" s="24"/>
+      <c r="E311" s="24"/>
+      <c r="F311" s="24"/>
+      <c r="G311" s="24"/>
+      <c r="H311" s="24"/>
+      <c r="I311" s="24"/>
+      <c r="J311" s="24"/>
+      <c r="K311" s="24"/>
+      <c r="L311" s="24"/>
+      <c r="M311" s="24"/>
+      <c r="N311" s="24"/>
+      <c r="O311" s="24"/>
+      <c r="P311" s="24"/>
+      <c r="Q311" s="24"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -19470,26 +19510,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A23:Q23"/>
+    <mergeCell ref="A42:Q42"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="A132:Q132"/>
+    <mergeCell ref="A149:Q149"/>
+    <mergeCell ref="A167:Q167"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A219:Q219"/>
     <mergeCell ref="A236:Q236"/>
     <mergeCell ref="A254:Q254"/>
     <mergeCell ref="A273:Q273"/>
     <mergeCell ref="A292:Q292"/>
     <mergeCell ref="A311:Q311"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A167:Q167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="A23:Q23"/>
-    <mergeCell ref="A42:Q42"/>
   </mergeCells>
   <dataValidations count="268">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Pick" error="Pick must be NE or SEA" promptTitle="ATS Pick" prompt="Pick NE or SEA" sqref="F6:Q6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -23986,25 +24026,34 @@
       <c r="D110" t="s">
         <v>83</v>
       </c>
+      <c r="E110">
+        <v>17</v>
+      </c>
       <c r="F110" t="s">
         <v>59</v>
       </c>
+      <c r="G110">
+        <v>23</v>
+      </c>
+      <c r="H110">
+        <v>7.5</v>
+      </c>
       <c r="I110" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>SF</v>
       </c>
       <c r="J110" t="str">
         <f t="shared" si="11"/>
-        <v/>
+        <v>WAS</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D111" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="E111" s="16" t="str">
+      <c r="E111" s="16">
         <f>IF(AND(E110&lt;&gt;"",G110&lt;&gt;""),E110+G110,"")</f>
-        <v/>
+        <v>40</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29408,17 +29457,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -31806,7 +31855,7 @@
       </c>
       <c r="E81">
         <f>IFERROR(INDEX(C$81:C$92,MATCH(9,A$81:A$92,0)),0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F81" t="str">
         <f>IF(C81=0,"-",IF(C81&gt;E81,"W",IF(C81&lt;E81,"L",IF(AND('Picks Detail'!E114&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,A81)&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,D81)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A81)-'Picks Detail'!E114)&lt;ABS(INDEX('Picks Detail'!F114:Q114,1,D81)-'Picks Detail'!E114),"W",IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A81)-'Picks Detail'!E114)&gt;ABS(INDEX('Picks Detail'!F114:Q114,1,D81)-'Picks Detail'!E114),"L","T")),"T"))))</f>
@@ -31882,11 +31931,11 @@
       </c>
       <c r="F83" t="str">
         <f>IF(C83=0,"-",IF(C83&gt;E83,"W",IF(C83&lt;E83,"L",IF(AND('Picks Detail'!E114&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,A83)&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,D83)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A83)-'Picks Detail'!E114)&lt;ABS(INDEX('Picks Detail'!F114:Q114,1,D83)-'Picks Detail'!E114),"W",IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A83)-'Picks Detail'!E114)&gt;ABS(INDEX('Picks Detail'!F114:Q114,1,D83)-'Picks Detail'!E114),"L","T")),"T"))))</f>
-        <v>T</v>
+        <v>L</v>
       </c>
       <c r="G83">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H83">
         <f t="shared" si="16"/>
@@ -31894,7 +31943,7 @@
       </c>
       <c r="I83">
         <f t="shared" si="17"/>
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32026,11 +32075,11 @@
       </c>
       <c r="F87" t="str">
         <f>IF(C87=0,"-",IF(C87&gt;E87,"W",IF(C87&lt;E87,"L",IF(AND('Picks Detail'!E114&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,A87)&lt;&gt;"",INDEX('Picks Detail'!F114:Q114,1,D87)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A87)-'Picks Detail'!E114)&lt;ABS(INDEX('Picks Detail'!F114:Q114,1,D87)-'Picks Detail'!E114),"W",IF(ABS(INDEX('Picks Detail'!F114:Q114,1,A87)-'Picks Detail'!E114)&gt;ABS(INDEX('Picks Detail'!F114:Q114,1,D87)-'Picks Detail'!E114),"L","T")),"T"))))</f>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="G87">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H87">
         <f t="shared" si="16"/>
@@ -32038,7 +32087,7 @@
       </c>
       <c r="I87">
         <f t="shared" si="17"/>
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32087,7 +32136,7 @@
       </c>
       <c r="C89" s="3">
         <f>SUMPRODUCT(('Picks Detail'!N100:N113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!N100:N113='Picks Detail'!E100:E113))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -32106,11 +32155,11 @@
       </c>
       <c r="H89">
         <f t="shared" si="16"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I89">
         <f t="shared" si="17"/>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32241,17 +32290,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -35074,17 +35123,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -37907,19 +37956,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -38166,15 +38215,15 @@
       </c>
       <c r="H7">
         <f>Helper!H6</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I7">
         <f>Helper!I6</f>
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J7">
         <f>Helper!J6</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K7">
         <f>MAX(Helper!C6:H6)</f>
@@ -38256,15 +38305,15 @@
       </c>
       <c r="H9">
         <f>Helper!H8</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I9">
         <f>Helper!I8</f>
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="J9">
         <f>Helper!J8</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9">
         <f>MAX(Helper!C8:H8)</f>
@@ -38301,15 +38350,15 @@
       </c>
       <c r="H10">
         <f>Helper!H9</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I10">
         <f>Helper!I9</f>
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J10">
         <f>Helper!J9</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10">
         <f>MAX(Helper!C9:H9)</f>
@@ -38346,15 +38395,15 @@
       </c>
       <c r="H11">
         <f>Helper!H10</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I11">
         <f>Helper!I10</f>
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="J11">
         <f>Helper!J10</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11">
         <f>MAX(Helper!C10:H10)</f>
@@ -38391,15 +38440,15 @@
       </c>
       <c r="H12">
         <f>Helper!H11</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I12">
         <f>Helper!I11</f>
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="J12">
         <f>Helper!J11</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12">
         <f>MAX(Helper!C11:H11)</f>
@@ -38436,15 +38485,15 @@
       </c>
       <c r="H13">
         <f>Helper!H12</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I13">
         <f>Helper!I12</f>
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J13">
         <f>Helper!J12</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13">
         <f>MAX(Helper!C12:H12)</f>
@@ -39941,7 +39990,7 @@
       </c>
       <c r="C61">
         <f>Helper!I6</f>
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D61">
         <f>Helper!R6</f>
@@ -39953,11 +40002,11 @@
       </c>
       <c r="F61">
         <f>Helper!AE6</f>
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G61">
         <f>Helper!K6</f>
-        <v>65.000500000000002</v>
+        <v>71.000500000000002</v>
       </c>
       <c r="H61">
         <f>Helper!T6</f>
@@ -40007,7 +40056,7 @@
       </c>
       <c r="C63">
         <f>Helper!I8</f>
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D63">
         <f>Helper!R8</f>
@@ -40019,11 +40068,11 @@
       </c>
       <c r="F63">
         <f>Helper!AE8</f>
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G63">
         <f>Helper!K8</f>
-        <v>53.000700000000002</v>
+        <v>59.000700000000002</v>
       </c>
       <c r="H63">
         <f>Helper!T8</f>
@@ -40040,7 +40089,7 @@
       </c>
       <c r="C64">
         <f>Helper!I9</f>
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D64">
         <f>Helper!R9</f>
@@ -40052,11 +40101,11 @@
       </c>
       <c r="F64">
         <f>Helper!AE9</f>
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G64">
         <f>Helper!K9</f>
-        <v>50.000799999999998</v>
+        <v>56.000799999999998</v>
       </c>
       <c r="H64">
         <f>Helper!T9</f>
@@ -40073,7 +40122,7 @@
       </c>
       <c r="C65">
         <f>Helper!I10</f>
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D65">
         <f>Helper!R10</f>
@@ -40085,11 +40134,11 @@
       </c>
       <c r="F65">
         <f>Helper!AE10</f>
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G65">
         <f>Helper!K10</f>
-        <v>49.000900000000001</v>
+        <v>56.000900000000001</v>
       </c>
       <c r="H65">
         <f>Helper!T10</f>
@@ -40106,7 +40155,7 @@
       </c>
       <c r="C66">
         <f>Helper!I11</f>
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D66">
         <f>Helper!R11</f>
@@ -40118,11 +40167,11 @@
       </c>
       <c r="F66">
         <f>Helper!AE11</f>
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G66">
         <f>Helper!K11</f>
-        <v>62.000999999999998</v>
+        <v>68.001000000000005</v>
       </c>
       <c r="H66">
         <f>Helper!T11</f>
@@ -40139,7 +40188,7 @@
       </c>
       <c r="C67">
         <f>Helper!I12</f>
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D67">
         <f>Helper!R12</f>
@@ -40151,11 +40200,11 @@
       </c>
       <c r="F67">
         <f>Helper!AE12</f>
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G67">
         <f>Helper!K12</f>
-        <v>54.001100000000001</v>
+        <v>60.001100000000001</v>
       </c>
       <c r="H67">
         <f>Helper!T12</f>
@@ -40258,7 +40307,7 @@
       </c>
       <c r="B5" t="str">
         <f>INDEX(Helper!B$2:B$13,MATCH(MAX(Helper!K$2:K$13),Helper!K$2:K$13,0))</f>
-        <v>Chris Simmons</v>
+        <v>Mikayla Simmons</v>
       </c>
       <c r="C5" t="s">
         <v>252</v>
@@ -40268,7 +40317,7 @@
       </c>
       <c r="E5" t="str">
         <f>B5</f>
-        <v>Chris Simmons</v>
+        <v>Mikayla Simmons</v>
       </c>
       <c r="F5" t="str">
         <f>IF(B5="","—","QUALIFIED")</f>
@@ -40426,7 +40475,7 @@
       </c>
       <c r="B13" t="str">
         <f>INDEX(H$40:H$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
-        <v>Evan Loeser</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="C13">
         <f>INDEX(I$40:I$51,MATCH(MAX(K$40:K$51),K$40:K$51,0))</f>
@@ -40476,7 +40525,7 @@
       </c>
       <c r="B17" t="str">
         <f>E5</f>
-        <v>Chris Simmons</v>
+        <v>Mikayla Simmons</v>
       </c>
       <c r="C17" t="str">
         <f>D5</f>
@@ -40541,7 +40590,7 @@
       </c>
       <c r="B22" t="str">
         <f>B13</f>
-        <v>Evan Loeser</v>
+        <v>Zach Zarra</v>
       </c>
       <c r="C22" t="str">
         <f>"Wild Card 1"</f>
@@ -40683,7 +40732,7 @@
       </c>
       <c r="C30">
         <f>IF(Roster!$B$16&gt;=7,IF(Roster!B7=$B$5,25,0),0)+IF(Roster!$B$16&gt;=13,IF(Roster!B7=$B$6,25,0),0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D30">
         <f>IF(Roster!$B$16&gt;=19,IF(Roster!B7=$B$7,10,0)+IF(Roster!B7=$B$8,10,0)+IF(Roster!B7=$B$9,10,0),0)</f>
@@ -40695,7 +40744,7 @@
       </c>
       <c r="F30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40879,7 +40928,7 @@
       </c>
       <c r="C38">
         <f>SUM(C26:C37)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D38">
         <f>SUM(D26:D37)</f>
@@ -40891,7 +40940,7 @@
       </c>
       <c r="F38">
         <f>SUM(F26:F37)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40928,11 +40977,11 @@
       </c>
       <c r="J41" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41">
         <f>IF(J41,-1,I41+0.00002)</f>
-        <v>-1</v>
+        <v>68.000020000000006</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40978,15 +41027,15 @@
       </c>
       <c r="I44">
         <f>Helper!AE6</f>
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J44" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44">
         <f>IF(J44,-1,I44+0.00005)</f>
-        <v>65.000050000000002</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41014,7 +41063,7 @@
       </c>
       <c r="I46">
         <f>Helper!AE8</f>
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="J46" t="b">
         <f t="shared" si="1"/>
@@ -41022,7 +41071,7 @@
       </c>
       <c r="K46">
         <f>IF(J46,-1,I46+0.00007)</f>
-        <v>53.000070000000001</v>
+        <v>59.000070000000001</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41032,7 +41081,7 @@
       </c>
       <c r="I47">
         <f>Helper!AE9</f>
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J47" t="b">
         <f t="shared" si="1"/>
@@ -41050,7 +41099,7 @@
       </c>
       <c r="I48">
         <f>Helper!AE10</f>
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="J48" t="b">
         <f t="shared" si="1"/>
@@ -41058,7 +41107,7 @@
       </c>
       <c r="K48">
         <f>IF(J48,-1,I48+0.00009)</f>
-        <v>49.00009</v>
+        <v>56.00009</v>
       </c>
     </row>
     <row r="49" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41068,7 +41117,7 @@
       </c>
       <c r="I49">
         <f>Helper!AE11</f>
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="J49" t="b">
         <f t="shared" si="1"/>
@@ -41076,7 +41125,7 @@
       </c>
       <c r="K49">
         <f>IF(J49,-1,I49+0.0001)</f>
-        <v>62.000100000000003</v>
+        <v>68.000100000000003</v>
       </c>
     </row>
     <row r="50" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41086,7 +41135,7 @@
       </c>
       <c r="I50">
         <f>Helper!AE12</f>
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J50" t="b">
         <f t="shared" si="1"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{9DE1E4DF-9D2F-41C3-82DE-6EA75B0925C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A07085-08BC-419C-BFB0-2E79FB4E6512}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{9DE1E4DF-9D2F-41C3-82DE-6EA75B0925C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7136F83-DF11-402D-BC63-46F541BB18AB}"/>
   <bookViews>
-    <workbookView xWindow="29400" yWindow="-120" windowWidth="28320" windowHeight="16440" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29400" yWindow="-120" windowWidth="28320" windowHeight="16440" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1430,9 +1430,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1702,6 +1702,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -7513,67 +7517,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8541,25 +8545,25 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="25"/>
-      <c r="N23" s="25"/>
-      <c r="O23" s="25"/>
-      <c r="P23" s="25"/>
-      <c r="Q23" s="25"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
+      <c r="O23" s="27"/>
+      <c r="P23" s="27"/>
+      <c r="Q23" s="27"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -9527,25 +9531,25 @@
       </c>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="25" t="s">
+      <c r="A42" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
-      <c r="I42" s="25"/>
-      <c r="J42" s="25"/>
-      <c r="K42" s="25"/>
-      <c r="L42" s="25"/>
-      <c r="M42" s="25"/>
-      <c r="N42" s="25"/>
-      <c r="O42" s="25"/>
-      <c r="P42" s="25"/>
-      <c r="Q42" s="25"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="27"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27"/>
+      <c r="I42" s="27"/>
+      <c r="J42" s="27"/>
+      <c r="K42" s="27"/>
+      <c r="L42" s="27"/>
+      <c r="M42" s="27"/>
+      <c r="N42" s="27"/>
+      <c r="O42" s="27"/>
+      <c r="P42" s="27"/>
+      <c r="Q42" s="27"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -10475,25 +10479,25 @@
       </c>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="25" t="s">
+      <c r="A61" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="25"/>
-      <c r="C61" s="25"/>
-      <c r="D61" s="25"/>
-      <c r="E61" s="25"/>
-      <c r="F61" s="25"/>
-      <c r="G61" s="25"/>
-      <c r="H61" s="25"/>
-      <c r="I61" s="25"/>
-      <c r="J61" s="25"/>
-      <c r="K61" s="25"/>
-      <c r="L61" s="25"/>
-      <c r="M61" s="25"/>
-      <c r="N61" s="25"/>
-      <c r="O61" s="25"/>
-      <c r="P61" s="25"/>
-      <c r="Q61" s="25"/>
+      <c r="B61" s="27"/>
+      <c r="C61" s="27"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="27"/>
+      <c r="G61" s="27"/>
+      <c r="H61" s="27"/>
+      <c r="I61" s="27"/>
+      <c r="J61" s="27"/>
+      <c r="K61" s="27"/>
+      <c r="L61" s="27"/>
+      <c r="M61" s="27"/>
+      <c r="N61" s="27"/>
+      <c r="O61" s="27"/>
+      <c r="P61" s="27"/>
+      <c r="Q61" s="27"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -11461,25 +11465,25 @@
       </c>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="25" t="s">
+      <c r="A80" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="25"/>
-      <c r="C80" s="25"/>
-      <c r="D80" s="25"/>
-      <c r="E80" s="25"/>
-      <c r="F80" s="25"/>
-      <c r="G80" s="25"/>
-      <c r="H80" s="25"/>
-      <c r="I80" s="25"/>
-      <c r="J80" s="25"/>
-      <c r="K80" s="25"/>
-      <c r="L80" s="25"/>
-      <c r="M80" s="25"/>
-      <c r="N80" s="25"/>
-      <c r="O80" s="25"/>
-      <c r="P80" s="25"/>
-      <c r="Q80" s="25"/>
+      <c r="B80" s="27"/>
+      <c r="C80" s="27"/>
+      <c r="D80" s="27"/>
+      <c r="E80" s="27"/>
+      <c r="F80" s="27"/>
+      <c r="G80" s="27"/>
+      <c r="H80" s="27"/>
+      <c r="I80" s="27"/>
+      <c r="J80" s="27"/>
+      <c r="K80" s="27"/>
+      <c r="L80" s="27"/>
+      <c r="M80" s="27"/>
+      <c r="N80" s="27"/>
+      <c r="O80" s="27"/>
+      <c r="P80" s="27"/>
+      <c r="Q80" s="27"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -12353,25 +12357,25 @@
       </c>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="25" t="s">
+      <c r="A98" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="25"/>
-      <c r="C98" s="25"/>
-      <c r="D98" s="25"/>
-      <c r="E98" s="25"/>
-      <c r="F98" s="25"/>
-      <c r="G98" s="25"/>
-      <c r="H98" s="25"/>
-      <c r="I98" s="25"/>
-      <c r="J98" s="25"/>
-      <c r="K98" s="25"/>
-      <c r="L98" s="25"/>
-      <c r="M98" s="25"/>
-      <c r="N98" s="25"/>
-      <c r="O98" s="25"/>
-      <c r="P98" s="25"/>
-      <c r="Q98" s="25"/>
+      <c r="B98" s="27"/>
+      <c r="C98" s="27"/>
+      <c r="D98" s="27"/>
+      <c r="E98" s="27"/>
+      <c r="F98" s="27"/>
+      <c r="G98" s="27"/>
+      <c r="H98" s="27"/>
+      <c r="I98" s="27"/>
+      <c r="J98" s="27"/>
+      <c r="K98" s="27"/>
+      <c r="L98" s="27"/>
+      <c r="M98" s="27"/>
+      <c r="N98" s="27"/>
+      <c r="O98" s="27"/>
+      <c r="P98" s="27"/>
+      <c r="Q98" s="27"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -13195,39 +13199,39 @@
       </c>
     </row>
     <row r="115" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="25" t="s">
+      <c r="A115" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="25"/>
-      <c r="C115" s="25"/>
-      <c r="D115" s="25"/>
-      <c r="E115" s="25"/>
-      <c r="F115" s="25"/>
-      <c r="G115" s="25"/>
-      <c r="H115" s="25"/>
-      <c r="I115" s="25"/>
-      <c r="J115" s="25"/>
-      <c r="K115" s="25"/>
-      <c r="L115" s="25"/>
-      <c r="M115" s="25"/>
-      <c r="N115" s="25"/>
-      <c r="O115" s="25"/>
-      <c r="P115" s="25"/>
-      <c r="Q115" s="25"/>
-      <c r="S115" s="25" t="s">
+      <c r="B115" s="27"/>
+      <c r="C115" s="27"/>
+      <c r="D115" s="27"/>
+      <c r="E115" s="27"/>
+      <c r="F115" s="27"/>
+      <c r="G115" s="27"/>
+      <c r="H115" s="27"/>
+      <c r="I115" s="27"/>
+      <c r="J115" s="27"/>
+      <c r="K115" s="27"/>
+      <c r="L115" s="27"/>
+      <c r="M115" s="27"/>
+      <c r="N115" s="27"/>
+      <c r="O115" s="27"/>
+      <c r="P115" s="27"/>
+      <c r="Q115" s="27"/>
+      <c r="S115" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="T115" s="25"/>
-      <c r="U115" s="25"/>
-      <c r="V115" s="25"/>
-      <c r="W115" s="25"/>
-      <c r="X115" s="25"/>
-      <c r="Y115" s="25"/>
-      <c r="Z115" s="25"/>
-      <c r="AA115" s="25"/>
-      <c r="AB115" s="25"/>
-      <c r="AC115" s="25"/>
-      <c r="AD115" s="25"/>
+      <c r="T115" s="27"/>
+      <c r="U115" s="27"/>
+      <c r="V115" s="27"/>
+      <c r="W115" s="27"/>
+      <c r="X115" s="27"/>
+      <c r="Y115" s="27"/>
+      <c r="Z115" s="27"/>
+      <c r="AA115" s="27"/>
+      <c r="AB115" s="27"/>
+      <c r="AC115" s="27"/>
+      <c r="AD115" s="27"/>
     </row>
     <row r="116" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -13333,7 +13337,7 @@
       </c>
       <c r="E117" s="9" t="str">
         <f>'NFL Schedule'!J114</f>
-        <v/>
+        <v>NE</v>
       </c>
       <c r="F117" s="10"/>
       <c r="G117" s="10"/>
@@ -13979,39 +13983,39 @@
       </c>
     </row>
     <row r="132" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="25" t="s">
+      <c r="A132" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="B132" s="25"/>
-      <c r="C132" s="25"/>
-      <c r="D132" s="25"/>
-      <c r="E132" s="25"/>
-      <c r="F132" s="25"/>
-      <c r="G132" s="25"/>
-      <c r="H132" s="25"/>
-      <c r="I132" s="25"/>
-      <c r="J132" s="25"/>
-      <c r="K132" s="25"/>
-      <c r="L132" s="25"/>
-      <c r="M132" s="25"/>
-      <c r="N132" s="25"/>
-      <c r="O132" s="25"/>
-      <c r="P132" s="25"/>
-      <c r="Q132" s="25"/>
-      <c r="S132" s="25" t="s">
+      <c r="B132" s="27"/>
+      <c r="C132" s="27"/>
+      <c r="D132" s="27"/>
+      <c r="E132" s="27"/>
+      <c r="F132" s="27"/>
+      <c r="G132" s="27"/>
+      <c r="H132" s="27"/>
+      <c r="I132" s="27"/>
+      <c r="J132" s="27"/>
+      <c r="K132" s="27"/>
+      <c r="L132" s="27"/>
+      <c r="M132" s="27"/>
+      <c r="N132" s="27"/>
+      <c r="O132" s="27"/>
+      <c r="P132" s="27"/>
+      <c r="Q132" s="27"/>
+      <c r="S132" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="T132" s="25"/>
-      <c r="U132" s="25"/>
-      <c r="V132" s="25"/>
-      <c r="W132" s="25"/>
-      <c r="X132" s="25"/>
-      <c r="Y132" s="25"/>
-      <c r="Z132" s="25"/>
-      <c r="AA132" s="25"/>
-      <c r="AB132" s="25"/>
-      <c r="AC132" s="25"/>
-      <c r="AD132" s="25"/>
+      <c r="T132" s="27"/>
+      <c r="U132" s="27"/>
+      <c r="V132" s="27"/>
+      <c r="W132" s="27"/>
+      <c r="X132" s="27"/>
+      <c r="Y132" s="27"/>
+      <c r="Z132" s="27"/>
+      <c r="AA132" s="27"/>
+      <c r="AB132" s="27"/>
+      <c r="AC132" s="27"/>
+      <c r="AD132" s="27"/>
     </row>
     <row r="133" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -14763,39 +14767,39 @@
       </c>
     </row>
     <row r="149" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="25" t="s">
+      <c r="A149" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="B149" s="25"/>
-      <c r="C149" s="25"/>
-      <c r="D149" s="25"/>
-      <c r="E149" s="25"/>
-      <c r="F149" s="25"/>
-      <c r="G149" s="25"/>
-      <c r="H149" s="25"/>
-      <c r="I149" s="25"/>
-      <c r="J149" s="25"/>
-      <c r="K149" s="25"/>
-      <c r="L149" s="25"/>
-      <c r="M149" s="25"/>
-      <c r="N149" s="25"/>
-      <c r="O149" s="25"/>
-      <c r="P149" s="25"/>
-      <c r="Q149" s="25"/>
-      <c r="S149" s="25" t="s">
+      <c r="B149" s="27"/>
+      <c r="C149" s="27"/>
+      <c r="D149" s="27"/>
+      <c r="E149" s="27"/>
+      <c r="F149" s="27"/>
+      <c r="G149" s="27"/>
+      <c r="H149" s="27"/>
+      <c r="I149" s="27"/>
+      <c r="J149" s="27"/>
+      <c r="K149" s="27"/>
+      <c r="L149" s="27"/>
+      <c r="M149" s="27"/>
+      <c r="N149" s="27"/>
+      <c r="O149" s="27"/>
+      <c r="P149" s="27"/>
+      <c r="Q149" s="27"/>
+      <c r="S149" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="T149" s="25"/>
-      <c r="U149" s="25"/>
-      <c r="V149" s="25"/>
-      <c r="W149" s="25"/>
-      <c r="X149" s="25"/>
-      <c r="Y149" s="25"/>
-      <c r="Z149" s="25"/>
-      <c r="AA149" s="25"/>
-      <c r="AB149" s="25"/>
-      <c r="AC149" s="25"/>
-      <c r="AD149" s="25"/>
+      <c r="T149" s="27"/>
+      <c r="U149" s="27"/>
+      <c r="V149" s="27"/>
+      <c r="W149" s="27"/>
+      <c r="X149" s="27"/>
+      <c r="Y149" s="27"/>
+      <c r="Z149" s="27"/>
+      <c r="AA149" s="27"/>
+      <c r="AB149" s="27"/>
+      <c r="AC149" s="27"/>
+      <c r="AD149" s="27"/>
     </row>
     <row r="150" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -15589,39 +15593,39 @@
       </c>
     </row>
     <row r="167" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="25" t="s">
+      <c r="A167" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="B167" s="25"/>
-      <c r="C167" s="25"/>
-      <c r="D167" s="25"/>
-      <c r="E167" s="25"/>
-      <c r="F167" s="25"/>
-      <c r="G167" s="25"/>
-      <c r="H167" s="25"/>
-      <c r="I167" s="25"/>
-      <c r="J167" s="25"/>
-      <c r="K167" s="25"/>
-      <c r="L167" s="25"/>
-      <c r="M167" s="25"/>
-      <c r="N167" s="25"/>
-      <c r="O167" s="25"/>
-      <c r="P167" s="25"/>
-      <c r="Q167" s="25"/>
-      <c r="S167" s="25" t="s">
+      <c r="B167" s="27"/>
+      <c r="C167" s="27"/>
+      <c r="D167" s="27"/>
+      <c r="E167" s="27"/>
+      <c r="F167" s="27"/>
+      <c r="G167" s="27"/>
+      <c r="H167" s="27"/>
+      <c r="I167" s="27"/>
+      <c r="J167" s="27"/>
+      <c r="K167" s="27"/>
+      <c r="L167" s="27"/>
+      <c r="M167" s="27"/>
+      <c r="N167" s="27"/>
+      <c r="O167" s="27"/>
+      <c r="P167" s="27"/>
+      <c r="Q167" s="27"/>
+      <c r="S167" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="T167" s="25"/>
-      <c r="U167" s="25"/>
-      <c r="V167" s="25"/>
-      <c r="W167" s="25"/>
-      <c r="X167" s="25"/>
-      <c r="Y167" s="25"/>
-      <c r="Z167" s="25"/>
-      <c r="AA167" s="25"/>
-      <c r="AB167" s="25"/>
-      <c r="AC167" s="25"/>
-      <c r="AD167" s="25"/>
+      <c r="T167" s="27"/>
+      <c r="U167" s="27"/>
+      <c r="V167" s="27"/>
+      <c r="W167" s="27"/>
+      <c r="X167" s="27"/>
+      <c r="Y167" s="27"/>
+      <c r="Z167" s="27"/>
+      <c r="AA167" s="27"/>
+      <c r="AB167" s="27"/>
+      <c r="AC167" s="27"/>
+      <c r="AD167" s="27"/>
     </row>
     <row r="168" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -16373,39 +16377,39 @@
       </c>
     </row>
     <row r="184" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="25" t="s">
+      <c r="A184" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="B184" s="25"/>
-      <c r="C184" s="25"/>
-      <c r="D184" s="25"/>
-      <c r="E184" s="25"/>
-      <c r="F184" s="25"/>
-      <c r="G184" s="25"/>
-      <c r="H184" s="25"/>
-      <c r="I184" s="25"/>
-      <c r="J184" s="25"/>
-      <c r="K184" s="25"/>
-      <c r="L184" s="25"/>
-      <c r="M184" s="25"/>
-      <c r="N184" s="25"/>
-      <c r="O184" s="25"/>
-      <c r="P184" s="25"/>
-      <c r="Q184" s="25"/>
-      <c r="S184" s="25" t="s">
+      <c r="B184" s="27"/>
+      <c r="C184" s="27"/>
+      <c r="D184" s="27"/>
+      <c r="E184" s="27"/>
+      <c r="F184" s="27"/>
+      <c r="G184" s="27"/>
+      <c r="H184" s="27"/>
+      <c r="I184" s="27"/>
+      <c r="J184" s="27"/>
+      <c r="K184" s="27"/>
+      <c r="L184" s="27"/>
+      <c r="M184" s="27"/>
+      <c r="N184" s="27"/>
+      <c r="O184" s="27"/>
+      <c r="P184" s="27"/>
+      <c r="Q184" s="27"/>
+      <c r="S184" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="T184" s="25"/>
-      <c r="U184" s="25"/>
-      <c r="V184" s="25"/>
-      <c r="W184" s="25"/>
-      <c r="X184" s="25"/>
-      <c r="Y184" s="25"/>
-      <c r="Z184" s="25"/>
-      <c r="AA184" s="25"/>
-      <c r="AB184" s="25"/>
-      <c r="AC184" s="25"/>
-      <c r="AD184" s="25"/>
+      <c r="T184" s="27"/>
+      <c r="U184" s="27"/>
+      <c r="V184" s="27"/>
+      <c r="W184" s="27"/>
+      <c r="X184" s="27"/>
+      <c r="Y184" s="27"/>
+      <c r="Z184" s="27"/>
+      <c r="AA184" s="27"/>
+      <c r="AB184" s="27"/>
+      <c r="AC184" s="27"/>
+      <c r="AD184" s="27"/>
     </row>
     <row r="185" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -17115,39 +17119,39 @@
       </c>
     </row>
     <row r="200" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="25" t="s">
+      <c r="A200" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="B200" s="25"/>
-      <c r="C200" s="25"/>
-      <c r="D200" s="25"/>
-      <c r="E200" s="25"/>
-      <c r="F200" s="25"/>
-      <c r="G200" s="25"/>
-      <c r="H200" s="25"/>
-      <c r="I200" s="25"/>
-      <c r="J200" s="25"/>
-      <c r="K200" s="25"/>
-      <c r="L200" s="25"/>
-      <c r="M200" s="25"/>
-      <c r="N200" s="25"/>
-      <c r="O200" s="25"/>
-      <c r="P200" s="25"/>
-      <c r="Q200" s="25"/>
-      <c r="S200" s="25" t="s">
+      <c r="B200" s="27"/>
+      <c r="C200" s="27"/>
+      <c r="D200" s="27"/>
+      <c r="E200" s="27"/>
+      <c r="F200" s="27"/>
+      <c r="G200" s="27"/>
+      <c r="H200" s="27"/>
+      <c r="I200" s="27"/>
+      <c r="J200" s="27"/>
+      <c r="K200" s="27"/>
+      <c r="L200" s="27"/>
+      <c r="M200" s="27"/>
+      <c r="N200" s="27"/>
+      <c r="O200" s="27"/>
+      <c r="P200" s="27"/>
+      <c r="Q200" s="27"/>
+      <c r="S200" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="T200" s="25"/>
-      <c r="U200" s="25"/>
-      <c r="V200" s="25"/>
-      <c r="W200" s="25"/>
-      <c r="X200" s="25"/>
-      <c r="Y200" s="25"/>
-      <c r="Z200" s="25"/>
-      <c r="AA200" s="25"/>
-      <c r="AB200" s="25"/>
-      <c r="AC200" s="25"/>
-      <c r="AD200" s="25"/>
+      <c r="T200" s="27"/>
+      <c r="U200" s="27"/>
+      <c r="V200" s="27"/>
+      <c r="W200" s="27"/>
+      <c r="X200" s="27"/>
+      <c r="Y200" s="27"/>
+      <c r="Z200" s="27"/>
+      <c r="AA200" s="27"/>
+      <c r="AB200" s="27"/>
+      <c r="AC200" s="27"/>
+      <c r="AD200" s="27"/>
     </row>
     <row r="201" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -17983,25 +17987,25 @@
       </c>
     </row>
     <row r="219" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="25" t="s">
+      <c r="A219" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="B219" s="25"/>
-      <c r="C219" s="25"/>
-      <c r="D219" s="25"/>
-      <c r="E219" s="25"/>
-      <c r="F219" s="25"/>
-      <c r="G219" s="25"/>
-      <c r="H219" s="25"/>
-      <c r="I219" s="25"/>
-      <c r="J219" s="25"/>
-      <c r="K219" s="25"/>
-      <c r="L219" s="25"/>
-      <c r="M219" s="25"/>
-      <c r="N219" s="25"/>
-      <c r="O219" s="25"/>
-      <c r="P219" s="25"/>
-      <c r="Q219" s="25"/>
+      <c r="B219" s="27"/>
+      <c r="C219" s="27"/>
+      <c r="D219" s="27"/>
+      <c r="E219" s="27"/>
+      <c r="F219" s="27"/>
+      <c r="G219" s="27"/>
+      <c r="H219" s="27"/>
+      <c r="I219" s="27"/>
+      <c r="J219" s="27"/>
+      <c r="K219" s="27"/>
+      <c r="L219" s="27"/>
+      <c r="M219" s="27"/>
+      <c r="N219" s="27"/>
+      <c r="O219" s="27"/>
+      <c r="P219" s="27"/>
+      <c r="Q219" s="27"/>
     </row>
     <row r="220" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -18501,25 +18505,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="25" t="s">
+      <c r="A236" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="B236" s="25"/>
-      <c r="C236" s="25"/>
-      <c r="D236" s="25"/>
-      <c r="E236" s="25"/>
-      <c r="F236" s="25"/>
-      <c r="G236" s="25"/>
-      <c r="H236" s="25"/>
-      <c r="I236" s="25"/>
-      <c r="J236" s="25"/>
-      <c r="K236" s="25"/>
-      <c r="L236" s="25"/>
-      <c r="M236" s="25"/>
-      <c r="N236" s="25"/>
-      <c r="O236" s="25"/>
-      <c r="P236" s="25"/>
-      <c r="Q236" s="25"/>
+      <c r="B236" s="27"/>
+      <c r="C236" s="27"/>
+      <c r="D236" s="27"/>
+      <c r="E236" s="27"/>
+      <c r="F236" s="27"/>
+      <c r="G236" s="27"/>
+      <c r="H236" s="27"/>
+      <c r="I236" s="27"/>
+      <c r="J236" s="27"/>
+      <c r="K236" s="27"/>
+      <c r="L236" s="27"/>
+      <c r="M236" s="27"/>
+      <c r="N236" s="27"/>
+      <c r="O236" s="27"/>
+      <c r="P236" s="27"/>
+      <c r="Q236" s="27"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -19049,25 +19053,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="25" t="s">
+      <c r="A254" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="B254" s="25"/>
-      <c r="C254" s="25"/>
-      <c r="D254" s="25"/>
-      <c r="E254" s="25"/>
-      <c r="F254" s="25"/>
-      <c r="G254" s="25"/>
-      <c r="H254" s="25"/>
-      <c r="I254" s="25"/>
-      <c r="J254" s="25"/>
-      <c r="K254" s="25"/>
-      <c r="L254" s="25"/>
-      <c r="M254" s="25"/>
-      <c r="N254" s="25"/>
-      <c r="O254" s="25"/>
-      <c r="P254" s="25"/>
-      <c r="Q254" s="25"/>
+      <c r="B254" s="27"/>
+      <c r="C254" s="27"/>
+      <c r="D254" s="27"/>
+      <c r="E254" s="27"/>
+      <c r="F254" s="27"/>
+      <c r="G254" s="27"/>
+      <c r="H254" s="27"/>
+      <c r="I254" s="27"/>
+      <c r="J254" s="27"/>
+      <c r="K254" s="27"/>
+      <c r="L254" s="27"/>
+      <c r="M254" s="27"/>
+      <c r="N254" s="27"/>
+      <c r="O254" s="27"/>
+      <c r="P254" s="27"/>
+      <c r="Q254" s="27"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -19627,25 +19631,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="25" t="s">
+      <c r="A273" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="B273" s="25"/>
-      <c r="C273" s="25"/>
-      <c r="D273" s="25"/>
-      <c r="E273" s="25"/>
-      <c r="F273" s="25"/>
-      <c r="G273" s="25"/>
-      <c r="H273" s="25"/>
-      <c r="I273" s="25"/>
-      <c r="J273" s="25"/>
-      <c r="K273" s="25"/>
-      <c r="L273" s="25"/>
-      <c r="M273" s="25"/>
-      <c r="N273" s="25"/>
-      <c r="O273" s="25"/>
-      <c r="P273" s="25"/>
-      <c r="Q273" s="25"/>
+      <c r="B273" s="27"/>
+      <c r="C273" s="27"/>
+      <c r="D273" s="27"/>
+      <c r="E273" s="27"/>
+      <c r="F273" s="27"/>
+      <c r="G273" s="27"/>
+      <c r="H273" s="27"/>
+      <c r="I273" s="27"/>
+      <c r="J273" s="27"/>
+      <c r="K273" s="27"/>
+      <c r="L273" s="27"/>
+      <c r="M273" s="27"/>
+      <c r="N273" s="27"/>
+      <c r="O273" s="27"/>
+      <c r="P273" s="27"/>
+      <c r="Q273" s="27"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -20205,25 +20209,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="25" t="s">
+      <c r="A292" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="B292" s="25"/>
-      <c r="C292" s="25"/>
-      <c r="D292" s="25"/>
-      <c r="E292" s="25"/>
-      <c r="F292" s="25"/>
-      <c r="G292" s="25"/>
-      <c r="H292" s="25"/>
-      <c r="I292" s="25"/>
-      <c r="J292" s="25"/>
-      <c r="K292" s="25"/>
-      <c r="L292" s="25"/>
-      <c r="M292" s="25"/>
-      <c r="N292" s="25"/>
-      <c r="O292" s="25"/>
-      <c r="P292" s="25"/>
-      <c r="Q292" s="25"/>
+      <c r="B292" s="27"/>
+      <c r="C292" s="27"/>
+      <c r="D292" s="27"/>
+      <c r="E292" s="27"/>
+      <c r="F292" s="27"/>
+      <c r="G292" s="27"/>
+      <c r="H292" s="27"/>
+      <c r="I292" s="27"/>
+      <c r="J292" s="27"/>
+      <c r="K292" s="27"/>
+      <c r="L292" s="27"/>
+      <c r="M292" s="27"/>
+      <c r="N292" s="27"/>
+      <c r="O292" s="27"/>
+      <c r="P292" s="27"/>
+      <c r="Q292" s="27"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -20783,25 +20787,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="25" t="s">
+      <c r="A311" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="B311" s="25"/>
-      <c r="C311" s="25"/>
-      <c r="D311" s="25"/>
-      <c r="E311" s="25"/>
-      <c r="F311" s="25"/>
-      <c r="G311" s="25"/>
-      <c r="H311" s="25"/>
-      <c r="I311" s="25"/>
-      <c r="J311" s="25"/>
-      <c r="K311" s="25"/>
-      <c r="L311" s="25"/>
-      <c r="M311" s="25"/>
-      <c r="N311" s="25"/>
-      <c r="O311" s="25"/>
-      <c r="P311" s="25"/>
-      <c r="Q311" s="25"/>
+      <c r="B311" s="27"/>
+      <c r="C311" s="27"/>
+      <c r="D311" s="27"/>
+      <c r="E311" s="27"/>
+      <c r="F311" s="27"/>
+      <c r="G311" s="27"/>
+      <c r="H311" s="27"/>
+      <c r="I311" s="27"/>
+      <c r="J311" s="27"/>
+      <c r="K311" s="27"/>
+      <c r="L311" s="27"/>
+      <c r="M311" s="27"/>
+      <c r="N311" s="27"/>
+      <c r="O311" s="27"/>
+      <c r="P311" s="27"/>
+      <c r="Q311" s="27"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -21362,32 +21366,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="A23:Q23"/>
-    <mergeCell ref="A42:Q42"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="S115:AD115"/>
+    <mergeCell ref="A236:Q236"/>
+    <mergeCell ref="A254:Q254"/>
+    <mergeCell ref="A273:Q273"/>
+    <mergeCell ref="A292:Q292"/>
+    <mergeCell ref="A311:Q311"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="S184:AD184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="S200:AD200"/>
+    <mergeCell ref="A219:Q219"/>
     <mergeCell ref="A132:Q132"/>
     <mergeCell ref="S132:AD132"/>
     <mergeCell ref="A149:Q149"/>
     <mergeCell ref="S149:AD149"/>
     <mergeCell ref="A167:Q167"/>
     <mergeCell ref="S167:AD167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="S184:AD184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="S200:AD200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A236:Q236"/>
-    <mergeCell ref="A254:Q254"/>
-    <mergeCell ref="A273:Q273"/>
-    <mergeCell ref="A292:Q292"/>
-    <mergeCell ref="A311:Q311"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="S115:AD115"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A23:Q23"/>
+    <mergeCell ref="A42:Q42"/>
   </mergeCells>
   <conditionalFormatting sqref="S117:AD130">
     <cfRule type="expression" dxfId="23" priority="2">
@@ -26084,16 +26088,25 @@
       <c r="D114" t="s">
         <v>57</v>
       </c>
+      <c r="E114">
+        <v>15</v>
+      </c>
       <c r="F114" t="s">
         <v>61</v>
       </c>
+      <c r="G114">
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <v>23</v>
+      </c>
       <c r="I114" t="str">
         <f t="shared" ref="I114:I127" si="12">IF(OR(E114="",G114=""),"",IF(E114&gt;G114,D114,IF(G114&gt;E114,F114,"TIE")))</f>
-        <v/>
+        <v>NE</v>
       </c>
       <c r="J114" t="str">
         <f t="shared" ref="J114:J127" si="13">IF(OR(E114="",G114="",H114=""),"",IF(E114+H114&gt;G114,D114,IF(E114+H114&lt;G114,F114,"PUSH")))</f>
-        <v/>
+        <v>NE</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{9DE1E4DF-9D2F-41C3-82DE-6EA75B0925C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7136F83-DF11-402D-BC63-46F541BB18AB}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{9DE1E4DF-9D2F-41C3-82DE-6EA75B0925C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DAA369C-AF5F-4C27-BAA1-05D5AA990CA3}"/>
   <bookViews>
     <workbookView xWindow="29400" yWindow="-120" windowWidth="28320" windowHeight="16440" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1426,13 +1426,13 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1895,12 +1895,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
+      <c r="A1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -4632,14 +4632,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -5584,14 +5584,14 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
+      <c r="B56" s="24"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="24"/>
+      <c r="E56" s="24"/>
+      <c r="F56" s="24"/>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
@@ -6536,14 +6536,14 @@
       </c>
     </row>
     <row r="111" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="23" t="s">
+      <c r="A111" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="B111" s="23"/>
-      <c r="C111" s="23"/>
-      <c r="D111" s="23"/>
-      <c r="E111" s="23"/>
-      <c r="F111" s="23"/>
+      <c r="B111" s="24"/>
+      <c r="C111" s="24"/>
+      <c r="D111" s="24"/>
+      <c r="E111" s="24"/>
+      <c r="F111" s="24"/>
     </row>
     <row r="112" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
@@ -7517,67 +7517,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="25"/>
+      <c r="P4" s="25"/>
+      <c r="Q4" s="25"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8545,25 +8545,25 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="27"/>
-      <c r="Q23" s="27"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="25"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="25"/>
+      <c r="P23" s="25"/>
+      <c r="Q23" s="25"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -9531,25 +9531,25 @@
       </c>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="27" t="s">
+      <c r="A42" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="27"/>
-      <c r="H42" s="27"/>
-      <c r="I42" s="27"/>
-      <c r="J42" s="27"/>
-      <c r="K42" s="27"/>
-      <c r="L42" s="27"/>
-      <c r="M42" s="27"/>
-      <c r="N42" s="27"/>
-      <c r="O42" s="27"/>
-      <c r="P42" s="27"/>
-      <c r="Q42" s="27"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
+      <c r="I42" s="25"/>
+      <c r="J42" s="25"/>
+      <c r="K42" s="25"/>
+      <c r="L42" s="25"/>
+      <c r="M42" s="25"/>
+      <c r="N42" s="25"/>
+      <c r="O42" s="25"/>
+      <c r="P42" s="25"/>
+      <c r="Q42" s="25"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -10479,25 +10479,25 @@
       </c>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="27" t="s">
+      <c r="A61" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="27"/>
-      <c r="C61" s="27"/>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27"/>
-      <c r="H61" s="27"/>
-      <c r="I61" s="27"/>
-      <c r="J61" s="27"/>
-      <c r="K61" s="27"/>
-      <c r="L61" s="27"/>
-      <c r="M61" s="27"/>
-      <c r="N61" s="27"/>
-      <c r="O61" s="27"/>
-      <c r="P61" s="27"/>
-      <c r="Q61" s="27"/>
+      <c r="B61" s="25"/>
+      <c r="C61" s="25"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="25"/>
+      <c r="G61" s="25"/>
+      <c r="H61" s="25"/>
+      <c r="I61" s="25"/>
+      <c r="J61" s="25"/>
+      <c r="K61" s="25"/>
+      <c r="L61" s="25"/>
+      <c r="M61" s="25"/>
+      <c r="N61" s="25"/>
+      <c r="O61" s="25"/>
+      <c r="P61" s="25"/>
+      <c r="Q61" s="25"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -11465,25 +11465,25 @@
       </c>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="27" t="s">
+      <c r="A80" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="27"/>
-      <c r="C80" s="27"/>
-      <c r="D80" s="27"/>
-      <c r="E80" s="27"/>
-      <c r="F80" s="27"/>
-      <c r="G80" s="27"/>
-      <c r="H80" s="27"/>
-      <c r="I80" s="27"/>
-      <c r="J80" s="27"/>
-      <c r="K80" s="27"/>
-      <c r="L80" s="27"/>
-      <c r="M80" s="27"/>
-      <c r="N80" s="27"/>
-      <c r="O80" s="27"/>
-      <c r="P80" s="27"/>
-      <c r="Q80" s="27"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="25"/>
+      <c r="D80" s="25"/>
+      <c r="E80" s="25"/>
+      <c r="F80" s="25"/>
+      <c r="G80" s="25"/>
+      <c r="H80" s="25"/>
+      <c r="I80" s="25"/>
+      <c r="J80" s="25"/>
+      <c r="K80" s="25"/>
+      <c r="L80" s="25"/>
+      <c r="M80" s="25"/>
+      <c r="N80" s="25"/>
+      <c r="O80" s="25"/>
+      <c r="P80" s="25"/>
+      <c r="Q80" s="25"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -12357,25 +12357,25 @@
       </c>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="27" t="s">
+      <c r="A98" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="27"/>
-      <c r="C98" s="27"/>
-      <c r="D98" s="27"/>
-      <c r="E98" s="27"/>
-      <c r="F98" s="27"/>
-      <c r="G98" s="27"/>
-      <c r="H98" s="27"/>
-      <c r="I98" s="27"/>
-      <c r="J98" s="27"/>
-      <c r="K98" s="27"/>
-      <c r="L98" s="27"/>
-      <c r="M98" s="27"/>
-      <c r="N98" s="27"/>
-      <c r="O98" s="27"/>
-      <c r="P98" s="27"/>
-      <c r="Q98" s="27"/>
+      <c r="B98" s="25"/>
+      <c r="C98" s="25"/>
+      <c r="D98" s="25"/>
+      <c r="E98" s="25"/>
+      <c r="F98" s="25"/>
+      <c r="G98" s="25"/>
+      <c r="H98" s="25"/>
+      <c r="I98" s="25"/>
+      <c r="J98" s="25"/>
+      <c r="K98" s="25"/>
+      <c r="L98" s="25"/>
+      <c r="M98" s="25"/>
+      <c r="N98" s="25"/>
+      <c r="O98" s="25"/>
+      <c r="P98" s="25"/>
+      <c r="Q98" s="25"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -13199,39 +13199,39 @@
       </c>
     </row>
     <row r="115" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="27" t="s">
+      <c r="A115" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="27"/>
-      <c r="C115" s="27"/>
-      <c r="D115" s="27"/>
-      <c r="E115" s="27"/>
-      <c r="F115" s="27"/>
-      <c r="G115" s="27"/>
-      <c r="H115" s="27"/>
-      <c r="I115" s="27"/>
-      <c r="J115" s="27"/>
-      <c r="K115" s="27"/>
-      <c r="L115" s="27"/>
-      <c r="M115" s="27"/>
-      <c r="N115" s="27"/>
-      <c r="O115" s="27"/>
-      <c r="P115" s="27"/>
-      <c r="Q115" s="27"/>
-      <c r="S115" s="27" t="s">
+      <c r="B115" s="25"/>
+      <c r="C115" s="25"/>
+      <c r="D115" s="25"/>
+      <c r="E115" s="25"/>
+      <c r="F115" s="25"/>
+      <c r="G115" s="25"/>
+      <c r="H115" s="25"/>
+      <c r="I115" s="25"/>
+      <c r="J115" s="25"/>
+      <c r="K115" s="25"/>
+      <c r="L115" s="25"/>
+      <c r="M115" s="25"/>
+      <c r="N115" s="25"/>
+      <c r="O115" s="25"/>
+      <c r="P115" s="25"/>
+      <c r="Q115" s="25"/>
+      <c r="S115" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="T115" s="27"/>
-      <c r="U115" s="27"/>
-      <c r="V115" s="27"/>
-      <c r="W115" s="27"/>
-      <c r="X115" s="27"/>
-      <c r="Y115" s="27"/>
-      <c r="Z115" s="27"/>
-      <c r="AA115" s="27"/>
-      <c r="AB115" s="27"/>
-      <c r="AC115" s="27"/>
-      <c r="AD115" s="27"/>
+      <c r="T115" s="25"/>
+      <c r="U115" s="25"/>
+      <c r="V115" s="25"/>
+      <c r="W115" s="25"/>
+      <c r="X115" s="25"/>
+      <c r="Y115" s="25"/>
+      <c r="Z115" s="25"/>
+      <c r="AA115" s="25"/>
+      <c r="AB115" s="25"/>
+      <c r="AC115" s="25"/>
+      <c r="AD115" s="25"/>
     </row>
     <row r="116" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="E117" s="9" t="str">
         <f>'NFL Schedule'!J114</f>
-        <v>NE</v>
+        <v/>
       </c>
       <c r="F117" s="10"/>
       <c r="G117" s="10"/>
@@ -13983,39 +13983,39 @@
       </c>
     </row>
     <row r="132" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="27" t="s">
+      <c r="A132" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="B132" s="27"/>
-      <c r="C132" s="27"/>
-      <c r="D132" s="27"/>
-      <c r="E132" s="27"/>
-      <c r="F132" s="27"/>
-      <c r="G132" s="27"/>
-      <c r="H132" s="27"/>
-      <c r="I132" s="27"/>
-      <c r="J132" s="27"/>
-      <c r="K132" s="27"/>
-      <c r="L132" s="27"/>
-      <c r="M132" s="27"/>
-      <c r="N132" s="27"/>
-      <c r="O132" s="27"/>
-      <c r="P132" s="27"/>
-      <c r="Q132" s="27"/>
-      <c r="S132" s="27" t="s">
+      <c r="B132" s="25"/>
+      <c r="C132" s="25"/>
+      <c r="D132" s="25"/>
+      <c r="E132" s="25"/>
+      <c r="F132" s="25"/>
+      <c r="G132" s="25"/>
+      <c r="H132" s="25"/>
+      <c r="I132" s="25"/>
+      <c r="J132" s="25"/>
+      <c r="K132" s="25"/>
+      <c r="L132" s="25"/>
+      <c r="M132" s="25"/>
+      <c r="N132" s="25"/>
+      <c r="O132" s="25"/>
+      <c r="P132" s="25"/>
+      <c r="Q132" s="25"/>
+      <c r="S132" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="T132" s="27"/>
-      <c r="U132" s="27"/>
-      <c r="V132" s="27"/>
-      <c r="W132" s="27"/>
-      <c r="X132" s="27"/>
-      <c r="Y132" s="27"/>
-      <c r="Z132" s="27"/>
-      <c r="AA132" s="27"/>
-      <c r="AB132" s="27"/>
-      <c r="AC132" s="27"/>
-      <c r="AD132" s="27"/>
+      <c r="T132" s="25"/>
+      <c r="U132" s="25"/>
+      <c r="V132" s="25"/>
+      <c r="W132" s="25"/>
+      <c r="X132" s="25"/>
+      <c r="Y132" s="25"/>
+      <c r="Z132" s="25"/>
+      <c r="AA132" s="25"/>
+      <c r="AB132" s="25"/>
+      <c r="AC132" s="25"/>
+      <c r="AD132" s="25"/>
     </row>
     <row r="133" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -14767,39 +14767,39 @@
       </c>
     </row>
     <row r="149" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="27" t="s">
+      <c r="A149" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="B149" s="27"/>
-      <c r="C149" s="27"/>
-      <c r="D149" s="27"/>
-      <c r="E149" s="27"/>
-      <c r="F149" s="27"/>
-      <c r="G149" s="27"/>
-      <c r="H149" s="27"/>
-      <c r="I149" s="27"/>
-      <c r="J149" s="27"/>
-      <c r="K149" s="27"/>
-      <c r="L149" s="27"/>
-      <c r="M149" s="27"/>
-      <c r="N149" s="27"/>
-      <c r="O149" s="27"/>
-      <c r="P149" s="27"/>
-      <c r="Q149" s="27"/>
-      <c r="S149" s="27" t="s">
+      <c r="B149" s="25"/>
+      <c r="C149" s="25"/>
+      <c r="D149" s="25"/>
+      <c r="E149" s="25"/>
+      <c r="F149" s="25"/>
+      <c r="G149" s="25"/>
+      <c r="H149" s="25"/>
+      <c r="I149" s="25"/>
+      <c r="J149" s="25"/>
+      <c r="K149" s="25"/>
+      <c r="L149" s="25"/>
+      <c r="M149" s="25"/>
+      <c r="N149" s="25"/>
+      <c r="O149" s="25"/>
+      <c r="P149" s="25"/>
+      <c r="Q149" s="25"/>
+      <c r="S149" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="T149" s="27"/>
-      <c r="U149" s="27"/>
-      <c r="V149" s="27"/>
-      <c r="W149" s="27"/>
-      <c r="X149" s="27"/>
-      <c r="Y149" s="27"/>
-      <c r="Z149" s="27"/>
-      <c r="AA149" s="27"/>
-      <c r="AB149" s="27"/>
-      <c r="AC149" s="27"/>
-      <c r="AD149" s="27"/>
+      <c r="T149" s="25"/>
+      <c r="U149" s="25"/>
+      <c r="V149" s="25"/>
+      <c r="W149" s="25"/>
+      <c r="X149" s="25"/>
+      <c r="Y149" s="25"/>
+      <c r="Z149" s="25"/>
+      <c r="AA149" s="25"/>
+      <c r="AB149" s="25"/>
+      <c r="AC149" s="25"/>
+      <c r="AD149" s="25"/>
     </row>
     <row r="150" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -15593,39 +15593,39 @@
       </c>
     </row>
     <row r="167" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="27" t="s">
+      <c r="A167" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="B167" s="27"/>
-      <c r="C167" s="27"/>
-      <c r="D167" s="27"/>
-      <c r="E167" s="27"/>
-      <c r="F167" s="27"/>
-      <c r="G167" s="27"/>
-      <c r="H167" s="27"/>
-      <c r="I167" s="27"/>
-      <c r="J167" s="27"/>
-      <c r="K167" s="27"/>
-      <c r="L167" s="27"/>
-      <c r="M167" s="27"/>
-      <c r="N167" s="27"/>
-      <c r="O167" s="27"/>
-      <c r="P167" s="27"/>
-      <c r="Q167" s="27"/>
-      <c r="S167" s="27" t="s">
+      <c r="B167" s="25"/>
+      <c r="C167" s="25"/>
+      <c r="D167" s="25"/>
+      <c r="E167" s="25"/>
+      <c r="F167" s="25"/>
+      <c r="G167" s="25"/>
+      <c r="H167" s="25"/>
+      <c r="I167" s="25"/>
+      <c r="J167" s="25"/>
+      <c r="K167" s="25"/>
+      <c r="L167" s="25"/>
+      <c r="M167" s="25"/>
+      <c r="N167" s="25"/>
+      <c r="O167" s="25"/>
+      <c r="P167" s="25"/>
+      <c r="Q167" s="25"/>
+      <c r="S167" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="T167" s="27"/>
-      <c r="U167" s="27"/>
-      <c r="V167" s="27"/>
-      <c r="W167" s="27"/>
-      <c r="X167" s="27"/>
-      <c r="Y167" s="27"/>
-      <c r="Z167" s="27"/>
-      <c r="AA167" s="27"/>
-      <c r="AB167" s="27"/>
-      <c r="AC167" s="27"/>
-      <c r="AD167" s="27"/>
+      <c r="T167" s="25"/>
+      <c r="U167" s="25"/>
+      <c r="V167" s="25"/>
+      <c r="W167" s="25"/>
+      <c r="X167" s="25"/>
+      <c r="Y167" s="25"/>
+      <c r="Z167" s="25"/>
+      <c r="AA167" s="25"/>
+      <c r="AB167" s="25"/>
+      <c r="AC167" s="25"/>
+      <c r="AD167" s="25"/>
     </row>
     <row r="168" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -16377,39 +16377,39 @@
       </c>
     </row>
     <row r="184" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="27" t="s">
+      <c r="A184" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="B184" s="27"/>
-      <c r="C184" s="27"/>
-      <c r="D184" s="27"/>
-      <c r="E184" s="27"/>
-      <c r="F184" s="27"/>
-      <c r="G184" s="27"/>
-      <c r="H184" s="27"/>
-      <c r="I184" s="27"/>
-      <c r="J184" s="27"/>
-      <c r="K184" s="27"/>
-      <c r="L184" s="27"/>
-      <c r="M184" s="27"/>
-      <c r="N184" s="27"/>
-      <c r="O184" s="27"/>
-      <c r="P184" s="27"/>
-      <c r="Q184" s="27"/>
-      <c r="S184" s="27" t="s">
+      <c r="B184" s="25"/>
+      <c r="C184" s="25"/>
+      <c r="D184" s="25"/>
+      <c r="E184" s="25"/>
+      <c r="F184" s="25"/>
+      <c r="G184" s="25"/>
+      <c r="H184" s="25"/>
+      <c r="I184" s="25"/>
+      <c r="J184" s="25"/>
+      <c r="K184" s="25"/>
+      <c r="L184" s="25"/>
+      <c r="M184" s="25"/>
+      <c r="N184" s="25"/>
+      <c r="O184" s="25"/>
+      <c r="P184" s="25"/>
+      <c r="Q184" s="25"/>
+      <c r="S184" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="T184" s="27"/>
-      <c r="U184" s="27"/>
-      <c r="V184" s="27"/>
-      <c r="W184" s="27"/>
-      <c r="X184" s="27"/>
-      <c r="Y184" s="27"/>
-      <c r="Z184" s="27"/>
-      <c r="AA184" s="27"/>
-      <c r="AB184" s="27"/>
-      <c r="AC184" s="27"/>
-      <c r="AD184" s="27"/>
+      <c r="T184" s="25"/>
+      <c r="U184" s="25"/>
+      <c r="V184" s="25"/>
+      <c r="W184" s="25"/>
+      <c r="X184" s="25"/>
+      <c r="Y184" s="25"/>
+      <c r="Z184" s="25"/>
+      <c r="AA184" s="25"/>
+      <c r="AB184" s="25"/>
+      <c r="AC184" s="25"/>
+      <c r="AD184" s="25"/>
     </row>
     <row r="185" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -17119,39 +17119,39 @@
       </c>
     </row>
     <row r="200" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="27" t="s">
+      <c r="A200" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="B200" s="27"/>
-      <c r="C200" s="27"/>
-      <c r="D200" s="27"/>
-      <c r="E200" s="27"/>
-      <c r="F200" s="27"/>
-      <c r="G200" s="27"/>
-      <c r="H200" s="27"/>
-      <c r="I200" s="27"/>
-      <c r="J200" s="27"/>
-      <c r="K200" s="27"/>
-      <c r="L200" s="27"/>
-      <c r="M200" s="27"/>
-      <c r="N200" s="27"/>
-      <c r="O200" s="27"/>
-      <c r="P200" s="27"/>
-      <c r="Q200" s="27"/>
-      <c r="S200" s="27" t="s">
+      <c r="B200" s="25"/>
+      <c r="C200" s="25"/>
+      <c r="D200" s="25"/>
+      <c r="E200" s="25"/>
+      <c r="F200" s="25"/>
+      <c r="G200" s="25"/>
+      <c r="H200" s="25"/>
+      <c r="I200" s="25"/>
+      <c r="J200" s="25"/>
+      <c r="K200" s="25"/>
+      <c r="L200" s="25"/>
+      <c r="M200" s="25"/>
+      <c r="N200" s="25"/>
+      <c r="O200" s="25"/>
+      <c r="P200" s="25"/>
+      <c r="Q200" s="25"/>
+      <c r="S200" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="T200" s="27"/>
-      <c r="U200" s="27"/>
-      <c r="V200" s="27"/>
-      <c r="W200" s="27"/>
-      <c r="X200" s="27"/>
-      <c r="Y200" s="27"/>
-      <c r="Z200" s="27"/>
-      <c r="AA200" s="27"/>
-      <c r="AB200" s="27"/>
-      <c r="AC200" s="27"/>
-      <c r="AD200" s="27"/>
+      <c r="T200" s="25"/>
+      <c r="U200" s="25"/>
+      <c r="V200" s="25"/>
+      <c r="W200" s="25"/>
+      <c r="X200" s="25"/>
+      <c r="Y200" s="25"/>
+      <c r="Z200" s="25"/>
+      <c r="AA200" s="25"/>
+      <c r="AB200" s="25"/>
+      <c r="AC200" s="25"/>
+      <c r="AD200" s="25"/>
     </row>
     <row r="201" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -17987,25 +17987,25 @@
       </c>
     </row>
     <row r="219" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="27" t="s">
+      <c r="A219" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="B219" s="27"/>
-      <c r="C219" s="27"/>
-      <c r="D219" s="27"/>
-      <c r="E219" s="27"/>
-      <c r="F219" s="27"/>
-      <c r="G219" s="27"/>
-      <c r="H219" s="27"/>
-      <c r="I219" s="27"/>
-      <c r="J219" s="27"/>
-      <c r="K219" s="27"/>
-      <c r="L219" s="27"/>
-      <c r="M219" s="27"/>
-      <c r="N219" s="27"/>
-      <c r="O219" s="27"/>
-      <c r="P219" s="27"/>
-      <c r="Q219" s="27"/>
+      <c r="B219" s="25"/>
+      <c r="C219" s="25"/>
+      <c r="D219" s="25"/>
+      <c r="E219" s="25"/>
+      <c r="F219" s="25"/>
+      <c r="G219" s="25"/>
+      <c r="H219" s="25"/>
+      <c r="I219" s="25"/>
+      <c r="J219" s="25"/>
+      <c r="K219" s="25"/>
+      <c r="L219" s="25"/>
+      <c r="M219" s="25"/>
+      <c r="N219" s="25"/>
+      <c r="O219" s="25"/>
+      <c r="P219" s="25"/>
+      <c r="Q219" s="25"/>
     </row>
     <row r="220" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -18505,25 +18505,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="27" t="s">
+      <c r="A236" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="B236" s="27"/>
-      <c r="C236" s="27"/>
-      <c r="D236" s="27"/>
-      <c r="E236" s="27"/>
-      <c r="F236" s="27"/>
-      <c r="G236" s="27"/>
-      <c r="H236" s="27"/>
-      <c r="I236" s="27"/>
-      <c r="J236" s="27"/>
-      <c r="K236" s="27"/>
-      <c r="L236" s="27"/>
-      <c r="M236" s="27"/>
-      <c r="N236" s="27"/>
-      <c r="O236" s="27"/>
-      <c r="P236" s="27"/>
-      <c r="Q236" s="27"/>
+      <c r="B236" s="25"/>
+      <c r="C236" s="25"/>
+      <c r="D236" s="25"/>
+      <c r="E236" s="25"/>
+      <c r="F236" s="25"/>
+      <c r="G236" s="25"/>
+      <c r="H236" s="25"/>
+      <c r="I236" s="25"/>
+      <c r="J236" s="25"/>
+      <c r="K236" s="25"/>
+      <c r="L236" s="25"/>
+      <c r="M236" s="25"/>
+      <c r="N236" s="25"/>
+      <c r="O236" s="25"/>
+      <c r="P236" s="25"/>
+      <c r="Q236" s="25"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -19053,25 +19053,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="27" t="s">
+      <c r="A254" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="B254" s="27"/>
-      <c r="C254" s="27"/>
-      <c r="D254" s="27"/>
-      <c r="E254" s="27"/>
-      <c r="F254" s="27"/>
-      <c r="G254" s="27"/>
-      <c r="H254" s="27"/>
-      <c r="I254" s="27"/>
-      <c r="J254" s="27"/>
-      <c r="K254" s="27"/>
-      <c r="L254" s="27"/>
-      <c r="M254" s="27"/>
-      <c r="N254" s="27"/>
-      <c r="O254" s="27"/>
-      <c r="P254" s="27"/>
-      <c r="Q254" s="27"/>
+      <c r="B254" s="25"/>
+      <c r="C254" s="25"/>
+      <c r="D254" s="25"/>
+      <c r="E254" s="25"/>
+      <c r="F254" s="25"/>
+      <c r="G254" s="25"/>
+      <c r="H254" s="25"/>
+      <c r="I254" s="25"/>
+      <c r="J254" s="25"/>
+      <c r="K254" s="25"/>
+      <c r="L254" s="25"/>
+      <c r="M254" s="25"/>
+      <c r="N254" s="25"/>
+      <c r="O254" s="25"/>
+      <c r="P254" s="25"/>
+      <c r="Q254" s="25"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -19631,25 +19631,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="27" t="s">
+      <c r="A273" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="B273" s="27"/>
-      <c r="C273" s="27"/>
-      <c r="D273" s="27"/>
-      <c r="E273" s="27"/>
-      <c r="F273" s="27"/>
-      <c r="G273" s="27"/>
-      <c r="H273" s="27"/>
-      <c r="I273" s="27"/>
-      <c r="J273" s="27"/>
-      <c r="K273" s="27"/>
-      <c r="L273" s="27"/>
-      <c r="M273" s="27"/>
-      <c r="N273" s="27"/>
-      <c r="O273" s="27"/>
-      <c r="P273" s="27"/>
-      <c r="Q273" s="27"/>
+      <c r="B273" s="25"/>
+      <c r="C273" s="25"/>
+      <c r="D273" s="25"/>
+      <c r="E273" s="25"/>
+      <c r="F273" s="25"/>
+      <c r="G273" s="25"/>
+      <c r="H273" s="25"/>
+      <c r="I273" s="25"/>
+      <c r="J273" s="25"/>
+      <c r="K273" s="25"/>
+      <c r="L273" s="25"/>
+      <c r="M273" s="25"/>
+      <c r="N273" s="25"/>
+      <c r="O273" s="25"/>
+      <c r="P273" s="25"/>
+      <c r="Q273" s="25"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -20209,25 +20209,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="27" t="s">
+      <c r="A292" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="B292" s="27"/>
-      <c r="C292" s="27"/>
-      <c r="D292" s="27"/>
-      <c r="E292" s="27"/>
-      <c r="F292" s="27"/>
-      <c r="G292" s="27"/>
-      <c r="H292" s="27"/>
-      <c r="I292" s="27"/>
-      <c r="J292" s="27"/>
-      <c r="K292" s="27"/>
-      <c r="L292" s="27"/>
-      <c r="M292" s="27"/>
-      <c r="N292" s="27"/>
-      <c r="O292" s="27"/>
-      <c r="P292" s="27"/>
-      <c r="Q292" s="27"/>
+      <c r="B292" s="25"/>
+      <c r="C292" s="25"/>
+      <c r="D292" s="25"/>
+      <c r="E292" s="25"/>
+      <c r="F292" s="25"/>
+      <c r="G292" s="25"/>
+      <c r="H292" s="25"/>
+      <c r="I292" s="25"/>
+      <c r="J292" s="25"/>
+      <c r="K292" s="25"/>
+      <c r="L292" s="25"/>
+      <c r="M292" s="25"/>
+      <c r="N292" s="25"/>
+      <c r="O292" s="25"/>
+      <c r="P292" s="25"/>
+      <c r="Q292" s="25"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -20787,25 +20787,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="27" t="s">
+      <c r="A311" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="B311" s="27"/>
-      <c r="C311" s="27"/>
-      <c r="D311" s="27"/>
-      <c r="E311" s="27"/>
-      <c r="F311" s="27"/>
-      <c r="G311" s="27"/>
-      <c r="H311" s="27"/>
-      <c r="I311" s="27"/>
-      <c r="J311" s="27"/>
-      <c r="K311" s="27"/>
-      <c r="L311" s="27"/>
-      <c r="M311" s="27"/>
-      <c r="N311" s="27"/>
-      <c r="O311" s="27"/>
-      <c r="P311" s="27"/>
-      <c r="Q311" s="27"/>
+      <c r="B311" s="25"/>
+      <c r="C311" s="25"/>
+      <c r="D311" s="25"/>
+      <c r="E311" s="25"/>
+      <c r="F311" s="25"/>
+      <c r="G311" s="25"/>
+      <c r="H311" s="25"/>
+      <c r="I311" s="25"/>
+      <c r="J311" s="25"/>
+      <c r="K311" s="25"/>
+      <c r="L311" s="25"/>
+      <c r="M311" s="25"/>
+      <c r="N311" s="25"/>
+      <c r="O311" s="25"/>
+      <c r="P311" s="25"/>
+      <c r="Q311" s="25"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -21366,32 +21366,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A236:Q236"/>
-    <mergeCell ref="A254:Q254"/>
-    <mergeCell ref="A273:Q273"/>
-    <mergeCell ref="A292:Q292"/>
-    <mergeCell ref="A311:Q311"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="S184:AD184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="S200:AD200"/>
-    <mergeCell ref="A219:Q219"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A23:Q23"/>
+    <mergeCell ref="A42:Q42"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="S115:AD115"/>
     <mergeCell ref="A132:Q132"/>
     <mergeCell ref="S132:AD132"/>
     <mergeCell ref="A149:Q149"/>
     <mergeCell ref="S149:AD149"/>
     <mergeCell ref="A167:Q167"/>
     <mergeCell ref="S167:AD167"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="S115:AD115"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="A23:Q23"/>
-    <mergeCell ref="A42:Q42"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="S184:AD184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="S200:AD200"/>
+    <mergeCell ref="A219:Q219"/>
+    <mergeCell ref="A236:Q236"/>
+    <mergeCell ref="A254:Q254"/>
+    <mergeCell ref="A273:Q273"/>
+    <mergeCell ref="A292:Q292"/>
+    <mergeCell ref="A311:Q311"/>
   </mergeCells>
   <conditionalFormatting sqref="S117:AD130">
     <cfRule type="expression" dxfId="23" priority="2">
@@ -26088,25 +26088,16 @@
       <c r="D114" t="s">
         <v>57</v>
       </c>
-      <c r="E114">
-        <v>15</v>
-      </c>
       <c r="F114" t="s">
         <v>61</v>
       </c>
-      <c r="G114">
-        <v>0</v>
-      </c>
-      <c r="H114">
-        <v>23</v>
-      </c>
       <c r="I114" t="str">
         <f t="shared" ref="I114:I127" si="12">IF(OR(E114="",G114=""),"",IF(E114&gt;G114,D114,IF(G114&gt;E114,F114,"TIE")))</f>
-        <v>NE</v>
+        <v/>
       </c>
       <c r="J114" t="str">
         <f t="shared" ref="J114:J127" si="13">IF(OR(E114="",G114="",H114=""),"",IF(E114+H114&gt;G114,D114,IF(E114+H114&lt;G114,F114,"PUSH")))</f>
-        <v>NE</v>
+        <v/>
       </c>
     </row>
     <row r="115" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31448,17 +31439,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -34281,17 +34272,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>209</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -37114,17 +37105,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>213</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -39947,19 +39938,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{9DE1E4DF-9D2F-41C3-82DE-6EA75B0925C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DAA369C-AF5F-4C27-BAA1-05D5AA990CA3}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{9DE1E4DF-9D2F-41C3-82DE-6EA75B0925C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{569BC34D-A021-4EC5-A238-8CFB9833C48B}"/>
   <bookViews>
-    <workbookView xWindow="29400" yWindow="-120" windowWidth="28320" windowHeight="16440" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29400" yWindow="-120" windowWidth="28320" windowHeight="16440" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4355" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4363" uniqueCount="359">
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -1430,9 +1430,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="B6" t="str">
         <f>'Playoff Picture'!B18</f>
-        <v>Jake Andrews</v>
+        <v>Chris Simmons</v>
       </c>
       <c r="C6" s="3">
         <v>5</v>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B9" t="str">
         <f>'Playoff Picture'!B21</f>
-        <v>Jeffrey Loeser</v>
+        <v>Jake Andrews</v>
       </c>
       <c r="C9" s="3">
         <v>2</v>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="B15" t="str">
         <f>INDEX($B$5:$B$10,MATCH(LARGE($H$5:$H$10,2),$H$5:$H$10,0))</f>
-        <v>Jake Andrews</v>
+        <v>Chris Simmons</v>
       </c>
       <c r="C15">
         <f>INDEX($C$5:$C$10,MATCH(LARGE($H$5:$H$10,2),$H$5:$H$10,0))</f>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="B18" t="str">
         <f>INDEX($B$5:$B$10,MATCH(LARGE($H$5:$H$10,5),$H$5:$H$10,0))</f>
-        <v>Jeffrey Loeser</v>
+        <v>Jake Andrews</v>
       </c>
       <c r="C18">
         <f>INDEX($C$5:$C$10,MATCH(LARGE($H$5:$H$10,5),$H$5:$H$10,0))</f>
@@ -2553,7 +2553,7 @@
     <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>'Playoff Wild Card'!B15</f>
-        <v>Jake Andrews</v>
+        <v>Chris Simmons</v>
       </c>
       <c r="B7">
         <f>'Playoff Wild Card'!C15</f>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="B14" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>Jake Andrews</v>
+        <v>Chris Simmons</v>
       </c>
       <c r="C14">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
@@ -2878,7 +2878,7 @@
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>A7</f>
-        <v>Jake Andrews</v>
+        <v>Chris Simmons</v>
       </c>
       <c r="B23" s="3">
         <v>0</v>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="L3">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H7,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G7,0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M3">
         <f>IF(Roster!$B$16&gt;=8,'Wk 7-12 Input'!H22,0)+IF(Roster!$B$16&gt;8,'Wk 7-12 Input'!G22,0)</f>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="R3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S3">
         <f>IF(AND(Roster!$B$16&gt;7,'Wk 7-12 Input'!F7="W"),1,0)+IF(AND(Roster!$B$16&gt;8,'Wk 7-12 Input'!F22="W"),1,0)+IF(AND(Roster!$B$16&gt;9,'Wk 7-12 Input'!F37="W"),1,0)+IF(AND(Roster!$B$16&gt;10,'Wk 7-12 Input'!F52="W"),1,0)+IF(AND(Roster!$B$16&gt;11,'Wk 7-12 Input'!F67="W"),1,0)+IF(AND(Roster!$B$16&gt;12,'Wk 7-12 Input'!F82="W"),1,0)</f>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="T3">
         <f>R3+0.0002</f>
-        <v>2.0000000000000001E-4</v>
+        <v>8.0001999999999995</v>
       </c>
       <c r="U3" t="str">
         <f>IF(Roster!$B$16&gt;13,'Wk 13-18 Input'!F7,"-")</f>
@@ -3316,11 +3316,11 @@
       </c>
       <c r="AE3">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="AF3">
         <f>AE3+0.0002</f>
-        <v>68.000200000000007</v>
+        <v>76.000200000000007</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="L7">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H11,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G11,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <f>IF(Roster!$B$16&gt;=8,'Wk 7-12 Input'!H26,0)+IF(Roster!$B$16&gt;8,'Wk 7-12 Input'!G26,0)</f>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="R7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S7">
         <f>IF(AND(Roster!$B$16&gt;7,'Wk 7-12 Input'!F11="W"),1,0)+IF(AND(Roster!$B$16&gt;8,'Wk 7-12 Input'!F26="W"),1,0)+IF(AND(Roster!$B$16&gt;9,'Wk 7-12 Input'!F41="W"),1,0)+IF(AND(Roster!$B$16&gt;10,'Wk 7-12 Input'!F56="W"),1,0)+IF(AND(Roster!$B$16&gt;11,'Wk 7-12 Input'!F71="W"),1,0)+IF(AND(Roster!$B$16&gt;12,'Wk 7-12 Input'!F86="W"),1,0)</f>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="T7">
         <f>R7+0.0006</f>
-        <v>5.9999999999999995E-4</v>
+        <v>6.0006000000000004</v>
       </c>
       <c r="U7" t="str">
         <f>IF(Roster!$B$16&gt;13,'Wk 13-18 Input'!F11,"-")</f>
@@ -3832,11 +3832,11 @@
       </c>
       <c r="AE7">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="AF7">
         <f>AE7+0.0006</f>
-        <v>60.000599999999999</v>
+        <v>66.000600000000006</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="L10">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H14,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G14,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <f>IF(Roster!$B$16&gt;=8,'Wk 7-12 Input'!H29,0)+IF(Roster!$B$16&gt;8,'Wk 7-12 Input'!G29,0)</f>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="R10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S10">
         <f>IF(AND(Roster!$B$16&gt;7,'Wk 7-12 Input'!F14="W"),1,0)+IF(AND(Roster!$B$16&gt;8,'Wk 7-12 Input'!F29="W"),1,0)+IF(AND(Roster!$B$16&gt;9,'Wk 7-12 Input'!F44="W"),1,0)+IF(AND(Roster!$B$16&gt;10,'Wk 7-12 Input'!F59="W"),1,0)+IF(AND(Roster!$B$16&gt;11,'Wk 7-12 Input'!F74="W"),1,0)+IF(AND(Roster!$B$16&gt;12,'Wk 7-12 Input'!F89="W"),1,0)</f>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="T10">
         <f>R10+0.0009</f>
-        <v>8.9999999999999998E-4</v>
+        <v>6.0008999999999997</v>
       </c>
       <c r="U10" t="str">
         <f>IF(Roster!$B$16&gt;13,'Wk 13-18 Input'!F14,"-")</f>
@@ -4219,11 +4219,11 @@
       </c>
       <c r="AE10">
         <f t="shared" si="2"/>
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="AF10">
         <f>AE10+0.0009</f>
-        <v>56.000900000000001</v>
+        <v>62.000900000000001</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="L12">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H16,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G16,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <f>IF(Roster!$B$16&gt;=8,'Wk 7-12 Input'!H31,0)+IF(Roster!$B$16&gt;8,'Wk 7-12 Input'!G31,0)</f>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="R12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S12">
         <f>IF(AND(Roster!$B$16&gt;7,'Wk 7-12 Input'!F16="W"),1,0)+IF(AND(Roster!$B$16&gt;8,'Wk 7-12 Input'!F31="W"),1,0)+IF(AND(Roster!$B$16&gt;9,'Wk 7-12 Input'!F46="W"),1,0)+IF(AND(Roster!$B$16&gt;10,'Wk 7-12 Input'!F61="W"),1,0)+IF(AND(Roster!$B$16&gt;11,'Wk 7-12 Input'!F76="W"),1,0)+IF(AND(Roster!$B$16&gt;12,'Wk 7-12 Input'!F91="W"),1,0)</f>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="T12">
         <f>R12+0.0011</f>
-        <v>1.1000000000000001E-3</v>
+        <v>6.0011000000000001</v>
       </c>
       <c r="U12" t="str">
         <f>IF(Roster!$B$16&gt;13,'Wk 13-18 Input'!F16,"-")</f>
@@ -4477,11 +4477,11 @@
       </c>
       <c r="AE12">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="AF12">
         <f>AE12+0.0011</f>
-        <v>60.001100000000001</v>
+        <v>66.001099999999994</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="L13">
         <f>IF(Roster!$B$16&gt;=7,'Wk 7-12 Input'!H17,0)+IF(Roster!$B$16&gt;7,'Wk 7-12 Input'!G17,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <f>IF(Roster!$B$16&gt;=8,'Wk 7-12 Input'!H32,0)+IF(Roster!$B$16&gt;8,'Wk 7-12 Input'!G32,0)</f>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="R13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S13">
         <f>IF(AND(Roster!$B$16&gt;7,'Wk 7-12 Input'!F17="W"),1,0)+IF(AND(Roster!$B$16&gt;8,'Wk 7-12 Input'!F32="W"),1,0)+IF(AND(Roster!$B$16&gt;9,'Wk 7-12 Input'!F47="W"),1,0)+IF(AND(Roster!$B$16&gt;10,'Wk 7-12 Input'!F62="W"),1,0)+IF(AND(Roster!$B$16&gt;11,'Wk 7-12 Input'!F77="W"),1,0)+IF(AND(Roster!$B$16&gt;12,'Wk 7-12 Input'!F92="W"),1,0)</f>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="T13">
         <f>R13+0.0012</f>
-        <v>1.1999999999999999E-3</v>
+        <v>6.0011999999999999</v>
       </c>
       <c r="U13" t="str">
         <f>IF(Roster!$B$16&gt;13,'Wk 13-18 Input'!F17,"-")</f>
@@ -4606,11 +4606,11 @@
       </c>
       <c r="AE13">
         <f t="shared" si="2"/>
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="AF13">
         <f>AE13+0.0012</f>
-        <v>48.001199999999997</v>
+        <v>54.001199999999997</v>
       </c>
     </row>
   </sheetData>
@@ -7517,67 +7517,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8545,25 +8545,25 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="25"/>
-      <c r="N23" s="25"/>
-      <c r="O23" s="25"/>
-      <c r="P23" s="25"/>
-      <c r="Q23" s="25"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
+      <c r="O23" s="27"/>
+      <c r="P23" s="27"/>
+      <c r="Q23" s="27"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -9531,25 +9531,25 @@
       </c>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="25" t="s">
+      <c r="A42" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
-      <c r="I42" s="25"/>
-      <c r="J42" s="25"/>
-      <c r="K42" s="25"/>
-      <c r="L42" s="25"/>
-      <c r="M42" s="25"/>
-      <c r="N42" s="25"/>
-      <c r="O42" s="25"/>
-      <c r="P42" s="25"/>
-      <c r="Q42" s="25"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="27"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27"/>
+      <c r="I42" s="27"/>
+      <c r="J42" s="27"/>
+      <c r="K42" s="27"/>
+      <c r="L42" s="27"/>
+      <c r="M42" s="27"/>
+      <c r="N42" s="27"/>
+      <c r="O42" s="27"/>
+      <c r="P42" s="27"/>
+      <c r="Q42" s="27"/>
     </row>
     <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -10479,25 +10479,25 @@
       </c>
     </row>
     <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="25" t="s">
+      <c r="A61" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="25"/>
-      <c r="C61" s="25"/>
-      <c r="D61" s="25"/>
-      <c r="E61" s="25"/>
-      <c r="F61" s="25"/>
-      <c r="G61" s="25"/>
-      <c r="H61" s="25"/>
-      <c r="I61" s="25"/>
-      <c r="J61" s="25"/>
-      <c r="K61" s="25"/>
-      <c r="L61" s="25"/>
-      <c r="M61" s="25"/>
-      <c r="N61" s="25"/>
-      <c r="O61" s="25"/>
-      <c r="P61" s="25"/>
-      <c r="Q61" s="25"/>
+      <c r="B61" s="27"/>
+      <c r="C61" s="27"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="27"/>
+      <c r="G61" s="27"/>
+      <c r="H61" s="27"/>
+      <c r="I61" s="27"/>
+      <c r="J61" s="27"/>
+      <c r="K61" s="27"/>
+      <c r="L61" s="27"/>
+      <c r="M61" s="27"/>
+      <c r="N61" s="27"/>
+      <c r="O61" s="27"/>
+      <c r="P61" s="27"/>
+      <c r="Q61" s="27"/>
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -11465,25 +11465,25 @@
       </c>
     </row>
     <row r="80" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="25" t="s">
+      <c r="A80" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="25"/>
-      <c r="C80" s="25"/>
-      <c r="D80" s="25"/>
-      <c r="E80" s="25"/>
-      <c r="F80" s="25"/>
-      <c r="G80" s="25"/>
-      <c r="H80" s="25"/>
-      <c r="I80" s="25"/>
-      <c r="J80" s="25"/>
-      <c r="K80" s="25"/>
-      <c r="L80" s="25"/>
-      <c r="M80" s="25"/>
-      <c r="N80" s="25"/>
-      <c r="O80" s="25"/>
-      <c r="P80" s="25"/>
-      <c r="Q80" s="25"/>
+      <c r="B80" s="27"/>
+      <c r="C80" s="27"/>
+      <c r="D80" s="27"/>
+      <c r="E80" s="27"/>
+      <c r="F80" s="27"/>
+      <c r="G80" s="27"/>
+      <c r="H80" s="27"/>
+      <c r="I80" s="27"/>
+      <c r="J80" s="27"/>
+      <c r="K80" s="27"/>
+      <c r="L80" s="27"/>
+      <c r="M80" s="27"/>
+      <c r="N80" s="27"/>
+      <c r="O80" s="27"/>
+      <c r="P80" s="27"/>
+      <c r="Q80" s="27"/>
     </row>
     <row r="81" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
@@ -12357,25 +12357,25 @@
       </c>
     </row>
     <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="25" t="s">
+      <c r="A98" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="25"/>
-      <c r="C98" s="25"/>
-      <c r="D98" s="25"/>
-      <c r="E98" s="25"/>
-      <c r="F98" s="25"/>
-      <c r="G98" s="25"/>
-      <c r="H98" s="25"/>
-      <c r="I98" s="25"/>
-      <c r="J98" s="25"/>
-      <c r="K98" s="25"/>
-      <c r="L98" s="25"/>
-      <c r="M98" s="25"/>
-      <c r="N98" s="25"/>
-      <c r="O98" s="25"/>
-      <c r="P98" s="25"/>
-      <c r="Q98" s="25"/>
+      <c r="B98" s="27"/>
+      <c r="C98" s="27"/>
+      <c r="D98" s="27"/>
+      <c r="E98" s="27"/>
+      <c r="F98" s="27"/>
+      <c r="G98" s="27"/>
+      <c r="H98" s="27"/>
+      <c r="I98" s="27"/>
+      <c r="J98" s="27"/>
+      <c r="K98" s="27"/>
+      <c r="L98" s="27"/>
+      <c r="M98" s="27"/>
+      <c r="N98" s="27"/>
+      <c r="O98" s="27"/>
+      <c r="P98" s="27"/>
+      <c r="Q98" s="27"/>
     </row>
     <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
@@ -13199,39 +13199,39 @@
       </c>
     </row>
     <row r="115" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="25" t="s">
+      <c r="A115" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="25"/>
-      <c r="C115" s="25"/>
-      <c r="D115" s="25"/>
-      <c r="E115" s="25"/>
-      <c r="F115" s="25"/>
-      <c r="G115" s="25"/>
-      <c r="H115" s="25"/>
-      <c r="I115" s="25"/>
-      <c r="J115" s="25"/>
-      <c r="K115" s="25"/>
-      <c r="L115" s="25"/>
-      <c r="M115" s="25"/>
-      <c r="N115" s="25"/>
-      <c r="O115" s="25"/>
-      <c r="P115" s="25"/>
-      <c r="Q115" s="25"/>
-      <c r="S115" s="25" t="s">
+      <c r="B115" s="27"/>
+      <c r="C115" s="27"/>
+      <c r="D115" s="27"/>
+      <c r="E115" s="27"/>
+      <c r="F115" s="27"/>
+      <c r="G115" s="27"/>
+      <c r="H115" s="27"/>
+      <c r="I115" s="27"/>
+      <c r="J115" s="27"/>
+      <c r="K115" s="27"/>
+      <c r="L115" s="27"/>
+      <c r="M115" s="27"/>
+      <c r="N115" s="27"/>
+      <c r="O115" s="27"/>
+      <c r="P115" s="27"/>
+      <c r="Q115" s="27"/>
+      <c r="S115" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="T115" s="25"/>
-      <c r="U115" s="25"/>
-      <c r="V115" s="25"/>
-      <c r="W115" s="25"/>
-      <c r="X115" s="25"/>
-      <c r="Y115" s="25"/>
-      <c r="Z115" s="25"/>
-      <c r="AA115" s="25"/>
-      <c r="AB115" s="25"/>
-      <c r="AC115" s="25"/>
-      <c r="AD115" s="25"/>
+      <c r="T115" s="27"/>
+      <c r="U115" s="27"/>
+      <c r="V115" s="27"/>
+      <c r="W115" s="27"/>
+      <c r="X115" s="27"/>
+      <c r="Y115" s="27"/>
+      <c r="Z115" s="27"/>
+      <c r="AA115" s="27"/>
+      <c r="AB115" s="27"/>
+      <c r="AC115" s="27"/>
+      <c r="AD115" s="27"/>
     </row>
     <row r="116" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
@@ -13337,32 +13337,64 @@
       </c>
       <c r="E117" s="9" t="str">
         <f>'NFL Schedule'!J114</f>
-        <v/>
-      </c>
-      <c r="F117" s="10"/>
-      <c r="G117" s="10"/>
+        <v>CHI</v>
+      </c>
+      <c r="F117" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G117" s="10" t="s">
+        <v>61</v>
+      </c>
       <c r="H117" s="10"/>
       <c r="I117" s="10"/>
       <c r="J117" s="10"/>
-      <c r="K117" s="10"/>
-      <c r="L117" s="10"/>
+      <c r="K117" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="L117" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="M117" s="10"/>
-      <c r="N117" s="10"/>
-      <c r="O117" s="10"/>
-      <c r="P117" s="10"/>
-      <c r="Q117" s="10"/>
-      <c r="S117" s="15"/>
-      <c r="T117" s="15"/>
+      <c r="N117" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="O117" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P117" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q117" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S117" s="15">
+        <v>3</v>
+      </c>
+      <c r="T117" s="15">
+        <v>8</v>
+      </c>
       <c r="U117" s="15"/>
       <c r="V117" s="15"/>
       <c r="W117" s="15"/>
-      <c r="X117" s="15"/>
-      <c r="Y117" s="15"/>
+      <c r="X117" s="15">
+        <v>6</v>
+      </c>
+      <c r="Y117" s="15">
+        <v>8</v>
+      </c>
       <c r="Z117" s="15"/>
-      <c r="AA117" s="15"/>
-      <c r="AB117" s="15"/>
-      <c r="AC117" s="15"/>
-      <c r="AD117" s="15"/>
+      <c r="AA117" s="15">
+        <v>6</v>
+      </c>
+      <c r="AB117" s="15">
+        <v>5</v>
+      </c>
+      <c r="AC117" s="15">
+        <v>6</v>
+      </c>
+      <c r="AD117" s="15">
+        <v>6</v>
+      </c>
     </row>
     <row r="118" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="7">
@@ -13935,11 +13967,11 @@
       <c r="Q131" s="14"/>
       <c r="S131" s="11" t="str">
         <f t="shared" ref="S131:AD131" si="0">IF(COUNT(S117:S130)=0,"",IF(AND(COUNT(S117:S130)=8,SUM(S117:S130)=36,MIN(S117:S130)&gt;=1,MAX(S117:S130)&lt;=8,SUMPRODUCT((S117:S130&lt;&gt;"")*(COUNTIF(S117:S130,S117:S130)&gt;1))=0,COUNTA(F117:F130)=8),"✓","FIX"))</f>
-        <v/>
+        <v>FIX</v>
       </c>
       <c r="T131" s="11" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>FIX</v>
       </c>
       <c r="U131" s="11" t="str">
         <f t="shared" si="0"/>
@@ -13955,11 +13987,11 @@
       </c>
       <c r="X131" s="11" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>FIX</v>
       </c>
       <c r="Y131" s="11" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>FIX</v>
       </c>
       <c r="Z131" s="11" t="str">
         <f t="shared" si="0"/>
@@ -13967,55 +13999,55 @@
       </c>
       <c r="AA131" s="11" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>FIX</v>
       </c>
       <c r="AB131" s="11" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>FIX</v>
       </c>
       <c r="AC131" s="11" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>FIX</v>
       </c>
       <c r="AD131" s="11" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>FIX</v>
       </c>
     </row>
     <row r="132" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="25" t="s">
+      <c r="A132" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="B132" s="25"/>
-      <c r="C132" s="25"/>
-      <c r="D132" s="25"/>
-      <c r="E132" s="25"/>
-      <c r="F132" s="25"/>
-      <c r="G132" s="25"/>
-      <c r="H132" s="25"/>
-      <c r="I132" s="25"/>
-      <c r="J132" s="25"/>
-      <c r="K132" s="25"/>
-      <c r="L132" s="25"/>
-      <c r="M132" s="25"/>
-      <c r="N132" s="25"/>
-      <c r="O132" s="25"/>
-      <c r="P132" s="25"/>
-      <c r="Q132" s="25"/>
-      <c r="S132" s="25" t="s">
+      <c r="B132" s="27"/>
+      <c r="C132" s="27"/>
+      <c r="D132" s="27"/>
+      <c r="E132" s="27"/>
+      <c r="F132" s="27"/>
+      <c r="G132" s="27"/>
+      <c r="H132" s="27"/>
+      <c r="I132" s="27"/>
+      <c r="J132" s="27"/>
+      <c r="K132" s="27"/>
+      <c r="L132" s="27"/>
+      <c r="M132" s="27"/>
+      <c r="N132" s="27"/>
+      <c r="O132" s="27"/>
+      <c r="P132" s="27"/>
+      <c r="Q132" s="27"/>
+      <c r="S132" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="T132" s="25"/>
-      <c r="U132" s="25"/>
-      <c r="V132" s="25"/>
-      <c r="W132" s="25"/>
-      <c r="X132" s="25"/>
-      <c r="Y132" s="25"/>
-      <c r="Z132" s="25"/>
-      <c r="AA132" s="25"/>
-      <c r="AB132" s="25"/>
-      <c r="AC132" s="25"/>
-      <c r="AD132" s="25"/>
+      <c r="T132" s="27"/>
+      <c r="U132" s="27"/>
+      <c r="V132" s="27"/>
+      <c r="W132" s="27"/>
+      <c r="X132" s="27"/>
+      <c r="Y132" s="27"/>
+      <c r="Z132" s="27"/>
+      <c r="AA132" s="27"/>
+      <c r="AB132" s="27"/>
+      <c r="AC132" s="27"/>
+      <c r="AD132" s="27"/>
     </row>
     <row r="133" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
@@ -14767,39 +14799,39 @@
       </c>
     </row>
     <row r="149" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="25" t="s">
+      <c r="A149" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="B149" s="25"/>
-      <c r="C149" s="25"/>
-      <c r="D149" s="25"/>
-      <c r="E149" s="25"/>
-      <c r="F149" s="25"/>
-      <c r="G149" s="25"/>
-      <c r="H149" s="25"/>
-      <c r="I149" s="25"/>
-      <c r="J149" s="25"/>
-      <c r="K149" s="25"/>
-      <c r="L149" s="25"/>
-      <c r="M149" s="25"/>
-      <c r="N149" s="25"/>
-      <c r="O149" s="25"/>
-      <c r="P149" s="25"/>
-      <c r="Q149" s="25"/>
-      <c r="S149" s="25" t="s">
+      <c r="B149" s="27"/>
+      <c r="C149" s="27"/>
+      <c r="D149" s="27"/>
+      <c r="E149" s="27"/>
+      <c r="F149" s="27"/>
+      <c r="G149" s="27"/>
+      <c r="H149" s="27"/>
+      <c r="I149" s="27"/>
+      <c r="J149" s="27"/>
+      <c r="K149" s="27"/>
+      <c r="L149" s="27"/>
+      <c r="M149" s="27"/>
+      <c r="N149" s="27"/>
+      <c r="O149" s="27"/>
+      <c r="P149" s="27"/>
+      <c r="Q149" s="27"/>
+      <c r="S149" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="T149" s="25"/>
-      <c r="U149" s="25"/>
-      <c r="V149" s="25"/>
-      <c r="W149" s="25"/>
-      <c r="X149" s="25"/>
-      <c r="Y149" s="25"/>
-      <c r="Z149" s="25"/>
-      <c r="AA149" s="25"/>
-      <c r="AB149" s="25"/>
-      <c r="AC149" s="25"/>
-      <c r="AD149" s="25"/>
+      <c r="T149" s="27"/>
+      <c r="U149" s="27"/>
+      <c r="V149" s="27"/>
+      <c r="W149" s="27"/>
+      <c r="X149" s="27"/>
+      <c r="Y149" s="27"/>
+      <c r="Z149" s="27"/>
+      <c r="AA149" s="27"/>
+      <c r="AB149" s="27"/>
+      <c r="AC149" s="27"/>
+      <c r="AD149" s="27"/>
     </row>
     <row r="150" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
@@ -15593,39 +15625,39 @@
       </c>
     </row>
     <row r="167" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="25" t="s">
+      <c r="A167" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="B167" s="25"/>
-      <c r="C167" s="25"/>
-      <c r="D167" s="25"/>
-      <c r="E167" s="25"/>
-      <c r="F167" s="25"/>
-      <c r="G167" s="25"/>
-      <c r="H167" s="25"/>
-      <c r="I167" s="25"/>
-      <c r="J167" s="25"/>
-      <c r="K167" s="25"/>
-      <c r="L167" s="25"/>
-      <c r="M167" s="25"/>
-      <c r="N167" s="25"/>
-      <c r="O167" s="25"/>
-      <c r="P167" s="25"/>
-      <c r="Q167" s="25"/>
-      <c r="S167" s="25" t="s">
+      <c r="B167" s="27"/>
+      <c r="C167" s="27"/>
+      <c r="D167" s="27"/>
+      <c r="E167" s="27"/>
+      <c r="F167" s="27"/>
+      <c r="G167" s="27"/>
+      <c r="H167" s="27"/>
+      <c r="I167" s="27"/>
+      <c r="J167" s="27"/>
+      <c r="K167" s="27"/>
+      <c r="L167" s="27"/>
+      <c r="M167" s="27"/>
+      <c r="N167" s="27"/>
+      <c r="O167" s="27"/>
+      <c r="P167" s="27"/>
+      <c r="Q167" s="27"/>
+      <c r="S167" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="T167" s="25"/>
-      <c r="U167" s="25"/>
-      <c r="V167" s="25"/>
-      <c r="W167" s="25"/>
-      <c r="X167" s="25"/>
-      <c r="Y167" s="25"/>
-      <c r="Z167" s="25"/>
-      <c r="AA167" s="25"/>
-      <c r="AB167" s="25"/>
-      <c r="AC167" s="25"/>
-      <c r="AD167" s="25"/>
+      <c r="T167" s="27"/>
+      <c r="U167" s="27"/>
+      <c r="V167" s="27"/>
+      <c r="W167" s="27"/>
+      <c r="X167" s="27"/>
+      <c r="Y167" s="27"/>
+      <c r="Z167" s="27"/>
+      <c r="AA167" s="27"/>
+      <c r="AB167" s="27"/>
+      <c r="AC167" s="27"/>
+      <c r="AD167" s="27"/>
     </row>
     <row r="168" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
@@ -16377,39 +16409,39 @@
       </c>
     </row>
     <row r="184" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="25" t="s">
+      <c r="A184" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="B184" s="25"/>
-      <c r="C184" s="25"/>
-      <c r="D184" s="25"/>
-      <c r="E184" s="25"/>
-      <c r="F184" s="25"/>
-      <c r="G184" s="25"/>
-      <c r="H184" s="25"/>
-      <c r="I184" s="25"/>
-      <c r="J184" s="25"/>
-      <c r="K184" s="25"/>
-      <c r="L184" s="25"/>
-      <c r="M184" s="25"/>
-      <c r="N184" s="25"/>
-      <c r="O184" s="25"/>
-      <c r="P184" s="25"/>
-      <c r="Q184" s="25"/>
-      <c r="S184" s="25" t="s">
+      <c r="B184" s="27"/>
+      <c r="C184" s="27"/>
+      <c r="D184" s="27"/>
+      <c r="E184" s="27"/>
+      <c r="F184" s="27"/>
+      <c r="G184" s="27"/>
+      <c r="H184" s="27"/>
+      <c r="I184" s="27"/>
+      <c r="J184" s="27"/>
+      <c r="K184" s="27"/>
+      <c r="L184" s="27"/>
+      <c r="M184" s="27"/>
+      <c r="N184" s="27"/>
+      <c r="O184" s="27"/>
+      <c r="P184" s="27"/>
+      <c r="Q184" s="27"/>
+      <c r="S184" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="T184" s="25"/>
-      <c r="U184" s="25"/>
-      <c r="V184" s="25"/>
-      <c r="W184" s="25"/>
-      <c r="X184" s="25"/>
-      <c r="Y184" s="25"/>
-      <c r="Z184" s="25"/>
-      <c r="AA184" s="25"/>
-      <c r="AB184" s="25"/>
-      <c r="AC184" s="25"/>
-      <c r="AD184" s="25"/>
+      <c r="T184" s="27"/>
+      <c r="U184" s="27"/>
+      <c r="V184" s="27"/>
+      <c r="W184" s="27"/>
+      <c r="X184" s="27"/>
+      <c r="Y184" s="27"/>
+      <c r="Z184" s="27"/>
+      <c r="AA184" s="27"/>
+      <c r="AB184" s="27"/>
+      <c r="AC184" s="27"/>
+      <c r="AD184" s="27"/>
     </row>
     <row r="185" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
@@ -17119,39 +17151,39 @@
       </c>
     </row>
     <row r="200" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="25" t="s">
+      <c r="A200" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="B200" s="25"/>
-      <c r="C200" s="25"/>
-      <c r="D200" s="25"/>
-      <c r="E200" s="25"/>
-      <c r="F200" s="25"/>
-      <c r="G200" s="25"/>
-      <c r="H200" s="25"/>
-      <c r="I200" s="25"/>
-      <c r="J200" s="25"/>
-      <c r="K200" s="25"/>
-      <c r="L200" s="25"/>
-      <c r="M200" s="25"/>
-      <c r="N200" s="25"/>
-      <c r="O200" s="25"/>
-      <c r="P200" s="25"/>
-      <c r="Q200" s="25"/>
-      <c r="S200" s="25" t="s">
+      <c r="B200" s="27"/>
+      <c r="C200" s="27"/>
+      <c r="D200" s="27"/>
+      <c r="E200" s="27"/>
+      <c r="F200" s="27"/>
+      <c r="G200" s="27"/>
+      <c r="H200" s="27"/>
+      <c r="I200" s="27"/>
+      <c r="J200" s="27"/>
+      <c r="K200" s="27"/>
+      <c r="L200" s="27"/>
+      <c r="M200" s="27"/>
+      <c r="N200" s="27"/>
+      <c r="O200" s="27"/>
+      <c r="P200" s="27"/>
+      <c r="Q200" s="27"/>
+      <c r="S200" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="T200" s="25"/>
-      <c r="U200" s="25"/>
-      <c r="V200" s="25"/>
-      <c r="W200" s="25"/>
-      <c r="X200" s="25"/>
-      <c r="Y200" s="25"/>
-      <c r="Z200" s="25"/>
-      <c r="AA200" s="25"/>
-      <c r="AB200" s="25"/>
-      <c r="AC200" s="25"/>
-      <c r="AD200" s="25"/>
+      <c r="T200" s="27"/>
+      <c r="U200" s="27"/>
+      <c r="V200" s="27"/>
+      <c r="W200" s="27"/>
+      <c r="X200" s="27"/>
+      <c r="Y200" s="27"/>
+      <c r="Z200" s="27"/>
+      <c r="AA200" s="27"/>
+      <c r="AB200" s="27"/>
+      <c r="AC200" s="27"/>
+      <c r="AD200" s="27"/>
     </row>
     <row r="201" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
@@ -17987,25 +18019,25 @@
       </c>
     </row>
     <row r="219" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="25" t="s">
+      <c r="A219" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="B219" s="25"/>
-      <c r="C219" s="25"/>
-      <c r="D219" s="25"/>
-      <c r="E219" s="25"/>
-      <c r="F219" s="25"/>
-      <c r="G219" s="25"/>
-      <c r="H219" s="25"/>
-      <c r="I219" s="25"/>
-      <c r="J219" s="25"/>
-      <c r="K219" s="25"/>
-      <c r="L219" s="25"/>
-      <c r="M219" s="25"/>
-      <c r="N219" s="25"/>
-      <c r="O219" s="25"/>
-      <c r="P219" s="25"/>
-      <c r="Q219" s="25"/>
+      <c r="B219" s="27"/>
+      <c r="C219" s="27"/>
+      <c r="D219" s="27"/>
+      <c r="E219" s="27"/>
+      <c r="F219" s="27"/>
+      <c r="G219" s="27"/>
+      <c r="H219" s="27"/>
+      <c r="I219" s="27"/>
+      <c r="J219" s="27"/>
+      <c r="K219" s="27"/>
+      <c r="L219" s="27"/>
+      <c r="M219" s="27"/>
+      <c r="N219" s="27"/>
+      <c r="O219" s="27"/>
+      <c r="P219" s="27"/>
+      <c r="Q219" s="27"/>
     </row>
     <row r="220" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
@@ -18505,25 +18537,25 @@
       <c r="Q235" s="14"/>
     </row>
     <row r="236" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="25" t="s">
+      <c r="A236" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="B236" s="25"/>
-      <c r="C236" s="25"/>
-      <c r="D236" s="25"/>
-      <c r="E236" s="25"/>
-      <c r="F236" s="25"/>
-      <c r="G236" s="25"/>
-      <c r="H236" s="25"/>
-      <c r="I236" s="25"/>
-      <c r="J236" s="25"/>
-      <c r="K236" s="25"/>
-      <c r="L236" s="25"/>
-      <c r="M236" s="25"/>
-      <c r="N236" s="25"/>
-      <c r="O236" s="25"/>
-      <c r="P236" s="25"/>
-      <c r="Q236" s="25"/>
+      <c r="B236" s="27"/>
+      <c r="C236" s="27"/>
+      <c r="D236" s="27"/>
+      <c r="E236" s="27"/>
+      <c r="F236" s="27"/>
+      <c r="G236" s="27"/>
+      <c r="H236" s="27"/>
+      <c r="I236" s="27"/>
+      <c r="J236" s="27"/>
+      <c r="K236" s="27"/>
+      <c r="L236" s="27"/>
+      <c r="M236" s="27"/>
+      <c r="N236" s="27"/>
+      <c r="O236" s="27"/>
+      <c r="P236" s="27"/>
+      <c r="Q236" s="27"/>
     </row>
     <row r="237" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
@@ -19053,25 +19085,25 @@
       <c r="Q253" s="14"/>
     </row>
     <row r="254" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="25" t="s">
+      <c r="A254" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="B254" s="25"/>
-      <c r="C254" s="25"/>
-      <c r="D254" s="25"/>
-      <c r="E254" s="25"/>
-      <c r="F254" s="25"/>
-      <c r="G254" s="25"/>
-      <c r="H254" s="25"/>
-      <c r="I254" s="25"/>
-      <c r="J254" s="25"/>
-      <c r="K254" s="25"/>
-      <c r="L254" s="25"/>
-      <c r="M254" s="25"/>
-      <c r="N254" s="25"/>
-      <c r="O254" s="25"/>
-      <c r="P254" s="25"/>
-      <c r="Q254" s="25"/>
+      <c r="B254" s="27"/>
+      <c r="C254" s="27"/>
+      <c r="D254" s="27"/>
+      <c r="E254" s="27"/>
+      <c r="F254" s="27"/>
+      <c r="G254" s="27"/>
+      <c r="H254" s="27"/>
+      <c r="I254" s="27"/>
+      <c r="J254" s="27"/>
+      <c r="K254" s="27"/>
+      <c r="L254" s="27"/>
+      <c r="M254" s="27"/>
+      <c r="N254" s="27"/>
+      <c r="O254" s="27"/>
+      <c r="P254" s="27"/>
+      <c r="Q254" s="27"/>
     </row>
     <row r="255" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
@@ -19631,25 +19663,25 @@
       <c r="Q272" s="14"/>
     </row>
     <row r="273" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="25" t="s">
+      <c r="A273" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="B273" s="25"/>
-      <c r="C273" s="25"/>
-      <c r="D273" s="25"/>
-      <c r="E273" s="25"/>
-      <c r="F273" s="25"/>
-      <c r="G273" s="25"/>
-      <c r="H273" s="25"/>
-      <c r="I273" s="25"/>
-      <c r="J273" s="25"/>
-      <c r="K273" s="25"/>
-      <c r="L273" s="25"/>
-      <c r="M273" s="25"/>
-      <c r="N273" s="25"/>
-      <c r="O273" s="25"/>
-      <c r="P273" s="25"/>
-      <c r="Q273" s="25"/>
+      <c r="B273" s="27"/>
+      <c r="C273" s="27"/>
+      <c r="D273" s="27"/>
+      <c r="E273" s="27"/>
+      <c r="F273" s="27"/>
+      <c r="G273" s="27"/>
+      <c r="H273" s="27"/>
+      <c r="I273" s="27"/>
+      <c r="J273" s="27"/>
+      <c r="K273" s="27"/>
+      <c r="L273" s="27"/>
+      <c r="M273" s="27"/>
+      <c r="N273" s="27"/>
+      <c r="O273" s="27"/>
+      <c r="P273" s="27"/>
+      <c r="Q273" s="27"/>
     </row>
     <row r="274" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
@@ -20209,25 +20241,25 @@
       <c r="Q291" s="14"/>
     </row>
     <row r="292" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="25" t="s">
+      <c r="A292" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="B292" s="25"/>
-      <c r="C292" s="25"/>
-      <c r="D292" s="25"/>
-      <c r="E292" s="25"/>
-      <c r="F292" s="25"/>
-      <c r="G292" s="25"/>
-      <c r="H292" s="25"/>
-      <c r="I292" s="25"/>
-      <c r="J292" s="25"/>
-      <c r="K292" s="25"/>
-      <c r="L292" s="25"/>
-      <c r="M292" s="25"/>
-      <c r="N292" s="25"/>
-      <c r="O292" s="25"/>
-      <c r="P292" s="25"/>
-      <c r="Q292" s="25"/>
+      <c r="B292" s="27"/>
+      <c r="C292" s="27"/>
+      <c r="D292" s="27"/>
+      <c r="E292" s="27"/>
+      <c r="F292" s="27"/>
+      <c r="G292" s="27"/>
+      <c r="H292" s="27"/>
+      <c r="I292" s="27"/>
+      <c r="J292" s="27"/>
+      <c r="K292" s="27"/>
+      <c r="L292" s="27"/>
+      <c r="M292" s="27"/>
+      <c r="N292" s="27"/>
+      <c r="O292" s="27"/>
+      <c r="P292" s="27"/>
+      <c r="Q292" s="27"/>
     </row>
     <row r="293" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
@@ -20787,25 +20819,25 @@
       <c r="Q310" s="14"/>
     </row>
     <row r="311" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="25" t="s">
+      <c r="A311" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="B311" s="25"/>
-      <c r="C311" s="25"/>
-      <c r="D311" s="25"/>
-      <c r="E311" s="25"/>
-      <c r="F311" s="25"/>
-      <c r="G311" s="25"/>
-      <c r="H311" s="25"/>
-      <c r="I311" s="25"/>
-      <c r="J311" s="25"/>
-      <c r="K311" s="25"/>
-      <c r="L311" s="25"/>
-      <c r="M311" s="25"/>
-      <c r="N311" s="25"/>
-      <c r="O311" s="25"/>
-      <c r="P311" s="25"/>
-      <c r="Q311" s="25"/>
+      <c r="B311" s="27"/>
+      <c r="C311" s="27"/>
+      <c r="D311" s="27"/>
+      <c r="E311" s="27"/>
+      <c r="F311" s="27"/>
+      <c r="G311" s="27"/>
+      <c r="H311" s="27"/>
+      <c r="I311" s="27"/>
+      <c r="J311" s="27"/>
+      <c r="K311" s="27"/>
+      <c r="L311" s="27"/>
+      <c r="M311" s="27"/>
+      <c r="N311" s="27"/>
+      <c r="O311" s="27"/>
+      <c r="P311" s="27"/>
+      <c r="Q311" s="27"/>
     </row>
     <row r="312" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
@@ -21366,32 +21398,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="A23:Q23"/>
-    <mergeCell ref="A42:Q42"/>
-    <mergeCell ref="A61:Q61"/>
-    <mergeCell ref="A80:Q80"/>
-    <mergeCell ref="A98:Q98"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="S115:AD115"/>
+    <mergeCell ref="A236:Q236"/>
+    <mergeCell ref="A254:Q254"/>
+    <mergeCell ref="A273:Q273"/>
+    <mergeCell ref="A292:Q292"/>
+    <mergeCell ref="A311:Q311"/>
+    <mergeCell ref="A184:Q184"/>
+    <mergeCell ref="S184:AD184"/>
+    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="S200:AD200"/>
+    <mergeCell ref="A219:Q219"/>
     <mergeCell ref="A132:Q132"/>
     <mergeCell ref="S132:AD132"/>
     <mergeCell ref="A149:Q149"/>
     <mergeCell ref="S149:AD149"/>
     <mergeCell ref="A167:Q167"/>
     <mergeCell ref="S167:AD167"/>
-    <mergeCell ref="A184:Q184"/>
-    <mergeCell ref="S184:AD184"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="S200:AD200"/>
-    <mergeCell ref="A219:Q219"/>
-    <mergeCell ref="A236:Q236"/>
-    <mergeCell ref="A254:Q254"/>
-    <mergeCell ref="A273:Q273"/>
-    <mergeCell ref="A292:Q292"/>
-    <mergeCell ref="A311:Q311"/>
+    <mergeCell ref="A61:Q61"/>
+    <mergeCell ref="A80:Q80"/>
+    <mergeCell ref="A98:Q98"/>
+    <mergeCell ref="A115:Q115"/>
+    <mergeCell ref="S115:AD115"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A23:Q23"/>
+    <mergeCell ref="A42:Q42"/>
   </mergeCells>
   <conditionalFormatting sqref="S117:AD130">
     <cfRule type="expression" dxfId="23" priority="2">
@@ -26088,16 +26120,25 @@
       <c r="D114" t="s">
         <v>57</v>
       </c>
+      <c r="E114">
+        <v>24</v>
+      </c>
       <c r="F114" t="s">
         <v>61</v>
       </c>
+      <c r="G114">
+        <v>30</v>
+      </c>
+      <c r="H114">
+        <v>-3.5</v>
+      </c>
       <c r="I114" t="str">
         <f t="shared" ref="I114:I127" si="12">IF(OR(E114="",G114=""),"",IF(E114&gt;G114,D114,IF(G114&gt;E114,F114,"TIE")))</f>
-        <v/>
+        <v>CHI</v>
       </c>
       <c r="J114" t="str">
         <f t="shared" ref="J114:J127" si="13">IF(OR(E114="",G114="",H114=""),"",IF(E114+H114&gt;G114,D114,IF(E114+H114&lt;G114,F114,"PUSH")))</f>
-        <v/>
+        <v>CHI</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34369,30 +34410,30 @@
       </c>
       <c r="C7" s="3">
         <f>SUMPRODUCT(('Picks Detail'!G117:G130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*('Picks Detail'!G117:G130='Picks Detail'!E117:E130)*('Picks Detail'!T117:T130))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D7">
         <v>9</v>
       </c>
       <c r="E7">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(9,A$6:A$17,0)),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F7" t="str">
         <f>IF(C7=0,"-",IF(C7&gt;E7,"W",IF(C7&lt;E7,"L",IF(AND('Picks Detail'!E131&lt;&gt;"",INDEX('Picks Detail'!F131:Q131,1,A7)&lt;&gt;"",INDEX('Picks Detail'!F131:Q131,1,D7)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F131:Q131,1,A7)-'Picks Detail'!E131)&lt;ABS(INDEX('Picks Detail'!F131:Q131,1,D7)-'Picks Detail'!E131),"W",IF(ABS(INDEX('Picks Detail'!F131:Q131,1,A7)-'Picks Detail'!E131)&gt;ABS(INDEX('Picks Detail'!F131:Q131,1,D7)-'Picks Detail'!E131),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34484,7 +34525,7 @@
       </c>
       <c r="E10">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(11,A$6:A$17,0)),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F10" t="str">
         <f>IF(C10=0,"-",IF(C10&gt;E10,"W",IF(C10&lt;E10,"L",IF(AND('Picks Detail'!E131&lt;&gt;"",INDEX('Picks Detail'!F131:Q131,1,A10)&lt;&gt;"",INDEX('Picks Detail'!F131:Q131,1,D10)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F131:Q131,1,A10)-'Picks Detail'!E131)&lt;ABS(INDEX('Picks Detail'!F131:Q131,1,D10)-'Picks Detail'!E131),"W",IF(ABS(INDEX('Picks Detail'!F131:Q131,1,A10)-'Picks Detail'!E131)&gt;ABS(INDEX('Picks Detail'!F131:Q131,1,D10)-'Picks Detail'!E131),"L","T")),"T"))))</f>
@@ -34513,30 +34554,30 @@
       </c>
       <c r="C11" s="3">
         <f>SUMPRODUCT(('Picks Detail'!K117:K130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*('Picks Detail'!K117:K130='Picks Detail'!E117:E130)*('Picks Detail'!X117:X130))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D11">
         <v>12</v>
       </c>
       <c r="E11">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(12,A$6:A$17,0)),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F11" t="str">
         <f>IF(C11=0,"-",IF(C11&gt;E11,"W",IF(C11&lt;E11,"L",IF(AND('Picks Detail'!E131&lt;&gt;"",INDEX('Picks Detail'!F131:Q131,1,A11)&lt;&gt;"",INDEX('Picks Detail'!F131:Q131,1,D11)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F131:Q131,1,A11)-'Picks Detail'!E131)&lt;ABS(INDEX('Picks Detail'!F131:Q131,1,D11)-'Picks Detail'!E131),"W",IF(ABS(INDEX('Picks Detail'!F131:Q131,1,A11)-'Picks Detail'!E131)&gt;ABS(INDEX('Picks Detail'!F131:Q131,1,D11)-'Picks Detail'!E131),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>T</v>
       </c>
       <c r="G11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34621,18 +34662,18 @@
       </c>
       <c r="C14" s="3">
         <f>SUMPRODUCT(('Picks Detail'!N117:N130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*('Picks Detail'!N117:N130='Picks Detail'!E117:E130)*('Picks Detail'!AA117:AA130))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D14">
         <v>2</v>
       </c>
       <c r="E14">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(2,A$6:A$17,0)),0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F14" t="str">
         <f>IF(C14=0,"-",IF(C14&gt;E14,"W",IF(C14&lt;E14,"L",IF(AND('Picks Detail'!E131&lt;&gt;"",INDEX('Picks Detail'!F131:Q131,1,A14)&lt;&gt;"",INDEX('Picks Detail'!F131:Q131,1,D14)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F131:Q131,1,A14)-'Picks Detail'!E131)&lt;ABS(INDEX('Picks Detail'!F131:Q131,1,D14)-'Picks Detail'!E131),"W",IF(ABS(INDEX('Picks Detail'!F131:Q131,1,A14)-'Picks Detail'!E131)&gt;ABS(INDEX('Picks Detail'!F131:Q131,1,D14)-'Picks Detail'!E131),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G14">
         <f t="shared" si="0"/>
@@ -34640,11 +34681,11 @@
       </c>
       <c r="H14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34693,7 +34734,7 @@
       </c>
       <c r="C16" s="3">
         <f>SUMPRODUCT(('Picks Detail'!P117:P130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*('Picks Detail'!P117:P130='Picks Detail'!E117:E130)*('Picks Detail'!AC117:AC130))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <v>5</v>
@@ -34704,19 +34745,19 @@
       </c>
       <c r="F16" t="str">
         <f>IF(C16=0,"-",IF(C16&gt;E16,"W",IF(C16&lt;E16,"L",IF(AND('Picks Detail'!E131&lt;&gt;"",INDEX('Picks Detail'!F131:Q131,1,A16)&lt;&gt;"",INDEX('Picks Detail'!F131:Q131,1,D16)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F131:Q131,1,A16)-'Picks Detail'!E131)&lt;ABS(INDEX('Picks Detail'!F131:Q131,1,D16)-'Picks Detail'!E131),"W",IF(ABS(INDEX('Picks Detail'!F131:Q131,1,A16)-'Picks Detail'!E131)&gt;ABS(INDEX('Picks Detail'!F131:Q131,1,D16)-'Picks Detail'!E131),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34729,30 +34770,30 @@
       </c>
       <c r="C17" s="3">
         <f>SUMPRODUCT(('Picks Detail'!Q117:Q130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*('Picks Detail'!Q117:Q130='Picks Detail'!E117:E130)*('Picks Detail'!AD117:AD130))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D17">
         <v>6</v>
       </c>
       <c r="E17">
         <f>IFERROR(INDEX(C$6:C$17,MATCH(6,A$6:A$17,0)),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F17" t="str">
         <f>IF(C17=0,"-",IF(C17&gt;E17,"W",IF(C17&lt;E17,"L",IF(AND('Picks Detail'!E131&lt;&gt;"",INDEX('Picks Detail'!F131:Q131,1,A17)&lt;&gt;"",INDEX('Picks Detail'!F131:Q131,1,D17)&lt;&gt;""),IF(ABS(INDEX('Picks Detail'!F131:Q131,1,A17)-'Picks Detail'!E131)&lt;ABS(INDEX('Picks Detail'!F131:Q131,1,D17)-'Picks Detail'!E131),"W",IF(ABS(INDEX('Picks Detail'!F131:Q131,1,A17)-'Picks Detail'!E131)&gt;ABS(INDEX('Picks Detail'!F131:Q131,1,D17)-'Picks Detail'!E131),"L","T")),"T"))))</f>
-        <v>-</v>
+        <v>T</v>
       </c>
       <c r="G17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40632,7 +40673,7 @@
       </c>
       <c r="C19">
         <f>Helper!L3</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D19">
         <f>Helper!M3</f>
@@ -40656,7 +40697,7 @@
       </c>
       <c r="I19">
         <f>Helper!R3</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J19">
         <f>Helper!S3</f>
@@ -40664,7 +40705,7 @@
       </c>
       <c r="K19">
         <f>MAX(Helper!L3:Q3)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40812,7 +40853,7 @@
       </c>
       <c r="C23">
         <f>Helper!L7</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <f>Helper!M7</f>
@@ -40836,7 +40877,7 @@
       </c>
       <c r="I23">
         <f>Helper!R7</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <f>Helper!S7</f>
@@ -40844,7 +40885,7 @@
       </c>
       <c r="K23">
         <f>MAX(Helper!L7:Q7)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40947,7 +40988,7 @@
       </c>
       <c r="C26">
         <f>Helper!L10</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D26">
         <f>Helper!M10</f>
@@ -40971,7 +41012,7 @@
       </c>
       <c r="I26">
         <f>Helper!R10</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J26">
         <f>Helper!S10</f>
@@ -40979,7 +41020,7 @@
       </c>
       <c r="K26">
         <f>MAX(Helper!L10:Q10)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41037,7 +41078,7 @@
       </c>
       <c r="C28">
         <f>Helper!L12</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D28">
         <f>Helper!M12</f>
@@ -41061,7 +41102,7 @@
       </c>
       <c r="I28">
         <f>Helper!R12</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <f>Helper!S12</f>
@@ -41069,7 +41110,7 @@
       </c>
       <c r="K28">
         <f>MAX(Helper!L12:Q12)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41082,7 +41123,7 @@
       </c>
       <c r="C29">
         <f>Helper!L13</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D29">
         <f>Helper!M13</f>
@@ -41106,7 +41147,7 @@
       </c>
       <c r="I29">
         <f>Helper!R13</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J29">
         <f>Helper!S13</f>
@@ -41114,7 +41155,7 @@
       </c>
       <c r="K29">
         <f>MAX(Helper!L13:Q13)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -41877,7 +41918,7 @@
       </c>
       <c r="D58">
         <f>Helper!R3</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E58">
         <f>Helper!AC3</f>
@@ -41885,7 +41926,7 @@
       </c>
       <c r="F58">
         <f>Helper!AE3</f>
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G58">
         <f>Helper!K3</f>
@@ -41893,7 +41934,7 @@
       </c>
       <c r="H58">
         <f>Helper!T3</f>
-        <v>2.0000000000000001E-4</v>
+        <v>8.0001999999999995</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42009,7 +42050,7 @@
       </c>
       <c r="D62">
         <f>Helper!R7</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E62">
         <f>Helper!AC7</f>
@@ -42017,7 +42058,7 @@
       </c>
       <c r="F62">
         <f>Helper!AE7</f>
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G62">
         <f>Helper!K7</f>
@@ -42025,7 +42066,7 @@
       </c>
       <c r="H62">
         <f>Helper!T7</f>
-        <v>5.9999999999999995E-4</v>
+        <v>6.0006000000000004</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42108,7 +42149,7 @@
       </c>
       <c r="D65">
         <f>Helper!R10</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E65">
         <f>Helper!AC10</f>
@@ -42116,7 +42157,7 @@
       </c>
       <c r="F65">
         <f>Helper!AE10</f>
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G65">
         <f>Helper!K10</f>
@@ -42124,7 +42165,7 @@
       </c>
       <c r="H65">
         <f>Helper!T10</f>
-        <v>8.9999999999999998E-4</v>
+        <v>6.0008999999999997</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42174,7 +42215,7 @@
       </c>
       <c r="D67">
         <f>Helper!R12</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E67">
         <f>Helper!AC12</f>
@@ -42182,7 +42223,7 @@
       </c>
       <c r="F67">
         <f>Helper!AE12</f>
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G67">
         <f>Helper!K12</f>
@@ -42190,7 +42231,7 @@
       </c>
       <c r="H67">
         <f>Helper!T12</f>
-        <v>1.1000000000000001E-3</v>
+        <v>6.0011000000000001</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42207,7 +42248,7 @@
       </c>
       <c r="D68">
         <f>Helper!R13</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E68">
         <f>Helper!AC13</f>
@@ -42215,7 +42256,7 @@
       </c>
       <c r="F68">
         <f>Helper!AE13</f>
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G68">
         <f>Helper!K13</f>
@@ -42223,7 +42264,7 @@
       </c>
       <c r="H68">
         <f>Helper!T13</f>
-        <v>1.1999999999999999E-3</v>
+        <v>6.0011999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -42316,7 +42357,7 @@
       </c>
       <c r="B6" t="str">
         <f>INDEX(Helper!B$2:B$13,MATCH(MAX(Helper!T$2:T$13),Helper!T$2:T$13,0))</f>
-        <v>Jake Andrews</v>
+        <v>Chris Simmons</v>
       </c>
       <c r="C6" t="s">
         <v>265</v>
@@ -42326,7 +42367,7 @@
       </c>
       <c r="E6" t="str">
         <f>IF(B6&lt;&gt;$E$5,B6,INDEX(Helper!B$2:B$13,MATCH(LARGE(Helper!T$2:T$13,2),Helper!T$2:T$13,0)))</f>
-        <v>Jake Andrews</v>
+        <v>Chris Simmons</v>
       </c>
       <c r="F6" t="str">
         <f>IF(E6=B6,"QUALIFIED","PASS → "&amp;E6)</f>
@@ -42407,11 +42448,11 @@
       </c>
       <c r="E9" t="str">
         <f>IF(AND(H13&lt;&gt;$E$5,H13&lt;&gt;$E$6,H13&lt;&gt;$E$7,H13&lt;&gt;$E$8),H13,IF(AND(H14&lt;&gt;$E$5,H14&lt;&gt;$E$6,H14&lt;&gt;$E$7,H14&lt;&gt;$E$8),H14,IF(AND(H15&lt;&gt;$E$5,H15&lt;&gt;$E$6,H15&lt;&gt;$E$7,H15&lt;&gt;$E$8),H15,H16)))</f>
-        <v>Jeffrey Loeser</v>
+        <v>Jake Andrews</v>
       </c>
       <c r="F9" t="str">
         <f>IF(E9=B9,"QUALIFIED","PASS → "&amp;E9)</f>
-        <v>PASS → Jeffrey Loeser</v>
+        <v>QUALIFIED</v>
       </c>
       <c r="H9" t="str">
         <f>INDEX(Helper!B$6:B$9,MATCH(LARGE(Helper!AD$6:AD$9,1),Helper!AD$6:AD$9,0))</f>
@@ -42520,7 +42561,7 @@
       </c>
       <c r="B18" t="str">
         <f>E6</f>
-        <v>Jake Andrews</v>
+        <v>Chris Simmons</v>
       </c>
       <c r="C18" t="str">
         <f>D6</f>
@@ -42559,7 +42600,7 @@
       </c>
       <c r="B21" t="str">
         <f>E9</f>
-        <v>Jeffrey Loeser</v>
+        <v>Jake Andrews</v>
       </c>
       <c r="C21" t="str">
         <f>"Div C"</f>
@@ -42955,15 +42996,15 @@
       </c>
       <c r="I41">
         <f>Helper!AE3</f>
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J41" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41">
         <f>IF(J41,-1,I41+0.00002)</f>
-        <v>68.000020000000006</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43027,7 +43068,7 @@
       </c>
       <c r="I45">
         <f>Helper!AE7</f>
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J45" t="b">
         <f t="shared" si="1"/>
@@ -43035,7 +43076,7 @@
       </c>
       <c r="K45">
         <f>IF(J45,-1,I45+0.00006)</f>
-        <v>60.000059999999998</v>
+        <v>66.000060000000005</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43081,7 +43122,7 @@
       </c>
       <c r="I48">
         <f>Helper!AE10</f>
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="J48" t="b">
         <f t="shared" si="1"/>
@@ -43089,7 +43130,7 @@
       </c>
       <c r="K48">
         <f>IF(J48,-1,I48+0.00009)</f>
-        <v>56.00009</v>
+        <v>62.00009</v>
       </c>
     </row>
     <row r="49" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43117,15 +43158,15 @@
       </c>
       <c r="I50">
         <f>Helper!AE12</f>
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J50" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50">
         <f>IF(J50,-1,I50+0.00011)</f>
-        <v>-1</v>
+        <v>66.000110000000006</v>
       </c>
     </row>
     <row r="51" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43135,7 +43176,7 @@
       </c>
       <c r="I51">
         <f>Helper!AE13</f>
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J51" t="b">
         <f t="shared" si="1"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -27,7 +27,7 @@
     <sheet name="Updates" sheetId="12" r:id="rId12"/>
     <sheet name="Helper" sheetId="13" state="hidden" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr fullCalcOnLoad="1" calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31540,7 +31540,7 @@
         <v>Evan Loeser</v>
       </c>
       <c r="C6" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!F6:F21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*('Picks Detail'!F6:F21='Picks Detail'!E6:E21))</f>
+        <f>SUMPRODUCT(('Picks Detail'!F6:F21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*((('Picks Detail'!F6:F21='Picks Detail'!E6:E21)+('Picks Detail'!E6:E21="PUSH"))&gt;0))</f>
         <v>5</v>
       </c>
       <c r="D6">
@@ -31576,7 +31576,7 @@
         <v>Chris Simmons</v>
       </c>
       <c r="C7" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!G6:G21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*('Picks Detail'!G6:G21='Picks Detail'!E6:E21))</f>
+        <f>SUMPRODUCT(('Picks Detail'!G6:G21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*((('Picks Detail'!G6:G21='Picks Detail'!E6:E21)+('Picks Detail'!E6:E21="PUSH"))&gt;0))</f>
         <v>7</v>
       </c>
       <c r="D7">
@@ -31612,7 +31612,7 @@
         <v>Jack Smith</v>
       </c>
       <c r="C8" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!H6:H21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*('Picks Detail'!H6:H21='Picks Detail'!E6:E21))</f>
+        <f>SUMPRODUCT(('Picks Detail'!H6:H21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*((('Picks Detail'!H6:H21='Picks Detail'!E6:E21)+('Picks Detail'!E6:E21="PUSH"))&gt;0))</f>
         <v>8</v>
       </c>
       <c r="D8">
@@ -31648,7 +31648,7 @@
         <v>Luke Ussery</v>
       </c>
       <c r="C9" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!I6:I21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*('Picks Detail'!I6:I21='Picks Detail'!E6:E21))</f>
+        <f>SUMPRODUCT(('Picks Detail'!I6:I21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*((('Picks Detail'!I6:I21='Picks Detail'!E6:E21)+('Picks Detail'!E6:E21="PUSH"))&gt;0))</f>
         <v>6</v>
       </c>
       <c r="D9">
@@ -31684,7 +31684,7 @@
         <v>Mikayla Simmons</v>
       </c>
       <c r="C10" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!J6:J21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*('Picks Detail'!J6:J21='Picks Detail'!E6:E21))</f>
+        <f>SUMPRODUCT(('Picks Detail'!J6:J21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*((('Picks Detail'!J6:J21='Picks Detail'!E6:E21)+('Picks Detail'!E6:E21="PUSH"))&gt;0))</f>
         <v>10</v>
       </c>
       <c r="D10">
@@ -31720,7 +31720,7 @@
         <v>Alan Loeser</v>
       </c>
       <c r="C11" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!K6:K21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*('Picks Detail'!K6:K21='Picks Detail'!E6:E21))</f>
+        <f>SUMPRODUCT(('Picks Detail'!K6:K21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*((('Picks Detail'!K6:K21='Picks Detail'!E6:E21)+('Picks Detail'!E6:E21="PUSH"))&gt;0))</f>
         <v>7</v>
       </c>
       <c r="D11">
@@ -31756,7 +31756,7 @@
         <v>Caleb Simmons</v>
       </c>
       <c r="C12" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!L6:L21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*('Picks Detail'!L6:L21='Picks Detail'!E6:E21))</f>
+        <f>SUMPRODUCT(('Picks Detail'!L6:L21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*((('Picks Detail'!L6:L21='Picks Detail'!E6:E21)+('Picks Detail'!E6:E21="PUSH"))&gt;0))</f>
         <v>7</v>
       </c>
       <c r="D12">
@@ -31792,7 +31792,7 @@
         <v>Larry Loeser</v>
       </c>
       <c r="C13" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!M6:M21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*('Picks Detail'!M6:M21='Picks Detail'!E6:E21))</f>
+        <f>SUMPRODUCT(('Picks Detail'!M6:M21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*((('Picks Detail'!M6:M21='Picks Detail'!E6:E21)+('Picks Detail'!E6:E21="PUSH"))&gt;0))</f>
         <v>8</v>
       </c>
       <c r="D13">
@@ -31828,7 +31828,7 @@
         <v>Daddy Michael</v>
       </c>
       <c r="C14" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!N6:N21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*('Picks Detail'!N6:N21='Picks Detail'!E6:E21))</f>
+        <f>SUMPRODUCT(('Picks Detail'!N6:N21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*((('Picks Detail'!N6:N21='Picks Detail'!E6:E21)+('Picks Detail'!E6:E21="PUSH"))&gt;0))</f>
         <v>8</v>
       </c>
       <c r="D14">
@@ -31864,7 +31864,7 @@
         <v>Zach Zarra</v>
       </c>
       <c r="C15" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!O6:O21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*('Picks Detail'!O6:O21='Picks Detail'!E6:E21))</f>
+        <f>SUMPRODUCT(('Picks Detail'!O6:O21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*((('Picks Detail'!O6:O21='Picks Detail'!E6:E21)+('Picks Detail'!E6:E21="PUSH"))&gt;0))</f>
         <v>11</v>
       </c>
       <c r="D15">
@@ -31900,7 +31900,7 @@
         <v>Jeffrey Loeser</v>
       </c>
       <c r="C16" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!P6:P21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*('Picks Detail'!P6:P21='Picks Detail'!E6:E21))</f>
+        <f>SUMPRODUCT(('Picks Detail'!P6:P21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*((('Picks Detail'!P6:P21='Picks Detail'!E6:E21)+('Picks Detail'!E6:E21="PUSH"))&gt;0))</f>
         <v>10</v>
       </c>
       <c r="D16">
@@ -31936,7 +31936,7 @@
         <v>Jake Andrews</v>
       </c>
       <c r="C17" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!Q6:Q21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*('Picks Detail'!Q6:Q21='Picks Detail'!E6:E21))</f>
+        <f>SUMPRODUCT(('Picks Detail'!Q6:Q21&lt;&gt;"")*('Picks Detail'!E6:E21&lt;&gt;"")*((('Picks Detail'!Q6:Q21='Picks Detail'!E6:E21)+('Picks Detail'!E6:E21="PUSH"))&gt;0))</f>
         <v>9</v>
       </c>
       <c r="D17">
@@ -32006,7 +32006,7 @@
         <v>Evan Loeser</v>
       </c>
       <c r="C21" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!F25:F40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!F25:F40='Picks Detail'!E25:E40))</f>
+        <f>SUMPRODUCT(('Picks Detail'!F25:F40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*((('Picks Detail'!F25:F40='Picks Detail'!E25:E40)+('Picks Detail'!E25:E40="PUSH"))&gt;0))</f>
         <v>8</v>
       </c>
       <c r="D21">
@@ -32042,7 +32042,7 @@
         <v>Chris Simmons</v>
       </c>
       <c r="C22" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!G25:G40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!G25:G40='Picks Detail'!E25:E40))</f>
+        <f>SUMPRODUCT(('Picks Detail'!G25:G40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*((('Picks Detail'!G25:G40='Picks Detail'!E25:E40)+('Picks Detail'!E25:E40="PUSH"))&gt;0))</f>
         <v>8</v>
       </c>
       <c r="D22">
@@ -32078,7 +32078,7 @@
         <v>Jack Smith</v>
       </c>
       <c r="C23" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!H25:H40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!H25:H40='Picks Detail'!E25:E40))</f>
+        <f>SUMPRODUCT(('Picks Detail'!H25:H40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*((('Picks Detail'!H25:H40='Picks Detail'!E25:E40)+('Picks Detail'!E25:E40="PUSH"))&gt;0))</f>
         <v>6</v>
       </c>
       <c r="D23">
@@ -32114,7 +32114,7 @@
         <v>Luke Ussery</v>
       </c>
       <c r="C24" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!I25:I40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!I25:I40='Picks Detail'!E25:E40))</f>
+        <f>SUMPRODUCT(('Picks Detail'!I25:I40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*((('Picks Detail'!I25:I40='Picks Detail'!E25:E40)+('Picks Detail'!E25:E40="PUSH"))&gt;0))</f>
         <v>8</v>
       </c>
       <c r="D24">
@@ -32150,7 +32150,7 @@
         <v>Mikayla Simmons</v>
       </c>
       <c r="C25" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!J25:J40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!J25:J40='Picks Detail'!E25:E40))</f>
+        <f>SUMPRODUCT(('Picks Detail'!J25:J40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*((('Picks Detail'!J25:J40='Picks Detail'!E25:E40)+('Picks Detail'!E25:E40="PUSH"))&gt;0))</f>
         <v>6</v>
       </c>
       <c r="D25">
@@ -32186,7 +32186,7 @@
         <v>Alan Loeser</v>
       </c>
       <c r="C26" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!K25:K40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!K25:K40='Picks Detail'!E25:E40))</f>
+        <f>SUMPRODUCT(('Picks Detail'!K25:K40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*((('Picks Detail'!K25:K40='Picks Detail'!E25:E40)+('Picks Detail'!E25:E40="PUSH"))&gt;0))</f>
         <v>7</v>
       </c>
       <c r="D26">
@@ -32222,7 +32222,7 @@
         <v>Caleb Simmons</v>
       </c>
       <c r="C27" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!L25:L40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!L25:L40='Picks Detail'!E25:E40))</f>
+        <f>SUMPRODUCT(('Picks Detail'!L25:L40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*((('Picks Detail'!L25:L40='Picks Detail'!E25:E40)+('Picks Detail'!E25:E40="PUSH"))&gt;0))</f>
         <v>6</v>
       </c>
       <c r="D27">
@@ -32258,7 +32258,7 @@
         <v>Larry Loeser</v>
       </c>
       <c r="C28" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!M25:M40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!M25:M40='Picks Detail'!E25:E40))</f>
+        <f>SUMPRODUCT(('Picks Detail'!M25:M40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*((('Picks Detail'!M25:M40='Picks Detail'!E25:E40)+('Picks Detail'!E25:E40="PUSH"))&gt;0))</f>
         <v>4</v>
       </c>
       <c r="D28">
@@ -32294,7 +32294,7 @@
         <v>Daddy Michael</v>
       </c>
       <c r="C29" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!N25:N40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!N25:N40='Picks Detail'!E25:E40))</f>
+        <f>SUMPRODUCT(('Picks Detail'!N25:N40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*((('Picks Detail'!N25:N40='Picks Detail'!E25:E40)+('Picks Detail'!E25:E40="PUSH"))&gt;0))</f>
         <v>7</v>
       </c>
       <c r="D29">
@@ -32330,7 +32330,7 @@
         <v>Zach Zarra</v>
       </c>
       <c r="C30" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!O25:O40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!O25:O40='Picks Detail'!E25:E40))</f>
+        <f>SUMPRODUCT(('Picks Detail'!O25:O40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*((('Picks Detail'!O25:O40='Picks Detail'!E25:E40)+('Picks Detail'!E25:E40="PUSH"))&gt;0))</f>
         <v>8</v>
       </c>
       <c r="D30">
@@ -32366,7 +32366,7 @@
         <v>Jeffrey Loeser</v>
       </c>
       <c r="C31" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!P25:P40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!P25:P40='Picks Detail'!E25:E40))</f>
+        <f>SUMPRODUCT(('Picks Detail'!P25:P40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*((('Picks Detail'!P25:P40='Picks Detail'!E25:E40)+('Picks Detail'!E25:E40="PUSH"))&gt;0))</f>
         <v>6</v>
       </c>
       <c r="D31">
@@ -32402,7 +32402,7 @@
         <v>Jake Andrews</v>
       </c>
       <c r="C32" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!Q25:Q40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*('Picks Detail'!Q25:Q40='Picks Detail'!E25:E40))</f>
+        <f>SUMPRODUCT(('Picks Detail'!Q25:Q40&lt;&gt;"")*('Picks Detail'!E25:E40&lt;&gt;"")*((('Picks Detail'!Q25:Q40='Picks Detail'!E25:E40)+('Picks Detail'!E25:E40="PUSH"))&gt;0))</f>
         <v>4</v>
       </c>
       <c r="D32">
@@ -32472,7 +32472,7 @@
         <v>Evan Loeser</v>
       </c>
       <c r="C36" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!F44:F59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!F44:F59='Picks Detail'!E44:E59))</f>
+        <f>SUMPRODUCT(('Picks Detail'!F44:F59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*((('Picks Detail'!F44:F59='Picks Detail'!E44:E59)+('Picks Detail'!E44:E59="PUSH"))&gt;0))</f>
         <v>12</v>
       </c>
       <c r="D36">
@@ -32508,7 +32508,7 @@
         <v>Chris Simmons</v>
       </c>
       <c r="C37" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!G44:G59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!G44:G59='Picks Detail'!E44:E59))</f>
+        <f>SUMPRODUCT(('Picks Detail'!G44:G59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*((('Picks Detail'!G44:G59='Picks Detail'!E44:E59)+('Picks Detail'!E44:E59="PUSH"))&gt;0))</f>
         <v>8</v>
       </c>
       <c r="D37">
@@ -32544,7 +32544,7 @@
         <v>Jack Smith</v>
       </c>
       <c r="C38" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!H44:H59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!H44:H59='Picks Detail'!E44:E59))</f>
+        <f>SUMPRODUCT(('Picks Detail'!H44:H59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*((('Picks Detail'!H44:H59='Picks Detail'!E44:E59)+('Picks Detail'!E44:E59="PUSH"))&gt;0))</f>
         <v>8</v>
       </c>
       <c r="D38">
@@ -32580,7 +32580,7 @@
         <v>Luke Ussery</v>
       </c>
       <c r="C39" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!I44:I59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!I44:I59='Picks Detail'!E44:E59))</f>
+        <f>SUMPRODUCT(('Picks Detail'!I44:I59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*((('Picks Detail'!I44:I59='Picks Detail'!E44:E59)+('Picks Detail'!E44:E59="PUSH"))&gt;0))</f>
         <v>0</v>
       </c>
       <c r="D39">
@@ -32616,7 +32616,7 @@
         <v>Mikayla Simmons</v>
       </c>
       <c r="C40" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!J44:J59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!J44:J59='Picks Detail'!E44:E59))</f>
+        <f>SUMPRODUCT(('Picks Detail'!J44:J59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*((('Picks Detail'!J44:J59='Picks Detail'!E44:E59)+('Picks Detail'!E44:E59="PUSH"))&gt;0))</f>
         <v>9</v>
       </c>
       <c r="D40">
@@ -32652,7 +32652,7 @@
         <v>Alan Loeser</v>
       </c>
       <c r="C41" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!K44:K59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!K44:K59='Picks Detail'!E44:E59))</f>
+        <f>SUMPRODUCT(('Picks Detail'!K44:K59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*((('Picks Detail'!K44:K59='Picks Detail'!E44:E59)+('Picks Detail'!E44:E59="PUSH"))&gt;0))</f>
         <v>7</v>
       </c>
       <c r="D41">
@@ -32688,7 +32688,7 @@
         <v>Caleb Simmons</v>
       </c>
       <c r="C42" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!L44:L59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!L44:L59='Picks Detail'!E44:E59))</f>
+        <f>SUMPRODUCT(('Picks Detail'!L44:L59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*((('Picks Detail'!L44:L59='Picks Detail'!E44:E59)+('Picks Detail'!E44:E59="PUSH"))&gt;0))</f>
         <v>8</v>
       </c>
       <c r="D42">
@@ -32724,7 +32724,7 @@
         <v>Larry Loeser</v>
       </c>
       <c r="C43" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!M44:M59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!M44:M59='Picks Detail'!E44:E59))</f>
+        <f>SUMPRODUCT(('Picks Detail'!M44:M59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*((('Picks Detail'!M44:M59='Picks Detail'!E44:E59)+('Picks Detail'!E44:E59="PUSH"))&gt;0))</f>
         <v>7</v>
       </c>
       <c r="D43">
@@ -32760,7 +32760,7 @@
         <v>Daddy Michael</v>
       </c>
       <c r="C44" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!N44:N59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!N44:N59='Picks Detail'!E44:E59))</f>
+        <f>SUMPRODUCT(('Picks Detail'!N44:N59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*((('Picks Detail'!N44:N59='Picks Detail'!E44:E59)+('Picks Detail'!E44:E59="PUSH"))&gt;0))</f>
         <v>8</v>
       </c>
       <c r="D44">
@@ -32796,7 +32796,7 @@
         <v>Zach Zarra</v>
       </c>
       <c r="C45" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!O44:O59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!O44:O59='Picks Detail'!E44:E59))</f>
+        <f>SUMPRODUCT(('Picks Detail'!O44:O59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*((('Picks Detail'!O44:O59='Picks Detail'!E44:E59)+('Picks Detail'!E44:E59="PUSH"))&gt;0))</f>
         <v>5</v>
       </c>
       <c r="D45">
@@ -32832,7 +32832,7 @@
         <v>Jeffrey Loeser</v>
       </c>
       <c r="C46" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!P44:P59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!P44:P59='Picks Detail'!E44:E59))</f>
+        <f>SUMPRODUCT(('Picks Detail'!P44:P59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*((('Picks Detail'!P44:P59='Picks Detail'!E44:E59)+('Picks Detail'!E44:E59="PUSH"))&gt;0))</f>
         <v>8</v>
       </c>
       <c r="D46">
@@ -32868,7 +32868,7 @@
         <v>Jake Andrews</v>
       </c>
       <c r="C47" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!Q44:Q59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*('Picks Detail'!Q44:Q59='Picks Detail'!E44:E59))</f>
+        <f>SUMPRODUCT(('Picks Detail'!Q44:Q59&lt;&gt;"")*('Picks Detail'!E44:E59&lt;&gt;"")*((('Picks Detail'!Q44:Q59='Picks Detail'!E44:E59)+('Picks Detail'!E44:E59="PUSH"))&gt;0))</f>
         <v>6</v>
       </c>
       <c r="D47">
@@ -32938,7 +32938,7 @@
         <v>Evan Loeser</v>
       </c>
       <c r="C51" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!F63:F78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!F63:F78='Picks Detail'!E63:E78))</f>
+        <f>SUMPRODUCT(('Picks Detail'!F63:F78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*((('Picks Detail'!F63:F78='Picks Detail'!E63:E78)+('Picks Detail'!E63:E78="PUSH"))&gt;0))</f>
         <v>8</v>
       </c>
       <c r="D51">
@@ -32974,7 +32974,7 @@
         <v>Chris Simmons</v>
       </c>
       <c r="C52" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!G63:G78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!G63:G78='Picks Detail'!E63:E78))</f>
+        <f>SUMPRODUCT(('Picks Detail'!G63:G78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*((('Picks Detail'!G63:G78='Picks Detail'!E63:E78)+('Picks Detail'!E63:E78="PUSH"))&gt;0))</f>
         <v>7</v>
       </c>
       <c r="D52">
@@ -33010,7 +33010,7 @@
         <v>Jack Smith</v>
       </c>
       <c r="C53" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!H63:H78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!H63:H78='Picks Detail'!E63:E78))</f>
+        <f>SUMPRODUCT(('Picks Detail'!H63:H78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*((('Picks Detail'!H63:H78='Picks Detail'!E63:E78)+('Picks Detail'!E63:E78="PUSH"))&gt;0))</f>
         <v>9</v>
       </c>
       <c r="D53">
@@ -33046,7 +33046,7 @@
         <v>Luke Ussery</v>
       </c>
       <c r="C54" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!I63:I78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!I63:I78='Picks Detail'!E63:E78))</f>
+        <f>SUMPRODUCT(('Picks Detail'!I63:I78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*((('Picks Detail'!I63:I78='Picks Detail'!E63:E78)+('Picks Detail'!E63:E78="PUSH"))&gt;0))</f>
         <v>12</v>
       </c>
       <c r="D54">
@@ -33082,7 +33082,7 @@
         <v>Mikayla Simmons</v>
       </c>
       <c r="C55" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!J63:J78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!J63:J78='Picks Detail'!E63:E78))</f>
+        <f>SUMPRODUCT(('Picks Detail'!J63:J78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*((('Picks Detail'!J63:J78='Picks Detail'!E63:E78)+('Picks Detail'!E63:E78="PUSH"))&gt;0))</f>
         <v>6</v>
       </c>
       <c r="D55">
@@ -33118,7 +33118,7 @@
         <v>Alan Loeser</v>
       </c>
       <c r="C56" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!K63:K78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!K63:K78='Picks Detail'!E63:E78))</f>
+        <f>SUMPRODUCT(('Picks Detail'!K63:K78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*((('Picks Detail'!K63:K78='Picks Detail'!E63:E78)+('Picks Detail'!E63:E78="PUSH"))&gt;0))</f>
         <v>7</v>
       </c>
       <c r="D56">
@@ -33154,7 +33154,7 @@
         <v>Caleb Simmons</v>
       </c>
       <c r="C57" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!L63:L78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!L63:L78='Picks Detail'!E63:E78))</f>
+        <f>SUMPRODUCT(('Picks Detail'!L63:L78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*((('Picks Detail'!L63:L78='Picks Detail'!E63:E78)+('Picks Detail'!E63:E78="PUSH"))&gt;0))</f>
         <v>6</v>
       </c>
       <c r="D57">
@@ -33190,7 +33190,7 @@
         <v>Larry Loeser</v>
       </c>
       <c r="C58" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!M63:M78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!M63:M78='Picks Detail'!E63:E78))</f>
+        <f>SUMPRODUCT(('Picks Detail'!M63:M78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*((('Picks Detail'!M63:M78='Picks Detail'!E63:E78)+('Picks Detail'!E63:E78="PUSH"))&gt;0))</f>
         <v>8</v>
       </c>
       <c r="D58">
@@ -33226,7 +33226,7 @@
         <v>Daddy Michael</v>
       </c>
       <c r="C59" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!N63:N78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!N63:N78='Picks Detail'!E63:E78))</f>
+        <f>SUMPRODUCT(('Picks Detail'!N63:N78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*((('Picks Detail'!N63:N78='Picks Detail'!E63:E78)+('Picks Detail'!E63:E78="PUSH"))&gt;0))</f>
         <v>8</v>
       </c>
       <c r="D59">
@@ -33262,7 +33262,7 @@
         <v>Zach Zarra</v>
       </c>
       <c r="C60" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!O63:O78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!O63:O78='Picks Detail'!E63:E78))</f>
+        <f>SUMPRODUCT(('Picks Detail'!O63:O78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*((('Picks Detail'!O63:O78='Picks Detail'!E63:E78)+('Picks Detail'!E63:E78="PUSH"))&gt;0))</f>
         <v>7</v>
       </c>
       <c r="D60">
@@ -33298,7 +33298,7 @@
         <v>Jeffrey Loeser</v>
       </c>
       <c r="C61" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!P63:P78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!P63:P78='Picks Detail'!E63:E78))</f>
+        <f>SUMPRODUCT(('Picks Detail'!P63:P78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*((('Picks Detail'!P63:P78='Picks Detail'!E63:E78)+('Picks Detail'!E63:E78="PUSH"))&gt;0))</f>
         <v>7</v>
       </c>
       <c r="D61">
@@ -33334,7 +33334,7 @@
         <v>Jake Andrews</v>
       </c>
       <c r="C62" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!Q63:Q78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*('Picks Detail'!Q63:Q78='Picks Detail'!E63:E78))</f>
+        <f>SUMPRODUCT(('Picks Detail'!Q63:Q78&lt;&gt;"")*('Picks Detail'!E63:E78&lt;&gt;"")*((('Picks Detail'!Q63:Q78='Picks Detail'!E63:E78)+('Picks Detail'!E63:E78="PUSH"))&gt;0))</f>
         <v>7</v>
       </c>
       <c r="D62">
@@ -33404,7 +33404,7 @@
         <v>Evan Loeser</v>
       </c>
       <c r="C66" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!F82:F96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!F82:F96='Picks Detail'!E82:E96))</f>
+        <f>SUMPRODUCT(('Picks Detail'!F82:F96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*((('Picks Detail'!F82:F96='Picks Detail'!E82:E96)+('Picks Detail'!E82:E96="PUSH"))&gt;0))</f>
         <v>9</v>
       </c>
       <c r="D66">
@@ -33440,7 +33440,7 @@
         <v>Chris Simmons</v>
       </c>
       <c r="C67" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!G82:G96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!G82:G96='Picks Detail'!E82:E96))</f>
+        <f>SUMPRODUCT(('Picks Detail'!G82:G96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*((('Picks Detail'!G82:G96='Picks Detail'!E82:E96)+('Picks Detail'!E82:E96="PUSH"))&gt;0))</f>
         <v>9</v>
       </c>
       <c r="D67">
@@ -33476,7 +33476,7 @@
         <v>Jack Smith</v>
       </c>
       <c r="C68" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!H82:H96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!H82:H96='Picks Detail'!E82:E96))</f>
+        <f>SUMPRODUCT(('Picks Detail'!H82:H96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*((('Picks Detail'!H82:H96='Picks Detail'!E82:E96)+('Picks Detail'!E82:E96="PUSH"))&gt;0))</f>
         <v>5</v>
       </c>
       <c r="D68">
@@ -33512,7 +33512,7 @@
         <v>Luke Ussery</v>
       </c>
       <c r="C69" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!I82:I96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!I82:I96='Picks Detail'!E82:E96))</f>
+        <f>SUMPRODUCT(('Picks Detail'!I82:I96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*((('Picks Detail'!I82:I96='Picks Detail'!E82:E96)+('Picks Detail'!E82:E96="PUSH"))&gt;0))</f>
         <v>0</v>
       </c>
       <c r="D69">
@@ -33548,7 +33548,7 @@
         <v>Mikayla Simmons</v>
       </c>
       <c r="C70" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!J82:J96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!J82:J96='Picks Detail'!E82:E96))</f>
+        <f>SUMPRODUCT(('Picks Detail'!J82:J96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*((('Picks Detail'!J82:J96='Picks Detail'!E82:E96)+('Picks Detail'!E82:E96="PUSH"))&gt;0))</f>
         <v>9</v>
       </c>
       <c r="D70">
@@ -33584,7 +33584,7 @@
         <v>Alan Loeser</v>
       </c>
       <c r="C71" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!K82:K96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!K82:K96='Picks Detail'!E82:E96))</f>
+        <f>SUMPRODUCT(('Picks Detail'!K82:K96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*((('Picks Detail'!K82:K96='Picks Detail'!E82:E96)+('Picks Detail'!E82:E96="PUSH"))&gt;0))</f>
         <v>10</v>
       </c>
       <c r="D71">
@@ -33620,7 +33620,7 @@
         <v>Caleb Simmons</v>
       </c>
       <c r="C72" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!L82:L96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!L82:L96='Picks Detail'!E82:E96))</f>
+        <f>SUMPRODUCT(('Picks Detail'!L82:L96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*((('Picks Detail'!L82:L96='Picks Detail'!E82:E96)+('Picks Detail'!E82:E96="PUSH"))&gt;0))</f>
         <v>7</v>
       </c>
       <c r="D72">
@@ -33656,7 +33656,7 @@
         <v>Larry Loeser</v>
       </c>
       <c r="C73" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!M82:M96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!M82:M96='Picks Detail'!E82:E96))</f>
+        <f>SUMPRODUCT(('Picks Detail'!M82:M96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*((('Picks Detail'!M82:M96='Picks Detail'!E82:E96)+('Picks Detail'!E82:E96="PUSH"))&gt;0))</f>
         <v>7</v>
       </c>
       <c r="D73">
@@ -33692,7 +33692,7 @@
         <v>Daddy Michael</v>
       </c>
       <c r="C74" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!N82:N96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!N82:N96='Picks Detail'!E82:E96))</f>
+        <f>SUMPRODUCT(('Picks Detail'!N82:N96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*((('Picks Detail'!N82:N96='Picks Detail'!E82:E96)+('Picks Detail'!E82:E96="PUSH"))&gt;0))</f>
         <v>6</v>
       </c>
       <c r="D74">
@@ -33728,7 +33728,7 @@
         <v>Zach Zarra</v>
       </c>
       <c r="C75" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!O82:O96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!O82:O96='Picks Detail'!E82:E96))</f>
+        <f>SUMPRODUCT(('Picks Detail'!O82:O96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*((('Picks Detail'!O82:O96='Picks Detail'!E82:E96)+('Picks Detail'!E82:E96="PUSH"))&gt;0))</f>
         <v>7</v>
       </c>
       <c r="D75">
@@ -33764,7 +33764,7 @@
         <v>Jeffrey Loeser</v>
       </c>
       <c r="C76" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!P82:P96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!P82:P96='Picks Detail'!E82:E96))</f>
+        <f>SUMPRODUCT(('Picks Detail'!P82:P96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*((('Picks Detail'!P82:P96='Picks Detail'!E82:E96)+('Picks Detail'!E82:E96="PUSH"))&gt;0))</f>
         <v>5</v>
       </c>
       <c r="D76">
@@ -33800,7 +33800,7 @@
         <v>Jake Andrews</v>
       </c>
       <c r="C77" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!Q82:Q96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*('Picks Detail'!Q82:Q96='Picks Detail'!E82:E96))</f>
+        <f>SUMPRODUCT(('Picks Detail'!Q82:Q96&lt;&gt;"")*('Picks Detail'!E82:E96&lt;&gt;"")*((('Picks Detail'!Q82:Q96='Picks Detail'!E82:E96)+('Picks Detail'!E82:E96="PUSH"))&gt;0))</f>
         <v>4</v>
       </c>
       <c r="D77">
@@ -33870,7 +33870,7 @@
         <v>Evan Loeser</v>
       </c>
       <c r="C81" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!F100:F113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!F100:F113='Picks Detail'!E100:E113))</f>
+        <f>SUMPRODUCT(('Picks Detail'!F100:F113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*((('Picks Detail'!F100:F113='Picks Detail'!E100:E113)+('Picks Detail'!E100:E113="PUSH"))&gt;0))</f>
         <v>5</v>
       </c>
       <c r="D81">
@@ -33906,7 +33906,7 @@
         <v>Chris Simmons</v>
       </c>
       <c r="C82" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!G100:G113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!G100:G113='Picks Detail'!E100:E113))</f>
+        <f>SUMPRODUCT(('Picks Detail'!G100:G113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*((('Picks Detail'!G100:G113='Picks Detail'!E100:E113)+('Picks Detail'!E100:E113="PUSH"))&gt;0))</f>
         <v>5</v>
       </c>
       <c r="D82">
@@ -33942,7 +33942,7 @@
         <v>Jack Smith</v>
       </c>
       <c r="C83" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!H100:H113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!H100:H113='Picks Detail'!E100:E113))</f>
+        <f>SUMPRODUCT(('Picks Detail'!H100:H113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*((('Picks Detail'!H100:H113='Picks Detail'!E100:E113)+('Picks Detail'!E100:E113="PUSH"))&gt;0))</f>
         <v>7</v>
       </c>
       <c r="D83">
@@ -33978,7 +33978,7 @@
         <v>Luke Ussery</v>
       </c>
       <c r="C84" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!I100:I113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!I100:I113='Picks Detail'!E100:E113))</f>
+        <f>SUMPRODUCT(('Picks Detail'!I100:I113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*((('Picks Detail'!I100:I113='Picks Detail'!E100:E113)+('Picks Detail'!E100:E113="PUSH"))&gt;0))</f>
         <v>0</v>
       </c>
       <c r="D84">
@@ -34014,7 +34014,7 @@
         <v>Mikayla Simmons</v>
       </c>
       <c r="C85" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!J100:J113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!J100:J113='Picks Detail'!E100:E113))</f>
+        <f>SUMPRODUCT(('Picks Detail'!J100:J113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*((('Picks Detail'!J100:J113='Picks Detail'!E100:E113)+('Picks Detail'!E100:E113="PUSH"))&gt;0))</f>
         <v>7</v>
       </c>
       <c r="D85">
@@ -34050,7 +34050,7 @@
         <v>Alan Loeser</v>
       </c>
       <c r="C86" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!K100:K113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!K100:K113='Picks Detail'!E100:E113))</f>
+        <f>SUMPRODUCT(('Picks Detail'!K100:K113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*((('Picks Detail'!K100:K113='Picks Detail'!E100:E113)+('Picks Detail'!E100:E113="PUSH"))&gt;0))</f>
         <v>4</v>
       </c>
       <c r="D86">
@@ -34086,7 +34086,7 @@
         <v>Caleb Simmons</v>
       </c>
       <c r="C87" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!L100:L113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!L100:L113='Picks Detail'!E100:E113))</f>
+        <f>SUMPRODUCT(('Picks Detail'!L100:L113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*((('Picks Detail'!L100:L113='Picks Detail'!E100:E113)+('Picks Detail'!E100:E113="PUSH"))&gt;0))</f>
         <v>7</v>
       </c>
       <c r="D87">
@@ -34122,7 +34122,7 @@
         <v>Larry Loeser</v>
       </c>
       <c r="C88" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!M100:M113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!M100:M113='Picks Detail'!E100:E113))</f>
+        <f>SUMPRODUCT(('Picks Detail'!M100:M113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*((('Picks Detail'!M100:M113='Picks Detail'!E100:E113)+('Picks Detail'!E100:E113="PUSH"))&gt;0))</f>
         <v>7</v>
       </c>
       <c r="D88">
@@ -34158,7 +34158,7 @@
         <v>Daddy Michael</v>
       </c>
       <c r="C89" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!N100:N113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!N100:N113='Picks Detail'!E100:E113))</f>
+        <f>SUMPRODUCT(('Picks Detail'!N100:N113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*((('Picks Detail'!N100:N113='Picks Detail'!E100:E113)+('Picks Detail'!E100:E113="PUSH"))&gt;0))</f>
         <v>7</v>
       </c>
       <c r="D89">
@@ -34194,7 +34194,7 @@
         <v>Zach Zarra</v>
       </c>
       <c r="C90" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!O100:O113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!O100:O113='Picks Detail'!E100:E113))</f>
+        <f>SUMPRODUCT(('Picks Detail'!O100:O113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*((('Picks Detail'!O100:O113='Picks Detail'!E100:E113)+('Picks Detail'!E100:E113="PUSH"))&gt;0))</f>
         <v>6</v>
       </c>
       <c r="D90">
@@ -34230,7 +34230,7 @@
         <v>Jeffrey Loeser</v>
       </c>
       <c r="C91" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!P100:P113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!P100:P113='Picks Detail'!E100:E113))</f>
+        <f>SUMPRODUCT(('Picks Detail'!P100:P113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*((('Picks Detail'!P100:P113='Picks Detail'!E100:E113)+('Picks Detail'!E100:E113="PUSH"))&gt;0))</f>
         <v>6</v>
       </c>
       <c r="D91">
@@ -34266,7 +34266,7 @@
         <v>Jake Andrews</v>
       </c>
       <c r="C92" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!Q100:Q113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*('Picks Detail'!Q100:Q113='Picks Detail'!E100:E113))</f>
+        <f>SUMPRODUCT(('Picks Detail'!Q100:Q113&lt;&gt;"")*('Picks Detail'!E100:E113&lt;&gt;"")*((('Picks Detail'!Q100:Q113='Picks Detail'!E100:E113)+('Picks Detail'!E100:E113="PUSH"))&gt;0))</f>
         <v>6</v>
       </c>
       <c r="D92">
@@ -34373,7 +34373,7 @@
         <v>Evan Loeser</v>
       </c>
       <c r="C6" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!F117:F130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*('Picks Detail'!F117:F130='Picks Detail'!E117:E130)*('Picks Detail'!S117:S130))</f>
+        <f>SUMPRODUCT(('Picks Detail'!F117:F130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*((('Picks Detail'!F117:F130='Picks Detail'!E117:E130)+('Picks Detail'!E117:E130="PUSH"))&gt;0)*('Picks Detail'!S117:S130))</f>
         <v>0</v>
       </c>
       <c r="D6">
@@ -34409,7 +34409,7 @@
         <v>Chris Simmons</v>
       </c>
       <c r="C7" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!G117:G130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*('Picks Detail'!G117:G130='Picks Detail'!E117:E130)*('Picks Detail'!T117:T130))</f>
+        <f>SUMPRODUCT(('Picks Detail'!G117:G130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*((('Picks Detail'!G117:G130='Picks Detail'!E117:E130)+('Picks Detail'!E117:E130="PUSH"))&gt;0)*('Picks Detail'!T117:T130))</f>
         <v>8</v>
       </c>
       <c r="D7">
@@ -34445,7 +34445,7 @@
         <v>Jack Smith</v>
       </c>
       <c r="C8" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!H117:H130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*('Picks Detail'!H117:H130='Picks Detail'!E117:E130)*('Picks Detail'!U117:U130))</f>
+        <f>SUMPRODUCT(('Picks Detail'!H117:H130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*((('Picks Detail'!H117:H130='Picks Detail'!E117:E130)+('Picks Detail'!E117:E130="PUSH"))&gt;0)*('Picks Detail'!U117:U130))</f>
         <v>0</v>
       </c>
       <c r="D8">
@@ -34481,7 +34481,7 @@
         <v>Luke Ussery</v>
       </c>
       <c r="C9" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!I117:I130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*('Picks Detail'!I117:I130='Picks Detail'!E117:E130)*('Picks Detail'!V117:V130))</f>
+        <f>SUMPRODUCT(('Picks Detail'!I117:I130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*((('Picks Detail'!I117:I130='Picks Detail'!E117:E130)+('Picks Detail'!E117:E130="PUSH"))&gt;0)*('Picks Detail'!V117:V130))</f>
         <v>0</v>
       </c>
       <c r="D9">
@@ -34517,7 +34517,7 @@
         <v>Mikayla Simmons</v>
       </c>
       <c r="C10" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!J117:J130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*('Picks Detail'!J117:J130='Picks Detail'!E117:E130)*('Picks Detail'!W117:W130))</f>
+        <f>SUMPRODUCT(('Picks Detail'!J117:J130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*((('Picks Detail'!J117:J130='Picks Detail'!E117:E130)+('Picks Detail'!E117:E130="PUSH"))&gt;0)*('Picks Detail'!W117:W130))</f>
         <v>0</v>
       </c>
       <c r="D10">
@@ -34553,7 +34553,7 @@
         <v>Alan Loeser</v>
       </c>
       <c r="C11" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!K117:K130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*('Picks Detail'!K117:K130='Picks Detail'!E117:E130)*('Picks Detail'!X117:X130))</f>
+        <f>SUMPRODUCT(('Picks Detail'!K117:K130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*((('Picks Detail'!K117:K130='Picks Detail'!E117:E130)+('Picks Detail'!E117:E130="PUSH"))&gt;0)*('Picks Detail'!X117:X130))</f>
         <v>6</v>
       </c>
       <c r="D11">
@@ -34589,7 +34589,7 @@
         <v>Caleb Simmons</v>
       </c>
       <c r="C12" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!L117:L130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*('Picks Detail'!L117:L130='Picks Detail'!E117:E130)*('Picks Detail'!Y117:Y130))</f>
+        <f>SUMPRODUCT(('Picks Detail'!L117:L130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*((('Picks Detail'!L117:L130='Picks Detail'!E117:E130)+('Picks Detail'!E117:E130="PUSH"))&gt;0)*('Picks Detail'!Y117:Y130))</f>
         <v>0</v>
       </c>
       <c r="D12">
@@ -34625,7 +34625,7 @@
         <v>Larry Loeser</v>
       </c>
       <c r="C13" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!M117:M130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*('Picks Detail'!M117:M130='Picks Detail'!E117:E130)*('Picks Detail'!Z117:Z130))</f>
+        <f>SUMPRODUCT(('Picks Detail'!M117:M130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*((('Picks Detail'!M117:M130='Picks Detail'!E117:E130)+('Picks Detail'!E117:E130="PUSH"))&gt;0)*('Picks Detail'!Z117:Z130))</f>
         <v>0</v>
       </c>
       <c r="D13">
@@ -34661,7 +34661,7 @@
         <v>Daddy Michael</v>
       </c>
       <c r="C14" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!N117:N130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*('Picks Detail'!N117:N130='Picks Detail'!E117:E130)*('Picks Detail'!AA117:AA130))</f>
+        <f>SUMPRODUCT(('Picks Detail'!N117:N130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*((('Picks Detail'!N117:N130='Picks Detail'!E117:E130)+('Picks Detail'!E117:E130="PUSH"))&gt;0)*('Picks Detail'!AA117:AA130))</f>
         <v>6</v>
       </c>
       <c r="D14">
@@ -34697,7 +34697,7 @@
         <v>Zach Zarra</v>
       </c>
       <c r="C15" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!O117:O130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*('Picks Detail'!O117:O130='Picks Detail'!E117:E130)*('Picks Detail'!AB117:AB130))</f>
+        <f>SUMPRODUCT(('Picks Detail'!O117:O130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*((('Picks Detail'!O117:O130='Picks Detail'!E117:E130)+('Picks Detail'!E117:E130="PUSH"))&gt;0)*('Picks Detail'!AB117:AB130))</f>
         <v>0</v>
       </c>
       <c r="D15">
@@ -34733,7 +34733,7 @@
         <v>Jeffrey Loeser</v>
       </c>
       <c r="C16" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!P117:P130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*('Picks Detail'!P117:P130='Picks Detail'!E117:E130)*('Picks Detail'!AC117:AC130))</f>
+        <f>SUMPRODUCT(('Picks Detail'!P117:P130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*((('Picks Detail'!P117:P130='Picks Detail'!E117:E130)+('Picks Detail'!E117:E130="PUSH"))&gt;0)*('Picks Detail'!AC117:AC130))</f>
         <v>6</v>
       </c>
       <c r="D16">
@@ -34769,7 +34769,7 @@
         <v>Jake Andrews</v>
       </c>
       <c r="C17" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!Q117:Q130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*('Picks Detail'!Q117:Q130='Picks Detail'!E117:E130)*('Picks Detail'!AD117:AD130))</f>
+        <f>SUMPRODUCT(('Picks Detail'!Q117:Q130&lt;&gt;"")*('Picks Detail'!E117:E130&lt;&gt;"")*((('Picks Detail'!Q117:Q130='Picks Detail'!E117:E130)+('Picks Detail'!E117:E130="PUSH"))&gt;0)*('Picks Detail'!AD117:AD130))</f>
         <v>6</v>
       </c>
       <c r="D17">
@@ -34839,7 +34839,7 @@
         <v>Evan Loeser</v>
       </c>
       <c r="C21" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!F134:F147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*('Picks Detail'!F134:F147='Picks Detail'!E134:E147)*('Picks Detail'!S134:S147))</f>
+        <f>SUMPRODUCT(('Picks Detail'!F134:F147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*((('Picks Detail'!F134:F147='Picks Detail'!E134:E147)+('Picks Detail'!E134:E147="PUSH"))&gt;0)*('Picks Detail'!S134:S147))</f>
         <v>0</v>
       </c>
       <c r="D21">
@@ -34875,7 +34875,7 @@
         <v>Chris Simmons</v>
       </c>
       <c r="C22" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!G134:G147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*('Picks Detail'!G134:G147='Picks Detail'!E134:E147)*('Picks Detail'!T134:T147))</f>
+        <f>SUMPRODUCT(('Picks Detail'!G134:G147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*((('Picks Detail'!G134:G147='Picks Detail'!E134:E147)+('Picks Detail'!E134:E147="PUSH"))&gt;0)*('Picks Detail'!T134:T147))</f>
         <v>0</v>
       </c>
       <c r="D22">
@@ -34911,7 +34911,7 @@
         <v>Jack Smith</v>
       </c>
       <c r="C23" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!H134:H147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*('Picks Detail'!H134:H147='Picks Detail'!E134:E147)*('Picks Detail'!U134:U147))</f>
+        <f>SUMPRODUCT(('Picks Detail'!H134:H147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*((('Picks Detail'!H134:H147='Picks Detail'!E134:E147)+('Picks Detail'!E134:E147="PUSH"))&gt;0)*('Picks Detail'!U134:U147))</f>
         <v>0</v>
       </c>
       <c r="D23">
@@ -34947,7 +34947,7 @@
         <v>Luke Ussery</v>
       </c>
       <c r="C24" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!I134:I147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*('Picks Detail'!I134:I147='Picks Detail'!E134:E147)*('Picks Detail'!V134:V147))</f>
+        <f>SUMPRODUCT(('Picks Detail'!I134:I147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*((('Picks Detail'!I134:I147='Picks Detail'!E134:E147)+('Picks Detail'!E134:E147="PUSH"))&gt;0)*('Picks Detail'!V134:V147))</f>
         <v>0</v>
       </c>
       <c r="D24">
@@ -34983,7 +34983,7 @@
         <v>Mikayla Simmons</v>
       </c>
       <c r="C25" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!J134:J147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*('Picks Detail'!J134:J147='Picks Detail'!E134:E147)*('Picks Detail'!W134:W147))</f>
+        <f>SUMPRODUCT(('Picks Detail'!J134:J147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*((('Picks Detail'!J134:J147='Picks Detail'!E134:E147)+('Picks Detail'!E134:E147="PUSH"))&gt;0)*('Picks Detail'!W134:W147))</f>
         <v>0</v>
       </c>
       <c r="D25">
@@ -35019,7 +35019,7 @@
         <v>Alan Loeser</v>
       </c>
       <c r="C26" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!K134:K147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*('Picks Detail'!K134:K147='Picks Detail'!E134:E147)*('Picks Detail'!X134:X147))</f>
+        <f>SUMPRODUCT(('Picks Detail'!K134:K147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*((('Picks Detail'!K134:K147='Picks Detail'!E134:E147)+('Picks Detail'!E134:E147="PUSH"))&gt;0)*('Picks Detail'!X134:X147))</f>
         <v>0</v>
       </c>
       <c r="D26">
@@ -35055,7 +35055,7 @@
         <v>Caleb Simmons</v>
       </c>
       <c r="C27" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!L134:L147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*('Picks Detail'!L134:L147='Picks Detail'!E134:E147)*('Picks Detail'!Y134:Y147))</f>
+        <f>SUMPRODUCT(('Picks Detail'!L134:L147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*((('Picks Detail'!L134:L147='Picks Detail'!E134:E147)+('Picks Detail'!E134:E147="PUSH"))&gt;0)*('Picks Detail'!Y134:Y147))</f>
         <v>0</v>
       </c>
       <c r="D27">
@@ -35091,7 +35091,7 @@
         <v>Larry Loeser</v>
       </c>
       <c r="C28" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!M134:M147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*('Picks Detail'!M134:M147='Picks Detail'!E134:E147)*('Picks Detail'!Z134:Z147))</f>
+        <f>SUMPRODUCT(('Picks Detail'!M134:M147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*((('Picks Detail'!M134:M147='Picks Detail'!E134:E147)+('Picks Detail'!E134:E147="PUSH"))&gt;0)*('Picks Detail'!Z134:Z147))</f>
         <v>0</v>
       </c>
       <c r="D28">
@@ -35127,7 +35127,7 @@
         <v>Daddy Michael</v>
       </c>
       <c r="C29" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!N134:N147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*('Picks Detail'!N134:N147='Picks Detail'!E134:E147)*('Picks Detail'!AA134:AA147))</f>
+        <f>SUMPRODUCT(('Picks Detail'!N134:N147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*((('Picks Detail'!N134:N147='Picks Detail'!E134:E147)+('Picks Detail'!E134:E147="PUSH"))&gt;0)*('Picks Detail'!AA134:AA147))</f>
         <v>0</v>
       </c>
       <c r="D29">
@@ -35163,7 +35163,7 @@
         <v>Zach Zarra</v>
       </c>
       <c r="C30" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!O134:O147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*('Picks Detail'!O134:O147='Picks Detail'!E134:E147)*('Picks Detail'!AB134:AB147))</f>
+        <f>SUMPRODUCT(('Picks Detail'!O134:O147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*((('Picks Detail'!O134:O147='Picks Detail'!E134:E147)+('Picks Detail'!E134:E147="PUSH"))&gt;0)*('Picks Detail'!AB134:AB147))</f>
         <v>0</v>
       </c>
       <c r="D30">
@@ -35199,7 +35199,7 @@
         <v>Jeffrey Loeser</v>
       </c>
       <c r="C31" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!P134:P147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*('Picks Detail'!P134:P147='Picks Detail'!E134:E147)*('Picks Detail'!AC134:AC147))</f>
+        <f>SUMPRODUCT(('Picks Detail'!P134:P147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*((('Picks Detail'!P134:P147='Picks Detail'!E134:E147)+('Picks Detail'!E134:E147="PUSH"))&gt;0)*('Picks Detail'!AC134:AC147))</f>
         <v>0</v>
       </c>
       <c r="D31">
@@ -35235,7 +35235,7 @@
         <v>Jake Andrews</v>
       </c>
       <c r="C32" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!Q134:Q147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*('Picks Detail'!Q134:Q147='Picks Detail'!E134:E147)*('Picks Detail'!AD134:AD147))</f>
+        <f>SUMPRODUCT(('Picks Detail'!Q134:Q147&lt;&gt;"")*('Picks Detail'!E134:E147&lt;&gt;"")*((('Picks Detail'!Q134:Q147='Picks Detail'!E134:E147)+('Picks Detail'!E134:E147="PUSH"))&gt;0)*('Picks Detail'!AD134:AD147))</f>
         <v>0</v>
       </c>
       <c r="D32">
@@ -35305,7 +35305,7 @@
         <v>Evan Loeser</v>
       </c>
       <c r="C36" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!F151:F165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*('Picks Detail'!F151:F165='Picks Detail'!E151:E165)*('Picks Detail'!S151:S165))</f>
+        <f>SUMPRODUCT(('Picks Detail'!F151:F165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*((('Picks Detail'!F151:F165='Picks Detail'!E151:E165)+('Picks Detail'!E151:E165="PUSH"))&gt;0)*('Picks Detail'!S151:S165))</f>
         <v>0</v>
       </c>
       <c r="D36">
@@ -35341,7 +35341,7 @@
         <v>Chris Simmons</v>
       </c>
       <c r="C37" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!G151:G165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*('Picks Detail'!G151:G165='Picks Detail'!E151:E165)*('Picks Detail'!T151:T165))</f>
+        <f>SUMPRODUCT(('Picks Detail'!G151:G165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*((('Picks Detail'!G151:G165='Picks Detail'!E151:E165)+('Picks Detail'!E151:E165="PUSH"))&gt;0)*('Picks Detail'!T151:T165))</f>
         <v>0</v>
       </c>
       <c r="D37">
@@ -35377,7 +35377,7 @@
         <v>Jack Smith</v>
       </c>
       <c r="C38" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!H151:H165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*('Picks Detail'!H151:H165='Picks Detail'!E151:E165)*('Picks Detail'!U151:U165))</f>
+        <f>SUMPRODUCT(('Picks Detail'!H151:H165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*((('Picks Detail'!H151:H165='Picks Detail'!E151:E165)+('Picks Detail'!E151:E165="PUSH"))&gt;0)*('Picks Detail'!U151:U165))</f>
         <v>0</v>
       </c>
       <c r="D38">
@@ -35413,7 +35413,7 @@
         <v>Luke Ussery</v>
       </c>
       <c r="C39" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!I151:I165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*('Picks Detail'!I151:I165='Picks Detail'!E151:E165)*('Picks Detail'!V151:V165))</f>
+        <f>SUMPRODUCT(('Picks Detail'!I151:I165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*((('Picks Detail'!I151:I165='Picks Detail'!E151:E165)+('Picks Detail'!E151:E165="PUSH"))&gt;0)*('Picks Detail'!V151:V165))</f>
         <v>0</v>
       </c>
       <c r="D39">
@@ -35449,7 +35449,7 @@
         <v>Mikayla Simmons</v>
       </c>
       <c r="C40" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!J151:J165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*('Picks Detail'!J151:J165='Picks Detail'!E151:E165)*('Picks Detail'!W151:W165))</f>
+        <f>SUMPRODUCT(('Picks Detail'!J151:J165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*((('Picks Detail'!J151:J165='Picks Detail'!E151:E165)+('Picks Detail'!E151:E165="PUSH"))&gt;0)*('Picks Detail'!W151:W165))</f>
         <v>0</v>
       </c>
       <c r="D40">
@@ -35485,7 +35485,7 @@
         <v>Alan Loeser</v>
       </c>
       <c r="C41" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!K151:K165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*('Picks Detail'!K151:K165='Picks Detail'!E151:E165)*('Picks Detail'!X151:X165))</f>
+        <f>SUMPRODUCT(('Picks Detail'!K151:K165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*((('Picks Detail'!K151:K165='Picks Detail'!E151:E165)+('Picks Detail'!E151:E165="PUSH"))&gt;0)*('Picks Detail'!X151:X165))</f>
         <v>0</v>
       </c>
       <c r="D41">
@@ -35521,7 +35521,7 @@
         <v>Caleb Simmons</v>
       </c>
       <c r="C42" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!L151:L165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*('Picks Detail'!L151:L165='Picks Detail'!E151:E165)*('Picks Detail'!Y151:Y165))</f>
+        <f>SUMPRODUCT(('Picks Detail'!L151:L165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*((('Picks Detail'!L151:L165='Picks Detail'!E151:E165)+('Picks Detail'!E151:E165="PUSH"))&gt;0)*('Picks Detail'!Y151:Y165))</f>
         <v>0</v>
       </c>
       <c r="D42">
@@ -35557,7 +35557,7 @@
         <v>Larry Loeser</v>
       </c>
       <c r="C43" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!M151:M165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*('Picks Detail'!M151:M165='Picks Detail'!E151:E165)*('Picks Detail'!Z151:Z165))</f>
+        <f>SUMPRODUCT(('Picks Detail'!M151:M165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*((('Picks Detail'!M151:M165='Picks Detail'!E151:E165)+('Picks Detail'!E151:E165="PUSH"))&gt;0)*('Picks Detail'!Z151:Z165))</f>
         <v>0</v>
       </c>
       <c r="D43">
@@ -35593,7 +35593,7 @@
         <v>Daddy Michael</v>
       </c>
       <c r="C44" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!N151:N165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*('Picks Detail'!N151:N165='Picks Detail'!E151:E165)*('Picks Detail'!AA151:AA165))</f>
+        <f>SUMPRODUCT(('Picks Detail'!N151:N165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*((('Picks Detail'!N151:N165='Picks Detail'!E151:E165)+('Picks Detail'!E151:E165="PUSH"))&gt;0)*('Picks Detail'!AA151:AA165))</f>
         <v>0</v>
       </c>
       <c r="D44">
@@ -35629,7 +35629,7 @@
         <v>Zach Zarra</v>
       </c>
       <c r="C45" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!O151:O165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*('Picks Detail'!O151:O165='Picks Detail'!E151:E165)*('Picks Detail'!AB151:AB165))</f>
+        <f>SUMPRODUCT(('Picks Detail'!O151:O165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*((('Picks Detail'!O151:O165='Picks Detail'!E151:E165)+('Picks Detail'!E151:E165="PUSH"))&gt;0)*('Picks Detail'!AB151:AB165))</f>
         <v>0</v>
       </c>
       <c r="D45">
@@ -35665,7 +35665,7 @@
         <v>Jeffrey Loeser</v>
       </c>
       <c r="C46" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!P151:P165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*('Picks Detail'!P151:P165='Picks Detail'!E151:E165)*('Picks Detail'!AC151:AC165))</f>
+        <f>SUMPRODUCT(('Picks Detail'!P151:P165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*((('Picks Detail'!P151:P165='Picks Detail'!E151:E165)+('Picks Detail'!E151:E165="PUSH"))&gt;0)*('Picks Detail'!AC151:AC165))</f>
         <v>0</v>
       </c>
       <c r="D46">
@@ -35701,7 +35701,7 @@
         <v>Jake Andrews</v>
       </c>
       <c r="C47" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!Q151:Q165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*('Picks Detail'!Q151:Q165='Picks Detail'!E151:E165)*('Picks Detail'!AD151:AD165))</f>
+        <f>SUMPRODUCT(('Picks Detail'!Q151:Q165&lt;&gt;"")*('Picks Detail'!E151:E165&lt;&gt;"")*((('Picks Detail'!Q151:Q165='Picks Detail'!E151:E165)+('Picks Detail'!E151:E165="PUSH"))&gt;0)*('Picks Detail'!AD151:AD165))</f>
         <v>0</v>
       </c>
       <c r="D47">
@@ -35771,7 +35771,7 @@
         <v>Evan Loeser</v>
       </c>
       <c r="C51" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!F169:F182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*('Picks Detail'!F169:F182='Picks Detail'!E169:E182)*('Picks Detail'!S169:S182))</f>
+        <f>SUMPRODUCT(('Picks Detail'!F169:F182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*((('Picks Detail'!F169:F182='Picks Detail'!E169:E182)+('Picks Detail'!E169:E182="PUSH"))&gt;0)*('Picks Detail'!S169:S182))</f>
         <v>0</v>
       </c>
       <c r="D51">
@@ -35807,7 +35807,7 @@
         <v>Chris Simmons</v>
       </c>
       <c r="C52" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!G169:G182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*('Picks Detail'!G169:G182='Picks Detail'!E169:E182)*('Picks Detail'!T169:T182))</f>
+        <f>SUMPRODUCT(('Picks Detail'!G169:G182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*((('Picks Detail'!G169:G182='Picks Detail'!E169:E182)+('Picks Detail'!E169:E182="PUSH"))&gt;0)*('Picks Detail'!T169:T182))</f>
         <v>0</v>
       </c>
       <c r="D52">
@@ -35843,7 +35843,7 @@
         <v>Jack Smith</v>
       </c>
       <c r="C53" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!H169:H182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*('Picks Detail'!H169:H182='Picks Detail'!E169:E182)*('Picks Detail'!U169:U182))</f>
+        <f>SUMPRODUCT(('Picks Detail'!H169:H182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*((('Picks Detail'!H169:H182='Picks Detail'!E169:E182)+('Picks Detail'!E169:E182="PUSH"))&gt;0)*('Picks Detail'!U169:U182))</f>
         <v>0</v>
       </c>
       <c r="D53">
@@ -35879,7 +35879,7 @@
         <v>Luke Ussery</v>
       </c>
       <c r="C54" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!I169:I182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*('Picks Detail'!I169:I182='Picks Detail'!E169:E182)*('Picks Detail'!V169:V182))</f>
+        <f>SUMPRODUCT(('Picks Detail'!I169:I182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*((('Picks Detail'!I169:I182='Picks Detail'!E169:E182)+('Picks Detail'!E169:E182="PUSH"))&gt;0)*('Picks Detail'!V169:V182))</f>
         <v>0</v>
       </c>
       <c r="D54">
@@ -35915,7 +35915,7 @@
         <v>Mikayla Simmons</v>
       </c>
       <c r="C55" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!J169:J182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*('Picks Detail'!J169:J182='Picks Detail'!E169:E182)*('Picks Detail'!W169:W182))</f>
+        <f>SUMPRODUCT(('Picks Detail'!J169:J182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*((('Picks Detail'!J169:J182='Picks Detail'!E169:E182)+('Picks Detail'!E169:E182="PUSH"))&gt;0)*('Picks Detail'!W169:W182))</f>
         <v>0</v>
       </c>
       <c r="D55">
@@ -35951,7 +35951,7 @@
         <v>Alan Loeser</v>
       </c>
       <c r="C56" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!K169:K182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*('Picks Detail'!K169:K182='Picks Detail'!E169:E182)*('Picks Detail'!X169:X182))</f>
+        <f>SUMPRODUCT(('Picks Detail'!K169:K182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*((('Picks Detail'!K169:K182='Picks Detail'!E169:E182)+('Picks Detail'!E169:E182="PUSH"))&gt;0)*('Picks Detail'!X169:X182))</f>
         <v>0</v>
       </c>
       <c r="D56">
@@ -35987,7 +35987,7 @@
         <v>Caleb Simmons</v>
       </c>
       <c r="C57" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!L169:L182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*('Picks Detail'!L169:L182='Picks Detail'!E169:E182)*('Picks Detail'!Y169:Y182))</f>
+        <f>SUMPRODUCT(('Picks Detail'!L169:L182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*((('Picks Detail'!L169:L182='Picks Detail'!E169:E182)+('Picks Detail'!E169:E182="PUSH"))&gt;0)*('Picks Detail'!Y169:Y182))</f>
         <v>0</v>
       </c>
       <c r="D57">
@@ -36023,7 +36023,7 @@
         <v>Larry Loeser</v>
       </c>
       <c r="C58" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!M169:M182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*('Picks Detail'!M169:M182='Picks Detail'!E169:E182)*('Picks Detail'!Z169:Z182))</f>
+        <f>SUMPRODUCT(('Picks Detail'!M169:M182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*((('Picks Detail'!M169:M182='Picks Detail'!E169:E182)+('Picks Detail'!E169:E182="PUSH"))&gt;0)*('Picks Detail'!Z169:Z182))</f>
         <v>0</v>
       </c>
       <c r="D58">
@@ -36059,7 +36059,7 @@
         <v>Daddy Michael</v>
       </c>
       <c r="C59" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!N169:N182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*('Picks Detail'!N169:N182='Picks Detail'!E169:E182)*('Picks Detail'!AA169:AA182))</f>
+        <f>SUMPRODUCT(('Picks Detail'!N169:N182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*((('Picks Detail'!N169:N182='Picks Detail'!E169:E182)+('Picks Detail'!E169:E182="PUSH"))&gt;0)*('Picks Detail'!AA169:AA182))</f>
         <v>0</v>
       </c>
       <c r="D59">
@@ -36095,7 +36095,7 @@
         <v>Zach Zarra</v>
       </c>
       <c r="C60" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!O169:O182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*('Picks Detail'!O169:O182='Picks Detail'!E169:E182)*('Picks Detail'!AB169:AB182))</f>
+        <f>SUMPRODUCT(('Picks Detail'!O169:O182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*((('Picks Detail'!O169:O182='Picks Detail'!E169:E182)+('Picks Detail'!E169:E182="PUSH"))&gt;0)*('Picks Detail'!AB169:AB182))</f>
         <v>0</v>
       </c>
       <c r="D60">
@@ -36131,7 +36131,7 @@
         <v>Jeffrey Loeser</v>
       </c>
       <c r="C61" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!P169:P182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*('Picks Detail'!P169:P182='Picks Detail'!E169:E182)*('Picks Detail'!AC169:AC182))</f>
+        <f>SUMPRODUCT(('Picks Detail'!P169:P182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*((('Picks Detail'!P169:P182='Picks Detail'!E169:E182)+('Picks Detail'!E169:E182="PUSH"))&gt;0)*('Picks Detail'!AC169:AC182))</f>
         <v>0</v>
       </c>
       <c r="D61">
@@ -36167,7 +36167,7 @@
         <v>Jake Andrews</v>
       </c>
       <c r="C62" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!Q169:Q182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*('Picks Detail'!Q169:Q182='Picks Detail'!E169:E182)*('Picks Detail'!AD169:AD182))</f>
+        <f>SUMPRODUCT(('Picks Detail'!Q169:Q182&lt;&gt;"")*('Picks Detail'!E169:E182&lt;&gt;"")*((('Picks Detail'!Q169:Q182='Picks Detail'!E169:E182)+('Picks Detail'!E169:E182="PUSH"))&gt;0)*('Picks Detail'!AD169:AD182))</f>
         <v>0</v>
       </c>
       <c r="D62">
@@ -36237,7 +36237,7 @@
         <v>Evan Loeser</v>
       </c>
       <c r="C66" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!F186:F198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*('Picks Detail'!F186:F198='Picks Detail'!E186:E198)*('Picks Detail'!S186:S198))</f>
+        <f>SUMPRODUCT(('Picks Detail'!F186:F198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*((('Picks Detail'!F186:F198='Picks Detail'!E186:E198)+('Picks Detail'!E186:E198="PUSH"))&gt;0)*('Picks Detail'!S186:S198))</f>
         <v>0</v>
       </c>
       <c r="D66">
@@ -36273,7 +36273,7 @@
         <v>Chris Simmons</v>
       </c>
       <c r="C67" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!G186:G198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*('Picks Detail'!G186:G198='Picks Detail'!E186:E198)*('Picks Detail'!T186:T198))</f>
+        <f>SUMPRODUCT(('Picks Detail'!G186:G198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*((('Picks Detail'!G186:G198='Picks Detail'!E186:E198)+('Picks Detail'!E186:E198="PUSH"))&gt;0)*('Picks Detail'!T186:T198))</f>
         <v>0</v>
       </c>
       <c r="D67">
@@ -36309,7 +36309,7 @@
         <v>Jack Smith</v>
       </c>
       <c r="C68" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!H186:H198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*('Picks Detail'!H186:H198='Picks Detail'!E186:E198)*('Picks Detail'!U186:U198))</f>
+        <f>SUMPRODUCT(('Picks Detail'!H186:H198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*((('Picks Detail'!H186:H198='Picks Detail'!E186:E198)+('Picks Detail'!E186:E198="PUSH"))&gt;0)*('Picks Detail'!U186:U198))</f>
         <v>0</v>
       </c>
       <c r="D68">
@@ -36345,7 +36345,7 @@
         <v>Luke Ussery</v>
       </c>
       <c r="C69" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!I186:I198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*('Picks Detail'!I186:I198='Picks Detail'!E186:E198)*('Picks Detail'!V186:V198))</f>
+        <f>SUMPRODUCT(('Picks Detail'!I186:I198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*((('Picks Detail'!I186:I198='Picks Detail'!E186:E198)+('Picks Detail'!E186:E198="PUSH"))&gt;0)*('Picks Detail'!V186:V198))</f>
         <v>0</v>
       </c>
       <c r="D69">
@@ -36381,7 +36381,7 @@
         <v>Mikayla Simmons</v>
       </c>
       <c r="C70" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!J186:J198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*('Picks Detail'!J186:J198='Picks Detail'!E186:E198)*('Picks Detail'!W186:W198))</f>
+        <f>SUMPRODUCT(('Picks Detail'!J186:J198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*((('Picks Detail'!J186:J198='Picks Detail'!E186:E198)+('Picks Detail'!E186:E198="PUSH"))&gt;0)*('Picks Detail'!W186:W198))</f>
         <v>0</v>
       </c>
       <c r="D70">
@@ -36417,7 +36417,7 @@
         <v>Alan Loeser</v>
       </c>
       <c r="C71" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!K186:K198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*('Picks Detail'!K186:K198='Picks Detail'!E186:E198)*('Picks Detail'!X186:X198))</f>
+        <f>SUMPRODUCT(('Picks Detail'!K186:K198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*((('Picks Detail'!K186:K198='Picks Detail'!E186:E198)+('Picks Detail'!E186:E198="PUSH"))&gt;0)*('Picks Detail'!X186:X198))</f>
         <v>0</v>
       </c>
       <c r="D71">
@@ -36453,7 +36453,7 @@
         <v>Caleb Simmons</v>
       </c>
       <c r="C72" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!L186:L198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*('Picks Detail'!L186:L198='Picks Detail'!E186:E198)*('Picks Detail'!Y186:Y198))</f>
+        <f>SUMPRODUCT(('Picks Detail'!L186:L198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*((('Picks Detail'!L186:L198='Picks Detail'!E186:E198)+('Picks Detail'!E186:E198="PUSH"))&gt;0)*('Picks Detail'!Y186:Y198))</f>
         <v>0</v>
       </c>
       <c r="D72">
@@ -36489,7 +36489,7 @@
         <v>Larry Loeser</v>
       </c>
       <c r="C73" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!M186:M198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*('Picks Detail'!M186:M198='Picks Detail'!E186:E198)*('Picks Detail'!Z186:Z198))</f>
+        <f>SUMPRODUCT(('Picks Detail'!M186:M198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*((('Picks Detail'!M186:M198='Picks Detail'!E186:E198)+('Picks Detail'!E186:E198="PUSH"))&gt;0)*('Picks Detail'!Z186:Z198))</f>
         <v>0</v>
       </c>
       <c r="D73">
@@ -36525,7 +36525,7 @@
         <v>Daddy Michael</v>
       </c>
       <c r="C74" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!N186:N198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*('Picks Detail'!N186:N198='Picks Detail'!E186:E198)*('Picks Detail'!AA186:AA198))</f>
+        <f>SUMPRODUCT(('Picks Detail'!N186:N198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*((('Picks Detail'!N186:N198='Picks Detail'!E186:E198)+('Picks Detail'!E186:E198="PUSH"))&gt;0)*('Picks Detail'!AA186:AA198))</f>
         <v>0</v>
       </c>
       <c r="D74">
@@ -36561,7 +36561,7 @@
         <v>Zach Zarra</v>
       </c>
       <c r="C75" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!O186:O198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*('Picks Detail'!O186:O198='Picks Detail'!E186:E198)*('Picks Detail'!AB186:AB198))</f>
+        <f>SUMPRODUCT(('Picks Detail'!O186:O198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*((('Picks Detail'!O186:O198='Picks Detail'!E186:E198)+('Picks Detail'!E186:E198="PUSH"))&gt;0)*('Picks Detail'!AB186:AB198))</f>
         <v>0</v>
       </c>
       <c r="D75">
@@ -36597,7 +36597,7 @@
         <v>Jeffrey Loeser</v>
       </c>
       <c r="C76" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!P186:P198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*('Picks Detail'!P186:P198='Picks Detail'!E186:E198)*('Picks Detail'!AC186:AC198))</f>
+        <f>SUMPRODUCT(('Picks Detail'!P186:P198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*((('Picks Detail'!P186:P198='Picks Detail'!E186:E198)+('Picks Detail'!E186:E198="PUSH"))&gt;0)*('Picks Detail'!AC186:AC198))</f>
         <v>0</v>
       </c>
       <c r="D76">
@@ -36633,7 +36633,7 @@
         <v>Jake Andrews</v>
       </c>
       <c r="C77" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!Q186:Q198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*('Picks Detail'!Q186:Q198='Picks Detail'!E186:E198)*('Picks Detail'!AD186:AD198))</f>
+        <f>SUMPRODUCT(('Picks Detail'!Q186:Q198&lt;&gt;"")*('Picks Detail'!E186:E198&lt;&gt;"")*((('Picks Detail'!Q186:Q198='Picks Detail'!E186:E198)+('Picks Detail'!E186:E198="PUSH"))&gt;0)*('Picks Detail'!AD186:AD198))</f>
         <v>0</v>
       </c>
       <c r="D77">
@@ -36703,7 +36703,7 @@
         <v>Evan Loeser</v>
       </c>
       <c r="C81" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!F202:F217&lt;&gt;"")*('Picks Detail'!E202:E217&lt;&gt;"")*('Picks Detail'!F202:F217='Picks Detail'!E202:E217)*('Picks Detail'!S202:S217))</f>
+        <f>SUMPRODUCT(('Picks Detail'!F202:F217&lt;&gt;"")*('Picks Detail'!E202:E217&lt;&gt;"")*((('Picks Detail'!F202:F217='Picks Detail'!E202:E217)+('Picks Detail'!E202:E217="PUSH"))&gt;0)*('Picks Detail'!S202:S217))</f>
         <v>0</v>
       </c>
       <c r="D81">
@@ -36739,7 +36739,7 @@
         <v>Chris Simmons</v>
       </c>
       <c r="C82" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!G202:G217&lt;&gt;"")*('Picks Detail'!E202:E217&lt;&gt;"")*('Picks Detail'!G202:G217='Picks Detail'!E202:E217)*('Picks Detail'!T202:T217))</f>
+        <f>SUMPRODUCT(('Picks Detail'!G202:G217&lt;&gt;"")*('Picks Detail'!E202:E217&lt;&gt;"")*((('Picks Detail'!G202:G217='Picks Detail'!E202:E217)+('Picks Detail'!E202:E217="PUSH"))&gt;0)*('Picks Detail'!T202:T217))</f>
         <v>0</v>
       </c>
       <c r="D82">
@@ -36775,7 +36775,7 @@
         <v>Jack Smith</v>
       </c>
       <c r="C83" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!H202:H217&lt;&gt;"")*('Picks Detail'!E202:E217&lt;&gt;"")*('Picks Detail'!H202:H217='Picks Detail'!E202:E217)*('Picks Detail'!U202:U217))</f>
+        <f>SUMPRODUCT(('Picks Detail'!H202:H217&lt;&gt;"")*('Picks Detail'!E202:E217&lt;&gt;"")*((('Picks Detail'!H202:H217='Picks Detail'!E202:E217)+('Picks Detail'!E202:E217="PUSH"))&gt;0)*('Picks Detail'!U202:U217))</f>
         <v>0</v>
       </c>
       <c r="D83">
@@ -36811,7 +36811,7 @@
         <v>Luke Ussery</v>
       </c>
       <c r="C84" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!I202:I217&lt;&gt;"")*('Picks Detail'!E202:E217&lt;&gt;"")*('Picks Detail'!I202:I217='Picks Detail'!E202:E217)*('Picks Detail'!V202:V217))</f>
+        <f>SUMPRODUCT(('Picks Detail'!I202:I217&lt;&gt;"")*('Picks Detail'!E202:E217&lt;&gt;"")*((('Picks Detail'!I202:I217='Picks Detail'!E202:E217)+('Picks Detail'!E202:E217="PUSH"))&gt;0)*('Picks Detail'!V202:V217))</f>
         <v>0</v>
       </c>
       <c r="D84">
@@ -36847,7 +36847,7 @@
         <v>Mikayla Simmons</v>
       </c>
       <c r="C85" s="3">
-        <f>SUMPRODUCT(('Picks Detail'!J202:J217&lt;&gt;"")*('Picks Detail'!E202:E217&lt;&gt;"")*('Picks Detail'!J202:J217='Picks Detail'!E202:E217)*('Picks Detail'!W202:W217))</f>
+        <f>SUMPRODUCT(('Picks Detail'!J202:J217&lt;&gt;"")*('Picks Detail'!E202:E217&lt;&gt;"")*((('Picks Detail'!J202:J217='Picks Detail'!E202:E217)+('Picks Detail'!E202:E217="PUSH"))&gt;0)*('Picks Detail'!W202:W217))</f>
         <v>0</v>
       </c>
       <c r="D85">
@@ -36883,7 +36883,7 @@
         <v>Alan Loeser</v>
       </c>
       <c r="C86" 